--- a/HINDUJA_GROUP_Technical_Metrics.xlsx
+++ b/HINDUJA_GROUP_Technical_Metrics.xlsx
@@ -181,19 +181,19 @@
     <t>Curr Value</t>
   </si>
   <si>
-    <t>Near 52W High</t>
-  </si>
-  <si>
-    <t>-2.9% → -0.8%</t>
-  </si>
-  <si>
-    <t>🟢 BREAKOUT WATCH</t>
-  </si>
-  <si>
-    <t>-2.9%</t>
+    <t>Left 52W High Zone</t>
+  </si>
+  <si>
+    <t>-0.8% → -2.2%</t>
+  </si>
+  <si>
+    <t>⚪ NEUTRAL</t>
   </si>
   <si>
     <t>-0.8%</t>
+  </si>
+  <si>
+    <t>-2.2%</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -245,7 +245,7 @@
     <numFmt numFmtId="166" formatCode="0.0"/>
     <numFmt numFmtId="167" formatCode="0.00%"/>
   </numFmts>
-  <fonts count="6">
+  <fonts count="7">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -279,7 +279,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FF1F4E79"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -291,8 +291,15 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="9">
+  <fills count="10">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -319,13 +326,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor rgb="FFDDEBF7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -406,11 +419,11 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="6" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
@@ -419,7 +432,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="167" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
@@ -778,8 +791,8 @@
     <col min="13" max="13" width="10.7109375" customWidth="1"/>
     <col min="14" max="14" width="11.7109375" customWidth="1"/>
     <col min="15" max="15" width="10.7109375" customWidth="1"/>
-    <col min="16" max="17" width="8.7109375" customWidth="1"/>
-    <col min="18" max="19" width="9.7109375" customWidth="1"/>
+    <col min="16" max="16" width="8.7109375" customWidth="1"/>
+    <col min="17" max="19" width="9.7109375" customWidth="1"/>
     <col min="20" max="20" width="22.7109375" customWidth="1"/>
     <col min="21" max="21" width="9.7109375" customWidth="1"/>
     <col min="22" max="22" width="10.7109375" customWidth="1"/>
@@ -918,10 +931,10 @@
         <v>42</v>
       </c>
       <c r="C2">
-        <v>163.75</v>
+        <v>156.65</v>
       </c>
       <c r="D2">
-        <v>-1.43</v>
+        <v>-4.34</v>
       </c>
       <c r="E2">
         <v>208.37</v>
@@ -930,46 +943,46 @@
         <v>130.44</v>
       </c>
       <c r="G2">
-        <v>-21.41</v>
+        <v>-24.82</v>
       </c>
       <c r="H2">
-        <v>25.54</v>
+        <v>20.09</v>
       </c>
       <c r="I2">
-        <v>-3.11</v>
+        <v>-7.85</v>
       </c>
       <c r="J2">
-        <v>-7.08</v>
+        <v>-8.73</v>
       </c>
       <c r="K2">
-        <v>3.84</v>
+        <v>-1.17</v>
       </c>
       <c r="L2">
-        <v>24.15</v>
+        <v>19.7</v>
       </c>
       <c r="M2">
-        <v>24.11</v>
+        <v>22</v>
       </c>
       <c r="N2">
         <v>60</v>
       </c>
       <c r="O2">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="P2">
-        <v>167.17</v>
+        <v>164.5</v>
       </c>
       <c r="Q2">
-        <v>172.09</v>
+        <v>171.07</v>
       </c>
       <c r="R2">
-        <v>166.64</v>
+        <v>166.45</v>
       </c>
       <c r="S2">
-        <v>169.81</v>
+        <v>169.86</v>
       </c>
       <c r="T2">
-        <v>-3.57</v>
+        <v>-7.78</v>
       </c>
       <c r="U2" t="s">
         <v>43</v>
@@ -984,43 +997,43 @@
         <v>1</v>
       </c>
       <c r="Y2">
-        <v>38.17</v>
+        <v>29.72</v>
       </c>
       <c r="Z2">
-        <v>-0.67</v>
+        <v>-1.61</v>
       </c>
       <c r="AA2">
-        <v>0.84</v>
+        <v>0.35</v>
       </c>
       <c r="AB2">
-        <v>-1.51</v>
+        <v>-1.96</v>
       </c>
       <c r="AC2">
         <v>0</v>
       </c>
       <c r="AD2">
-        <v>4.48</v>
+        <v>1.17</v>
       </c>
       <c r="AE2">
-        <v>4.19</v>
+        <v>4.51</v>
       </c>
       <c r="AF2">
-        <v>27.15</v>
+        <v>23.23</v>
       </c>
       <c r="AG2">
-        <v>180.57</v>
+        <v>181.67</v>
       </c>
       <c r="AH2">
-        <v>163.62</v>
+        <v>160.47</v>
       </c>
       <c r="AI2">
-        <v>175.08</v>
+        <v>174.54</v>
       </c>
       <c r="AJ2" t="s">
         <v>45</v>
       </c>
       <c r="AK2">
-        <v>24.02</v>
+        <v>28.67</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1031,10 +1044,10 @@
         <v>42</v>
       </c>
       <c r="C3">
-        <v>441.55</v>
+        <v>435.65</v>
       </c>
       <c r="D3">
-        <v>2.16</v>
+        <v>-1.34</v>
       </c>
       <c r="E3">
         <v>445.3</v>
@@ -1043,46 +1056,46 @@
         <v>225</v>
       </c>
       <c r="G3">
-        <v>-0.84</v>
+        <v>-2.17</v>
       </c>
       <c r="H3">
-        <v>96.23999999999999</v>
+        <v>93.62</v>
       </c>
       <c r="I3">
-        <v>3.3</v>
+        <v>-0.3</v>
       </c>
       <c r="J3">
-        <v>2.47</v>
+        <v>9.710000000000001</v>
       </c>
       <c r="K3">
-        <v>9.09</v>
+        <v>8.32</v>
       </c>
       <c r="L3">
-        <v>22.26</v>
+        <v>22.2</v>
       </c>
       <c r="M3">
-        <v>12.56</v>
+        <v>11.1</v>
       </c>
       <c r="N3">
-        <v>79</v>
+        <v>99</v>
       </c>
       <c r="O3">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="P3">
-        <v>435.6</v>
+        <v>435.34</v>
       </c>
       <c r="Q3">
-        <v>409.21</v>
+        <v>410.59</v>
       </c>
       <c r="R3">
-        <v>407.3</v>
+        <v>407.93</v>
       </c>
       <c r="S3">
-        <v>331.27</v>
+        <v>331.92</v>
       </c>
       <c r="T3">
-        <v>33.29</v>
+        <v>31.25</v>
       </c>
       <c r="U3" t="s">
         <v>43</v>
@@ -1097,43 +1110,43 @@
         <v>3</v>
       </c>
       <c r="Y3">
-        <v>66.45</v>
+        <v>62.1</v>
       </c>
       <c r="Z3">
-        <v>8.130000000000001</v>
+        <v>8.59</v>
       </c>
       <c r="AA3">
-        <v>3.77</v>
+        <v>4.73</v>
       </c>
       <c r="AB3">
-        <v>4.36</v>
+        <v>3.86</v>
       </c>
       <c r="AC3">
-        <v>90.95</v>
+        <v>90.11</v>
       </c>
       <c r="AD3">
-        <v>91.62</v>
+        <v>90.27</v>
       </c>
       <c r="AE3">
-        <v>14.25</v>
+        <v>14.38</v>
       </c>
       <c r="AF3">
-        <v>-43.68</v>
+        <v>-43.2</v>
       </c>
       <c r="AG3">
-        <v>446.24</v>
+        <v>449.46</v>
       </c>
       <c r="AH3">
-        <v>372.17</v>
+        <v>371.72</v>
       </c>
       <c r="AI3">
-        <v>393.69</v>
+        <v>396.9</v>
       </c>
       <c r="AJ3" t="s">
         <v>46</v>
       </c>
       <c r="AK3">
-        <v>49.32</v>
+        <v>51.3</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1144,10 +1157,10 @@
         <v>42</v>
       </c>
       <c r="C4">
-        <v>381.45</v>
+        <v>381.6</v>
       </c>
       <c r="D4">
-        <v>-0.63</v>
+        <v>0.04</v>
       </c>
       <c r="E4">
         <v>534</v>
@@ -1156,46 +1169,46 @@
         <v>344.7</v>
       </c>
       <c r="G4">
-        <v>-28.57</v>
+        <v>-28.54</v>
       </c>
       <c r="H4">
-        <v>10.66</v>
+        <v>10.7</v>
       </c>
       <c r="I4">
-        <v>-4.46</v>
+        <v>-3.53</v>
       </c>
       <c r="J4">
-        <v>-5.74</v>
+        <v>-6.62</v>
       </c>
       <c r="K4">
-        <v>-11</v>
+        <v>-11.11</v>
       </c>
       <c r="L4">
-        <v>-27.33</v>
+        <v>-27.45</v>
       </c>
       <c r="M4">
-        <v>-22.21</v>
+        <v>-22.09</v>
       </c>
       <c r="N4">
         <v>21</v>
       </c>
       <c r="O4">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="P4">
-        <v>386.71</v>
+        <v>383.92</v>
       </c>
       <c r="Q4">
-        <v>398.01</v>
+        <v>396.44</v>
       </c>
       <c r="R4">
-        <v>412.4</v>
+        <v>411.82</v>
       </c>
       <c r="S4">
-        <v>413.05</v>
+        <v>412.55</v>
       </c>
       <c r="T4">
-        <v>-7.65</v>
+        <v>-7.5</v>
       </c>
       <c r="U4" t="s">
         <v>44</v>
@@ -1210,34 +1223,34 @@
         <v>0</v>
       </c>
       <c r="Y4">
-        <v>27.5</v>
+        <v>27.76</v>
       </c>
       <c r="Z4">
-        <v>-7.88</v>
+        <v>-8.119999999999999</v>
       </c>
       <c r="AA4">
-        <v>-6.65</v>
+        <v>-6.95</v>
       </c>
       <c r="AB4">
-        <v>-1.23</v>
+        <v>-1.18</v>
       </c>
       <c r="AC4">
-        <v>0</v>
+        <v>0.64</v>
       </c>
       <c r="AD4">
-        <v>7.77</v>
+        <v>0.84</v>
       </c>
       <c r="AE4">
-        <v>10.89</v>
+        <v>10.93</v>
       </c>
       <c r="AF4">
-        <v>-40.08</v>
+        <v>-43.9</v>
       </c>
       <c r="AG4">
-        <v>415.27</v>
+        <v>413.66</v>
       </c>
       <c r="AH4">
-        <v>380.76</v>
+        <v>379.23</v>
       </c>
       <c r="AI4">
         <v>413.11</v>
@@ -1246,7 +1259,7 @@
         <v>45</v>
       </c>
       <c r="AK4">
-        <v>23.49</v>
+        <v>21.57</v>
       </c>
     </row>
     <row r="5" spans="1:37">
@@ -1257,10 +1270,10 @@
         <v>42</v>
       </c>
       <c r="C5">
-        <v>978.2</v>
+        <v>956.5</v>
       </c>
       <c r="D5">
-        <v>-1.52</v>
+        <v>-2.22</v>
       </c>
       <c r="E5">
         <v>1069.3</v>
@@ -1269,46 +1282,46 @@
         <v>712.75</v>
       </c>
       <c r="G5">
-        <v>-8.52</v>
+        <v>-10.55</v>
       </c>
       <c r="H5">
-        <v>37.24</v>
+        <v>34.2</v>
       </c>
       <c r="I5">
-        <v>-3</v>
+        <v>-4.16</v>
       </c>
       <c r="J5">
-        <v>-4.54</v>
+        <v>-6.3</v>
       </c>
       <c r="K5">
-        <v>4.82</v>
+        <v>3.29</v>
       </c>
       <c r="L5">
-        <v>31.1</v>
+        <v>27.32</v>
       </c>
       <c r="M5">
-        <v>0.23</v>
+        <v>-1.33</v>
       </c>
       <c r="N5">
-        <v>99</v>
+        <v>79</v>
       </c>
       <c r="O5">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="P5">
-        <v>994.24</v>
+        <v>985.9400000000001</v>
       </c>
       <c r="Q5">
-        <v>1003.6</v>
+        <v>1000.39</v>
       </c>
       <c r="R5">
-        <v>1012.07</v>
+        <v>1011.01</v>
       </c>
       <c r="S5">
-        <v>918.71</v>
+        <v>919.24</v>
       </c>
       <c r="T5">
-        <v>6.48</v>
+        <v>4.05</v>
       </c>
       <c r="U5" t="s">
         <v>44</v>
@@ -1323,43 +1336,43 @@
         <v>2</v>
       </c>
       <c r="Y5">
-        <v>41.24</v>
+        <v>35.57</v>
       </c>
       <c r="Z5">
-        <v>-4.46</v>
+        <v>-7.41</v>
       </c>
       <c r="AA5">
-        <v>-2.02</v>
+        <v>-3.1</v>
       </c>
       <c r="AB5">
-        <v>-2.44</v>
+        <v>-4.31</v>
       </c>
       <c r="AC5">
-        <v>42.17</v>
+        <v>18.11</v>
       </c>
       <c r="AD5">
-        <v>53.4</v>
+        <v>39.15</v>
       </c>
       <c r="AE5">
-        <v>20.03</v>
+        <v>20.71</v>
       </c>
       <c r="AF5">
-        <v>110.42</v>
+        <v>18.32</v>
       </c>
       <c r="AG5">
-        <v>1028.1</v>
+        <v>1031.4</v>
       </c>
       <c r="AH5">
-        <v>979.11</v>
+        <v>969.38</v>
       </c>
       <c r="AI5">
-        <v>1038.34</v>
+        <v>1031.88</v>
       </c>
       <c r="AJ5" t="s">
         <v>45</v>
       </c>
       <c r="AK5">
-        <v>13.19</v>
+        <v>16.68</v>
       </c>
     </row>
     <row r="6" spans="1:37">
@@ -1370,10 +1383,10 @@
         <v>42</v>
       </c>
       <c r="C6">
-        <v>2.86</v>
+        <v>2.75</v>
       </c>
       <c r="D6">
-        <v>-1.38</v>
+        <v>-3.85</v>
       </c>
       <c r="E6">
         <v>3.62</v>
@@ -1382,46 +1395,46 @@
         <v>1.84</v>
       </c>
       <c r="G6">
-        <v>-20.99</v>
+        <v>-24.03</v>
       </c>
       <c r="H6">
-        <v>55.43</v>
+        <v>49.46</v>
       </c>
       <c r="I6">
-        <v>1.06</v>
+        <v>-7.72</v>
       </c>
       <c r="J6">
-        <v>21.19</v>
+        <v>18.53</v>
       </c>
       <c r="K6">
-        <v>9.58</v>
+        <v>6.18</v>
       </c>
       <c r="L6">
-        <v>-18.52</v>
+        <v>-24.03</v>
       </c>
       <c r="M6">
-        <v>2.16</v>
+        <v>1.44</v>
       </c>
       <c r="N6">
         <v>40</v>
       </c>
       <c r="O6">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="P6">
-        <v>2.92</v>
+        <v>2.87</v>
       </c>
       <c r="Q6">
-        <v>2.78</v>
+        <v>2.81</v>
       </c>
       <c r="R6">
-        <v>2.52</v>
+        <v>2.53</v>
       </c>
       <c r="S6">
         <v>2.68</v>
       </c>
       <c r="T6">
-        <v>6.78</v>
+        <v>2.74</v>
       </c>
       <c r="U6" t="s">
         <v>43</v>
@@ -1436,34 +1449,34 @@
         <v>2</v>
       </c>
       <c r="Y6">
-        <v>58.4</v>
+        <v>50.98</v>
       </c>
       <c r="Z6">
+        <v>0.1</v>
+      </c>
+      <c r="AA6">
         <v>0.12</v>
       </c>
-      <c r="AA6">
-        <v>0.13</v>
-      </c>
       <c r="AB6">
-        <v>-0.01</v>
+        <v>-0.02</v>
       </c>
       <c r="AC6">
-        <v>3.37</v>
+        <v>0</v>
       </c>
       <c r="AD6">
-        <v>23.49</v>
+        <v>8.56</v>
       </c>
       <c r="AE6">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="AF6">
-        <v>-71.44</v>
+        <v>-56.82</v>
       </c>
       <c r="AG6">
-        <v>3.34</v>
+        <v>3.31</v>
       </c>
       <c r="AH6">
-        <v>2.23</v>
+        <v>2.3</v>
       </c>
       <c r="AI6">
         <v>2.65</v>
@@ -1472,7 +1485,7 @@
         <v>46</v>
       </c>
       <c r="AK6">
-        <v>40.28</v>
+        <v>37.93</v>
       </c>
     </row>
   </sheetData>
@@ -1705,13 +1718,13 @@
         <v>9</v>
       </c>
       <c r="C7" s="6">
-        <v>-5.99</v>
+        <v>-7.08</v>
       </c>
       <c r="D7" s="6">
-        <v>-7.08</v>
+        <v>-8.73</v>
       </c>
       <c r="E7" s="7">
-        <v>-1.09</v>
+        <v>-1.65</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -1722,13 +1735,13 @@
         <v>9</v>
       </c>
       <c r="C8" s="6">
-        <v>0.09</v>
+        <v>2.47</v>
       </c>
       <c r="D8" s="6">
-        <v>2.47</v>
+        <v>9.710000000000001</v>
       </c>
       <c r="E8" s="8">
-        <v>2.38</v>
+        <v>7.24</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -1739,13 +1752,13 @@
         <v>9</v>
       </c>
       <c r="C9" s="6">
-        <v>-5.63</v>
+        <v>-5.74</v>
       </c>
       <c r="D9" s="6">
-        <v>-5.74</v>
+        <v>-6.62</v>
       </c>
       <c r="E9" s="7">
-        <v>-0.11</v>
+        <v>-0.88</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -1756,13 +1769,13 @@
         <v>9</v>
       </c>
       <c r="C10" s="6">
-        <v>-2.38</v>
+        <v>-4.54</v>
       </c>
       <c r="D10" s="6">
-        <v>-4.54</v>
+        <v>-6.3</v>
       </c>
       <c r="E10" s="7">
-        <v>-2.16</v>
+        <v>-1.76</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -1773,13 +1786,13 @@
         <v>9</v>
       </c>
       <c r="C11" s="6">
-        <v>23.93</v>
+        <v>21.19</v>
       </c>
       <c r="D11" s="6">
-        <v>21.19</v>
+        <v>18.53</v>
       </c>
       <c r="E11" s="7">
-        <v>-2.74</v>
+        <v>-2.66</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -1790,13 +1803,13 @@
         <v>8</v>
       </c>
       <c r="C12" s="6">
-        <v>-1.91</v>
+        <v>-3.11</v>
       </c>
       <c r="D12" s="6">
-        <v>-3.11</v>
+        <v>-7.85</v>
       </c>
       <c r="E12" s="7">
-        <v>-1.2</v>
+        <v>-4.74</v>
       </c>
     </row>
     <row r="13" spans="1:6">
@@ -1807,13 +1820,13 @@
         <v>8</v>
       </c>
       <c r="C13" s="6">
-        <v>2.19</v>
+        <v>3.3</v>
       </c>
       <c r="D13" s="6">
-        <v>3.3</v>
-      </c>
-      <c r="E13" s="8">
-        <v>1.11</v>
+        <v>-0.3</v>
+      </c>
+      <c r="E13" s="7">
+        <v>-3.6</v>
       </c>
     </row>
     <row r="14" spans="1:6">
@@ -1824,13 +1837,13 @@
         <v>8</v>
       </c>
       <c r="C14" s="6">
-        <v>-2.33</v>
+        <v>-4.46</v>
       </c>
       <c r="D14" s="6">
-        <v>-4.46</v>
-      </c>
-      <c r="E14" s="7">
-        <v>-2.13</v>
+        <v>-3.53</v>
+      </c>
+      <c r="E14" s="8">
+        <v>0.93</v>
       </c>
     </row>
     <row r="15" spans="1:6">
@@ -1841,13 +1854,13 @@
         <v>8</v>
       </c>
       <c r="C15" s="6">
-        <v>-1.14</v>
+        <v>-3</v>
       </c>
       <c r="D15" s="6">
-        <v>-3</v>
+        <v>-4.16</v>
       </c>
       <c r="E15" s="7">
-        <v>-1.86</v>
+        <v>-1.16</v>
       </c>
     </row>
     <row r="16" spans="1:6">
@@ -1858,13 +1871,13 @@
         <v>8</v>
       </c>
       <c r="C16" s="6">
-        <v>2.47</v>
+        <v>1.06</v>
       </c>
       <c r="D16" s="6">
-        <v>1.06</v>
+        <v>-7.72</v>
       </c>
       <c r="E16" s="7">
-        <v>-1.41</v>
+        <v>-8.779999999999999</v>
       </c>
     </row>
     <row r="17" spans="1:5">
@@ -1875,13 +1888,13 @@
         <v>11</v>
       </c>
       <c r="C17" s="6">
-        <v>23.9</v>
+        <v>24.15</v>
       </c>
       <c r="D17" s="6">
-        <v>24.15</v>
-      </c>
-      <c r="E17" s="8">
-        <v>0.25</v>
+        <v>19.7</v>
+      </c>
+      <c r="E17" s="7">
+        <v>-4.45</v>
       </c>
     </row>
     <row r="18" spans="1:5">
@@ -1892,13 +1905,13 @@
         <v>11</v>
       </c>
       <c r="C18" s="6">
-        <v>20.09</v>
+        <v>22.26</v>
       </c>
       <c r="D18" s="6">
-        <v>22.26</v>
-      </c>
-      <c r="E18" s="8">
-        <v>2.17</v>
+        <v>22.2</v>
+      </c>
+      <c r="E18" s="7">
+        <v>-0.06</v>
       </c>
     </row>
     <row r="19" spans="1:5">
@@ -1909,13 +1922,13 @@
         <v>11</v>
       </c>
       <c r="C19" s="6">
-        <v>-26.73</v>
+        <v>-27.33</v>
       </c>
       <c r="D19" s="6">
-        <v>-27.33</v>
+        <v>-27.45</v>
       </c>
       <c r="E19" s="7">
-        <v>-0.6</v>
+        <v>-0.12</v>
       </c>
     </row>
     <row r="20" spans="1:5">
@@ -1926,13 +1939,13 @@
         <v>11</v>
       </c>
       <c r="C20" s="6">
-        <v>32.31</v>
+        <v>31.1</v>
       </c>
       <c r="D20" s="6">
-        <v>31.1</v>
+        <v>27.32</v>
       </c>
       <c r="E20" s="7">
-        <v>-1.21</v>
+        <v>-3.78</v>
       </c>
     </row>
     <row r="21" spans="1:5">
@@ -1943,13 +1956,13 @@
         <v>11</v>
       </c>
       <c r="C21" s="6">
-        <v>-17.85</v>
+        <v>-18.52</v>
       </c>
       <c r="D21" s="6">
-        <v>-18.52</v>
+        <v>-24.03</v>
       </c>
       <c r="E21" s="7">
-        <v>-0.67</v>
+        <v>-5.51</v>
       </c>
     </row>
     <row r="22" spans="1:5">
@@ -1960,13 +1973,13 @@
         <v>10</v>
       </c>
       <c r="C22" s="6">
-        <v>8.970000000000001</v>
+        <v>3.84</v>
       </c>
       <c r="D22" s="6">
-        <v>3.84</v>
+        <v>-1.17</v>
       </c>
       <c r="E22" s="7">
-        <v>-5.13</v>
+        <v>-5.01</v>
       </c>
     </row>
     <row r="23" spans="1:5">
@@ -1977,13 +1990,13 @@
         <v>10</v>
       </c>
       <c r="C23" s="6">
-        <v>7.42</v>
+        <v>9.09</v>
       </c>
       <c r="D23" s="6">
-        <v>9.09</v>
-      </c>
-      <c r="E23" s="8">
-        <v>1.67</v>
+        <v>8.32</v>
+      </c>
+      <c r="E23" s="7">
+        <v>-0.77</v>
       </c>
     </row>
     <row r="24" spans="1:5">
@@ -1994,13 +2007,13 @@
         <v>10</v>
       </c>
       <c r="C24" s="6">
-        <v>-10.23</v>
+        <v>-11</v>
       </c>
       <c r="D24" s="6">
-        <v>-11</v>
+        <v>-11.11</v>
       </c>
       <c r="E24" s="7">
-        <v>-0.77</v>
+        <v>-0.11</v>
       </c>
     </row>
     <row r="25" spans="1:5">
@@ -2011,13 +2024,13 @@
         <v>10</v>
       </c>
       <c r="C25" s="6">
-        <v>8.279999999999999</v>
+        <v>4.82</v>
       </c>
       <c r="D25" s="6">
-        <v>4.82</v>
+        <v>3.29</v>
       </c>
       <c r="E25" s="7">
-        <v>-3.46</v>
+        <v>-1.53</v>
       </c>
     </row>
     <row r="26" spans="1:5">
@@ -2028,13 +2041,13 @@
         <v>10</v>
       </c>
       <c r="C26" s="6">
-        <v>14.17</v>
+        <v>9.58</v>
       </c>
       <c r="D26" s="6">
-        <v>9.58</v>
+        <v>6.18</v>
       </c>
       <c r="E26" s="7">
-        <v>-4.59</v>
+        <v>-3.4</v>
       </c>
     </row>
     <row r="27" spans="1:5">
@@ -2045,13 +2058,13 @@
         <v>6</v>
       </c>
       <c r="C27" s="6">
-        <v>-20.28</v>
+        <v>-21.41</v>
       </c>
       <c r="D27" s="6">
-        <v>-21.41</v>
+        <v>-24.82</v>
       </c>
       <c r="E27" s="7">
-        <v>-1.13</v>
+        <v>-3.41</v>
       </c>
     </row>
     <row r="28" spans="1:5">
@@ -2062,13 +2075,13 @@
         <v>6</v>
       </c>
       <c r="C28" s="6">
-        <v>-2.94</v>
+        <v>-0.84</v>
       </c>
       <c r="D28" s="6">
-        <v>-0.84</v>
-      </c>
-      <c r="E28" s="8">
-        <v>2.1</v>
+        <v>-2.17</v>
+      </c>
+      <c r="E28" s="7">
+        <v>-1.33</v>
       </c>
     </row>
     <row r="29" spans="1:5">
@@ -2079,13 +2092,13 @@
         <v>6</v>
       </c>
       <c r="C29" s="6">
-        <v>-28.12</v>
+        <v>-28.57</v>
       </c>
       <c r="D29" s="6">
-        <v>-28.57</v>
-      </c>
-      <c r="E29" s="7">
-        <v>-0.45</v>
+        <v>-28.54</v>
+      </c>
+      <c r="E29" s="8">
+        <v>0.03</v>
       </c>
     </row>
     <row r="30" spans="1:5">
@@ -2096,13 +2109,13 @@
         <v>6</v>
       </c>
       <c r="C30" s="6">
-        <v>-7.11</v>
+        <v>-8.52</v>
       </c>
       <c r="D30" s="6">
-        <v>-8.52</v>
+        <v>-10.55</v>
       </c>
       <c r="E30" s="7">
-        <v>-1.41</v>
+        <v>-2.03</v>
       </c>
     </row>
     <row r="31" spans="1:5">
@@ -2113,13 +2126,13 @@
         <v>6</v>
       </c>
       <c r="C31" s="6">
-        <v>-19.89</v>
+        <v>-20.99</v>
       </c>
       <c r="D31" s="6">
-        <v>-20.99</v>
+        <v>-24.03</v>
       </c>
       <c r="E31" s="7">
-        <v>-1.1</v>
+        <v>-3.04</v>
       </c>
     </row>
     <row r="32" spans="1:5">
@@ -2130,13 +2143,13 @@
         <v>2</v>
       </c>
       <c r="C32" s="6">
-        <v>166.12</v>
+        <v>163.75</v>
       </c>
       <c r="D32" s="6">
-        <v>163.75</v>
+        <v>156.65</v>
       </c>
       <c r="E32" s="7">
-        <v>-2.37</v>
+        <v>-7.1</v>
       </c>
     </row>
     <row r="33" spans="1:5">
@@ -2147,13 +2160,13 @@
         <v>2</v>
       </c>
       <c r="C33" s="6">
-        <v>432.2</v>
+        <v>441.55</v>
       </c>
       <c r="D33" s="6">
-        <v>441.55</v>
-      </c>
-      <c r="E33" s="8">
-        <v>9.35</v>
+        <v>435.65</v>
+      </c>
+      <c r="E33" s="7">
+        <v>-5.9</v>
       </c>
     </row>
     <row r="34" spans="1:5">
@@ -2164,13 +2177,13 @@
         <v>2</v>
       </c>
       <c r="C34" s="6">
-        <v>383.85</v>
+        <v>381.45</v>
       </c>
       <c r="D34" s="6">
-        <v>381.45</v>
-      </c>
-      <c r="E34" s="7">
-        <v>-2.4</v>
+        <v>381.6</v>
+      </c>
+      <c r="E34" s="8">
+        <v>0.15</v>
       </c>
     </row>
     <row r="35" spans="1:5">
@@ -2181,13 +2194,13 @@
         <v>2</v>
       </c>
       <c r="C35" s="6">
-        <v>993.3</v>
+        <v>978.2</v>
       </c>
       <c r="D35" s="6">
-        <v>978.2</v>
+        <v>956.5</v>
       </c>
       <c r="E35" s="7">
-        <v>-15.1</v>
+        <v>-21.7</v>
       </c>
     </row>
     <row r="36" spans="1:5">
@@ -2198,18 +2211,18 @@
         <v>2</v>
       </c>
       <c r="C36" s="6">
-        <v>2.9</v>
+        <v>2.86</v>
       </c>
       <c r="D36" s="6">
-        <v>2.86</v>
+        <v>2.75</v>
       </c>
       <c r="E36" s="7">
-        <v>-0.04</v>
+        <v>-0.11</v>
       </c>
     </row>
     <row r="37" spans="1:5">
       <c r="A37" s="5" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B37" s="5" t="s">
         <v>13</v>
@@ -2218,27 +2231,27 @@
         <v>79</v>
       </c>
       <c r="D37" s="6">
-        <v>60</v>
-      </c>
-      <c r="E37" s="7">
-        <v>-19</v>
+        <v>99</v>
+      </c>
+      <c r="E37" s="8">
+        <v>20</v>
       </c>
     </row>
     <row r="38" spans="1:5">
       <c r="A38" s="5" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B38" s="5" t="s">
         <v>13</v>
       </c>
       <c r="C38" s="6">
-        <v>60</v>
+        <v>99</v>
       </c>
       <c r="D38" s="6">
         <v>79</v>
       </c>
-      <c r="E38" s="8">
-        <v>19</v>
+      <c r="E38" s="7">
+        <v>-20</v>
       </c>
     </row>
     <row r="39" spans="1:5">
@@ -2249,13 +2262,13 @@
         <v>24</v>
       </c>
       <c r="C39" s="6">
-        <v>41.86</v>
+        <v>38.17</v>
       </c>
       <c r="D39" s="6">
-        <v>38.17</v>
+        <v>29.72</v>
       </c>
       <c r="E39" s="7">
-        <v>-3.69</v>
+        <v>-8.449999999999999</v>
       </c>
     </row>
     <row r="40" spans="1:5">
@@ -2266,13 +2279,13 @@
         <v>24</v>
       </c>
       <c r="C40" s="6">
-        <v>62.59</v>
+        <v>66.45</v>
       </c>
       <c r="D40" s="6">
-        <v>66.45</v>
-      </c>
-      <c r="E40" s="8">
-        <v>3.86</v>
+        <v>62.1</v>
+      </c>
+      <c r="E40" s="7">
+        <v>-4.35</v>
       </c>
     </row>
     <row r="41" spans="1:5">
@@ -2283,13 +2296,13 @@
         <v>24</v>
       </c>
       <c r="C41" s="6">
-        <v>29.05</v>
+        <v>27.5</v>
       </c>
       <c r="D41" s="6">
-        <v>27.5</v>
-      </c>
-      <c r="E41" s="7">
-        <v>-1.55</v>
+        <v>27.76</v>
+      </c>
+      <c r="E41" s="8">
+        <v>0.26</v>
       </c>
     </row>
     <row r="42" spans="1:5">
@@ -2300,13 +2313,13 @@
         <v>24</v>
       </c>
       <c r="C42" s="6">
-        <v>45.97</v>
+        <v>41.24</v>
       </c>
       <c r="D42" s="6">
-        <v>41.24</v>
+        <v>35.57</v>
       </c>
       <c r="E42" s="7">
-        <v>-4.73</v>
+        <v>-5.67</v>
       </c>
     </row>
     <row r="43" spans="1:5">
@@ -2317,13 +2330,13 @@
         <v>24</v>
       </c>
       <c r="C43" s="6">
-        <v>61.42</v>
+        <v>58.4</v>
       </c>
       <c r="D43" s="6">
-        <v>58.4</v>
+        <v>50.98</v>
       </c>
       <c r="E43" s="7">
-        <v>-3.02</v>
+        <v>-7.42</v>
       </c>
     </row>
     <row r="44" spans="1:5">
@@ -2334,13 +2347,13 @@
         <v>31</v>
       </c>
       <c r="C44" s="6">
-        <v>10.25</v>
+        <v>27.15</v>
       </c>
       <c r="D44" s="6">
-        <v>27.15</v>
-      </c>
-      <c r="E44" s="8">
-        <v>16.9</v>
+        <v>23.23</v>
+      </c>
+      <c r="E44" s="7">
+        <v>-3.92</v>
       </c>
     </row>
     <row r="45" spans="1:5">
@@ -2351,13 +2364,13 @@
         <v>31</v>
       </c>
       <c r="C45" s="6">
-        <v>-77.45</v>
+        <v>-43.68</v>
       </c>
       <c r="D45" s="6">
-        <v>-43.68</v>
+        <v>-43.2</v>
       </c>
       <c r="E45" s="8">
-        <v>33.77</v>
+        <v>0.48</v>
       </c>
     </row>
     <row r="46" spans="1:5">
@@ -2368,13 +2381,13 @@
         <v>31</v>
       </c>
       <c r="C46" s="6">
-        <v>-63.08</v>
+        <v>-40.08</v>
       </c>
       <c r="D46" s="6">
-        <v>-40.08</v>
-      </c>
-      <c r="E46" s="8">
-        <v>23</v>
+        <v>-43.9</v>
+      </c>
+      <c r="E46" s="7">
+        <v>-3.82</v>
       </c>
     </row>
     <row r="47" spans="1:5">
@@ -2385,13 +2398,13 @@
         <v>31</v>
       </c>
       <c r="C47" s="6">
-        <v>-18.1</v>
+        <v>110.42</v>
       </c>
       <c r="D47" s="6">
-        <v>110.42</v>
-      </c>
-      <c r="E47" s="8">
-        <v>128.52</v>
+        <v>18.32</v>
+      </c>
+      <c r="E47" s="7">
+        <v>-92.09999999999999</v>
       </c>
     </row>
     <row r="48" spans="1:5">
@@ -2402,13 +2415,13 @@
         <v>31</v>
       </c>
       <c r="C48" s="6">
-        <v>-65.18000000000001</v>
+        <v>-71.44</v>
       </c>
       <c r="D48" s="6">
-        <v>-71.44</v>
-      </c>
-      <c r="E48" s="7">
-        <v>-6.26</v>
+        <v>-56.82</v>
+      </c>
+      <c r="E48" s="8">
+        <v>14.62</v>
       </c>
     </row>
   </sheetData>
@@ -2473,7 +2486,7 @@
         <v>5</v>
       </c>
       <c r="D2" s="11">
-        <v>46.4</v>
+        <v>41.2</v>
       </c>
       <c r="E2" s="11">
         <v>60</v>
@@ -2482,7 +2495,7 @@
         <v>1.3</v>
       </c>
       <c r="G2" s="11">
-        <v>3.3</v>
+        <v>1.1</v>
       </c>
       <c r="H2" s="11">
         <v>59.8</v>
@@ -2607,19 +2620,19 @@
     </row>
     <row r="2" spans="1:5">
       <c r="A2" s="14">
-        <v>0.2411</v>
+        <v>0.22</v>
       </c>
       <c r="B2" s="14">
-        <v>0.1256</v>
+        <v>0.111</v>
       </c>
       <c r="C2" s="14">
-        <v>0.0216</v>
+        <v>0.0144</v>
       </c>
       <c r="D2" s="14">
-        <v>0.0023</v>
+        <v>-0.0133</v>
       </c>
       <c r="E2" s="14">
-        <v>-0.2221</v>
+        <v>-0.2209</v>
       </c>
     </row>
   </sheetData>

--- a/HINDUJA_GROUP_Technical_Metrics.xlsx
+++ b/HINDUJA_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="222" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="218" uniqueCount="71">
   <si>
     <t>Symbol</t>
   </si>
@@ -181,19 +181,19 @@
     <t>Curr Value</t>
   </si>
   <si>
-    <t>Left 52W High Zone</t>
-  </si>
-  <si>
-    <t>-0.8% → -2.2%</t>
-  </si>
-  <si>
-    <t>⚪ NEUTRAL</t>
-  </si>
-  <si>
-    <t>-0.8%</t>
-  </si>
-  <si>
-    <t>-2.2%</t>
+    <t>RSI Oversold Recovery</t>
+  </si>
+  <si>
+    <t>27.8 → 35.2</t>
+  </si>
+  <si>
+    <t>🟢 BULLISH</t>
+  </si>
+  <si>
+    <t>27.8</t>
+  </si>
+  <si>
+    <t>35.2</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -245,7 +245,7 @@
     <numFmt numFmtId="166" formatCode="0.0"/>
     <numFmt numFmtId="167" formatCode="0.00%"/>
   </numFmts>
-  <fonts count="7">
+  <fonts count="6">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -279,7 +279,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF1F4E79"/>
+      <color rgb="FF006100"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -291,15 +291,8 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
-  <fills count="10">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -326,19 +319,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFDDEBF7"/>
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -419,11 +406,11 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="6" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
@@ -432,7 +419,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="167" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
@@ -791,14 +778,15 @@
     <col min="13" max="13" width="10.7109375" customWidth="1"/>
     <col min="14" max="14" width="11.7109375" customWidth="1"/>
     <col min="15" max="15" width="10.7109375" customWidth="1"/>
-    <col min="16" max="16" width="8.7109375" customWidth="1"/>
-    <col min="17" max="19" width="9.7109375" customWidth="1"/>
+    <col min="16" max="17" width="8.7109375" customWidth="1"/>
+    <col min="18" max="19" width="9.7109375" customWidth="1"/>
     <col min="20" max="20" width="22.7109375" customWidth="1"/>
     <col min="21" max="21" width="9.7109375" customWidth="1"/>
     <col min="22" max="22" width="10.7109375" customWidth="1"/>
     <col min="23" max="23" width="16.7109375" customWidth="1"/>
     <col min="24" max="24" width="13.7109375" customWidth="1"/>
-    <col min="25" max="26" width="7.7109375" customWidth="1"/>
+    <col min="25" max="25" width="7.7109375" customWidth="1"/>
+    <col min="26" max="26" width="8.7109375" customWidth="1"/>
     <col min="27" max="27" width="13.7109375" customWidth="1"/>
     <col min="28" max="28" width="11.7109375" customWidth="1"/>
     <col min="29" max="30" width="13.7109375" customWidth="1"/>
@@ -931,58 +919,58 @@
         <v>42</v>
       </c>
       <c r="C2">
-        <v>156.65</v>
+        <v>156.5</v>
       </c>
       <c r="D2">
-        <v>-4.34</v>
+        <v>-0.1</v>
       </c>
       <c r="E2">
         <v>208.37</v>
       </c>
       <c r="F2">
-        <v>130.44</v>
+        <v>130.81</v>
       </c>
       <c r="G2">
-        <v>-24.82</v>
+        <v>-24.89</v>
       </c>
       <c r="H2">
-        <v>20.09</v>
+        <v>19.64</v>
       </c>
       <c r="I2">
-        <v>-7.85</v>
+        <v>-7.4</v>
       </c>
       <c r="J2">
-        <v>-8.73</v>
+        <v>-11.63</v>
       </c>
       <c r="K2">
-        <v>-1.17</v>
+        <v>-1.92</v>
       </c>
       <c r="L2">
-        <v>19.7</v>
+        <v>19.98</v>
       </c>
       <c r="M2">
-        <v>22</v>
+        <v>22.18</v>
       </c>
       <c r="N2">
         <v>60</v>
       </c>
       <c r="O2">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="P2">
-        <v>164.5</v>
+        <v>162</v>
       </c>
       <c r="Q2">
-        <v>171.07</v>
+        <v>170.08</v>
       </c>
       <c r="R2">
-        <v>166.45</v>
+        <v>166.29</v>
       </c>
       <c r="S2">
         <v>169.86</v>
       </c>
       <c r="T2">
-        <v>-7.78</v>
+        <v>-7.86</v>
       </c>
       <c r="U2" t="s">
         <v>43</v>
@@ -997,43 +985,43 @@
         <v>1</v>
       </c>
       <c r="Y2">
-        <v>29.72</v>
+        <v>29.57</v>
       </c>
       <c r="Z2">
-        <v>-1.61</v>
+        <v>-2.34</v>
       </c>
       <c r="AA2">
-        <v>0.35</v>
+        <v>-0.19</v>
       </c>
       <c r="AB2">
-        <v>-1.96</v>
+        <v>-2.15</v>
       </c>
       <c r="AC2">
         <v>0</v>
       </c>
       <c r="AD2">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AE2">
-        <v>4.51</v>
+        <v>4.44</v>
       </c>
       <c r="AF2">
-        <v>23.23</v>
+        <v>-23.7</v>
       </c>
       <c r="AG2">
-        <v>181.67</v>
+        <v>182.2</v>
       </c>
       <c r="AH2">
-        <v>160.47</v>
+        <v>157.95</v>
       </c>
       <c r="AI2">
-        <v>174.54</v>
+        <v>169.79</v>
       </c>
       <c r="AJ2" t="s">
         <v>45</v>
       </c>
       <c r="AK2">
-        <v>28.67</v>
+        <v>33.3</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1044,10 +1032,10 @@
         <v>42</v>
       </c>
       <c r="C3">
-        <v>435.65</v>
+        <v>428.4</v>
       </c>
       <c r="D3">
-        <v>-1.34</v>
+        <v>-1.66</v>
       </c>
       <c r="E3">
         <v>445.3</v>
@@ -1056,46 +1044,46 @@
         <v>225</v>
       </c>
       <c r="G3">
-        <v>-2.17</v>
+        <v>-3.8</v>
       </c>
       <c r="H3">
-        <v>93.62</v>
+        <v>90.40000000000001</v>
       </c>
       <c r="I3">
-        <v>-0.3</v>
+        <v>-1.65</v>
       </c>
       <c r="J3">
-        <v>9.710000000000001</v>
+        <v>5</v>
       </c>
       <c r="K3">
-        <v>8.32</v>
+        <v>6.22</v>
       </c>
       <c r="L3">
-        <v>22.2</v>
+        <v>20.25</v>
       </c>
       <c r="M3">
-        <v>11.1</v>
+        <v>11.56</v>
       </c>
       <c r="N3">
         <v>99</v>
       </c>
       <c r="O3">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="P3">
-        <v>435.34</v>
+        <v>433.9</v>
       </c>
       <c r="Q3">
-        <v>410.59</v>
+        <v>411.93</v>
       </c>
       <c r="R3">
-        <v>407.93</v>
+        <v>408.4</v>
       </c>
       <c r="S3">
-        <v>331.92</v>
+        <v>332.52</v>
       </c>
       <c r="T3">
-        <v>31.25</v>
+        <v>28.83</v>
       </c>
       <c r="U3" t="s">
         <v>43</v>
@@ -1110,34 +1098,34 @@
         <v>3</v>
       </c>
       <c r="Y3">
-        <v>62.1</v>
+        <v>57.15</v>
       </c>
       <c r="Z3">
-        <v>8.59</v>
+        <v>8.279999999999999</v>
       </c>
       <c r="AA3">
-        <v>4.73</v>
+        <v>5.44</v>
       </c>
       <c r="AB3">
-        <v>3.86</v>
+        <v>2.83</v>
       </c>
       <c r="AC3">
-        <v>90.11</v>
+        <v>82.73</v>
       </c>
       <c r="AD3">
-        <v>90.27</v>
+        <v>87.93000000000001</v>
       </c>
       <c r="AE3">
-        <v>14.38</v>
+        <v>15.07</v>
       </c>
       <c r="AF3">
-        <v>-43.2</v>
+        <v>-46.4</v>
       </c>
       <c r="AG3">
-        <v>449.46</v>
+        <v>451.34</v>
       </c>
       <c r="AH3">
-        <v>371.72</v>
+        <v>372.51</v>
       </c>
       <c r="AI3">
         <v>396.9</v>
@@ -1146,7 +1134,7 @@
         <v>46</v>
       </c>
       <c r="AK3">
-        <v>51.3</v>
+        <v>46.52</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1157,10 +1145,10 @@
         <v>42</v>
       </c>
       <c r="C4">
-        <v>381.6</v>
+        <v>386.05</v>
       </c>
       <c r="D4">
-        <v>0.04</v>
+        <v>1.17</v>
       </c>
       <c r="E4">
         <v>534</v>
@@ -1169,46 +1157,46 @@
         <v>344.7</v>
       </c>
       <c r="G4">
-        <v>-28.54</v>
+        <v>-27.71</v>
       </c>
       <c r="H4">
-        <v>10.7</v>
+        <v>12</v>
       </c>
       <c r="I4">
-        <v>-3.53</v>
+        <v>-0.49</v>
       </c>
       <c r="J4">
-        <v>-6.62</v>
+        <v>-6.54</v>
       </c>
       <c r="K4">
-        <v>-11.11</v>
+        <v>-8.890000000000001</v>
       </c>
       <c r="L4">
-        <v>-27.45</v>
+        <v>-26.89</v>
       </c>
       <c r="M4">
-        <v>-22.09</v>
+        <v>-21.51</v>
       </c>
       <c r="N4">
         <v>21</v>
       </c>
       <c r="O4">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="P4">
-        <v>383.92</v>
+        <v>383.54</v>
       </c>
       <c r="Q4">
-        <v>396.44</v>
+        <v>395.4</v>
       </c>
       <c r="R4">
-        <v>411.82</v>
+        <v>411.32</v>
       </c>
       <c r="S4">
-        <v>412.55</v>
+        <v>412.06</v>
       </c>
       <c r="T4">
-        <v>-7.5</v>
+        <v>-6.31</v>
       </c>
       <c r="U4" t="s">
         <v>44</v>
@@ -1223,34 +1211,34 @@
         <v>0</v>
       </c>
       <c r="Y4">
-        <v>27.76</v>
+        <v>35.16</v>
       </c>
       <c r="Z4">
-        <v>-8.119999999999999</v>
+        <v>-7.87</v>
       </c>
       <c r="AA4">
-        <v>-6.95</v>
+        <v>-7.13</v>
       </c>
       <c r="AB4">
-        <v>-1.18</v>
+        <v>-0.74</v>
       </c>
       <c r="AC4">
-        <v>0.64</v>
+        <v>19.56</v>
       </c>
       <c r="AD4">
-        <v>0.84</v>
+        <v>6.73</v>
       </c>
       <c r="AE4">
-        <v>10.93</v>
+        <v>11.31</v>
       </c>
       <c r="AF4">
-        <v>-43.9</v>
+        <v>-38.3</v>
       </c>
       <c r="AG4">
-        <v>413.66</v>
+        <v>412.46</v>
       </c>
       <c r="AH4">
-        <v>379.23</v>
+        <v>378.33</v>
       </c>
       <c r="AI4">
         <v>413.11</v>
@@ -1259,7 +1247,7 @@
         <v>45</v>
       </c>
       <c r="AK4">
-        <v>21.57</v>
+        <v>21.79</v>
       </c>
     </row>
     <row r="5" spans="1:37">
@@ -1270,10 +1258,10 @@
         <v>42</v>
       </c>
       <c r="C5">
-        <v>956.5</v>
+        <v>946.5</v>
       </c>
       <c r="D5">
-        <v>-2.22</v>
+        <v>-1.05</v>
       </c>
       <c r="E5">
         <v>1069.3</v>
@@ -1282,46 +1270,46 @@
         <v>712.75</v>
       </c>
       <c r="G5">
-        <v>-10.55</v>
+        <v>-11.48</v>
       </c>
       <c r="H5">
-        <v>34.2</v>
+        <v>32.8</v>
       </c>
       <c r="I5">
-        <v>-4.16</v>
+        <v>-5.13</v>
       </c>
       <c r="J5">
-        <v>-6.3</v>
+        <v>-7.28</v>
       </c>
       <c r="K5">
-        <v>3.29</v>
+        <v>1.1</v>
       </c>
       <c r="L5">
-        <v>27.32</v>
+        <v>26.44</v>
       </c>
       <c r="M5">
-        <v>-1.33</v>
+        <v>-2.92</v>
       </c>
       <c r="N5">
         <v>79</v>
       </c>
       <c r="O5">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="P5">
-        <v>985.9400000000001</v>
+        <v>975.7</v>
       </c>
       <c r="Q5">
-        <v>1000.39</v>
+        <v>996.96</v>
       </c>
       <c r="R5">
-        <v>1011.01</v>
+        <v>1009.49</v>
       </c>
       <c r="S5">
-        <v>919.24</v>
+        <v>919.6900000000001</v>
       </c>
       <c r="T5">
-        <v>4.05</v>
+        <v>2.92</v>
       </c>
       <c r="U5" t="s">
         <v>44</v>
@@ -1336,43 +1324,43 @@
         <v>2</v>
       </c>
       <c r="Y5">
-        <v>35.57</v>
+        <v>33.3</v>
       </c>
       <c r="Z5">
-        <v>-7.41</v>
+        <v>-10.44</v>
       </c>
       <c r="AA5">
-        <v>-3.1</v>
+        <v>-4.56</v>
       </c>
       <c r="AB5">
-        <v>-4.31</v>
+        <v>-5.87</v>
       </c>
       <c r="AC5">
-        <v>18.11</v>
+        <v>3.28</v>
       </c>
       <c r="AD5">
-        <v>39.15</v>
+        <v>21.19</v>
       </c>
       <c r="AE5">
-        <v>20.71</v>
+        <v>20.42</v>
       </c>
       <c r="AF5">
-        <v>18.32</v>
+        <v>32.87</v>
       </c>
       <c r="AG5">
-        <v>1031.4</v>
+        <v>1035.42</v>
       </c>
       <c r="AH5">
-        <v>969.38</v>
+        <v>958.51</v>
       </c>
       <c r="AI5">
-        <v>1031.88</v>
+        <v>1014.05</v>
       </c>
       <c r="AJ5" t="s">
         <v>45</v>
       </c>
       <c r="AK5">
-        <v>16.68</v>
+        <v>20.84</v>
       </c>
     </row>
     <row r="6" spans="1:37">
@@ -1383,10 +1371,10 @@
         <v>42</v>
       </c>
       <c r="C6">
-        <v>2.75</v>
+        <v>2.89</v>
       </c>
       <c r="D6">
-        <v>-3.85</v>
+        <v>5.09</v>
       </c>
       <c r="E6">
         <v>3.62</v>
@@ -1395,46 +1383,46 @@
         <v>1.84</v>
       </c>
       <c r="G6">
-        <v>-24.03</v>
+        <v>-20.17</v>
       </c>
       <c r="H6">
-        <v>49.46</v>
+        <v>57.07</v>
       </c>
       <c r="I6">
-        <v>-7.72</v>
+        <v>-1.03</v>
       </c>
       <c r="J6">
-        <v>18.53</v>
+        <v>24.57</v>
       </c>
       <c r="K6">
-        <v>6.18</v>
+        <v>12.02</v>
       </c>
       <c r="L6">
-        <v>-24.03</v>
+        <v>-17.19</v>
       </c>
       <c r="M6">
-        <v>1.44</v>
+        <v>3.02</v>
       </c>
       <c r="N6">
         <v>40</v>
       </c>
       <c r="O6">
-        <v>57</v>
+        <v>65</v>
       </c>
       <c r="P6">
         <v>2.87</v>
       </c>
       <c r="Q6">
-        <v>2.81</v>
+        <v>2.84</v>
       </c>
       <c r="R6">
-        <v>2.53</v>
+        <v>2.54</v>
       </c>
       <c r="S6">
         <v>2.68</v>
       </c>
       <c r="T6">
-        <v>2.74</v>
+        <v>8.01</v>
       </c>
       <c r="U6" t="s">
         <v>43</v>
@@ -1449,7 +1437,7 @@
         <v>2</v>
       </c>
       <c r="Y6">
-        <v>50.98</v>
+        <v>58.25</v>
       </c>
       <c r="Z6">
         <v>0.1</v>
@@ -1461,22 +1449,22 @@
         <v>-0.02</v>
       </c>
       <c r="AC6">
-        <v>0</v>
+        <v>9.93</v>
       </c>
       <c r="AD6">
-        <v>8.56</v>
+        <v>4.43</v>
       </c>
       <c r="AE6">
-        <v>0.14</v>
+        <v>0.17</v>
       </c>
       <c r="AF6">
-        <v>-56.82</v>
+        <v>-42.13</v>
       </c>
       <c r="AG6">
-        <v>3.31</v>
+        <v>3.28</v>
       </c>
       <c r="AH6">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="AI6">
         <v>2.65</v>
@@ -1485,7 +1473,7 @@
         <v>46</v>
       </c>
       <c r="AK6">
-        <v>37.93</v>
+        <v>36.73</v>
       </c>
     </row>
   </sheetData>
@@ -1626,7 +1614,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F48"/>
+  <dimension ref="A1:F46"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.7109375" customWidth="1"/>
@@ -1666,7 +1654,7 @@
     </row>
     <row r="3" spans="1:6">
       <c r="A3" s="4" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B3" s="4" t="s">
         <v>53</v>
@@ -1718,13 +1706,13 @@
         <v>9</v>
       </c>
       <c r="C7" s="6">
-        <v>-7.08</v>
+        <v>-8.73</v>
       </c>
       <c r="D7" s="6">
-        <v>-8.73</v>
+        <v>-11.63</v>
       </c>
       <c r="E7" s="7">
-        <v>-1.65</v>
+        <v>-2.9</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -1735,13 +1723,13 @@
         <v>9</v>
       </c>
       <c r="C8" s="6">
-        <v>2.47</v>
+        <v>9.710000000000001</v>
       </c>
       <c r="D8" s="6">
-        <v>9.710000000000001</v>
-      </c>
-      <c r="E8" s="8">
-        <v>7.24</v>
+        <v>5</v>
+      </c>
+      <c r="E8" s="7">
+        <v>-4.71</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -1752,13 +1740,13 @@
         <v>9</v>
       </c>
       <c r="C9" s="6">
-        <v>-5.74</v>
+        <v>-6.62</v>
       </c>
       <c r="D9" s="6">
-        <v>-6.62</v>
-      </c>
-      <c r="E9" s="7">
-        <v>-0.88</v>
+        <v>-6.54</v>
+      </c>
+      <c r="E9" s="8">
+        <v>0.08</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -1769,13 +1757,13 @@
         <v>9</v>
       </c>
       <c r="C10" s="6">
-        <v>-4.54</v>
+        <v>-6.3</v>
       </c>
       <c r="D10" s="6">
-        <v>-6.3</v>
+        <v>-7.28</v>
       </c>
       <c r="E10" s="7">
-        <v>-1.76</v>
+        <v>-0.98</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -1786,13 +1774,13 @@
         <v>9</v>
       </c>
       <c r="C11" s="6">
-        <v>21.19</v>
+        <v>18.53</v>
       </c>
       <c r="D11" s="6">
-        <v>18.53</v>
-      </c>
-      <c r="E11" s="7">
-        <v>-2.66</v>
+        <v>24.57</v>
+      </c>
+      <c r="E11" s="8">
+        <v>6.04</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -1803,13 +1791,13 @@
         <v>8</v>
       </c>
       <c r="C12" s="6">
-        <v>-3.11</v>
+        <v>-7.85</v>
       </c>
       <c r="D12" s="6">
-        <v>-7.85</v>
-      </c>
-      <c r="E12" s="7">
-        <v>-4.74</v>
+        <v>-7.4</v>
+      </c>
+      <c r="E12" s="8">
+        <v>0.45</v>
       </c>
     </row>
     <row r="13" spans="1:6">
@@ -1820,13 +1808,13 @@
         <v>8</v>
       </c>
       <c r="C13" s="6">
-        <v>3.3</v>
+        <v>-0.3</v>
       </c>
       <c r="D13" s="6">
-        <v>-0.3</v>
+        <v>-1.65</v>
       </c>
       <c r="E13" s="7">
-        <v>-3.6</v>
+        <v>-1.35</v>
       </c>
     </row>
     <row r="14" spans="1:6">
@@ -1837,13 +1825,13 @@
         <v>8</v>
       </c>
       <c r="C14" s="6">
-        <v>-4.46</v>
+        <v>-3.53</v>
       </c>
       <c r="D14" s="6">
-        <v>-3.53</v>
+        <v>-0.49</v>
       </c>
       <c r="E14" s="8">
-        <v>0.93</v>
+        <v>3.04</v>
       </c>
     </row>
     <row r="15" spans="1:6">
@@ -1854,13 +1842,13 @@
         <v>8</v>
       </c>
       <c r="C15" s="6">
-        <v>-3</v>
+        <v>-4.16</v>
       </c>
       <c r="D15" s="6">
-        <v>-4.16</v>
+        <v>-5.13</v>
       </c>
       <c r="E15" s="7">
-        <v>-1.16</v>
+        <v>-0.97</v>
       </c>
     </row>
     <row r="16" spans="1:6">
@@ -1871,13 +1859,13 @@
         <v>8</v>
       </c>
       <c r="C16" s="6">
-        <v>1.06</v>
+        <v>-7.72</v>
       </c>
       <c r="D16" s="6">
-        <v>-7.72</v>
-      </c>
-      <c r="E16" s="7">
-        <v>-8.779999999999999</v>
+        <v>-1.03</v>
+      </c>
+      <c r="E16" s="8">
+        <v>6.69</v>
       </c>
     </row>
     <row r="17" spans="1:5">
@@ -1888,13 +1876,13 @@
         <v>11</v>
       </c>
       <c r="C17" s="6">
-        <v>24.15</v>
+        <v>19.7</v>
       </c>
       <c r="D17" s="6">
-        <v>19.7</v>
-      </c>
-      <c r="E17" s="7">
-        <v>-4.45</v>
+        <v>19.98</v>
+      </c>
+      <c r="E17" s="8">
+        <v>0.28</v>
       </c>
     </row>
     <row r="18" spans="1:5">
@@ -1905,13 +1893,13 @@
         <v>11</v>
       </c>
       <c r="C18" s="6">
-        <v>22.26</v>
+        <v>22.2</v>
       </c>
       <c r="D18" s="6">
-        <v>22.2</v>
+        <v>20.25</v>
       </c>
       <c r="E18" s="7">
-        <v>-0.06</v>
+        <v>-1.95</v>
       </c>
     </row>
     <row r="19" spans="1:5">
@@ -1922,13 +1910,13 @@
         <v>11</v>
       </c>
       <c r="C19" s="6">
-        <v>-27.33</v>
+        <v>-27.45</v>
       </c>
       <c r="D19" s="6">
-        <v>-27.45</v>
-      </c>
-      <c r="E19" s="7">
-        <v>-0.12</v>
+        <v>-26.89</v>
+      </c>
+      <c r="E19" s="8">
+        <v>0.5600000000000001</v>
       </c>
     </row>
     <row r="20" spans="1:5">
@@ -1939,13 +1927,13 @@
         <v>11</v>
       </c>
       <c r="C20" s="6">
-        <v>31.1</v>
+        <v>27.32</v>
       </c>
       <c r="D20" s="6">
-        <v>27.32</v>
+        <v>26.44</v>
       </c>
       <c r="E20" s="7">
-        <v>-3.78</v>
+        <v>-0.88</v>
       </c>
     </row>
     <row r="21" spans="1:5">
@@ -1956,13 +1944,13 @@
         <v>11</v>
       </c>
       <c r="C21" s="6">
-        <v>-18.52</v>
+        <v>-24.03</v>
       </c>
       <c r="D21" s="6">
-        <v>-24.03</v>
-      </c>
-      <c r="E21" s="7">
-        <v>-5.51</v>
+        <v>-17.19</v>
+      </c>
+      <c r="E21" s="8">
+        <v>6.84</v>
       </c>
     </row>
     <row r="22" spans="1:5">
@@ -1973,13 +1961,13 @@
         <v>10</v>
       </c>
       <c r="C22" s="6">
-        <v>3.84</v>
+        <v>-1.17</v>
       </c>
       <c r="D22" s="6">
-        <v>-1.17</v>
+        <v>-1.92</v>
       </c>
       <c r="E22" s="7">
-        <v>-5.01</v>
+        <v>-0.75</v>
       </c>
     </row>
     <row r="23" spans="1:5">
@@ -1990,13 +1978,13 @@
         <v>10</v>
       </c>
       <c r="C23" s="6">
-        <v>9.09</v>
+        <v>8.32</v>
       </c>
       <c r="D23" s="6">
-        <v>8.32</v>
+        <v>6.22</v>
       </c>
       <c r="E23" s="7">
-        <v>-0.77</v>
+        <v>-2.1</v>
       </c>
     </row>
     <row r="24" spans="1:5">
@@ -2007,13 +1995,13 @@
         <v>10</v>
       </c>
       <c r="C24" s="6">
-        <v>-11</v>
+        <v>-11.11</v>
       </c>
       <c r="D24" s="6">
-        <v>-11.11</v>
-      </c>
-      <c r="E24" s="7">
-        <v>-0.11</v>
+        <v>-8.890000000000001</v>
+      </c>
+      <c r="E24" s="8">
+        <v>2.22</v>
       </c>
     </row>
     <row r="25" spans="1:5">
@@ -2024,13 +2012,13 @@
         <v>10</v>
       </c>
       <c r="C25" s="6">
-        <v>4.82</v>
+        <v>3.29</v>
       </c>
       <c r="D25" s="6">
-        <v>3.29</v>
+        <v>1.1</v>
       </c>
       <c r="E25" s="7">
-        <v>-1.53</v>
+        <v>-2.19</v>
       </c>
     </row>
     <row r="26" spans="1:5">
@@ -2041,13 +2029,13 @@
         <v>10</v>
       </c>
       <c r="C26" s="6">
-        <v>9.58</v>
+        <v>6.18</v>
       </c>
       <c r="D26" s="6">
-        <v>6.18</v>
-      </c>
-      <c r="E26" s="7">
-        <v>-3.4</v>
+        <v>12.02</v>
+      </c>
+      <c r="E26" s="8">
+        <v>5.84</v>
       </c>
     </row>
     <row r="27" spans="1:5">
@@ -2058,13 +2046,13 @@
         <v>6</v>
       </c>
       <c r="C27" s="6">
-        <v>-21.41</v>
+        <v>-24.82</v>
       </c>
       <c r="D27" s="6">
-        <v>-24.82</v>
+        <v>-24.89</v>
       </c>
       <c r="E27" s="7">
-        <v>-3.41</v>
+        <v>-0.07000000000000001</v>
       </c>
     </row>
     <row r="28" spans="1:5">
@@ -2075,13 +2063,13 @@
         <v>6</v>
       </c>
       <c r="C28" s="6">
-        <v>-0.84</v>
+        <v>-2.17</v>
       </c>
       <c r="D28" s="6">
-        <v>-2.17</v>
+        <v>-3.8</v>
       </c>
       <c r="E28" s="7">
-        <v>-1.33</v>
+        <v>-1.63</v>
       </c>
     </row>
     <row r="29" spans="1:5">
@@ -2092,13 +2080,13 @@
         <v>6</v>
       </c>
       <c r="C29" s="6">
-        <v>-28.57</v>
+        <v>-28.54</v>
       </c>
       <c r="D29" s="6">
-        <v>-28.54</v>
+        <v>-27.71</v>
       </c>
       <c r="E29" s="8">
-        <v>0.03</v>
+        <v>0.83</v>
       </c>
     </row>
     <row r="30" spans="1:5">
@@ -2109,13 +2097,13 @@
         <v>6</v>
       </c>
       <c r="C30" s="6">
-        <v>-8.52</v>
+        <v>-10.55</v>
       </c>
       <c r="D30" s="6">
-        <v>-10.55</v>
+        <v>-11.48</v>
       </c>
       <c r="E30" s="7">
-        <v>-2.03</v>
+        <v>-0.93</v>
       </c>
     </row>
     <row r="31" spans="1:5">
@@ -2126,13 +2114,13 @@
         <v>6</v>
       </c>
       <c r="C31" s="6">
-        <v>-20.99</v>
+        <v>-24.03</v>
       </c>
       <c r="D31" s="6">
-        <v>-24.03</v>
-      </c>
-      <c r="E31" s="7">
-        <v>-3.04</v>
+        <v>-20.17</v>
+      </c>
+      <c r="E31" s="8">
+        <v>3.86</v>
       </c>
     </row>
     <row r="32" spans="1:5">
@@ -2143,13 +2131,13 @@
         <v>2</v>
       </c>
       <c r="C32" s="6">
-        <v>163.75</v>
+        <v>156.65</v>
       </c>
       <c r="D32" s="6">
-        <v>156.65</v>
+        <v>156.5</v>
       </c>
       <c r="E32" s="7">
-        <v>-7.1</v>
+        <v>-0.15</v>
       </c>
     </row>
     <row r="33" spans="1:5">
@@ -2160,13 +2148,13 @@
         <v>2</v>
       </c>
       <c r="C33" s="6">
-        <v>441.55</v>
+        <v>435.65</v>
       </c>
       <c r="D33" s="6">
-        <v>435.65</v>
+        <v>428.4</v>
       </c>
       <c r="E33" s="7">
-        <v>-5.9</v>
+        <v>-7.25</v>
       </c>
     </row>
     <row r="34" spans="1:5">
@@ -2177,13 +2165,13 @@
         <v>2</v>
       </c>
       <c r="C34" s="6">
-        <v>381.45</v>
+        <v>381.6</v>
       </c>
       <c r="D34" s="6">
-        <v>381.6</v>
+        <v>386.05</v>
       </c>
       <c r="E34" s="8">
-        <v>0.15</v>
+        <v>4.45</v>
       </c>
     </row>
     <row r="35" spans="1:5">
@@ -2194,13 +2182,13 @@
         <v>2</v>
       </c>
       <c r="C35" s="6">
-        <v>978.2</v>
+        <v>956.5</v>
       </c>
       <c r="D35" s="6">
-        <v>956.5</v>
+        <v>946.5</v>
       </c>
       <c r="E35" s="7">
-        <v>-21.7</v>
+        <v>-10</v>
       </c>
     </row>
     <row r="36" spans="1:5">
@@ -2211,217 +2199,183 @@
         <v>2</v>
       </c>
       <c r="C36" s="6">
-        <v>2.86</v>
+        <v>2.75</v>
       </c>
       <c r="D36" s="6">
-        <v>2.75</v>
-      </c>
-      <c r="E36" s="7">
-        <v>-0.11</v>
+        <v>2.89</v>
+      </c>
+      <c r="E36" s="8">
+        <v>0.14</v>
       </c>
     </row>
     <row r="37" spans="1:5">
       <c r="A37" s="5" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B37" s="5" t="s">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="C37" s="6">
-        <v>79</v>
+        <v>29.72</v>
       </c>
       <c r="D37" s="6">
-        <v>99</v>
-      </c>
-      <c r="E37" s="8">
-        <v>20</v>
+        <v>29.57</v>
+      </c>
+      <c r="E37" s="7">
+        <v>-0.15</v>
       </c>
     </row>
     <row r="38" spans="1:5">
       <c r="A38" s="5" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B38" s="5" t="s">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="C38" s="6">
-        <v>99</v>
+        <v>62.1</v>
       </c>
       <c r="D38" s="6">
-        <v>79</v>
+        <v>57.15</v>
       </c>
       <c r="E38" s="7">
-        <v>-20</v>
+        <v>-4.95</v>
       </c>
     </row>
     <row r="39" spans="1:5">
       <c r="A39" s="5" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B39" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C39" s="6">
-        <v>38.17</v>
+        <v>27.76</v>
       </c>
       <c r="D39" s="6">
-        <v>29.72</v>
-      </c>
-      <c r="E39" s="7">
-        <v>-8.449999999999999</v>
+        <v>35.16</v>
+      </c>
+      <c r="E39" s="8">
+        <v>7.4</v>
       </c>
     </row>
     <row r="40" spans="1:5">
       <c r="A40" s="5" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B40" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C40" s="6">
-        <v>66.45</v>
+        <v>35.57</v>
       </c>
       <c r="D40" s="6">
-        <v>62.1</v>
+        <v>33.3</v>
       </c>
       <c r="E40" s="7">
-        <v>-4.35</v>
+        <v>-2.27</v>
       </c>
     </row>
     <row r="41" spans="1:5">
       <c r="A41" s="5" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="B41" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C41" s="6">
-        <v>27.5</v>
+        <v>50.98</v>
       </c>
       <c r="D41" s="6">
-        <v>27.76</v>
+        <v>58.25</v>
       </c>
       <c r="E41" s="8">
-        <v>0.26</v>
+        <v>7.27</v>
       </c>
     </row>
     <row r="42" spans="1:5">
       <c r="A42" s="5" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="B42" s="5" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="C42" s="6">
-        <v>41.24</v>
+        <v>23.23</v>
       </c>
       <c r="D42" s="6">
-        <v>35.57</v>
+        <v>-23.7</v>
       </c>
       <c r="E42" s="7">
-        <v>-5.67</v>
+        <v>-46.93</v>
       </c>
     </row>
     <row r="43" spans="1:5">
       <c r="A43" s="5" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="B43" s="5" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="C43" s="6">
-        <v>58.4</v>
+        <v>-43.2</v>
       </c>
       <c r="D43" s="6">
-        <v>50.98</v>
+        <v>-46.4</v>
       </c>
       <c r="E43" s="7">
-        <v>-7.42</v>
+        <v>-3.2</v>
       </c>
     </row>
     <row r="44" spans="1:5">
       <c r="A44" s="5" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B44" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C44" s="6">
-        <v>27.15</v>
+        <v>-43.9</v>
       </c>
       <c r="D44" s="6">
-        <v>23.23</v>
-      </c>
-      <c r="E44" s="7">
-        <v>-3.92</v>
+        <v>-38.3</v>
+      </c>
+      <c r="E44" s="8">
+        <v>5.6</v>
       </c>
     </row>
     <row r="45" spans="1:5">
       <c r="A45" s="5" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B45" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C45" s="6">
-        <v>-43.68</v>
+        <v>18.32</v>
       </c>
       <c r="D45" s="6">
-        <v>-43.2</v>
+        <v>32.87</v>
       </c>
       <c r="E45" s="8">
-        <v>0.48</v>
+        <v>14.55</v>
       </c>
     </row>
     <row r="46" spans="1:5">
       <c r="A46" s="5" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="B46" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C46" s="6">
-        <v>-40.08</v>
+        <v>-56.82</v>
       </c>
       <c r="D46" s="6">
-        <v>-43.9</v>
-      </c>
-      <c r="E46" s="7">
-        <v>-3.82</v>
-      </c>
-    </row>
-    <row r="47" spans="1:5">
-      <c r="A47" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B47" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C47" s="6">
-        <v>110.42</v>
-      </c>
-      <c r="D47" s="6">
-        <v>18.32</v>
-      </c>
-      <c r="E47" s="7">
-        <v>-92.09999999999999</v>
-      </c>
-    </row>
-    <row r="48" spans="1:5">
-      <c r="A48" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B48" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C48" s="6">
-        <v>-71.44</v>
-      </c>
-      <c r="D48" s="6">
-        <v>-56.82</v>
-      </c>
-      <c r="E48" s="8">
-        <v>14.62</v>
+        <v>-42.13</v>
+      </c>
+      <c r="E46" s="8">
+        <v>14.69</v>
       </c>
     </row>
   </sheetData>
@@ -2486,16 +2440,16 @@
         <v>5</v>
       </c>
       <c r="D2" s="11">
-        <v>41.2</v>
+        <v>42.7</v>
       </c>
       <c r="E2" s="11">
         <v>60</v>
       </c>
       <c r="F2" s="11">
-        <v>1.3</v>
+        <v>0.8</v>
       </c>
       <c r="G2" s="11">
-        <v>1.1</v>
+        <v>1.7</v>
       </c>
       <c r="H2" s="11">
         <v>59.8</v>
@@ -2620,19 +2574,19 @@
     </row>
     <row r="2" spans="1:5">
       <c r="A2" s="14">
-        <v>0.22</v>
+        <v>0.2218</v>
       </c>
       <c r="B2" s="14">
-        <v>0.111</v>
+        <v>0.1156</v>
       </c>
       <c r="C2" s="14">
-        <v>0.0144</v>
+        <v>0.0302</v>
       </c>
       <c r="D2" s="14">
-        <v>-0.0133</v>
+        <v>-0.0292</v>
       </c>
       <c r="E2" s="14">
-        <v>-0.2209</v>
+        <v>-0.2151</v>
       </c>
     </row>
   </sheetData>

--- a/HINDUJA_GROUP_Technical_Metrics.xlsx
+++ b/HINDUJA_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="218" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="224" uniqueCount="76">
   <si>
     <t>Symbol</t>
   </si>
@@ -181,19 +181,34 @@
     <t>Curr Value</t>
   </si>
   <si>
+    <t>Near 52W High</t>
+  </si>
+  <si>
+    <t>-3.8% → 0.0%</t>
+  </si>
+  <si>
+    <t>🟢 BREAKOUT WATCH</t>
+  </si>
+  <si>
+    <t>-3.8%</t>
+  </si>
+  <si>
+    <t>0.0%</t>
+  </si>
+  <si>
     <t>RSI Oversold Recovery</t>
   </si>
   <si>
-    <t>27.8 → 35.2</t>
+    <t>29.6 → 34.6</t>
   </si>
   <si>
     <t>🟢 BULLISH</t>
   </si>
   <si>
-    <t>27.8</t>
-  </si>
-  <si>
-    <t>35.2</t>
+    <t>29.6</t>
+  </si>
+  <si>
+    <t>34.6</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -405,8 +420,8 @@
     <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -919,10 +934,10 @@
         <v>42</v>
       </c>
       <c r="C2">
-        <v>156.5</v>
+        <v>158.62</v>
       </c>
       <c r="D2">
-        <v>-0.1</v>
+        <v>1.35</v>
       </c>
       <c r="E2">
         <v>208.37</v>
@@ -931,46 +946,46 @@
         <v>130.81</v>
       </c>
       <c r="G2">
-        <v>-24.89</v>
+        <v>-23.88</v>
       </c>
       <c r="H2">
-        <v>19.64</v>
+        <v>21.26</v>
       </c>
       <c r="I2">
-        <v>-7.4</v>
+        <v>-5.02</v>
       </c>
       <c r="J2">
-        <v>-11.63</v>
+        <v>-10.05</v>
       </c>
       <c r="K2">
-        <v>-1.92</v>
+        <v>0.11</v>
       </c>
       <c r="L2">
-        <v>19.98</v>
+        <v>21.13</v>
       </c>
       <c r="M2">
-        <v>22.18</v>
+        <v>22.92</v>
       </c>
       <c r="N2">
         <v>60</v>
       </c>
       <c r="O2">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="P2">
-        <v>162</v>
+        <v>160.33</v>
       </c>
       <c r="Q2">
-        <v>170.08</v>
+        <v>169.35</v>
       </c>
       <c r="R2">
-        <v>166.29</v>
+        <v>166.34</v>
       </c>
       <c r="S2">
-        <v>169.86</v>
+        <v>169.88</v>
       </c>
       <c r="T2">
-        <v>-7.86</v>
+        <v>-6.63</v>
       </c>
       <c r="U2" t="s">
         <v>43</v>
@@ -985,34 +1000,34 @@
         <v>1</v>
       </c>
       <c r="Y2">
-        <v>29.57</v>
+        <v>34.56</v>
       </c>
       <c r="Z2">
-        <v>-2.34</v>
+        <v>-2.72</v>
       </c>
       <c r="AA2">
-        <v>-0.19</v>
+        <v>-0.6899999999999999</v>
       </c>
       <c r="AB2">
-        <v>-2.15</v>
+        <v>-2.02</v>
       </c>
       <c r="AC2">
-        <v>0</v>
+        <v>5.85</v>
       </c>
       <c r="AD2">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AE2">
-        <v>4.44</v>
+        <v>4.37</v>
       </c>
       <c r="AF2">
-        <v>-23.7</v>
+        <v>-28.51</v>
       </c>
       <c r="AG2">
-        <v>182.2</v>
+        <v>182.41</v>
       </c>
       <c r="AH2">
-        <v>157.95</v>
+        <v>156.3</v>
       </c>
       <c r="AI2">
         <v>169.79</v>
@@ -1021,7 +1036,7 @@
         <v>45</v>
       </c>
       <c r="AK2">
-        <v>33.3</v>
+        <v>35.4</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1032,58 +1047,58 @@
         <v>42</v>
       </c>
       <c r="C3">
-        <v>428.4</v>
+        <v>456.15</v>
       </c>
       <c r="D3">
-        <v>-1.66</v>
+        <v>6.48</v>
       </c>
       <c r="E3">
-        <v>445.3</v>
+        <v>456.15</v>
       </c>
       <c r="F3">
         <v>225</v>
       </c>
       <c r="G3">
-        <v>-3.8</v>
+        <v>0</v>
       </c>
       <c r="H3">
-        <v>90.40000000000001</v>
+        <v>102.73</v>
       </c>
       <c r="I3">
-        <v>-1.65</v>
+        <v>5.66</v>
       </c>
       <c r="J3">
-        <v>5</v>
+        <v>13.57</v>
       </c>
       <c r="K3">
-        <v>6.22</v>
+        <v>7.34</v>
       </c>
       <c r="L3">
-        <v>20.25</v>
+        <v>29.53</v>
       </c>
       <c r="M3">
-        <v>11.56</v>
+        <v>13.03</v>
       </c>
       <c r="N3">
         <v>99</v>
       </c>
       <c r="O3">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="P3">
-        <v>433.9</v>
+        <v>438.79</v>
       </c>
       <c r="Q3">
-        <v>411.93</v>
+        <v>414.81</v>
       </c>
       <c r="R3">
-        <v>408.4</v>
+        <v>409.63</v>
       </c>
       <c r="S3">
-        <v>332.52</v>
+        <v>333.28</v>
       </c>
       <c r="T3">
-        <v>28.83</v>
+        <v>36.87</v>
       </c>
       <c r="U3" t="s">
         <v>43</v>
@@ -1098,43 +1113,43 @@
         <v>3</v>
       </c>
       <c r="Y3">
-        <v>57.15</v>
+        <v>67.73999999999999</v>
       </c>
       <c r="Z3">
-        <v>8.279999999999999</v>
+        <v>10.15</v>
       </c>
       <c r="AA3">
-        <v>5.44</v>
+        <v>6.38</v>
       </c>
       <c r="AB3">
-        <v>2.83</v>
+        <v>3.77</v>
       </c>
       <c r="AC3">
         <v>82.73</v>
       </c>
       <c r="AD3">
-        <v>87.93000000000001</v>
+        <v>85.19</v>
       </c>
       <c r="AE3">
-        <v>15.07</v>
+        <v>16.17</v>
       </c>
       <c r="AF3">
-        <v>-46.4</v>
+        <v>196.64</v>
       </c>
       <c r="AG3">
-        <v>451.34</v>
+        <v>458.31</v>
       </c>
       <c r="AH3">
-        <v>372.51</v>
+        <v>371.3</v>
       </c>
       <c r="AI3">
-        <v>396.9</v>
+        <v>397.19</v>
       </c>
       <c r="AJ3" t="s">
         <v>46</v>
       </c>
       <c r="AK3">
-        <v>46.52</v>
+        <v>45.58</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1145,10 +1160,10 @@
         <v>42</v>
       </c>
       <c r="C4">
-        <v>386.05</v>
+        <v>386.35</v>
       </c>
       <c r="D4">
-        <v>1.17</v>
+        <v>0.08</v>
       </c>
       <c r="E4">
         <v>534</v>
@@ -1157,25 +1172,25 @@
         <v>344.7</v>
       </c>
       <c r="G4">
-        <v>-27.71</v>
+        <v>-27.65</v>
       </c>
       <c r="H4">
-        <v>12</v>
+        <v>12.08</v>
       </c>
       <c r="I4">
-        <v>-0.49</v>
+        <v>0.42</v>
       </c>
       <c r="J4">
-        <v>-6.54</v>
+        <v>-5.06</v>
       </c>
       <c r="K4">
-        <v>-8.890000000000001</v>
+        <v>-8.94</v>
       </c>
       <c r="L4">
-        <v>-26.89</v>
+        <v>-27.54</v>
       </c>
       <c r="M4">
-        <v>-21.51</v>
+        <v>-22.21</v>
       </c>
       <c r="N4">
         <v>21</v>
@@ -1184,19 +1199,19 @@
         <v>27</v>
       </c>
       <c r="P4">
-        <v>383.54</v>
+        <v>383.86</v>
       </c>
       <c r="Q4">
-        <v>395.4</v>
+        <v>394.31</v>
       </c>
       <c r="R4">
-        <v>411.32</v>
+        <v>410.92</v>
       </c>
       <c r="S4">
-        <v>412.06</v>
+        <v>411.57</v>
       </c>
       <c r="T4">
-        <v>-6.31</v>
+        <v>-6.13</v>
       </c>
       <c r="U4" t="s">
         <v>44</v>
@@ -1211,34 +1226,34 @@
         <v>0</v>
       </c>
       <c r="Y4">
-        <v>35.16</v>
+        <v>35.64</v>
       </c>
       <c r="Z4">
-        <v>-7.87</v>
+        <v>-7.55</v>
       </c>
       <c r="AA4">
-        <v>-7.13</v>
+        <v>-7.22</v>
       </c>
       <c r="AB4">
-        <v>-0.74</v>
+        <v>-0.34</v>
       </c>
       <c r="AC4">
-        <v>19.56</v>
+        <v>39.66</v>
       </c>
       <c r="AD4">
-        <v>6.73</v>
+        <v>19.95</v>
       </c>
       <c r="AE4">
-        <v>11.31</v>
+        <v>11.18</v>
       </c>
       <c r="AF4">
-        <v>-38.3</v>
+        <v>42.35</v>
       </c>
       <c r="AG4">
-        <v>412.46</v>
+        <v>410.75</v>
       </c>
       <c r="AH4">
-        <v>378.33</v>
+        <v>377.88</v>
       </c>
       <c r="AI4">
         <v>413.11</v>
@@ -1247,7 +1262,7 @@
         <v>45</v>
       </c>
       <c r="AK4">
-        <v>21.79</v>
+        <v>21.59</v>
       </c>
     </row>
     <row r="5" spans="1:37">
@@ -1258,10 +1273,10 @@
         <v>42</v>
       </c>
       <c r="C5">
-        <v>946.5</v>
+        <v>958.2</v>
       </c>
       <c r="D5">
-        <v>-1.05</v>
+        <v>1.24</v>
       </c>
       <c r="E5">
         <v>1069.3</v>
@@ -1270,46 +1285,46 @@
         <v>712.75</v>
       </c>
       <c r="G5">
-        <v>-11.48</v>
+        <v>-10.39</v>
       </c>
       <c r="H5">
-        <v>32.8</v>
+        <v>34.44</v>
       </c>
       <c r="I5">
-        <v>-5.13</v>
+        <v>-4.56</v>
       </c>
       <c r="J5">
-        <v>-7.28</v>
+        <v>-5.6</v>
       </c>
       <c r="K5">
-        <v>1.1</v>
+        <v>2.07</v>
       </c>
       <c r="L5">
-        <v>26.44</v>
+        <v>29.4</v>
       </c>
       <c r="M5">
-        <v>-2.92</v>
+        <v>-2.66</v>
       </c>
       <c r="N5">
         <v>79</v>
       </c>
       <c r="O5">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="P5">
-        <v>975.7</v>
+        <v>966.54</v>
       </c>
       <c r="Q5">
-        <v>996.96</v>
+        <v>994.04</v>
       </c>
       <c r="R5">
-        <v>1009.49</v>
+        <v>1008.76</v>
       </c>
       <c r="S5">
-        <v>919.6900000000001</v>
+        <v>920.1799999999999</v>
       </c>
       <c r="T5">
-        <v>2.92</v>
+        <v>4.13</v>
       </c>
       <c r="U5" t="s">
         <v>44</v>
@@ -1324,34 +1339,34 @@
         <v>2</v>
       </c>
       <c r="Y5">
-        <v>33.3</v>
+        <v>38.27</v>
       </c>
       <c r="Z5">
-        <v>-10.44</v>
+        <v>-11.75</v>
       </c>
       <c r="AA5">
-        <v>-4.56</v>
+        <v>-6</v>
       </c>
       <c r="AB5">
-        <v>-5.87</v>
+        <v>-5.75</v>
       </c>
       <c r="AC5">
-        <v>3.28</v>
+        <v>8.35</v>
       </c>
       <c r="AD5">
-        <v>21.19</v>
+        <v>9.91</v>
       </c>
       <c r="AE5">
-        <v>20.42</v>
+        <v>20.78</v>
       </c>
       <c r="AF5">
-        <v>32.87</v>
+        <v>198.87</v>
       </c>
       <c r="AG5">
-        <v>1035.42</v>
+        <v>1034.99</v>
       </c>
       <c r="AH5">
-        <v>958.51</v>
+        <v>953.09</v>
       </c>
       <c r="AI5">
         <v>1014.05</v>
@@ -1360,7 +1375,7 @@
         <v>45</v>
       </c>
       <c r="AK5">
-        <v>20.84</v>
+        <v>21.92</v>
       </c>
     </row>
     <row r="6" spans="1:37">
@@ -1371,10 +1386,10 @@
         <v>42</v>
       </c>
       <c r="C6">
-        <v>2.89</v>
+        <v>2.82</v>
       </c>
       <c r="D6">
-        <v>5.09</v>
+        <v>-2.42</v>
       </c>
       <c r="E6">
         <v>3.62</v>
@@ -1383,22 +1398,22 @@
         <v>1.84</v>
       </c>
       <c r="G6">
-        <v>-20.17</v>
+        <v>-22.1</v>
       </c>
       <c r="H6">
-        <v>57.07</v>
+        <v>53.26</v>
       </c>
       <c r="I6">
-        <v>-1.03</v>
+        <v>-3.75</v>
       </c>
       <c r="J6">
-        <v>24.57</v>
+        <v>24.23</v>
       </c>
       <c r="K6">
-        <v>12.02</v>
+        <v>7.63</v>
       </c>
       <c r="L6">
-        <v>-17.19</v>
+        <v>-18.97</v>
       </c>
       <c r="M6">
         <v>3.02</v>
@@ -1407,22 +1422,22 @@
         <v>40</v>
       </c>
       <c r="O6">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="P6">
+        <v>2.84</v>
+      </c>
+      <c r="Q6">
         <v>2.87</v>
       </c>
-      <c r="Q6">
-        <v>2.84</v>
-      </c>
       <c r="R6">
-        <v>2.54</v>
+        <v>2.55</v>
       </c>
       <c r="S6">
-        <v>2.68</v>
+        <v>2.67</v>
       </c>
       <c r="T6">
-        <v>8.01</v>
+        <v>5.45</v>
       </c>
       <c r="U6" t="s">
         <v>43</v>
@@ -1437,34 +1452,34 @@
         <v>2</v>
       </c>
       <c r="Y6">
-        <v>58.25</v>
+        <v>53.94</v>
       </c>
       <c r="Z6">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="AA6">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="AB6">
         <v>-0.02</v>
       </c>
       <c r="AC6">
-        <v>9.93</v>
+        <v>13.97</v>
       </c>
       <c r="AD6">
-        <v>4.43</v>
+        <v>7.97</v>
       </c>
       <c r="AE6">
-        <v>0.17</v>
+        <v>0.16</v>
       </c>
       <c r="AF6">
-        <v>-42.13</v>
+        <v>-77.47</v>
       </c>
       <c r="AG6">
-        <v>3.28</v>
+        <v>3.21</v>
       </c>
       <c r="AH6">
-        <v>2.4</v>
+        <v>2.52</v>
       </c>
       <c r="AI6">
         <v>2.65</v>
@@ -1473,7 +1488,7 @@
         <v>46</v>
       </c>
       <c r="AK6">
-        <v>36.73</v>
+        <v>35.7</v>
       </c>
     </row>
   </sheetData>
@@ -1614,7 +1629,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F46"/>
+  <dimension ref="A1:F47"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.7109375" customWidth="1"/>
@@ -1654,7 +1669,7 @@
     </row>
     <row r="3" spans="1:6">
       <c r="A3" s="4" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B3" s="4" t="s">
         <v>53</v>
@@ -1672,716 +1687,736 @@
         <v>57</v>
       </c>
     </row>
-    <row r="5" spans="1:6">
-      <c r="A5" s="2" t="s">
+    <row r="4" spans="1:6">
+      <c r="A4" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="B4" s="4" t="s">
         <v>58</v>
       </c>
-      <c r="B5" s="2"/>
-      <c r="C5" s="2"/>
-      <c r="D5" s="2"/>
-      <c r="E5" s="2"/>
+      <c r="C4" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="F4" s="4" t="s">
+        <v>62</v>
+      </c>
     </row>
     <row r="6" spans="1:6">
-      <c r="A6" s="3" t="s">
+      <c r="A6" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="B6" s="2"/>
+      <c r="C6" s="2"/>
+      <c r="D6" s="2"/>
+      <c r="E6" s="2"/>
+    </row>
+    <row r="7" spans="1:6">
+      <c r="A7" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B6" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="E6" s="3" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6">
-      <c r="A7" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B7" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C7" s="6">
-        <v>-8.73</v>
-      </c>
-      <c r="D7" s="6">
-        <v>-11.63</v>
-      </c>
-      <c r="E7" s="7">
-        <v>-2.9</v>
+      <c r="B7" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>67</v>
       </c>
     </row>
     <row r="8" spans="1:6">
       <c r="A8" s="5" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B8" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C8" s="6">
-        <v>9.710000000000001</v>
+        <v>-11.63</v>
       </c>
       <c r="D8" s="6">
-        <v>5</v>
+        <v>-10.05</v>
       </c>
       <c r="E8" s="7">
-        <v>-4.71</v>
+        <v>1.58</v>
       </c>
     </row>
     <row r="9" spans="1:6">
       <c r="A9" s="5" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B9" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C9" s="6">
-        <v>-6.62</v>
+        <v>5</v>
       </c>
       <c r="D9" s="6">
-        <v>-6.54</v>
-      </c>
-      <c r="E9" s="8">
-        <v>0.08</v>
+        <v>13.57</v>
+      </c>
+      <c r="E9" s="7">
+        <v>8.57</v>
       </c>
     </row>
     <row r="10" spans="1:6">
       <c r="A10" s="5" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B10" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C10" s="6">
-        <v>-6.3</v>
+        <v>-6.54</v>
       </c>
       <c r="D10" s="6">
-        <v>-7.28</v>
+        <v>-5.06</v>
       </c>
       <c r="E10" s="7">
-        <v>-0.98</v>
+        <v>1.48</v>
       </c>
     </row>
     <row r="11" spans="1:6">
       <c r="A11" s="5" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B11" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C11" s="6">
-        <v>18.53</v>
+        <v>-7.28</v>
       </c>
       <c r="D11" s="6">
-        <v>24.57</v>
-      </c>
-      <c r="E11" s="8">
-        <v>6.04</v>
+        <v>-5.6</v>
+      </c>
+      <c r="E11" s="7">
+        <v>1.68</v>
       </c>
     </row>
     <row r="12" spans="1:6">
       <c r="A12" s="5" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C12" s="6">
-        <v>-7.85</v>
+        <v>24.57</v>
       </c>
       <c r="D12" s="6">
-        <v>-7.4</v>
+        <v>24.23</v>
       </c>
       <c r="E12" s="8">
-        <v>0.45</v>
+        <v>-0.34</v>
       </c>
     </row>
     <row r="13" spans="1:6">
       <c r="A13" s="5" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B13" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C13" s="6">
-        <v>-0.3</v>
+        <v>-7.4</v>
       </c>
       <c r="D13" s="6">
-        <v>-1.65</v>
+        <v>-5.02</v>
       </c>
       <c r="E13" s="7">
-        <v>-1.35</v>
+        <v>2.38</v>
       </c>
     </row>
     <row r="14" spans="1:6">
       <c r="A14" s="5" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B14" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C14" s="6">
-        <v>-3.53</v>
+        <v>-1.65</v>
       </c>
       <c r="D14" s="6">
-        <v>-0.49</v>
-      </c>
-      <c r="E14" s="8">
-        <v>3.04</v>
+        <v>5.66</v>
+      </c>
+      <c r="E14" s="7">
+        <v>7.31</v>
       </c>
     </row>
     <row r="15" spans="1:6">
       <c r="A15" s="5" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B15" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C15" s="6">
-        <v>-4.16</v>
+        <v>-0.49</v>
       </c>
       <c r="D15" s="6">
-        <v>-5.13</v>
+        <v>0.42</v>
       </c>
       <c r="E15" s="7">
-        <v>-0.97</v>
+        <v>0.91</v>
       </c>
     </row>
     <row r="16" spans="1:6">
       <c r="A16" s="5" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B16" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C16" s="6">
-        <v>-7.72</v>
+        <v>-5.13</v>
       </c>
       <c r="D16" s="6">
-        <v>-1.03</v>
-      </c>
-      <c r="E16" s="8">
-        <v>6.69</v>
+        <v>-4.56</v>
+      </c>
+      <c r="E16" s="7">
+        <v>0.57</v>
       </c>
     </row>
     <row r="17" spans="1:5">
       <c r="A17" s="5" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="C17" s="6">
-        <v>19.7</v>
+        <v>-1.03</v>
       </c>
       <c r="D17" s="6">
-        <v>19.98</v>
+        <v>-3.75</v>
       </c>
       <c r="E17" s="8">
-        <v>0.28</v>
+        <v>-2.72</v>
       </c>
     </row>
     <row r="18" spans="1:5">
       <c r="A18" s="5" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B18" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C18" s="6">
-        <v>22.2</v>
+        <v>19.98</v>
       </c>
       <c r="D18" s="6">
-        <v>20.25</v>
+        <v>21.13</v>
       </c>
       <c r="E18" s="7">
-        <v>-1.95</v>
+        <v>1.15</v>
       </c>
     </row>
     <row r="19" spans="1:5">
       <c r="A19" s="5" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B19" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C19" s="6">
-        <v>-27.45</v>
+        <v>20.25</v>
       </c>
       <c r="D19" s="6">
-        <v>-26.89</v>
-      </c>
-      <c r="E19" s="8">
-        <v>0.5600000000000001</v>
+        <v>29.53</v>
+      </c>
+      <c r="E19" s="7">
+        <v>9.279999999999999</v>
       </c>
     </row>
     <row r="20" spans="1:5">
       <c r="A20" s="5" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B20" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C20" s="6">
-        <v>27.32</v>
+        <v>-26.89</v>
       </c>
       <c r="D20" s="6">
-        <v>26.44</v>
-      </c>
-      <c r="E20" s="7">
-        <v>-0.88</v>
+        <v>-27.54</v>
+      </c>
+      <c r="E20" s="8">
+        <v>-0.65</v>
       </c>
     </row>
     <row r="21" spans="1:5">
       <c r="A21" s="5" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B21" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C21" s="6">
-        <v>-24.03</v>
+        <v>26.44</v>
       </c>
       <c r="D21" s="6">
-        <v>-17.19</v>
-      </c>
-      <c r="E21" s="8">
-        <v>6.84</v>
+        <v>29.4</v>
+      </c>
+      <c r="E21" s="7">
+        <v>2.96</v>
       </c>
     </row>
     <row r="22" spans="1:5">
       <c r="A22" s="5" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C22" s="6">
-        <v>-1.17</v>
+        <v>-17.19</v>
       </c>
       <c r="D22" s="6">
-        <v>-1.92</v>
-      </c>
-      <c r="E22" s="7">
-        <v>-0.75</v>
+        <v>-18.97</v>
+      </c>
+      <c r="E22" s="8">
+        <v>-1.78</v>
       </c>
     </row>
     <row r="23" spans="1:5">
       <c r="A23" s="5" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B23" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C23" s="6">
-        <v>8.32</v>
+        <v>-1.92</v>
       </c>
       <c r="D23" s="6">
-        <v>6.22</v>
+        <v>0.11</v>
       </c>
       <c r="E23" s="7">
-        <v>-2.1</v>
+        <v>2.03</v>
       </c>
     </row>
     <row r="24" spans="1:5">
       <c r="A24" s="5" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B24" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C24" s="6">
-        <v>-11.11</v>
+        <v>6.22</v>
       </c>
       <c r="D24" s="6">
-        <v>-8.890000000000001</v>
-      </c>
-      <c r="E24" s="8">
-        <v>2.22</v>
+        <v>7.34</v>
+      </c>
+      <c r="E24" s="7">
+        <v>1.12</v>
       </c>
     </row>
     <row r="25" spans="1:5">
       <c r="A25" s="5" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B25" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C25" s="6">
-        <v>3.29</v>
+        <v>-8.890000000000001</v>
       </c>
       <c r="D25" s="6">
-        <v>1.1</v>
-      </c>
-      <c r="E25" s="7">
-        <v>-2.19</v>
+        <v>-8.94</v>
+      </c>
+      <c r="E25" s="8">
+        <v>-0.05</v>
       </c>
     </row>
     <row r="26" spans="1:5">
       <c r="A26" s="5" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B26" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C26" s="6">
-        <v>6.18</v>
+        <v>1.1</v>
       </c>
       <c r="D26" s="6">
-        <v>12.02</v>
-      </c>
-      <c r="E26" s="8">
-        <v>5.84</v>
+        <v>2.07</v>
+      </c>
+      <c r="E26" s="7">
+        <v>0.97</v>
       </c>
     </row>
     <row r="27" spans="1:5">
       <c r="A27" s="5" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="B27" s="5" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C27" s="6">
-        <v>-24.82</v>
+        <v>12.02</v>
       </c>
       <c r="D27" s="6">
-        <v>-24.89</v>
-      </c>
-      <c r="E27" s="7">
-        <v>-0.07000000000000001</v>
+        <v>7.63</v>
+      </c>
+      <c r="E27" s="8">
+        <v>-4.39</v>
       </c>
     </row>
     <row r="28" spans="1:5">
       <c r="A28" s="5" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B28" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C28" s="6">
-        <v>-2.17</v>
+        <v>-24.89</v>
       </c>
       <c r="D28" s="6">
-        <v>-3.8</v>
+        <v>-23.88</v>
       </c>
       <c r="E28" s="7">
-        <v>-1.63</v>
+        <v>1.01</v>
       </c>
     </row>
     <row r="29" spans="1:5">
       <c r="A29" s="5" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B29" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C29" s="6">
-        <v>-28.54</v>
+        <v>-3.8</v>
       </c>
       <c r="D29" s="6">
-        <v>-27.71</v>
-      </c>
-      <c r="E29" s="8">
-        <v>0.83</v>
+        <v>0</v>
+      </c>
+      <c r="E29" s="7">
+        <v>3.8</v>
       </c>
     </row>
     <row r="30" spans="1:5">
       <c r="A30" s="5" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B30" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C30" s="6">
-        <v>-10.55</v>
+        <v>-27.71</v>
       </c>
       <c r="D30" s="6">
-        <v>-11.48</v>
+        <v>-27.65</v>
       </c>
       <c r="E30" s="7">
-        <v>-0.93</v>
+        <v>0.06</v>
       </c>
     </row>
     <row r="31" spans="1:5">
       <c r="A31" s="5" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B31" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C31" s="6">
-        <v>-24.03</v>
+        <v>-11.48</v>
       </c>
       <c r="D31" s="6">
-        <v>-20.17</v>
-      </c>
-      <c r="E31" s="8">
-        <v>3.86</v>
+        <v>-10.39</v>
+      </c>
+      <c r="E31" s="7">
+        <v>1.09</v>
       </c>
     </row>
     <row r="32" spans="1:5">
       <c r="A32" s="5" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="B32" s="5" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C32" s="6">
-        <v>156.65</v>
+        <v>-20.17</v>
       </c>
       <c r="D32" s="6">
-        <v>156.5</v>
-      </c>
-      <c r="E32" s="7">
-        <v>-0.15</v>
+        <v>-22.1</v>
+      </c>
+      <c r="E32" s="8">
+        <v>-1.93</v>
       </c>
     </row>
     <row r="33" spans="1:5">
       <c r="A33" s="5" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B33" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C33" s="6">
-        <v>435.65</v>
+        <v>156.5</v>
       </c>
       <c r="D33" s="6">
-        <v>428.4</v>
+        <v>158.62</v>
       </c>
       <c r="E33" s="7">
-        <v>-7.25</v>
+        <v>2.12</v>
       </c>
     </row>
     <row r="34" spans="1:5">
       <c r="A34" s="5" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B34" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C34" s="6">
-        <v>381.6</v>
+        <v>428.4</v>
       </c>
       <c r="D34" s="6">
-        <v>386.05</v>
-      </c>
-      <c r="E34" s="8">
-        <v>4.45</v>
+        <v>456.15</v>
+      </c>
+      <c r="E34" s="7">
+        <v>27.75</v>
       </c>
     </row>
     <row r="35" spans="1:5">
       <c r="A35" s="5" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B35" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C35" s="6">
-        <v>956.5</v>
+        <v>386.05</v>
       </c>
       <c r="D35" s="6">
-        <v>946.5</v>
+        <v>386.35</v>
       </c>
       <c r="E35" s="7">
-        <v>-10</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="36" spans="1:5">
       <c r="A36" s="5" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B36" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C36" s="6">
-        <v>2.75</v>
+        <v>946.5</v>
       </c>
       <c r="D36" s="6">
-        <v>2.89</v>
-      </c>
-      <c r="E36" s="8">
-        <v>0.14</v>
+        <v>958.2</v>
+      </c>
+      <c r="E36" s="7">
+        <v>11.7</v>
       </c>
     </row>
     <row r="37" spans="1:5">
       <c r="A37" s="5" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="B37" s="5" t="s">
-        <v>24</v>
+        <v>2</v>
       </c>
       <c r="C37" s="6">
-        <v>29.72</v>
+        <v>2.89</v>
       </c>
       <c r="D37" s="6">
-        <v>29.57</v>
-      </c>
-      <c r="E37" s="7">
-        <v>-0.15</v>
+        <v>2.82</v>
+      </c>
+      <c r="E37" s="8">
+        <v>-0.07000000000000001</v>
       </c>
     </row>
     <row r="38" spans="1:5">
       <c r="A38" s="5" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B38" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C38" s="6">
-        <v>62.1</v>
+        <v>29.57</v>
       </c>
       <c r="D38" s="6">
-        <v>57.15</v>
+        <v>34.56</v>
       </c>
       <c r="E38" s="7">
-        <v>-4.95</v>
+        <v>4.99</v>
       </c>
     </row>
     <row r="39" spans="1:5">
       <c r="A39" s="5" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B39" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C39" s="6">
-        <v>27.76</v>
+        <v>57.15</v>
       </c>
       <c r="D39" s="6">
-        <v>35.16</v>
-      </c>
-      <c r="E39" s="8">
-        <v>7.4</v>
+        <v>67.73999999999999</v>
+      </c>
+      <c r="E39" s="7">
+        <v>10.59</v>
       </c>
     </row>
     <row r="40" spans="1:5">
       <c r="A40" s="5" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B40" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C40" s="6">
-        <v>35.57</v>
+        <v>35.16</v>
       </c>
       <c r="D40" s="6">
-        <v>33.3</v>
+        <v>35.64</v>
       </c>
       <c r="E40" s="7">
-        <v>-2.27</v>
+        <v>0.48</v>
       </c>
     </row>
     <row r="41" spans="1:5">
       <c r="A41" s="5" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B41" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C41" s="6">
-        <v>50.98</v>
+        <v>33.3</v>
       </c>
       <c r="D41" s="6">
-        <v>58.25</v>
-      </c>
-      <c r="E41" s="8">
-        <v>7.27</v>
+        <v>38.27</v>
+      </c>
+      <c r="E41" s="7">
+        <v>4.97</v>
       </c>
     </row>
     <row r="42" spans="1:5">
       <c r="A42" s="5" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="B42" s="5" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="C42" s="6">
-        <v>23.23</v>
+        <v>58.25</v>
       </c>
       <c r="D42" s="6">
-        <v>-23.7</v>
-      </c>
-      <c r="E42" s="7">
-        <v>-46.93</v>
+        <v>53.94</v>
+      </c>
+      <c r="E42" s="8">
+        <v>-4.31</v>
       </c>
     </row>
     <row r="43" spans="1:5">
       <c r="A43" s="5" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B43" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C43" s="6">
-        <v>-43.2</v>
+        <v>-23.7</v>
       </c>
       <c r="D43" s="6">
-        <v>-46.4</v>
-      </c>
-      <c r="E43" s="7">
-        <v>-3.2</v>
+        <v>-28.51</v>
+      </c>
+      <c r="E43" s="8">
+        <v>-4.81</v>
       </c>
     </row>
     <row r="44" spans="1:5">
       <c r="A44" s="5" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B44" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C44" s="6">
-        <v>-43.9</v>
+        <v>-46.4</v>
       </c>
       <c r="D44" s="6">
-        <v>-38.3</v>
-      </c>
-      <c r="E44" s="8">
-        <v>5.6</v>
+        <v>196.64</v>
+      </c>
+      <c r="E44" s="7">
+        <v>243.04</v>
       </c>
     </row>
     <row r="45" spans="1:5">
       <c r="A45" s="5" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B45" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C45" s="6">
-        <v>18.32</v>
+        <v>-38.3</v>
       </c>
       <c r="D45" s="6">
-        <v>32.87</v>
-      </c>
-      <c r="E45" s="8">
-        <v>14.55</v>
+        <v>42.35</v>
+      </c>
+      <c r="E45" s="7">
+        <v>80.65000000000001</v>
       </c>
     </row>
     <row r="46" spans="1:5">
       <c r="A46" s="5" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B46" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C46" s="6">
-        <v>-56.82</v>
+        <v>32.87</v>
       </c>
       <c r="D46" s="6">
+        <v>198.87</v>
+      </c>
+      <c r="E46" s="7">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5">
+      <c r="A47" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B47" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C47" s="6">
         <v>-42.13</v>
       </c>
-      <c r="E46" s="8">
-        <v>14.69</v>
+      <c r="D47" s="6">
+        <v>-77.47</v>
+      </c>
+      <c r="E47" s="8">
+        <v>-35.34</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A5:E5"/>
+    <mergeCell ref="A6:E6"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2405,28 +2440,28 @@
         <v>1</v>
       </c>
       <c r="B1" s="9" t="s">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="C1" s="9" t="s">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="D1" s="9" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="E1" s="9" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="F1" s="9" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="G1" s="9" t="s">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="H1" s="9" t="s">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="I1" s="9" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
     </row>
     <row r="2" spans="1:9">
@@ -2440,16 +2475,16 @@
         <v>5</v>
       </c>
       <c r="D2" s="11">
-        <v>42.7</v>
+        <v>46</v>
       </c>
       <c r="E2" s="11">
         <v>60</v>
       </c>
       <c r="F2" s="11">
-        <v>0.8</v>
+        <v>3.4</v>
       </c>
       <c r="G2" s="11">
-        <v>1.7</v>
+        <v>1.6</v>
       </c>
       <c r="H2" s="11">
         <v>59.8</v>
@@ -2574,19 +2609,19 @@
     </row>
     <row r="2" spans="1:5">
       <c r="A2" s="14">
-        <v>0.2218</v>
+        <v>0.2292</v>
       </c>
       <c r="B2" s="14">
-        <v>0.1156</v>
+        <v>0.1303</v>
       </c>
       <c r="C2" s="14">
         <v>0.0302</v>
       </c>
       <c r="D2" s="14">
-        <v>-0.0292</v>
+        <v>-0.0266</v>
       </c>
       <c r="E2" s="14">
-        <v>-0.2151</v>
+        <v>-0.2221</v>
       </c>
     </row>
   </sheetData>

--- a/HINDUJA_GROUP_Technical_Metrics.xlsx
+++ b/HINDUJA_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="224" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="218" uniqueCount="71">
   <si>
     <t>Symbol</t>
   </si>
@@ -181,34 +181,19 @@
     <t>Curr Value</t>
   </si>
   <si>
-    <t>Near 52W High</t>
-  </si>
-  <si>
-    <t>-3.8% → 0.0%</t>
-  </si>
-  <si>
-    <t>🟢 BREAKOUT WATCH</t>
-  </si>
-  <si>
-    <t>-3.8%</t>
+    <t>Left 52W High Zone</t>
+  </si>
+  <si>
+    <t>0.0% → -2.2%</t>
+  </si>
+  <si>
+    <t>⚪ NEUTRAL</t>
   </si>
   <si>
     <t>0.0%</t>
   </si>
   <si>
-    <t>RSI Oversold Recovery</t>
-  </si>
-  <si>
-    <t>29.6 → 34.6</t>
-  </si>
-  <si>
-    <t>🟢 BULLISH</t>
-  </si>
-  <si>
-    <t>29.6</t>
-  </si>
-  <si>
-    <t>34.6</t>
+    <t>-2.2%</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -260,7 +245,7 @@
     <numFmt numFmtId="166" formatCode="0.0"/>
     <numFmt numFmtId="167" formatCode="0.00%"/>
   </numFmts>
-  <fonts count="6">
+  <fonts count="7">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -294,6 +279,13 @@
     </font>
     <font>
       <sz val="11"/>
+      <color rgb="FF1F4E79"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color rgb="FF006100"/>
       <name val="Calibri"/>
       <family val="2"/>
@@ -307,7 +299,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="9">
+  <fills count="10">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -329,6 +321,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF4A6FA5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDDEBF7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -420,12 +418,12 @@
     <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="6" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
@@ -434,7 +432,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="167" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
@@ -782,7 +780,7 @@
   <cols>
     <col min="1" max="1" width="12.7109375" customWidth="1"/>
     <col min="2" max="2" width="9.7109375" customWidth="1"/>
-    <col min="3" max="3" width="8.7109375" customWidth="1"/>
+    <col min="3" max="3" width="7.7109375" customWidth="1"/>
     <col min="4" max="4" width="11.7109375" customWidth="1"/>
     <col min="5" max="5" width="10.7109375" customWidth="1"/>
     <col min="6" max="6" width="9.7109375" customWidth="1"/>
@@ -934,58 +932,58 @@
         <v>42</v>
       </c>
       <c r="C2">
-        <v>158.62</v>
+        <v>163</v>
       </c>
       <c r="D2">
-        <v>1.35</v>
+        <v>2.76</v>
       </c>
       <c r="E2">
         <v>208.37</v>
       </c>
       <c r="F2">
-        <v>130.81</v>
+        <v>131.36</v>
       </c>
       <c r="G2">
-        <v>-23.88</v>
+        <v>-21.77</v>
       </c>
       <c r="H2">
-        <v>21.26</v>
+        <v>24.09</v>
       </c>
       <c r="I2">
-        <v>-5.02</v>
+        <v>-1.88</v>
       </c>
       <c r="J2">
-        <v>-10.05</v>
+        <v>-5.83</v>
       </c>
       <c r="K2">
-        <v>0.11</v>
+        <v>4.05</v>
       </c>
       <c r="L2">
-        <v>21.13</v>
+        <v>24.61</v>
       </c>
       <c r="M2">
-        <v>22.92</v>
+        <v>23.63</v>
       </c>
       <c r="N2">
         <v>60</v>
       </c>
       <c r="O2">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="P2">
-        <v>160.33</v>
+        <v>159.7</v>
       </c>
       <c r="Q2">
-        <v>169.35</v>
+        <v>168.81</v>
       </c>
       <c r="R2">
-        <v>166.34</v>
+        <v>166.5</v>
       </c>
       <c r="S2">
-        <v>169.88</v>
+        <v>169.9</v>
       </c>
       <c r="T2">
-        <v>-6.63</v>
+        <v>-4.06</v>
       </c>
       <c r="U2" t="s">
         <v>43</v>
@@ -1000,34 +998,34 @@
         <v>1</v>
       </c>
       <c r="Y2">
-        <v>34.56</v>
+        <v>43.48</v>
       </c>
       <c r="Z2">
-        <v>-2.72</v>
+        <v>-2.63</v>
       </c>
       <c r="AA2">
-        <v>-0.6899999999999999</v>
+        <v>-1.08</v>
       </c>
       <c r="AB2">
-        <v>-2.02</v>
+        <v>-1.55</v>
       </c>
       <c r="AC2">
-        <v>5.85</v>
+        <v>22.29</v>
       </c>
       <c r="AD2">
-        <v>1.95</v>
+        <v>9.380000000000001</v>
       </c>
       <c r="AE2">
-        <v>4.37</v>
+        <v>4.39</v>
       </c>
       <c r="AF2">
-        <v>-28.51</v>
+        <v>46.95</v>
       </c>
       <c r="AG2">
-        <v>182.41</v>
+        <v>181.99</v>
       </c>
       <c r="AH2">
-        <v>156.3</v>
+        <v>155.64</v>
       </c>
       <c r="AI2">
         <v>169.79</v>
@@ -1036,7 +1034,7 @@
         <v>45</v>
       </c>
       <c r="AK2">
-        <v>35.4</v>
+        <v>33.27</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1047,10 +1045,10 @@
         <v>42</v>
       </c>
       <c r="C3">
-        <v>456.15</v>
+        <v>446.1</v>
       </c>
       <c r="D3">
-        <v>6.48</v>
+        <v>-2.2</v>
       </c>
       <c r="E3">
         <v>456.15</v>
@@ -1059,46 +1057,46 @@
         <v>225</v>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>-2.2</v>
       </c>
       <c r="H3">
-        <v>102.73</v>
+        <v>98.27</v>
       </c>
       <c r="I3">
-        <v>5.66</v>
+        <v>3.22</v>
       </c>
       <c r="J3">
-        <v>13.57</v>
+        <v>11.93</v>
       </c>
       <c r="K3">
-        <v>7.34</v>
+        <v>1.97</v>
       </c>
       <c r="L3">
-        <v>29.53</v>
+        <v>28.74</v>
       </c>
       <c r="M3">
-        <v>13.03</v>
+        <v>13.09</v>
       </c>
       <c r="N3">
         <v>99</v>
       </c>
       <c r="O3">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="P3">
-        <v>438.79</v>
+        <v>441.57</v>
       </c>
       <c r="Q3">
-        <v>414.81</v>
+        <v>417.2</v>
       </c>
       <c r="R3">
-        <v>409.63</v>
+        <v>410.35</v>
       </c>
       <c r="S3">
-        <v>333.28</v>
+        <v>333.97</v>
       </c>
       <c r="T3">
-        <v>36.87</v>
+        <v>33.57</v>
       </c>
       <c r="U3" t="s">
         <v>43</v>
@@ -1113,43 +1111,43 @@
         <v>3</v>
       </c>
       <c r="Y3">
-        <v>67.73999999999999</v>
+        <v>61.79</v>
       </c>
       <c r="Z3">
-        <v>10.15</v>
+        <v>10.7</v>
       </c>
       <c r="AA3">
-        <v>6.38</v>
+        <v>7.25</v>
       </c>
       <c r="AB3">
-        <v>3.77</v>
+        <v>3.45</v>
       </c>
       <c r="AC3">
-        <v>82.73</v>
+        <v>80.95</v>
       </c>
       <c r="AD3">
-        <v>85.19</v>
+        <v>82.14</v>
       </c>
       <c r="AE3">
-        <v>16.17</v>
+        <v>16.39</v>
       </c>
       <c r="AF3">
-        <v>196.64</v>
+        <v>21.46</v>
       </c>
       <c r="AG3">
-        <v>458.31</v>
+        <v>462.11</v>
       </c>
       <c r="AH3">
-        <v>371.3</v>
+        <v>372.29</v>
       </c>
       <c r="AI3">
-        <v>397.19</v>
+        <v>402.61</v>
       </c>
       <c r="AJ3" t="s">
         <v>46</v>
       </c>
       <c r="AK3">
-        <v>45.58</v>
+        <v>45.12</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1160,10 +1158,10 @@
         <v>42</v>
       </c>
       <c r="C4">
-        <v>386.35</v>
+        <v>379.4</v>
       </c>
       <c r="D4">
-        <v>0.08</v>
+        <v>-1.8</v>
       </c>
       <c r="E4">
         <v>534</v>
@@ -1172,46 +1170,46 @@
         <v>344.7</v>
       </c>
       <c r="G4">
-        <v>-27.65</v>
+        <v>-28.95</v>
       </c>
       <c r="H4">
-        <v>12.08</v>
+        <v>10.07</v>
       </c>
       <c r="I4">
-        <v>0.42</v>
+        <v>-1.16</v>
       </c>
       <c r="J4">
-        <v>-5.06</v>
+        <v>-7.01</v>
       </c>
       <c r="K4">
-        <v>-8.94</v>
+        <v>-10.71</v>
       </c>
       <c r="L4">
-        <v>-27.54</v>
+        <v>-28.6</v>
       </c>
       <c r="M4">
-        <v>-22.21</v>
+        <v>-21.77</v>
       </c>
       <c r="N4">
         <v>21</v>
       </c>
       <c r="O4">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="P4">
-        <v>383.86</v>
+        <v>382.97</v>
       </c>
       <c r="Q4">
-        <v>394.31</v>
+        <v>392.96</v>
       </c>
       <c r="R4">
-        <v>410.92</v>
+        <v>410.31</v>
       </c>
       <c r="S4">
-        <v>411.57</v>
+        <v>411.03</v>
       </c>
       <c r="T4">
-        <v>-6.13</v>
+        <v>-7.7</v>
       </c>
       <c r="U4" t="s">
         <v>44</v>
@@ -1226,34 +1224,34 @@
         <v>0</v>
       </c>
       <c r="Y4">
-        <v>35.64</v>
+        <v>30.1</v>
       </c>
       <c r="Z4">
-        <v>-7.55</v>
+        <v>-7.77</v>
       </c>
       <c r="AA4">
-        <v>-7.22</v>
+        <v>-7.33</v>
       </c>
       <c r="AB4">
-        <v>-0.34</v>
+        <v>-0.45</v>
       </c>
       <c r="AC4">
-        <v>39.66</v>
+        <v>45.43</v>
       </c>
       <c r="AD4">
-        <v>19.95</v>
+        <v>34.88</v>
       </c>
       <c r="AE4">
-        <v>11.18</v>
+        <v>10.98</v>
       </c>
       <c r="AF4">
-        <v>42.35</v>
+        <v>30.46</v>
       </c>
       <c r="AG4">
-        <v>410.75</v>
+        <v>409.63</v>
       </c>
       <c r="AH4">
-        <v>377.88</v>
+        <v>376.29</v>
       </c>
       <c r="AI4">
         <v>413.11</v>
@@ -1262,7 +1260,7 @@
         <v>45</v>
       </c>
       <c r="AK4">
-        <v>21.59</v>
+        <v>23.06</v>
       </c>
     </row>
     <row r="5" spans="1:37">
@@ -1273,10 +1271,10 @@
         <v>42</v>
       </c>
       <c r="C5">
-        <v>958.2</v>
+        <v>966.3</v>
       </c>
       <c r="D5">
-        <v>1.24</v>
+        <v>0.85</v>
       </c>
       <c r="E5">
         <v>1069.3</v>
@@ -1285,46 +1283,46 @@
         <v>712.75</v>
       </c>
       <c r="G5">
-        <v>-10.39</v>
+        <v>-9.630000000000001</v>
       </c>
       <c r="H5">
-        <v>34.44</v>
+        <v>35.57</v>
       </c>
       <c r="I5">
-        <v>-4.56</v>
+        <v>-2.72</v>
       </c>
       <c r="J5">
-        <v>-5.6</v>
+        <v>-4.96</v>
       </c>
       <c r="K5">
-        <v>2.07</v>
+        <v>1.99</v>
       </c>
       <c r="L5">
-        <v>29.4</v>
+        <v>30.6</v>
       </c>
       <c r="M5">
-        <v>-2.66</v>
+        <v>-1.79</v>
       </c>
       <c r="N5">
         <v>79</v>
       </c>
       <c r="O5">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="P5">
-        <v>966.54</v>
+        <v>961.14</v>
       </c>
       <c r="Q5">
-        <v>994.04</v>
+        <v>991.95</v>
       </c>
       <c r="R5">
-        <v>1008.76</v>
+        <v>1007.79</v>
       </c>
       <c r="S5">
-        <v>920.1799999999999</v>
+        <v>920.78</v>
       </c>
       <c r="T5">
-        <v>4.13</v>
+        <v>4.94</v>
       </c>
       <c r="U5" t="s">
         <v>44</v>
@@ -1339,34 +1337,34 @@
         <v>2</v>
       </c>
       <c r="Y5">
-        <v>38.27</v>
+        <v>41.51</v>
       </c>
       <c r="Z5">
-        <v>-11.75</v>
+        <v>-12.01</v>
       </c>
       <c r="AA5">
-        <v>-6</v>
+        <v>-7.2</v>
       </c>
       <c r="AB5">
-        <v>-5.75</v>
+        <v>-4.8</v>
       </c>
       <c r="AC5">
-        <v>8.35</v>
+        <v>22.16</v>
       </c>
       <c r="AD5">
-        <v>9.91</v>
+        <v>11.26</v>
       </c>
       <c r="AE5">
-        <v>20.78</v>
+        <v>20.3</v>
       </c>
       <c r="AF5">
-        <v>198.87</v>
+        <v>318.4</v>
       </c>
       <c r="AG5">
-        <v>1034.99</v>
+        <v>1034.14</v>
       </c>
       <c r="AH5">
-        <v>953.09</v>
+        <v>949.77</v>
       </c>
       <c r="AI5">
         <v>1014.05</v>
@@ -1375,7 +1373,7 @@
         <v>45</v>
       </c>
       <c r="AK5">
-        <v>21.92</v>
+        <v>22.85</v>
       </c>
     </row>
     <row r="6" spans="1:37">
@@ -1386,10 +1384,10 @@
         <v>42</v>
       </c>
       <c r="C6">
-        <v>2.82</v>
+        <v>2.78</v>
       </c>
       <c r="D6">
-        <v>-2.42</v>
+        <v>-1.42</v>
       </c>
       <c r="E6">
         <v>3.62</v>
@@ -1398,25 +1396,25 @@
         <v>1.84</v>
       </c>
       <c r="G6">
-        <v>-22.1</v>
+        <v>-23.2</v>
       </c>
       <c r="H6">
-        <v>53.26</v>
+        <v>51.09</v>
       </c>
       <c r="I6">
-        <v>-3.75</v>
+        <v>-4.14</v>
       </c>
       <c r="J6">
-        <v>24.23</v>
+        <v>23.56</v>
       </c>
       <c r="K6">
-        <v>7.63</v>
+        <v>6.51</v>
       </c>
       <c r="L6">
-        <v>-18.97</v>
+        <v>-20.57</v>
       </c>
       <c r="M6">
-        <v>3.02</v>
+        <v>3.33</v>
       </c>
       <c r="N6">
         <v>40</v>
@@ -1425,19 +1423,19 @@
         <v>60</v>
       </c>
       <c r="P6">
-        <v>2.84</v>
+        <v>2.82</v>
       </c>
       <c r="Q6">
-        <v>2.87</v>
+        <v>2.89</v>
       </c>
       <c r="R6">
-        <v>2.55</v>
+        <v>2.56</v>
       </c>
       <c r="S6">
         <v>2.67</v>
       </c>
       <c r="T6">
-        <v>5.45</v>
+        <v>4.02</v>
       </c>
       <c r="U6" t="s">
         <v>43</v>
@@ -1452,34 +1450,34 @@
         <v>2</v>
       </c>
       <c r="Y6">
-        <v>53.94</v>
+        <v>51.59</v>
       </c>
       <c r="Z6">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="AA6">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="AB6">
-        <v>-0.02</v>
+        <v>-0.03</v>
       </c>
       <c r="AC6">
-        <v>13.97</v>
+        <v>15.2</v>
       </c>
       <c r="AD6">
-        <v>7.97</v>
+        <v>13.03</v>
       </c>
       <c r="AE6">
         <v>0.16</v>
       </c>
       <c r="AF6">
-        <v>-77.47</v>
+        <v>-60.93</v>
       </c>
       <c r="AG6">
-        <v>3.21</v>
+        <v>3.09</v>
       </c>
       <c r="AH6">
-        <v>2.52</v>
+        <v>2.69</v>
       </c>
       <c r="AI6">
         <v>2.65</v>
@@ -1488,7 +1486,7 @@
         <v>46</v>
       </c>
       <c r="AK6">
-        <v>35.7</v>
+        <v>33.42</v>
       </c>
     </row>
   </sheetData>
@@ -1629,7 +1627,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F47"/>
+  <dimension ref="A1:F46"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.7109375" customWidth="1"/>
@@ -1687,736 +1685,716 @@
         <v>57</v>
       </c>
     </row>
-    <row r="4" spans="1:6">
-      <c r="A4" s="4" t="s">
+    <row r="5" spans="1:6">
+      <c r="A5" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="B5" s="2"/>
+      <c r="C5" s="2"/>
+      <c r="D5" s="2"/>
+      <c r="E5" s="2"/>
+    </row>
+    <row r="6" spans="1:6">
+      <c r="A6" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6">
+      <c r="A7" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B4" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="C4" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="D4" s="4" t="s">
-        <v>60</v>
-      </c>
-      <c r="E4" s="4" t="s">
-        <v>61</v>
-      </c>
-      <c r="F4" s="4" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6">
-      <c r="A6" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="B6" s="2"/>
-      <c r="C6" s="2"/>
-      <c r="D6" s="2"/>
-      <c r="E6" s="2"/>
-    </row>
-    <row r="7" spans="1:6">
-      <c r="A7" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="D7" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="E7" s="3" t="s">
-        <v>67</v>
+      <c r="B7" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C7" s="6">
+        <v>-10.05</v>
+      </c>
+      <c r="D7" s="6">
+        <v>-5.83</v>
+      </c>
+      <c r="E7" s="7">
+        <v>4.22</v>
       </c>
     </row>
     <row r="8" spans="1:6">
       <c r="A8" s="5" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B8" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C8" s="6">
-        <v>-11.63</v>
+        <v>13.57</v>
       </c>
       <c r="D8" s="6">
-        <v>-10.05</v>
-      </c>
-      <c r="E8" s="7">
-        <v>1.58</v>
+        <v>11.93</v>
+      </c>
+      <c r="E8" s="8">
+        <v>-1.64</v>
       </c>
     </row>
     <row r="9" spans="1:6">
       <c r="A9" s="5" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B9" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C9" s="6">
-        <v>5</v>
+        <v>-5.06</v>
       </c>
       <c r="D9" s="6">
-        <v>13.57</v>
-      </c>
-      <c r="E9" s="7">
-        <v>8.57</v>
+        <v>-7.01</v>
+      </c>
+      <c r="E9" s="8">
+        <v>-1.95</v>
       </c>
     </row>
     <row r="10" spans="1:6">
       <c r="A10" s="5" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B10" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C10" s="6">
-        <v>-6.54</v>
+        <v>-5.6</v>
       </c>
       <c r="D10" s="6">
-        <v>-5.06</v>
+        <v>-4.96</v>
       </c>
       <c r="E10" s="7">
-        <v>1.48</v>
+        <v>0.64</v>
       </c>
     </row>
     <row r="11" spans="1:6">
       <c r="A11" s="5" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B11" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C11" s="6">
-        <v>-7.28</v>
+        <v>24.23</v>
       </c>
       <c r="D11" s="6">
-        <v>-5.6</v>
-      </c>
-      <c r="E11" s="7">
-        <v>1.68</v>
+        <v>23.56</v>
+      </c>
+      <c r="E11" s="8">
+        <v>-0.67</v>
       </c>
     </row>
     <row r="12" spans="1:6">
       <c r="A12" s="5" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C12" s="6">
-        <v>24.57</v>
+        <v>-5.02</v>
       </c>
       <c r="D12" s="6">
-        <v>24.23</v>
-      </c>
-      <c r="E12" s="8">
-        <v>-0.34</v>
+        <v>-1.88</v>
+      </c>
+      <c r="E12" s="7">
+        <v>3.14</v>
       </c>
     </row>
     <row r="13" spans="1:6">
       <c r="A13" s="5" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B13" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C13" s="6">
-        <v>-7.4</v>
+        <v>5.66</v>
       </c>
       <c r="D13" s="6">
-        <v>-5.02</v>
-      </c>
-      <c r="E13" s="7">
-        <v>2.38</v>
+        <v>3.22</v>
+      </c>
+      <c r="E13" s="8">
+        <v>-2.44</v>
       </c>
     </row>
     <row r="14" spans="1:6">
       <c r="A14" s="5" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B14" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C14" s="6">
-        <v>-1.65</v>
+        <v>0.42</v>
       </c>
       <c r="D14" s="6">
-        <v>5.66</v>
-      </c>
-      <c r="E14" s="7">
-        <v>7.31</v>
+        <v>-1.16</v>
+      </c>
+      <c r="E14" s="8">
+        <v>-1.58</v>
       </c>
     </row>
     <row r="15" spans="1:6">
       <c r="A15" s="5" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B15" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C15" s="6">
-        <v>-0.49</v>
+        <v>-4.56</v>
       </c>
       <c r="D15" s="6">
-        <v>0.42</v>
+        <v>-2.72</v>
       </c>
       <c r="E15" s="7">
-        <v>0.91</v>
+        <v>1.84</v>
       </c>
     </row>
     <row r="16" spans="1:6">
       <c r="A16" s="5" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B16" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C16" s="6">
-        <v>-5.13</v>
+        <v>-3.75</v>
       </c>
       <c r="D16" s="6">
-        <v>-4.56</v>
-      </c>
-      <c r="E16" s="7">
-        <v>0.57</v>
+        <v>-4.14</v>
+      </c>
+      <c r="E16" s="8">
+        <v>-0.39</v>
       </c>
     </row>
     <row r="17" spans="1:5">
       <c r="A17" s="5" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="C17" s="6">
-        <v>-1.03</v>
+        <v>21.13</v>
       </c>
       <c r="D17" s="6">
-        <v>-3.75</v>
-      </c>
-      <c r="E17" s="8">
-        <v>-2.72</v>
+        <v>24.61</v>
+      </c>
+      <c r="E17" s="7">
+        <v>3.48</v>
       </c>
     </row>
     <row r="18" spans="1:5">
       <c r="A18" s="5" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B18" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C18" s="6">
-        <v>19.98</v>
+        <v>29.53</v>
       </c>
       <c r="D18" s="6">
-        <v>21.13</v>
-      </c>
-      <c r="E18" s="7">
-        <v>1.15</v>
+        <v>28.74</v>
+      </c>
+      <c r="E18" s="8">
+        <v>-0.79</v>
       </c>
     </row>
     <row r="19" spans="1:5">
       <c r="A19" s="5" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B19" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C19" s="6">
-        <v>20.25</v>
+        <v>-27.54</v>
       </c>
       <c r="D19" s="6">
-        <v>29.53</v>
-      </c>
-      <c r="E19" s="7">
-        <v>9.279999999999999</v>
+        <v>-28.6</v>
+      </c>
+      <c r="E19" s="8">
+        <v>-1.06</v>
       </c>
     </row>
     <row r="20" spans="1:5">
       <c r="A20" s="5" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B20" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C20" s="6">
-        <v>-26.89</v>
+        <v>29.4</v>
       </c>
       <c r="D20" s="6">
-        <v>-27.54</v>
-      </c>
-      <c r="E20" s="8">
-        <v>-0.65</v>
+        <v>30.6</v>
+      </c>
+      <c r="E20" s="7">
+        <v>1.2</v>
       </c>
     </row>
     <row r="21" spans="1:5">
       <c r="A21" s="5" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B21" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C21" s="6">
-        <v>26.44</v>
+        <v>-18.97</v>
       </c>
       <c r="D21" s="6">
-        <v>29.4</v>
-      </c>
-      <c r="E21" s="7">
-        <v>2.96</v>
+        <v>-20.57</v>
+      </c>
+      <c r="E21" s="8">
+        <v>-1.6</v>
       </c>
     </row>
     <row r="22" spans="1:5">
       <c r="A22" s="5" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C22" s="6">
-        <v>-17.19</v>
+        <v>0.11</v>
       </c>
       <c r="D22" s="6">
-        <v>-18.97</v>
-      </c>
-      <c r="E22" s="8">
-        <v>-1.78</v>
+        <v>4.05</v>
+      </c>
+      <c r="E22" s="7">
+        <v>3.94</v>
       </c>
     </row>
     <row r="23" spans="1:5">
       <c r="A23" s="5" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B23" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C23" s="6">
-        <v>-1.92</v>
+        <v>7.34</v>
       </c>
       <c r="D23" s="6">
-        <v>0.11</v>
-      </c>
-      <c r="E23" s="7">
-        <v>2.03</v>
+        <v>1.97</v>
+      </c>
+      <c r="E23" s="8">
+        <v>-5.37</v>
       </c>
     </row>
     <row r="24" spans="1:5">
       <c r="A24" s="5" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B24" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C24" s="6">
-        <v>6.22</v>
+        <v>-8.94</v>
       </c>
       <c r="D24" s="6">
-        <v>7.34</v>
-      </c>
-      <c r="E24" s="7">
-        <v>1.12</v>
+        <v>-10.71</v>
+      </c>
+      <c r="E24" s="8">
+        <v>-1.77</v>
       </c>
     </row>
     <row r="25" spans="1:5">
       <c r="A25" s="5" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B25" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C25" s="6">
-        <v>-8.890000000000001</v>
+        <v>2.07</v>
       </c>
       <c r="D25" s="6">
-        <v>-8.94</v>
+        <v>1.99</v>
       </c>
       <c r="E25" s="8">
-        <v>-0.05</v>
+        <v>-0.08</v>
       </c>
     </row>
     <row r="26" spans="1:5">
       <c r="A26" s="5" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B26" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C26" s="6">
-        <v>1.1</v>
+        <v>7.63</v>
       </c>
       <c r="D26" s="6">
-        <v>2.07</v>
-      </c>
-      <c r="E26" s="7">
-        <v>0.97</v>
+        <v>6.51</v>
+      </c>
+      <c r="E26" s="8">
+        <v>-1.12</v>
       </c>
     </row>
     <row r="27" spans="1:5">
       <c r="A27" s="5" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="B27" s="5" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C27" s="6">
-        <v>12.02</v>
+        <v>-23.88</v>
       </c>
       <c r="D27" s="6">
-        <v>7.63</v>
-      </c>
-      <c r="E27" s="8">
-        <v>-4.39</v>
+        <v>-21.77</v>
+      </c>
+      <c r="E27" s="7">
+        <v>2.11</v>
       </c>
     </row>
     <row r="28" spans="1:5">
       <c r="A28" s="5" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B28" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C28" s="6">
-        <v>-24.89</v>
+        <v>0</v>
       </c>
       <c r="D28" s="6">
-        <v>-23.88</v>
-      </c>
-      <c r="E28" s="7">
-        <v>1.01</v>
+        <v>-2.2</v>
+      </c>
+      <c r="E28" s="8">
+        <v>-2.2</v>
       </c>
     </row>
     <row r="29" spans="1:5">
       <c r="A29" s="5" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B29" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C29" s="6">
-        <v>-3.8</v>
+        <v>-27.65</v>
       </c>
       <c r="D29" s="6">
-        <v>0</v>
-      </c>
-      <c r="E29" s="7">
-        <v>3.8</v>
+        <v>-28.95</v>
+      </c>
+      <c r="E29" s="8">
+        <v>-1.3</v>
       </c>
     </row>
     <row r="30" spans="1:5">
       <c r="A30" s="5" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B30" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C30" s="6">
-        <v>-27.71</v>
+        <v>-10.39</v>
       </c>
       <c r="D30" s="6">
-        <v>-27.65</v>
+        <v>-9.630000000000001</v>
       </c>
       <c r="E30" s="7">
-        <v>0.06</v>
+        <v>0.76</v>
       </c>
     </row>
     <row r="31" spans="1:5">
       <c r="A31" s="5" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B31" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C31" s="6">
-        <v>-11.48</v>
+        <v>-22.1</v>
       </c>
       <c r="D31" s="6">
-        <v>-10.39</v>
-      </c>
-      <c r="E31" s="7">
-        <v>1.09</v>
+        <v>-23.2</v>
+      </c>
+      <c r="E31" s="8">
+        <v>-1.1</v>
       </c>
     </row>
     <row r="32" spans="1:5">
       <c r="A32" s="5" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="B32" s="5" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="C32" s="6">
-        <v>-20.17</v>
+        <v>158.62</v>
       </c>
       <c r="D32" s="6">
-        <v>-22.1</v>
-      </c>
-      <c r="E32" s="8">
-        <v>-1.93</v>
+        <v>163</v>
+      </c>
+      <c r="E32" s="7">
+        <v>4.38</v>
       </c>
     </row>
     <row r="33" spans="1:5">
       <c r="A33" s="5" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B33" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C33" s="6">
-        <v>156.5</v>
+        <v>456.15</v>
       </c>
       <c r="D33" s="6">
-        <v>158.62</v>
-      </c>
-      <c r="E33" s="7">
-        <v>2.12</v>
+        <v>446.1</v>
+      </c>
+      <c r="E33" s="8">
+        <v>-10.05</v>
       </c>
     </row>
     <row r="34" spans="1:5">
       <c r="A34" s="5" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B34" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C34" s="6">
-        <v>428.4</v>
+        <v>386.35</v>
       </c>
       <c r="D34" s="6">
-        <v>456.15</v>
-      </c>
-      <c r="E34" s="7">
-        <v>27.75</v>
+        <v>379.4</v>
+      </c>
+      <c r="E34" s="8">
+        <v>-6.95</v>
       </c>
     </row>
     <row r="35" spans="1:5">
       <c r="A35" s="5" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B35" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C35" s="6">
-        <v>386.05</v>
+        <v>958.2</v>
       </c>
       <c r="D35" s="6">
-        <v>386.35</v>
+        <v>966.3</v>
       </c>
       <c r="E35" s="7">
-        <v>0.3</v>
+        <v>8.1</v>
       </c>
     </row>
     <row r="36" spans="1:5">
       <c r="A36" s="5" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B36" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C36" s="6">
-        <v>946.5</v>
+        <v>2.82</v>
       </c>
       <c r="D36" s="6">
-        <v>958.2</v>
-      </c>
-      <c r="E36" s="7">
-        <v>11.7</v>
+        <v>2.78</v>
+      </c>
+      <c r="E36" s="8">
+        <v>-0.04</v>
       </c>
     </row>
     <row r="37" spans="1:5">
       <c r="A37" s="5" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="B37" s="5" t="s">
-        <v>2</v>
+        <v>24</v>
       </c>
       <c r="C37" s="6">
-        <v>2.89</v>
+        <v>34.56</v>
       </c>
       <c r="D37" s="6">
-        <v>2.82</v>
-      </c>
-      <c r="E37" s="8">
-        <v>-0.07000000000000001</v>
+        <v>43.48</v>
+      </c>
+      <c r="E37" s="7">
+        <v>8.92</v>
       </c>
     </row>
     <row r="38" spans="1:5">
       <c r="A38" s="5" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B38" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C38" s="6">
-        <v>29.57</v>
+        <v>67.73999999999999</v>
       </c>
       <c r="D38" s="6">
-        <v>34.56</v>
-      </c>
-      <c r="E38" s="7">
-        <v>4.99</v>
+        <v>61.79</v>
+      </c>
+      <c r="E38" s="8">
+        <v>-5.95</v>
       </c>
     </row>
     <row r="39" spans="1:5">
       <c r="A39" s="5" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B39" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C39" s="6">
-        <v>57.15</v>
+        <v>35.64</v>
       </c>
       <c r="D39" s="6">
-        <v>67.73999999999999</v>
-      </c>
-      <c r="E39" s="7">
-        <v>10.59</v>
+        <v>30.1</v>
+      </c>
+      <c r="E39" s="8">
+        <v>-5.54</v>
       </c>
     </row>
     <row r="40" spans="1:5">
       <c r="A40" s="5" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B40" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C40" s="6">
-        <v>35.16</v>
+        <v>38.27</v>
       </c>
       <c r="D40" s="6">
-        <v>35.64</v>
+        <v>41.51</v>
       </c>
       <c r="E40" s="7">
-        <v>0.48</v>
+        <v>3.24</v>
       </c>
     </row>
     <row r="41" spans="1:5">
       <c r="A41" s="5" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B41" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C41" s="6">
-        <v>33.3</v>
+        <v>53.94</v>
       </c>
       <c r="D41" s="6">
-        <v>38.27</v>
-      </c>
-      <c r="E41" s="7">
-        <v>4.97</v>
+        <v>51.59</v>
+      </c>
+      <c r="E41" s="8">
+        <v>-2.35</v>
       </c>
     </row>
     <row r="42" spans="1:5">
       <c r="A42" s="5" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="B42" s="5" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="C42" s="6">
-        <v>58.25</v>
+        <v>-28.51</v>
       </c>
       <c r="D42" s="6">
-        <v>53.94</v>
-      </c>
-      <c r="E42" s="8">
-        <v>-4.31</v>
+        <v>46.95</v>
+      </c>
+      <c r="E42" s="7">
+        <v>75.45999999999999</v>
       </c>
     </row>
     <row r="43" spans="1:5">
       <c r="A43" s="5" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B43" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C43" s="6">
-        <v>-23.7</v>
+        <v>196.64</v>
       </c>
       <c r="D43" s="6">
-        <v>-28.51</v>
+        <v>21.46</v>
       </c>
       <c r="E43" s="8">
-        <v>-4.81</v>
+        <v>-175.18</v>
       </c>
     </row>
     <row r="44" spans="1:5">
       <c r="A44" s="5" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B44" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C44" s="6">
-        <v>-46.4</v>
+        <v>42.35</v>
       </c>
       <c r="D44" s="6">
-        <v>196.64</v>
-      </c>
-      <c r="E44" s="7">
-        <v>243.04</v>
+        <v>30.46</v>
+      </c>
+      <c r="E44" s="8">
+        <v>-11.89</v>
       </c>
     </row>
     <row r="45" spans="1:5">
       <c r="A45" s="5" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B45" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C45" s="6">
-        <v>-38.3</v>
+        <v>198.87</v>
       </c>
       <c r="D45" s="6">
-        <v>42.35</v>
+        <v>318.4</v>
       </c>
       <c r="E45" s="7">
-        <v>80.65000000000001</v>
+        <v>119.53</v>
       </c>
     </row>
     <row r="46" spans="1:5">
       <c r="A46" s="5" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B46" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C46" s="6">
-        <v>32.87</v>
+        <v>-77.47</v>
       </c>
       <c r="D46" s="6">
-        <v>198.87</v>
+        <v>-60.93</v>
       </c>
       <c r="E46" s="7">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="47" spans="1:5">
-      <c r="A47" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B47" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C47" s="6">
-        <v>-42.13</v>
-      </c>
-      <c r="D47" s="6">
-        <v>-77.47</v>
-      </c>
-      <c r="E47" s="8">
-        <v>-35.34</v>
+        <v>16.54</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A6:E6"/>
+    <mergeCell ref="A5:E5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2440,28 +2418,28 @@
         <v>1</v>
       </c>
       <c r="B1" s="9" t="s">
+        <v>63</v>
+      </c>
+      <c r="C1" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="D1" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="E1" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="F1" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="G1" s="9" t="s">
         <v>68</v>
       </c>
-      <c r="C1" s="9" t="s">
+      <c r="H1" s="9" t="s">
         <v>69</v>
       </c>
-      <c r="D1" s="9" t="s">
+      <c r="I1" s="9" t="s">
         <v>70</v>
-      </c>
-      <c r="E1" s="9" t="s">
-        <v>71</v>
-      </c>
-      <c r="F1" s="9" t="s">
-        <v>72</v>
-      </c>
-      <c r="G1" s="9" t="s">
-        <v>73</v>
-      </c>
-      <c r="H1" s="9" t="s">
-        <v>74</v>
-      </c>
-      <c r="I1" s="9" t="s">
-        <v>75</v>
       </c>
     </row>
     <row r="2" spans="1:9">
@@ -2475,16 +2453,16 @@
         <v>5</v>
       </c>
       <c r="D2" s="11">
-        <v>46</v>
+        <v>45.7</v>
       </c>
       <c r="E2" s="11">
         <v>60</v>
       </c>
       <c r="F2" s="11">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="G2" s="11">
-        <v>1.6</v>
+        <v>0.8</v>
       </c>
       <c r="H2" s="11">
         <v>59.8</v>
@@ -2609,19 +2587,19 @@
     </row>
     <row r="2" spans="1:5">
       <c r="A2" s="14">
-        <v>0.2292</v>
+        <v>0.2363</v>
       </c>
       <c r="B2" s="14">
-        <v>0.1303</v>
+        <v>0.1309</v>
       </c>
       <c r="C2" s="14">
-        <v>0.0302</v>
+        <v>0.0333</v>
       </c>
       <c r="D2" s="14">
-        <v>-0.0266</v>
+        <v>-0.0179</v>
       </c>
       <c r="E2" s="14">
-        <v>-0.2221</v>
+        <v>-0.2177</v>
       </c>
     </row>
   </sheetData>

--- a/HINDUJA_GROUP_Technical_Metrics.xlsx
+++ b/HINDUJA_GROUP_Technical_Metrics.xlsx
@@ -181,19 +181,19 @@
     <t>Curr Value</t>
   </si>
   <si>
-    <t>Left 52W High Zone</t>
-  </si>
-  <si>
-    <t>0.0% → -2.2%</t>
-  </si>
-  <si>
-    <t>⚪ NEUTRAL</t>
-  </si>
-  <si>
-    <t>0.0%</t>
+    <t>Near 52W High</t>
+  </si>
+  <si>
+    <t>-2.2% → -0.6%</t>
+  </si>
+  <si>
+    <t>🟢 BREAKOUT WATCH</t>
   </si>
   <si>
     <t>-2.2%</t>
+  </si>
+  <si>
+    <t>-0.6%</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -245,7 +245,7 @@
     <numFmt numFmtId="166" formatCode="0.0"/>
     <numFmt numFmtId="167" formatCode="0.00%"/>
   </numFmts>
-  <fonts count="7">
+  <fonts count="6">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -279,13 +279,6 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF1F4E79"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
       <color rgb="FF006100"/>
       <name val="Calibri"/>
       <family val="2"/>
@@ -299,7 +292,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="10">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -321,12 +314,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF4A6FA5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDDEBF7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -419,11 +406,11 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="6" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
@@ -432,7 +419,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="167" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
@@ -780,7 +767,7 @@
   <cols>
     <col min="1" max="1" width="12.7109375" customWidth="1"/>
     <col min="2" max="2" width="9.7109375" customWidth="1"/>
-    <col min="3" max="3" width="7.7109375" customWidth="1"/>
+    <col min="3" max="3" width="8.7109375" customWidth="1"/>
     <col min="4" max="4" width="11.7109375" customWidth="1"/>
     <col min="5" max="5" width="10.7109375" customWidth="1"/>
     <col min="6" max="6" width="9.7109375" customWidth="1"/>
@@ -932,10 +919,10 @@
         <v>42</v>
       </c>
       <c r="C2">
-        <v>163</v>
+        <v>161.75</v>
       </c>
       <c r="D2">
-        <v>2.76</v>
+        <v>-0.77</v>
       </c>
       <c r="E2">
         <v>208.37</v>
@@ -944,25 +931,25 @@
         <v>131.36</v>
       </c>
       <c r="G2">
-        <v>-21.77</v>
+        <v>-22.37</v>
       </c>
       <c r="H2">
-        <v>24.09</v>
+        <v>23.13</v>
       </c>
       <c r="I2">
-        <v>-1.88</v>
+        <v>-1.22</v>
       </c>
       <c r="J2">
-        <v>-5.83</v>
+        <v>-6.93</v>
       </c>
       <c r="K2">
-        <v>4.05</v>
+        <v>2.9</v>
       </c>
       <c r="L2">
-        <v>24.61</v>
+        <v>23.11</v>
       </c>
       <c r="M2">
-        <v>23.63</v>
+        <v>23.06</v>
       </c>
       <c r="N2">
         <v>60</v>
@@ -971,19 +958,19 @@
         <v>74</v>
       </c>
       <c r="P2">
-        <v>159.7</v>
+        <v>159.3</v>
       </c>
       <c r="Q2">
-        <v>168.81</v>
+        <v>168.25</v>
       </c>
       <c r="R2">
-        <v>166.5</v>
+        <v>166.58</v>
       </c>
       <c r="S2">
-        <v>169.9</v>
+        <v>169.92</v>
       </c>
       <c r="T2">
-        <v>-4.06</v>
+        <v>-4.81</v>
       </c>
       <c r="U2" t="s">
         <v>43</v>
@@ -998,34 +985,34 @@
         <v>1</v>
       </c>
       <c r="Y2">
-        <v>43.48</v>
+        <v>41.73</v>
       </c>
       <c r="Z2">
         <v>-2.63</v>
       </c>
       <c r="AA2">
-        <v>-1.08</v>
+        <v>-1.39</v>
       </c>
       <c r="AB2">
-        <v>-1.55</v>
+        <v>-1.24</v>
       </c>
       <c r="AC2">
-        <v>22.29</v>
+        <v>43.64</v>
       </c>
       <c r="AD2">
-        <v>9.380000000000001</v>
+        <v>23.92</v>
       </c>
       <c r="AE2">
-        <v>4.39</v>
+        <v>4.24</v>
       </c>
       <c r="AF2">
-        <v>46.95</v>
+        <v>-35.88</v>
       </c>
       <c r="AG2">
-        <v>181.99</v>
+        <v>181.63</v>
       </c>
       <c r="AH2">
-        <v>155.64</v>
+        <v>154.87</v>
       </c>
       <c r="AI2">
         <v>169.79</v>
@@ -1034,7 +1021,7 @@
         <v>45</v>
       </c>
       <c r="AK2">
-        <v>33.27</v>
+        <v>31.35</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1045,10 +1032,10 @@
         <v>42</v>
       </c>
       <c r="C3">
-        <v>446.1</v>
+        <v>453.45</v>
       </c>
       <c r="D3">
-        <v>-2.2</v>
+        <v>1.65</v>
       </c>
       <c r="E3">
         <v>456.15</v>
@@ -1057,46 +1044,46 @@
         <v>225</v>
       </c>
       <c r="G3">
-        <v>-2.2</v>
+        <v>-0.59</v>
       </c>
       <c r="H3">
-        <v>98.27</v>
+        <v>101.53</v>
       </c>
       <c r="I3">
-        <v>3.22</v>
+        <v>2.7</v>
       </c>
       <c r="J3">
-        <v>11.93</v>
+        <v>13.86</v>
       </c>
       <c r="K3">
-        <v>1.97</v>
+        <v>1.83</v>
       </c>
       <c r="L3">
-        <v>28.74</v>
+        <v>21.76</v>
       </c>
       <c r="M3">
-        <v>13.09</v>
+        <v>13.45</v>
       </c>
       <c r="N3">
         <v>99</v>
       </c>
       <c r="O3">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="P3">
-        <v>441.57</v>
+        <v>443.95</v>
       </c>
       <c r="Q3">
-        <v>417.2</v>
+        <v>419.84</v>
       </c>
       <c r="R3">
-        <v>410.35</v>
+        <v>411.3</v>
       </c>
       <c r="S3">
-        <v>333.97</v>
+        <v>334.73</v>
       </c>
       <c r="T3">
-        <v>33.57</v>
+        <v>35.47</v>
       </c>
       <c r="U3" t="s">
         <v>43</v>
@@ -1111,34 +1098,34 @@
         <v>3</v>
       </c>
       <c r="Y3">
-        <v>61.79</v>
+        <v>64.26000000000001</v>
       </c>
       <c r="Z3">
-        <v>10.7</v>
+        <v>11.6</v>
       </c>
       <c r="AA3">
-        <v>7.25</v>
+        <v>8.119999999999999</v>
       </c>
       <c r="AB3">
-        <v>3.45</v>
+        <v>3.48</v>
       </c>
       <c r="AC3">
-        <v>80.95</v>
+        <v>88.45</v>
       </c>
       <c r="AD3">
-        <v>82.14</v>
+        <v>84.04000000000001</v>
       </c>
       <c r="AE3">
-        <v>16.39</v>
+        <v>16.13</v>
       </c>
       <c r="AF3">
-        <v>21.46</v>
+        <v>53.54</v>
       </c>
       <c r="AG3">
-        <v>462.11</v>
+        <v>466.81</v>
       </c>
       <c r="AH3">
-        <v>372.29</v>
+        <v>372.87</v>
       </c>
       <c r="AI3">
         <v>402.61</v>
@@ -1147,7 +1134,7 @@
         <v>46</v>
       </c>
       <c r="AK3">
-        <v>45.12</v>
+        <v>44.69</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1158,10 +1145,10 @@
         <v>42</v>
       </c>
       <c r="C4">
-        <v>379.4</v>
+        <v>377.8</v>
       </c>
       <c r="D4">
-        <v>-1.8</v>
+        <v>-0.42</v>
       </c>
       <c r="E4">
         <v>534</v>
@@ -1170,46 +1157,46 @@
         <v>344.7</v>
       </c>
       <c r="G4">
-        <v>-28.95</v>
+        <v>-29.25</v>
       </c>
       <c r="H4">
-        <v>10.07</v>
+        <v>9.6</v>
       </c>
       <c r="I4">
-        <v>-1.16</v>
+        <v>-0.96</v>
       </c>
       <c r="J4">
-        <v>-7.01</v>
+        <v>-7.06</v>
       </c>
       <c r="K4">
-        <v>-10.71</v>
+        <v>-12.83</v>
       </c>
       <c r="L4">
-        <v>-28.6</v>
+        <v>-28.03</v>
       </c>
       <c r="M4">
-        <v>-21.77</v>
+        <v>-21.71</v>
       </c>
       <c r="N4">
         <v>21</v>
       </c>
       <c r="O4">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="P4">
-        <v>382.97</v>
+        <v>382.24</v>
       </c>
       <c r="Q4">
-        <v>392.96</v>
+        <v>391.74</v>
       </c>
       <c r="R4">
-        <v>410.31</v>
+        <v>409.61</v>
       </c>
       <c r="S4">
-        <v>411.03</v>
+        <v>410.56</v>
       </c>
       <c r="T4">
-        <v>-7.7</v>
+        <v>-7.98</v>
       </c>
       <c r="U4" t="s">
         <v>44</v>
@@ -1224,43 +1211,43 @@
         <v>0</v>
       </c>
       <c r="Y4">
-        <v>30.1</v>
+        <v>28.98</v>
       </c>
       <c r="Z4">
-        <v>-7.77</v>
+        <v>-7.99</v>
       </c>
       <c r="AA4">
-        <v>-7.33</v>
+        <v>-7.46</v>
       </c>
       <c r="AB4">
-        <v>-0.45</v>
+        <v>-0.53</v>
       </c>
       <c r="AC4">
-        <v>45.43</v>
+        <v>30.16</v>
       </c>
       <c r="AD4">
-        <v>34.88</v>
+        <v>38.42</v>
       </c>
       <c r="AE4">
-        <v>10.98</v>
+        <v>10.83</v>
       </c>
       <c r="AF4">
-        <v>30.46</v>
+        <v>-48.73</v>
       </c>
       <c r="AG4">
-        <v>409.63</v>
+        <v>409.11</v>
       </c>
       <c r="AH4">
-        <v>376.29</v>
+        <v>374.36</v>
       </c>
       <c r="AI4">
-        <v>413.11</v>
+        <v>412.97</v>
       </c>
       <c r="AJ4" t="s">
         <v>45</v>
       </c>
       <c r="AK4">
-        <v>23.06</v>
+        <v>25.01</v>
       </c>
     </row>
     <row r="5" spans="1:37">
@@ -1271,10 +1258,10 @@
         <v>42</v>
       </c>
       <c r="C5">
-        <v>966.3</v>
+        <v>956</v>
       </c>
       <c r="D5">
-        <v>0.85</v>
+        <v>-1.07</v>
       </c>
       <c r="E5">
         <v>1069.3</v>
@@ -1283,46 +1270,46 @@
         <v>712.75</v>
       </c>
       <c r="G5">
-        <v>-9.630000000000001</v>
+        <v>-10.6</v>
       </c>
       <c r="H5">
-        <v>35.57</v>
+        <v>34.13</v>
       </c>
       <c r="I5">
-        <v>-2.72</v>
+        <v>-2.27</v>
       </c>
       <c r="J5">
-        <v>-4.96</v>
+        <v>-5.16</v>
       </c>
       <c r="K5">
-        <v>1.99</v>
+        <v>3.79</v>
       </c>
       <c r="L5">
-        <v>30.6</v>
+        <v>28.8</v>
       </c>
       <c r="M5">
-        <v>-1.79</v>
+        <v>-2.84</v>
       </c>
       <c r="N5">
         <v>79</v>
       </c>
       <c r="O5">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="P5">
-        <v>961.14</v>
+        <v>956.7</v>
       </c>
       <c r="Q5">
-        <v>991.95</v>
+        <v>989.48</v>
       </c>
       <c r="R5">
-        <v>1007.79</v>
+        <v>1006.59</v>
       </c>
       <c r="S5">
-        <v>920.78</v>
+        <v>921.3099999999999</v>
       </c>
       <c r="T5">
-        <v>4.94</v>
+        <v>3.77</v>
       </c>
       <c r="U5" t="s">
         <v>44</v>
@@ -1337,34 +1324,34 @@
         <v>2</v>
       </c>
       <c r="Y5">
-        <v>41.51</v>
+        <v>38.72</v>
       </c>
       <c r="Z5">
-        <v>-12.01</v>
+        <v>-12.89</v>
       </c>
       <c r="AA5">
-        <v>-7.2</v>
+        <v>-8.34</v>
       </c>
       <c r="AB5">
-        <v>-4.8</v>
+        <v>-4.55</v>
       </c>
       <c r="AC5">
-        <v>22.16</v>
+        <v>32.44</v>
       </c>
       <c r="AD5">
-        <v>11.26</v>
+        <v>20.98</v>
       </c>
       <c r="AE5">
-        <v>20.3</v>
+        <v>19.58</v>
       </c>
       <c r="AF5">
-        <v>318.4</v>
+        <v>-66.77</v>
       </c>
       <c r="AG5">
-        <v>1034.14</v>
+        <v>1034.05</v>
       </c>
       <c r="AH5">
-        <v>949.77</v>
+        <v>944.9</v>
       </c>
       <c r="AI5">
         <v>1014.05</v>
@@ -1373,7 +1360,7 @@
         <v>45</v>
       </c>
       <c r="AK5">
-        <v>22.85</v>
+        <v>23.65</v>
       </c>
     </row>
     <row r="6" spans="1:37">
@@ -1384,10 +1371,10 @@
         <v>42</v>
       </c>
       <c r="C6">
-        <v>2.78</v>
+        <v>2.79</v>
       </c>
       <c r="D6">
-        <v>-1.42</v>
+        <v>0.36</v>
       </c>
       <c r="E6">
         <v>3.62</v>
@@ -1396,25 +1383,25 @@
         <v>1.84</v>
       </c>
       <c r="G6">
-        <v>-23.2</v>
+        <v>-22.93</v>
       </c>
       <c r="H6">
-        <v>51.09</v>
+        <v>51.63</v>
       </c>
       <c r="I6">
-        <v>-4.14</v>
+        <v>-2.45</v>
       </c>
       <c r="J6">
-        <v>23.56</v>
+        <v>23.45</v>
       </c>
       <c r="K6">
-        <v>6.51</v>
+        <v>11.16</v>
       </c>
       <c r="L6">
-        <v>-20.57</v>
+        <v>-20.96</v>
       </c>
       <c r="M6">
-        <v>3.33</v>
+        <v>3.49</v>
       </c>
       <c r="N6">
         <v>40</v>
@@ -1423,19 +1410,19 @@
         <v>60</v>
       </c>
       <c r="P6">
-        <v>2.82</v>
+        <v>2.81</v>
       </c>
       <c r="Q6">
-        <v>2.89</v>
+        <v>2.9</v>
       </c>
       <c r="R6">
-        <v>2.56</v>
+        <v>2.57</v>
       </c>
       <c r="S6">
         <v>2.67</v>
       </c>
       <c r="T6">
-        <v>4.02</v>
+        <v>4.45</v>
       </c>
       <c r="U6" t="s">
         <v>43</v>
@@ -1450,10 +1437,10 @@
         <v>2</v>
       </c>
       <c r="Y6">
-        <v>51.59</v>
+        <v>52.16</v>
       </c>
       <c r="Z6">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="AA6">
         <v>0.1</v>
@@ -1462,22 +1449,22 @@
         <v>-0.03</v>
       </c>
       <c r="AC6">
-        <v>15.2</v>
+        <v>7.61</v>
       </c>
       <c r="AD6">
-        <v>13.03</v>
+        <v>12.26</v>
       </c>
       <c r="AE6">
         <v>0.16</v>
       </c>
       <c r="AF6">
-        <v>-60.93</v>
+        <v>-66.13</v>
       </c>
       <c r="AG6">
-        <v>3.09</v>
+        <v>3.08</v>
       </c>
       <c r="AH6">
-        <v>2.69</v>
+        <v>2.71</v>
       </c>
       <c r="AI6">
         <v>2.65</v>
@@ -1486,7 +1473,7 @@
         <v>46</v>
       </c>
       <c r="AK6">
-        <v>33.42</v>
+        <v>31.15</v>
       </c>
     </row>
   </sheetData>
@@ -1719,13 +1706,13 @@
         <v>9</v>
       </c>
       <c r="C7" s="6">
-        <v>-10.05</v>
+        <v>-5.83</v>
       </c>
       <c r="D7" s="6">
-        <v>-5.83</v>
+        <v>-6.93</v>
       </c>
       <c r="E7" s="7">
-        <v>4.22</v>
+        <v>-1.1</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -1736,13 +1723,13 @@
         <v>9</v>
       </c>
       <c r="C8" s="6">
-        <v>13.57</v>
+        <v>11.93</v>
       </c>
       <c r="D8" s="6">
-        <v>11.93</v>
+        <v>13.86</v>
       </c>
       <c r="E8" s="8">
-        <v>-1.64</v>
+        <v>1.93</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -1753,13 +1740,13 @@
         <v>9</v>
       </c>
       <c r="C9" s="6">
-        <v>-5.06</v>
+        <v>-7.01</v>
       </c>
       <c r="D9" s="6">
-        <v>-7.01</v>
-      </c>
-      <c r="E9" s="8">
-        <v>-1.95</v>
+        <v>-7.06</v>
+      </c>
+      <c r="E9" s="7">
+        <v>-0.05</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -1770,13 +1757,13 @@
         <v>9</v>
       </c>
       <c r="C10" s="6">
-        <v>-5.6</v>
+        <v>-4.96</v>
       </c>
       <c r="D10" s="6">
-        <v>-4.96</v>
+        <v>-5.16</v>
       </c>
       <c r="E10" s="7">
-        <v>0.64</v>
+        <v>-0.2</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -1787,13 +1774,13 @@
         <v>9</v>
       </c>
       <c r="C11" s="6">
-        <v>24.23</v>
+        <v>23.56</v>
       </c>
       <c r="D11" s="6">
-        <v>23.56</v>
-      </c>
-      <c r="E11" s="8">
-        <v>-0.67</v>
+        <v>23.45</v>
+      </c>
+      <c r="E11" s="7">
+        <v>-0.11</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -1804,13 +1791,13 @@
         <v>8</v>
       </c>
       <c r="C12" s="6">
-        <v>-5.02</v>
+        <v>-1.88</v>
       </c>
       <c r="D12" s="6">
-        <v>-1.88</v>
-      </c>
-      <c r="E12" s="7">
-        <v>3.14</v>
+        <v>-1.22</v>
+      </c>
+      <c r="E12" s="8">
+        <v>0.66</v>
       </c>
     </row>
     <row r="13" spans="1:6">
@@ -1821,13 +1808,13 @@
         <v>8</v>
       </c>
       <c r="C13" s="6">
-        <v>5.66</v>
+        <v>3.22</v>
       </c>
       <c r="D13" s="6">
-        <v>3.22</v>
-      </c>
-      <c r="E13" s="8">
-        <v>-2.44</v>
+        <v>2.7</v>
+      </c>
+      <c r="E13" s="7">
+        <v>-0.52</v>
       </c>
     </row>
     <row r="14" spans="1:6">
@@ -1838,13 +1825,13 @@
         <v>8</v>
       </c>
       <c r="C14" s="6">
-        <v>0.42</v>
+        <v>-1.16</v>
       </c>
       <c r="D14" s="6">
-        <v>-1.16</v>
+        <v>-0.96</v>
       </c>
       <c r="E14" s="8">
-        <v>-1.58</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="15" spans="1:6">
@@ -1855,13 +1842,13 @@
         <v>8</v>
       </c>
       <c r="C15" s="6">
-        <v>-4.56</v>
+        <v>-2.72</v>
       </c>
       <c r="D15" s="6">
-        <v>-2.72</v>
-      </c>
-      <c r="E15" s="7">
-        <v>1.84</v>
+        <v>-2.27</v>
+      </c>
+      <c r="E15" s="8">
+        <v>0.45</v>
       </c>
     </row>
     <row r="16" spans="1:6">
@@ -1872,13 +1859,13 @@
         <v>8</v>
       </c>
       <c r="C16" s="6">
-        <v>-3.75</v>
+        <v>-4.14</v>
       </c>
       <c r="D16" s="6">
-        <v>-4.14</v>
+        <v>-2.45</v>
       </c>
       <c r="E16" s="8">
-        <v>-0.39</v>
+        <v>1.69</v>
       </c>
     </row>
     <row r="17" spans="1:5">
@@ -1889,13 +1876,13 @@
         <v>11</v>
       </c>
       <c r="C17" s="6">
-        <v>21.13</v>
+        <v>24.61</v>
       </c>
       <c r="D17" s="6">
-        <v>24.61</v>
+        <v>23.11</v>
       </c>
       <c r="E17" s="7">
-        <v>3.48</v>
+        <v>-1.5</v>
       </c>
     </row>
     <row r="18" spans="1:5">
@@ -1906,13 +1893,13 @@
         <v>11</v>
       </c>
       <c r="C18" s="6">
-        <v>29.53</v>
+        <v>28.74</v>
       </c>
       <c r="D18" s="6">
-        <v>28.74</v>
-      </c>
-      <c r="E18" s="8">
-        <v>-0.79</v>
+        <v>21.76</v>
+      </c>
+      <c r="E18" s="7">
+        <v>-6.98</v>
       </c>
     </row>
     <row r="19" spans="1:5">
@@ -1923,13 +1910,13 @@
         <v>11</v>
       </c>
       <c r="C19" s="6">
-        <v>-27.54</v>
+        <v>-28.6</v>
       </c>
       <c r="D19" s="6">
-        <v>-28.6</v>
+        <v>-28.03</v>
       </c>
       <c r="E19" s="8">
-        <v>-1.06</v>
+        <v>0.57</v>
       </c>
     </row>
     <row r="20" spans="1:5">
@@ -1940,13 +1927,13 @@
         <v>11</v>
       </c>
       <c r="C20" s="6">
-        <v>29.4</v>
+        <v>30.6</v>
       </c>
       <c r="D20" s="6">
-        <v>30.6</v>
+        <v>28.8</v>
       </c>
       <c r="E20" s="7">
-        <v>1.2</v>
+        <v>-1.8</v>
       </c>
     </row>
     <row r="21" spans="1:5">
@@ -1957,13 +1944,13 @@
         <v>11</v>
       </c>
       <c r="C21" s="6">
-        <v>-18.97</v>
+        <v>-20.57</v>
       </c>
       <c r="D21" s="6">
-        <v>-20.57</v>
-      </c>
-      <c r="E21" s="8">
-        <v>-1.6</v>
+        <v>-20.96</v>
+      </c>
+      <c r="E21" s="7">
+        <v>-0.39</v>
       </c>
     </row>
     <row r="22" spans="1:5">
@@ -1974,13 +1961,13 @@
         <v>10</v>
       </c>
       <c r="C22" s="6">
-        <v>0.11</v>
+        <v>4.05</v>
       </c>
       <c r="D22" s="6">
-        <v>4.05</v>
+        <v>2.9</v>
       </c>
       <c r="E22" s="7">
-        <v>3.94</v>
+        <v>-1.15</v>
       </c>
     </row>
     <row r="23" spans="1:5">
@@ -1991,13 +1978,13 @@
         <v>10</v>
       </c>
       <c r="C23" s="6">
-        <v>7.34</v>
+        <v>1.97</v>
       </c>
       <c r="D23" s="6">
-        <v>1.97</v>
-      </c>
-      <c r="E23" s="8">
-        <v>-5.37</v>
+        <v>1.83</v>
+      </c>
+      <c r="E23" s="7">
+        <v>-0.14</v>
       </c>
     </row>
     <row r="24" spans="1:5">
@@ -2008,13 +1995,13 @@
         <v>10</v>
       </c>
       <c r="C24" s="6">
-        <v>-8.94</v>
+        <v>-10.71</v>
       </c>
       <c r="D24" s="6">
-        <v>-10.71</v>
-      </c>
-      <c r="E24" s="8">
-        <v>-1.77</v>
+        <v>-12.83</v>
+      </c>
+      <c r="E24" s="7">
+        <v>-2.12</v>
       </c>
     </row>
     <row r="25" spans="1:5">
@@ -2025,13 +2012,13 @@
         <v>10</v>
       </c>
       <c r="C25" s="6">
-        <v>2.07</v>
+        <v>1.99</v>
       </c>
       <c r="D25" s="6">
-        <v>1.99</v>
+        <v>3.79</v>
       </c>
       <c r="E25" s="8">
-        <v>-0.08</v>
+        <v>1.8</v>
       </c>
     </row>
     <row r="26" spans="1:5">
@@ -2042,13 +2029,13 @@
         <v>10</v>
       </c>
       <c r="C26" s="6">
-        <v>7.63</v>
+        <v>6.51</v>
       </c>
       <c r="D26" s="6">
-        <v>6.51</v>
+        <v>11.16</v>
       </c>
       <c r="E26" s="8">
-        <v>-1.12</v>
+        <v>4.65</v>
       </c>
     </row>
     <row r="27" spans="1:5">
@@ -2059,13 +2046,13 @@
         <v>6</v>
       </c>
       <c r="C27" s="6">
-        <v>-23.88</v>
+        <v>-21.77</v>
       </c>
       <c r="D27" s="6">
-        <v>-21.77</v>
+        <v>-22.37</v>
       </c>
       <c r="E27" s="7">
-        <v>2.11</v>
+        <v>-0.6</v>
       </c>
     </row>
     <row r="28" spans="1:5">
@@ -2076,13 +2063,13 @@
         <v>6</v>
       </c>
       <c r="C28" s="6">
-        <v>0</v>
+        <v>-2.2</v>
       </c>
       <c r="D28" s="6">
-        <v>-2.2</v>
+        <v>-0.59</v>
       </c>
       <c r="E28" s="8">
-        <v>-2.2</v>
+        <v>1.61</v>
       </c>
     </row>
     <row r="29" spans="1:5">
@@ -2093,13 +2080,13 @@
         <v>6</v>
       </c>
       <c r="C29" s="6">
-        <v>-27.65</v>
+        <v>-28.95</v>
       </c>
       <c r="D29" s="6">
-        <v>-28.95</v>
-      </c>
-      <c r="E29" s="8">
-        <v>-1.3</v>
+        <v>-29.25</v>
+      </c>
+      <c r="E29" s="7">
+        <v>-0.3</v>
       </c>
     </row>
     <row r="30" spans="1:5">
@@ -2110,13 +2097,13 @@
         <v>6</v>
       </c>
       <c r="C30" s="6">
-        <v>-10.39</v>
+        <v>-9.630000000000001</v>
       </c>
       <c r="D30" s="6">
-        <v>-9.630000000000001</v>
+        <v>-10.6</v>
       </c>
       <c r="E30" s="7">
-        <v>0.76</v>
+        <v>-0.97</v>
       </c>
     </row>
     <row r="31" spans="1:5">
@@ -2127,13 +2114,13 @@
         <v>6</v>
       </c>
       <c r="C31" s="6">
-        <v>-22.1</v>
+        <v>-23.2</v>
       </c>
       <c r="D31" s="6">
-        <v>-23.2</v>
+        <v>-22.93</v>
       </c>
       <c r="E31" s="8">
-        <v>-1.1</v>
+        <v>0.27</v>
       </c>
     </row>
     <row r="32" spans="1:5">
@@ -2144,13 +2131,13 @@
         <v>2</v>
       </c>
       <c r="C32" s="6">
-        <v>158.62</v>
+        <v>163</v>
       </c>
       <c r="D32" s="6">
-        <v>163</v>
+        <v>161.75</v>
       </c>
       <c r="E32" s="7">
-        <v>4.38</v>
+        <v>-1.25</v>
       </c>
     </row>
     <row r="33" spans="1:5">
@@ -2161,13 +2148,13 @@
         <v>2</v>
       </c>
       <c r="C33" s="6">
-        <v>456.15</v>
+        <v>446.1</v>
       </c>
       <c r="D33" s="6">
-        <v>446.1</v>
+        <v>453.45</v>
       </c>
       <c r="E33" s="8">
-        <v>-10.05</v>
+        <v>7.35</v>
       </c>
     </row>
     <row r="34" spans="1:5">
@@ -2178,13 +2165,13 @@
         <v>2</v>
       </c>
       <c r="C34" s="6">
-        <v>386.35</v>
+        <v>379.4</v>
       </c>
       <c r="D34" s="6">
-        <v>379.4</v>
-      </c>
-      <c r="E34" s="8">
-        <v>-6.95</v>
+        <v>377.8</v>
+      </c>
+      <c r="E34" s="7">
+        <v>-1.6</v>
       </c>
     </row>
     <row r="35" spans="1:5">
@@ -2195,13 +2182,13 @@
         <v>2</v>
       </c>
       <c r="C35" s="6">
-        <v>958.2</v>
+        <v>966.3</v>
       </c>
       <c r="D35" s="6">
-        <v>966.3</v>
+        <v>956</v>
       </c>
       <c r="E35" s="7">
-        <v>8.1</v>
+        <v>-10.3</v>
       </c>
     </row>
     <row r="36" spans="1:5">
@@ -2212,13 +2199,13 @@
         <v>2</v>
       </c>
       <c r="C36" s="6">
-        <v>2.82</v>
+        <v>2.78</v>
       </c>
       <c r="D36" s="6">
-        <v>2.78</v>
+        <v>2.79</v>
       </c>
       <c r="E36" s="8">
-        <v>-0.04</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="37" spans="1:5">
@@ -2229,13 +2216,13 @@
         <v>24</v>
       </c>
       <c r="C37" s="6">
-        <v>34.56</v>
+        <v>43.48</v>
       </c>
       <c r="D37" s="6">
-        <v>43.48</v>
+        <v>41.73</v>
       </c>
       <c r="E37" s="7">
-        <v>8.92</v>
+        <v>-1.75</v>
       </c>
     </row>
     <row r="38" spans="1:5">
@@ -2246,13 +2233,13 @@
         <v>24</v>
       </c>
       <c r="C38" s="6">
-        <v>67.73999999999999</v>
+        <v>61.79</v>
       </c>
       <c r="D38" s="6">
-        <v>61.79</v>
+        <v>64.26000000000001</v>
       </c>
       <c r="E38" s="8">
-        <v>-5.95</v>
+        <v>2.47</v>
       </c>
     </row>
     <row r="39" spans="1:5">
@@ -2263,13 +2250,13 @@
         <v>24</v>
       </c>
       <c r="C39" s="6">
-        <v>35.64</v>
+        <v>30.1</v>
       </c>
       <c r="D39" s="6">
-        <v>30.1</v>
-      </c>
-      <c r="E39" s="8">
-        <v>-5.54</v>
+        <v>28.98</v>
+      </c>
+      <c r="E39" s="7">
+        <v>-1.12</v>
       </c>
     </row>
     <row r="40" spans="1:5">
@@ -2280,13 +2267,13 @@
         <v>24</v>
       </c>
       <c r="C40" s="6">
-        <v>38.27</v>
+        <v>41.51</v>
       </c>
       <c r="D40" s="6">
-        <v>41.51</v>
+        <v>38.72</v>
       </c>
       <c r="E40" s="7">
-        <v>3.24</v>
+        <v>-2.79</v>
       </c>
     </row>
     <row r="41" spans="1:5">
@@ -2297,13 +2284,13 @@
         <v>24</v>
       </c>
       <c r="C41" s="6">
-        <v>53.94</v>
+        <v>51.59</v>
       </c>
       <c r="D41" s="6">
-        <v>51.59</v>
+        <v>52.16</v>
       </c>
       <c r="E41" s="8">
-        <v>-2.35</v>
+        <v>0.57</v>
       </c>
     </row>
     <row r="42" spans="1:5">
@@ -2314,13 +2301,13 @@
         <v>31</v>
       </c>
       <c r="C42" s="6">
-        <v>-28.51</v>
+        <v>46.95</v>
       </c>
       <c r="D42" s="6">
-        <v>46.95</v>
+        <v>-35.88</v>
       </c>
       <c r="E42" s="7">
-        <v>75.45999999999999</v>
+        <v>-82.83</v>
       </c>
     </row>
     <row r="43" spans="1:5">
@@ -2331,13 +2318,13 @@
         <v>31</v>
       </c>
       <c r="C43" s="6">
-        <v>196.64</v>
+        <v>21.46</v>
       </c>
       <c r="D43" s="6">
-        <v>21.46</v>
+        <v>53.54</v>
       </c>
       <c r="E43" s="8">
-        <v>-175.18</v>
+        <v>32.08</v>
       </c>
     </row>
     <row r="44" spans="1:5">
@@ -2348,13 +2335,13 @@
         <v>31</v>
       </c>
       <c r="C44" s="6">
-        <v>42.35</v>
+        <v>30.46</v>
       </c>
       <c r="D44" s="6">
-        <v>30.46</v>
-      </c>
-      <c r="E44" s="8">
-        <v>-11.89</v>
+        <v>-48.73</v>
+      </c>
+      <c r="E44" s="7">
+        <v>-79.19</v>
       </c>
     </row>
     <row r="45" spans="1:5">
@@ -2365,13 +2352,13 @@
         <v>31</v>
       </c>
       <c r="C45" s="6">
-        <v>198.87</v>
+        <v>318.4</v>
       </c>
       <c r="D45" s="6">
-        <v>318.4</v>
+        <v>-66.77</v>
       </c>
       <c r="E45" s="7">
-        <v>119.53</v>
+        <v>-385.17</v>
       </c>
     </row>
     <row r="46" spans="1:5">
@@ -2382,13 +2369,13 @@
         <v>31</v>
       </c>
       <c r="C46" s="6">
-        <v>-77.47</v>
+        <v>-60.93</v>
       </c>
       <c r="D46" s="6">
-        <v>-60.93</v>
+        <v>-66.13</v>
       </c>
       <c r="E46" s="7">
-        <v>16.54</v>
+        <v>-5.2</v>
       </c>
     </row>
   </sheetData>
@@ -2453,16 +2440,16 @@
         <v>5</v>
       </c>
       <c r="D2" s="11">
-        <v>45.7</v>
+        <v>45.2</v>
       </c>
       <c r="E2" s="11">
         <v>60</v>
       </c>
       <c r="F2" s="11">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="G2" s="11">
-        <v>0.8</v>
+        <v>1.4</v>
       </c>
       <c r="H2" s="11">
         <v>59.8</v>
@@ -2587,19 +2574,19 @@
     </row>
     <row r="2" spans="1:5">
       <c r="A2" s="14">
-        <v>0.2363</v>
+        <v>0.2306</v>
       </c>
       <c r="B2" s="14">
-        <v>0.1309</v>
+        <v>0.1345</v>
       </c>
       <c r="C2" s="14">
-        <v>0.0333</v>
+        <v>0.0349</v>
       </c>
       <c r="D2" s="14">
-        <v>-0.0179</v>
+        <v>-0.0284</v>
       </c>
       <c r="E2" s="14">
-        <v>-0.2177</v>
+        <v>-0.2171</v>
       </c>
     </row>
   </sheetData>

--- a/HINDUJA_GROUP_Technical_Metrics.xlsx
+++ b/HINDUJA_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="218" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="236" uniqueCount="81">
   <si>
     <t>Symbol</t>
   </si>
@@ -181,19 +181,49 @@
     <t>Curr Value</t>
   </si>
   <si>
-    <t>Near 52W High</t>
-  </si>
-  <si>
-    <t>-2.2% → -0.6%</t>
-  </si>
-  <si>
-    <t>🟢 BREAKOUT WATCH</t>
-  </si>
-  <si>
-    <t>-2.2%</t>
+    <t>RSI Oversold Recovery</t>
+  </si>
+  <si>
+    <t>29.0 → 32.1</t>
+  </si>
+  <si>
+    <t>🟢 BULLISH</t>
+  </si>
+  <si>
+    <t>29.0</t>
+  </si>
+  <si>
+    <t>32.1</t>
+  </si>
+  <si>
+    <t>Left 52W High Zone</t>
+  </si>
+  <si>
+    <t>-0.6% → -9.9%</t>
+  </si>
+  <si>
+    <t>⚪ NEUTRAL</t>
   </si>
   <si>
     <t>-0.6%</t>
+  </si>
+  <si>
+    <t>-9.9%</t>
+  </si>
+  <si>
+    <t>RSI Momentum</t>
+  </si>
+  <si>
+    <t>64.3 → 45.8</t>
+  </si>
+  <si>
+    <t>🔴 BEARISH</t>
+  </si>
+  <si>
+    <t>64.3</t>
+  </si>
+  <si>
+    <t>45.8</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -245,7 +275,7 @@
     <numFmt numFmtId="166" formatCode="0.0"/>
     <numFmt numFmtId="167" formatCode="0.00%"/>
   </numFmts>
-  <fonts count="6">
+  <fonts count="7">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -286,13 +316,20 @@
     </font>
     <font>
       <sz val="11"/>
+      <color rgb="FF1F4E79"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color rgb="FF9C0006"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="9">
+  <fills count="10">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -320,6 +357,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDDEBF7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -395,7 +438,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -403,14 +446,16 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="6" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
@@ -419,7 +464,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="167" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
@@ -919,10 +964,10 @@
         <v>42</v>
       </c>
       <c r="C2">
-        <v>161.75</v>
+        <v>160.75</v>
       </c>
       <c r="D2">
-        <v>-0.77</v>
+        <v>-0.62</v>
       </c>
       <c r="E2">
         <v>208.37</v>
@@ -931,46 +976,46 @@
         <v>131.36</v>
       </c>
       <c r="G2">
-        <v>-22.37</v>
+        <v>-22.85</v>
       </c>
       <c r="H2">
-        <v>23.13</v>
+        <v>22.37</v>
       </c>
       <c r="I2">
-        <v>-1.22</v>
+        <v>2.62</v>
       </c>
       <c r="J2">
-        <v>-6.93</v>
+        <v>-7.08</v>
       </c>
       <c r="K2">
-        <v>2.9</v>
+        <v>6.13</v>
       </c>
       <c r="L2">
-        <v>23.11</v>
+        <v>20.35</v>
       </c>
       <c r="M2">
-        <v>23.06</v>
+        <v>22.64</v>
       </c>
       <c r="N2">
-        <v>60</v>
+        <v>79</v>
       </c>
       <c r="O2">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="P2">
-        <v>159.3</v>
+        <v>160.12</v>
       </c>
       <c r="Q2">
-        <v>168.25</v>
+        <v>167.62</v>
       </c>
       <c r="R2">
-        <v>166.58</v>
+        <v>166.61</v>
       </c>
       <c r="S2">
-        <v>169.92</v>
+        <v>169.93</v>
       </c>
       <c r="T2">
-        <v>-4.81</v>
+        <v>-5.4</v>
       </c>
       <c r="U2" t="s">
         <v>43</v>
@@ -985,34 +1030,34 @@
         <v>1</v>
       </c>
       <c r="Y2">
-        <v>41.73</v>
+        <v>40.33</v>
       </c>
       <c r="Z2">
-        <v>-2.63</v>
+        <v>-2.68</v>
       </c>
       <c r="AA2">
-        <v>-1.39</v>
+        <v>-1.65</v>
       </c>
       <c r="AB2">
-        <v>-1.24</v>
+        <v>-1.03</v>
       </c>
       <c r="AC2">
-        <v>43.64</v>
+        <v>56.78</v>
       </c>
       <c r="AD2">
-        <v>23.92</v>
+        <v>40.9</v>
       </c>
       <c r="AE2">
-        <v>4.24</v>
+        <v>4.25</v>
       </c>
       <c r="AF2">
-        <v>-35.88</v>
+        <v>-27.88</v>
       </c>
       <c r="AG2">
-        <v>181.63</v>
+        <v>181.19</v>
       </c>
       <c r="AH2">
-        <v>154.87</v>
+        <v>154.06</v>
       </c>
       <c r="AI2">
         <v>169.79</v>
@@ -1021,7 +1066,7 @@
         <v>45</v>
       </c>
       <c r="AK2">
-        <v>31.35</v>
+        <v>30.5</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1032,10 +1077,10 @@
         <v>42</v>
       </c>
       <c r="C3">
-        <v>453.45</v>
+        <v>411.05</v>
       </c>
       <c r="D3">
-        <v>1.65</v>
+        <v>-9.35</v>
       </c>
       <c r="E3">
         <v>456.15</v>
@@ -1044,46 +1089,46 @@
         <v>225</v>
       </c>
       <c r="G3">
-        <v>-0.59</v>
+        <v>-9.890000000000001</v>
       </c>
       <c r="H3">
-        <v>101.53</v>
+        <v>82.69</v>
       </c>
       <c r="I3">
-        <v>2.7</v>
+        <v>-5.65</v>
       </c>
       <c r="J3">
-        <v>13.86</v>
+        <v>2.61</v>
       </c>
       <c r="K3">
-        <v>1.83</v>
+        <v>-3.51</v>
       </c>
       <c r="L3">
-        <v>21.76</v>
+        <v>11.61</v>
       </c>
       <c r="M3">
-        <v>13.45</v>
+        <v>9.68</v>
       </c>
       <c r="N3">
-        <v>99</v>
+        <v>60</v>
       </c>
       <c r="O3">
-        <v>76</v>
+        <v>66</v>
       </c>
       <c r="P3">
-        <v>443.95</v>
+        <v>439.03</v>
       </c>
       <c r="Q3">
-        <v>419.84</v>
+        <v>420.47</v>
       </c>
       <c r="R3">
-        <v>411.3</v>
+        <v>411.46</v>
       </c>
       <c r="S3">
-        <v>334.73</v>
+        <v>335.28</v>
       </c>
       <c r="T3">
-        <v>35.47</v>
+        <v>22.6</v>
       </c>
       <c r="U3" t="s">
         <v>43</v>
@@ -1098,34 +1143,34 @@
         <v>3</v>
       </c>
       <c r="Y3">
-        <v>64.26000000000001</v>
+        <v>45.82</v>
       </c>
       <c r="Z3">
-        <v>11.6</v>
+        <v>8.779999999999999</v>
       </c>
       <c r="AA3">
-        <v>8.119999999999999</v>
+        <v>8.25</v>
       </c>
       <c r="AB3">
-        <v>3.48</v>
+        <v>0.53</v>
       </c>
       <c r="AC3">
-        <v>88.45</v>
+        <v>57.91</v>
       </c>
       <c r="AD3">
-        <v>84.04000000000001</v>
+        <v>75.77</v>
       </c>
       <c r="AE3">
-        <v>16.13</v>
+        <v>18.34</v>
       </c>
       <c r="AF3">
-        <v>53.54</v>
+        <v>-22.63</v>
       </c>
       <c r="AG3">
-        <v>466.81</v>
+        <v>466.56</v>
       </c>
       <c r="AH3">
-        <v>372.87</v>
+        <v>374.39</v>
       </c>
       <c r="AI3">
         <v>402.61</v>
@@ -1134,7 +1179,7 @@
         <v>46</v>
       </c>
       <c r="AK3">
-        <v>44.69</v>
+        <v>41.51</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1145,10 +1190,10 @@
         <v>42</v>
       </c>
       <c r="C4">
-        <v>377.8</v>
+        <v>379.65</v>
       </c>
       <c r="D4">
-        <v>-0.42</v>
+        <v>0.49</v>
       </c>
       <c r="E4">
         <v>534</v>
@@ -1157,25 +1202,25 @@
         <v>344.7</v>
       </c>
       <c r="G4">
-        <v>-29.25</v>
+        <v>-28.9</v>
       </c>
       <c r="H4">
-        <v>9.6</v>
+        <v>10.14</v>
       </c>
       <c r="I4">
-        <v>-0.96</v>
+        <v>-0.51</v>
       </c>
       <c r="J4">
-        <v>-7.06</v>
+        <v>-5.62</v>
       </c>
       <c r="K4">
-        <v>-12.83</v>
+        <v>-10.64</v>
       </c>
       <c r="L4">
-        <v>-28.03</v>
+        <v>-26.88</v>
       </c>
       <c r="M4">
-        <v>-21.71</v>
+        <v>-21.76</v>
       </c>
       <c r="N4">
         <v>21</v>
@@ -1184,19 +1229,19 @@
         <v>24</v>
       </c>
       <c r="P4">
-        <v>382.24</v>
+        <v>381.85</v>
       </c>
       <c r="Q4">
-        <v>391.74</v>
+        <v>390.62</v>
       </c>
       <c r="R4">
-        <v>409.61</v>
+        <v>408.85</v>
       </c>
       <c r="S4">
-        <v>410.56</v>
+        <v>410.13</v>
       </c>
       <c r="T4">
-        <v>-7.98</v>
+        <v>-7.43</v>
       </c>
       <c r="U4" t="s">
         <v>44</v>
@@ -1211,34 +1256,34 @@
         <v>0</v>
       </c>
       <c r="Y4">
-        <v>28.98</v>
+        <v>32.12</v>
       </c>
       <c r="Z4">
-        <v>-7.99</v>
+        <v>-7.92</v>
       </c>
       <c r="AA4">
-        <v>-7.46</v>
+        <v>-7.55</v>
       </c>
       <c r="AB4">
-        <v>-0.53</v>
+        <v>-0.36</v>
       </c>
       <c r="AC4">
-        <v>30.16</v>
+        <v>21.46</v>
       </c>
       <c r="AD4">
-        <v>38.42</v>
+        <v>32.35</v>
       </c>
       <c r="AE4">
-        <v>10.83</v>
+        <v>10.77</v>
       </c>
       <c r="AF4">
-        <v>-48.73</v>
+        <v>-26.49</v>
       </c>
       <c r="AG4">
-        <v>409.11</v>
+        <v>408.08</v>
       </c>
       <c r="AH4">
-        <v>374.36</v>
+        <v>373.16</v>
       </c>
       <c r="AI4">
         <v>412.97</v>
@@ -1247,7 +1292,7 @@
         <v>45</v>
       </c>
       <c r="AK4">
-        <v>25.01</v>
+        <v>25.81</v>
       </c>
     </row>
     <row r="5" spans="1:37">
@@ -1258,10 +1303,10 @@
         <v>42</v>
       </c>
       <c r="C5">
-        <v>956</v>
+        <v>955</v>
       </c>
       <c r="D5">
-        <v>-1.07</v>
+        <v>-0.1</v>
       </c>
       <c r="E5">
         <v>1069.3</v>
@@ -1270,46 +1315,46 @@
         <v>712.75</v>
       </c>
       <c r="G5">
-        <v>-10.6</v>
+        <v>-10.69</v>
       </c>
       <c r="H5">
-        <v>34.13</v>
+        <v>33.99</v>
       </c>
       <c r="I5">
-        <v>-2.27</v>
+        <v>-0.16</v>
       </c>
       <c r="J5">
-        <v>-5.16</v>
+        <v>-5.03</v>
       </c>
       <c r="K5">
-        <v>3.79</v>
+        <v>5.47</v>
       </c>
       <c r="L5">
-        <v>28.8</v>
+        <v>29.22</v>
       </c>
       <c r="M5">
-        <v>-2.84</v>
+        <v>-2.92</v>
       </c>
       <c r="N5">
-        <v>79</v>
+        <v>99</v>
       </c>
       <c r="O5">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="P5">
-        <v>956.7</v>
+        <v>956.4</v>
       </c>
       <c r="Q5">
-        <v>989.48</v>
+        <v>986.3</v>
       </c>
       <c r="R5">
-        <v>1006.59</v>
+        <v>1005.43</v>
       </c>
       <c r="S5">
-        <v>921.3099999999999</v>
+        <v>921.85</v>
       </c>
       <c r="T5">
-        <v>3.77</v>
+        <v>3.6</v>
       </c>
       <c r="U5" t="s">
         <v>44</v>
@@ -1324,43 +1369,43 @@
         <v>2</v>
       </c>
       <c r="Y5">
-        <v>38.72</v>
+        <v>38.45</v>
       </c>
       <c r="Z5">
-        <v>-12.89</v>
+        <v>-13.51</v>
       </c>
       <c r="AA5">
-        <v>-8.34</v>
+        <v>-9.369999999999999</v>
       </c>
       <c r="AB5">
-        <v>-4.55</v>
+        <v>-4.14</v>
       </c>
       <c r="AC5">
-        <v>32.44</v>
+        <v>33.85</v>
       </c>
       <c r="AD5">
-        <v>20.98</v>
+        <v>29.48</v>
       </c>
       <c r="AE5">
-        <v>19.58</v>
+        <v>19.2</v>
       </c>
       <c r="AF5">
-        <v>-66.77</v>
+        <v>-44.68</v>
       </c>
       <c r="AG5">
-        <v>1034.05</v>
+        <v>1031.23</v>
       </c>
       <c r="AH5">
-        <v>944.9</v>
+        <v>941.38</v>
       </c>
       <c r="AI5">
-        <v>1014.05</v>
+        <v>1013.99</v>
       </c>
       <c r="AJ5" t="s">
         <v>45</v>
       </c>
       <c r="AK5">
-        <v>23.65</v>
+        <v>25.5</v>
       </c>
     </row>
     <row r="6" spans="1:37">
@@ -1371,10 +1416,10 @@
         <v>42</v>
       </c>
       <c r="C6">
-        <v>2.79</v>
+        <v>2.76</v>
       </c>
       <c r="D6">
-        <v>0.36</v>
+        <v>-1.08</v>
       </c>
       <c r="E6">
         <v>3.62</v>
@@ -1383,37 +1428,37 @@
         <v>1.84</v>
       </c>
       <c r="G6">
-        <v>-22.93</v>
+        <v>-23.76</v>
       </c>
       <c r="H6">
-        <v>51.63</v>
+        <v>50</v>
       </c>
       <c r="I6">
-        <v>-2.45</v>
+        <v>0.36</v>
       </c>
       <c r="J6">
-        <v>23.45</v>
+        <v>1.85</v>
       </c>
       <c r="K6">
-        <v>11.16</v>
+        <v>9.52</v>
       </c>
       <c r="L6">
-        <v>-20.96</v>
+        <v>-22.69</v>
       </c>
       <c r="M6">
-        <v>3.49</v>
+        <v>3.01</v>
       </c>
       <c r="N6">
         <v>40</v>
       </c>
       <c r="O6">
-        <v>60</v>
+        <v>47</v>
       </c>
       <c r="P6">
         <v>2.81</v>
       </c>
       <c r="Q6">
-        <v>2.9</v>
+        <v>2.88</v>
       </c>
       <c r="R6">
         <v>2.57</v>
@@ -1422,7 +1467,7 @@
         <v>2.67</v>
       </c>
       <c r="T6">
-        <v>4.45</v>
+        <v>3.39</v>
       </c>
       <c r="U6" t="s">
         <v>43</v>
@@ -1437,34 +1482,34 @@
         <v>2</v>
       </c>
       <c r="Y6">
-        <v>52.16</v>
+        <v>50.27</v>
       </c>
       <c r="Z6">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="AA6">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="AB6">
         <v>-0.03</v>
       </c>
       <c r="AC6">
-        <v>7.61</v>
+        <v>3.57</v>
       </c>
       <c r="AD6">
-        <v>12.26</v>
+        <v>8.789999999999999</v>
       </c>
       <c r="AE6">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
       <c r="AF6">
-        <v>-66.13</v>
+        <v>-73.84999999999999</v>
       </c>
       <c r="AG6">
-        <v>3.08</v>
+        <v>3.07</v>
       </c>
       <c r="AH6">
-        <v>2.71</v>
+        <v>2.7</v>
       </c>
       <c r="AI6">
         <v>2.65</v>
@@ -1473,7 +1518,7 @@
         <v>46</v>
       </c>
       <c r="AK6">
-        <v>31.15</v>
+        <v>29.19</v>
       </c>
     </row>
   </sheetData>
@@ -1614,7 +1659,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F46"/>
+  <dimension ref="A1:F51"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.7109375" customWidth="1"/>
@@ -1654,7 +1699,7 @@
     </row>
     <row r="3" spans="1:6">
       <c r="A3" s="4" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B3" s="4" t="s">
         <v>53</v>
@@ -1672,716 +1717,807 @@
         <v>57</v>
       </c>
     </row>
+    <row r="4" spans="1:6">
+      <c r="A4" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B4" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="C4" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="D4" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="E4" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="F4" s="5" t="s">
+        <v>62</v>
+      </c>
+    </row>
     <row r="5" spans="1:6">
-      <c r="A5" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="B5" s="2"/>
-      <c r="C5" s="2"/>
-      <c r="D5" s="2"/>
-      <c r="E5" s="2"/>
-    </row>
-    <row r="6" spans="1:6">
-      <c r="A6" s="3" t="s">
+      <c r="A5" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="B5" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="C5" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="D5" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="E5" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="F5" s="6" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6">
+      <c r="A7" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="B7" s="2"/>
+      <c r="C7" s="2"/>
+      <c r="D7" s="2"/>
+      <c r="E7" s="2"/>
+    </row>
+    <row r="8" spans="1:6">
+      <c r="A8" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B6" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="C6" s="3" t="s">
+      <c r="B8" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="A9" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="B9" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="C9" s="8">
+        <v>-6.93</v>
+      </c>
+      <c r="D9" s="8">
+        <v>-7.08</v>
+      </c>
+      <c r="E9" s="9">
+        <v>-0.15</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="A10" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="B10" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="C10" s="8">
+        <v>13.86</v>
+      </c>
+      <c r="D10" s="8">
+        <v>2.61</v>
+      </c>
+      <c r="E10" s="9">
+        <v>-11.25</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="A11" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="B11" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="C11" s="8">
+        <v>-7.06</v>
+      </c>
+      <c r="D11" s="8">
+        <v>-5.62</v>
+      </c>
+      <c r="E11" s="10">
+        <v>1.44</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6">
+      <c r="A12" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="B12" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="C12" s="8">
+        <v>-5.16</v>
+      </c>
+      <c r="D12" s="8">
+        <v>-5.03</v>
+      </c>
+      <c r="E12" s="10">
+        <v>0.13</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6">
+      <c r="A13" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="B13" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="C13" s="8">
+        <v>23.45</v>
+      </c>
+      <c r="D13" s="8">
+        <v>1.85</v>
+      </c>
+      <c r="E13" s="9">
+        <v>-21.6</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6">
+      <c r="A14" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="B14" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="C14" s="8">
+        <v>-1.22</v>
+      </c>
+      <c r="D14" s="8">
+        <v>2.62</v>
+      </c>
+      <c r="E14" s="10">
+        <v>3.84</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6">
+      <c r="A15" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="B15" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="C15" s="8">
+        <v>2.7</v>
+      </c>
+      <c r="D15" s="8">
+        <v>-5.65</v>
+      </c>
+      <c r="E15" s="9">
+        <v>-8.35</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6">
+      <c r="A16" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="B16" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="C16" s="8">
+        <v>-0.96</v>
+      </c>
+      <c r="D16" s="8">
+        <v>-0.51</v>
+      </c>
+      <c r="E16" s="10">
+        <v>0.45</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="B17" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="C17" s="8">
+        <v>-2.27</v>
+      </c>
+      <c r="D17" s="8">
+        <v>-0.16</v>
+      </c>
+      <c r="E17" s="10">
+        <v>2.11</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="B18" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="C18" s="8">
+        <v>-2.45</v>
+      </c>
+      <c r="D18" s="8">
+        <v>0.36</v>
+      </c>
+      <c r="E18" s="10">
+        <v>2.81</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="B19" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="C19" s="8">
+        <v>23.11</v>
+      </c>
+      <c r="D19" s="8">
+        <v>20.35</v>
+      </c>
+      <c r="E19" s="9">
+        <v>-2.76</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="B20" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="C20" s="8">
+        <v>21.76</v>
+      </c>
+      <c r="D20" s="8">
+        <v>11.61</v>
+      </c>
+      <c r="E20" s="9">
+        <v>-10.15</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="B21" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="C21" s="8">
+        <v>-28.03</v>
+      </c>
+      <c r="D21" s="8">
+        <v>-26.88</v>
+      </c>
+      <c r="E21" s="10">
+        <v>1.15</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="B22" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="C22" s="8">
+        <v>28.8</v>
+      </c>
+      <c r="D22" s="8">
+        <v>29.22</v>
+      </c>
+      <c r="E22" s="10">
+        <v>0.42</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="B23" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="C23" s="8">
+        <v>-20.96</v>
+      </c>
+      <c r="D23" s="8">
+        <v>-22.69</v>
+      </c>
+      <c r="E23" s="9">
+        <v>-1.73</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5">
+      <c r="A24" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="B24" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="C24" s="8">
+        <v>2.9</v>
+      </c>
+      <c r="D24" s="8">
+        <v>6.13</v>
+      </c>
+      <c r="E24" s="10">
+        <v>3.23</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5">
+      <c r="A25" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="B25" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="C25" s="8">
+        <v>1.83</v>
+      </c>
+      <c r="D25" s="8">
+        <v>-3.51</v>
+      </c>
+      <c r="E25" s="9">
+        <v>-5.34</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
+      <c r="A26" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="B26" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="C26" s="8">
+        <v>-12.83</v>
+      </c>
+      <c r="D26" s="8">
+        <v>-10.64</v>
+      </c>
+      <c r="E26" s="10">
+        <v>2.19</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5">
+      <c r="A27" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="B27" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="C27" s="8">
+        <v>3.79</v>
+      </c>
+      <c r="D27" s="8">
+        <v>5.47</v>
+      </c>
+      <c r="E27" s="10">
+        <v>1.68</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5">
+      <c r="A28" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="B28" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="C28" s="8">
+        <v>11.16</v>
+      </c>
+      <c r="D28" s="8">
+        <v>9.52</v>
+      </c>
+      <c r="E28" s="9">
+        <v>-1.64</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5">
+      <c r="A29" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="B29" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="C29" s="8">
+        <v>-22.37</v>
+      </c>
+      <c r="D29" s="8">
+        <v>-22.85</v>
+      </c>
+      <c r="E29" s="9">
+        <v>-0.48</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5">
+      <c r="A30" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="B30" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="C30" s="8">
+        <v>-0.59</v>
+      </c>
+      <c r="D30" s="8">
+        <v>-9.890000000000001</v>
+      </c>
+      <c r="E30" s="9">
+        <v>-9.300000000000001</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5">
+      <c r="A31" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="B31" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="C31" s="8">
+        <v>-29.25</v>
+      </c>
+      <c r="D31" s="8">
+        <v>-28.9</v>
+      </c>
+      <c r="E31" s="10">
+        <v>0.35</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5">
+      <c r="A32" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="B32" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="C32" s="8">
+        <v>-10.6</v>
+      </c>
+      <c r="D32" s="8">
+        <v>-10.69</v>
+      </c>
+      <c r="E32" s="9">
+        <v>-0.09</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5">
+      <c r="A33" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="B33" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="C33" s="8">
+        <v>-22.93</v>
+      </c>
+      <c r="D33" s="8">
+        <v>-23.76</v>
+      </c>
+      <c r="E33" s="9">
+        <v>-0.83</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5">
+      <c r="A34" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="B34" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="C34" s="8">
+        <v>161.75</v>
+      </c>
+      <c r="D34" s="8">
+        <v>160.75</v>
+      </c>
+      <c r="E34" s="9">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5">
+      <c r="A35" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="B35" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="C35" s="8">
+        <v>453.45</v>
+      </c>
+      <c r="D35" s="8">
+        <v>411.05</v>
+      </c>
+      <c r="E35" s="9">
+        <v>-42.4</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5">
+      <c r="A36" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="B36" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="C36" s="8">
+        <v>377.8</v>
+      </c>
+      <c r="D36" s="8">
+        <v>379.65</v>
+      </c>
+      <c r="E36" s="10">
+        <v>1.85</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5">
+      <c r="A37" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="B37" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="C37" s="8">
+        <v>956</v>
+      </c>
+      <c r="D37" s="8">
+        <v>955</v>
+      </c>
+      <c r="E37" s="9">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5">
+      <c r="A38" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="B38" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="C38" s="8">
+        <v>2.79</v>
+      </c>
+      <c r="D38" s="8">
+        <v>2.76</v>
+      </c>
+      <c r="E38" s="9">
+        <v>-0.03</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5">
+      <c r="A39" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="B39" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="C39" s="8">
         <v>60</v>
       </c>
-      <c r="D6" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="E6" s="3" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6">
-      <c r="A7" s="5" t="s">
+      <c r="D39" s="8">
+        <v>79</v>
+      </c>
+      <c r="E39" s="10">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5">
+      <c r="A40" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="B40" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="C40" s="8">
+        <v>99</v>
+      </c>
+      <c r="D40" s="8">
+        <v>60</v>
+      </c>
+      <c r="E40" s="9">
+        <v>-39</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5">
+      <c r="A41" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="B41" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="C41" s="8">
+        <v>79</v>
+      </c>
+      <c r="D41" s="8">
+        <v>99</v>
+      </c>
+      <c r="E41" s="10">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5">
+      <c r="A42" s="7" t="s">
         <v>37</v>
       </c>
-      <c r="B7" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C7" s="6">
-        <v>-5.83</v>
-      </c>
-      <c r="D7" s="6">
-        <v>-6.93</v>
-      </c>
-      <c r="E7" s="7">
-        <v>-1.1</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6">
-      <c r="A8" s="5" t="s">
+      <c r="B42" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="C42" s="8">
+        <v>41.73</v>
+      </c>
+      <c r="D42" s="8">
+        <v>40.33</v>
+      </c>
+      <c r="E42" s="9">
+        <v>-1.4</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5">
+      <c r="A43" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="B8" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C8" s="6">
-        <v>11.93</v>
-      </c>
-      <c r="D8" s="6">
-        <v>13.86</v>
-      </c>
-      <c r="E8" s="8">
-        <v>1.93</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
-      <c r="A9" s="5" t="s">
+      <c r="B43" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="C43" s="8">
+        <v>64.26000000000001</v>
+      </c>
+      <c r="D43" s="8">
+        <v>45.82</v>
+      </c>
+      <c r="E43" s="9">
+        <v>-18.44</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5">
+      <c r="A44" s="7" t="s">
         <v>39</v>
       </c>
-      <c r="B9" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C9" s="6">
-        <v>-7.01</v>
-      </c>
-      <c r="D9" s="6">
-        <v>-7.06</v>
-      </c>
-      <c r="E9" s="7">
-        <v>-0.05</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
-      <c r="A10" s="5" t="s">
+      <c r="B44" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="C44" s="8">
+        <v>28.98</v>
+      </c>
+      <c r="D44" s="8">
+        <v>32.12</v>
+      </c>
+      <c r="E44" s="10">
+        <v>3.14</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5">
+      <c r="A45" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="B10" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C10" s="6">
-        <v>-4.96</v>
-      </c>
-      <c r="D10" s="6">
-        <v>-5.16</v>
-      </c>
-      <c r="E10" s="7">
-        <v>-0.2</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
-      <c r="A11" s="5" t="s">
+      <c r="B45" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="C45" s="8">
+        <v>38.72</v>
+      </c>
+      <c r="D45" s="8">
+        <v>38.45</v>
+      </c>
+      <c r="E45" s="9">
+        <v>-0.27</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5">
+      <c r="A46" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="B11" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C11" s="6">
-        <v>23.56</v>
-      </c>
-      <c r="D11" s="6">
-        <v>23.45</v>
-      </c>
-      <c r="E11" s="7">
-        <v>-0.11</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
-      <c r="A12" s="5" t="s">
+      <c r="B46" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="C46" s="8">
+        <v>52.16</v>
+      </c>
+      <c r="D46" s="8">
+        <v>50.27</v>
+      </c>
+      <c r="E46" s="9">
+        <v>-1.89</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5">
+      <c r="A47" s="7" t="s">
         <v>37</v>
       </c>
-      <c r="B12" s="5" t="s">
+      <c r="B47" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="C47" s="8">
+        <v>-35.88</v>
+      </c>
+      <c r="D47" s="8">
+        <v>-27.88</v>
+      </c>
+      <c r="E47" s="10">
         <v>8</v>
       </c>
-      <c r="C12" s="6">
-        <v>-1.88</v>
-      </c>
-      <c r="D12" s="6">
-        <v>-1.22</v>
-      </c>
-      <c r="E12" s="8">
-        <v>0.66</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
-      <c r="A13" s="5" t="s">
+    </row>
+    <row r="48" spans="1:5">
+      <c r="A48" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="B13" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C13" s="6">
-        <v>3.22</v>
-      </c>
-      <c r="D13" s="6">
-        <v>2.7</v>
-      </c>
-      <c r="E13" s="7">
-        <v>-0.52</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
-      <c r="A14" s="5" t="s">
+      <c r="B48" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="C48" s="8">
+        <v>53.54</v>
+      </c>
+      <c r="D48" s="8">
+        <v>-22.63</v>
+      </c>
+      <c r="E48" s="9">
+        <v>-76.17</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5">
+      <c r="A49" s="7" t="s">
         <v>39</v>
       </c>
-      <c r="B14" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C14" s="6">
-        <v>-1.16</v>
-      </c>
-      <c r="D14" s="6">
-        <v>-0.96</v>
-      </c>
-      <c r="E14" s="8">
-        <v>0.2</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6">
-      <c r="A15" s="5" t="s">
+      <c r="B49" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="C49" s="8">
+        <v>-48.73</v>
+      </c>
+      <c r="D49" s="8">
+        <v>-26.49</v>
+      </c>
+      <c r="E49" s="10">
+        <v>22.24</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5">
+      <c r="A50" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="B15" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C15" s="6">
-        <v>-2.72</v>
-      </c>
-      <c r="D15" s="6">
-        <v>-2.27</v>
-      </c>
-      <c r="E15" s="8">
-        <v>0.45</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
-      <c r="A16" s="5" t="s">
+      <c r="B50" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="C50" s="8">
+        <v>-66.77</v>
+      </c>
+      <c r="D50" s="8">
+        <v>-44.68</v>
+      </c>
+      <c r="E50" s="10">
+        <v>22.09</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5">
+      <c r="A51" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="B16" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C16" s="6">
-        <v>-4.14</v>
-      </c>
-      <c r="D16" s="6">
-        <v>-2.45</v>
-      </c>
-      <c r="E16" s="8">
-        <v>1.69</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5">
-      <c r="A17" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B17" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C17" s="6">
-        <v>24.61</v>
-      </c>
-      <c r="D17" s="6">
-        <v>23.11</v>
-      </c>
-      <c r="E17" s="7">
-        <v>-1.5</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5">
-      <c r="A18" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B18" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C18" s="6">
-        <v>28.74</v>
-      </c>
-      <c r="D18" s="6">
-        <v>21.76</v>
-      </c>
-      <c r="E18" s="7">
-        <v>-6.98</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5">
-      <c r="A19" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B19" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C19" s="6">
-        <v>-28.6</v>
-      </c>
-      <c r="D19" s="6">
-        <v>-28.03</v>
-      </c>
-      <c r="E19" s="8">
-        <v>0.57</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5">
-      <c r="A20" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B20" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C20" s="6">
-        <v>30.6</v>
-      </c>
-      <c r="D20" s="6">
-        <v>28.8</v>
-      </c>
-      <c r="E20" s="7">
-        <v>-1.8</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5">
-      <c r="A21" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B21" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C21" s="6">
-        <v>-20.57</v>
-      </c>
-      <c r="D21" s="6">
-        <v>-20.96</v>
-      </c>
-      <c r="E21" s="7">
-        <v>-0.39</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5">
-      <c r="A22" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B22" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C22" s="6">
-        <v>4.05</v>
-      </c>
-      <c r="D22" s="6">
-        <v>2.9</v>
-      </c>
-      <c r="E22" s="7">
-        <v>-1.15</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5">
-      <c r="A23" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B23" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C23" s="6">
-        <v>1.97</v>
-      </c>
-      <c r="D23" s="6">
-        <v>1.83</v>
-      </c>
-      <c r="E23" s="7">
-        <v>-0.14</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5">
-      <c r="A24" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B24" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C24" s="6">
-        <v>-10.71</v>
-      </c>
-      <c r="D24" s="6">
-        <v>-12.83</v>
-      </c>
-      <c r="E24" s="7">
-        <v>-2.12</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5">
-      <c r="A25" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B25" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C25" s="6">
-        <v>1.99</v>
-      </c>
-      <c r="D25" s="6">
-        <v>3.79</v>
-      </c>
-      <c r="E25" s="8">
-        <v>1.8</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5">
-      <c r="A26" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B26" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C26" s="6">
-        <v>6.51</v>
-      </c>
-      <c r="D26" s="6">
-        <v>11.16</v>
-      </c>
-      <c r="E26" s="8">
-        <v>4.65</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5">
-      <c r="A27" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B27" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C27" s="6">
-        <v>-21.77</v>
-      </c>
-      <c r="D27" s="6">
-        <v>-22.37</v>
-      </c>
-      <c r="E27" s="7">
-        <v>-0.6</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5">
-      <c r="A28" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B28" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C28" s="6">
-        <v>-2.2</v>
-      </c>
-      <c r="D28" s="6">
-        <v>-0.59</v>
-      </c>
-      <c r="E28" s="8">
-        <v>1.61</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5">
-      <c r="A29" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B29" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C29" s="6">
-        <v>-28.95</v>
-      </c>
-      <c r="D29" s="6">
-        <v>-29.25</v>
-      </c>
-      <c r="E29" s="7">
-        <v>-0.3</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5">
-      <c r="A30" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B30" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C30" s="6">
-        <v>-9.630000000000001</v>
-      </c>
-      <c r="D30" s="6">
-        <v>-10.6</v>
-      </c>
-      <c r="E30" s="7">
-        <v>-0.97</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5">
-      <c r="A31" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B31" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C31" s="6">
-        <v>-23.2</v>
-      </c>
-      <c r="D31" s="6">
-        <v>-22.93</v>
-      </c>
-      <c r="E31" s="8">
-        <v>0.27</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5">
-      <c r="A32" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B32" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C32" s="6">
-        <v>163</v>
-      </c>
-      <c r="D32" s="6">
-        <v>161.75</v>
-      </c>
-      <c r="E32" s="7">
-        <v>-1.25</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5">
-      <c r="A33" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B33" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C33" s="6">
-        <v>446.1</v>
-      </c>
-      <c r="D33" s="6">
-        <v>453.45</v>
-      </c>
-      <c r="E33" s="8">
-        <v>7.35</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5">
-      <c r="A34" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B34" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C34" s="6">
-        <v>379.4</v>
-      </c>
-      <c r="D34" s="6">
-        <v>377.8</v>
-      </c>
-      <c r="E34" s="7">
-        <v>-1.6</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5">
-      <c r="A35" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B35" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C35" s="6">
-        <v>966.3</v>
-      </c>
-      <c r="D35" s="6">
-        <v>956</v>
-      </c>
-      <c r="E35" s="7">
-        <v>-10.3</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5">
-      <c r="A36" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B36" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C36" s="6">
-        <v>2.78</v>
-      </c>
-      <c r="D36" s="6">
-        <v>2.79</v>
-      </c>
-      <c r="E36" s="8">
-        <v>0.01</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5">
-      <c r="A37" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B37" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C37" s="6">
-        <v>43.48</v>
-      </c>
-      <c r="D37" s="6">
-        <v>41.73</v>
-      </c>
-      <c r="E37" s="7">
-        <v>-1.75</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5">
-      <c r="A38" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B38" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C38" s="6">
-        <v>61.79</v>
-      </c>
-      <c r="D38" s="6">
-        <v>64.26000000000001</v>
-      </c>
-      <c r="E38" s="8">
-        <v>2.47</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5">
-      <c r="A39" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B39" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C39" s="6">
-        <v>30.1</v>
-      </c>
-      <c r="D39" s="6">
-        <v>28.98</v>
-      </c>
-      <c r="E39" s="7">
-        <v>-1.12</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5">
-      <c r="A40" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B40" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C40" s="6">
-        <v>41.51</v>
-      </c>
-      <c r="D40" s="6">
-        <v>38.72</v>
-      </c>
-      <c r="E40" s="7">
-        <v>-2.79</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5">
-      <c r="A41" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B41" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C41" s="6">
-        <v>51.59</v>
-      </c>
-      <c r="D41" s="6">
-        <v>52.16</v>
-      </c>
-      <c r="E41" s="8">
-        <v>0.57</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5">
-      <c r="A42" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B42" s="5" t="s">
+      <c r="B51" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="C42" s="6">
-        <v>46.95</v>
-      </c>
-      <c r="D42" s="6">
-        <v>-35.88</v>
-      </c>
-      <c r="E42" s="7">
-        <v>-82.83</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5">
-      <c r="A43" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B43" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C43" s="6">
-        <v>21.46</v>
-      </c>
-      <c r="D43" s="6">
-        <v>53.54</v>
-      </c>
-      <c r="E43" s="8">
-        <v>32.08</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5">
-      <c r="A44" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B44" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C44" s="6">
-        <v>30.46</v>
-      </c>
-      <c r="D44" s="6">
-        <v>-48.73</v>
-      </c>
-      <c r="E44" s="7">
-        <v>-79.19</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5">
-      <c r="A45" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B45" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C45" s="6">
-        <v>318.4</v>
-      </c>
-      <c r="D45" s="6">
-        <v>-66.77</v>
-      </c>
-      <c r="E45" s="7">
-        <v>-385.17</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5">
-      <c r="A46" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B46" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C46" s="6">
-        <v>-60.93</v>
-      </c>
-      <c r="D46" s="6">
+      <c r="C51" s="8">
         <v>-66.13</v>
       </c>
-      <c r="E46" s="7">
-        <v>-5.2</v>
+      <c r="D51" s="8">
+        <v>-73.84999999999999</v>
+      </c>
+      <c r="E51" s="9">
+        <v>-7.72</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A5:E5"/>
+    <mergeCell ref="A7:E7"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2401,60 +2537,60 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="28" customHeight="1">
-      <c r="A1" s="9" t="s">
+      <c r="A1" s="11" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="9" t="s">
-        <v>63</v>
-      </c>
-      <c r="C1" s="9" t="s">
-        <v>64</v>
-      </c>
-      <c r="D1" s="9" t="s">
-        <v>65</v>
-      </c>
-      <c r="E1" s="9" t="s">
-        <v>66</v>
-      </c>
-      <c r="F1" s="9" t="s">
-        <v>67</v>
-      </c>
-      <c r="G1" s="9" t="s">
-        <v>68</v>
-      </c>
-      <c r="H1" s="9" t="s">
-        <v>69</v>
-      </c>
-      <c r="I1" s="9" t="s">
-        <v>70</v>
+      <c r="B1" s="11" t="s">
+        <v>73</v>
+      </c>
+      <c r="C1" s="11" t="s">
+        <v>74</v>
+      </c>
+      <c r="D1" s="11" t="s">
+        <v>75</v>
+      </c>
+      <c r="E1" s="11" t="s">
+        <v>76</v>
+      </c>
+      <c r="F1" s="11" t="s">
+        <v>77</v>
+      </c>
+      <c r="G1" s="11" t="s">
+        <v>78</v>
+      </c>
+      <c r="H1" s="11" t="s">
+        <v>79</v>
+      </c>
+      <c r="I1" s="11" t="s">
+        <v>80</v>
       </c>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="10" t="s">
+      <c r="A2" s="12" t="s">
         <v>42</v>
       </c>
-      <c r="B2" s="11">
+      <c r="B2" s="13">
         <v>57.92</v>
       </c>
-      <c r="C2" s="12">
+      <c r="C2" s="14">
         <v>5</v>
       </c>
-      <c r="D2" s="11">
-        <v>45.2</v>
-      </c>
-      <c r="E2" s="11">
+      <c r="D2" s="13">
+        <v>41.4</v>
+      </c>
+      <c r="E2" s="13">
         <v>60</v>
       </c>
-      <c r="F2" s="11">
-        <v>3.6</v>
-      </c>
-      <c r="G2" s="11">
+      <c r="F2" s="13">
+        <v>-2.7</v>
+      </c>
+      <c r="G2" s="13">
         <v>1.4</v>
       </c>
-      <c r="H2" s="11">
+      <c r="H2" s="13">
         <v>59.8</v>
       </c>
-      <c r="I2" s="11">
+      <c r="I2" s="13">
         <v>20</v>
       </c>
     </row>
@@ -2556,37 +2692,37 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
-      <c r="A1" s="13" t="s">
+      <c r="A1" s="15" t="s">
         <v>37</v>
       </c>
-      <c r="B1" s="13" t="s">
+      <c r="B1" s="15" t="s">
         <v>38</v>
       </c>
-      <c r="C1" s="13" t="s">
+      <c r="C1" s="15" t="s">
         <v>41</v>
       </c>
-      <c r="D1" s="13" t="s">
+      <c r="D1" s="15" t="s">
         <v>40</v>
       </c>
-      <c r="E1" s="13" t="s">
+      <c r="E1" s="15" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="2" spans="1:5">
-      <c r="A2" s="14">
-        <v>0.2306</v>
-      </c>
-      <c r="B2" s="14">
-        <v>0.1345</v>
-      </c>
-      <c r="C2" s="14">
-        <v>0.0349</v>
-      </c>
-      <c r="D2" s="14">
-        <v>-0.0284</v>
-      </c>
-      <c r="E2" s="14">
-        <v>-0.2171</v>
+      <c r="A2" s="16">
+        <v>0.2264</v>
+      </c>
+      <c r="B2" s="16">
+        <v>0.0968</v>
+      </c>
+      <c r="C2" s="16">
+        <v>0.0301</v>
+      </c>
+      <c r="D2" s="16">
+        <v>-0.0292</v>
+      </c>
+      <c r="E2" s="16">
+        <v>-0.2176</v>
       </c>
     </row>
   </sheetData>

--- a/HINDUJA_GROUP_Technical_Metrics.xlsx
+++ b/HINDUJA_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="236" uniqueCount="81">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="203" uniqueCount="62">
   <si>
     <t>Symbol</t>
   </si>
@@ -166,64 +166,7 @@
     <t>▶  SIGNAL EVENTS (vs Previous Run)</t>
   </si>
   <si>
-    <t>Signal</t>
-  </si>
-  <si>
-    <t>Change</t>
-  </si>
-  <si>
-    <t>Direction</t>
-  </si>
-  <si>
-    <t>Prev Value</t>
-  </si>
-  <si>
-    <t>Curr Value</t>
-  </si>
-  <si>
-    <t>RSI Oversold Recovery</t>
-  </si>
-  <si>
-    <t>29.0 → 32.1</t>
-  </si>
-  <si>
-    <t>🟢 BULLISH</t>
-  </si>
-  <si>
-    <t>29.0</t>
-  </si>
-  <si>
-    <t>32.1</t>
-  </si>
-  <si>
-    <t>Left 52W High Zone</t>
-  </si>
-  <si>
-    <t>-0.6% → -9.9%</t>
-  </si>
-  <si>
-    <t>⚪ NEUTRAL</t>
-  </si>
-  <si>
-    <t>-0.6%</t>
-  </si>
-  <si>
-    <t>-9.9%</t>
-  </si>
-  <si>
-    <t>RSI Momentum</t>
-  </si>
-  <si>
-    <t>64.3 → 45.8</t>
-  </si>
-  <si>
-    <t>🔴 BEARISH</t>
-  </si>
-  <si>
-    <t>64.3</t>
-  </si>
-  <si>
-    <t>45.8</t>
+    <t>No signal events detected since last run.</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -275,7 +218,7 @@
     <numFmt numFmtId="166" formatCode="0.0"/>
     <numFmt numFmtId="167" formatCode="0.00%"/>
   </numFmts>
-  <fonts count="7">
+  <fonts count="6">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -316,20 +259,13 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF1F4E79"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
       <color rgb="FF9C0006"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="10">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -357,12 +293,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDDEBF7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -438,24 +368,21 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="6" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
@@ -464,7 +391,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="167" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
@@ -964,10 +891,10 @@
         <v>42</v>
       </c>
       <c r="C2">
-        <v>160.75</v>
+        <v>162.89</v>
       </c>
       <c r="D2">
-        <v>-0.62</v>
+        <v>1.33</v>
       </c>
       <c r="E2">
         <v>208.37</v>
@@ -976,46 +903,46 @@
         <v>131.36</v>
       </c>
       <c r="G2">
-        <v>-22.85</v>
+        <v>-21.83</v>
       </c>
       <c r="H2">
-        <v>22.37</v>
+        <v>24</v>
       </c>
       <c r="I2">
-        <v>2.62</v>
+        <v>4.08</v>
       </c>
       <c r="J2">
-        <v>-7.08</v>
+        <v>-6</v>
       </c>
       <c r="K2">
-        <v>6.13</v>
+        <v>5.15</v>
       </c>
       <c r="L2">
-        <v>20.35</v>
+        <v>20.21</v>
       </c>
       <c r="M2">
-        <v>22.64</v>
+        <v>22.86</v>
       </c>
       <c r="N2">
         <v>79</v>
       </c>
       <c r="O2">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="P2">
-        <v>160.12</v>
+        <v>161.4</v>
       </c>
       <c r="Q2">
-        <v>167.62</v>
+        <v>167.03</v>
       </c>
       <c r="R2">
-        <v>166.61</v>
+        <v>166.77</v>
       </c>
       <c r="S2">
-        <v>169.93</v>
+        <v>169.95</v>
       </c>
       <c r="T2">
-        <v>-5.4</v>
+        <v>-4.16</v>
       </c>
       <c r="U2" t="s">
         <v>43</v>
@@ -1030,34 +957,34 @@
         <v>1</v>
       </c>
       <c r="Y2">
-        <v>40.33</v>
+        <v>44.61</v>
       </c>
       <c r="Z2">
-        <v>-2.68</v>
+        <v>-2.52</v>
       </c>
       <c r="AA2">
-        <v>-1.65</v>
+        <v>-1.82</v>
       </c>
       <c r="AB2">
-        <v>-1.03</v>
+        <v>-0.7</v>
       </c>
       <c r="AC2">
-        <v>56.78</v>
+        <v>66.86</v>
       </c>
       <c r="AD2">
-        <v>40.9</v>
+        <v>55.76</v>
       </c>
       <c r="AE2">
-        <v>4.25</v>
+        <v>4.12</v>
       </c>
       <c r="AF2">
-        <v>-27.88</v>
+        <v>-68.15000000000001</v>
       </c>
       <c r="AG2">
-        <v>181.19</v>
+        <v>180.32</v>
       </c>
       <c r="AH2">
-        <v>154.06</v>
+        <v>153.74</v>
       </c>
       <c r="AI2">
         <v>169.79</v>
@@ -1066,7 +993,7 @@
         <v>45</v>
       </c>
       <c r="AK2">
-        <v>30.5</v>
+        <v>29.76</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1077,10 +1004,10 @@
         <v>42</v>
       </c>
       <c r="C3">
-        <v>411.05</v>
+        <v>392.75</v>
       </c>
       <c r="D3">
-        <v>-9.35</v>
+        <v>-4.45</v>
       </c>
       <c r="E3">
         <v>456.15</v>
@@ -1089,46 +1016,46 @@
         <v>225</v>
       </c>
       <c r="G3">
-        <v>-9.890000000000001</v>
+        <v>-13.9</v>
       </c>
       <c r="H3">
-        <v>82.69</v>
+        <v>74.56</v>
       </c>
       <c r="I3">
-        <v>-5.65</v>
+        <v>-8.32</v>
       </c>
       <c r="J3">
-        <v>2.61</v>
+        <v>-1.42</v>
       </c>
       <c r="K3">
-        <v>-3.51</v>
+        <v>-7.37</v>
       </c>
       <c r="L3">
-        <v>11.61</v>
+        <v>8.15</v>
       </c>
       <c r="M3">
-        <v>9.68</v>
+        <v>8.369999999999999</v>
       </c>
       <c r="N3">
         <v>60</v>
       </c>
       <c r="O3">
-        <v>66</v>
+        <v>58</v>
       </c>
       <c r="P3">
-        <v>439.03</v>
+        <v>431.9</v>
       </c>
       <c r="Q3">
-        <v>420.47</v>
+        <v>420.33</v>
       </c>
       <c r="R3">
-        <v>411.46</v>
+        <v>411.25</v>
       </c>
       <c r="S3">
-        <v>335.28</v>
+        <v>335.77</v>
       </c>
       <c r="T3">
-        <v>22.6</v>
+        <v>16.97</v>
       </c>
       <c r="U3" t="s">
         <v>43</v>
@@ -1143,43 +1070,43 @@
         <v>3</v>
       </c>
       <c r="Y3">
-        <v>45.82</v>
+        <v>40.43</v>
       </c>
       <c r="Z3">
-        <v>8.779999999999999</v>
+        <v>5.02</v>
       </c>
       <c r="AA3">
-        <v>8.25</v>
+        <v>7.6</v>
       </c>
       <c r="AB3">
-        <v>0.53</v>
+        <v>-2.59</v>
       </c>
       <c r="AC3">
-        <v>57.91</v>
+        <v>31.87</v>
       </c>
       <c r="AD3">
-        <v>75.77</v>
+        <v>59.41</v>
       </c>
       <c r="AE3">
-        <v>18.34</v>
+        <v>18.79</v>
       </c>
       <c r="AF3">
-        <v>-22.63</v>
+        <v>-43.86</v>
       </c>
       <c r="AG3">
-        <v>466.56</v>
+        <v>466.76</v>
       </c>
       <c r="AH3">
-        <v>374.39</v>
+        <v>373.89</v>
       </c>
       <c r="AI3">
-        <v>402.61</v>
+        <v>457.85</v>
       </c>
       <c r="AJ3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="AK3">
-        <v>41.51</v>
+        <v>40.84</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1190,10 +1117,10 @@
         <v>42</v>
       </c>
       <c r="C4">
-        <v>379.65</v>
+        <v>378.5</v>
       </c>
       <c r="D4">
-        <v>0.49</v>
+        <v>-0.3</v>
       </c>
       <c r="E4">
         <v>534</v>
@@ -1202,46 +1129,46 @@
         <v>344.7</v>
       </c>
       <c r="G4">
-        <v>-28.9</v>
+        <v>-29.12</v>
       </c>
       <c r="H4">
-        <v>10.14</v>
+        <v>9.81</v>
       </c>
       <c r="I4">
-        <v>-0.51</v>
+        <v>-1.96</v>
       </c>
       <c r="J4">
-        <v>-5.62</v>
+        <v>-5.86</v>
       </c>
       <c r="K4">
-        <v>-10.64</v>
+        <v>-10.96</v>
       </c>
       <c r="L4">
-        <v>-26.88</v>
+        <v>-28.6</v>
       </c>
       <c r="M4">
-        <v>-21.76</v>
+        <v>-21.84</v>
       </c>
       <c r="N4">
         <v>21</v>
       </c>
       <c r="O4">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="P4">
-        <v>381.85</v>
+        <v>380.34</v>
       </c>
       <c r="Q4">
-        <v>390.62</v>
+        <v>389.48</v>
       </c>
       <c r="R4">
-        <v>408.85</v>
+        <v>407.35</v>
       </c>
       <c r="S4">
-        <v>410.13</v>
+        <v>409.66</v>
       </c>
       <c r="T4">
-        <v>-7.43</v>
+        <v>-7.61</v>
       </c>
       <c r="U4" t="s">
         <v>44</v>
@@ -1256,43 +1183,43 @@
         <v>0</v>
       </c>
       <c r="Y4">
-        <v>32.12</v>
+        <v>31.19</v>
       </c>
       <c r="Z4">
-        <v>-7.92</v>
+        <v>-7.86</v>
       </c>
       <c r="AA4">
-        <v>-7.55</v>
+        <v>-7.61</v>
       </c>
       <c r="AB4">
-        <v>-0.36</v>
+        <v>-0.25</v>
       </c>
       <c r="AC4">
-        <v>21.46</v>
+        <v>24.17</v>
       </c>
       <c r="AD4">
-        <v>32.35</v>
+        <v>25.26</v>
       </c>
       <c r="AE4">
-        <v>10.77</v>
+        <v>10.57</v>
       </c>
       <c r="AF4">
-        <v>-26.49</v>
+        <v>40.29</v>
       </c>
       <c r="AG4">
-        <v>408.08</v>
+        <v>406.98</v>
       </c>
       <c r="AH4">
-        <v>373.16</v>
+        <v>371.98</v>
       </c>
       <c r="AI4">
-        <v>412.97</v>
+        <v>411.76</v>
       </c>
       <c r="AJ4" t="s">
         <v>45</v>
       </c>
       <c r="AK4">
-        <v>25.81</v>
+        <v>26.51</v>
       </c>
     </row>
     <row r="5" spans="1:37">
@@ -1303,10 +1230,10 @@
         <v>42</v>
       </c>
       <c r="C5">
-        <v>955</v>
+        <v>959.3</v>
       </c>
       <c r="D5">
-        <v>-0.1</v>
+        <v>0.45</v>
       </c>
       <c r="E5">
         <v>1069.3</v>
@@ -1315,46 +1242,46 @@
         <v>712.75</v>
       </c>
       <c r="G5">
-        <v>-10.69</v>
+        <v>-10.29</v>
       </c>
       <c r="H5">
-        <v>33.99</v>
+        <v>34.59</v>
       </c>
       <c r="I5">
-        <v>-0.16</v>
+        <v>1.35</v>
       </c>
       <c r="J5">
-        <v>-5.03</v>
+        <v>-5.8</v>
       </c>
       <c r="K5">
-        <v>5.47</v>
+        <v>3.42</v>
       </c>
       <c r="L5">
-        <v>29.22</v>
+        <v>30.44</v>
       </c>
       <c r="M5">
-        <v>-2.92</v>
+        <v>-3.3</v>
       </c>
       <c r="N5">
         <v>99</v>
       </c>
       <c r="O5">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="P5">
-        <v>956.4</v>
+        <v>958.96</v>
       </c>
       <c r="Q5">
-        <v>986.3</v>
+        <v>983.52</v>
       </c>
       <c r="R5">
-        <v>1005.43</v>
+        <v>1004.67</v>
       </c>
       <c r="S5">
-        <v>921.85</v>
+        <v>922.33</v>
       </c>
       <c r="T5">
-        <v>3.6</v>
+        <v>4.01</v>
       </c>
       <c r="U5" t="s">
         <v>44</v>
@@ -1369,34 +1296,34 @@
         <v>2</v>
       </c>
       <c r="Y5">
-        <v>38.45</v>
+        <v>40.38</v>
       </c>
       <c r="Z5">
         <v>-13.51</v>
       </c>
       <c r="AA5">
-        <v>-9.369999999999999</v>
+        <v>-10.2</v>
       </c>
       <c r="AB5">
-        <v>-4.14</v>
+        <v>-3.3</v>
       </c>
       <c r="AC5">
-        <v>33.85</v>
+        <v>33.45</v>
       </c>
       <c r="AD5">
-        <v>29.48</v>
+        <v>33.25</v>
       </c>
       <c r="AE5">
-        <v>19.2</v>
+        <v>19.18</v>
       </c>
       <c r="AF5">
-        <v>-44.68</v>
+        <v>49.77</v>
       </c>
       <c r="AG5">
-        <v>1031.23</v>
+        <v>1027.86</v>
       </c>
       <c r="AH5">
-        <v>941.38</v>
+        <v>939.1799999999999</v>
       </c>
       <c r="AI5">
         <v>1013.99</v>
@@ -1405,7 +1332,7 @@
         <v>45</v>
       </c>
       <c r="AK5">
-        <v>25.5</v>
+        <v>24.68</v>
       </c>
     </row>
     <row r="6" spans="1:37">
@@ -1419,55 +1346,55 @@
         <v>2.76</v>
       </c>
       <c r="D6">
-        <v>-1.08</v>
+        <v>0</v>
       </c>
       <c r="E6">
-        <v>3.62</v>
+        <v>3.61</v>
       </c>
       <c r="F6">
         <v>1.84</v>
       </c>
       <c r="G6">
-        <v>-23.76</v>
+        <v>-23.55</v>
       </c>
       <c r="H6">
         <v>50</v>
       </c>
       <c r="I6">
-        <v>0.36</v>
+        <v>-4.5</v>
       </c>
       <c r="J6">
-        <v>1.85</v>
+        <v>-9.210000000000001</v>
       </c>
       <c r="K6">
-        <v>9.52</v>
+        <v>6.56</v>
       </c>
       <c r="L6">
-        <v>-22.69</v>
+        <v>-23.76</v>
       </c>
       <c r="M6">
-        <v>3.01</v>
+        <v>3.8</v>
       </c>
       <c r="N6">
         <v>40</v>
       </c>
       <c r="O6">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="P6">
-        <v>2.81</v>
+        <v>2.78</v>
       </c>
       <c r="Q6">
-        <v>2.88</v>
+        <v>2.87</v>
       </c>
       <c r="R6">
-        <v>2.57</v>
+        <v>2.58</v>
       </c>
       <c r="S6">
         <v>2.67</v>
       </c>
       <c r="T6">
-        <v>3.39</v>
+        <v>3.45</v>
       </c>
       <c r="U6" t="s">
         <v>43</v>
@@ -1485,28 +1412,28 @@
         <v>50.27</v>
       </c>
       <c r="Z6">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="AA6">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="AB6">
         <v>-0.03</v>
       </c>
       <c r="AC6">
-        <v>3.57</v>
+        <v>2.34</v>
       </c>
       <c r="AD6">
-        <v>8.789999999999999</v>
+        <v>4.51</v>
       </c>
       <c r="AE6">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="AF6">
-        <v>-73.84999999999999</v>
+        <v>-70.37</v>
       </c>
       <c r="AG6">
-        <v>3.07</v>
+        <v>3.03</v>
       </c>
       <c r="AH6">
         <v>2.7</v>
@@ -1518,7 +1445,7 @@
         <v>46</v>
       </c>
       <c r="AK6">
-        <v>29.19</v>
+        <v>28.25</v>
       </c>
     </row>
   </sheetData>
@@ -1659,7 +1586,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F51"/>
+  <dimension ref="A1:F44"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.7109375" customWidth="1"/>
@@ -1679,845 +1606,685 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="3" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6">
+      <c r="A5" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="B5" s="2"/>
+      <c r="C5" s="2"/>
+      <c r="D5" s="2"/>
+      <c r="E5" s="2"/>
+    </row>
+    <row r="6" spans="1:6">
+      <c r="A6" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="D2" s="3" t="s">
+      <c r="B6" s="4" t="s">
         <v>50</v>
       </c>
-      <c r="E2" s="3" t="s">
+      <c r="C6" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="F2" s="3" t="s">
+      <c r="D6" s="4" t="s">
         <v>52</v>
       </c>
-    </row>
-    <row r="3" spans="1:6">
-      <c r="A3" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="B3" s="4" t="s">
+      <c r="E6" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="C3" s="4" t="s">
-        <v>54</v>
-      </c>
-      <c r="D3" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="E3" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="F3" s="4" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6">
-      <c r="A4" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B4" s="5" t="s">
-        <v>58</v>
-      </c>
-      <c r="C4" s="5" t="s">
-        <v>59</v>
-      </c>
-      <c r="D4" s="5" t="s">
-        <v>60</v>
-      </c>
-      <c r="E4" s="5" t="s">
-        <v>61</v>
-      </c>
-      <c r="F4" s="5" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6">
-      <c r="A5" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="B5" s="6" t="s">
-        <v>63</v>
-      </c>
-      <c r="C5" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="D5" s="6" t="s">
-        <v>65</v>
-      </c>
-      <c r="E5" s="6" t="s">
-        <v>66</v>
-      </c>
-      <c r="F5" s="6" t="s">
-        <v>67</v>
-      </c>
     </row>
     <row r="7" spans="1:6">
-      <c r="A7" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="B7" s="2"/>
-      <c r="C7" s="2"/>
-      <c r="D7" s="2"/>
-      <c r="E7" s="2"/>
+      <c r="A7" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C7" s="5">
+        <v>-7.08</v>
+      </c>
+      <c r="D7" s="5">
+        <v>-6</v>
+      </c>
+      <c r="E7" s="6">
+        <v>1.08</v>
+      </c>
     </row>
     <row r="8" spans="1:6">
       <c r="A8" s="3" t="s">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="C8" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="D8" s="3" t="s">
-        <v>71</v>
-      </c>
-      <c r="E8" s="3" t="s">
-        <v>72</v>
+        <v>9</v>
+      </c>
+      <c r="C8" s="5">
+        <v>2.61</v>
+      </c>
+      <c r="D8" s="5">
+        <v>-1.42</v>
+      </c>
+      <c r="E8" s="7">
+        <v>-4.03</v>
       </c>
     </row>
     <row r="9" spans="1:6">
-      <c r="A9" s="7" t="s">
+      <c r="A9" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C9" s="5">
+        <v>-5.62</v>
+      </c>
+      <c r="D9" s="5">
+        <v>-5.86</v>
+      </c>
+      <c r="E9" s="7">
+        <v>-0.24</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="A10" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C10" s="5">
+        <v>-5.03</v>
+      </c>
+      <c r="D10" s="5">
+        <v>-5.8</v>
+      </c>
+      <c r="E10" s="7">
+        <v>-0.77</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="A11" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C11" s="5">
+        <v>1.85</v>
+      </c>
+      <c r="D11" s="5">
+        <v>-9.210000000000001</v>
+      </c>
+      <c r="E11" s="7">
+        <v>-11.06</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6">
+      <c r="A12" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B9" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="C9" s="8">
-        <v>-6.93</v>
-      </c>
-      <c r="D9" s="8">
-        <v>-7.08</v>
-      </c>
-      <c r="E9" s="9">
-        <v>-0.15</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
-      <c r="A10" s="7" t="s">
+      <c r="B12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C12" s="5">
+        <v>2.62</v>
+      </c>
+      <c r="D12" s="5">
+        <v>4.08</v>
+      </c>
+      <c r="E12" s="6">
+        <v>1.46</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6">
+      <c r="A13" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B10" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="C10" s="8">
-        <v>13.86</v>
-      </c>
-      <c r="D10" s="8">
-        <v>2.61</v>
-      </c>
-      <c r="E10" s="9">
-        <v>-11.25</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
-      <c r="A11" s="7" t="s">
+      <c r="B13" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C13" s="5">
+        <v>-5.65</v>
+      </c>
+      <c r="D13" s="5">
+        <v>-8.32</v>
+      </c>
+      <c r="E13" s="7">
+        <v>-2.67</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6">
+      <c r="A14" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B11" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="C11" s="8">
-        <v>-7.06</v>
-      </c>
-      <c r="D11" s="8">
-        <v>-5.62</v>
-      </c>
-      <c r="E11" s="10">
-        <v>1.44</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
-      <c r="A12" s="7" t="s">
+      <c r="B14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C14" s="5">
+        <v>-0.51</v>
+      </c>
+      <c r="D14" s="5">
+        <v>-1.96</v>
+      </c>
+      <c r="E14" s="7">
+        <v>-1.45</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6">
+      <c r="A15" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="B12" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="C12" s="8">
-        <v>-5.16</v>
-      </c>
-      <c r="D12" s="8">
-        <v>-5.03</v>
-      </c>
-      <c r="E12" s="10">
-        <v>0.13</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
-      <c r="A13" s="7" t="s">
+      <c r="B15" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C15" s="5">
+        <v>-0.16</v>
+      </c>
+      <c r="D15" s="5">
+        <v>1.35</v>
+      </c>
+      <c r="E15" s="6">
+        <v>1.51</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6">
+      <c r="A16" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="B13" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="C13" s="8">
-        <v>23.45</v>
-      </c>
-      <c r="D13" s="8">
-        <v>1.85</v>
-      </c>
-      <c r="E13" s="9">
-        <v>-21.6</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
-      <c r="A14" s="7" t="s">
+      <c r="B16" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C16" s="5">
+        <v>0.36</v>
+      </c>
+      <c r="D16" s="5">
+        <v>-4.5</v>
+      </c>
+      <c r="E16" s="7">
+        <v>-4.86</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B14" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="C14" s="8">
-        <v>-1.22</v>
-      </c>
-      <c r="D14" s="8">
-        <v>2.62</v>
-      </c>
-      <c r="E14" s="10">
-        <v>3.84</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6">
-      <c r="A15" s="7" t="s">
+      <c r="B17" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C17" s="5">
+        <v>20.35</v>
+      </c>
+      <c r="D17" s="5">
+        <v>20.21</v>
+      </c>
+      <c r="E17" s="7">
+        <v>-0.14</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B15" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="C15" s="8">
-        <v>2.7</v>
-      </c>
-      <c r="D15" s="8">
-        <v>-5.65</v>
-      </c>
-      <c r="E15" s="9">
-        <v>-8.35</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
-      <c r="A16" s="7" t="s">
+      <c r="B18" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C18" s="5">
+        <v>11.61</v>
+      </c>
+      <c r="D18" s="5">
+        <v>8.15</v>
+      </c>
+      <c r="E18" s="7">
+        <v>-3.46</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B16" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="C16" s="8">
-        <v>-0.96</v>
-      </c>
-      <c r="D16" s="8">
-        <v>-0.51</v>
-      </c>
-      <c r="E16" s="10">
-        <v>0.45</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5">
-      <c r="A17" s="7" t="s">
+      <c r="B19" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C19" s="5">
+        <v>-26.88</v>
+      </c>
+      <c r="D19" s="5">
+        <v>-28.6</v>
+      </c>
+      <c r="E19" s="7">
+        <v>-1.72</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="B17" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="C17" s="8">
-        <v>-2.27</v>
-      </c>
-      <c r="D17" s="8">
-        <v>-0.16</v>
-      </c>
-      <c r="E17" s="10">
-        <v>2.11</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5">
-      <c r="A18" s="7" t="s">
+      <c r="B20" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C20" s="5">
+        <v>29.22</v>
+      </c>
+      <c r="D20" s="5">
+        <v>30.44</v>
+      </c>
+      <c r="E20" s="6">
+        <v>1.22</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="B18" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="C18" s="8">
-        <v>-2.45</v>
-      </c>
-      <c r="D18" s="8">
-        <v>0.36</v>
-      </c>
-      <c r="E18" s="10">
-        <v>2.81</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5">
-      <c r="A19" s="7" t="s">
+      <c r="B21" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C21" s="5">
+        <v>-22.69</v>
+      </c>
+      <c r="D21" s="5">
+        <v>-23.76</v>
+      </c>
+      <c r="E21" s="7">
+        <v>-1.07</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B19" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="C19" s="8">
-        <v>23.11</v>
-      </c>
-      <c r="D19" s="8">
-        <v>20.35</v>
-      </c>
-      <c r="E19" s="9">
-        <v>-2.76</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5">
-      <c r="A20" s="7" t="s">
+      <c r="B22" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C22" s="5">
+        <v>6.13</v>
+      </c>
+      <c r="D22" s="5">
+        <v>5.15</v>
+      </c>
+      <c r="E22" s="7">
+        <v>-0.98</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B20" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="C20" s="8">
-        <v>21.76</v>
-      </c>
-      <c r="D20" s="8">
-        <v>11.61</v>
-      </c>
-      <c r="E20" s="9">
-        <v>-10.15</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5">
-      <c r="A21" s="7" t="s">
+      <c r="B23" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C23" s="5">
+        <v>-3.51</v>
+      </c>
+      <c r="D23" s="5">
+        <v>-7.37</v>
+      </c>
+      <c r="E23" s="7">
+        <v>-3.86</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5">
+      <c r="A24" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B21" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="C21" s="8">
-        <v>-28.03</v>
-      </c>
-      <c r="D21" s="8">
-        <v>-26.88</v>
-      </c>
-      <c r="E21" s="10">
-        <v>1.15</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5">
-      <c r="A22" s="7" t="s">
+      <c r="B24" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C24" s="5">
+        <v>-10.64</v>
+      </c>
+      <c r="D24" s="5">
+        <v>-10.96</v>
+      </c>
+      <c r="E24" s="7">
+        <v>-0.32</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5">
+      <c r="A25" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="B22" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="C22" s="8">
-        <v>28.8</v>
-      </c>
-      <c r="D22" s="8">
-        <v>29.22</v>
-      </c>
-      <c r="E22" s="10">
-        <v>0.42</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5">
-      <c r="A23" s="7" t="s">
+      <c r="B25" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C25" s="5">
+        <v>5.47</v>
+      </c>
+      <c r="D25" s="5">
+        <v>3.42</v>
+      </c>
+      <c r="E25" s="7">
+        <v>-2.05</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
+      <c r="A26" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="B23" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="C23" s="8">
-        <v>-20.96</v>
-      </c>
-      <c r="D23" s="8">
-        <v>-22.69</v>
-      </c>
-      <c r="E23" s="9">
-        <v>-1.73</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5">
-      <c r="A24" s="7" t="s">
+      <c r="B26" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C26" s="5">
+        <v>9.52</v>
+      </c>
+      <c r="D26" s="5">
+        <v>6.56</v>
+      </c>
+      <c r="E26" s="7">
+        <v>-2.96</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5">
+      <c r="A27" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B24" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="C24" s="8">
-        <v>2.9</v>
-      </c>
-      <c r="D24" s="8">
-        <v>6.13</v>
-      </c>
-      <c r="E24" s="10">
-        <v>3.23</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5">
-      <c r="A25" s="7" t="s">
+      <c r="B27" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C27" s="5">
+        <v>-22.85</v>
+      </c>
+      <c r="D27" s="5">
+        <v>-21.83</v>
+      </c>
+      <c r="E27" s="6">
+        <v>1.02</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5">
+      <c r="A28" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B25" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="C25" s="8">
-        <v>1.83</v>
-      </c>
-      <c r="D25" s="8">
-        <v>-3.51</v>
-      </c>
-      <c r="E25" s="9">
-        <v>-5.34</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5">
-      <c r="A26" s="7" t="s">
+      <c r="B28" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C28" s="5">
+        <v>-9.890000000000001</v>
+      </c>
+      <c r="D28" s="5">
+        <v>-13.9</v>
+      </c>
+      <c r="E28" s="7">
+        <v>-4.01</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5">
+      <c r="A29" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B26" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="C26" s="8">
-        <v>-12.83</v>
-      </c>
-      <c r="D26" s="8">
-        <v>-10.64</v>
-      </c>
-      <c r="E26" s="10">
-        <v>2.19</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5">
-      <c r="A27" s="7" t="s">
+      <c r="B29" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C29" s="5">
+        <v>-28.9</v>
+      </c>
+      <c r="D29" s="5">
+        <v>-29.12</v>
+      </c>
+      <c r="E29" s="7">
+        <v>-0.22</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5">
+      <c r="A30" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="B27" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="C27" s="8">
-        <v>3.79</v>
-      </c>
-      <c r="D27" s="8">
-        <v>5.47</v>
-      </c>
-      <c r="E27" s="10">
-        <v>1.68</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5">
-      <c r="A28" s="7" t="s">
+      <c r="B30" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C30" s="5">
+        <v>-10.69</v>
+      </c>
+      <c r="D30" s="5">
+        <v>-10.29</v>
+      </c>
+      <c r="E30" s="6">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5">
+      <c r="A31" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="B28" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="C28" s="8">
-        <v>11.16</v>
-      </c>
-      <c r="D28" s="8">
-        <v>9.52</v>
-      </c>
-      <c r="E28" s="9">
-        <v>-1.64</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5">
-      <c r="A29" s="7" t="s">
+      <c r="B31" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C31" s="5">
+        <v>-23.76</v>
+      </c>
+      <c r="D31" s="5">
+        <v>-23.55</v>
+      </c>
+      <c r="E31" s="6">
+        <v>0.21</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5">
+      <c r="A32" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B29" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="C29" s="8">
-        <v>-22.37</v>
-      </c>
-      <c r="D29" s="8">
-        <v>-22.85</v>
-      </c>
-      <c r="E29" s="9">
-        <v>-0.48</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5">
-      <c r="A30" s="7" t="s">
+      <c r="B32" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C32" s="5">
+        <v>160.75</v>
+      </c>
+      <c r="D32" s="5">
+        <v>162.89</v>
+      </c>
+      <c r="E32" s="6">
+        <v>2.14</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5">
+      <c r="A33" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B30" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="C30" s="8">
-        <v>-0.59</v>
-      </c>
-      <c r="D30" s="8">
-        <v>-9.890000000000001</v>
-      </c>
-      <c r="E30" s="9">
-        <v>-9.300000000000001</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5">
-      <c r="A31" s="7" t="s">
+      <c r="B33" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C33" s="5">
+        <v>411.05</v>
+      </c>
+      <c r="D33" s="5">
+        <v>392.75</v>
+      </c>
+      <c r="E33" s="7">
+        <v>-18.3</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5">
+      <c r="A34" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B31" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="C31" s="8">
-        <v>-29.25</v>
-      </c>
-      <c r="D31" s="8">
-        <v>-28.9</v>
-      </c>
-      <c r="E31" s="10">
-        <v>0.35</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5">
-      <c r="A32" s="7" t="s">
+      <c r="B34" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C34" s="5">
+        <v>379.65</v>
+      </c>
+      <c r="D34" s="5">
+        <v>378.5</v>
+      </c>
+      <c r="E34" s="7">
+        <v>-1.15</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5">
+      <c r="A35" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="B32" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="C32" s="8">
-        <v>-10.6</v>
-      </c>
-      <c r="D32" s="8">
-        <v>-10.69</v>
-      </c>
-      <c r="E32" s="9">
-        <v>-0.09</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5">
-      <c r="A33" s="7" t="s">
+      <c r="B35" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C35" s="5">
+        <v>955</v>
+      </c>
+      <c r="D35" s="5">
+        <v>959.3</v>
+      </c>
+      <c r="E35" s="6">
+        <v>4.3</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5">
+      <c r="A36" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B36" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C36" s="5">
+        <v>40.33</v>
+      </c>
+      <c r="D36" s="5">
+        <v>44.61</v>
+      </c>
+      <c r="E36" s="6">
+        <v>4.28</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5">
+      <c r="A37" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B37" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C37" s="5">
+        <v>45.82</v>
+      </c>
+      <c r="D37" s="5">
+        <v>40.43</v>
+      </c>
+      <c r="E37" s="7">
+        <v>-5.39</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5">
+      <c r="A38" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B38" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C38" s="5">
+        <v>32.12</v>
+      </c>
+      <c r="D38" s="5">
+        <v>31.19</v>
+      </c>
+      <c r="E38" s="7">
+        <v>-0.93</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5">
+      <c r="A39" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B39" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C39" s="5">
+        <v>38.45</v>
+      </c>
+      <c r="D39" s="5">
+        <v>40.38</v>
+      </c>
+      <c r="E39" s="6">
+        <v>1.93</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5">
+      <c r="A40" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B40" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C40" s="5">
+        <v>-27.88</v>
+      </c>
+      <c r="D40" s="5">
+        <v>-68.15000000000001</v>
+      </c>
+      <c r="E40" s="7">
+        <v>-40.27</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5">
+      <c r="A41" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B41" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C41" s="5">
+        <v>-22.63</v>
+      </c>
+      <c r="D41" s="5">
+        <v>-43.86</v>
+      </c>
+      <c r="E41" s="7">
+        <v>-21.23</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5">
+      <c r="A42" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B42" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C42" s="5">
+        <v>-26.49</v>
+      </c>
+      <c r="D42" s="5">
+        <v>40.29</v>
+      </c>
+      <c r="E42" s="6">
+        <v>66.78</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5">
+      <c r="A43" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B43" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C43" s="5">
+        <v>-44.68</v>
+      </c>
+      <c r="D43" s="5">
+        <v>49.77</v>
+      </c>
+      <c r="E43" s="6">
+        <v>94.45</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5">
+      <c r="A44" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="B33" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="C33" s="8">
-        <v>-22.93</v>
-      </c>
-      <c r="D33" s="8">
-        <v>-23.76</v>
-      </c>
-      <c r="E33" s="9">
-        <v>-0.83</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5">
-      <c r="A34" s="7" t="s">
-        <v>37</v>
-      </c>
-      <c r="B34" s="7" t="s">
-        <v>2</v>
-      </c>
-      <c r="C34" s="8">
-        <v>161.75</v>
-      </c>
-      <c r="D34" s="8">
-        <v>160.75</v>
-      </c>
-      <c r="E34" s="9">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5">
-      <c r="A35" s="7" t="s">
-        <v>38</v>
-      </c>
-      <c r="B35" s="7" t="s">
-        <v>2</v>
-      </c>
-      <c r="C35" s="8">
-        <v>453.45</v>
-      </c>
-      <c r="D35" s="8">
-        <v>411.05</v>
-      </c>
-      <c r="E35" s="9">
-        <v>-42.4</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5">
-      <c r="A36" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="B36" s="7" t="s">
-        <v>2</v>
-      </c>
-      <c r="C36" s="8">
-        <v>377.8</v>
-      </c>
-      <c r="D36" s="8">
-        <v>379.65</v>
-      </c>
-      <c r="E36" s="10">
-        <v>1.85</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5">
-      <c r="A37" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="B37" s="7" t="s">
-        <v>2</v>
-      </c>
-      <c r="C37" s="8">
-        <v>956</v>
-      </c>
-      <c r="D37" s="8">
-        <v>955</v>
-      </c>
-      <c r="E37" s="9">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5">
-      <c r="A38" s="7" t="s">
-        <v>41</v>
-      </c>
-      <c r="B38" s="7" t="s">
-        <v>2</v>
-      </c>
-      <c r="C38" s="8">
-        <v>2.79</v>
-      </c>
-      <c r="D38" s="8">
-        <v>2.76</v>
-      </c>
-      <c r="E38" s="9">
-        <v>-0.03</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5">
-      <c r="A39" s="7" t="s">
-        <v>37</v>
-      </c>
-      <c r="B39" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="C39" s="8">
-        <v>60</v>
-      </c>
-      <c r="D39" s="8">
-        <v>79</v>
-      </c>
-      <c r="E39" s="10">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5">
-      <c r="A40" s="7" t="s">
-        <v>38</v>
-      </c>
-      <c r="B40" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="C40" s="8">
-        <v>99</v>
-      </c>
-      <c r="D40" s="8">
-        <v>60</v>
-      </c>
-      <c r="E40" s="9">
-        <v>-39</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5">
-      <c r="A41" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="B41" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="C41" s="8">
-        <v>79</v>
-      </c>
-      <c r="D41" s="8">
-        <v>99</v>
-      </c>
-      <c r="E41" s="10">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5">
-      <c r="A42" s="7" t="s">
-        <v>37</v>
-      </c>
-      <c r="B42" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="C42" s="8">
-        <v>41.73</v>
-      </c>
-      <c r="D42" s="8">
-        <v>40.33</v>
-      </c>
-      <c r="E42" s="9">
-        <v>-1.4</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5">
-      <c r="A43" s="7" t="s">
-        <v>38</v>
-      </c>
-      <c r="B43" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="C43" s="8">
-        <v>64.26000000000001</v>
-      </c>
-      <c r="D43" s="8">
-        <v>45.82</v>
-      </c>
-      <c r="E43" s="9">
-        <v>-18.44</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5">
-      <c r="A44" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="B44" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="C44" s="8">
-        <v>28.98</v>
-      </c>
-      <c r="D44" s="8">
-        <v>32.12</v>
-      </c>
-      <c r="E44" s="10">
-        <v>3.14</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5">
-      <c r="A45" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="B45" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="C45" s="8">
-        <v>38.72</v>
-      </c>
-      <c r="D45" s="8">
-        <v>38.45</v>
-      </c>
-      <c r="E45" s="9">
-        <v>-0.27</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5">
-      <c r="A46" s="7" t="s">
-        <v>41</v>
-      </c>
-      <c r="B46" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="C46" s="8">
-        <v>52.16</v>
-      </c>
-      <c r="D46" s="8">
-        <v>50.27</v>
-      </c>
-      <c r="E46" s="9">
-        <v>-1.89</v>
-      </c>
-    </row>
-    <row r="47" spans="1:5">
-      <c r="A47" s="7" t="s">
-        <v>37</v>
-      </c>
-      <c r="B47" s="7" t="s">
+      <c r="B44" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="C47" s="8">
-        <v>-35.88</v>
-      </c>
-      <c r="D47" s="8">
-        <v>-27.88</v>
-      </c>
-      <c r="E47" s="10">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="48" spans="1:5">
-      <c r="A48" s="7" t="s">
-        <v>38</v>
-      </c>
-      <c r="B48" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="C48" s="8">
-        <v>53.54</v>
-      </c>
-      <c r="D48" s="8">
-        <v>-22.63</v>
-      </c>
-      <c r="E48" s="9">
-        <v>-76.17</v>
-      </c>
-    </row>
-    <row r="49" spans="1:5">
-      <c r="A49" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="B49" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="C49" s="8">
-        <v>-48.73</v>
-      </c>
-      <c r="D49" s="8">
-        <v>-26.49</v>
-      </c>
-      <c r="E49" s="10">
-        <v>22.24</v>
-      </c>
-    </row>
-    <row r="50" spans="1:5">
-      <c r="A50" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="B50" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="C50" s="8">
-        <v>-66.77</v>
-      </c>
-      <c r="D50" s="8">
-        <v>-44.68</v>
-      </c>
-      <c r="E50" s="10">
-        <v>22.09</v>
-      </c>
-    </row>
-    <row r="51" spans="1:5">
-      <c r="A51" s="7" t="s">
-        <v>41</v>
-      </c>
-      <c r="B51" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="C51" s="8">
-        <v>-66.13</v>
-      </c>
-      <c r="D51" s="8">
+      <c r="C44" s="5">
         <v>-73.84999999999999</v>
       </c>
-      <c r="E51" s="9">
-        <v>-7.72</v>
+      <c r="D44" s="5">
+        <v>-70.37</v>
+      </c>
+      <c r="E44" s="6">
+        <v>3.48</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A7:E7"/>
+    <mergeCell ref="A5:E5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2537,60 +2304,60 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="28" customHeight="1">
-      <c r="A1" s="11" t="s">
+      <c r="A1" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="11" t="s">
-        <v>73</v>
-      </c>
-      <c r="C1" s="11" t="s">
-        <v>74</v>
-      </c>
-      <c r="D1" s="11" t="s">
-        <v>75</v>
-      </c>
-      <c r="E1" s="11" t="s">
-        <v>76</v>
-      </c>
-      <c r="F1" s="11" t="s">
-        <v>77</v>
-      </c>
-      <c r="G1" s="11" t="s">
-        <v>78</v>
-      </c>
-      <c r="H1" s="11" t="s">
-        <v>79</v>
-      </c>
-      <c r="I1" s="11" t="s">
-        <v>80</v>
+      <c r="B1" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="C1" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="D1" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="E1" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="F1" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="G1" s="8" t="s">
+        <v>59</v>
+      </c>
+      <c r="H1" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="I1" s="8" t="s">
+        <v>61</v>
       </c>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="12" t="s">
+      <c r="A2" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="B2" s="13">
+      <c r="B2" s="10">
         <v>57.92</v>
       </c>
-      <c r="C2" s="14">
+      <c r="C2" s="11">
         <v>5</v>
       </c>
-      <c r="D2" s="13">
+      <c r="D2" s="10">
         <v>41.4</v>
       </c>
-      <c r="E2" s="13">
+      <c r="E2" s="10">
         <v>60</v>
       </c>
-      <c r="F2" s="13">
-        <v>-2.7</v>
-      </c>
-      <c r="G2" s="13">
-        <v>1.4</v>
-      </c>
-      <c r="H2" s="13">
+      <c r="F2" s="10">
+        <v>-5.7</v>
+      </c>
+      <c r="G2" s="10">
+        <v>-0.6</v>
+      </c>
+      <c r="H2" s="10">
         <v>59.8</v>
       </c>
-      <c r="I2" s="13">
+      <c r="I2" s="10">
         <v>20</v>
       </c>
     </row>
@@ -2692,37 +2459,37 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
-      <c r="A1" s="15" t="s">
+      <c r="A1" s="12" t="s">
         <v>37</v>
       </c>
-      <c r="B1" s="15" t="s">
+      <c r="B1" s="12" t="s">
         <v>38</v>
       </c>
-      <c r="C1" s="15" t="s">
+      <c r="C1" s="12" t="s">
         <v>41</v>
       </c>
-      <c r="D1" s="15" t="s">
+      <c r="D1" s="12" t="s">
         <v>40</v>
       </c>
-      <c r="E1" s="15" t="s">
+      <c r="E1" s="12" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="2" spans="1:5">
-      <c r="A2" s="16">
-        <v>0.2264</v>
-      </c>
-      <c r="B2" s="16">
-        <v>0.0968</v>
-      </c>
-      <c r="C2" s="16">
-        <v>0.0301</v>
-      </c>
-      <c r="D2" s="16">
-        <v>-0.0292</v>
-      </c>
-      <c r="E2" s="16">
-        <v>-0.2176</v>
+      <c r="A2" s="13">
+        <v>0.2286</v>
+      </c>
+      <c r="B2" s="13">
+        <v>0.0837</v>
+      </c>
+      <c r="C2" s="13">
+        <v>0.038</v>
+      </c>
+      <c r="D2" s="13">
+        <v>-0.033</v>
+      </c>
+      <c r="E2" s="13">
+        <v>-0.2184</v>
       </c>
     </row>
   </sheetData>

--- a/HINDUJA_GROUP_Technical_Metrics.xlsx
+++ b/HINDUJA_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="203" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="224" uniqueCount="73">
   <si>
     <t>Symbol</t>
   </si>
@@ -151,12 +151,12 @@
     <t>Unknown</t>
   </si>
   <si>
+    <t>No</t>
+  </si>
+  <si>
     <t>Yes</t>
   </si>
   <si>
-    <t>No</t>
-  </si>
-  <si>
     <t>DOWN</t>
   </si>
   <si>
@@ -166,7 +166,40 @@
     <t>▶  SIGNAL EVENTS (vs Previous Run)</t>
   </si>
   <si>
-    <t>No signal events detected since last run.</t>
+    <t>Signal</t>
+  </si>
+  <si>
+    <t>Change</t>
+  </si>
+  <si>
+    <t>Direction</t>
+  </si>
+  <si>
+    <t>Prev Value</t>
+  </si>
+  <si>
+    <t>Curr Value</t>
+  </si>
+  <si>
+    <t>20 DMA &gt; 50 DMA</t>
+  </si>
+  <si>
+    <t>Yes → No</t>
+  </si>
+  <si>
+    <t>🔴 BEARISH</t>
+  </si>
+  <si>
+    <t>RSI Momentum</t>
+  </si>
+  <si>
+    <t>50.3 → 45.8</t>
+  </si>
+  <si>
+    <t>50.3</t>
+  </si>
+  <si>
+    <t>45.8</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -252,14 +285,14 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FF9C0006"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FF006100"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -292,13 +325,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -368,14 +401,15 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -891,10 +925,10 @@
         <v>42</v>
       </c>
       <c r="C2">
-        <v>162.89</v>
+        <v>157.3</v>
       </c>
       <c r="D2">
-        <v>1.33</v>
+        <v>-3.43</v>
       </c>
       <c r="E2">
         <v>208.37</v>
@@ -903,88 +937,88 @@
         <v>131.36</v>
       </c>
       <c r="G2">
-        <v>-21.83</v>
+        <v>-24.51</v>
       </c>
       <c r="H2">
-        <v>24</v>
+        <v>19.75</v>
       </c>
       <c r="I2">
-        <v>4.08</v>
+        <v>-0.83</v>
       </c>
       <c r="J2">
-        <v>-6</v>
+        <v>-9.949999999999999</v>
       </c>
       <c r="K2">
-        <v>5.15</v>
+        <v>-2.1</v>
       </c>
       <c r="L2">
-        <v>20.21</v>
+        <v>14.33</v>
       </c>
       <c r="M2">
-        <v>22.86</v>
+        <v>22.28</v>
       </c>
       <c r="N2">
         <v>79</v>
       </c>
       <c r="O2">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="P2">
-        <v>161.4</v>
+        <v>161.14</v>
       </c>
       <c r="Q2">
-        <v>167.03</v>
+        <v>165.95</v>
       </c>
       <c r="R2">
-        <v>166.77</v>
+        <v>166.78</v>
       </c>
       <c r="S2">
         <v>169.95</v>
       </c>
       <c r="T2">
-        <v>-4.16</v>
+        <v>-7.44</v>
       </c>
       <c r="U2" t="s">
         <v>43</v>
       </c>
       <c r="V2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="W2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="X2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y2">
-        <v>44.61</v>
+        <v>37.13</v>
       </c>
       <c r="Z2">
-        <v>-2.52</v>
+        <v>-2.81</v>
       </c>
       <c r="AA2">
-        <v>-1.82</v>
+        <v>-2.02</v>
       </c>
       <c r="AB2">
-        <v>-0.7</v>
+        <v>-0.79</v>
       </c>
       <c r="AC2">
-        <v>66.86</v>
+        <v>58.83</v>
       </c>
       <c r="AD2">
-        <v>55.76</v>
+        <v>60.82</v>
       </c>
       <c r="AE2">
-        <v>4.12</v>
+        <v>4.25</v>
       </c>
       <c r="AF2">
-        <v>-68.15000000000001</v>
+        <v>-33.99</v>
       </c>
       <c r="AG2">
-        <v>180.32</v>
+        <v>178.64</v>
       </c>
       <c r="AH2">
-        <v>153.74</v>
+        <v>153.25</v>
       </c>
       <c r="AI2">
         <v>169.79</v>
@@ -993,7 +1027,7 @@
         <v>45</v>
       </c>
       <c r="AK2">
-        <v>29.76</v>
+        <v>31.76</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1004,10 +1038,10 @@
         <v>42</v>
       </c>
       <c r="C3">
-        <v>392.75</v>
+        <v>380.25</v>
       </c>
       <c r="D3">
-        <v>-4.45</v>
+        <v>-3.18</v>
       </c>
       <c r="E3">
         <v>456.15</v>
@@ -1016,97 +1050,97 @@
         <v>225</v>
       </c>
       <c r="G3">
-        <v>-13.9</v>
+        <v>-16.64</v>
       </c>
       <c r="H3">
-        <v>74.56</v>
+        <v>69</v>
       </c>
       <c r="I3">
-        <v>-8.32</v>
+        <v>-16.64</v>
       </c>
       <c r="J3">
-        <v>-1.42</v>
+        <v>-3.9</v>
       </c>
       <c r="K3">
-        <v>-7.37</v>
+        <v>-6.98</v>
       </c>
       <c r="L3">
-        <v>8.15</v>
+        <v>4.09</v>
       </c>
       <c r="M3">
-        <v>8.369999999999999</v>
+        <v>7.59</v>
       </c>
       <c r="N3">
         <v>60</v>
       </c>
       <c r="O3">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="P3">
-        <v>431.9</v>
+        <v>416.72</v>
       </c>
       <c r="Q3">
-        <v>420.33</v>
+        <v>419.47</v>
       </c>
       <c r="R3">
-        <v>411.25</v>
+        <v>410.79</v>
       </c>
       <c r="S3">
-        <v>335.77</v>
+        <v>336.2</v>
       </c>
       <c r="T3">
-        <v>16.97</v>
+        <v>13.1</v>
       </c>
       <c r="U3" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="V3" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="W3" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="X3">
         <v>3</v>
       </c>
       <c r="Y3">
-        <v>40.43</v>
+        <v>37.21</v>
       </c>
       <c r="Z3">
-        <v>5.02</v>
+        <v>1.01</v>
       </c>
       <c r="AA3">
-        <v>7.6</v>
+        <v>6.29</v>
       </c>
       <c r="AB3">
-        <v>-2.59</v>
+        <v>-5.27</v>
       </c>
       <c r="AC3">
-        <v>31.87</v>
+        <v>2.79</v>
       </c>
       <c r="AD3">
-        <v>59.41</v>
+        <v>30.86</v>
       </c>
       <c r="AE3">
-        <v>18.79</v>
+        <v>18.96</v>
       </c>
       <c r="AF3">
-        <v>-43.86</v>
+        <v>-61.45</v>
       </c>
       <c r="AG3">
-        <v>466.76</v>
+        <v>468.26</v>
       </c>
       <c r="AH3">
-        <v>373.89</v>
+        <v>370.67</v>
       </c>
       <c r="AI3">
-        <v>457.85</v>
+        <v>444.49</v>
       </c>
       <c r="AJ3" t="s">
         <v>45</v>
       </c>
       <c r="AK3">
-        <v>40.84</v>
+        <v>41.43</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1117,10 +1151,10 @@
         <v>42</v>
       </c>
       <c r="C4">
-        <v>378.5</v>
+        <v>374.55</v>
       </c>
       <c r="D4">
-        <v>-0.3</v>
+        <v>-1.04</v>
       </c>
       <c r="E4">
         <v>534</v>
@@ -1129,97 +1163,97 @@
         <v>344.7</v>
       </c>
       <c r="G4">
-        <v>-29.12</v>
+        <v>-29.86</v>
       </c>
       <c r="H4">
-        <v>9.81</v>
+        <v>8.66</v>
       </c>
       <c r="I4">
-        <v>-1.96</v>
+        <v>-3.05</v>
       </c>
       <c r="J4">
-        <v>-5.86</v>
+        <v>-6.67</v>
       </c>
       <c r="K4">
-        <v>-10.96</v>
+        <v>-10.87</v>
       </c>
       <c r="L4">
-        <v>-28.6</v>
+        <v>-29.46</v>
       </c>
       <c r="M4">
-        <v>-21.84</v>
+        <v>-21.89</v>
       </c>
       <c r="N4">
         <v>21</v>
       </c>
       <c r="O4">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="P4">
-        <v>380.34</v>
+        <v>377.98</v>
       </c>
       <c r="Q4">
-        <v>389.48</v>
+        <v>388.11</v>
       </c>
       <c r="R4">
-        <v>407.35</v>
+        <v>405.92</v>
       </c>
       <c r="S4">
-        <v>409.66</v>
+        <v>409.19</v>
       </c>
       <c r="T4">
-        <v>-7.61</v>
+        <v>-8.470000000000001</v>
       </c>
       <c r="U4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="V4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="W4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="X4">
         <v>0</v>
       </c>
       <c r="Y4">
-        <v>31.19</v>
+        <v>28.2</v>
       </c>
       <c r="Z4">
-        <v>-7.86</v>
+        <v>-8.039999999999999</v>
       </c>
       <c r="AA4">
-        <v>-7.61</v>
+        <v>-7.7</v>
       </c>
       <c r="AB4">
-        <v>-0.25</v>
+        <v>-0.34</v>
       </c>
       <c r="AC4">
-        <v>24.17</v>
+        <v>22.24</v>
       </c>
       <c r="AD4">
-        <v>25.26</v>
+        <v>22.62</v>
       </c>
       <c r="AE4">
-        <v>10.57</v>
+        <v>10.38</v>
       </c>
       <c r="AF4">
-        <v>40.29</v>
+        <v>-49.74</v>
       </c>
       <c r="AG4">
-        <v>406.98</v>
+        <v>405.79</v>
       </c>
       <c r="AH4">
-        <v>371.98</v>
+        <v>370.43</v>
       </c>
       <c r="AI4">
-        <v>411.76</v>
+        <v>408.12</v>
       </c>
       <c r="AJ4" t="s">
         <v>45</v>
       </c>
       <c r="AK4">
-        <v>26.51</v>
+        <v>28.43</v>
       </c>
     </row>
     <row r="5" spans="1:37">
@@ -1230,10 +1264,10 @@
         <v>42</v>
       </c>
       <c r="C5">
-        <v>959.3</v>
+        <v>919.5</v>
       </c>
       <c r="D5">
-        <v>0.45</v>
+        <v>-4.15</v>
       </c>
       <c r="E5">
         <v>1069.3</v>
@@ -1242,97 +1276,97 @@
         <v>712.75</v>
       </c>
       <c r="G5">
-        <v>-10.29</v>
+        <v>-14.01</v>
       </c>
       <c r="H5">
-        <v>34.59</v>
+        <v>29.01</v>
       </c>
       <c r="I5">
-        <v>1.35</v>
+        <v>-4.04</v>
       </c>
       <c r="J5">
-        <v>-5.8</v>
+        <v>-9.41</v>
       </c>
       <c r="K5">
-        <v>3.42</v>
+        <v>0.06</v>
       </c>
       <c r="L5">
-        <v>30.44</v>
+        <v>23.52</v>
       </c>
       <c r="M5">
-        <v>-3.3</v>
+        <v>-4.02</v>
       </c>
       <c r="N5">
         <v>99</v>
       </c>
       <c r="O5">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="P5">
-        <v>958.96</v>
+        <v>951.22</v>
       </c>
       <c r="Q5">
-        <v>983.52</v>
+        <v>979.29</v>
       </c>
       <c r="R5">
-        <v>1004.67</v>
+        <v>1002.87</v>
       </c>
       <c r="S5">
-        <v>922.33</v>
+        <v>922.58</v>
       </c>
       <c r="T5">
-        <v>4.01</v>
+        <v>-0.33</v>
       </c>
       <c r="U5" t="s">
+        <v>43</v>
+      </c>
+      <c r="V5" t="s">
         <v>44</v>
       </c>
-      <c r="V5" t="s">
+      <c r="W5" t="s">
         <v>43</v>
       </c>
-      <c r="W5" t="s">
-        <v>44</v>
-      </c>
       <c r="X5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y5">
-        <v>40.38</v>
+        <v>30.78</v>
       </c>
       <c r="Z5">
-        <v>-13.51</v>
+        <v>-16.52</v>
       </c>
       <c r="AA5">
-        <v>-10.2</v>
+        <v>-11.46</v>
       </c>
       <c r="AB5">
-        <v>-3.3</v>
+        <v>-5.06</v>
       </c>
       <c r="AC5">
-        <v>33.45</v>
+        <v>23.18</v>
       </c>
       <c r="AD5">
-        <v>33.25</v>
+        <v>30.16</v>
       </c>
       <c r="AE5">
-        <v>19.18</v>
+        <v>21.38</v>
       </c>
       <c r="AF5">
-        <v>49.77</v>
+        <v>219.68</v>
       </c>
       <c r="AG5">
-        <v>1027.86</v>
+        <v>1030.92</v>
       </c>
       <c r="AH5">
-        <v>939.1799999999999</v>
+        <v>927.67</v>
       </c>
       <c r="AI5">
-        <v>1013.99</v>
+        <v>983.25</v>
       </c>
       <c r="AJ5" t="s">
         <v>45</v>
       </c>
       <c r="AK5">
-        <v>24.68</v>
+        <v>29.02</v>
       </c>
     </row>
     <row r="6" spans="1:37">
@@ -1343,100 +1377,100 @@
         <v>42</v>
       </c>
       <c r="C6">
-        <v>2.76</v>
+        <v>2.69</v>
       </c>
       <c r="D6">
-        <v>0</v>
+        <v>-2.54</v>
       </c>
       <c r="E6">
-        <v>3.61</v>
+        <v>3.55</v>
       </c>
       <c r="F6">
         <v>1.84</v>
       </c>
       <c r="G6">
-        <v>-23.55</v>
+        <v>-24.23</v>
       </c>
       <c r="H6">
-        <v>50</v>
+        <v>46.2</v>
       </c>
       <c r="I6">
-        <v>-4.5</v>
+        <v>-4.61</v>
       </c>
       <c r="J6">
-        <v>-9.210000000000001</v>
+        <v>-12.66</v>
       </c>
       <c r="K6">
-        <v>6.56</v>
+        <v>9.35</v>
       </c>
       <c r="L6">
-        <v>-23.76</v>
+        <v>-25.48</v>
       </c>
       <c r="M6">
-        <v>3.8</v>
+        <v>3.27</v>
       </c>
       <c r="N6">
         <v>40</v>
       </c>
       <c r="O6">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="P6">
-        <v>2.78</v>
+        <v>2.76</v>
       </c>
       <c r="Q6">
-        <v>2.87</v>
+        <v>2.85</v>
       </c>
       <c r="R6">
-        <v>2.58</v>
+        <v>2.59</v>
       </c>
       <c r="S6">
         <v>2.67</v>
       </c>
       <c r="T6">
-        <v>3.45</v>
+        <v>0.89</v>
       </c>
       <c r="U6" t="s">
+        <v>44</v>
+      </c>
+      <c r="V6" t="s">
         <v>43</v>
       </c>
-      <c r="V6" t="s">
-        <v>44</v>
-      </c>
       <c r="W6" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="X6">
         <v>2</v>
       </c>
       <c r="Y6">
-        <v>50.27</v>
+        <v>45.8</v>
       </c>
       <c r="Z6">
-        <v>0.05</v>
+        <v>0.03</v>
       </c>
       <c r="AA6">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="AB6">
-        <v>-0.03</v>
+        <v>-0.04</v>
       </c>
       <c r="AC6">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="AD6">
-        <v>4.51</v>
+        <v>1.97</v>
       </c>
       <c r="AE6">
         <v>0.14</v>
       </c>
       <c r="AF6">
-        <v>-70.37</v>
+        <v>-20.38</v>
       </c>
       <c r="AG6">
-        <v>3.03</v>
+        <v>3.02</v>
       </c>
       <c r="AH6">
-        <v>2.7</v>
+        <v>2.68</v>
       </c>
       <c r="AI6">
         <v>2.65</v>
@@ -1445,7 +1479,7 @@
         <v>46</v>
       </c>
       <c r="AK6">
-        <v>28.25</v>
+        <v>24.91</v>
       </c>
     </row>
   </sheetData>
@@ -1586,7 +1620,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F44"/>
+  <dimension ref="A1:F47"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.7109375" customWidth="1"/>
@@ -1606,685 +1640,774 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="3" t="s">
         <v>48</v>
       </c>
-    </row>
-    <row r="5" spans="1:6">
-      <c r="A5" s="2" t="s">
+      <c r="C2" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="B5" s="2"/>
-      <c r="C5" s="2"/>
-      <c r="D5" s="2"/>
-      <c r="E5" s="2"/>
+      <c r="D2" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
+      <c r="A3" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6">
+      <c r="A4" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="F4" s="4" t="s">
+        <v>59</v>
+      </c>
     </row>
     <row r="6" spans="1:6">
-      <c r="A6" s="4" t="s">
-        <v>0</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>51</v>
-      </c>
-      <c r="D6" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="E6" s="4" t="s">
-        <v>53</v>
-      </c>
+      <c r="A6" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="B6" s="2"/>
+      <c r="C6" s="2"/>
+      <c r="D6" s="2"/>
+      <c r="E6" s="2"/>
     </row>
     <row r="7" spans="1:6">
       <c r="A7" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6">
+      <c r="A8" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B7" s="3" t="s">
+      <c r="B8" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C7" s="5">
-        <v>-7.08</v>
-      </c>
-      <c r="D7" s="5">
+      <c r="C8" s="6">
         <v>-6</v>
       </c>
-      <c r="E7" s="6">
-        <v>1.08</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6">
-      <c r="A8" s="3" t="s">
+      <c r="D8" s="6">
+        <v>-9.949999999999999</v>
+      </c>
+      <c r="E8" s="7">
+        <v>-3.95</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="A9" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B8" s="3" t="s">
+      <c r="B9" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C8" s="5">
-        <v>2.61</v>
-      </c>
-      <c r="D8" s="5">
+      <c r="C9" s="6">
         <v>-1.42</v>
       </c>
-      <c r="E8" s="7">
-        <v>-4.03</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
-      <c r="A9" s="3" t="s">
+      <c r="D9" s="6">
+        <v>-3.9</v>
+      </c>
+      <c r="E9" s="7">
+        <v>-2.48</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="A10" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B9" s="3" t="s">
+      <c r="B10" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C9" s="5">
-        <v>-5.62</v>
-      </c>
-      <c r="D9" s="5">
+      <c r="C10" s="6">
         <v>-5.86</v>
       </c>
-      <c r="E9" s="7">
-        <v>-0.24</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
-      <c r="A10" s="3" t="s">
+      <c r="D10" s="6">
+        <v>-6.67</v>
+      </c>
+      <c r="E10" s="7">
+        <v>-0.8100000000000001</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="A11" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="B10" s="3" t="s">
+      <c r="B11" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C10" s="5">
-        <v>-5.03</v>
-      </c>
-      <c r="D10" s="5">
+      <c r="C11" s="6">
         <v>-5.8</v>
       </c>
-      <c r="E10" s="7">
-        <v>-0.77</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
-      <c r="A11" s="3" t="s">
+      <c r="D11" s="6">
+        <v>-9.41</v>
+      </c>
+      <c r="E11" s="7">
+        <v>-3.61</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6">
+      <c r="A12" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B11" s="3" t="s">
+      <c r="B12" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C11" s="5">
-        <v>1.85</v>
-      </c>
-      <c r="D11" s="5">
+      <c r="C12" s="6">
         <v>-9.210000000000001</v>
       </c>
-      <c r="E11" s="7">
-        <v>-11.06</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
-      <c r="A12" s="3" t="s">
+      <c r="D12" s="6">
+        <v>-12.66</v>
+      </c>
+      <c r="E12" s="7">
+        <v>-3.45</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6">
+      <c r="A13" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B12" s="3" t="s">
+      <c r="B13" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="C12" s="5">
-        <v>2.62</v>
-      </c>
-      <c r="D12" s="5">
+      <c r="C13" s="6">
         <v>4.08</v>
       </c>
-      <c r="E12" s="6">
-        <v>1.46</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
-      <c r="A13" s="3" t="s">
+      <c r="D13" s="6">
+        <v>-0.83</v>
+      </c>
+      <c r="E13" s="7">
+        <v>-4.91</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6">
+      <c r="A14" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B13" s="3" t="s">
+      <c r="B14" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="C13" s="5">
-        <v>-5.65</v>
-      </c>
-      <c r="D13" s="5">
+      <c r="C14" s="6">
         <v>-8.32</v>
       </c>
-      <c r="E13" s="7">
-        <v>-2.67</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
-      <c r="A14" s="3" t="s">
+      <c r="D14" s="6">
+        <v>-16.64</v>
+      </c>
+      <c r="E14" s="7">
+        <v>-8.32</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6">
+      <c r="A15" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B14" s="3" t="s">
+      <c r="B15" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="C14" s="5">
-        <v>-0.51</v>
-      </c>
-      <c r="D14" s="5">
+      <c r="C15" s="6">
         <v>-1.96</v>
       </c>
-      <c r="E14" s="7">
-        <v>-1.45</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6">
-      <c r="A15" s="3" t="s">
+      <c r="D15" s="6">
+        <v>-3.05</v>
+      </c>
+      <c r="E15" s="7">
+        <v>-1.09</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6">
+      <c r="A16" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="B15" s="3" t="s">
+      <c r="B16" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="C15" s="5">
-        <v>-0.16</v>
-      </c>
-      <c r="D15" s="5">
+      <c r="C16" s="6">
         <v>1.35</v>
       </c>
-      <c r="E15" s="6">
-        <v>1.51</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
-      <c r="A16" s="3" t="s">
+      <c r="D16" s="6">
+        <v>-4.04</v>
+      </c>
+      <c r="E16" s="7">
+        <v>-5.39</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B16" s="3" t="s">
+      <c r="B17" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="C16" s="5">
-        <v>0.36</v>
-      </c>
-      <c r="D16" s="5">
+      <c r="C17" s="6">
         <v>-4.5</v>
       </c>
-      <c r="E16" s="7">
-        <v>-4.86</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5">
-      <c r="A17" s="3" t="s">
+      <c r="D17" s="6">
+        <v>-4.61</v>
+      </c>
+      <c r="E17" s="7">
+        <v>-0.11</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B17" s="3" t="s">
+      <c r="B18" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="C17" s="5">
-        <v>20.35</v>
-      </c>
-      <c r="D17" s="5">
+      <c r="C18" s="6">
         <v>20.21</v>
       </c>
-      <c r="E17" s="7">
-        <v>-0.14</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5">
-      <c r="A18" s="3" t="s">
+      <c r="D18" s="6">
+        <v>14.33</v>
+      </c>
+      <c r="E18" s="7">
+        <v>-5.88</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B18" s="3" t="s">
+      <c r="B19" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="C18" s="5">
-        <v>11.61</v>
-      </c>
-      <c r="D18" s="5">
+      <c r="C19" s="6">
         <v>8.15</v>
       </c>
-      <c r="E18" s="7">
-        <v>-3.46</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5">
-      <c r="A19" s="3" t="s">
+      <c r="D19" s="6">
+        <v>4.09</v>
+      </c>
+      <c r="E19" s="7">
+        <v>-4.06</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B19" s="3" t="s">
+      <c r="B20" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="C19" s="5">
-        <v>-26.88</v>
-      </c>
-      <c r="D19" s="5">
+      <c r="C20" s="6">
         <v>-28.6</v>
       </c>
-      <c r="E19" s="7">
+      <c r="D20" s="6">
+        <v>-29.46</v>
+      </c>
+      <c r="E20" s="7">
+        <v>-0.86</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B21" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C21" s="6">
+        <v>30.44</v>
+      </c>
+      <c r="D21" s="6">
+        <v>23.52</v>
+      </c>
+      <c r="E21" s="7">
+        <v>-6.92</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B22" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C22" s="6">
+        <v>-23.76</v>
+      </c>
+      <c r="D22" s="6">
+        <v>-25.48</v>
+      </c>
+      <c r="E22" s="7">
         <v>-1.72</v>
       </c>
     </row>
-    <row r="20" spans="1:5">
-      <c r="A20" s="3" t="s">
+    <row r="23" spans="1:5">
+      <c r="A23" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B23" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C23" s="6">
+        <v>5.15</v>
+      </c>
+      <c r="D23" s="6">
+        <v>-2.1</v>
+      </c>
+      <c r="E23" s="7">
+        <v>-7.25</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5">
+      <c r="A24" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B24" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C24" s="6">
+        <v>-7.37</v>
+      </c>
+      <c r="D24" s="6">
+        <v>-6.98</v>
+      </c>
+      <c r="E24" s="8">
+        <v>0.39</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5">
+      <c r="A25" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B25" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C25" s="6">
+        <v>-10.96</v>
+      </c>
+      <c r="D25" s="6">
+        <v>-10.87</v>
+      </c>
+      <c r="E25" s="8">
+        <v>0.09</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
+      <c r="A26" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="B20" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C20" s="5">
-        <v>29.22</v>
-      </c>
-      <c r="D20" s="5">
-        <v>30.44</v>
-      </c>
-      <c r="E20" s="6">
-        <v>1.22</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5">
-      <c r="A21" s="3" t="s">
+      <c r="B26" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C26" s="6">
+        <v>3.42</v>
+      </c>
+      <c r="D26" s="6">
+        <v>0.06</v>
+      </c>
+      <c r="E26" s="7">
+        <v>-3.36</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5">
+      <c r="A27" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B21" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C21" s="5">
-        <v>-22.69</v>
-      </c>
-      <c r="D21" s="5">
-        <v>-23.76</v>
-      </c>
-      <c r="E21" s="7">
-        <v>-1.07</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5">
-      <c r="A22" s="3" t="s">
+      <c r="B27" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C27" s="6">
+        <v>6.56</v>
+      </c>
+      <c r="D27" s="6">
+        <v>9.35</v>
+      </c>
+      <c r="E27" s="8">
+        <v>2.79</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5">
+      <c r="A28" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B22" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C22" s="5">
-        <v>6.13</v>
-      </c>
-      <c r="D22" s="5">
-        <v>5.15</v>
-      </c>
-      <c r="E22" s="7">
-        <v>-0.98</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5">
-      <c r="A23" s="3" t="s">
+      <c r="B28" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C28" s="6">
+        <v>-21.83</v>
+      </c>
+      <c r="D28" s="6">
+        <v>-24.51</v>
+      </c>
+      <c r="E28" s="7">
+        <v>-2.68</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5">
+      <c r="A29" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B23" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C23" s="5">
-        <v>-3.51</v>
-      </c>
-      <c r="D23" s="5">
-        <v>-7.37</v>
-      </c>
-      <c r="E23" s="7">
-        <v>-3.86</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5">
-      <c r="A24" s="3" t="s">
+      <c r="B29" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C29" s="6">
+        <v>-13.9</v>
+      </c>
+      <c r="D29" s="6">
+        <v>-16.64</v>
+      </c>
+      <c r="E29" s="7">
+        <v>-2.74</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5">
+      <c r="A30" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B24" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C24" s="5">
-        <v>-10.64</v>
-      </c>
-      <c r="D24" s="5">
-        <v>-10.96</v>
-      </c>
-      <c r="E24" s="7">
-        <v>-0.32</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5">
-      <c r="A25" s="3" t="s">
+      <c r="B30" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C30" s="6">
+        <v>-29.12</v>
+      </c>
+      <c r="D30" s="6">
+        <v>-29.86</v>
+      </c>
+      <c r="E30" s="7">
+        <v>-0.74</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5">
+      <c r="A31" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="B25" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C25" s="5">
-        <v>5.47</v>
-      </c>
-      <c r="D25" s="5">
-        <v>3.42</v>
-      </c>
-      <c r="E25" s="7">
-        <v>-2.05</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5">
-      <c r="A26" s="3" t="s">
+      <c r="B31" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C31" s="6">
+        <v>-10.29</v>
+      </c>
+      <c r="D31" s="6">
+        <v>-14.01</v>
+      </c>
+      <c r="E31" s="7">
+        <v>-3.72</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5">
+      <c r="A32" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B26" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C26" s="5">
-        <v>9.52</v>
-      </c>
-      <c r="D26" s="5">
-        <v>6.56</v>
-      </c>
-      <c r="E26" s="7">
-        <v>-2.96</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5">
-      <c r="A27" s="3" t="s">
+      <c r="B32" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C32" s="6">
+        <v>-23.55</v>
+      </c>
+      <c r="D32" s="6">
+        <v>-24.23</v>
+      </c>
+      <c r="E32" s="7">
+        <v>-0.68</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5">
+      <c r="A33" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B27" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C27" s="5">
-        <v>-22.85</v>
-      </c>
-      <c r="D27" s="5">
-        <v>-21.83</v>
-      </c>
-      <c r="E27" s="6">
-        <v>1.02</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5">
-      <c r="A28" s="3" t="s">
+      <c r="B33" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C33" s="6">
+        <v>162.89</v>
+      </c>
+      <c r="D33" s="6">
+        <v>157.3</v>
+      </c>
+      <c r="E33" s="7">
+        <v>-5.59</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5">
+      <c r="A34" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B28" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C28" s="5">
-        <v>-9.890000000000001</v>
-      </c>
-      <c r="D28" s="5">
-        <v>-13.9</v>
-      </c>
-      <c r="E28" s="7">
-        <v>-4.01</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5">
-      <c r="A29" s="3" t="s">
+      <c r="B34" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C34" s="6">
+        <v>392.75</v>
+      </c>
+      <c r="D34" s="6">
+        <v>380.25</v>
+      </c>
+      <c r="E34" s="7">
+        <v>-12.5</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5">
+      <c r="A35" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B29" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C29" s="5">
-        <v>-28.9</v>
-      </c>
-      <c r="D29" s="5">
-        <v>-29.12</v>
-      </c>
-      <c r="E29" s="7">
-        <v>-0.22</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5">
-      <c r="A30" s="3" t="s">
+      <c r="B35" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C35" s="6">
+        <v>378.5</v>
+      </c>
+      <c r="D35" s="6">
+        <v>374.55</v>
+      </c>
+      <c r="E35" s="7">
+        <v>-3.95</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5">
+      <c r="A36" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="B30" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C30" s="5">
-        <v>-10.69</v>
-      </c>
-      <c r="D30" s="5">
-        <v>-10.29</v>
-      </c>
-      <c r="E30" s="6">
-        <v>0.4</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5">
-      <c r="A31" s="3" t="s">
+      <c r="B36" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C36" s="6">
+        <v>959.3</v>
+      </c>
+      <c r="D36" s="6">
+        <v>919.5</v>
+      </c>
+      <c r="E36" s="7">
+        <v>-39.8</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5">
+      <c r="A37" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B31" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C31" s="5">
-        <v>-23.76</v>
-      </c>
-      <c r="D31" s="5">
-        <v>-23.55</v>
-      </c>
-      <c r="E31" s="6">
-        <v>0.21</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5">
-      <c r="A32" s="3" t="s">
+      <c r="B37" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C37" s="6">
+        <v>2.76</v>
+      </c>
+      <c r="D37" s="6">
+        <v>2.69</v>
+      </c>
+      <c r="E37" s="7">
+        <v>-0.07000000000000001</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5">
+      <c r="A38" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B32" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C32" s="5">
-        <v>160.75</v>
-      </c>
-      <c r="D32" s="5">
-        <v>162.89</v>
-      </c>
-      <c r="E32" s="6">
-        <v>2.14</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5">
-      <c r="A33" s="3" t="s">
+      <c r="B38" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C38" s="6">
+        <v>44.61</v>
+      </c>
+      <c r="D38" s="6">
+        <v>37.13</v>
+      </c>
+      <c r="E38" s="7">
+        <v>-7.48</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5">
+      <c r="A39" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B33" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C33" s="5">
-        <v>411.05</v>
-      </c>
-      <c r="D33" s="5">
-        <v>392.75</v>
-      </c>
-      <c r="E33" s="7">
-        <v>-18.3</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5">
-      <c r="A34" s="3" t="s">
+      <c r="B39" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C39" s="6">
+        <v>40.43</v>
+      </c>
+      <c r="D39" s="6">
+        <v>37.21</v>
+      </c>
+      <c r="E39" s="7">
+        <v>-3.22</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5">
+      <c r="A40" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B34" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C34" s="5">
-        <v>379.65</v>
-      </c>
-      <c r="D34" s="5">
-        <v>378.5</v>
-      </c>
-      <c r="E34" s="7">
-        <v>-1.15</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5">
-      <c r="A35" s="3" t="s">
+      <c r="B40" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C40" s="6">
+        <v>31.19</v>
+      </c>
+      <c r="D40" s="6">
+        <v>28.2</v>
+      </c>
+      <c r="E40" s="7">
+        <v>-2.99</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5">
+      <c r="A41" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="B35" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C35" s="5">
-        <v>955</v>
-      </c>
-      <c r="D35" s="5">
-        <v>959.3</v>
-      </c>
-      <c r="E35" s="6">
-        <v>4.3</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5">
-      <c r="A36" s="3" t="s">
+      <c r="B41" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C41" s="6">
+        <v>40.38</v>
+      </c>
+      <c r="D41" s="6">
+        <v>30.78</v>
+      </c>
+      <c r="E41" s="7">
+        <v>-9.6</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5">
+      <c r="A42" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B42" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C42" s="6">
+        <v>50.27</v>
+      </c>
+      <c r="D42" s="6">
+        <v>45.8</v>
+      </c>
+      <c r="E42" s="7">
+        <v>-4.47</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5">
+      <c r="A43" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B36" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C36" s="5">
-        <v>40.33</v>
-      </c>
-      <c r="D36" s="5">
-        <v>44.61</v>
-      </c>
-      <c r="E36" s="6">
-        <v>4.28</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5">
-      <c r="A37" s="3" t="s">
+      <c r="B43" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C43" s="6">
+        <v>-68.15000000000001</v>
+      </c>
+      <c r="D43" s="6">
+        <v>-33.99</v>
+      </c>
+      <c r="E43" s="8">
+        <v>34.16</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5">
+      <c r="A44" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B37" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C37" s="5">
-        <v>45.82</v>
-      </c>
-      <c r="D37" s="5">
-        <v>40.43</v>
-      </c>
-      <c r="E37" s="7">
-        <v>-5.39</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5">
-      <c r="A38" s="3" t="s">
+      <c r="B44" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C44" s="6">
+        <v>-43.86</v>
+      </c>
+      <c r="D44" s="6">
+        <v>-61.45</v>
+      </c>
+      <c r="E44" s="7">
+        <v>-17.59</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5">
+      <c r="A45" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B38" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C38" s="5">
-        <v>32.12</v>
-      </c>
-      <c r="D38" s="5">
-        <v>31.19</v>
-      </c>
-      <c r="E38" s="7">
-        <v>-0.93</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5">
-      <c r="A39" s="3" t="s">
+      <c r="B45" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C45" s="6">
+        <v>40.29</v>
+      </c>
+      <c r="D45" s="6">
+        <v>-49.74</v>
+      </c>
+      <c r="E45" s="7">
+        <v>-90.03</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5">
+      <c r="A46" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="B39" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C39" s="5">
-        <v>38.45</v>
-      </c>
-      <c r="D39" s="5">
-        <v>40.38</v>
-      </c>
-      <c r="E39" s="6">
-        <v>1.93</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5">
-      <c r="A40" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B40" s="3" t="s">
+      <c r="B46" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="C40" s="5">
-        <v>-27.88</v>
-      </c>
-      <c r="D40" s="5">
-        <v>-68.15000000000001</v>
-      </c>
-      <c r="E40" s="7">
-        <v>-40.27</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5">
-      <c r="A41" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="B41" s="3" t="s">
+      <c r="C46" s="6">
+        <v>49.77</v>
+      </c>
+      <c r="D46" s="6">
+        <v>219.68</v>
+      </c>
+      <c r="E46" s="8">
+        <v>169.91</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5">
+      <c r="A47" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B47" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="C41" s="5">
-        <v>-22.63</v>
-      </c>
-      <c r="D41" s="5">
-        <v>-43.86</v>
-      </c>
-      <c r="E41" s="7">
-        <v>-21.23</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5">
-      <c r="A42" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="B42" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C42" s="5">
-        <v>-26.49</v>
-      </c>
-      <c r="D42" s="5">
-        <v>40.29</v>
-      </c>
-      <c r="E42" s="6">
-        <v>66.78</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5">
-      <c r="A43" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="B43" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C43" s="5">
-        <v>-44.68</v>
-      </c>
-      <c r="D43" s="5">
-        <v>49.77</v>
-      </c>
-      <c r="E43" s="6">
-        <v>94.45</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5">
-      <c r="A44" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="B44" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C44" s="5">
-        <v>-73.84999999999999</v>
-      </c>
-      <c r="D44" s="5">
+      <c r="C47" s="6">
         <v>-70.37</v>
       </c>
-      <c r="E44" s="6">
-        <v>3.48</v>
+      <c r="D47" s="6">
+        <v>-20.38</v>
+      </c>
+      <c r="E47" s="8">
+        <v>49.99</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A5:E5"/>
+    <mergeCell ref="A6:E6"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2304,60 +2427,60 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="28" customHeight="1">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="8" t="s">
-        <v>54</v>
-      </c>
-      <c r="C1" s="8" t="s">
-        <v>55</v>
-      </c>
-      <c r="D1" s="8" t="s">
-        <v>56</v>
-      </c>
-      <c r="E1" s="8" t="s">
-        <v>57</v>
-      </c>
-      <c r="F1" s="8" t="s">
-        <v>58</v>
-      </c>
-      <c r="G1" s="8" t="s">
-        <v>59</v>
-      </c>
-      <c r="H1" s="8" t="s">
-        <v>60</v>
-      </c>
-      <c r="I1" s="8" t="s">
-        <v>61</v>
+      <c r="B1" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="C1" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="D1" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="E1" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="F1" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="G1" s="9" t="s">
+        <v>70</v>
+      </c>
+      <c r="H1" s="9" t="s">
+        <v>71</v>
+      </c>
+      <c r="I1" s="9" t="s">
+        <v>72</v>
       </c>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="9" t="s">
+      <c r="A2" s="10" t="s">
         <v>42</v>
       </c>
-      <c r="B2" s="10">
-        <v>57.92</v>
-      </c>
-      <c r="C2" s="11">
+      <c r="B2" s="11">
+        <v>49.92</v>
+      </c>
+      <c r="C2" s="12">
         <v>5</v>
       </c>
-      <c r="D2" s="10">
-        <v>41.4</v>
-      </c>
-      <c r="E2" s="10">
-        <v>60</v>
-      </c>
-      <c r="F2" s="10">
-        <v>-5.7</v>
-      </c>
-      <c r="G2" s="10">
-        <v>-0.6</v>
-      </c>
-      <c r="H2" s="10">
+      <c r="D2" s="11">
+        <v>35.8</v>
+      </c>
+      <c r="E2" s="11">
+        <v>40</v>
+      </c>
+      <c r="F2" s="11">
+        <v>-8.5</v>
+      </c>
+      <c r="G2" s="11">
+        <v>-2.1</v>
+      </c>
+      <c r="H2" s="11">
         <v>59.8</v>
       </c>
-      <c r="I2" s="10">
+      <c r="I2" s="11">
         <v>20</v>
       </c>
     </row>
@@ -2459,37 +2582,37 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
-      <c r="A1" s="12" t="s">
+      <c r="A1" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="B1" s="12" t="s">
+      <c r="B1" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="C1" s="12" t="s">
+      <c r="C1" s="13" t="s">
         <v>41</v>
       </c>
-      <c r="D1" s="12" t="s">
+      <c r="D1" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="E1" s="12" t="s">
+      <c r="E1" s="13" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="2" spans="1:5">
-      <c r="A2" s="13">
-        <v>0.2286</v>
-      </c>
-      <c r="B2" s="13">
-        <v>0.0837</v>
-      </c>
-      <c r="C2" s="13">
-        <v>0.038</v>
-      </c>
-      <c r="D2" s="13">
-        <v>-0.033</v>
-      </c>
-      <c r="E2" s="13">
-        <v>-0.2184</v>
+      <c r="A2" s="14">
+        <v>0.2228</v>
+      </c>
+      <c r="B2" s="14">
+        <v>0.0759</v>
+      </c>
+      <c r="C2" s="14">
+        <v>0.0327</v>
+      </c>
+      <c r="D2" s="14">
+        <v>-0.04019999999999999</v>
+      </c>
+      <c r="E2" s="14">
+        <v>-0.2189</v>
       </c>
     </row>
   </sheetData>

--- a/HINDUJA_GROUP_Technical_Metrics.xlsx
+++ b/HINDUJA_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="224" uniqueCount="73">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="218" uniqueCount="70">
   <si>
     <t>Symbol</t>
   </si>
@@ -160,9 +160,6 @@
     <t>DOWN</t>
   </si>
   <si>
-    <t>UP</t>
-  </si>
-  <si>
     <t>▶  SIGNAL EVENTS (vs Previous Run)</t>
   </si>
   <si>
@@ -181,25 +178,19 @@
     <t>Curr Value</t>
   </si>
   <si>
-    <t>20 DMA &gt; 50 DMA</t>
-  </si>
-  <si>
-    <t>Yes → No</t>
-  </si>
-  <si>
-    <t>🔴 BEARISH</t>
-  </si>
-  <si>
-    <t>RSI Momentum</t>
-  </si>
-  <si>
-    <t>50.3 → 45.8</t>
-  </si>
-  <si>
-    <t>50.3</t>
-  </si>
-  <si>
-    <t>45.8</t>
+    <t>RSI Oversold Recovery</t>
+  </si>
+  <si>
+    <t>28.2 → 31.9</t>
+  </si>
+  <si>
+    <t>🟢 BULLISH</t>
+  </si>
+  <si>
+    <t>28.2</t>
+  </si>
+  <si>
+    <t>31.9</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -285,14 +276,14 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FF006100"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FF9C0006"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -325,13 +316,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -411,8 +402,8 @@
     <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -925,10 +916,10 @@
         <v>42</v>
       </c>
       <c r="C2">
-        <v>157.3</v>
+        <v>159.08</v>
       </c>
       <c r="D2">
-        <v>-3.43</v>
+        <v>1.13</v>
       </c>
       <c r="E2">
         <v>208.37</v>
@@ -937,46 +928,46 @@
         <v>131.36</v>
       </c>
       <c r="G2">
-        <v>-24.51</v>
+        <v>-23.66</v>
       </c>
       <c r="H2">
-        <v>19.75</v>
+        <v>21.1</v>
       </c>
       <c r="I2">
-        <v>-0.83</v>
+        <v>-2.4</v>
       </c>
       <c r="J2">
-        <v>-9.949999999999999</v>
+        <v>-11.15</v>
       </c>
       <c r="K2">
-        <v>-2.1</v>
+        <v>1.09</v>
       </c>
       <c r="L2">
-        <v>14.33</v>
+        <v>16.83</v>
       </c>
       <c r="M2">
-        <v>22.28</v>
+        <v>22.01</v>
       </c>
       <c r="N2">
         <v>79</v>
       </c>
       <c r="O2">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="P2">
-        <v>161.14</v>
+        <v>160.35</v>
       </c>
       <c r="Q2">
-        <v>165.95</v>
+        <v>165.03</v>
       </c>
       <c r="R2">
-        <v>166.78</v>
+        <v>166.87</v>
       </c>
       <c r="S2">
-        <v>169.95</v>
+        <v>169.96</v>
       </c>
       <c r="T2">
-        <v>-7.44</v>
+        <v>-6.4</v>
       </c>
       <c r="U2" t="s">
         <v>43</v>
@@ -991,34 +982,34 @@
         <v>0</v>
       </c>
       <c r="Y2">
-        <v>37.13</v>
+        <v>40.55</v>
       </c>
       <c r="Z2">
-        <v>-2.81</v>
+        <v>-2.87</v>
       </c>
       <c r="AA2">
-        <v>-2.02</v>
+        <v>-2.19</v>
       </c>
       <c r="AB2">
-        <v>-0.79</v>
+        <v>-0.68</v>
       </c>
       <c r="AC2">
-        <v>58.83</v>
+        <v>59.2</v>
       </c>
       <c r="AD2">
-        <v>60.82</v>
+        <v>61.63</v>
       </c>
       <c r="AE2">
-        <v>4.25</v>
+        <v>4.19</v>
       </c>
       <c r="AF2">
-        <v>-33.99</v>
+        <v>-16.5</v>
       </c>
       <c r="AG2">
-        <v>178.64</v>
+        <v>176.86</v>
       </c>
       <c r="AH2">
-        <v>153.25</v>
+        <v>153.2</v>
       </c>
       <c r="AI2">
         <v>169.79</v>
@@ -1027,7 +1018,7 @@
         <v>45</v>
       </c>
       <c r="AK2">
-        <v>31.76</v>
+        <v>33.99</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1038,10 +1029,10 @@
         <v>42</v>
       </c>
       <c r="C3">
-        <v>380.25</v>
+        <v>384.1</v>
       </c>
       <c r="D3">
-        <v>-3.18</v>
+        <v>1.01</v>
       </c>
       <c r="E3">
         <v>456.15</v>
@@ -1050,46 +1041,46 @@
         <v>225</v>
       </c>
       <c r="G3">
-        <v>-16.64</v>
+        <v>-15.8</v>
       </c>
       <c r="H3">
-        <v>69</v>
+        <v>70.70999999999999</v>
       </c>
       <c r="I3">
-        <v>-16.64</v>
+        <v>-13.9</v>
       </c>
       <c r="J3">
-        <v>-3.9</v>
+        <v>-3.35</v>
       </c>
       <c r="K3">
-        <v>-6.98</v>
+        <v>-4.77</v>
       </c>
       <c r="L3">
-        <v>4.09</v>
+        <v>4.05</v>
       </c>
       <c r="M3">
-        <v>7.59</v>
+        <v>8.359999999999999</v>
       </c>
       <c r="N3">
         <v>60</v>
       </c>
       <c r="O3">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="P3">
-        <v>416.72</v>
+        <v>404.32</v>
       </c>
       <c r="Q3">
-        <v>419.47</v>
+        <v>418.81</v>
       </c>
       <c r="R3">
-        <v>410.79</v>
+        <v>410.41</v>
       </c>
       <c r="S3">
-        <v>336.2</v>
+        <v>336.69</v>
       </c>
       <c r="T3">
-        <v>13.1</v>
+        <v>14.08</v>
       </c>
       <c r="U3" t="s">
         <v>44</v>
@@ -1104,34 +1095,34 @@
         <v>3</v>
       </c>
       <c r="Y3">
-        <v>37.21</v>
+        <v>38.82</v>
       </c>
       <c r="Z3">
-        <v>1.01</v>
+        <v>-1.83</v>
       </c>
       <c r="AA3">
-        <v>6.29</v>
+        <v>4.66</v>
       </c>
       <c r="AB3">
-        <v>-5.27</v>
+        <v>-6.49</v>
       </c>
       <c r="AC3">
-        <v>2.79</v>
+        <v>1.76</v>
       </c>
       <c r="AD3">
-        <v>30.86</v>
+        <v>12.14</v>
       </c>
       <c r="AE3">
-        <v>18.96</v>
+        <v>19</v>
       </c>
       <c r="AF3">
-        <v>-61.45</v>
+        <v>-79.73999999999999</v>
       </c>
       <c r="AG3">
-        <v>468.26</v>
+        <v>469.2</v>
       </c>
       <c r="AH3">
-        <v>370.67</v>
+        <v>368.41</v>
       </c>
       <c r="AI3">
         <v>444.49</v>
@@ -1140,7 +1131,7 @@
         <v>45</v>
       </c>
       <c r="AK3">
-        <v>41.43</v>
+        <v>41.94</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1151,10 +1142,10 @@
         <v>42</v>
       </c>
       <c r="C4">
-        <v>374.55</v>
+        <v>376.6</v>
       </c>
       <c r="D4">
-        <v>-1.04</v>
+        <v>0.55</v>
       </c>
       <c r="E4">
         <v>534</v>
@@ -1163,46 +1154,46 @@
         <v>344.7</v>
       </c>
       <c r="G4">
-        <v>-29.86</v>
+        <v>-29.48</v>
       </c>
       <c r="H4">
-        <v>8.66</v>
+        <v>9.25</v>
       </c>
       <c r="I4">
-        <v>-3.05</v>
+        <v>-0.74</v>
       </c>
       <c r="J4">
-        <v>-6.67</v>
+        <v>-6.31</v>
       </c>
       <c r="K4">
-        <v>-10.87</v>
+        <v>-9.42</v>
       </c>
       <c r="L4">
-        <v>-29.46</v>
+        <v>-27.98</v>
       </c>
       <c r="M4">
-        <v>-21.89</v>
+        <v>-21.75</v>
       </c>
       <c r="N4">
         <v>21</v>
       </c>
       <c r="O4">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="P4">
-        <v>377.98</v>
+        <v>377.42</v>
       </c>
       <c r="Q4">
-        <v>388.11</v>
+        <v>386.81</v>
       </c>
       <c r="R4">
-        <v>405.92</v>
+        <v>404.71</v>
       </c>
       <c r="S4">
-        <v>409.19</v>
+        <v>408.81</v>
       </c>
       <c r="T4">
-        <v>-8.470000000000001</v>
+        <v>-7.88</v>
       </c>
       <c r="U4" t="s">
         <v>43</v>
@@ -1217,43 +1208,43 @@
         <v>0</v>
       </c>
       <c r="Y4">
-        <v>28.2</v>
+        <v>31.86</v>
       </c>
       <c r="Z4">
-        <v>-8.039999999999999</v>
+        <v>-7.93</v>
       </c>
       <c r="AA4">
-        <v>-7.7</v>
+        <v>-7.75</v>
       </c>
       <c r="AB4">
-        <v>-0.34</v>
+        <v>-0.19</v>
       </c>
       <c r="AC4">
-        <v>22.24</v>
+        <v>25.25</v>
       </c>
       <c r="AD4">
-        <v>22.62</v>
+        <v>23.89</v>
       </c>
       <c r="AE4">
-        <v>10.38</v>
+        <v>10.42</v>
       </c>
       <c r="AF4">
-        <v>-49.74</v>
+        <v>-26.47</v>
       </c>
       <c r="AG4">
-        <v>405.79</v>
+        <v>403.82</v>
       </c>
       <c r="AH4">
-        <v>370.43</v>
+        <v>369.8</v>
       </c>
       <c r="AI4">
-        <v>408.12</v>
+        <v>405.81</v>
       </c>
       <c r="AJ4" t="s">
         <v>45</v>
       </c>
       <c r="AK4">
-        <v>28.43</v>
+        <v>31.45</v>
       </c>
     </row>
     <row r="5" spans="1:37">
@@ -1264,10 +1255,10 @@
         <v>42</v>
       </c>
       <c r="C5">
-        <v>919.5</v>
+        <v>912.2</v>
       </c>
       <c r="D5">
-        <v>-4.15</v>
+        <v>-0.79</v>
       </c>
       <c r="E5">
         <v>1069.3</v>
@@ -1276,46 +1267,46 @@
         <v>712.75</v>
       </c>
       <c r="G5">
-        <v>-14.01</v>
+        <v>-14.69</v>
       </c>
       <c r="H5">
-        <v>29.01</v>
+        <v>27.98</v>
       </c>
       <c r="I5">
-        <v>-4.04</v>
+        <v>-5.6</v>
       </c>
       <c r="J5">
-        <v>-9.41</v>
+        <v>-9.140000000000001</v>
       </c>
       <c r="K5">
-        <v>0.06</v>
+        <v>-0.35</v>
       </c>
       <c r="L5">
-        <v>23.52</v>
+        <v>24.23</v>
       </c>
       <c r="M5">
-        <v>-4.02</v>
+        <v>-3.97</v>
       </c>
       <c r="N5">
         <v>99</v>
       </c>
       <c r="O5">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="P5">
-        <v>951.22</v>
+        <v>940.4</v>
       </c>
       <c r="Q5">
-        <v>979.29</v>
+        <v>974.76</v>
       </c>
       <c r="R5">
-        <v>1002.87</v>
+        <v>1000.84</v>
       </c>
       <c r="S5">
-        <v>922.58</v>
+        <v>922.9299999999999</v>
       </c>
       <c r="T5">
-        <v>-0.33</v>
+        <v>-1.16</v>
       </c>
       <c r="U5" t="s">
         <v>43</v>
@@ -1330,43 +1321,43 @@
         <v>1</v>
       </c>
       <c r="Y5">
-        <v>30.78</v>
+        <v>29.4</v>
       </c>
       <c r="Z5">
-        <v>-16.52</v>
+        <v>-19.28</v>
       </c>
       <c r="AA5">
-        <v>-11.46</v>
+        <v>-13.03</v>
       </c>
       <c r="AB5">
-        <v>-5.06</v>
+        <v>-6.25</v>
       </c>
       <c r="AC5">
-        <v>23.18</v>
+        <v>13.41</v>
       </c>
       <c r="AD5">
-        <v>30.16</v>
+        <v>23.35</v>
       </c>
       <c r="AE5">
-        <v>21.38</v>
+        <v>21.07</v>
       </c>
       <c r="AF5">
-        <v>219.68</v>
+        <v>-30.28</v>
       </c>
       <c r="AG5">
-        <v>1030.92</v>
+        <v>1033.15</v>
       </c>
       <c r="AH5">
-        <v>927.67</v>
+        <v>916.37</v>
       </c>
       <c r="AI5">
-        <v>983.25</v>
+        <v>978.61</v>
       </c>
       <c r="AJ5" t="s">
         <v>45</v>
       </c>
       <c r="AK5">
-        <v>29.02</v>
+        <v>32.96</v>
       </c>
     </row>
     <row r="6" spans="1:37">
@@ -1377,37 +1368,37 @@
         <v>42</v>
       </c>
       <c r="C6">
-        <v>2.69</v>
+        <v>2.61</v>
       </c>
       <c r="D6">
-        <v>-2.54</v>
+        <v>-2.97</v>
       </c>
       <c r="E6">
-        <v>3.55</v>
+        <v>3.49</v>
       </c>
       <c r="F6">
         <v>1.84</v>
       </c>
       <c r="G6">
-        <v>-24.23</v>
+        <v>-25.21</v>
       </c>
       <c r="H6">
-        <v>46.2</v>
+        <v>41.85</v>
       </c>
       <c r="I6">
-        <v>-4.61</v>
+        <v>-6.12</v>
       </c>
       <c r="J6">
-        <v>-12.66</v>
+        <v>-13.29</v>
       </c>
       <c r="K6">
-        <v>9.35</v>
+        <v>11.06</v>
       </c>
       <c r="L6">
-        <v>-25.48</v>
+        <v>-26.48</v>
       </c>
       <c r="M6">
-        <v>3.27</v>
+        <v>3.29</v>
       </c>
       <c r="N6">
         <v>40</v>
@@ -1416,19 +1407,19 @@
         <v>43</v>
       </c>
       <c r="P6">
-        <v>2.76</v>
+        <v>2.72</v>
       </c>
       <c r="Q6">
-        <v>2.85</v>
+        <v>2.83</v>
       </c>
       <c r="R6">
         <v>2.59</v>
       </c>
       <c r="S6">
-        <v>2.67</v>
+        <v>2.66</v>
       </c>
       <c r="T6">
-        <v>0.89</v>
+        <v>-2.04</v>
       </c>
       <c r="U6" t="s">
         <v>44</v>
@@ -1440,16 +1431,16 @@
         <v>43</v>
       </c>
       <c r="X6">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y6">
-        <v>45.8</v>
+        <v>41.28</v>
       </c>
       <c r="Z6">
-        <v>0.03</v>
+        <v>0.02</v>
       </c>
       <c r="AA6">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="AB6">
         <v>-0.04</v>
@@ -1458,28 +1449,28 @@
         <v>0</v>
       </c>
       <c r="AD6">
-        <v>1.97</v>
+        <v>0.78</v>
       </c>
       <c r="AE6">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="AF6">
-        <v>-20.38</v>
+        <v>9.380000000000001</v>
       </c>
       <c r="AG6">
         <v>3.02</v>
       </c>
       <c r="AH6">
-        <v>2.68</v>
+        <v>2.64</v>
       </c>
       <c r="AI6">
-        <v>2.65</v>
+        <v>3.06</v>
       </c>
       <c r="AJ6" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="AK6">
-        <v>24.91</v>
+        <v>25.32</v>
       </c>
     </row>
   </sheetData>
@@ -1620,7 +1611,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F47"/>
+  <dimension ref="A1:F46"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.7109375" customWidth="1"/>
@@ -1630,7 +1621,7 @@
   <sheetData>
     <row r="1" spans="1:6">
       <c r="A1" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -1643,771 +1634,751 @@
         <v>0</v>
       </c>
       <c r="B2" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="C2" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="D2" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="D2" s="3" t="s">
+      <c r="E2" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="E2" s="3" t="s">
+      <c r="F2" s="3" t="s">
         <v>51</v>
-      </c>
-      <c r="F2" s="3" t="s">
-        <v>52</v>
       </c>
     </row>
     <row r="3" spans="1:6">
       <c r="A3" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6">
+      <c r="A5" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="B5" s="2"/>
+      <c r="C5" s="2"/>
+      <c r="D5" s="2"/>
+      <c r="E5" s="2"/>
+    </row>
+    <row r="6" spans="1:6">
+      <c r="A6" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6">
+      <c r="A7" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B3" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="C3" s="4" t="s">
-        <v>54</v>
-      </c>
-      <c r="D3" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="E3" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="F3" s="4" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6">
-      <c r="A4" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="B4" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="C4" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="D4" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="E4" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="F4" s="4" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6">
-      <c r="A6" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="B6" s="2"/>
-      <c r="C6" s="2"/>
-      <c r="D6" s="2"/>
-      <c r="E6" s="2"/>
-    </row>
-    <row r="7" spans="1:6">
-      <c r="A7" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="D7" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="E7" s="3" t="s">
-        <v>64</v>
+      <c r="B7" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C7" s="6">
+        <v>-9.949999999999999</v>
+      </c>
+      <c r="D7" s="6">
+        <v>-11.15</v>
+      </c>
+      <c r="E7" s="7">
+        <v>-1.2</v>
       </c>
     </row>
     <row r="8" spans="1:6">
       <c r="A8" s="5" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B8" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C8" s="6">
-        <v>-6</v>
+        <v>-3.9</v>
       </c>
       <c r="D8" s="6">
-        <v>-9.949999999999999</v>
-      </c>
-      <c r="E8" s="7">
-        <v>-3.95</v>
+        <v>-3.35</v>
+      </c>
+      <c r="E8" s="8">
+        <v>0.55</v>
       </c>
     </row>
     <row r="9" spans="1:6">
       <c r="A9" s="5" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B9" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C9" s="6">
-        <v>-1.42</v>
+        <v>-6.67</v>
       </c>
       <c r="D9" s="6">
-        <v>-3.9</v>
-      </c>
-      <c r="E9" s="7">
-        <v>-2.48</v>
+        <v>-6.31</v>
+      </c>
+      <c r="E9" s="8">
+        <v>0.36</v>
       </c>
     </row>
     <row r="10" spans="1:6">
       <c r="A10" s="5" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B10" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C10" s="6">
-        <v>-5.86</v>
+        <v>-9.41</v>
       </c>
       <c r="D10" s="6">
-        <v>-6.67</v>
-      </c>
-      <c r="E10" s="7">
-        <v>-0.8100000000000001</v>
+        <v>-9.140000000000001</v>
+      </c>
+      <c r="E10" s="8">
+        <v>0.27</v>
       </c>
     </row>
     <row r="11" spans="1:6">
       <c r="A11" s="5" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B11" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C11" s="6">
-        <v>-5.8</v>
+        <v>-12.66</v>
       </c>
       <c r="D11" s="6">
-        <v>-9.41</v>
+        <v>-13.29</v>
       </c>
       <c r="E11" s="7">
-        <v>-3.61</v>
+        <v>-0.63</v>
       </c>
     </row>
     <row r="12" spans="1:6">
       <c r="A12" s="5" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C12" s="6">
-        <v>-9.210000000000001</v>
+        <v>-0.83</v>
       </c>
       <c r="D12" s="6">
-        <v>-12.66</v>
+        <v>-2.4</v>
       </c>
       <c r="E12" s="7">
-        <v>-3.45</v>
+        <v>-1.57</v>
       </c>
     </row>
     <row r="13" spans="1:6">
       <c r="A13" s="5" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B13" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C13" s="6">
-        <v>4.08</v>
+        <v>-16.64</v>
       </c>
       <c r="D13" s="6">
-        <v>-0.83</v>
-      </c>
-      <c r="E13" s="7">
-        <v>-4.91</v>
+        <v>-13.9</v>
+      </c>
+      <c r="E13" s="8">
+        <v>2.74</v>
       </c>
     </row>
     <row r="14" spans="1:6">
       <c r="A14" s="5" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B14" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C14" s="6">
-        <v>-8.32</v>
+        <v>-3.05</v>
       </c>
       <c r="D14" s="6">
-        <v>-16.64</v>
-      </c>
-      <c r="E14" s="7">
-        <v>-8.32</v>
+        <v>-0.74</v>
+      </c>
+      <c r="E14" s="8">
+        <v>2.31</v>
       </c>
     </row>
     <row r="15" spans="1:6">
       <c r="A15" s="5" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B15" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C15" s="6">
-        <v>-1.96</v>
+        <v>-4.04</v>
       </c>
       <c r="D15" s="6">
-        <v>-3.05</v>
+        <v>-5.6</v>
       </c>
       <c r="E15" s="7">
-        <v>-1.09</v>
+        <v>-1.56</v>
       </c>
     </row>
     <row r="16" spans="1:6">
       <c r="A16" s="5" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B16" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C16" s="6">
-        <v>1.35</v>
+        <v>-4.61</v>
       </c>
       <c r="D16" s="6">
-        <v>-4.04</v>
+        <v>-6.12</v>
       </c>
       <c r="E16" s="7">
-        <v>-5.39</v>
+        <v>-1.51</v>
       </c>
     </row>
     <row r="17" spans="1:5">
       <c r="A17" s="5" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="C17" s="6">
-        <v>-4.5</v>
+        <v>14.33</v>
       </c>
       <c r="D17" s="6">
-        <v>-4.61</v>
-      </c>
-      <c r="E17" s="7">
-        <v>-0.11</v>
+        <v>16.83</v>
+      </c>
+      <c r="E17" s="8">
+        <v>2.5</v>
       </c>
     </row>
     <row r="18" spans="1:5">
       <c r="A18" s="5" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B18" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C18" s="6">
-        <v>20.21</v>
+        <v>4.09</v>
       </c>
       <c r="D18" s="6">
-        <v>14.33</v>
+        <v>4.05</v>
       </c>
       <c r="E18" s="7">
-        <v>-5.88</v>
+        <v>-0.04</v>
       </c>
     </row>
     <row r="19" spans="1:5">
       <c r="A19" s="5" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B19" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C19" s="6">
-        <v>8.15</v>
+        <v>-29.46</v>
       </c>
       <c r="D19" s="6">
-        <v>4.09</v>
-      </c>
-      <c r="E19" s="7">
-        <v>-4.06</v>
+        <v>-27.98</v>
+      </c>
+      <c r="E19" s="8">
+        <v>1.48</v>
       </c>
     </row>
     <row r="20" spans="1:5">
       <c r="A20" s="5" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B20" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C20" s="6">
-        <v>-28.6</v>
+        <v>23.52</v>
       </c>
       <c r="D20" s="6">
-        <v>-29.46</v>
-      </c>
-      <c r="E20" s="7">
-        <v>-0.86</v>
+        <v>24.23</v>
+      </c>
+      <c r="E20" s="8">
+        <v>0.71</v>
       </c>
     </row>
     <row r="21" spans="1:5">
       <c r="A21" s="5" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B21" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C21" s="6">
-        <v>30.44</v>
+        <v>-25.48</v>
       </c>
       <c r="D21" s="6">
-        <v>23.52</v>
+        <v>-26.48</v>
       </c>
       <c r="E21" s="7">
-        <v>-6.92</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="22" spans="1:5">
       <c r="A22" s="5" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C22" s="6">
-        <v>-23.76</v>
+        <v>-2.1</v>
       </c>
       <c r="D22" s="6">
-        <v>-25.48</v>
-      </c>
-      <c r="E22" s="7">
-        <v>-1.72</v>
+        <v>1.09</v>
+      </c>
+      <c r="E22" s="8">
+        <v>3.19</v>
       </c>
     </row>
     <row r="23" spans="1:5">
       <c r="A23" s="5" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B23" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C23" s="6">
-        <v>5.15</v>
+        <v>-6.98</v>
       </c>
       <c r="D23" s="6">
-        <v>-2.1</v>
-      </c>
-      <c r="E23" s="7">
-        <v>-7.25</v>
+        <v>-4.77</v>
+      </c>
+      <c r="E23" s="8">
+        <v>2.21</v>
       </c>
     </row>
     <row r="24" spans="1:5">
       <c r="A24" s="5" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B24" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C24" s="6">
-        <v>-7.37</v>
+        <v>-10.87</v>
       </c>
       <c r="D24" s="6">
-        <v>-6.98</v>
+        <v>-9.42</v>
       </c>
       <c r="E24" s="8">
-        <v>0.39</v>
+        <v>1.45</v>
       </c>
     </row>
     <row r="25" spans="1:5">
       <c r="A25" s="5" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B25" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C25" s="6">
-        <v>-10.96</v>
+        <v>0.06</v>
       </c>
       <c r="D25" s="6">
-        <v>-10.87</v>
-      </c>
-      <c r="E25" s="8">
-        <v>0.09</v>
+        <v>-0.35</v>
+      </c>
+      <c r="E25" s="7">
+        <v>-0.41</v>
       </c>
     </row>
     <row r="26" spans="1:5">
       <c r="A26" s="5" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B26" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C26" s="6">
-        <v>3.42</v>
+        <v>9.35</v>
       </c>
       <c r="D26" s="6">
-        <v>0.06</v>
-      </c>
-      <c r="E26" s="7">
-        <v>-3.36</v>
+        <v>11.06</v>
+      </c>
+      <c r="E26" s="8">
+        <v>1.71</v>
       </c>
     </row>
     <row r="27" spans="1:5">
       <c r="A27" s="5" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="B27" s="5" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C27" s="6">
-        <v>6.56</v>
+        <v>-24.51</v>
       </c>
       <c r="D27" s="6">
-        <v>9.35</v>
+        <v>-23.66</v>
       </c>
       <c r="E27" s="8">
-        <v>2.79</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="28" spans="1:5">
       <c r="A28" s="5" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B28" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C28" s="6">
-        <v>-21.83</v>
+        <v>-16.64</v>
       </c>
       <c r="D28" s="6">
-        <v>-24.51</v>
-      </c>
-      <c r="E28" s="7">
-        <v>-2.68</v>
+        <v>-15.8</v>
+      </c>
+      <c r="E28" s="8">
+        <v>0.84</v>
       </c>
     </row>
     <row r="29" spans="1:5">
       <c r="A29" s="5" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B29" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C29" s="6">
-        <v>-13.9</v>
+        <v>-29.86</v>
       </c>
       <c r="D29" s="6">
-        <v>-16.64</v>
-      </c>
-      <c r="E29" s="7">
-        <v>-2.74</v>
+        <v>-29.48</v>
+      </c>
+      <c r="E29" s="8">
+        <v>0.38</v>
       </c>
     </row>
     <row r="30" spans="1:5">
       <c r="A30" s="5" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B30" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C30" s="6">
-        <v>-29.12</v>
+        <v>-14.01</v>
       </c>
       <c r="D30" s="6">
-        <v>-29.86</v>
+        <v>-14.69</v>
       </c>
       <c r="E30" s="7">
-        <v>-0.74</v>
+        <v>-0.68</v>
       </c>
     </row>
     <row r="31" spans="1:5">
       <c r="A31" s="5" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B31" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C31" s="6">
-        <v>-10.29</v>
+        <v>-24.23</v>
       </c>
       <c r="D31" s="6">
-        <v>-14.01</v>
+        <v>-25.21</v>
       </c>
       <c r="E31" s="7">
-        <v>-3.72</v>
+        <v>-0.98</v>
       </c>
     </row>
     <row r="32" spans="1:5">
       <c r="A32" s="5" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="B32" s="5" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="C32" s="6">
-        <v>-23.55</v>
+        <v>157.3</v>
       </c>
       <c r="D32" s="6">
-        <v>-24.23</v>
-      </c>
-      <c r="E32" s="7">
-        <v>-0.68</v>
+        <v>159.08</v>
+      </c>
+      <c r="E32" s="8">
+        <v>1.78</v>
       </c>
     </row>
     <row r="33" spans="1:5">
       <c r="A33" s="5" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B33" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C33" s="6">
-        <v>162.89</v>
+        <v>380.25</v>
       </c>
       <c r="D33" s="6">
-        <v>157.3</v>
-      </c>
-      <c r="E33" s="7">
-        <v>-5.59</v>
+        <v>384.1</v>
+      </c>
+      <c r="E33" s="8">
+        <v>3.85</v>
       </c>
     </row>
     <row r="34" spans="1:5">
       <c r="A34" s="5" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B34" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C34" s="6">
-        <v>392.75</v>
+        <v>374.55</v>
       </c>
       <c r="D34" s="6">
-        <v>380.25</v>
-      </c>
-      <c r="E34" s="7">
-        <v>-12.5</v>
+        <v>376.6</v>
+      </c>
+      <c r="E34" s="8">
+        <v>2.05</v>
       </c>
     </row>
     <row r="35" spans="1:5">
       <c r="A35" s="5" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B35" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C35" s="6">
-        <v>378.5</v>
+        <v>919.5</v>
       </c>
       <c r="D35" s="6">
-        <v>374.55</v>
+        <v>912.2</v>
       </c>
       <c r="E35" s="7">
-        <v>-3.95</v>
+        <v>-7.3</v>
       </c>
     </row>
     <row r="36" spans="1:5">
       <c r="A36" s="5" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B36" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C36" s="6">
-        <v>959.3</v>
+        <v>2.69</v>
       </c>
       <c r="D36" s="6">
-        <v>919.5</v>
+        <v>2.61</v>
       </c>
       <c r="E36" s="7">
-        <v>-39.8</v>
+        <v>-0.08</v>
       </c>
     </row>
     <row r="37" spans="1:5">
       <c r="A37" s="5" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="B37" s="5" t="s">
-        <v>2</v>
+        <v>24</v>
       </c>
       <c r="C37" s="6">
-        <v>2.76</v>
+        <v>37.13</v>
       </c>
       <c r="D37" s="6">
-        <v>2.69</v>
-      </c>
-      <c r="E37" s="7">
-        <v>-0.07000000000000001</v>
+        <v>40.55</v>
+      </c>
+      <c r="E37" s="8">
+        <v>3.42</v>
       </c>
     </row>
     <row r="38" spans="1:5">
       <c r="A38" s="5" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B38" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C38" s="6">
-        <v>44.61</v>
+        <v>37.21</v>
       </c>
       <c r="D38" s="6">
-        <v>37.13</v>
-      </c>
-      <c r="E38" s="7">
-        <v>-7.48</v>
+        <v>38.82</v>
+      </c>
+      <c r="E38" s="8">
+        <v>1.61</v>
       </c>
     </row>
     <row r="39" spans="1:5">
       <c r="A39" s="5" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B39" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C39" s="6">
-        <v>40.43</v>
+        <v>28.2</v>
       </c>
       <c r="D39" s="6">
-        <v>37.21</v>
-      </c>
-      <c r="E39" s="7">
-        <v>-3.22</v>
+        <v>31.86</v>
+      </c>
+      <c r="E39" s="8">
+        <v>3.66</v>
       </c>
     </row>
     <row r="40" spans="1:5">
       <c r="A40" s="5" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B40" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C40" s="6">
-        <v>31.19</v>
+        <v>30.78</v>
       </c>
       <c r="D40" s="6">
-        <v>28.2</v>
+        <v>29.4</v>
       </c>
       <c r="E40" s="7">
-        <v>-2.99</v>
+        <v>-1.38</v>
       </c>
     </row>
     <row r="41" spans="1:5">
       <c r="A41" s="5" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B41" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C41" s="6">
-        <v>40.38</v>
+        <v>45.8</v>
       </c>
       <c r="D41" s="6">
-        <v>30.78</v>
+        <v>41.28</v>
       </c>
       <c r="E41" s="7">
-        <v>-9.6</v>
+        <v>-4.52</v>
       </c>
     </row>
     <row r="42" spans="1:5">
       <c r="A42" s="5" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="B42" s="5" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="C42" s="6">
-        <v>50.27</v>
+        <v>-33.99</v>
       </c>
       <c r="D42" s="6">
-        <v>45.8</v>
-      </c>
-      <c r="E42" s="7">
-        <v>-4.47</v>
+        <v>-16.5</v>
+      </c>
+      <c r="E42" s="8">
+        <v>17.49</v>
       </c>
     </row>
     <row r="43" spans="1:5">
       <c r="A43" s="5" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B43" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C43" s="6">
-        <v>-68.15000000000001</v>
+        <v>-61.45</v>
       </c>
       <c r="D43" s="6">
-        <v>-33.99</v>
-      </c>
-      <c r="E43" s="8">
-        <v>34.16</v>
+        <v>-79.73999999999999</v>
+      </c>
+      <c r="E43" s="7">
+        <v>-18.29</v>
       </c>
     </row>
     <row r="44" spans="1:5">
       <c r="A44" s="5" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B44" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C44" s="6">
-        <v>-43.86</v>
+        <v>-49.74</v>
       </c>
       <c r="D44" s="6">
-        <v>-61.45</v>
-      </c>
-      <c r="E44" s="7">
-        <v>-17.59</v>
+        <v>-26.47</v>
+      </c>
+      <c r="E44" s="8">
+        <v>23.27</v>
       </c>
     </row>
     <row r="45" spans="1:5">
       <c r="A45" s="5" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B45" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C45" s="6">
-        <v>40.29</v>
+        <v>219.68</v>
       </c>
       <c r="D45" s="6">
-        <v>-49.74</v>
+        <v>-30.28</v>
       </c>
       <c r="E45" s="7">
-        <v>-90.03</v>
+        <v>-249.96</v>
       </c>
     </row>
     <row r="46" spans="1:5">
       <c r="A46" s="5" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B46" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C46" s="6">
-        <v>49.77</v>
+        <v>-20.38</v>
       </c>
       <c r="D46" s="6">
-        <v>219.68</v>
+        <v>9.380000000000001</v>
       </c>
       <c r="E46" s="8">
-        <v>169.91</v>
-      </c>
-    </row>
-    <row r="47" spans="1:5">
-      <c r="A47" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B47" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C47" s="6">
-        <v>-70.37</v>
-      </c>
-      <c r="D47" s="6">
-        <v>-20.38</v>
-      </c>
-      <c r="E47" s="8">
-        <v>49.99</v>
+        <v>29.76</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A6:E6"/>
+    <mergeCell ref="A5:E5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2431,28 +2402,28 @@
         <v>1</v>
       </c>
       <c r="B1" s="9" t="s">
+        <v>62</v>
+      </c>
+      <c r="C1" s="9" t="s">
+        <v>63</v>
+      </c>
+      <c r="D1" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="E1" s="9" t="s">
         <v>65</v>
       </c>
-      <c r="C1" s="9" t="s">
+      <c r="F1" s="9" t="s">
         <v>66</v>
       </c>
-      <c r="D1" s="9" t="s">
+      <c r="G1" s="9" t="s">
         <v>67</v>
       </c>
-      <c r="E1" s="9" t="s">
+      <c r="H1" s="9" t="s">
         <v>68</v>
       </c>
-      <c r="F1" s="9" t="s">
+      <c r="I1" s="9" t="s">
         <v>69</v>
-      </c>
-      <c r="G1" s="9" t="s">
-        <v>70</v>
-      </c>
-      <c r="H1" s="9" t="s">
-        <v>71</v>
-      </c>
-      <c r="I1" s="9" t="s">
-        <v>72</v>
       </c>
     </row>
     <row r="2" spans="1:9">
@@ -2460,22 +2431,22 @@
         <v>42</v>
       </c>
       <c r="B2" s="11">
-        <v>49.92</v>
+        <v>41.92</v>
       </c>
       <c r="C2" s="12">
         <v>5</v>
       </c>
       <c r="D2" s="11">
-        <v>35.8</v>
+        <v>36.4</v>
       </c>
       <c r="E2" s="11">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="F2" s="11">
-        <v>-8.5</v>
+        <v>-8.6</v>
       </c>
       <c r="G2" s="11">
-        <v>-2.1</v>
+        <v>-0.5</v>
       </c>
       <c r="H2" s="11">
         <v>59.8</v>
@@ -2600,19 +2571,19 @@
     </row>
     <row r="2" spans="1:5">
       <c r="A2" s="14">
-        <v>0.2228</v>
+        <v>0.2201</v>
       </c>
       <c r="B2" s="14">
-        <v>0.0759</v>
+        <v>0.08359999999999999</v>
       </c>
       <c r="C2" s="14">
-        <v>0.0327</v>
+        <v>0.0329</v>
       </c>
       <c r="D2" s="14">
-        <v>-0.04019999999999999</v>
+        <v>-0.0397</v>
       </c>
       <c r="E2" s="14">
-        <v>-0.2189</v>
+        <v>-0.2175</v>
       </c>
     </row>
   </sheetData>

--- a/HINDUJA_GROUP_Technical_Metrics.xlsx
+++ b/HINDUJA_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="218" uniqueCount="70">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="207" uniqueCount="61">
   <si>
     <t>Symbol</t>
   </si>
@@ -163,34 +163,7 @@
     <t>▶  SIGNAL EVENTS (vs Previous Run)</t>
   </si>
   <si>
-    <t>Signal</t>
-  </si>
-  <si>
-    <t>Change</t>
-  </si>
-  <si>
-    <t>Direction</t>
-  </si>
-  <si>
-    <t>Prev Value</t>
-  </si>
-  <si>
-    <t>Curr Value</t>
-  </si>
-  <si>
-    <t>RSI Oversold Recovery</t>
-  </si>
-  <si>
-    <t>28.2 → 31.9</t>
-  </si>
-  <si>
-    <t>🟢 BULLISH</t>
-  </si>
-  <si>
-    <t>28.2</t>
-  </si>
-  <si>
-    <t>31.9</t>
+    <t>No signal events detected since last run.</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -276,14 +249,14 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FF9C0006"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FF006100"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -316,13 +289,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -392,18 +365,17 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -775,8 +747,8 @@
     <col min="13" max="13" width="10.7109375" customWidth="1"/>
     <col min="14" max="14" width="11.7109375" customWidth="1"/>
     <col min="15" max="15" width="10.7109375" customWidth="1"/>
-    <col min="16" max="17" width="8.7109375" customWidth="1"/>
-    <col min="18" max="19" width="9.7109375" customWidth="1"/>
+    <col min="16" max="18" width="8.7109375" customWidth="1"/>
+    <col min="19" max="19" width="9.7109375" customWidth="1"/>
     <col min="20" max="20" width="22.7109375" customWidth="1"/>
     <col min="21" max="21" width="9.7109375" customWidth="1"/>
     <col min="22" max="22" width="10.7109375" customWidth="1"/>
@@ -916,10 +888,10 @@
         <v>42</v>
       </c>
       <c r="C2">
-        <v>159.08</v>
+        <v>155.22</v>
       </c>
       <c r="D2">
-        <v>1.13</v>
+        <v>-2.43</v>
       </c>
       <c r="E2">
         <v>208.37</v>
@@ -928,46 +900,46 @@
         <v>131.36</v>
       </c>
       <c r="G2">
-        <v>-23.66</v>
+        <v>-25.51</v>
       </c>
       <c r="H2">
-        <v>21.1</v>
+        <v>18.16</v>
       </c>
       <c r="I2">
-        <v>-2.4</v>
+        <v>-4.04</v>
       </c>
       <c r="J2">
-        <v>-11.15</v>
+        <v>-12.5</v>
       </c>
       <c r="K2">
-        <v>1.09</v>
+        <v>-1.57</v>
       </c>
       <c r="L2">
-        <v>16.83</v>
+        <v>10.34</v>
       </c>
       <c r="M2">
-        <v>22.01</v>
+        <v>21.53</v>
       </c>
       <c r="N2">
         <v>79</v>
       </c>
       <c r="O2">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="P2">
-        <v>160.35</v>
+        <v>159.05</v>
       </c>
       <c r="Q2">
-        <v>165.03</v>
+        <v>164</v>
       </c>
       <c r="R2">
         <v>166.87</v>
       </c>
       <c r="S2">
-        <v>169.96</v>
+        <v>169.95</v>
       </c>
       <c r="T2">
-        <v>-6.4</v>
+        <v>-8.67</v>
       </c>
       <c r="U2" t="s">
         <v>43</v>
@@ -982,43 +954,43 @@
         <v>0</v>
       </c>
       <c r="Y2">
-        <v>40.55</v>
+        <v>35.98</v>
       </c>
       <c r="Z2">
-        <v>-2.87</v>
+        <v>-3.19</v>
       </c>
       <c r="AA2">
-        <v>-2.19</v>
+        <v>-2.39</v>
       </c>
       <c r="AB2">
-        <v>-0.68</v>
+        <v>-0.8</v>
       </c>
       <c r="AC2">
-        <v>59.2</v>
+        <v>45.15</v>
       </c>
       <c r="AD2">
-        <v>61.63</v>
+        <v>54.39</v>
       </c>
       <c r="AE2">
-        <v>4.19</v>
+        <v>4.2</v>
       </c>
       <c r="AF2">
-        <v>-16.5</v>
+        <v>2.25</v>
       </c>
       <c r="AG2">
-        <v>176.86</v>
+        <v>175.47</v>
       </c>
       <c r="AH2">
-        <v>153.2</v>
+        <v>152.53</v>
       </c>
       <c r="AI2">
-        <v>169.79</v>
+        <v>169.39</v>
       </c>
       <c r="AJ2" t="s">
         <v>45</v>
       </c>
       <c r="AK2">
-        <v>33.99</v>
+        <v>36.64</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1029,10 +1001,10 @@
         <v>42</v>
       </c>
       <c r="C3">
-        <v>384.1</v>
+        <v>379</v>
       </c>
       <c r="D3">
-        <v>1.01</v>
+        <v>-1.33</v>
       </c>
       <c r="E3">
         <v>456.15</v>
@@ -1041,25 +1013,25 @@
         <v>225</v>
       </c>
       <c r="G3">
-        <v>-15.8</v>
+        <v>-16.91</v>
       </c>
       <c r="H3">
-        <v>70.70999999999999</v>
+        <v>68.44</v>
       </c>
       <c r="I3">
-        <v>-13.9</v>
+        <v>-16.42</v>
       </c>
       <c r="J3">
-        <v>-3.35</v>
+        <v>-4.62</v>
       </c>
       <c r="K3">
-        <v>-4.77</v>
+        <v>-7.21</v>
       </c>
       <c r="L3">
-        <v>4.05</v>
+        <v>4.12</v>
       </c>
       <c r="M3">
-        <v>8.359999999999999</v>
+        <v>8.630000000000001</v>
       </c>
       <c r="N3">
         <v>60</v>
@@ -1068,19 +1040,19 @@
         <v>57</v>
       </c>
       <c r="P3">
-        <v>404.32</v>
+        <v>389.43</v>
       </c>
       <c r="Q3">
-        <v>418.81</v>
+        <v>418.34</v>
       </c>
       <c r="R3">
-        <v>410.41</v>
+        <v>409.91</v>
       </c>
       <c r="S3">
-        <v>336.69</v>
+        <v>337.12</v>
       </c>
       <c r="T3">
-        <v>14.08</v>
+        <v>12.42</v>
       </c>
       <c r="U3" t="s">
         <v>44</v>
@@ -1095,43 +1067,43 @@
         <v>3</v>
       </c>
       <c r="Y3">
-        <v>38.82</v>
+        <v>37.45</v>
       </c>
       <c r="Z3">
-        <v>-1.83</v>
+        <v>-4.44</v>
       </c>
       <c r="AA3">
-        <v>4.66</v>
+        <v>2.84</v>
       </c>
       <c r="AB3">
-        <v>-6.49</v>
+        <v>-7.28</v>
       </c>
       <c r="AC3">
-        <v>1.76</v>
+        <v>2.03</v>
       </c>
       <c r="AD3">
-        <v>12.14</v>
+        <v>2.19</v>
       </c>
       <c r="AE3">
-        <v>19</v>
+        <v>18.59</v>
       </c>
       <c r="AF3">
-        <v>-79.73999999999999</v>
+        <v>-80.68000000000001</v>
       </c>
       <c r="AG3">
-        <v>469.2</v>
+        <v>470.07</v>
       </c>
       <c r="AH3">
-        <v>368.41</v>
+        <v>366.62</v>
       </c>
       <c r="AI3">
-        <v>444.49</v>
+        <v>438.11</v>
       </c>
       <c r="AJ3" t="s">
         <v>45</v>
       </c>
       <c r="AK3">
-        <v>41.94</v>
+        <v>42.69</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1142,10 +1114,10 @@
         <v>42</v>
       </c>
       <c r="C4">
-        <v>376.6</v>
+        <v>372.35</v>
       </c>
       <c r="D4">
-        <v>0.55</v>
+        <v>-1.13</v>
       </c>
       <c r="E4">
         <v>534</v>
@@ -1154,46 +1126,46 @@
         <v>344.7</v>
       </c>
       <c r="G4">
-        <v>-29.48</v>
+        <v>-30.27</v>
       </c>
       <c r="H4">
-        <v>9.25</v>
+        <v>8.02</v>
       </c>
       <c r="I4">
-        <v>-0.74</v>
+        <v>-1.44</v>
       </c>
       <c r="J4">
-        <v>-6.31</v>
+        <v>-7.5</v>
       </c>
       <c r="K4">
-        <v>-9.42</v>
+        <v>-9.800000000000001</v>
       </c>
       <c r="L4">
-        <v>-27.98</v>
+        <v>-28.08</v>
       </c>
       <c r="M4">
-        <v>-21.75</v>
+        <v>-21.89</v>
       </c>
       <c r="N4">
         <v>21</v>
       </c>
       <c r="O4">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="P4">
-        <v>377.42</v>
+        <v>376.33</v>
       </c>
       <c r="Q4">
-        <v>386.81</v>
+        <v>385.3</v>
       </c>
       <c r="R4">
-        <v>404.71</v>
+        <v>403.53</v>
       </c>
       <c r="S4">
-        <v>408.81</v>
+        <v>408.45</v>
       </c>
       <c r="T4">
-        <v>-7.88</v>
+        <v>-8.84</v>
       </c>
       <c r="U4" t="s">
         <v>43</v>
@@ -1208,34 +1180,34 @@
         <v>0</v>
       </c>
       <c r="Y4">
-        <v>31.86</v>
+        <v>28.6</v>
       </c>
       <c r="Z4">
-        <v>-7.93</v>
+        <v>-8.09</v>
       </c>
       <c r="AA4">
-        <v>-7.75</v>
+        <v>-7.81</v>
       </c>
       <c r="AB4">
-        <v>-0.19</v>
+        <v>-0.28</v>
       </c>
       <c r="AC4">
-        <v>25.25</v>
+        <v>20.64</v>
       </c>
       <c r="AD4">
-        <v>23.89</v>
+        <v>22.71</v>
       </c>
       <c r="AE4">
-        <v>10.42</v>
+        <v>10.39</v>
       </c>
       <c r="AF4">
-        <v>-26.47</v>
+        <v>-44.42</v>
       </c>
       <c r="AG4">
-        <v>403.82</v>
+        <v>401.78</v>
       </c>
       <c r="AH4">
-        <v>369.8</v>
+        <v>368.82</v>
       </c>
       <c r="AI4">
         <v>405.81</v>
@@ -1244,7 +1216,7 @@
         <v>45</v>
       </c>
       <c r="AK4">
-        <v>31.45</v>
+        <v>34.07</v>
       </c>
     </row>
     <row r="5" spans="1:37">
@@ -1255,10 +1227,10 @@
         <v>42</v>
       </c>
       <c r="C5">
-        <v>912.2</v>
+        <v>909.7</v>
       </c>
       <c r="D5">
-        <v>-0.79</v>
+        <v>-0.27</v>
       </c>
       <c r="E5">
         <v>1069.3</v>
@@ -1267,25 +1239,25 @@
         <v>712.75</v>
       </c>
       <c r="G5">
-        <v>-14.69</v>
+        <v>-14.93</v>
       </c>
       <c r="H5">
-        <v>27.98</v>
+        <v>27.63</v>
       </c>
       <c r="I5">
-        <v>-5.6</v>
+        <v>-4.84</v>
       </c>
       <c r="J5">
-        <v>-9.140000000000001</v>
+        <v>-9.289999999999999</v>
       </c>
       <c r="K5">
-        <v>-0.35</v>
+        <v>-1.57</v>
       </c>
       <c r="L5">
-        <v>24.23</v>
+        <v>20.45</v>
       </c>
       <c r="M5">
-        <v>-3.97</v>
+        <v>-3.75</v>
       </c>
       <c r="N5">
         <v>99</v>
@@ -1294,19 +1266,19 @@
         <v>70</v>
       </c>
       <c r="P5">
-        <v>940.4</v>
+        <v>931.14</v>
       </c>
       <c r="Q5">
-        <v>974.76</v>
+        <v>970.54</v>
       </c>
       <c r="R5">
-        <v>1000.84</v>
+        <v>998.49</v>
       </c>
       <c r="S5">
-        <v>922.9299999999999</v>
+        <v>923.26</v>
       </c>
       <c r="T5">
-        <v>-1.16</v>
+        <v>-1.47</v>
       </c>
       <c r="U5" t="s">
         <v>43</v>
@@ -1321,43 +1293,43 @@
         <v>1</v>
       </c>
       <c r="Y5">
-        <v>29.4</v>
+        <v>28.92</v>
       </c>
       <c r="Z5">
-        <v>-19.28</v>
+        <v>-21.42</v>
       </c>
       <c r="AA5">
-        <v>-13.03</v>
+        <v>-14.7</v>
       </c>
       <c r="AB5">
-        <v>-6.25</v>
+        <v>-6.71</v>
       </c>
       <c r="AC5">
-        <v>13.41</v>
+        <v>0</v>
       </c>
       <c r="AD5">
-        <v>23.35</v>
+        <v>12.2</v>
       </c>
       <c r="AE5">
-        <v>21.07</v>
+        <v>21.25</v>
       </c>
       <c r="AF5">
-        <v>-30.28</v>
+        <v>-12.88</v>
       </c>
       <c r="AG5">
-        <v>1033.15</v>
+        <v>1034.95</v>
       </c>
       <c r="AH5">
-        <v>916.37</v>
+        <v>906.14</v>
       </c>
       <c r="AI5">
-        <v>978.61</v>
+        <v>964.95</v>
       </c>
       <c r="AJ5" t="s">
         <v>45</v>
       </c>
       <c r="AK5">
-        <v>32.96</v>
+        <v>37.47</v>
       </c>
     </row>
     <row r="6" spans="1:37">
@@ -1368,58 +1340,58 @@
         <v>42</v>
       </c>
       <c r="C6">
-        <v>2.61</v>
+        <v>2.67</v>
       </c>
       <c r="D6">
-        <v>-2.97</v>
+        <v>2.3</v>
       </c>
       <c r="E6">
-        <v>3.49</v>
+        <v>3.45</v>
       </c>
       <c r="F6">
         <v>1.84</v>
       </c>
       <c r="G6">
-        <v>-25.21</v>
+        <v>-22.61</v>
       </c>
       <c r="H6">
-        <v>41.85</v>
+        <v>45.11</v>
       </c>
       <c r="I6">
-        <v>-6.12</v>
+        <v>-4.3</v>
       </c>
       <c r="J6">
-        <v>-13.29</v>
+        <v>-9.800000000000001</v>
       </c>
       <c r="K6">
-        <v>11.06</v>
+        <v>10.79</v>
       </c>
       <c r="L6">
-        <v>-26.48</v>
+        <v>-23.5</v>
       </c>
       <c r="M6">
-        <v>3.29</v>
+        <v>3.85</v>
       </c>
       <c r="N6">
         <v>40</v>
       </c>
       <c r="O6">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="P6">
-        <v>2.72</v>
+        <v>2.7</v>
       </c>
       <c r="Q6">
-        <v>2.83</v>
+        <v>2.81</v>
       </c>
       <c r="R6">
-        <v>2.59</v>
+        <v>2.6</v>
       </c>
       <c r="S6">
         <v>2.66</v>
       </c>
       <c r="T6">
-        <v>-2.04</v>
+        <v>0.26</v>
       </c>
       <c r="U6" t="s">
         <v>44</v>
@@ -1431,37 +1403,37 @@
         <v>43</v>
       </c>
       <c r="X6">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y6">
-        <v>41.28</v>
+        <v>45.62</v>
       </c>
       <c r="Z6">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
       <c r="AA6">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="AB6">
         <v>-0.04</v>
       </c>
       <c r="AC6">
-        <v>0</v>
+        <v>6.44</v>
       </c>
       <c r="AD6">
-        <v>0.78</v>
+        <v>2.15</v>
       </c>
       <c r="AE6">
         <v>0.15</v>
       </c>
       <c r="AF6">
-        <v>9.380000000000001</v>
+        <v>-15.8</v>
       </c>
       <c r="AG6">
-        <v>3.02</v>
+        <v>3</v>
       </c>
       <c r="AH6">
-        <v>2.64</v>
+        <v>2.63</v>
       </c>
       <c r="AI6">
         <v>3.06</v>
@@ -1470,7 +1442,7 @@
         <v>45</v>
       </c>
       <c r="AK6">
-        <v>25.32</v>
+        <v>25.67</v>
       </c>
     </row>
   </sheetData>
@@ -1631,47 +1603,12 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" s="3" t="s">
         <v>47</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="D2" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="E2" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="F2" s="3" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6">
-      <c r="A3" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="B3" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="C3" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="D3" s="4" t="s">
-        <v>54</v>
-      </c>
-      <c r="E3" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="F3" s="4" t="s">
-        <v>56</v>
       </c>
     </row>
     <row r="5" spans="1:6">
       <c r="A5" s="2" t="s">
-        <v>57</v>
+        <v>48</v>
       </c>
       <c r="B5" s="2"/>
       <c r="C5" s="2"/>
@@ -1679,700 +1616,700 @@
       <c r="E5" s="2"/>
     </row>
     <row r="6" spans="1:6">
-      <c r="A6" s="3" t="s">
+      <c r="A6" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B6" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="E6" s="3" t="s">
-        <v>61</v>
+      <c r="B6" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="E6" s="4" t="s">
+        <v>52</v>
       </c>
     </row>
     <row r="7" spans="1:6">
-      <c r="A7" s="5" t="s">
+      <c r="A7" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B7" s="5" t="s">
+      <c r="B7" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C7" s="6">
-        <v>-9.949999999999999</v>
-      </c>
-      <c r="D7" s="6">
+      <c r="C7" s="5">
         <v>-11.15</v>
       </c>
-      <c r="E7" s="7">
-        <v>-1.2</v>
+      <c r="D7" s="5">
+        <v>-12.5</v>
+      </c>
+      <c r="E7" s="6">
+        <v>-1.35</v>
       </c>
     </row>
     <row r="8" spans="1:6">
-      <c r="A8" s="5" t="s">
+      <c r="A8" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B8" s="5" t="s">
+      <c r="B8" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C8" s="6">
-        <v>-3.9</v>
-      </c>
-      <c r="D8" s="6">
+      <c r="C8" s="5">
         <v>-3.35</v>
       </c>
-      <c r="E8" s="8">
-        <v>0.55</v>
+      <c r="D8" s="5">
+        <v>-4.62</v>
+      </c>
+      <c r="E8" s="6">
+        <v>-1.27</v>
       </c>
     </row>
     <row r="9" spans="1:6">
-      <c r="A9" s="5" t="s">
+      <c r="A9" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B9" s="5" t="s">
+      <c r="B9" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C9" s="6">
-        <v>-6.67</v>
-      </c>
-      <c r="D9" s="6">
+      <c r="C9" s="5">
         <v>-6.31</v>
       </c>
-      <c r="E9" s="8">
-        <v>0.36</v>
+      <c r="D9" s="5">
+        <v>-7.5</v>
+      </c>
+      <c r="E9" s="6">
+        <v>-1.19</v>
       </c>
     </row>
     <row r="10" spans="1:6">
-      <c r="A10" s="5" t="s">
+      <c r="A10" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="B10" s="5" t="s">
+      <c r="B10" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C10" s="6">
-        <v>-9.41</v>
-      </c>
-      <c r="D10" s="6">
+      <c r="C10" s="5">
         <v>-9.140000000000001</v>
       </c>
-      <c r="E10" s="8">
-        <v>0.27</v>
+      <c r="D10" s="5">
+        <v>-9.289999999999999</v>
+      </c>
+      <c r="E10" s="6">
+        <v>-0.15</v>
       </c>
     </row>
     <row r="11" spans="1:6">
-      <c r="A11" s="5" t="s">
+      <c r="A11" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="B11" s="5" t="s">
+      <c r="B11" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C11" s="6">
-        <v>-12.66</v>
-      </c>
-      <c r="D11" s="6">
+      <c r="C11" s="5">
         <v>-13.29</v>
       </c>
+      <c r="D11" s="5">
+        <v>-9.800000000000001</v>
+      </c>
       <c r="E11" s="7">
-        <v>-0.63</v>
+        <v>3.49</v>
       </c>
     </row>
     <row r="12" spans="1:6">
-      <c r="A12" s="5" t="s">
+      <c r="A12" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B12" s="5" t="s">
+      <c r="B12" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C12" s="6">
-        <v>-0.83</v>
-      </c>
-      <c r="D12" s="6">
+      <c r="C12" s="5">
         <v>-2.4</v>
       </c>
-      <c r="E12" s="7">
+      <c r="D12" s="5">
+        <v>-4.04</v>
+      </c>
+      <c r="E12" s="6">
+        <v>-1.64</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6">
+      <c r="A13" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C13" s="5">
+        <v>-13.9</v>
+      </c>
+      <c r="D13" s="5">
+        <v>-16.42</v>
+      </c>
+      <c r="E13" s="6">
+        <v>-2.52</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6">
+      <c r="A14" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C14" s="5">
+        <v>-0.74</v>
+      </c>
+      <c r="D14" s="5">
+        <v>-1.44</v>
+      </c>
+      <c r="E14" s="6">
+        <v>-0.7</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6">
+      <c r="A15" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C15" s="5">
+        <v>-5.6</v>
+      </c>
+      <c r="D15" s="5">
+        <v>-4.84</v>
+      </c>
+      <c r="E15" s="7">
+        <v>0.76</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6">
+      <c r="A16" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C16" s="5">
+        <v>-6.12</v>
+      </c>
+      <c r="D16" s="5">
+        <v>-4.3</v>
+      </c>
+      <c r="E16" s="7">
+        <v>1.82</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C17" s="5">
+        <v>16.83</v>
+      </c>
+      <c r="D17" s="5">
+        <v>10.34</v>
+      </c>
+      <c r="E17" s="6">
+        <v>-6.49</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C18" s="5">
+        <v>4.05</v>
+      </c>
+      <c r="D18" s="5">
+        <v>4.12</v>
+      </c>
+      <c r="E18" s="7">
+        <v>0.07000000000000001</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C19" s="5">
+        <v>-27.98</v>
+      </c>
+      <c r="D19" s="5">
+        <v>-28.08</v>
+      </c>
+      <c r="E19" s="6">
+        <v>-0.1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C20" s="5">
+        <v>24.23</v>
+      </c>
+      <c r="D20" s="5">
+        <v>20.45</v>
+      </c>
+      <c r="E20" s="6">
+        <v>-3.78</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C21" s="5">
+        <v>-26.48</v>
+      </c>
+      <c r="D21" s="5">
+        <v>-23.5</v>
+      </c>
+      <c r="E21" s="7">
+        <v>2.98</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B22" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C22" s="5">
+        <v>1.09</v>
+      </c>
+      <c r="D22" s="5">
         <v>-1.57</v>
       </c>
-    </row>
-    <row r="13" spans="1:6">
-      <c r="A13" s="5" t="s">
+      <c r="E22" s="6">
+        <v>-2.66</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B13" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C13" s="6">
-        <v>-16.64</v>
-      </c>
-      <c r="D13" s="6">
-        <v>-13.9</v>
-      </c>
-      <c r="E13" s="8">
-        <v>2.74</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
-      <c r="A14" s="5" t="s">
+      <c r="B23" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C23" s="5">
+        <v>-4.77</v>
+      </c>
+      <c r="D23" s="5">
+        <v>-7.21</v>
+      </c>
+      <c r="E23" s="6">
+        <v>-2.44</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5">
+      <c r="A24" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B14" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C14" s="6">
-        <v>-3.05</v>
-      </c>
-      <c r="D14" s="6">
-        <v>-0.74</v>
-      </c>
-      <c r="E14" s="8">
-        <v>2.31</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6">
-      <c r="A15" s="5" t="s">
+      <c r="B24" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C24" s="5">
+        <v>-9.42</v>
+      </c>
+      <c r="D24" s="5">
+        <v>-9.800000000000001</v>
+      </c>
+      <c r="E24" s="6">
+        <v>-0.38</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5">
+      <c r="A25" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="B15" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C15" s="6">
-        <v>-4.04</v>
-      </c>
-      <c r="D15" s="6">
-        <v>-5.6</v>
-      </c>
-      <c r="E15" s="7">
-        <v>-1.56</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
-      <c r="A16" s="5" t="s">
+      <c r="B25" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C25" s="5">
+        <v>-0.35</v>
+      </c>
+      <c r="D25" s="5">
+        <v>-1.57</v>
+      </c>
+      <c r="E25" s="6">
+        <v>-1.22</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
+      <c r="A26" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="B16" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C16" s="6">
-        <v>-4.61</v>
-      </c>
-      <c r="D16" s="6">
-        <v>-6.12</v>
-      </c>
-      <c r="E16" s="7">
-        <v>-1.51</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5">
-      <c r="A17" s="5" t="s">
+      <c r="B26" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C26" s="5">
+        <v>11.06</v>
+      </c>
+      <c r="D26" s="5">
+        <v>10.79</v>
+      </c>
+      <c r="E26" s="6">
+        <v>-0.27</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5">
+      <c r="A27" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B17" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C17" s="6">
-        <v>14.33</v>
-      </c>
-      <c r="D17" s="6">
-        <v>16.83</v>
-      </c>
-      <c r="E17" s="8">
-        <v>2.5</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5">
-      <c r="A18" s="5" t="s">
+      <c r="B27" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C27" s="5">
+        <v>-23.66</v>
+      </c>
+      <c r="D27" s="5">
+        <v>-25.51</v>
+      </c>
+      <c r="E27" s="6">
+        <v>-1.85</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5">
+      <c r="A28" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B18" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C18" s="6">
-        <v>4.09</v>
-      </c>
-      <c r="D18" s="6">
-        <v>4.05</v>
-      </c>
-      <c r="E18" s="7">
-        <v>-0.04</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5">
-      <c r="A19" s="5" t="s">
+      <c r="B28" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C28" s="5">
+        <v>-15.8</v>
+      </c>
+      <c r="D28" s="5">
+        <v>-16.91</v>
+      </c>
+      <c r="E28" s="6">
+        <v>-1.11</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5">
+      <c r="A29" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B19" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C19" s="6">
-        <v>-29.46</v>
-      </c>
-      <c r="D19" s="6">
-        <v>-27.98</v>
-      </c>
-      <c r="E19" s="8">
-        <v>1.48</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5">
-      <c r="A20" s="5" t="s">
+      <c r="B29" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C29" s="5">
+        <v>-29.48</v>
+      </c>
+      <c r="D29" s="5">
+        <v>-30.27</v>
+      </c>
+      <c r="E29" s="6">
+        <v>-0.79</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5">
+      <c r="A30" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="B20" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C20" s="6">
-        <v>23.52</v>
-      </c>
-      <c r="D20" s="6">
-        <v>24.23</v>
-      </c>
-      <c r="E20" s="8">
-        <v>0.71</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5">
-      <c r="A21" s="5" t="s">
+      <c r="B30" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C30" s="5">
+        <v>-14.69</v>
+      </c>
+      <c r="D30" s="5">
+        <v>-14.93</v>
+      </c>
+      <c r="E30" s="6">
+        <v>-0.24</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5">
+      <c r="A31" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="B21" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C21" s="6">
-        <v>-25.48</v>
-      </c>
-      <c r="D21" s="6">
-        <v>-26.48</v>
-      </c>
-      <c r="E21" s="7">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5">
-      <c r="A22" s="5" t="s">
+      <c r="B31" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C31" s="5">
+        <v>-25.21</v>
+      </c>
+      <c r="D31" s="5">
+        <v>-22.61</v>
+      </c>
+      <c r="E31" s="7">
+        <v>2.6</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5">
+      <c r="A32" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B22" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C22" s="6">
-        <v>-2.1</v>
-      </c>
-      <c r="D22" s="6">
-        <v>1.09</v>
-      </c>
-      <c r="E22" s="8">
-        <v>3.19</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5">
-      <c r="A23" s="5" t="s">
+      <c r="B32" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C32" s="5">
+        <v>159.08</v>
+      </c>
+      <c r="D32" s="5">
+        <v>155.22</v>
+      </c>
+      <c r="E32" s="6">
+        <v>-3.86</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5">
+      <c r="A33" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B23" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C23" s="6">
-        <v>-6.98</v>
-      </c>
-      <c r="D23" s="6">
-        <v>-4.77</v>
-      </c>
-      <c r="E23" s="8">
-        <v>2.21</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5">
-      <c r="A24" s="5" t="s">
+      <c r="B33" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C33" s="5">
+        <v>384.1</v>
+      </c>
+      <c r="D33" s="5">
+        <v>379</v>
+      </c>
+      <c r="E33" s="6">
+        <v>-5.1</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5">
+      <c r="A34" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B24" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C24" s="6">
-        <v>-10.87</v>
-      </c>
-      <c r="D24" s="6">
-        <v>-9.42</v>
-      </c>
-      <c r="E24" s="8">
-        <v>1.45</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5">
-      <c r="A25" s="5" t="s">
+      <c r="B34" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C34" s="5">
+        <v>376.6</v>
+      </c>
+      <c r="D34" s="5">
+        <v>372.35</v>
+      </c>
+      <c r="E34" s="6">
+        <v>-4.25</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5">
+      <c r="A35" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="B25" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C25" s="6">
+      <c r="B35" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C35" s="5">
+        <v>912.2</v>
+      </c>
+      <c r="D35" s="5">
+        <v>909.7</v>
+      </c>
+      <c r="E35" s="6">
+        <v>-2.5</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5">
+      <c r="A36" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B36" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C36" s="5">
+        <v>2.61</v>
+      </c>
+      <c r="D36" s="5">
+        <v>2.67</v>
+      </c>
+      <c r="E36" s="7">
         <v>0.06</v>
       </c>
-      <c r="D25" s="6">
-        <v>-0.35</v>
-      </c>
-      <c r="E25" s="7">
-        <v>-0.41</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5">
-      <c r="A26" s="5" t="s">
+    </row>
+    <row r="37" spans="1:5">
+      <c r="A37" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B37" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C37" s="5">
+        <v>40.55</v>
+      </c>
+      <c r="D37" s="5">
+        <v>35.98</v>
+      </c>
+      <c r="E37" s="6">
+        <v>-4.57</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5">
+      <c r="A38" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B38" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C38" s="5">
+        <v>38.82</v>
+      </c>
+      <c r="D38" s="5">
+        <v>37.45</v>
+      </c>
+      <c r="E38" s="6">
+        <v>-1.37</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5">
+      <c r="A39" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B39" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C39" s="5">
+        <v>31.86</v>
+      </c>
+      <c r="D39" s="5">
+        <v>28.6</v>
+      </c>
+      <c r="E39" s="6">
+        <v>-3.26</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5">
+      <c r="A40" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B40" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C40" s="5">
+        <v>29.4</v>
+      </c>
+      <c r="D40" s="5">
+        <v>28.92</v>
+      </c>
+      <c r="E40" s="6">
+        <v>-0.48</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5">
+      <c r="A41" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="B26" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C26" s="6">
-        <v>9.35</v>
-      </c>
-      <c r="D26" s="6">
-        <v>11.06</v>
-      </c>
-      <c r="E26" s="8">
-        <v>1.71</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5">
-      <c r="A27" s="5" t="s">
+      <c r="B41" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C41" s="5">
+        <v>41.28</v>
+      </c>
+      <c r="D41" s="5">
+        <v>45.62</v>
+      </c>
+      <c r="E41" s="7">
+        <v>4.34</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5">
+      <c r="A42" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B27" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C27" s="6">
-        <v>-24.51</v>
-      </c>
-      <c r="D27" s="6">
-        <v>-23.66</v>
-      </c>
-      <c r="E27" s="8">
-        <v>0.85</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5">
-      <c r="A28" s="5" t="s">
+      <c r="B42" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C42" s="5">
+        <v>-16.5</v>
+      </c>
+      <c r="D42" s="5">
+        <v>2.25</v>
+      </c>
+      <c r="E42" s="7">
+        <v>18.75</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5">
+      <c r="A43" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B28" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C28" s="6">
-        <v>-16.64</v>
-      </c>
-      <c r="D28" s="6">
+      <c r="B43" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C43" s="5">
+        <v>-79.73999999999999</v>
+      </c>
+      <c r="D43" s="5">
+        <v>-80.68000000000001</v>
+      </c>
+      <c r="E43" s="6">
+        <v>-0.9399999999999999</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5">
+      <c r="A44" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B44" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C44" s="5">
+        <v>-26.47</v>
+      </c>
+      <c r="D44" s="5">
+        <v>-44.42</v>
+      </c>
+      <c r="E44" s="6">
+        <v>-17.95</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5">
+      <c r="A45" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B45" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C45" s="5">
+        <v>-30.28</v>
+      </c>
+      <c r="D45" s="5">
+        <v>-12.88</v>
+      </c>
+      <c r="E45" s="7">
+        <v>17.4</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5">
+      <c r="A46" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B46" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C46" s="5">
+        <v>9.380000000000001</v>
+      </c>
+      <c r="D46" s="5">
         <v>-15.8</v>
       </c>
-      <c r="E28" s="8">
-        <v>0.84</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5">
-      <c r="A29" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B29" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C29" s="6">
-        <v>-29.86</v>
-      </c>
-      <c r="D29" s="6">
-        <v>-29.48</v>
-      </c>
-      <c r="E29" s="8">
-        <v>0.38</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5">
-      <c r="A30" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B30" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C30" s="6">
-        <v>-14.01</v>
-      </c>
-      <c r="D30" s="6">
-        <v>-14.69</v>
-      </c>
-      <c r="E30" s="7">
-        <v>-0.68</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5">
-      <c r="A31" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B31" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C31" s="6">
-        <v>-24.23</v>
-      </c>
-      <c r="D31" s="6">
-        <v>-25.21</v>
-      </c>
-      <c r="E31" s="7">
-        <v>-0.98</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5">
-      <c r="A32" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B32" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C32" s="6">
-        <v>157.3</v>
-      </c>
-      <c r="D32" s="6">
-        <v>159.08</v>
-      </c>
-      <c r="E32" s="8">
-        <v>1.78</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5">
-      <c r="A33" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B33" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C33" s="6">
-        <v>380.25</v>
-      </c>
-      <c r="D33" s="6">
-        <v>384.1</v>
-      </c>
-      <c r="E33" s="8">
-        <v>3.85</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5">
-      <c r="A34" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B34" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C34" s="6">
-        <v>374.55</v>
-      </c>
-      <c r="D34" s="6">
-        <v>376.6</v>
-      </c>
-      <c r="E34" s="8">
-        <v>2.05</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5">
-      <c r="A35" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B35" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C35" s="6">
-        <v>919.5</v>
-      </c>
-      <c r="D35" s="6">
-        <v>912.2</v>
-      </c>
-      <c r="E35" s="7">
-        <v>-7.3</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5">
-      <c r="A36" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B36" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C36" s="6">
-        <v>2.69</v>
-      </c>
-      <c r="D36" s="6">
-        <v>2.61</v>
-      </c>
-      <c r="E36" s="7">
-        <v>-0.08</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5">
-      <c r="A37" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B37" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C37" s="6">
-        <v>37.13</v>
-      </c>
-      <c r="D37" s="6">
-        <v>40.55</v>
-      </c>
-      <c r="E37" s="8">
-        <v>3.42</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5">
-      <c r="A38" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B38" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C38" s="6">
-        <v>37.21</v>
-      </c>
-      <c r="D38" s="6">
-        <v>38.82</v>
-      </c>
-      <c r="E38" s="8">
-        <v>1.61</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5">
-      <c r="A39" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B39" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C39" s="6">
-        <v>28.2</v>
-      </c>
-      <c r="D39" s="6">
-        <v>31.86</v>
-      </c>
-      <c r="E39" s="8">
-        <v>3.66</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5">
-      <c r="A40" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B40" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C40" s="6">
-        <v>30.78</v>
-      </c>
-      <c r="D40" s="6">
-        <v>29.4</v>
-      </c>
-      <c r="E40" s="7">
-        <v>-1.38</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5">
-      <c r="A41" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B41" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C41" s="6">
-        <v>45.8</v>
-      </c>
-      <c r="D41" s="6">
-        <v>41.28</v>
-      </c>
-      <c r="E41" s="7">
-        <v>-4.52</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5">
-      <c r="A42" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B42" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C42" s="6">
-        <v>-33.99</v>
-      </c>
-      <c r="D42" s="6">
-        <v>-16.5</v>
-      </c>
-      <c r="E42" s="8">
-        <v>17.49</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5">
-      <c r="A43" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B43" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C43" s="6">
-        <v>-61.45</v>
-      </c>
-      <c r="D43" s="6">
-        <v>-79.73999999999999</v>
-      </c>
-      <c r="E43" s="7">
-        <v>-18.29</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5">
-      <c r="A44" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B44" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C44" s="6">
-        <v>-49.74</v>
-      </c>
-      <c r="D44" s="6">
-        <v>-26.47</v>
-      </c>
-      <c r="E44" s="8">
-        <v>23.27</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5">
-      <c r="A45" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B45" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C45" s="6">
-        <v>219.68</v>
-      </c>
-      <c r="D45" s="6">
-        <v>-30.28</v>
-      </c>
-      <c r="E45" s="7">
-        <v>-249.96</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5">
-      <c r="A46" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B46" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C46" s="6">
-        <v>-20.38</v>
-      </c>
-      <c r="D46" s="6">
-        <v>9.380000000000001</v>
-      </c>
-      <c r="E46" s="8">
-        <v>29.76</v>
+      <c r="E46" s="6">
+        <v>-25.18</v>
       </c>
     </row>
   </sheetData>
@@ -2398,60 +2335,60 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="28" customHeight="1">
-      <c r="A1" s="9" t="s">
+      <c r="A1" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="9" t="s">
-        <v>62</v>
-      </c>
-      <c r="C1" s="9" t="s">
-        <v>63</v>
-      </c>
-      <c r="D1" s="9" t="s">
-        <v>64</v>
-      </c>
-      <c r="E1" s="9" t="s">
-        <v>65</v>
-      </c>
-      <c r="F1" s="9" t="s">
-        <v>66</v>
-      </c>
-      <c r="G1" s="9" t="s">
-        <v>67</v>
-      </c>
-      <c r="H1" s="9" t="s">
-        <v>68</v>
-      </c>
-      <c r="I1" s="9" t="s">
-        <v>69</v>
+      <c r="B1" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="C1" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="D1" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="E1" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="F1" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="G1" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="H1" s="8" t="s">
+        <v>59</v>
+      </c>
+      <c r="I1" s="8" t="s">
+        <v>60</v>
       </c>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="10" t="s">
+      <c r="A2" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="B2" s="11">
-        <v>41.92</v>
-      </c>
-      <c r="C2" s="12">
+      <c r="B2" s="10">
+        <v>49.92</v>
+      </c>
+      <c r="C2" s="11">
         <v>5</v>
       </c>
-      <c r="D2" s="11">
-        <v>36.4</v>
-      </c>
-      <c r="E2" s="11">
-        <v>20</v>
-      </c>
-      <c r="F2" s="11">
-        <v>-8.6</v>
-      </c>
-      <c r="G2" s="11">
-        <v>-0.5</v>
-      </c>
-      <c r="H2" s="11">
+      <c r="D2" s="10">
+        <v>35.3</v>
+      </c>
+      <c r="E2" s="10">
+        <v>40</v>
+      </c>
+      <c r="F2" s="10">
+        <v>-8.699999999999999</v>
+      </c>
+      <c r="G2" s="10">
+        <v>-1.9</v>
+      </c>
+      <c r="H2" s="10">
         <v>59.8</v>
       </c>
-      <c r="I2" s="11">
+      <c r="I2" s="10">
         <v>20</v>
       </c>
     </row>
@@ -2553,37 +2490,37 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
-      <c r="A1" s="13" t="s">
+      <c r="A1" s="12" t="s">
         <v>37</v>
       </c>
-      <c r="B1" s="13" t="s">
+      <c r="B1" s="12" t="s">
         <v>38</v>
       </c>
-      <c r="C1" s="13" t="s">
+      <c r="C1" s="12" t="s">
         <v>41</v>
       </c>
-      <c r="D1" s="13" t="s">
+      <c r="D1" s="12" t="s">
         <v>40</v>
       </c>
-      <c r="E1" s="13" t="s">
+      <c r="E1" s="12" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="2" spans="1:5">
-      <c r="A2" s="14">
-        <v>0.2201</v>
-      </c>
-      <c r="B2" s="14">
-        <v>0.08359999999999999</v>
-      </c>
-      <c r="C2" s="14">
-        <v>0.0329</v>
-      </c>
-      <c r="D2" s="14">
-        <v>-0.0397</v>
-      </c>
-      <c r="E2" s="14">
-        <v>-0.2175</v>
+      <c r="A2" s="13">
+        <v>0.2153</v>
+      </c>
+      <c r="B2" s="13">
+        <v>0.0863</v>
+      </c>
+      <c r="C2" s="13">
+        <v>0.0385</v>
+      </c>
+      <c r="D2" s="13">
+        <v>-0.0375</v>
+      </c>
+      <c r="E2" s="13">
+        <v>-0.2189</v>
       </c>
     </row>
   </sheetData>

--- a/HINDUJA_GROUP_Technical_Metrics.xlsx
+++ b/HINDUJA_GROUP_Technical_Metrics.xlsx
@@ -888,10 +888,10 @@
         <v>42</v>
       </c>
       <c r="C2">
-        <v>155.22</v>
+        <v>153.44</v>
       </c>
       <c r="D2">
-        <v>-2.43</v>
+        <v>-1.15</v>
       </c>
       <c r="E2">
         <v>208.37</v>
@@ -900,46 +900,46 @@
         <v>131.36</v>
       </c>
       <c r="G2">
-        <v>-25.51</v>
+        <v>-26.36</v>
       </c>
       <c r="H2">
-        <v>18.16</v>
+        <v>16.81</v>
       </c>
       <c r="I2">
-        <v>-4.04</v>
+        <v>-4.55</v>
       </c>
       <c r="J2">
-        <v>-12.5</v>
+        <v>-12.7</v>
       </c>
       <c r="K2">
-        <v>-1.57</v>
+        <v>-5.47</v>
       </c>
       <c r="L2">
-        <v>10.34</v>
+        <v>10.44</v>
       </c>
       <c r="M2">
-        <v>21.53</v>
+        <v>21.31</v>
       </c>
       <c r="N2">
         <v>79</v>
       </c>
       <c r="O2">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="P2">
-        <v>159.05</v>
+        <v>157.59</v>
       </c>
       <c r="Q2">
-        <v>164</v>
+        <v>162.89</v>
       </c>
       <c r="R2">
-        <v>166.87</v>
+        <v>166.84</v>
       </c>
       <c r="S2">
-        <v>169.95</v>
+        <v>169.94</v>
       </c>
       <c r="T2">
-        <v>-8.67</v>
+        <v>-9.710000000000001</v>
       </c>
       <c r="U2" t="s">
         <v>43</v>
@@ -954,43 +954,43 @@
         <v>0</v>
       </c>
       <c r="Y2">
-        <v>35.98</v>
+        <v>34.07</v>
       </c>
       <c r="Z2">
-        <v>-3.19</v>
+        <v>-3.54</v>
       </c>
       <c r="AA2">
-        <v>-2.39</v>
+        <v>-2.62</v>
       </c>
       <c r="AB2">
-        <v>-0.8</v>
+        <v>-0.92</v>
       </c>
       <c r="AC2">
-        <v>45.15</v>
+        <v>41.8</v>
       </c>
       <c r="AD2">
-        <v>54.39</v>
+        <v>48.72</v>
       </c>
       <c r="AE2">
-        <v>4.2</v>
+        <v>4.12</v>
       </c>
       <c r="AF2">
-        <v>2.25</v>
+        <v>20.98</v>
       </c>
       <c r="AG2">
-        <v>175.47</v>
+        <v>173.91</v>
       </c>
       <c r="AH2">
-        <v>152.53</v>
+        <v>151.88</v>
       </c>
       <c r="AI2">
-        <v>169.39</v>
+        <v>166.34</v>
       </c>
       <c r="AJ2" t="s">
         <v>45</v>
       </c>
       <c r="AK2">
-        <v>36.64</v>
+        <v>39.95</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1001,10 +1001,10 @@
         <v>42</v>
       </c>
       <c r="C3">
-        <v>379</v>
+        <v>363.65</v>
       </c>
       <c r="D3">
-        <v>-1.33</v>
+        <v>-4.05</v>
       </c>
       <c r="E3">
         <v>456.15</v>
@@ -1013,46 +1013,46 @@
         <v>225</v>
       </c>
       <c r="G3">
-        <v>-16.91</v>
+        <v>-20.28</v>
       </c>
       <c r="H3">
-        <v>68.44</v>
+        <v>61.62</v>
       </c>
       <c r="I3">
-        <v>-16.42</v>
+        <v>-11.53</v>
       </c>
       <c r="J3">
-        <v>-4.62</v>
+        <v>-6.34</v>
       </c>
       <c r="K3">
-        <v>-7.21</v>
+        <v>-9.56</v>
       </c>
       <c r="L3">
-        <v>4.12</v>
+        <v>1.24</v>
       </c>
       <c r="M3">
-        <v>8.630000000000001</v>
+        <v>7.55</v>
       </c>
       <c r="N3">
         <v>60</v>
       </c>
       <c r="O3">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="P3">
-        <v>389.43</v>
+        <v>379.95</v>
       </c>
       <c r="Q3">
-        <v>418.34</v>
+        <v>416.9</v>
       </c>
       <c r="R3">
-        <v>409.91</v>
+        <v>409.17</v>
       </c>
       <c r="S3">
-        <v>337.12</v>
+        <v>337.51</v>
       </c>
       <c r="T3">
-        <v>12.42</v>
+        <v>7.75</v>
       </c>
       <c r="U3" t="s">
         <v>44</v>
@@ -1067,43 +1067,43 @@
         <v>3</v>
       </c>
       <c r="Y3">
-        <v>37.45</v>
+        <v>33.59</v>
       </c>
       <c r="Z3">
-        <v>-4.44</v>
+        <v>-7.66</v>
       </c>
       <c r="AA3">
-        <v>2.84</v>
+        <v>0.74</v>
       </c>
       <c r="AB3">
-        <v>-7.28</v>
+        <v>-8.4</v>
       </c>
       <c r="AC3">
         <v>2.03</v>
       </c>
       <c r="AD3">
-        <v>2.19</v>
+        <v>1.94</v>
       </c>
       <c r="AE3">
-        <v>18.59</v>
+        <v>18.79</v>
       </c>
       <c r="AF3">
-        <v>-80.68000000000001</v>
+        <v>-58.37</v>
       </c>
       <c r="AG3">
-        <v>470.07</v>
+        <v>473.08</v>
       </c>
       <c r="AH3">
-        <v>366.62</v>
+        <v>360.72</v>
       </c>
       <c r="AI3">
-        <v>438.11</v>
+        <v>426.76</v>
       </c>
       <c r="AJ3" t="s">
         <v>45</v>
       </c>
       <c r="AK3">
-        <v>42.69</v>
+        <v>44.82</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1114,10 +1114,10 @@
         <v>42</v>
       </c>
       <c r="C4">
-        <v>372.35</v>
+        <v>366.05</v>
       </c>
       <c r="D4">
-        <v>-1.13</v>
+        <v>-1.69</v>
       </c>
       <c r="E4">
         <v>534</v>
@@ -1126,46 +1126,46 @@
         <v>344.7</v>
       </c>
       <c r="G4">
-        <v>-30.27</v>
+        <v>-31.45</v>
       </c>
       <c r="H4">
-        <v>8.02</v>
+        <v>6.19</v>
       </c>
       <c r="I4">
-        <v>-1.44</v>
+        <v>-3.58</v>
       </c>
       <c r="J4">
-        <v>-7.5</v>
+        <v>-9.07</v>
       </c>
       <c r="K4">
-        <v>-9.800000000000001</v>
+        <v>-11.65</v>
       </c>
       <c r="L4">
-        <v>-28.08</v>
+        <v>-29.17</v>
       </c>
       <c r="M4">
-        <v>-21.89</v>
+        <v>-22.33</v>
       </c>
       <c r="N4">
         <v>21</v>
       </c>
       <c r="O4">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="P4">
-        <v>376.33</v>
+        <v>373.61</v>
       </c>
       <c r="Q4">
-        <v>385.3</v>
+        <v>383.58</v>
       </c>
       <c r="R4">
-        <v>403.53</v>
+        <v>402.25</v>
       </c>
       <c r="S4">
-        <v>408.45</v>
+        <v>408.05</v>
       </c>
       <c r="T4">
-        <v>-8.84</v>
+        <v>-10.29</v>
       </c>
       <c r="U4" t="s">
         <v>43</v>
@@ -1180,43 +1180,43 @@
         <v>0</v>
       </c>
       <c r="Y4">
-        <v>28.6</v>
+        <v>24.59</v>
       </c>
       <c r="Z4">
-        <v>-8.09</v>
+        <v>-8.630000000000001</v>
       </c>
       <c r="AA4">
-        <v>-7.81</v>
+        <v>-7.98</v>
       </c>
       <c r="AB4">
-        <v>-0.28</v>
+        <v>-0.65</v>
       </c>
       <c r="AC4">
-        <v>20.64</v>
+        <v>18.92</v>
       </c>
       <c r="AD4">
-        <v>22.71</v>
+        <v>21.6</v>
       </c>
       <c r="AE4">
-        <v>10.39</v>
+        <v>10.35</v>
       </c>
       <c r="AF4">
-        <v>-44.42</v>
+        <v>-46.31</v>
       </c>
       <c r="AG4">
-        <v>401.78</v>
+        <v>400.55</v>
       </c>
       <c r="AH4">
-        <v>368.82</v>
+        <v>366.6</v>
       </c>
       <c r="AI4">
-        <v>405.81</v>
+        <v>399.57</v>
       </c>
       <c r="AJ4" t="s">
         <v>45</v>
       </c>
       <c r="AK4">
-        <v>34.07</v>
+        <v>38.11</v>
       </c>
     </row>
     <row r="5" spans="1:37">
@@ -1227,10 +1227,10 @@
         <v>42</v>
       </c>
       <c r="C5">
-        <v>909.7</v>
+        <v>878</v>
       </c>
       <c r="D5">
-        <v>-0.27</v>
+        <v>-3.48</v>
       </c>
       <c r="E5">
         <v>1069.3</v>
@@ -1239,46 +1239,46 @@
         <v>712.75</v>
       </c>
       <c r="G5">
-        <v>-14.93</v>
+        <v>-17.89</v>
       </c>
       <c r="H5">
-        <v>27.63</v>
+        <v>23.18</v>
       </c>
       <c r="I5">
-        <v>-4.84</v>
+        <v>-8.06</v>
       </c>
       <c r="J5">
-        <v>-9.289999999999999</v>
+        <v>-11.67</v>
       </c>
       <c r="K5">
-        <v>-1.57</v>
+        <v>-6.75</v>
       </c>
       <c r="L5">
-        <v>20.45</v>
+        <v>18.53</v>
       </c>
       <c r="M5">
-        <v>-3.75</v>
+        <v>-4.23</v>
       </c>
       <c r="N5">
         <v>99</v>
       </c>
       <c r="O5">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="P5">
-        <v>931.14</v>
+        <v>915.74</v>
       </c>
       <c r="Q5">
-        <v>970.54</v>
+        <v>963.61</v>
       </c>
       <c r="R5">
-        <v>998.49</v>
+        <v>995.39</v>
       </c>
       <c r="S5">
-        <v>923.26</v>
+        <v>923.48</v>
       </c>
       <c r="T5">
-        <v>-1.47</v>
+        <v>-4.92</v>
       </c>
       <c r="U5" t="s">
         <v>43</v>
@@ -1293,43 +1293,43 @@
         <v>1</v>
       </c>
       <c r="Y5">
-        <v>28.92</v>
+        <v>23.67</v>
       </c>
       <c r="Z5">
-        <v>-21.42</v>
+        <v>-25.38</v>
       </c>
       <c r="AA5">
-        <v>-14.7</v>
+        <v>-16.84</v>
       </c>
       <c r="AB5">
-        <v>-6.71</v>
+        <v>-8.539999999999999</v>
       </c>
       <c r="AC5">
         <v>0</v>
       </c>
       <c r="AD5">
-        <v>12.2</v>
+        <v>4.47</v>
       </c>
       <c r="AE5">
-        <v>21.25</v>
+        <v>22</v>
       </c>
       <c r="AF5">
-        <v>-12.88</v>
+        <v>53.11</v>
       </c>
       <c r="AG5">
-        <v>1034.95</v>
+        <v>1036.43</v>
       </c>
       <c r="AH5">
-        <v>906.14</v>
+        <v>890.8</v>
       </c>
       <c r="AI5">
-        <v>964.95</v>
+        <v>959.04</v>
       </c>
       <c r="AJ5" t="s">
         <v>45</v>
       </c>
       <c r="AK5">
-        <v>37.47</v>
+        <v>41.96</v>
       </c>
     </row>
     <row r="6" spans="1:37">
@@ -1340,49 +1340,49 @@
         <v>42</v>
       </c>
       <c r="C6">
-        <v>2.67</v>
+        <v>2.62</v>
       </c>
       <c r="D6">
-        <v>2.3</v>
+        <v>-1.87</v>
       </c>
       <c r="E6">
-        <v>3.45</v>
+        <v>3.41</v>
       </c>
       <c r="F6">
         <v>1.84</v>
       </c>
       <c r="G6">
-        <v>-22.61</v>
+        <v>-23.17</v>
       </c>
       <c r="H6">
-        <v>45.11</v>
+        <v>42.39</v>
       </c>
       <c r="I6">
-        <v>-4.3</v>
+        <v>-5.07</v>
       </c>
       <c r="J6">
-        <v>-9.800000000000001</v>
+        <v>-13.25</v>
       </c>
       <c r="K6">
-        <v>10.79</v>
+        <v>8.710000000000001</v>
       </c>
       <c r="L6">
-        <v>-23.5</v>
+        <v>-24.06</v>
       </c>
       <c r="M6">
-        <v>3.85</v>
+        <v>3.18</v>
       </c>
       <c r="N6">
         <v>40</v>
       </c>
       <c r="O6">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="P6">
-        <v>2.7</v>
+        <v>2.67</v>
       </c>
       <c r="Q6">
-        <v>2.81</v>
+        <v>2.8</v>
       </c>
       <c r="R6">
         <v>2.6</v>
@@ -1391,7 +1391,7 @@
         <v>2.66</v>
       </c>
       <c r="T6">
-        <v>0.26</v>
+        <v>-1.55</v>
       </c>
       <c r="U6" t="s">
         <v>44</v>
@@ -1403,37 +1403,37 @@
         <v>43</v>
       </c>
       <c r="X6">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y6">
-        <v>45.62</v>
+        <v>42.78</v>
       </c>
       <c r="Z6">
-        <v>0.01</v>
+        <v>-0</v>
       </c>
       <c r="AA6">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="AB6">
         <v>-0.04</v>
       </c>
       <c r="AC6">
-        <v>6.44</v>
+        <v>8.67</v>
       </c>
       <c r="AD6">
-        <v>2.15</v>
+        <v>5.04</v>
       </c>
       <c r="AE6">
         <v>0.15</v>
       </c>
       <c r="AF6">
-        <v>-15.8</v>
+        <v>28.52</v>
       </c>
       <c r="AG6">
-        <v>3</v>
+        <v>3.01</v>
       </c>
       <c r="AH6">
-        <v>2.63</v>
+        <v>2.6</v>
       </c>
       <c r="AI6">
         <v>3.06</v>
@@ -1442,7 +1442,7 @@
         <v>45</v>
       </c>
       <c r="AK6">
-        <v>25.67</v>
+        <v>26.99</v>
       </c>
     </row>
   </sheetData>
@@ -1640,13 +1640,13 @@
         <v>9</v>
       </c>
       <c r="C7" s="5">
-        <v>-11.15</v>
+        <v>-12.5</v>
       </c>
       <c r="D7" s="5">
-        <v>-12.5</v>
+        <v>-12.7</v>
       </c>
       <c r="E7" s="6">
-        <v>-1.35</v>
+        <v>-0.2</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -1657,13 +1657,13 @@
         <v>9</v>
       </c>
       <c r="C8" s="5">
-        <v>-3.35</v>
+        <v>-4.62</v>
       </c>
       <c r="D8" s="5">
-        <v>-4.62</v>
+        <v>-6.34</v>
       </c>
       <c r="E8" s="6">
-        <v>-1.27</v>
+        <v>-1.72</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -1674,13 +1674,13 @@
         <v>9</v>
       </c>
       <c r="C9" s="5">
-        <v>-6.31</v>
+        <v>-7.5</v>
       </c>
       <c r="D9" s="5">
-        <v>-7.5</v>
+        <v>-9.07</v>
       </c>
       <c r="E9" s="6">
-        <v>-1.19</v>
+        <v>-1.57</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -1691,13 +1691,13 @@
         <v>9</v>
       </c>
       <c r="C10" s="5">
-        <v>-9.140000000000001</v>
+        <v>-9.289999999999999</v>
       </c>
       <c r="D10" s="5">
-        <v>-9.289999999999999</v>
+        <v>-11.67</v>
       </c>
       <c r="E10" s="6">
-        <v>-0.15</v>
+        <v>-2.38</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -1708,13 +1708,13 @@
         <v>9</v>
       </c>
       <c r="C11" s="5">
-        <v>-13.29</v>
+        <v>-9.800000000000001</v>
       </c>
       <c r="D11" s="5">
-        <v>-9.800000000000001</v>
-      </c>
-      <c r="E11" s="7">
-        <v>3.49</v>
+        <v>-13.25</v>
+      </c>
+      <c r="E11" s="6">
+        <v>-3.45</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -1725,13 +1725,13 @@
         <v>8</v>
       </c>
       <c r="C12" s="5">
-        <v>-2.4</v>
+        <v>-4.04</v>
       </c>
       <c r="D12" s="5">
-        <v>-4.04</v>
+        <v>-4.55</v>
       </c>
       <c r="E12" s="6">
-        <v>-1.64</v>
+        <v>-0.51</v>
       </c>
     </row>
     <row r="13" spans="1:6">
@@ -1742,13 +1742,13 @@
         <v>8</v>
       </c>
       <c r="C13" s="5">
-        <v>-13.9</v>
+        <v>-16.42</v>
       </c>
       <c r="D13" s="5">
-        <v>-16.42</v>
-      </c>
-      <c r="E13" s="6">
-        <v>-2.52</v>
+        <v>-11.53</v>
+      </c>
+      <c r="E13" s="7">
+        <v>4.89</v>
       </c>
     </row>
     <row r="14" spans="1:6">
@@ -1759,13 +1759,13 @@
         <v>8</v>
       </c>
       <c r="C14" s="5">
-        <v>-0.74</v>
+        <v>-1.44</v>
       </c>
       <c r="D14" s="5">
-        <v>-1.44</v>
+        <v>-3.58</v>
       </c>
       <c r="E14" s="6">
-        <v>-0.7</v>
+        <v>-2.14</v>
       </c>
     </row>
     <row r="15" spans="1:6">
@@ -1776,13 +1776,13 @@
         <v>8</v>
       </c>
       <c r="C15" s="5">
-        <v>-5.6</v>
+        <v>-4.84</v>
       </c>
       <c r="D15" s="5">
-        <v>-4.84</v>
-      </c>
-      <c r="E15" s="7">
-        <v>0.76</v>
+        <v>-8.06</v>
+      </c>
+      <c r="E15" s="6">
+        <v>-3.22</v>
       </c>
     </row>
     <row r="16" spans="1:6">
@@ -1793,13 +1793,13 @@
         <v>8</v>
       </c>
       <c r="C16" s="5">
-        <v>-6.12</v>
+        <v>-4.3</v>
       </c>
       <c r="D16" s="5">
-        <v>-4.3</v>
-      </c>
-      <c r="E16" s="7">
-        <v>1.82</v>
+        <v>-5.07</v>
+      </c>
+      <c r="E16" s="6">
+        <v>-0.77</v>
       </c>
     </row>
     <row r="17" spans="1:5">
@@ -1810,13 +1810,13 @@
         <v>11</v>
       </c>
       <c r="C17" s="5">
-        <v>16.83</v>
+        <v>10.34</v>
       </c>
       <c r="D17" s="5">
-        <v>10.34</v>
-      </c>
-      <c r="E17" s="6">
-        <v>-6.49</v>
+        <v>10.44</v>
+      </c>
+      <c r="E17" s="7">
+        <v>0.1</v>
       </c>
     </row>
     <row r="18" spans="1:5">
@@ -1827,13 +1827,13 @@
         <v>11</v>
       </c>
       <c r="C18" s="5">
-        <v>4.05</v>
+        <v>4.12</v>
       </c>
       <c r="D18" s="5">
-        <v>4.12</v>
-      </c>
-      <c r="E18" s="7">
-        <v>0.07000000000000001</v>
+        <v>1.24</v>
+      </c>
+      <c r="E18" s="6">
+        <v>-2.88</v>
       </c>
     </row>
     <row r="19" spans="1:5">
@@ -1844,13 +1844,13 @@
         <v>11</v>
       </c>
       <c r="C19" s="5">
-        <v>-27.98</v>
+        <v>-28.08</v>
       </c>
       <c r="D19" s="5">
-        <v>-28.08</v>
+        <v>-29.17</v>
       </c>
       <c r="E19" s="6">
-        <v>-0.1</v>
+        <v>-1.09</v>
       </c>
     </row>
     <row r="20" spans="1:5">
@@ -1861,13 +1861,13 @@
         <v>11</v>
       </c>
       <c r="C20" s="5">
-        <v>24.23</v>
+        <v>20.45</v>
       </c>
       <c r="D20" s="5">
-        <v>20.45</v>
+        <v>18.53</v>
       </c>
       <c r="E20" s="6">
-        <v>-3.78</v>
+        <v>-1.92</v>
       </c>
     </row>
     <row r="21" spans="1:5">
@@ -1878,13 +1878,13 @@
         <v>11</v>
       </c>
       <c r="C21" s="5">
-        <v>-26.48</v>
+        <v>-23.5</v>
       </c>
       <c r="D21" s="5">
-        <v>-23.5</v>
-      </c>
-      <c r="E21" s="7">
-        <v>2.98</v>
+        <v>-24.06</v>
+      </c>
+      <c r="E21" s="6">
+        <v>-0.5600000000000001</v>
       </c>
     </row>
     <row r="22" spans="1:5">
@@ -1895,13 +1895,13 @@
         <v>10</v>
       </c>
       <c r="C22" s="5">
-        <v>1.09</v>
+        <v>-1.57</v>
       </c>
       <c r="D22" s="5">
-        <v>-1.57</v>
+        <v>-5.47</v>
       </c>
       <c r="E22" s="6">
-        <v>-2.66</v>
+        <v>-3.9</v>
       </c>
     </row>
     <row r="23" spans="1:5">
@@ -1912,13 +1912,13 @@
         <v>10</v>
       </c>
       <c r="C23" s="5">
-        <v>-4.77</v>
+        <v>-7.21</v>
       </c>
       <c r="D23" s="5">
-        <v>-7.21</v>
+        <v>-9.56</v>
       </c>
       <c r="E23" s="6">
-        <v>-2.44</v>
+        <v>-2.35</v>
       </c>
     </row>
     <row r="24" spans="1:5">
@@ -1929,13 +1929,13 @@
         <v>10</v>
       </c>
       <c r="C24" s="5">
-        <v>-9.42</v>
+        <v>-9.800000000000001</v>
       </c>
       <c r="D24" s="5">
-        <v>-9.800000000000001</v>
+        <v>-11.65</v>
       </c>
       <c r="E24" s="6">
-        <v>-0.38</v>
+        <v>-1.85</v>
       </c>
     </row>
     <row r="25" spans="1:5">
@@ -1946,13 +1946,13 @@
         <v>10</v>
       </c>
       <c r="C25" s="5">
-        <v>-0.35</v>
+        <v>-1.57</v>
       </c>
       <c r="D25" s="5">
-        <v>-1.57</v>
+        <v>-6.75</v>
       </c>
       <c r="E25" s="6">
-        <v>-1.22</v>
+        <v>-5.18</v>
       </c>
     </row>
     <row r="26" spans="1:5">
@@ -1963,13 +1963,13 @@
         <v>10</v>
       </c>
       <c r="C26" s="5">
-        <v>11.06</v>
+        <v>10.79</v>
       </c>
       <c r="D26" s="5">
-        <v>10.79</v>
+        <v>8.710000000000001</v>
       </c>
       <c r="E26" s="6">
-        <v>-0.27</v>
+        <v>-2.08</v>
       </c>
     </row>
     <row r="27" spans="1:5">
@@ -1980,13 +1980,13 @@
         <v>6</v>
       </c>
       <c r="C27" s="5">
-        <v>-23.66</v>
+        <v>-25.51</v>
       </c>
       <c r="D27" s="5">
-        <v>-25.51</v>
+        <v>-26.36</v>
       </c>
       <c r="E27" s="6">
-        <v>-1.85</v>
+        <v>-0.85</v>
       </c>
     </row>
     <row r="28" spans="1:5">
@@ -1997,13 +1997,13 @@
         <v>6</v>
       </c>
       <c r="C28" s="5">
-        <v>-15.8</v>
+        <v>-16.91</v>
       </c>
       <c r="D28" s="5">
-        <v>-16.91</v>
+        <v>-20.28</v>
       </c>
       <c r="E28" s="6">
-        <v>-1.11</v>
+        <v>-3.37</v>
       </c>
     </row>
     <row r="29" spans="1:5">
@@ -2014,13 +2014,13 @@
         <v>6</v>
       </c>
       <c r="C29" s="5">
-        <v>-29.48</v>
+        <v>-30.27</v>
       </c>
       <c r="D29" s="5">
-        <v>-30.27</v>
+        <v>-31.45</v>
       </c>
       <c r="E29" s="6">
-        <v>-0.79</v>
+        <v>-1.18</v>
       </c>
     </row>
     <row r="30" spans="1:5">
@@ -2031,13 +2031,13 @@
         <v>6</v>
       </c>
       <c r="C30" s="5">
-        <v>-14.69</v>
+        <v>-14.93</v>
       </c>
       <c r="D30" s="5">
-        <v>-14.93</v>
+        <v>-17.89</v>
       </c>
       <c r="E30" s="6">
-        <v>-0.24</v>
+        <v>-2.96</v>
       </c>
     </row>
     <row r="31" spans="1:5">
@@ -2048,13 +2048,13 @@
         <v>6</v>
       </c>
       <c r="C31" s="5">
-        <v>-25.21</v>
+        <v>-22.61</v>
       </c>
       <c r="D31" s="5">
-        <v>-22.61</v>
-      </c>
-      <c r="E31" s="7">
-        <v>2.6</v>
+        <v>-23.17</v>
+      </c>
+      <c r="E31" s="6">
+        <v>-0.5600000000000001</v>
       </c>
     </row>
     <row r="32" spans="1:5">
@@ -2065,13 +2065,13 @@
         <v>2</v>
       </c>
       <c r="C32" s="5">
-        <v>159.08</v>
+        <v>155.22</v>
       </c>
       <c r="D32" s="5">
-        <v>155.22</v>
+        <v>153.44</v>
       </c>
       <c r="E32" s="6">
-        <v>-3.86</v>
+        <v>-1.78</v>
       </c>
     </row>
     <row r="33" spans="1:5">
@@ -2082,13 +2082,13 @@
         <v>2</v>
       </c>
       <c r="C33" s="5">
-        <v>384.1</v>
+        <v>379</v>
       </c>
       <c r="D33" s="5">
-        <v>379</v>
+        <v>363.65</v>
       </c>
       <c r="E33" s="6">
-        <v>-5.1</v>
+        <v>-15.35</v>
       </c>
     </row>
     <row r="34" spans="1:5">
@@ -2099,13 +2099,13 @@
         <v>2</v>
       </c>
       <c r="C34" s="5">
-        <v>376.6</v>
+        <v>372.35</v>
       </c>
       <c r="D34" s="5">
-        <v>372.35</v>
+        <v>366.05</v>
       </c>
       <c r="E34" s="6">
-        <v>-4.25</v>
+        <v>-6.3</v>
       </c>
     </row>
     <row r="35" spans="1:5">
@@ -2116,13 +2116,13 @@
         <v>2</v>
       </c>
       <c r="C35" s="5">
-        <v>912.2</v>
+        <v>909.7</v>
       </c>
       <c r="D35" s="5">
-        <v>909.7</v>
+        <v>878</v>
       </c>
       <c r="E35" s="6">
-        <v>-2.5</v>
+        <v>-31.7</v>
       </c>
     </row>
     <row r="36" spans="1:5">
@@ -2133,13 +2133,13 @@
         <v>2</v>
       </c>
       <c r="C36" s="5">
-        <v>2.61</v>
+        <v>2.67</v>
       </c>
       <c r="D36" s="5">
-        <v>2.67</v>
-      </c>
-      <c r="E36" s="7">
-        <v>0.06</v>
+        <v>2.62</v>
+      </c>
+      <c r="E36" s="6">
+        <v>-0.05</v>
       </c>
     </row>
     <row r="37" spans="1:5">
@@ -2150,13 +2150,13 @@
         <v>24</v>
       </c>
       <c r="C37" s="5">
-        <v>40.55</v>
+        <v>35.98</v>
       </c>
       <c r="D37" s="5">
-        <v>35.98</v>
+        <v>34.07</v>
       </c>
       <c r="E37" s="6">
-        <v>-4.57</v>
+        <v>-1.91</v>
       </c>
     </row>
     <row r="38" spans="1:5">
@@ -2167,13 +2167,13 @@
         <v>24</v>
       </c>
       <c r="C38" s="5">
-        <v>38.82</v>
+        <v>37.45</v>
       </c>
       <c r="D38" s="5">
-        <v>37.45</v>
+        <v>33.59</v>
       </c>
       <c r="E38" s="6">
-        <v>-1.37</v>
+        <v>-3.86</v>
       </c>
     </row>
     <row r="39" spans="1:5">
@@ -2184,13 +2184,13 @@
         <v>24</v>
       </c>
       <c r="C39" s="5">
-        <v>31.86</v>
+        <v>28.6</v>
       </c>
       <c r="D39" s="5">
-        <v>28.6</v>
+        <v>24.59</v>
       </c>
       <c r="E39" s="6">
-        <v>-3.26</v>
+        <v>-4.01</v>
       </c>
     </row>
     <row r="40" spans="1:5">
@@ -2201,13 +2201,13 @@
         <v>24</v>
       </c>
       <c r="C40" s="5">
-        <v>29.4</v>
+        <v>28.92</v>
       </c>
       <c r="D40" s="5">
-        <v>28.92</v>
+        <v>23.67</v>
       </c>
       <c r="E40" s="6">
-        <v>-0.48</v>
+        <v>-5.25</v>
       </c>
     </row>
     <row r="41" spans="1:5">
@@ -2218,13 +2218,13 @@
         <v>24</v>
       </c>
       <c r="C41" s="5">
-        <v>41.28</v>
+        <v>45.62</v>
       </c>
       <c r="D41" s="5">
-        <v>45.62</v>
-      </c>
-      <c r="E41" s="7">
-        <v>4.34</v>
+        <v>42.78</v>
+      </c>
+      <c r="E41" s="6">
+        <v>-2.84</v>
       </c>
     </row>
     <row r="42" spans="1:5">
@@ -2235,13 +2235,13 @@
         <v>31</v>
       </c>
       <c r="C42" s="5">
-        <v>-16.5</v>
+        <v>2.25</v>
       </c>
       <c r="D42" s="5">
-        <v>2.25</v>
+        <v>20.98</v>
       </c>
       <c r="E42" s="7">
-        <v>18.75</v>
+        <v>18.73</v>
       </c>
     </row>
     <row r="43" spans="1:5">
@@ -2252,13 +2252,13 @@
         <v>31</v>
       </c>
       <c r="C43" s="5">
-        <v>-79.73999999999999</v>
+        <v>-80.68000000000001</v>
       </c>
       <c r="D43" s="5">
-        <v>-80.68000000000001</v>
-      </c>
-      <c r="E43" s="6">
-        <v>-0.9399999999999999</v>
+        <v>-58.37</v>
+      </c>
+      <c r="E43" s="7">
+        <v>22.31</v>
       </c>
     </row>
     <row r="44" spans="1:5">
@@ -2269,13 +2269,13 @@
         <v>31</v>
       </c>
       <c r="C44" s="5">
-        <v>-26.47</v>
+        <v>-44.42</v>
       </c>
       <c r="D44" s="5">
-        <v>-44.42</v>
+        <v>-46.31</v>
       </c>
       <c r="E44" s="6">
-        <v>-17.95</v>
+        <v>-1.89</v>
       </c>
     </row>
     <row r="45" spans="1:5">
@@ -2286,13 +2286,13 @@
         <v>31</v>
       </c>
       <c r="C45" s="5">
-        <v>-30.28</v>
+        <v>-12.88</v>
       </c>
       <c r="D45" s="5">
-        <v>-12.88</v>
+        <v>53.11</v>
       </c>
       <c r="E45" s="7">
-        <v>17.4</v>
+        <v>65.98999999999999</v>
       </c>
     </row>
     <row r="46" spans="1:5">
@@ -2303,13 +2303,13 @@
         <v>31</v>
       </c>
       <c r="C46" s="5">
-        <v>9.380000000000001</v>
+        <v>-15.8</v>
       </c>
       <c r="D46" s="5">
-        <v>-15.8</v>
-      </c>
-      <c r="E46" s="6">
-        <v>-25.18</v>
+        <v>28.52</v>
+      </c>
+      <c r="E46" s="7">
+        <v>44.32</v>
       </c>
     </row>
   </sheetData>
@@ -2368,22 +2368,22 @@
         <v>42</v>
       </c>
       <c r="B2" s="10">
-        <v>49.92</v>
+        <v>41.92</v>
       </c>
       <c r="C2" s="11">
         <v>5</v>
       </c>
       <c r="D2" s="10">
-        <v>35.3</v>
+        <v>31.7</v>
       </c>
       <c r="E2" s="10">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="F2" s="10">
-        <v>-8.699999999999999</v>
+        <v>-10.6</v>
       </c>
       <c r="G2" s="10">
-        <v>-1.9</v>
+        <v>-4.9</v>
       </c>
       <c r="H2" s="10">
         <v>59.8</v>
@@ -2508,19 +2508,19 @@
     </row>
     <row r="2" spans="1:5">
       <c r="A2" s="13">
-        <v>0.2153</v>
+        <v>0.2131</v>
       </c>
       <c r="B2" s="13">
-        <v>0.0863</v>
+        <v>0.0755</v>
       </c>
       <c r="C2" s="13">
-        <v>0.0385</v>
+        <v>0.0318</v>
       </c>
       <c r="D2" s="13">
-        <v>-0.0375</v>
+        <v>-0.0423</v>
       </c>
       <c r="E2" s="13">
-        <v>-0.2189</v>
+        <v>-0.2233</v>
       </c>
     </row>
   </sheetData>

--- a/HINDUJA_GROUP_Technical_Metrics.xlsx
+++ b/HINDUJA_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="207" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="224" uniqueCount="73">
   <si>
     <t>Symbol</t>
   </si>
@@ -163,7 +163,43 @@
     <t>▶  SIGNAL EVENTS (vs Previous Run)</t>
   </si>
   <si>
-    <t>No signal events detected since last run.</t>
+    <t>Signal</t>
+  </si>
+  <si>
+    <t>Change</t>
+  </si>
+  <si>
+    <t>Direction</t>
+  </si>
+  <si>
+    <t>Prev Value</t>
+  </si>
+  <si>
+    <t>Curr Value</t>
+  </si>
+  <si>
+    <t>RSI Oversold Recovery</t>
+  </si>
+  <si>
+    <t>24.6 → 31.2</t>
+  </si>
+  <si>
+    <t>🟢 BULLISH</t>
+  </si>
+  <si>
+    <t>24.6</t>
+  </si>
+  <si>
+    <t>31.2</t>
+  </si>
+  <si>
+    <t>23.7 → 33.3</t>
+  </si>
+  <si>
+    <t>23.7</t>
+  </si>
+  <si>
+    <t>33.3</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -249,14 +285,14 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FF006100"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FF9C0006"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -289,13 +325,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -365,14 +401,15 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -888,10 +925,10 @@
         <v>42</v>
       </c>
       <c r="C2">
-        <v>153.44</v>
+        <v>154.19</v>
       </c>
       <c r="D2">
-        <v>-1.15</v>
+        <v>0.49</v>
       </c>
       <c r="E2">
         <v>208.37</v>
@@ -900,46 +937,46 @@
         <v>131.36</v>
       </c>
       <c r="G2">
-        <v>-26.36</v>
+        <v>-26</v>
       </c>
       <c r="H2">
-        <v>16.81</v>
+        <v>17.38</v>
       </c>
       <c r="I2">
-        <v>-4.55</v>
+        <v>-5.34</v>
       </c>
       <c r="J2">
-        <v>-12.7</v>
+        <v>-12.21</v>
       </c>
       <c r="K2">
-        <v>-5.47</v>
+        <v>-6.4</v>
       </c>
       <c r="L2">
-        <v>10.44</v>
+        <v>12.42</v>
       </c>
       <c r="M2">
-        <v>21.31</v>
+        <v>20.61</v>
       </c>
       <c r="N2">
         <v>79</v>
       </c>
       <c r="O2">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="P2">
-        <v>157.59</v>
+        <v>155.85</v>
       </c>
       <c r="Q2">
-        <v>162.89</v>
+        <v>162.08</v>
       </c>
       <c r="R2">
-        <v>166.84</v>
+        <v>166.85</v>
       </c>
       <c r="S2">
-        <v>169.94</v>
+        <v>169.93</v>
       </c>
       <c r="T2">
-        <v>-9.710000000000001</v>
+        <v>-9.26</v>
       </c>
       <c r="U2" t="s">
         <v>43</v>
@@ -954,34 +991,34 @@
         <v>0</v>
       </c>
       <c r="Y2">
-        <v>34.07</v>
+        <v>35.62</v>
       </c>
       <c r="Z2">
-        <v>-3.54</v>
+        <v>-3.72</v>
       </c>
       <c r="AA2">
-        <v>-2.62</v>
+        <v>-2.84</v>
       </c>
       <c r="AB2">
-        <v>-0.92</v>
+        <v>-0.88</v>
       </c>
       <c r="AC2">
-        <v>41.8</v>
+        <v>35.85</v>
       </c>
       <c r="AD2">
-        <v>48.72</v>
+        <v>40.93</v>
       </c>
       <c r="AE2">
-        <v>4.12</v>
+        <v>4.03</v>
       </c>
       <c r="AF2">
-        <v>20.98</v>
+        <v>47.87</v>
       </c>
       <c r="AG2">
-        <v>173.91</v>
+        <v>173.13</v>
       </c>
       <c r="AH2">
-        <v>151.88</v>
+        <v>151.02</v>
       </c>
       <c r="AI2">
         <v>166.34</v>
@@ -990,7 +1027,7 @@
         <v>45</v>
       </c>
       <c r="AK2">
-        <v>39.95</v>
+        <v>41.63</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1001,10 +1038,10 @@
         <v>42</v>
       </c>
       <c r="C3">
-        <v>363.65</v>
+        <v>362.45</v>
       </c>
       <c r="D3">
-        <v>-4.05</v>
+        <v>-0.33</v>
       </c>
       <c r="E3">
         <v>456.15</v>
@@ -1013,46 +1050,46 @@
         <v>225</v>
       </c>
       <c r="G3">
-        <v>-20.28</v>
+        <v>-20.54</v>
       </c>
       <c r="H3">
-        <v>61.62</v>
+        <v>61.09</v>
       </c>
       <c r="I3">
-        <v>-11.53</v>
+        <v>-7.71</v>
       </c>
       <c r="J3">
-        <v>-6.34</v>
+        <v>-7.66</v>
       </c>
       <c r="K3">
-        <v>-9.56</v>
+        <v>-9.460000000000001</v>
       </c>
       <c r="L3">
-        <v>1.24</v>
+        <v>1.4</v>
       </c>
       <c r="M3">
-        <v>7.55</v>
+        <v>7.83</v>
       </c>
       <c r="N3">
         <v>60</v>
       </c>
       <c r="O3">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="P3">
-        <v>379.95</v>
+        <v>373.89</v>
       </c>
       <c r="Q3">
-        <v>416.9</v>
+        <v>415.66</v>
       </c>
       <c r="R3">
-        <v>409.17</v>
+        <v>408.43</v>
       </c>
       <c r="S3">
-        <v>337.51</v>
+        <v>337.86</v>
       </c>
       <c r="T3">
-        <v>7.75</v>
+        <v>7.28</v>
       </c>
       <c r="U3" t="s">
         <v>44</v>
@@ -1067,43 +1104,43 @@
         <v>3</v>
       </c>
       <c r="Y3">
-        <v>33.59</v>
+        <v>33.3</v>
       </c>
       <c r="Z3">
-        <v>-7.66</v>
+        <v>-10.19</v>
       </c>
       <c r="AA3">
-        <v>0.74</v>
+        <v>-1.44</v>
       </c>
       <c r="AB3">
-        <v>-8.4</v>
+        <v>-8.75</v>
       </c>
       <c r="AC3">
-        <v>2.03</v>
+        <v>0.26</v>
       </c>
       <c r="AD3">
-        <v>1.94</v>
+        <v>1.44</v>
       </c>
       <c r="AE3">
-        <v>18.79</v>
+        <v>18.16</v>
       </c>
       <c r="AF3">
-        <v>-58.37</v>
+        <v>-87.91</v>
       </c>
       <c r="AG3">
-        <v>473.08</v>
+        <v>475.57</v>
       </c>
       <c r="AH3">
-        <v>360.72</v>
+        <v>355.74</v>
       </c>
       <c r="AI3">
-        <v>426.76</v>
+        <v>420.1</v>
       </c>
       <c r="AJ3" t="s">
         <v>45</v>
       </c>
       <c r="AK3">
-        <v>44.82</v>
+        <v>46.66</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1114,10 +1151,10 @@
         <v>42</v>
       </c>
       <c r="C4">
-        <v>366.05</v>
+        <v>370.05</v>
       </c>
       <c r="D4">
-        <v>-1.69</v>
+        <v>1.09</v>
       </c>
       <c r="E4">
         <v>534</v>
@@ -1126,46 +1163,46 @@
         <v>344.7</v>
       </c>
       <c r="G4">
-        <v>-31.45</v>
+        <v>-30.7</v>
       </c>
       <c r="H4">
-        <v>6.19</v>
+        <v>7.35</v>
       </c>
       <c r="I4">
-        <v>-3.58</v>
+        <v>-2.23</v>
       </c>
       <c r="J4">
-        <v>-9.07</v>
+        <v>-7.61</v>
       </c>
       <c r="K4">
-        <v>-11.65</v>
+        <v>-11.76</v>
       </c>
       <c r="L4">
-        <v>-29.17</v>
+        <v>-27.71</v>
       </c>
       <c r="M4">
-        <v>-22.33</v>
+        <v>-22.17</v>
       </c>
       <c r="N4">
         <v>21</v>
       </c>
       <c r="O4">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="P4">
-        <v>373.61</v>
+        <v>371.92</v>
       </c>
       <c r="Q4">
-        <v>383.58</v>
+        <v>382.39</v>
       </c>
       <c r="R4">
-        <v>402.25</v>
+        <v>401.04</v>
       </c>
       <c r="S4">
-        <v>408.05</v>
+        <v>407.66</v>
       </c>
       <c r="T4">
-        <v>-10.29</v>
+        <v>-9.23</v>
       </c>
       <c r="U4" t="s">
         <v>43</v>
@@ -1180,34 +1217,34 @@
         <v>0</v>
       </c>
       <c r="Y4">
-        <v>24.59</v>
+        <v>31.19</v>
       </c>
       <c r="Z4">
         <v>-8.630000000000001</v>
       </c>
       <c r="AA4">
-        <v>-7.98</v>
+        <v>-8.109999999999999</v>
       </c>
       <c r="AB4">
-        <v>-0.65</v>
+        <v>-0.52</v>
       </c>
       <c r="AC4">
-        <v>18.92</v>
+        <v>24.41</v>
       </c>
       <c r="AD4">
-        <v>21.6</v>
+        <v>21.32</v>
       </c>
       <c r="AE4">
-        <v>10.35</v>
+        <v>10.39</v>
       </c>
       <c r="AF4">
-        <v>-46.31</v>
+        <v>-2.69</v>
       </c>
       <c r="AG4">
-        <v>400.55</v>
+        <v>399.69</v>
       </c>
       <c r="AH4">
-        <v>366.6</v>
+        <v>365.09</v>
       </c>
       <c r="AI4">
         <v>399.57</v>
@@ -1216,7 +1253,7 @@
         <v>45</v>
       </c>
       <c r="AK4">
-        <v>38.11</v>
+        <v>39.19</v>
       </c>
     </row>
     <row r="5" spans="1:37">
@@ -1227,10 +1264,10 @@
         <v>42</v>
       </c>
       <c r="C5">
-        <v>878</v>
+        <v>901.4</v>
       </c>
       <c r="D5">
-        <v>-3.48</v>
+        <v>2.67</v>
       </c>
       <c r="E5">
         <v>1069.3</v>
@@ -1239,46 +1276,46 @@
         <v>712.75</v>
       </c>
       <c r="G5">
-        <v>-17.89</v>
+        <v>-15.7</v>
       </c>
       <c r="H5">
-        <v>23.18</v>
+        <v>26.47</v>
       </c>
       <c r="I5">
-        <v>-8.06</v>
+        <v>-6.04</v>
       </c>
       <c r="J5">
-        <v>-11.67</v>
+        <v>-11.33</v>
       </c>
       <c r="K5">
-        <v>-6.75</v>
+        <v>-4.46</v>
       </c>
       <c r="L5">
-        <v>18.53</v>
+        <v>21.69</v>
       </c>
       <c r="M5">
-        <v>-4.23</v>
+        <v>-3.53</v>
       </c>
       <c r="N5">
         <v>99</v>
       </c>
       <c r="O5">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="P5">
-        <v>915.74</v>
+        <v>904.16</v>
       </c>
       <c r="Q5">
-        <v>963.61</v>
+        <v>959.0599999999999</v>
       </c>
       <c r="R5">
-        <v>995.39</v>
+        <v>992.15</v>
       </c>
       <c r="S5">
-        <v>923.48</v>
+        <v>923.8099999999999</v>
       </c>
       <c r="T5">
-        <v>-4.92</v>
+        <v>-2.43</v>
       </c>
       <c r="U5" t="s">
         <v>43</v>
@@ -1293,34 +1330,34 @@
         <v>1</v>
       </c>
       <c r="Y5">
-        <v>23.67</v>
+        <v>33.3</v>
       </c>
       <c r="Z5">
-        <v>-25.38</v>
+        <v>-26.32</v>
       </c>
       <c r="AA5">
-        <v>-16.84</v>
+        <v>-18.74</v>
       </c>
       <c r="AB5">
-        <v>-8.539999999999999</v>
+        <v>-7.59</v>
       </c>
       <c r="AC5">
-        <v>0</v>
+        <v>14.41</v>
       </c>
       <c r="AD5">
-        <v>4.47</v>
+        <v>4.8</v>
       </c>
       <c r="AE5">
-        <v>22</v>
+        <v>22.15</v>
       </c>
       <c r="AF5">
-        <v>53.11</v>
+        <v>10.77</v>
       </c>
       <c r="AG5">
-        <v>1036.43</v>
+        <v>1035.56</v>
       </c>
       <c r="AH5">
-        <v>890.8</v>
+        <v>882.55</v>
       </c>
       <c r="AI5">
         <v>959.04</v>
@@ -1329,7 +1366,7 @@
         <v>45</v>
       </c>
       <c r="AK5">
-        <v>41.96</v>
+        <v>45.85</v>
       </c>
     </row>
     <row r="6" spans="1:37">
@@ -1340,58 +1377,58 @@
         <v>42</v>
       </c>
       <c r="C6">
-        <v>2.62</v>
+        <v>2.61</v>
       </c>
       <c r="D6">
-        <v>-1.87</v>
+        <v>-0.38</v>
       </c>
       <c r="E6">
-        <v>3.41</v>
+        <v>3.38</v>
       </c>
       <c r="F6">
         <v>1.84</v>
       </c>
       <c r="G6">
-        <v>-23.17</v>
+        <v>-22.78</v>
       </c>
       <c r="H6">
-        <v>42.39</v>
+        <v>41.85</v>
       </c>
       <c r="I6">
-        <v>-5.07</v>
+        <v>-5.43</v>
       </c>
       <c r="J6">
-        <v>-13.25</v>
+        <v>-7.77</v>
       </c>
       <c r="K6">
-        <v>8.710000000000001</v>
+        <v>7.41</v>
       </c>
       <c r="L6">
-        <v>-24.06</v>
+        <v>-23.46</v>
       </c>
       <c r="M6">
-        <v>3.18</v>
+        <v>2.74</v>
       </c>
       <c r="N6">
         <v>40</v>
       </c>
       <c r="O6">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="P6">
-        <v>2.67</v>
+        <v>2.64</v>
       </c>
       <c r="Q6">
-        <v>2.8</v>
+        <v>2.79</v>
       </c>
       <c r="R6">
-        <v>2.6</v>
+        <v>2.61</v>
       </c>
       <c r="S6">
         <v>2.66</v>
       </c>
       <c r="T6">
-        <v>-1.55</v>
+        <v>-1.86</v>
       </c>
       <c r="U6" t="s">
         <v>44</v>
@@ -1406,43 +1443,43 @@
         <v>1</v>
       </c>
       <c r="Y6">
-        <v>42.78</v>
+        <v>42.22</v>
       </c>
       <c r="Z6">
-        <v>-0</v>
+        <v>-0.01</v>
       </c>
       <c r="AA6">
-        <v>0.04</v>
+        <v>0.03</v>
       </c>
       <c r="AB6">
         <v>-0.04</v>
       </c>
       <c r="AC6">
-        <v>8.67</v>
+        <v>10.22</v>
       </c>
       <c r="AD6">
-        <v>5.04</v>
+        <v>8.44</v>
       </c>
       <c r="AE6">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="AF6">
-        <v>28.52</v>
+        <v>-44.09</v>
       </c>
       <c r="AG6">
         <v>3.01</v>
       </c>
       <c r="AH6">
-        <v>2.6</v>
+        <v>2.57</v>
       </c>
       <c r="AI6">
-        <v>3.06</v>
+        <v>3.05</v>
       </c>
       <c r="AJ6" t="s">
         <v>45</v>
       </c>
       <c r="AK6">
-        <v>26.99</v>
+        <v>28.14</v>
       </c>
     </row>
   </sheetData>
@@ -1583,7 +1620,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F46"/>
+  <dimension ref="A1:F47"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.7109375" customWidth="1"/>
@@ -1603,719 +1640,774 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="3" t="s">
         <v>47</v>
       </c>
-    </row>
-    <row r="5" spans="1:6">
-      <c r="A5" s="2" t="s">
+      <c r="C2" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="B5" s="2"/>
-      <c r="C5" s="2"/>
-      <c r="D5" s="2"/>
-      <c r="E5" s="2"/>
+      <c r="D2" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
+      <c r="A3" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6">
+      <c r="A4" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="F4" s="4" t="s">
+        <v>59</v>
+      </c>
     </row>
     <row r="6" spans="1:6">
-      <c r="A6" s="4" t="s">
-        <v>0</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>49</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="D6" s="4" t="s">
-        <v>51</v>
-      </c>
-      <c r="E6" s="4" t="s">
-        <v>52</v>
-      </c>
+      <c r="A6" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="B6" s="2"/>
+      <c r="C6" s="2"/>
+      <c r="D6" s="2"/>
+      <c r="E6" s="2"/>
     </row>
     <row r="7" spans="1:6">
       <c r="A7" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6">
+      <c r="A8" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B7" s="3" t="s">
+      <c r="B8" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C7" s="5">
-        <v>-12.5</v>
-      </c>
-      <c r="D7" s="5">
+      <c r="C8" s="6">
         <v>-12.7</v>
       </c>
-      <c r="E7" s="6">
-        <v>-0.2</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6">
-      <c r="A8" s="3" t="s">
+      <c r="D8" s="6">
+        <v>-12.21</v>
+      </c>
+      <c r="E8" s="7">
+        <v>0.49</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="A9" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B8" s="3" t="s">
+      <c r="B9" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C8" s="5">
-        <v>-4.62</v>
-      </c>
-      <c r="D8" s="5">
+      <c r="C9" s="6">
         <v>-6.34</v>
       </c>
-      <c r="E8" s="6">
-        <v>-1.72</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
-      <c r="A9" s="3" t="s">
+      <c r="D9" s="6">
+        <v>-7.66</v>
+      </c>
+      <c r="E9" s="8">
+        <v>-1.32</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="A10" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B9" s="3" t="s">
+      <c r="B10" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C9" s="5">
-        <v>-7.5</v>
-      </c>
-      <c r="D9" s="5">
+      <c r="C10" s="6">
         <v>-9.07</v>
       </c>
-      <c r="E9" s="6">
-        <v>-1.57</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
-      <c r="A10" s="3" t="s">
+      <c r="D10" s="6">
+        <v>-7.61</v>
+      </c>
+      <c r="E10" s="7">
+        <v>1.46</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="A11" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="B10" s="3" t="s">
+      <c r="B11" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C10" s="5">
-        <v>-9.289999999999999</v>
-      </c>
-      <c r="D10" s="5">
+      <c r="C11" s="6">
         <v>-11.67</v>
       </c>
-      <c r="E10" s="6">
-        <v>-2.38</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
-      <c r="A11" s="3" t="s">
+      <c r="D11" s="6">
+        <v>-11.33</v>
+      </c>
+      <c r="E11" s="7">
+        <v>0.34</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6">
+      <c r="A12" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B11" s="3" t="s">
+      <c r="B12" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C11" s="5">
-        <v>-9.800000000000001</v>
-      </c>
-      <c r="D11" s="5">
+      <c r="C12" s="6">
         <v>-13.25</v>
       </c>
-      <c r="E11" s="6">
-        <v>-3.45</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
-      <c r="A12" s="3" t="s">
+      <c r="D12" s="6">
+        <v>-7.77</v>
+      </c>
+      <c r="E12" s="7">
+        <v>5.48</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6">
+      <c r="A13" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B12" s="3" t="s">
+      <c r="B13" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="C12" s="5">
-        <v>-4.04</v>
-      </c>
-      <c r="D12" s="5">
+      <c r="C13" s="6">
         <v>-4.55</v>
       </c>
-      <c r="E12" s="6">
-        <v>-0.51</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
-      <c r="A13" s="3" t="s">
+      <c r="D13" s="6">
+        <v>-5.34</v>
+      </c>
+      <c r="E13" s="8">
+        <v>-0.79</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6">
+      <c r="A14" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B13" s="3" t="s">
+      <c r="B14" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="C13" s="5">
-        <v>-16.42</v>
-      </c>
-      <c r="D13" s="5">
+      <c r="C14" s="6">
         <v>-11.53</v>
       </c>
-      <c r="E13" s="7">
-        <v>4.89</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
-      <c r="A14" s="3" t="s">
+      <c r="D14" s="6">
+        <v>-7.71</v>
+      </c>
+      <c r="E14" s="7">
+        <v>3.82</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6">
+      <c r="A15" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B14" s="3" t="s">
+      <c r="B15" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="C14" s="5">
-        <v>-1.44</v>
-      </c>
-      <c r="D14" s="5">
+      <c r="C15" s="6">
         <v>-3.58</v>
       </c>
-      <c r="E14" s="6">
-        <v>-2.14</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6">
-      <c r="A15" s="3" t="s">
+      <c r="D15" s="6">
+        <v>-2.23</v>
+      </c>
+      <c r="E15" s="7">
+        <v>1.35</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6">
+      <c r="A16" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="B15" s="3" t="s">
+      <c r="B16" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="C15" s="5">
-        <v>-4.84</v>
-      </c>
-      <c r="D15" s="5">
+      <c r="C16" s="6">
         <v>-8.06</v>
       </c>
-      <c r="E15" s="6">
-        <v>-3.22</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
-      <c r="A16" s="3" t="s">
+      <c r="D16" s="6">
+        <v>-6.04</v>
+      </c>
+      <c r="E16" s="7">
+        <v>2.02</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B16" s="3" t="s">
+      <c r="B17" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="C16" s="5">
-        <v>-4.3</v>
-      </c>
-      <c r="D16" s="5">
+      <c r="C17" s="6">
         <v>-5.07</v>
       </c>
-      <c r="E16" s="6">
-        <v>-0.77</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5">
-      <c r="A17" s="3" t="s">
+      <c r="D17" s="6">
+        <v>-5.43</v>
+      </c>
+      <c r="E17" s="8">
+        <v>-0.36</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B17" s="3" t="s">
+      <c r="B18" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="C17" s="5">
-        <v>10.34</v>
-      </c>
-      <c r="D17" s="5">
+      <c r="C18" s="6">
         <v>10.44</v>
       </c>
-      <c r="E17" s="7">
+      <c r="D18" s="6">
+        <v>12.42</v>
+      </c>
+      <c r="E18" s="7">
+        <v>1.98</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B19" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C19" s="6">
+        <v>1.24</v>
+      </c>
+      <c r="D19" s="6">
+        <v>1.4</v>
+      </c>
+      <c r="E19" s="7">
+        <v>0.16</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B20" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C20" s="6">
+        <v>-29.17</v>
+      </c>
+      <c r="D20" s="6">
+        <v>-27.71</v>
+      </c>
+      <c r="E20" s="7">
+        <v>1.46</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B21" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C21" s="6">
+        <v>18.53</v>
+      </c>
+      <c r="D21" s="6">
+        <v>21.69</v>
+      </c>
+      <c r="E21" s="7">
+        <v>3.16</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B22" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C22" s="6">
+        <v>-24.06</v>
+      </c>
+      <c r="D22" s="6">
+        <v>-23.46</v>
+      </c>
+      <c r="E22" s="7">
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B23" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C23" s="6">
+        <v>-5.47</v>
+      </c>
+      <c r="D23" s="6">
+        <v>-6.4</v>
+      </c>
+      <c r="E23" s="8">
+        <v>-0.93</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5">
+      <c r="A24" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B24" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C24" s="6">
+        <v>-9.56</v>
+      </c>
+      <c r="D24" s="6">
+        <v>-9.460000000000001</v>
+      </c>
+      <c r="E24" s="7">
         <v>0.1</v>
       </c>
     </row>
-    <row r="18" spans="1:5">
-      <c r="A18" s="3" t="s">
+    <row r="25" spans="1:5">
+      <c r="A25" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B25" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C25" s="6">
+        <v>-11.65</v>
+      </c>
+      <c r="D25" s="6">
+        <v>-11.76</v>
+      </c>
+      <c r="E25" s="8">
+        <v>-0.11</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
+      <c r="A26" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B26" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C26" s="6">
+        <v>-6.75</v>
+      </c>
+      <c r="D26" s="6">
+        <v>-4.46</v>
+      </c>
+      <c r="E26" s="7">
+        <v>2.29</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5">
+      <c r="A27" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B27" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C27" s="6">
+        <v>8.710000000000001</v>
+      </c>
+      <c r="D27" s="6">
+        <v>7.41</v>
+      </c>
+      <c r="E27" s="8">
+        <v>-1.3</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5">
+      <c r="A28" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B28" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C28" s="6">
+        <v>-26.36</v>
+      </c>
+      <c r="D28" s="6">
+        <v>-26</v>
+      </c>
+      <c r="E28" s="7">
+        <v>0.36</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5">
+      <c r="A29" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B18" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C18" s="5">
-        <v>4.12</v>
-      </c>
-      <c r="D18" s="5">
-        <v>1.24</v>
-      </c>
-      <c r="E18" s="6">
-        <v>-2.88</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5">
-      <c r="A19" s="3" t="s">
+      <c r="B29" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C29" s="6">
+        <v>-20.28</v>
+      </c>
+      <c r="D29" s="6">
+        <v>-20.54</v>
+      </c>
+      <c r="E29" s="8">
+        <v>-0.26</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5">
+      <c r="A30" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B19" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C19" s="5">
-        <v>-28.08</v>
-      </c>
-      <c r="D19" s="5">
-        <v>-29.17</v>
-      </c>
-      <c r="E19" s="6">
-        <v>-1.09</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5">
-      <c r="A20" s="3" t="s">
+      <c r="B30" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C30" s="6">
+        <v>-31.45</v>
+      </c>
+      <c r="D30" s="6">
+        <v>-30.7</v>
+      </c>
+      <c r="E30" s="7">
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5">
+      <c r="A31" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="B20" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C20" s="5">
-        <v>20.45</v>
-      </c>
-      <c r="D20" s="5">
-        <v>18.53</v>
-      </c>
-      <c r="E20" s="6">
-        <v>-1.92</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5">
-      <c r="A21" s="3" t="s">
+      <c r="B31" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C31" s="6">
+        <v>-17.89</v>
+      </c>
+      <c r="D31" s="6">
+        <v>-15.7</v>
+      </c>
+      <c r="E31" s="7">
+        <v>2.19</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5">
+      <c r="A32" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B21" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C21" s="5">
-        <v>-23.5</v>
-      </c>
-      <c r="D21" s="5">
-        <v>-24.06</v>
-      </c>
-      <c r="E21" s="6">
+      <c r="B32" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C32" s="6">
+        <v>-23.17</v>
+      </c>
+      <c r="D32" s="6">
+        <v>-22.78</v>
+      </c>
+      <c r="E32" s="7">
+        <v>0.39</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5">
+      <c r="A33" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B33" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C33" s="6">
+        <v>153.44</v>
+      </c>
+      <c r="D33" s="6">
+        <v>154.19</v>
+      </c>
+      <c r="E33" s="7">
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5">
+      <c r="A34" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B34" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C34" s="6">
+        <v>363.65</v>
+      </c>
+      <c r="D34" s="6">
+        <v>362.45</v>
+      </c>
+      <c r="E34" s="8">
+        <v>-1.2</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5">
+      <c r="A35" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B35" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C35" s="6">
+        <v>366.05</v>
+      </c>
+      <c r="D35" s="6">
+        <v>370.05</v>
+      </c>
+      <c r="E35" s="7">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5">
+      <c r="A36" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B36" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C36" s="6">
+        <v>878</v>
+      </c>
+      <c r="D36" s="6">
+        <v>901.4</v>
+      </c>
+      <c r="E36" s="7">
+        <v>23.4</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5">
+      <c r="A37" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B37" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C37" s="6">
+        <v>2.62</v>
+      </c>
+      <c r="D37" s="6">
+        <v>2.61</v>
+      </c>
+      <c r="E37" s="8">
+        <v>-0.01</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5">
+      <c r="A38" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B38" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C38" s="6">
+        <v>34.07</v>
+      </c>
+      <c r="D38" s="6">
+        <v>35.62</v>
+      </c>
+      <c r="E38" s="7">
+        <v>1.55</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5">
+      <c r="A39" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B39" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C39" s="6">
+        <v>33.59</v>
+      </c>
+      <c r="D39" s="6">
+        <v>33.3</v>
+      </c>
+      <c r="E39" s="8">
+        <v>-0.29</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5">
+      <c r="A40" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B40" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C40" s="6">
+        <v>24.59</v>
+      </c>
+      <c r="D40" s="6">
+        <v>31.19</v>
+      </c>
+      <c r="E40" s="7">
+        <v>6.6</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5">
+      <c r="A41" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B41" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C41" s="6">
+        <v>23.67</v>
+      </c>
+      <c r="D41" s="6">
+        <v>33.3</v>
+      </c>
+      <c r="E41" s="7">
+        <v>9.630000000000001</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5">
+      <c r="A42" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B42" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C42" s="6">
+        <v>42.78</v>
+      </c>
+      <c r="D42" s="6">
+        <v>42.22</v>
+      </c>
+      <c r="E42" s="8">
         <v>-0.5600000000000001</v>
       </c>
     </row>
-    <row r="22" spans="1:5">
-      <c r="A22" s="3" t="s">
+    <row r="43" spans="1:5">
+      <c r="A43" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B22" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C22" s="5">
-        <v>-1.57</v>
-      </c>
-      <c r="D22" s="5">
-        <v>-5.47</v>
-      </c>
-      <c r="E22" s="6">
-        <v>-3.9</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5">
-      <c r="A23" s="3" t="s">
+      <c r="B43" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C43" s="6">
+        <v>20.98</v>
+      </c>
+      <c r="D43" s="6">
+        <v>47.87</v>
+      </c>
+      <c r="E43" s="7">
+        <v>26.89</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5">
+      <c r="A44" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B23" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C23" s="5">
-        <v>-7.21</v>
-      </c>
-      <c r="D23" s="5">
-        <v>-9.56</v>
-      </c>
-      <c r="E23" s="6">
-        <v>-2.35</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5">
-      <c r="A24" s="3" t="s">
+      <c r="B44" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C44" s="6">
+        <v>-58.37</v>
+      </c>
+      <c r="D44" s="6">
+        <v>-87.91</v>
+      </c>
+      <c r="E44" s="8">
+        <v>-29.54</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5">
+      <c r="A45" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B24" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C24" s="5">
-        <v>-9.800000000000001</v>
-      </c>
-      <c r="D24" s="5">
-        <v>-11.65</v>
-      </c>
-      <c r="E24" s="6">
-        <v>-1.85</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5">
-      <c r="A25" s="3" t="s">
+      <c r="B45" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C45" s="6">
+        <v>-46.31</v>
+      </c>
+      <c r="D45" s="6">
+        <v>-2.69</v>
+      </c>
+      <c r="E45" s="7">
+        <v>43.62</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5">
+      <c r="A46" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="B25" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C25" s="5">
-        <v>-1.57</v>
-      </c>
-      <c r="D25" s="5">
-        <v>-6.75</v>
-      </c>
-      <c r="E25" s="6">
-        <v>-5.18</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5">
-      <c r="A26" s="3" t="s">
+      <c r="B46" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C46" s="6">
+        <v>53.11</v>
+      </c>
+      <c r="D46" s="6">
+        <v>10.77</v>
+      </c>
+      <c r="E46" s="8">
+        <v>-42.34</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5">
+      <c r="A47" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B26" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C26" s="5">
-        <v>10.79</v>
-      </c>
-      <c r="D26" s="5">
-        <v>8.710000000000001</v>
-      </c>
-      <c r="E26" s="6">
-        <v>-2.08</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5">
-      <c r="A27" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B27" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C27" s="5">
-        <v>-25.51</v>
-      </c>
-      <c r="D27" s="5">
-        <v>-26.36</v>
-      </c>
-      <c r="E27" s="6">
-        <v>-0.85</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5">
-      <c r="A28" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="B28" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C28" s="5">
-        <v>-16.91</v>
-      </c>
-      <c r="D28" s="5">
-        <v>-20.28</v>
-      </c>
-      <c r="E28" s="6">
-        <v>-3.37</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5">
-      <c r="A29" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="B29" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C29" s="5">
-        <v>-30.27</v>
-      </c>
-      <c r="D29" s="5">
-        <v>-31.45</v>
-      </c>
-      <c r="E29" s="6">
-        <v>-1.18</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5">
-      <c r="A30" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="B30" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C30" s="5">
-        <v>-14.93</v>
-      </c>
-      <c r="D30" s="5">
-        <v>-17.89</v>
-      </c>
-      <c r="E30" s="6">
-        <v>-2.96</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5">
-      <c r="A31" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="B31" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C31" s="5">
-        <v>-22.61</v>
-      </c>
-      <c r="D31" s="5">
-        <v>-23.17</v>
-      </c>
-      <c r="E31" s="6">
-        <v>-0.5600000000000001</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5">
-      <c r="A32" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B32" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C32" s="5">
-        <v>155.22</v>
-      </c>
-      <c r="D32" s="5">
-        <v>153.44</v>
-      </c>
-      <c r="E32" s="6">
-        <v>-1.78</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5">
-      <c r="A33" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="B33" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C33" s="5">
-        <v>379</v>
-      </c>
-      <c r="D33" s="5">
-        <v>363.65</v>
-      </c>
-      <c r="E33" s="6">
-        <v>-15.35</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5">
-      <c r="A34" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="B34" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C34" s="5">
-        <v>372.35</v>
-      </c>
-      <c r="D34" s="5">
-        <v>366.05</v>
-      </c>
-      <c r="E34" s="6">
-        <v>-6.3</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5">
-      <c r="A35" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="B35" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C35" s="5">
-        <v>909.7</v>
-      </c>
-      <c r="D35" s="5">
-        <v>878</v>
-      </c>
-      <c r="E35" s="6">
-        <v>-31.7</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5">
-      <c r="A36" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="B36" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C36" s="5">
-        <v>2.67</v>
-      </c>
-      <c r="D36" s="5">
-        <v>2.62</v>
-      </c>
-      <c r="E36" s="6">
-        <v>-0.05</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5">
-      <c r="A37" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B37" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C37" s="5">
-        <v>35.98</v>
-      </c>
-      <c r="D37" s="5">
-        <v>34.07</v>
-      </c>
-      <c r="E37" s="6">
-        <v>-1.91</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5">
-      <c r="A38" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="B38" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C38" s="5">
-        <v>37.45</v>
-      </c>
-      <c r="D38" s="5">
-        <v>33.59</v>
-      </c>
-      <c r="E38" s="6">
-        <v>-3.86</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5">
-      <c r="A39" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="B39" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C39" s="5">
-        <v>28.6</v>
-      </c>
-      <c r="D39" s="5">
-        <v>24.59</v>
-      </c>
-      <c r="E39" s="6">
-        <v>-4.01</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5">
-      <c r="A40" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="B40" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C40" s="5">
-        <v>28.92</v>
-      </c>
-      <c r="D40" s="5">
-        <v>23.67</v>
-      </c>
-      <c r="E40" s="6">
-        <v>-5.25</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5">
-      <c r="A41" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="B41" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C41" s="5">
-        <v>45.62</v>
-      </c>
-      <c r="D41" s="5">
-        <v>42.78</v>
-      </c>
-      <c r="E41" s="6">
-        <v>-2.84</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5">
-      <c r="A42" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B42" s="3" t="s">
+      <c r="B47" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="C42" s="5">
-        <v>2.25</v>
-      </c>
-      <c r="D42" s="5">
-        <v>20.98</v>
-      </c>
-      <c r="E42" s="7">
-        <v>18.73</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5">
-      <c r="A43" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="B43" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C43" s="5">
-        <v>-80.68000000000001</v>
-      </c>
-      <c r="D43" s="5">
-        <v>-58.37</v>
-      </c>
-      <c r="E43" s="7">
-        <v>22.31</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5">
-      <c r="A44" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="B44" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C44" s="5">
-        <v>-44.42</v>
-      </c>
-      <c r="D44" s="5">
-        <v>-46.31</v>
-      </c>
-      <c r="E44" s="6">
-        <v>-1.89</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5">
-      <c r="A45" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="B45" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C45" s="5">
-        <v>-12.88</v>
-      </c>
-      <c r="D45" s="5">
-        <v>53.11</v>
-      </c>
-      <c r="E45" s="7">
-        <v>65.98999999999999</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5">
-      <c r="A46" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="B46" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C46" s="5">
-        <v>-15.8</v>
-      </c>
-      <c r="D46" s="5">
+      <c r="C47" s="6">
         <v>28.52</v>
       </c>
-      <c r="E46" s="7">
-        <v>44.32</v>
+      <c r="D47" s="6">
+        <v>-44.09</v>
+      </c>
+      <c r="E47" s="8">
+        <v>-72.61</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A5:E5"/>
+    <mergeCell ref="A6:E6"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2335,60 +2427,60 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="28" customHeight="1">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="8" t="s">
-        <v>53</v>
-      </c>
-      <c r="C1" s="8" t="s">
-        <v>54</v>
-      </c>
-      <c r="D1" s="8" t="s">
-        <v>55</v>
-      </c>
-      <c r="E1" s="8" t="s">
-        <v>56</v>
-      </c>
-      <c r="F1" s="8" t="s">
-        <v>57</v>
-      </c>
-      <c r="G1" s="8" t="s">
-        <v>58</v>
-      </c>
-      <c r="H1" s="8" t="s">
-        <v>59</v>
-      </c>
-      <c r="I1" s="8" t="s">
-        <v>60</v>
+      <c r="B1" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="C1" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="D1" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="E1" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="F1" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="G1" s="9" t="s">
+        <v>70</v>
+      </c>
+      <c r="H1" s="9" t="s">
+        <v>71</v>
+      </c>
+      <c r="I1" s="9" t="s">
+        <v>72</v>
       </c>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="9" t="s">
+      <c r="A2" s="10" t="s">
         <v>42</v>
       </c>
-      <c r="B2" s="10">
+      <c r="B2" s="11">
         <v>41.92</v>
       </c>
-      <c r="C2" s="11">
+      <c r="C2" s="12">
         <v>5</v>
       </c>
-      <c r="D2" s="10">
-        <v>31.7</v>
-      </c>
-      <c r="E2" s="10">
+      <c r="D2" s="11">
+        <v>35.1</v>
+      </c>
+      <c r="E2" s="11">
         <v>20</v>
       </c>
-      <c r="F2" s="10">
-        <v>-10.6</v>
-      </c>
-      <c r="G2" s="10">
+      <c r="F2" s="11">
+        <v>-9.300000000000001</v>
+      </c>
+      <c r="G2" s="11">
         <v>-4.9</v>
       </c>
-      <c r="H2" s="10">
+      <c r="H2" s="11">
         <v>59.8</v>
       </c>
-      <c r="I2" s="10">
+      <c r="I2" s="11">
         <v>20</v>
       </c>
     </row>
@@ -2490,37 +2582,37 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
-      <c r="A1" s="12" t="s">
+      <c r="A1" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="B1" s="12" t="s">
+      <c r="B1" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="C1" s="12" t="s">
+      <c r="C1" s="13" t="s">
         <v>41</v>
       </c>
-      <c r="D1" s="12" t="s">
+      <c r="D1" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="E1" s="12" t="s">
+      <c r="E1" s="13" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="2" spans="1:5">
-      <c r="A2" s="13">
-        <v>0.2131</v>
-      </c>
-      <c r="B2" s="13">
-        <v>0.0755</v>
-      </c>
-      <c r="C2" s="13">
-        <v>0.0318</v>
-      </c>
-      <c r="D2" s="13">
-        <v>-0.0423</v>
-      </c>
-      <c r="E2" s="13">
-        <v>-0.2233</v>
+      <c r="A2" s="14">
+        <v>0.2061</v>
+      </c>
+      <c r="B2" s="14">
+        <v>0.07829999999999999</v>
+      </c>
+      <c r="C2" s="14">
+        <v>0.0274</v>
+      </c>
+      <c r="D2" s="14">
+        <v>-0.0353</v>
+      </c>
+      <c r="E2" s="14">
+        <v>-0.2217</v>
       </c>
     </row>
   </sheetData>

--- a/HINDUJA_GROUP_Technical_Metrics.xlsx
+++ b/HINDUJA_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="224" uniqueCount="73">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="207" uniqueCount="61">
   <si>
     <t>Symbol</t>
   </si>
@@ -163,43 +163,7 @@
     <t>▶  SIGNAL EVENTS (vs Previous Run)</t>
   </si>
   <si>
-    <t>Signal</t>
-  </si>
-  <si>
-    <t>Change</t>
-  </si>
-  <si>
-    <t>Direction</t>
-  </si>
-  <si>
-    <t>Prev Value</t>
-  </si>
-  <si>
-    <t>Curr Value</t>
-  </si>
-  <si>
-    <t>RSI Oversold Recovery</t>
-  </si>
-  <si>
-    <t>24.6 → 31.2</t>
-  </si>
-  <si>
-    <t>🟢 BULLISH</t>
-  </si>
-  <si>
-    <t>24.6</t>
-  </si>
-  <si>
-    <t>31.2</t>
-  </si>
-  <si>
-    <t>23.7 → 33.3</t>
-  </si>
-  <si>
-    <t>23.7</t>
-  </si>
-  <si>
-    <t>33.3</t>
+    <t>No signal events detected since last run.</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -401,15 +365,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -925,10 +888,10 @@
         <v>42</v>
       </c>
       <c r="C2">
-        <v>154.19</v>
+        <v>150.48</v>
       </c>
       <c r="D2">
-        <v>0.49</v>
+        <v>-2.41</v>
       </c>
       <c r="E2">
         <v>208.37</v>
@@ -937,46 +900,46 @@
         <v>131.36</v>
       </c>
       <c r="G2">
-        <v>-26</v>
+        <v>-27.78</v>
       </c>
       <c r="H2">
-        <v>17.38</v>
+        <v>14.56</v>
       </c>
       <c r="I2">
-        <v>-5.34</v>
+        <v>-4.34</v>
       </c>
       <c r="J2">
-        <v>-12.21</v>
+        <v>-11.76</v>
       </c>
       <c r="K2">
-        <v>-6.4</v>
+        <v>-8.44</v>
       </c>
       <c r="L2">
-        <v>12.42</v>
+        <v>8.56</v>
       </c>
       <c r="M2">
-        <v>20.61</v>
+        <v>20.57</v>
       </c>
       <c r="N2">
         <v>79</v>
       </c>
       <c r="O2">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="P2">
-        <v>155.85</v>
+        <v>154.48</v>
       </c>
       <c r="Q2">
-        <v>162.08</v>
+        <v>161.2</v>
       </c>
       <c r="R2">
-        <v>166.85</v>
+        <v>166.8</v>
       </c>
       <c r="S2">
-        <v>169.93</v>
+        <v>169.87</v>
       </c>
       <c r="T2">
-        <v>-9.26</v>
+        <v>-11.42</v>
       </c>
       <c r="U2" t="s">
         <v>43</v>
@@ -991,43 +954,43 @@
         <v>0</v>
       </c>
       <c r="Y2">
-        <v>35.62</v>
+        <v>31.66</v>
       </c>
       <c r="Z2">
-        <v>-3.72</v>
+        <v>-4.11</v>
       </c>
       <c r="AA2">
-        <v>-2.84</v>
+        <v>-3.09</v>
       </c>
       <c r="AB2">
-        <v>-0.88</v>
+        <v>-1.02</v>
       </c>
       <c r="AC2">
-        <v>35.85</v>
+        <v>28.02</v>
       </c>
       <c r="AD2">
-        <v>40.93</v>
+        <v>35.22</v>
       </c>
       <c r="AE2">
-        <v>4.03</v>
+        <v>4.19</v>
       </c>
       <c r="AF2">
-        <v>47.87</v>
+        <v>69.59</v>
       </c>
       <c r="AG2">
-        <v>173.13</v>
+        <v>173.04</v>
       </c>
       <c r="AH2">
-        <v>151.02</v>
+        <v>149.37</v>
       </c>
       <c r="AI2">
-        <v>166.34</v>
+        <v>164.26</v>
       </c>
       <c r="AJ2" t="s">
         <v>45</v>
       </c>
       <c r="AK2">
-        <v>41.63</v>
+        <v>45.04</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1038,10 +1001,10 @@
         <v>42</v>
       </c>
       <c r="C3">
-        <v>362.45</v>
+        <v>351.65</v>
       </c>
       <c r="D3">
-        <v>-0.33</v>
+        <v>-2.98</v>
       </c>
       <c r="E3">
         <v>456.15</v>
@@ -1050,46 +1013,46 @@
         <v>225</v>
       </c>
       <c r="G3">
-        <v>-20.54</v>
+        <v>-22.91</v>
       </c>
       <c r="H3">
-        <v>61.09</v>
+        <v>56.29</v>
       </c>
       <c r="I3">
-        <v>-7.71</v>
+        <v>-7.52</v>
       </c>
       <c r="J3">
-        <v>-7.66</v>
+        <v>-9.220000000000001</v>
       </c>
       <c r="K3">
-        <v>-9.460000000000001</v>
+        <v>-12.85</v>
       </c>
       <c r="L3">
-        <v>1.4</v>
+        <v>0.03</v>
       </c>
       <c r="M3">
-        <v>7.83</v>
+        <v>7.16</v>
       </c>
       <c r="N3">
         <v>60</v>
       </c>
       <c r="O3">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="P3">
-        <v>373.89</v>
+        <v>368.17</v>
       </c>
       <c r="Q3">
-        <v>415.66</v>
+        <v>413.65</v>
       </c>
       <c r="R3">
-        <v>408.43</v>
+        <v>407.6</v>
       </c>
       <c r="S3">
-        <v>337.86</v>
+        <v>338.11</v>
       </c>
       <c r="T3">
-        <v>7.28</v>
+        <v>4.01</v>
       </c>
       <c r="U3" t="s">
         <v>44</v>
@@ -1104,43 +1067,43 @@
         <v>3</v>
       </c>
       <c r="Y3">
-        <v>33.3</v>
+        <v>30.74</v>
       </c>
       <c r="Z3">
-        <v>-10.19</v>
+        <v>-12.92</v>
       </c>
       <c r="AA3">
-        <v>-1.44</v>
+        <v>-3.74</v>
       </c>
       <c r="AB3">
-        <v>-8.75</v>
+        <v>-9.18</v>
       </c>
       <c r="AC3">
-        <v>0.26</v>
+        <v>0</v>
       </c>
       <c r="AD3">
-        <v>1.44</v>
+        <v>0.76</v>
       </c>
       <c r="AE3">
-        <v>18.16</v>
+        <v>18.32</v>
       </c>
       <c r="AF3">
-        <v>-87.91</v>
+        <v>-76.40000000000001</v>
       </c>
       <c r="AG3">
-        <v>475.57</v>
+        <v>479.34</v>
       </c>
       <c r="AH3">
-        <v>355.74</v>
+        <v>347.97</v>
       </c>
       <c r="AI3">
-        <v>420.1</v>
+        <v>408.99</v>
       </c>
       <c r="AJ3" t="s">
         <v>45</v>
       </c>
       <c r="AK3">
-        <v>46.66</v>
+        <v>49.51</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1151,10 +1114,10 @@
         <v>42</v>
       </c>
       <c r="C4">
-        <v>370.05</v>
+        <v>367.05</v>
       </c>
       <c r="D4">
-        <v>1.09</v>
+        <v>-0.8100000000000001</v>
       </c>
       <c r="E4">
         <v>534</v>
@@ -1163,46 +1126,46 @@
         <v>344.7</v>
       </c>
       <c r="G4">
-        <v>-30.7</v>
+        <v>-31.26</v>
       </c>
       <c r="H4">
-        <v>7.35</v>
+        <v>6.48</v>
       </c>
       <c r="I4">
-        <v>-2.23</v>
+        <v>-2</v>
       </c>
       <c r="J4">
-        <v>-7.61</v>
+        <v>-6.77</v>
       </c>
       <c r="K4">
-        <v>-11.76</v>
+        <v>-11.89</v>
       </c>
       <c r="L4">
-        <v>-27.71</v>
+        <v>-27.6</v>
       </c>
       <c r="M4">
-        <v>-22.17</v>
+        <v>-22.13</v>
       </c>
       <c r="N4">
         <v>21</v>
       </c>
       <c r="O4">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="P4">
-        <v>371.92</v>
+        <v>370.42</v>
       </c>
       <c r="Q4">
-        <v>382.39</v>
+        <v>381.09</v>
       </c>
       <c r="R4">
-        <v>401.04</v>
+        <v>399.82</v>
       </c>
       <c r="S4">
-        <v>407.66</v>
+        <v>407.26</v>
       </c>
       <c r="T4">
-        <v>-9.23</v>
+        <v>-9.869999999999999</v>
       </c>
       <c r="U4" t="s">
         <v>43</v>
@@ -1217,34 +1180,34 @@
         <v>0</v>
       </c>
       <c r="Y4">
-        <v>31.19</v>
+        <v>29.13</v>
       </c>
       <c r="Z4">
-        <v>-8.630000000000001</v>
+        <v>-8.77</v>
       </c>
       <c r="AA4">
-        <v>-8.109999999999999</v>
+        <v>-8.24</v>
       </c>
       <c r="AB4">
-        <v>-0.52</v>
+        <v>-0.53</v>
       </c>
       <c r="AC4">
-        <v>24.41</v>
+        <v>33.6</v>
       </c>
       <c r="AD4">
-        <v>21.32</v>
+        <v>25.64</v>
       </c>
       <c r="AE4">
-        <v>10.39</v>
+        <v>10.52</v>
       </c>
       <c r="AF4">
-        <v>-2.69</v>
+        <v>-38.24</v>
       </c>
       <c r="AG4">
-        <v>399.69</v>
+        <v>398.91</v>
       </c>
       <c r="AH4">
-        <v>365.09</v>
+        <v>363.27</v>
       </c>
       <c r="AI4">
         <v>399.57</v>
@@ -1253,7 +1216,7 @@
         <v>45</v>
       </c>
       <c r="AK4">
-        <v>39.19</v>
+        <v>40.77</v>
       </c>
     </row>
     <row r="5" spans="1:37">
@@ -1264,58 +1227,58 @@
         <v>42</v>
       </c>
       <c r="C5">
-        <v>901.4</v>
+        <v>886.85</v>
       </c>
       <c r="D5">
-        <v>2.67</v>
+        <v>-1.61</v>
       </c>
       <c r="E5">
         <v>1069.3</v>
       </c>
       <c r="F5">
-        <v>712.75</v>
+        <v>723.4</v>
       </c>
       <c r="G5">
-        <v>-15.7</v>
+        <v>-17.06</v>
       </c>
       <c r="H5">
-        <v>26.47</v>
+        <v>22.59</v>
       </c>
       <c r="I5">
-        <v>-6.04</v>
+        <v>-3.55</v>
       </c>
       <c r="J5">
-        <v>-11.33</v>
+        <v>-10.65</v>
       </c>
       <c r="K5">
-        <v>-4.46</v>
+        <v>-8.98</v>
       </c>
       <c r="L5">
-        <v>21.69</v>
+        <v>24.43</v>
       </c>
       <c r="M5">
-        <v>-3.53</v>
+        <v>-3.71</v>
       </c>
       <c r="N5">
         <v>99</v>
       </c>
       <c r="O5">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="P5">
-        <v>904.16</v>
+        <v>897.63</v>
       </c>
       <c r="Q5">
-        <v>959.0599999999999</v>
+        <v>954.5</v>
       </c>
       <c r="R5">
-        <v>992.15</v>
+        <v>988.5</v>
       </c>
       <c r="S5">
-        <v>923.8099999999999</v>
+        <v>924.01</v>
       </c>
       <c r="T5">
-        <v>-2.43</v>
+        <v>-4.02</v>
       </c>
       <c r="U5" t="s">
         <v>43</v>
@@ -1330,43 +1293,43 @@
         <v>1</v>
       </c>
       <c r="Y5">
-        <v>33.3</v>
+        <v>30.71</v>
       </c>
       <c r="Z5">
-        <v>-26.32</v>
+        <v>-27.93</v>
       </c>
       <c r="AA5">
-        <v>-18.74</v>
+        <v>-20.57</v>
       </c>
       <c r="AB5">
-        <v>-7.59</v>
+        <v>-7.35</v>
       </c>
       <c r="AC5">
-        <v>14.41</v>
+        <v>27.56</v>
       </c>
       <c r="AD5">
-        <v>4.8</v>
+        <v>13.99</v>
       </c>
       <c r="AE5">
-        <v>22.15</v>
+        <v>22.07</v>
       </c>
       <c r="AF5">
-        <v>10.77</v>
+        <v>-21.3</v>
       </c>
       <c r="AG5">
-        <v>1035.56</v>
+        <v>1036.88</v>
       </c>
       <c r="AH5">
-        <v>882.55</v>
+        <v>872.11</v>
       </c>
       <c r="AI5">
-        <v>959.04</v>
+        <v>956.74</v>
       </c>
       <c r="AJ5" t="s">
         <v>45</v>
       </c>
       <c r="AK5">
-        <v>45.85</v>
+        <v>49.48</v>
       </c>
     </row>
     <row r="6" spans="1:37">
@@ -1377,10 +1340,10 @@
         <v>42</v>
       </c>
       <c r="C6">
-        <v>2.61</v>
+        <v>2.54</v>
       </c>
       <c r="D6">
-        <v>-0.38</v>
+        <v>-2.68</v>
       </c>
       <c r="E6">
         <v>3.38</v>
@@ -1389,37 +1352,37 @@
         <v>1.84</v>
       </c>
       <c r="G6">
-        <v>-22.78</v>
+        <v>-24.85</v>
       </c>
       <c r="H6">
-        <v>41.85</v>
+        <v>38.04</v>
       </c>
       <c r="I6">
-        <v>-5.43</v>
+        <v>-5.58</v>
       </c>
       <c r="J6">
-        <v>-7.77</v>
+        <v>-10.88</v>
       </c>
       <c r="K6">
-        <v>7.41</v>
+        <v>4.53</v>
       </c>
       <c r="L6">
-        <v>-23.46</v>
+        <v>-24.63</v>
       </c>
       <c r="M6">
-        <v>2.74</v>
+        <v>2.18</v>
       </c>
       <c r="N6">
         <v>40</v>
       </c>
       <c r="O6">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="P6">
-        <v>2.64</v>
+        <v>2.61</v>
       </c>
       <c r="Q6">
-        <v>2.79</v>
+        <v>2.78</v>
       </c>
       <c r="R6">
         <v>2.61</v>
@@ -1428,7 +1391,7 @@
         <v>2.66</v>
       </c>
       <c r="T6">
-        <v>-1.86</v>
+        <v>-4.41</v>
       </c>
       <c r="U6" t="s">
         <v>44</v>
@@ -1443,43 +1406,43 @@
         <v>1</v>
       </c>
       <c r="Y6">
-        <v>42.22</v>
+        <v>38.4</v>
       </c>
       <c r="Z6">
-        <v>-0.01</v>
+        <v>-0.02</v>
       </c>
       <c r="AA6">
-        <v>0.03</v>
+        <v>0.02</v>
       </c>
       <c r="AB6">
         <v>-0.04</v>
       </c>
       <c r="AC6">
-        <v>10.22</v>
+        <v>3.78</v>
       </c>
       <c r="AD6">
-        <v>8.44</v>
+        <v>7.55</v>
       </c>
       <c r="AE6">
         <v>0.14</v>
       </c>
       <c r="AF6">
-        <v>-44.09</v>
+        <v>-13.04</v>
       </c>
       <c r="AG6">
-        <v>3.01</v>
+        <v>3.02</v>
       </c>
       <c r="AH6">
-        <v>2.57</v>
+        <v>2.53</v>
       </c>
       <c r="AI6">
-        <v>3.05</v>
+        <v>2.99</v>
       </c>
       <c r="AJ6" t="s">
         <v>45</v>
       </c>
       <c r="AK6">
-        <v>28.14</v>
+        <v>30.87</v>
       </c>
     </row>
   </sheetData>
@@ -1620,7 +1583,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F47"/>
+  <dimension ref="A1:F46"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.7109375" customWidth="1"/>
@@ -1640,774 +1603,719 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="3" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6">
+      <c r="A5" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="B5" s="2"/>
+      <c r="C5" s="2"/>
+      <c r="D5" s="2"/>
+      <c r="E5" s="2"/>
+    </row>
+    <row r="6" spans="1:6">
+      <c r="A6" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="D2" s="3" t="s">
+      <c r="B6" s="4" t="s">
         <v>49</v>
       </c>
-      <c r="E2" s="3" t="s">
+      <c r="C6" s="4" t="s">
         <v>50</v>
       </c>
-      <c r="F2" s="3" t="s">
+      <c r="D6" s="4" t="s">
         <v>51</v>
       </c>
-    </row>
-    <row r="3" spans="1:6">
-      <c r="A3" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="B3" s="4" t="s">
+      <c r="E6" s="4" t="s">
         <v>52</v>
       </c>
-      <c r="C3" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="D3" s="4" t="s">
-        <v>54</v>
-      </c>
-      <c r="E3" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="F3" s="4" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6">
-      <c r="A4" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="B4" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="C4" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="D4" s="4" t="s">
-        <v>54</v>
-      </c>
-      <c r="E4" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="F4" s="4" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6">
-      <c r="A6" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="B6" s="2"/>
-      <c r="C6" s="2"/>
-      <c r="D6" s="2"/>
-      <c r="E6" s="2"/>
     </row>
     <row r="7" spans="1:6">
       <c r="A7" s="3" t="s">
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="D7" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="E7" s="3" t="s">
-        <v>64</v>
+        <v>9</v>
+      </c>
+      <c r="C7" s="5">
+        <v>-12.21</v>
+      </c>
+      <c r="D7" s="5">
+        <v>-11.76</v>
+      </c>
+      <c r="E7" s="6">
+        <v>0.45</v>
       </c>
     </row>
     <row r="8" spans="1:6">
-      <c r="A8" s="5" t="s">
+      <c r="A8" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C8" s="5">
+        <v>-7.66</v>
+      </c>
+      <c r="D8" s="5">
+        <v>-9.220000000000001</v>
+      </c>
+      <c r="E8" s="7">
+        <v>-1.56</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="A9" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C9" s="5">
+        <v>-7.61</v>
+      </c>
+      <c r="D9" s="5">
+        <v>-6.77</v>
+      </c>
+      <c r="E9" s="6">
+        <v>0.84</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="A10" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C10" s="5">
+        <v>-11.33</v>
+      </c>
+      <c r="D10" s="5">
+        <v>-10.65</v>
+      </c>
+      <c r="E10" s="6">
+        <v>0.68</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="A11" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C11" s="5">
+        <v>-7.77</v>
+      </c>
+      <c r="D11" s="5">
+        <v>-10.88</v>
+      </c>
+      <c r="E11" s="7">
+        <v>-3.11</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6">
+      <c r="A12" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B8" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C8" s="6">
-        <v>-12.7</v>
-      </c>
-      <c r="D8" s="6">
-        <v>-12.21</v>
-      </c>
-      <c r="E8" s="7">
-        <v>0.49</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
-      <c r="A9" s="5" t="s">
+      <c r="B12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C12" s="5">
+        <v>-5.34</v>
+      </c>
+      <c r="D12" s="5">
+        <v>-4.34</v>
+      </c>
+      <c r="E12" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6">
+      <c r="A13" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B9" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C9" s="6">
-        <v>-6.34</v>
-      </c>
-      <c r="D9" s="6">
-        <v>-7.66</v>
-      </c>
-      <c r="E9" s="8">
-        <v>-1.32</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
-      <c r="A10" s="5" t="s">
+      <c r="B13" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C13" s="5">
+        <v>-7.71</v>
+      </c>
+      <c r="D13" s="5">
+        <v>-7.52</v>
+      </c>
+      <c r="E13" s="6">
+        <v>0.19</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6">
+      <c r="A14" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B10" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C10" s="6">
-        <v>-9.07</v>
-      </c>
-      <c r="D10" s="6">
-        <v>-7.61</v>
-      </c>
-      <c r="E10" s="7">
-        <v>1.46</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
-      <c r="A11" s="5" t="s">
+      <c r="B14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C14" s="5">
+        <v>-2.23</v>
+      </c>
+      <c r="D14" s="5">
+        <v>-2</v>
+      </c>
+      <c r="E14" s="6">
+        <v>0.23</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6">
+      <c r="A15" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="B11" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C11" s="6">
-        <v>-11.67</v>
-      </c>
-      <c r="D11" s="6">
-        <v>-11.33</v>
-      </c>
-      <c r="E11" s="7">
-        <v>0.34</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
-      <c r="A12" s="5" t="s">
+      <c r="B15" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C15" s="5">
+        <v>-6.04</v>
+      </c>
+      <c r="D15" s="5">
+        <v>-3.55</v>
+      </c>
+      <c r="E15" s="6">
+        <v>2.49</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6">
+      <c r="A16" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="B12" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C12" s="6">
-        <v>-13.25</v>
-      </c>
-      <c r="D12" s="6">
-        <v>-7.77</v>
-      </c>
-      <c r="E12" s="7">
-        <v>5.48</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
-      <c r="A13" s="5" t="s">
+      <c r="B16" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C16" s="5">
+        <v>-5.43</v>
+      </c>
+      <c r="D16" s="5">
+        <v>-5.58</v>
+      </c>
+      <c r="E16" s="7">
+        <v>-0.15</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B13" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C13" s="6">
-        <v>-4.55</v>
-      </c>
-      <c r="D13" s="6">
-        <v>-5.34</v>
-      </c>
-      <c r="E13" s="8">
-        <v>-0.79</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
-      <c r="A14" s="5" t="s">
+      <c r="B17" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C17" s="5">
+        <v>12.42</v>
+      </c>
+      <c r="D17" s="5">
+        <v>8.56</v>
+      </c>
+      <c r="E17" s="7">
+        <v>-3.86</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B14" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C14" s="6">
-        <v>-11.53</v>
-      </c>
-      <c r="D14" s="6">
-        <v>-7.71</v>
-      </c>
-      <c r="E14" s="7">
-        <v>3.82</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6">
-      <c r="A15" s="5" t="s">
+      <c r="B18" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C18" s="5">
+        <v>1.4</v>
+      </c>
+      <c r="D18" s="5">
+        <v>0.03</v>
+      </c>
+      <c r="E18" s="7">
+        <v>-1.37</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B15" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C15" s="6">
-        <v>-3.58</v>
-      </c>
-      <c r="D15" s="6">
-        <v>-2.23</v>
-      </c>
-      <c r="E15" s="7">
-        <v>1.35</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
-      <c r="A16" s="5" t="s">
+      <c r="B19" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C19" s="5">
+        <v>-27.71</v>
+      </c>
+      <c r="D19" s="5">
+        <v>-27.6</v>
+      </c>
+      <c r="E19" s="6">
+        <v>0.11</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="B16" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C16" s="6">
-        <v>-8.06</v>
-      </c>
-      <c r="D16" s="6">
-        <v>-6.04</v>
-      </c>
-      <c r="E16" s="7">
-        <v>2.02</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5">
-      <c r="A17" s="5" t="s">
+      <c r="B20" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C20" s="5">
+        <v>21.69</v>
+      </c>
+      <c r="D20" s="5">
+        <v>24.43</v>
+      </c>
+      <c r="E20" s="6">
+        <v>2.74</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="B17" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C17" s="6">
-        <v>-5.07</v>
-      </c>
-      <c r="D17" s="6">
-        <v>-5.43</v>
-      </c>
-      <c r="E17" s="8">
-        <v>-0.36</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5">
-      <c r="A18" s="5" t="s">
+      <c r="B21" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C21" s="5">
+        <v>-23.46</v>
+      </c>
+      <c r="D21" s="5">
+        <v>-24.63</v>
+      </c>
+      <c r="E21" s="7">
+        <v>-1.17</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B18" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C18" s="6">
-        <v>10.44</v>
-      </c>
-      <c r="D18" s="6">
-        <v>12.42</v>
-      </c>
-      <c r="E18" s="7">
-        <v>1.98</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5">
-      <c r="A19" s="5" t="s">
+      <c r="B22" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C22" s="5">
+        <v>-6.4</v>
+      </c>
+      <c r="D22" s="5">
+        <v>-8.44</v>
+      </c>
+      <c r="E22" s="7">
+        <v>-2.04</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B19" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C19" s="6">
-        <v>1.24</v>
-      </c>
-      <c r="D19" s="6">
-        <v>1.4</v>
-      </c>
-      <c r="E19" s="7">
-        <v>0.16</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5">
-      <c r="A20" s="5" t="s">
+      <c r="B23" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C23" s="5">
+        <v>-9.460000000000001</v>
+      </c>
+      <c r="D23" s="5">
+        <v>-12.85</v>
+      </c>
+      <c r="E23" s="7">
+        <v>-3.39</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5">
+      <c r="A24" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B20" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C20" s="6">
-        <v>-29.17</v>
-      </c>
-      <c r="D20" s="6">
-        <v>-27.71</v>
-      </c>
-      <c r="E20" s="7">
-        <v>1.46</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5">
-      <c r="A21" s="5" t="s">
+      <c r="B24" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C24" s="5">
+        <v>-11.76</v>
+      </c>
+      <c r="D24" s="5">
+        <v>-11.89</v>
+      </c>
+      <c r="E24" s="7">
+        <v>-0.13</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5">
+      <c r="A25" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="B21" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C21" s="6">
-        <v>18.53</v>
-      </c>
-      <c r="D21" s="6">
-        <v>21.69</v>
-      </c>
-      <c r="E21" s="7">
-        <v>3.16</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5">
-      <c r="A22" s="5" t="s">
+      <c r="B25" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C25" s="5">
+        <v>-4.46</v>
+      </c>
+      <c r="D25" s="5">
+        <v>-8.98</v>
+      </c>
+      <c r="E25" s="7">
+        <v>-4.52</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
+      <c r="A26" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="B22" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C22" s="6">
-        <v>-24.06</v>
-      </c>
-      <c r="D22" s="6">
-        <v>-23.46</v>
-      </c>
-      <c r="E22" s="7">
-        <v>0.6</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5">
-      <c r="A23" s="5" t="s">
+      <c r="B26" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C26" s="5">
+        <v>7.41</v>
+      </c>
+      <c r="D26" s="5">
+        <v>4.53</v>
+      </c>
+      <c r="E26" s="7">
+        <v>-2.88</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5">
+      <c r="A27" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B23" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C23" s="6">
-        <v>-5.47</v>
-      </c>
-      <c r="D23" s="6">
-        <v>-6.4</v>
-      </c>
-      <c r="E23" s="8">
-        <v>-0.93</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5">
-      <c r="A24" s="5" t="s">
+      <c r="B27" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C27" s="5">
+        <v>-26</v>
+      </c>
+      <c r="D27" s="5">
+        <v>-27.78</v>
+      </c>
+      <c r="E27" s="7">
+        <v>-1.78</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5">
+      <c r="A28" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B24" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C24" s="6">
-        <v>-9.56</v>
-      </c>
-      <c r="D24" s="6">
-        <v>-9.460000000000001</v>
-      </c>
-      <c r="E24" s="7">
-        <v>0.1</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5">
-      <c r="A25" s="5" t="s">
+      <c r="B28" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C28" s="5">
+        <v>-20.54</v>
+      </c>
+      <c r="D28" s="5">
+        <v>-22.91</v>
+      </c>
+      <c r="E28" s="7">
+        <v>-2.37</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5">
+      <c r="A29" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B25" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C25" s="6">
-        <v>-11.65</v>
-      </c>
-      <c r="D25" s="6">
-        <v>-11.76</v>
-      </c>
-      <c r="E25" s="8">
-        <v>-0.11</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5">
-      <c r="A26" s="5" t="s">
+      <c r="B29" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C29" s="5">
+        <v>-30.7</v>
+      </c>
+      <c r="D29" s="5">
+        <v>-31.26</v>
+      </c>
+      <c r="E29" s="7">
+        <v>-0.5600000000000001</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5">
+      <c r="A30" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="B26" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C26" s="6">
-        <v>-6.75</v>
-      </c>
-      <c r="D26" s="6">
-        <v>-4.46</v>
-      </c>
-      <c r="E26" s="7">
-        <v>2.29</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5">
-      <c r="A27" s="5" t="s">
+      <c r="B30" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C30" s="5">
+        <v>-15.7</v>
+      </c>
+      <c r="D30" s="5">
+        <v>-17.06</v>
+      </c>
+      <c r="E30" s="7">
+        <v>-1.36</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5">
+      <c r="A31" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="B27" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C27" s="6">
-        <v>8.710000000000001</v>
-      </c>
-      <c r="D27" s="6">
-        <v>7.41</v>
-      </c>
-      <c r="E27" s="8">
-        <v>-1.3</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5">
-      <c r="A28" s="5" t="s">
+      <c r="B31" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C31" s="5">
+        <v>-22.78</v>
+      </c>
+      <c r="D31" s="5">
+        <v>-24.85</v>
+      </c>
+      <c r="E31" s="7">
+        <v>-2.07</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5">
+      <c r="A32" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B28" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C28" s="6">
-        <v>-26.36</v>
-      </c>
-      <c r="D28" s="6">
-        <v>-26</v>
-      </c>
-      <c r="E28" s="7">
-        <v>0.36</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5">
-      <c r="A29" s="5" t="s">
+      <c r="B32" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C32" s="5">
+        <v>154.19</v>
+      </c>
+      <c r="D32" s="5">
+        <v>150.48</v>
+      </c>
+      <c r="E32" s="7">
+        <v>-3.71</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5">
+      <c r="A33" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B29" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C29" s="6">
-        <v>-20.28</v>
-      </c>
-      <c r="D29" s="6">
-        <v>-20.54</v>
-      </c>
-      <c r="E29" s="8">
-        <v>-0.26</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5">
-      <c r="A30" s="5" t="s">
+      <c r="B33" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C33" s="5">
+        <v>362.45</v>
+      </c>
+      <c r="D33" s="5">
+        <v>351.65</v>
+      </c>
+      <c r="E33" s="7">
+        <v>-10.8</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5">
+      <c r="A34" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B30" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C30" s="6">
-        <v>-31.45</v>
-      </c>
-      <c r="D30" s="6">
-        <v>-30.7</v>
-      </c>
-      <c r="E30" s="7">
-        <v>0.75</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5">
-      <c r="A31" s="5" t="s">
+      <c r="B34" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C34" s="5">
+        <v>370.05</v>
+      </c>
+      <c r="D34" s="5">
+        <v>367.05</v>
+      </c>
+      <c r="E34" s="7">
+        <v>-3</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5">
+      <c r="A35" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="B31" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C31" s="6">
-        <v>-17.89</v>
-      </c>
-      <c r="D31" s="6">
-        <v>-15.7</v>
-      </c>
-      <c r="E31" s="7">
-        <v>2.19</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5">
-      <c r="A32" s="5" t="s">
+      <c r="B35" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C35" s="5">
+        <v>901.4</v>
+      </c>
+      <c r="D35" s="5">
+        <v>886.85</v>
+      </c>
+      <c r="E35" s="7">
+        <v>-14.55</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5">
+      <c r="A36" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="B32" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C32" s="6">
-        <v>-23.17</v>
-      </c>
-      <c r="D32" s="6">
-        <v>-22.78</v>
-      </c>
-      <c r="E32" s="7">
-        <v>0.39</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5">
-      <c r="A33" s="5" t="s">
+      <c r="B36" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C36" s="5">
+        <v>2.61</v>
+      </c>
+      <c r="D36" s="5">
+        <v>2.54</v>
+      </c>
+      <c r="E36" s="7">
+        <v>-0.07000000000000001</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5">
+      <c r="A37" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B33" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C33" s="6">
-        <v>153.44</v>
-      </c>
-      <c r="D33" s="6">
-        <v>154.19</v>
-      </c>
-      <c r="E33" s="7">
-        <v>0.75</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5">
-      <c r="A34" s="5" t="s">
+      <c r="B37" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C37" s="5">
+        <v>35.62</v>
+      </c>
+      <c r="D37" s="5">
+        <v>31.66</v>
+      </c>
+      <c r="E37" s="7">
+        <v>-3.96</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5">
+      <c r="A38" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B34" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C34" s="6">
-        <v>363.65</v>
-      </c>
-      <c r="D34" s="6">
-        <v>362.45</v>
-      </c>
-      <c r="E34" s="8">
-        <v>-1.2</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5">
-      <c r="A35" s="5" t="s">
+      <c r="B38" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C38" s="5">
+        <v>33.3</v>
+      </c>
+      <c r="D38" s="5">
+        <v>30.74</v>
+      </c>
+      <c r="E38" s="7">
+        <v>-2.56</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5">
+      <c r="A39" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B35" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C35" s="6">
-        <v>366.05</v>
-      </c>
-      <c r="D35" s="6">
-        <v>370.05</v>
-      </c>
-      <c r="E35" s="7">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5">
-      <c r="A36" s="5" t="s">
+      <c r="B39" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C39" s="5">
+        <v>31.19</v>
+      </c>
+      <c r="D39" s="5">
+        <v>29.13</v>
+      </c>
+      <c r="E39" s="7">
+        <v>-2.06</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5">
+      <c r="A40" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="B36" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C36" s="6">
-        <v>878</v>
-      </c>
-      <c r="D36" s="6">
-        <v>901.4</v>
-      </c>
-      <c r="E36" s="7">
-        <v>23.4</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5">
-      <c r="A37" s="5" t="s">
+      <c r="B40" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C40" s="5">
+        <v>33.3</v>
+      </c>
+      <c r="D40" s="5">
+        <v>30.71</v>
+      </c>
+      <c r="E40" s="7">
+        <v>-2.59</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5">
+      <c r="A41" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="B37" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C37" s="6">
-        <v>2.62</v>
-      </c>
-      <c r="D37" s="6">
-        <v>2.61</v>
-      </c>
-      <c r="E37" s="8">
-        <v>-0.01</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5">
-      <c r="A38" s="5" t="s">
+      <c r="B41" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C41" s="5">
+        <v>42.22</v>
+      </c>
+      <c r="D41" s="5">
+        <v>38.4</v>
+      </c>
+      <c r="E41" s="7">
+        <v>-3.82</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5">
+      <c r="A42" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B38" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C38" s="6">
-        <v>34.07</v>
-      </c>
-      <c r="D38" s="6">
-        <v>35.62</v>
-      </c>
-      <c r="E38" s="7">
-        <v>1.55</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5">
-      <c r="A39" s="5" t="s">
+      <c r="B42" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C42" s="5">
+        <v>47.87</v>
+      </c>
+      <c r="D42" s="5">
+        <v>69.59</v>
+      </c>
+      <c r="E42" s="6">
+        <v>21.72</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5">
+      <c r="A43" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B39" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C39" s="6">
-        <v>33.59</v>
-      </c>
-      <c r="D39" s="6">
-        <v>33.3</v>
-      </c>
-      <c r="E39" s="8">
-        <v>-0.29</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5">
-      <c r="A40" s="5" t="s">
+      <c r="B43" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C43" s="5">
+        <v>-87.91</v>
+      </c>
+      <c r="D43" s="5">
+        <v>-76.40000000000001</v>
+      </c>
+      <c r="E43" s="6">
+        <v>11.51</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5">
+      <c r="A44" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B40" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C40" s="6">
-        <v>24.59</v>
-      </c>
-      <c r="D40" s="6">
-        <v>31.19</v>
-      </c>
-      <c r="E40" s="7">
-        <v>6.6</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5">
-      <c r="A41" s="5" t="s">
+      <c r="B44" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C44" s="5">
+        <v>-2.69</v>
+      </c>
+      <c r="D44" s="5">
+        <v>-38.24</v>
+      </c>
+      <c r="E44" s="7">
+        <v>-35.55</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5">
+      <c r="A45" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="B41" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C41" s="6">
-        <v>23.67</v>
-      </c>
-      <c r="D41" s="6">
-        <v>33.3</v>
-      </c>
-      <c r="E41" s="7">
-        <v>9.630000000000001</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5">
-      <c r="A42" s="5" t="s">
+      <c r="B45" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C45" s="5">
+        <v>10.77</v>
+      </c>
+      <c r="D45" s="5">
+        <v>-21.3</v>
+      </c>
+      <c r="E45" s="7">
+        <v>-32.07</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5">
+      <c r="A46" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="B42" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C42" s="6">
-        <v>42.78</v>
-      </c>
-      <c r="D42" s="6">
-        <v>42.22</v>
-      </c>
-      <c r="E42" s="8">
-        <v>-0.5600000000000001</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5">
-      <c r="A43" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B43" s="5" t="s">
+      <c r="B46" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="C43" s="6">
-        <v>20.98</v>
-      </c>
-      <c r="D43" s="6">
-        <v>47.87</v>
-      </c>
-      <c r="E43" s="7">
-        <v>26.89</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5">
-      <c r="A44" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B44" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C44" s="6">
-        <v>-58.37</v>
-      </c>
-      <c r="D44" s="6">
-        <v>-87.91</v>
-      </c>
-      <c r="E44" s="8">
-        <v>-29.54</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5">
-      <c r="A45" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B45" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C45" s="6">
-        <v>-46.31</v>
-      </c>
-      <c r="D45" s="6">
-        <v>-2.69</v>
-      </c>
-      <c r="E45" s="7">
-        <v>43.62</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5">
-      <c r="A46" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B46" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C46" s="6">
-        <v>53.11</v>
-      </c>
-      <c r="D46" s="6">
-        <v>10.77</v>
-      </c>
-      <c r="E46" s="8">
-        <v>-42.34</v>
-      </c>
-    </row>
-    <row r="47" spans="1:5">
-      <c r="A47" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B47" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C47" s="6">
-        <v>28.52</v>
-      </c>
-      <c r="D47" s="6">
+      <c r="C46" s="5">
         <v>-44.09</v>
       </c>
-      <c r="E47" s="8">
-        <v>-72.61</v>
+      <c r="D46" s="5">
+        <v>-13.04</v>
+      </c>
+      <c r="E46" s="6">
+        <v>31.05</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A6:E6"/>
+    <mergeCell ref="A5:E5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2427,60 +2335,60 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="28" customHeight="1">
-      <c r="A1" s="9" t="s">
+      <c r="A1" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="9" t="s">
-        <v>65</v>
-      </c>
-      <c r="C1" s="9" t="s">
-        <v>66</v>
-      </c>
-      <c r="D1" s="9" t="s">
-        <v>67</v>
-      </c>
-      <c r="E1" s="9" t="s">
-        <v>68</v>
-      </c>
-      <c r="F1" s="9" t="s">
-        <v>69</v>
-      </c>
-      <c r="G1" s="9" t="s">
-        <v>70</v>
-      </c>
-      <c r="H1" s="9" t="s">
-        <v>71</v>
-      </c>
-      <c r="I1" s="9" t="s">
-        <v>72</v>
+      <c r="B1" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="C1" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="D1" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="E1" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="F1" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="G1" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="H1" s="8" t="s">
+        <v>59</v>
+      </c>
+      <c r="I1" s="8" t="s">
+        <v>60</v>
       </c>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="10" t="s">
+      <c r="A2" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="B2" s="11">
+      <c r="B2" s="10">
         <v>41.92</v>
       </c>
-      <c r="C2" s="12">
+      <c r="C2" s="11">
         <v>5</v>
       </c>
-      <c r="D2" s="11">
-        <v>35.1</v>
-      </c>
-      <c r="E2" s="11">
+      <c r="D2" s="10">
+        <v>32.1</v>
+      </c>
+      <c r="E2" s="10">
         <v>20</v>
       </c>
-      <c r="F2" s="11">
-        <v>-9.300000000000001</v>
-      </c>
-      <c r="G2" s="11">
-        <v>-4.9</v>
-      </c>
-      <c r="H2" s="11">
+      <c r="F2" s="10">
+        <v>-9.9</v>
+      </c>
+      <c r="G2" s="10">
+        <v>-7.5</v>
+      </c>
+      <c r="H2" s="10">
         <v>59.8</v>
       </c>
-      <c r="I2" s="11">
+      <c r="I2" s="10">
         <v>20</v>
       </c>
     </row>
@@ -2582,37 +2490,37 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
-      <c r="A1" s="13" t="s">
+      <c r="A1" s="12" t="s">
         <v>37</v>
       </c>
-      <c r="B1" s="13" t="s">
+      <c r="B1" s="12" t="s">
         <v>38</v>
       </c>
-      <c r="C1" s="13" t="s">
+      <c r="C1" s="12" t="s">
         <v>41</v>
       </c>
-      <c r="D1" s="13" t="s">
+      <c r="D1" s="12" t="s">
         <v>40</v>
       </c>
-      <c r="E1" s="13" t="s">
+      <c r="E1" s="12" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="2" spans="1:5">
-      <c r="A2" s="14">
-        <v>0.2061</v>
-      </c>
-      <c r="B2" s="14">
-        <v>0.07829999999999999</v>
-      </c>
-      <c r="C2" s="14">
-        <v>0.0274</v>
-      </c>
-      <c r="D2" s="14">
-        <v>-0.0353</v>
-      </c>
-      <c r="E2" s="14">
-        <v>-0.2217</v>
+      <c r="A2" s="13">
+        <v>0.2057</v>
+      </c>
+      <c r="B2" s="13">
+        <v>0.0716</v>
+      </c>
+      <c r="C2" s="13">
+        <v>0.0218</v>
+      </c>
+      <c r="D2" s="13">
+        <v>-0.0371</v>
+      </c>
+      <c r="E2" s="13">
+        <v>-0.2213</v>
       </c>
     </row>
   </sheetData>

--- a/HINDUJA_GROUP_Technical_Metrics.xlsx
+++ b/HINDUJA_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="207" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="211" uniqueCount="61">
   <si>
     <t>Symbol</t>
   </si>
@@ -888,10 +888,10 @@
         <v>42</v>
       </c>
       <c r="C2">
-        <v>150.48</v>
+        <v>152.6</v>
       </c>
       <c r="D2">
-        <v>-2.41</v>
+        <v>1.41</v>
       </c>
       <c r="E2">
         <v>208.37</v>
@@ -900,46 +900,46 @@
         <v>131.36</v>
       </c>
       <c r="G2">
-        <v>-27.78</v>
+        <v>-26.76</v>
       </c>
       <c r="H2">
-        <v>14.56</v>
+        <v>16.17</v>
       </c>
       <c r="I2">
-        <v>-4.34</v>
+        <v>-4.07</v>
       </c>
       <c r="J2">
-        <v>-11.76</v>
+        <v>-9.109999999999999</v>
       </c>
       <c r="K2">
-        <v>-8.44</v>
+        <v>-8.140000000000001</v>
       </c>
       <c r="L2">
-        <v>8.56</v>
+        <v>9.710000000000001</v>
       </c>
       <c r="M2">
-        <v>20.57</v>
+        <v>20.64</v>
       </c>
       <c r="N2">
         <v>79</v>
       </c>
       <c r="O2">
-        <v>58</v>
+        <v>66</v>
       </c>
       <c r="P2">
-        <v>154.48</v>
+        <v>153.19</v>
       </c>
       <c r="Q2">
-        <v>161.2</v>
+        <v>160.37</v>
       </c>
       <c r="R2">
-        <v>166.8</v>
+        <v>166.84</v>
       </c>
       <c r="S2">
-        <v>169.87</v>
+        <v>169.82</v>
       </c>
       <c r="T2">
-        <v>-11.42</v>
+        <v>-10.14</v>
       </c>
       <c r="U2" t="s">
         <v>43</v>
@@ -954,34 +954,34 @@
         <v>0</v>
       </c>
       <c r="Y2">
-        <v>31.66</v>
+        <v>36.04</v>
       </c>
       <c r="Z2">
-        <v>-4.11</v>
+        <v>-4.2</v>
       </c>
       <c r="AA2">
-        <v>-3.09</v>
+        <v>-3.32</v>
       </c>
       <c r="AB2">
-        <v>-1.02</v>
+        <v>-0.89</v>
       </c>
       <c r="AC2">
-        <v>28.02</v>
+        <v>32.37</v>
       </c>
       <c r="AD2">
-        <v>35.22</v>
+        <v>32.08</v>
       </c>
       <c r="AE2">
-        <v>4.19</v>
+        <v>4.12</v>
       </c>
       <c r="AF2">
-        <v>69.59</v>
+        <v>-19.45</v>
       </c>
       <c r="AG2">
-        <v>173.04</v>
+        <v>172.15</v>
       </c>
       <c r="AH2">
-        <v>149.37</v>
+        <v>148.59</v>
       </c>
       <c r="AI2">
         <v>164.26</v>
@@ -990,7 +990,7 @@
         <v>45</v>
       </c>
       <c r="AK2">
-        <v>45.04</v>
+        <v>48</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1001,10 +1001,10 @@
         <v>42</v>
       </c>
       <c r="C3">
-        <v>351.65</v>
+        <v>347.7</v>
       </c>
       <c r="D3">
-        <v>-2.98</v>
+        <v>-1.12</v>
       </c>
       <c r="E3">
         <v>456.15</v>
@@ -1013,46 +1013,46 @@
         <v>225</v>
       </c>
       <c r="G3">
-        <v>-22.91</v>
+        <v>-23.78</v>
       </c>
       <c r="H3">
-        <v>56.29</v>
+        <v>54.53</v>
       </c>
       <c r="I3">
-        <v>-7.52</v>
+        <v>-9.48</v>
       </c>
       <c r="J3">
-        <v>-9.220000000000001</v>
+        <v>-11.23</v>
       </c>
       <c r="K3">
-        <v>-12.85</v>
+        <v>-13.95</v>
       </c>
       <c r="L3">
-        <v>0.03</v>
+        <v>-2.15</v>
       </c>
       <c r="M3">
-        <v>7.16</v>
+        <v>6.64</v>
       </c>
       <c r="N3">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="O3">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="P3">
-        <v>368.17</v>
+        <v>360.89</v>
       </c>
       <c r="Q3">
-        <v>413.65</v>
+        <v>409.89</v>
       </c>
       <c r="R3">
-        <v>407.6</v>
+        <v>406.74</v>
       </c>
       <c r="S3">
-        <v>338.11</v>
+        <v>338.29</v>
       </c>
       <c r="T3">
-        <v>4.01</v>
+        <v>2.78</v>
       </c>
       <c r="U3" t="s">
         <v>44</v>
@@ -1067,43 +1067,43 @@
         <v>3</v>
       </c>
       <c r="Y3">
-        <v>30.74</v>
+        <v>29.84</v>
       </c>
       <c r="Z3">
-        <v>-12.92</v>
+        <v>-15.22</v>
       </c>
       <c r="AA3">
-        <v>-3.74</v>
+        <v>-6.04</v>
       </c>
       <c r="AB3">
-        <v>-9.18</v>
+        <v>-9.19</v>
       </c>
       <c r="AC3">
         <v>0</v>
       </c>
       <c r="AD3">
-        <v>0.76</v>
+        <v>0.09</v>
       </c>
       <c r="AE3">
-        <v>18.32</v>
+        <v>17.98</v>
       </c>
       <c r="AF3">
-        <v>-76.40000000000001</v>
+        <v>-89.42</v>
       </c>
       <c r="AG3">
-        <v>479.34</v>
+        <v>481.67</v>
       </c>
       <c r="AH3">
-        <v>347.97</v>
+        <v>338.11</v>
       </c>
       <c r="AI3">
-        <v>408.99</v>
+        <v>404.18</v>
       </c>
       <c r="AJ3" t="s">
         <v>45</v>
       </c>
       <c r="AK3">
-        <v>49.51</v>
+        <v>52.01</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1114,10 +1114,10 @@
         <v>42</v>
       </c>
       <c r="C4">
-        <v>367.05</v>
+        <v>364.95</v>
       </c>
       <c r="D4">
-        <v>-0.8100000000000001</v>
+        <v>-0.57</v>
       </c>
       <c r="E4">
         <v>534</v>
@@ -1126,46 +1126,46 @@
         <v>344.7</v>
       </c>
       <c r="G4">
-        <v>-31.26</v>
+        <v>-31.66</v>
       </c>
       <c r="H4">
-        <v>6.48</v>
+        <v>5.87</v>
       </c>
       <c r="I4">
-        <v>-2</v>
+        <v>-3.09</v>
       </c>
       <c r="J4">
-        <v>-6.77</v>
+        <v>-7.16</v>
       </c>
       <c r="K4">
-        <v>-11.89</v>
+        <v>-11.07</v>
       </c>
       <c r="L4">
-        <v>-27.6</v>
+        <v>-26.98</v>
       </c>
       <c r="M4">
-        <v>-22.13</v>
+        <v>-22.31</v>
       </c>
       <c r="N4">
         <v>21</v>
       </c>
       <c r="O4">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="P4">
-        <v>370.42</v>
+        <v>368.09</v>
       </c>
       <c r="Q4">
-        <v>381.09</v>
+        <v>379.69</v>
       </c>
       <c r="R4">
-        <v>399.82</v>
+        <v>398.61</v>
       </c>
       <c r="S4">
-        <v>407.26</v>
+        <v>406.85</v>
       </c>
       <c r="T4">
-        <v>-9.869999999999999</v>
+        <v>-10.3</v>
       </c>
       <c r="U4" t="s">
         <v>43</v>
@@ -1180,43 +1180,43 @@
         <v>0</v>
       </c>
       <c r="Y4">
-        <v>29.13</v>
+        <v>27.75</v>
       </c>
       <c r="Z4">
-        <v>-8.77</v>
+        <v>-8.949999999999999</v>
       </c>
       <c r="AA4">
-        <v>-8.24</v>
+        <v>-8.380000000000001</v>
       </c>
       <c r="AB4">
-        <v>-0.53</v>
+        <v>-0.57</v>
       </c>
       <c r="AC4">
-        <v>33.6</v>
+        <v>43.13</v>
       </c>
       <c r="AD4">
-        <v>25.64</v>
+        <v>33.71</v>
       </c>
       <c r="AE4">
-        <v>10.52</v>
+        <v>10.6</v>
       </c>
       <c r="AF4">
-        <v>-38.24</v>
+        <v>-48.93</v>
       </c>
       <c r="AG4">
-        <v>398.91</v>
+        <v>397.97</v>
       </c>
       <c r="AH4">
-        <v>363.27</v>
+        <v>361.4</v>
       </c>
       <c r="AI4">
-        <v>399.57</v>
+        <v>398.96</v>
       </c>
       <c r="AJ4" t="s">
         <v>45</v>
       </c>
       <c r="AK4">
-        <v>40.77</v>
+        <v>42.66</v>
       </c>
     </row>
     <row r="5" spans="1:37">
@@ -1227,58 +1227,58 @@
         <v>42</v>
       </c>
       <c r="C5">
-        <v>886.85</v>
+        <v>886.6</v>
       </c>
       <c r="D5">
-        <v>-1.61</v>
+        <v>-0.03</v>
       </c>
       <c r="E5">
         <v>1069.3</v>
       </c>
       <c r="F5">
-        <v>723.4</v>
+        <v>735.55</v>
       </c>
       <c r="G5">
-        <v>-17.06</v>
+        <v>-17.09</v>
       </c>
       <c r="H5">
-        <v>22.59</v>
+        <v>20.54</v>
       </c>
       <c r="I5">
-        <v>-3.55</v>
+        <v>-2.81</v>
       </c>
       <c r="J5">
-        <v>-10.65</v>
+        <v>-9.35</v>
       </c>
       <c r="K5">
-        <v>-8.98</v>
+        <v>-12.2</v>
       </c>
       <c r="L5">
-        <v>24.43</v>
+        <v>22.56</v>
       </c>
       <c r="M5">
-        <v>-3.71</v>
+        <v>-4.81</v>
       </c>
       <c r="N5">
         <v>99</v>
       </c>
       <c r="O5">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="P5">
-        <v>897.63</v>
+        <v>892.51</v>
       </c>
       <c r="Q5">
-        <v>954.5</v>
+        <v>948.59</v>
       </c>
       <c r="R5">
-        <v>988.5</v>
+        <v>986.13</v>
       </c>
       <c r="S5">
-        <v>924.01</v>
+        <v>924.1900000000001</v>
       </c>
       <c r="T5">
-        <v>-4.02</v>
+        <v>-4.07</v>
       </c>
       <c r="U5" t="s">
         <v>43</v>
@@ -1293,43 +1293,43 @@
         <v>1</v>
       </c>
       <c r="Y5">
-        <v>30.71</v>
+        <v>30.66</v>
       </c>
       <c r="Z5">
-        <v>-27.93</v>
+        <v>-28.88</v>
       </c>
       <c r="AA5">
-        <v>-20.57</v>
+        <v>-22.24</v>
       </c>
       <c r="AB5">
-        <v>-7.35</v>
+        <v>-6.65</v>
       </c>
       <c r="AC5">
-        <v>27.56</v>
+        <v>40.63</v>
       </c>
       <c r="AD5">
-        <v>13.99</v>
+        <v>27.53</v>
       </c>
       <c r="AE5">
-        <v>22.07</v>
+        <v>21.89</v>
       </c>
       <c r="AF5">
-        <v>-21.3</v>
+        <v>9.83</v>
       </c>
       <c r="AG5">
-        <v>1036.88</v>
+        <v>1032.72</v>
       </c>
       <c r="AH5">
-        <v>872.11</v>
+        <v>864.46</v>
       </c>
       <c r="AI5">
-        <v>956.74</v>
+        <v>956.15</v>
       </c>
       <c r="AJ5" t="s">
         <v>45</v>
       </c>
       <c r="AK5">
-        <v>49.48</v>
+        <v>52.63</v>
       </c>
     </row>
     <row r="6" spans="1:37">
@@ -1340,10 +1340,10 @@
         <v>42</v>
       </c>
       <c r="C6">
-        <v>2.54</v>
+        <v>2.59</v>
       </c>
       <c r="D6">
-        <v>-2.68</v>
+        <v>1.97</v>
       </c>
       <c r="E6">
         <v>3.38</v>
@@ -1352,46 +1352,46 @@
         <v>1.84</v>
       </c>
       <c r="G6">
-        <v>-24.85</v>
+        <v>-23.37</v>
       </c>
       <c r="H6">
-        <v>38.04</v>
+        <v>40.76</v>
       </c>
       <c r="I6">
-        <v>-5.58</v>
+        <v>-0.77</v>
       </c>
       <c r="J6">
-        <v>-10.88</v>
+        <v>-9.119999999999999</v>
       </c>
       <c r="K6">
-        <v>4.53</v>
+        <v>7.92</v>
       </c>
       <c r="L6">
-        <v>-24.63</v>
+        <v>-22.69</v>
       </c>
       <c r="M6">
-        <v>2.18</v>
+        <v>0.63</v>
       </c>
       <c r="N6">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="O6">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="P6">
         <v>2.61</v>
       </c>
       <c r="Q6">
-        <v>2.78</v>
+        <v>2.76</v>
       </c>
       <c r="R6">
-        <v>2.61</v>
+        <v>2.62</v>
       </c>
       <c r="S6">
         <v>2.66</v>
       </c>
       <c r="T6">
-        <v>-4.41</v>
+        <v>-2.45</v>
       </c>
       <c r="U6" t="s">
         <v>44</v>
@@ -1406,34 +1406,34 @@
         <v>1</v>
       </c>
       <c r="Y6">
-        <v>38.4</v>
+        <v>42.41</v>
       </c>
       <c r="Z6">
-        <v>-0.02</v>
+        <v>-0.03</v>
       </c>
       <c r="AA6">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
       <c r="AB6">
         <v>-0.04</v>
       </c>
       <c r="AC6">
-        <v>3.78</v>
+        <v>8.279999999999999</v>
       </c>
       <c r="AD6">
-        <v>7.55</v>
+        <v>7.43</v>
       </c>
       <c r="AE6">
         <v>0.14</v>
       </c>
       <c r="AF6">
-        <v>-13.04</v>
+        <v>-11.02</v>
       </c>
       <c r="AG6">
         <v>3.02</v>
       </c>
       <c r="AH6">
-        <v>2.53</v>
+        <v>2.51</v>
       </c>
       <c r="AI6">
         <v>2.99</v>
@@ -1442,7 +1442,7 @@
         <v>45</v>
       </c>
       <c r="AK6">
-        <v>30.87</v>
+        <v>31.37</v>
       </c>
     </row>
   </sheetData>
@@ -1583,7 +1583,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F46"/>
+  <dimension ref="A1:F48"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.7109375" customWidth="1"/>
@@ -1640,13 +1640,13 @@
         <v>9</v>
       </c>
       <c r="C7" s="5">
-        <v>-12.21</v>
+        <v>-11.76</v>
       </c>
       <c r="D7" s="5">
-        <v>-11.76</v>
+        <v>-9.109999999999999</v>
       </c>
       <c r="E7" s="6">
-        <v>0.45</v>
+        <v>2.65</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -1657,13 +1657,13 @@
         <v>9</v>
       </c>
       <c r="C8" s="5">
-        <v>-7.66</v>
+        <v>-9.220000000000001</v>
       </c>
       <c r="D8" s="5">
-        <v>-9.220000000000001</v>
+        <v>-11.23</v>
       </c>
       <c r="E8" s="7">
-        <v>-1.56</v>
+        <v>-2.01</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -1674,13 +1674,13 @@
         <v>9</v>
       </c>
       <c r="C9" s="5">
-        <v>-7.61</v>
+        <v>-6.77</v>
       </c>
       <c r="D9" s="5">
-        <v>-6.77</v>
-      </c>
-      <c r="E9" s="6">
-        <v>0.84</v>
+        <v>-7.16</v>
+      </c>
+      <c r="E9" s="7">
+        <v>-0.39</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -1691,13 +1691,13 @@
         <v>9</v>
       </c>
       <c r="C10" s="5">
-        <v>-11.33</v>
+        <v>-10.65</v>
       </c>
       <c r="D10" s="5">
-        <v>-10.65</v>
+        <v>-9.35</v>
       </c>
       <c r="E10" s="6">
-        <v>0.68</v>
+        <v>1.3</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -1708,13 +1708,13 @@
         <v>9</v>
       </c>
       <c r="C11" s="5">
-        <v>-7.77</v>
+        <v>-10.88</v>
       </c>
       <c r="D11" s="5">
-        <v>-10.88</v>
-      </c>
-      <c r="E11" s="7">
-        <v>-3.11</v>
+        <v>-9.119999999999999</v>
+      </c>
+      <c r="E11" s="6">
+        <v>1.76</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -1725,13 +1725,13 @@
         <v>8</v>
       </c>
       <c r="C12" s="5">
-        <v>-5.34</v>
+        <v>-4.34</v>
       </c>
       <c r="D12" s="5">
-        <v>-4.34</v>
+        <v>-4.07</v>
       </c>
       <c r="E12" s="6">
-        <v>1</v>
+        <v>0.27</v>
       </c>
     </row>
     <row r="13" spans="1:6">
@@ -1742,13 +1742,13 @@
         <v>8</v>
       </c>
       <c r="C13" s="5">
-        <v>-7.71</v>
+        <v>-7.52</v>
       </c>
       <c r="D13" s="5">
-        <v>-7.52</v>
-      </c>
-      <c r="E13" s="6">
-        <v>0.19</v>
+        <v>-9.48</v>
+      </c>
+      <c r="E13" s="7">
+        <v>-1.96</v>
       </c>
     </row>
     <row r="14" spans="1:6">
@@ -1759,13 +1759,13 @@
         <v>8</v>
       </c>
       <c r="C14" s="5">
-        <v>-2.23</v>
+        <v>-2</v>
       </c>
       <c r="D14" s="5">
-        <v>-2</v>
-      </c>
-      <c r="E14" s="6">
-        <v>0.23</v>
+        <v>-3.09</v>
+      </c>
+      <c r="E14" s="7">
+        <v>-1.09</v>
       </c>
     </row>
     <row r="15" spans="1:6">
@@ -1776,13 +1776,13 @@
         <v>8</v>
       </c>
       <c r="C15" s="5">
-        <v>-6.04</v>
+        <v>-3.55</v>
       </c>
       <c r="D15" s="5">
-        <v>-3.55</v>
+        <v>-2.81</v>
       </c>
       <c r="E15" s="6">
-        <v>2.49</v>
+        <v>0.74</v>
       </c>
     </row>
     <row r="16" spans="1:6">
@@ -1793,13 +1793,13 @@
         <v>8</v>
       </c>
       <c r="C16" s="5">
-        <v>-5.43</v>
+        <v>-5.58</v>
       </c>
       <c r="D16" s="5">
-        <v>-5.58</v>
-      </c>
-      <c r="E16" s="7">
-        <v>-0.15</v>
+        <v>-0.77</v>
+      </c>
+      <c r="E16" s="6">
+        <v>4.81</v>
       </c>
     </row>
     <row r="17" spans="1:5">
@@ -1810,13 +1810,13 @@
         <v>11</v>
       </c>
       <c r="C17" s="5">
-        <v>12.42</v>
+        <v>8.56</v>
       </c>
       <c r="D17" s="5">
-        <v>8.56</v>
-      </c>
-      <c r="E17" s="7">
-        <v>-3.86</v>
+        <v>9.710000000000001</v>
+      </c>
+      <c r="E17" s="6">
+        <v>1.15</v>
       </c>
     </row>
     <row r="18" spans="1:5">
@@ -1827,13 +1827,13 @@
         <v>11</v>
       </c>
       <c r="C18" s="5">
-        <v>1.4</v>
+        <v>0.03</v>
       </c>
       <c r="D18" s="5">
-        <v>0.03</v>
+        <v>-2.15</v>
       </c>
       <c r="E18" s="7">
-        <v>-1.37</v>
+        <v>-2.18</v>
       </c>
     </row>
     <row r="19" spans="1:5">
@@ -1844,13 +1844,13 @@
         <v>11</v>
       </c>
       <c r="C19" s="5">
-        <v>-27.71</v>
+        <v>-27.6</v>
       </c>
       <c r="D19" s="5">
-        <v>-27.6</v>
+        <v>-26.98</v>
       </c>
       <c r="E19" s="6">
-        <v>0.11</v>
+        <v>0.62</v>
       </c>
     </row>
     <row r="20" spans="1:5">
@@ -1861,13 +1861,13 @@
         <v>11</v>
       </c>
       <c r="C20" s="5">
-        <v>21.69</v>
+        <v>24.43</v>
       </c>
       <c r="D20" s="5">
-        <v>24.43</v>
-      </c>
-      <c r="E20" s="6">
-        <v>2.74</v>
+        <v>22.56</v>
+      </c>
+      <c r="E20" s="7">
+        <v>-1.87</v>
       </c>
     </row>
     <row r="21" spans="1:5">
@@ -1878,13 +1878,13 @@
         <v>11</v>
       </c>
       <c r="C21" s="5">
-        <v>-23.46</v>
+        <v>-24.63</v>
       </c>
       <c r="D21" s="5">
-        <v>-24.63</v>
-      </c>
-      <c r="E21" s="7">
-        <v>-1.17</v>
+        <v>-22.69</v>
+      </c>
+      <c r="E21" s="6">
+        <v>1.94</v>
       </c>
     </row>
     <row r="22" spans="1:5">
@@ -1895,13 +1895,13 @@
         <v>10</v>
       </c>
       <c r="C22" s="5">
-        <v>-6.4</v>
+        <v>-8.44</v>
       </c>
       <c r="D22" s="5">
-        <v>-8.44</v>
-      </c>
-      <c r="E22" s="7">
-        <v>-2.04</v>
+        <v>-8.140000000000001</v>
+      </c>
+      <c r="E22" s="6">
+        <v>0.3</v>
       </c>
     </row>
     <row r="23" spans="1:5">
@@ -1912,13 +1912,13 @@
         <v>10</v>
       </c>
       <c r="C23" s="5">
-        <v>-9.460000000000001</v>
+        <v>-12.85</v>
       </c>
       <c r="D23" s="5">
-        <v>-12.85</v>
+        <v>-13.95</v>
       </c>
       <c r="E23" s="7">
-        <v>-3.39</v>
+        <v>-1.1</v>
       </c>
     </row>
     <row r="24" spans="1:5">
@@ -1929,13 +1929,13 @@
         <v>10</v>
       </c>
       <c r="C24" s="5">
-        <v>-11.76</v>
+        <v>-11.89</v>
       </c>
       <c r="D24" s="5">
-        <v>-11.89</v>
-      </c>
-      <c r="E24" s="7">
-        <v>-0.13</v>
+        <v>-11.07</v>
+      </c>
+      <c r="E24" s="6">
+        <v>0.82</v>
       </c>
     </row>
     <row r="25" spans="1:5">
@@ -1946,13 +1946,13 @@
         <v>10</v>
       </c>
       <c r="C25" s="5">
-        <v>-4.46</v>
+        <v>-8.98</v>
       </c>
       <c r="D25" s="5">
-        <v>-8.98</v>
+        <v>-12.2</v>
       </c>
       <c r="E25" s="7">
-        <v>-4.52</v>
+        <v>-3.22</v>
       </c>
     </row>
     <row r="26" spans="1:5">
@@ -1963,13 +1963,13 @@
         <v>10</v>
       </c>
       <c r="C26" s="5">
-        <v>7.41</v>
+        <v>4.53</v>
       </c>
       <c r="D26" s="5">
-        <v>4.53</v>
-      </c>
-      <c r="E26" s="7">
-        <v>-2.88</v>
+        <v>7.92</v>
+      </c>
+      <c r="E26" s="6">
+        <v>3.39</v>
       </c>
     </row>
     <row r="27" spans="1:5">
@@ -1980,13 +1980,13 @@
         <v>6</v>
       </c>
       <c r="C27" s="5">
-        <v>-26</v>
+        <v>-27.78</v>
       </c>
       <c r="D27" s="5">
-        <v>-27.78</v>
-      </c>
-      <c r="E27" s="7">
-        <v>-1.78</v>
+        <v>-26.76</v>
+      </c>
+      <c r="E27" s="6">
+        <v>1.02</v>
       </c>
     </row>
     <row r="28" spans="1:5">
@@ -1997,13 +1997,13 @@
         <v>6</v>
       </c>
       <c r="C28" s="5">
-        <v>-20.54</v>
+        <v>-22.91</v>
       </c>
       <c r="D28" s="5">
-        <v>-22.91</v>
+        <v>-23.78</v>
       </c>
       <c r="E28" s="7">
-        <v>-2.37</v>
+        <v>-0.87</v>
       </c>
     </row>
     <row r="29" spans="1:5">
@@ -2014,13 +2014,13 @@
         <v>6</v>
       </c>
       <c r="C29" s="5">
-        <v>-30.7</v>
+        <v>-31.26</v>
       </c>
       <c r="D29" s="5">
-        <v>-31.26</v>
+        <v>-31.66</v>
       </c>
       <c r="E29" s="7">
-        <v>-0.5600000000000001</v>
+        <v>-0.4</v>
       </c>
     </row>
     <row r="30" spans="1:5">
@@ -2031,13 +2031,13 @@
         <v>6</v>
       </c>
       <c r="C30" s="5">
-        <v>-15.7</v>
+        <v>-17.06</v>
       </c>
       <c r="D30" s="5">
-        <v>-17.06</v>
+        <v>-17.09</v>
       </c>
       <c r="E30" s="7">
-        <v>-1.36</v>
+        <v>-0.03</v>
       </c>
     </row>
     <row r="31" spans="1:5">
@@ -2048,13 +2048,13 @@
         <v>6</v>
       </c>
       <c r="C31" s="5">
-        <v>-22.78</v>
+        <v>-24.85</v>
       </c>
       <c r="D31" s="5">
-        <v>-24.85</v>
-      </c>
-      <c r="E31" s="7">
-        <v>-2.07</v>
+        <v>-23.37</v>
+      </c>
+      <c r="E31" s="6">
+        <v>1.48</v>
       </c>
     </row>
     <row r="32" spans="1:5">
@@ -2065,13 +2065,13 @@
         <v>2</v>
       </c>
       <c r="C32" s="5">
-        <v>154.19</v>
+        <v>150.48</v>
       </c>
       <c r="D32" s="5">
-        <v>150.48</v>
-      </c>
-      <c r="E32" s="7">
-        <v>-3.71</v>
+        <v>152.6</v>
+      </c>
+      <c r="E32" s="6">
+        <v>2.12</v>
       </c>
     </row>
     <row r="33" spans="1:5">
@@ -2082,13 +2082,13 @@
         <v>2</v>
       </c>
       <c r="C33" s="5">
-        <v>362.45</v>
+        <v>351.65</v>
       </c>
       <c r="D33" s="5">
-        <v>351.65</v>
+        <v>347.7</v>
       </c>
       <c r="E33" s="7">
-        <v>-10.8</v>
+        <v>-3.95</v>
       </c>
     </row>
     <row r="34" spans="1:5">
@@ -2099,13 +2099,13 @@
         <v>2</v>
       </c>
       <c r="C34" s="5">
-        <v>370.05</v>
+        <v>367.05</v>
       </c>
       <c r="D34" s="5">
-        <v>367.05</v>
+        <v>364.95</v>
       </c>
       <c r="E34" s="7">
-        <v>-3</v>
+        <v>-2.1</v>
       </c>
     </row>
     <row r="35" spans="1:5">
@@ -2116,13 +2116,13 @@
         <v>2</v>
       </c>
       <c r="C35" s="5">
-        <v>901.4</v>
+        <v>886.85</v>
       </c>
       <c r="D35" s="5">
-        <v>886.85</v>
+        <v>886.6</v>
       </c>
       <c r="E35" s="7">
-        <v>-14.55</v>
+        <v>-0.25</v>
       </c>
     </row>
     <row r="36" spans="1:5">
@@ -2133,183 +2133,217 @@
         <v>2</v>
       </c>
       <c r="C36" s="5">
-        <v>2.61</v>
+        <v>2.54</v>
       </c>
       <c r="D36" s="5">
-        <v>2.54</v>
-      </c>
-      <c r="E36" s="7">
-        <v>-0.07000000000000001</v>
+        <v>2.59</v>
+      </c>
+      <c r="E36" s="6">
+        <v>0.05</v>
       </c>
     </row>
     <row r="37" spans="1:5">
       <c r="A37" s="3" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="C37" s="5">
-        <v>35.62</v>
+        <v>60</v>
       </c>
       <c r="D37" s="5">
-        <v>31.66</v>
+        <v>40</v>
       </c>
       <c r="E37" s="7">
-        <v>-3.96</v>
+        <v>-20</v>
       </c>
     </row>
     <row r="38" spans="1:5">
       <c r="A38" s="3" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="C38" s="5">
-        <v>33.3</v>
+        <v>40</v>
       </c>
       <c r="D38" s="5">
-        <v>30.74</v>
-      </c>
-      <c r="E38" s="7">
-        <v>-2.56</v>
+        <v>60</v>
+      </c>
+      <c r="E38" s="6">
+        <v>20</v>
       </c>
     </row>
     <row r="39" spans="1:5">
       <c r="A39" s="3" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B39" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C39" s="5">
-        <v>31.19</v>
+        <v>31.66</v>
       </c>
       <c r="D39" s="5">
-        <v>29.13</v>
-      </c>
-      <c r="E39" s="7">
-        <v>-2.06</v>
+        <v>36.04</v>
+      </c>
+      <c r="E39" s="6">
+        <v>4.38</v>
       </c>
     </row>
     <row r="40" spans="1:5">
       <c r="A40" s="3" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B40" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C40" s="5">
-        <v>33.3</v>
+        <v>30.74</v>
       </c>
       <c r="D40" s="5">
-        <v>30.71</v>
+        <v>29.84</v>
       </c>
       <c r="E40" s="7">
-        <v>-2.59</v>
+        <v>-0.9</v>
       </c>
     </row>
     <row r="41" spans="1:5">
       <c r="A41" s="3" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B41" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C41" s="5">
-        <v>42.22</v>
+        <v>29.13</v>
       </c>
       <c r="D41" s="5">
-        <v>38.4</v>
+        <v>27.75</v>
       </c>
       <c r="E41" s="7">
-        <v>-3.82</v>
+        <v>-1.38</v>
       </c>
     </row>
     <row r="42" spans="1:5">
       <c r="A42" s="3" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="C42" s="5">
-        <v>47.87</v>
+        <v>30.71</v>
       </c>
       <c r="D42" s="5">
-        <v>69.59</v>
-      </c>
-      <c r="E42" s="6">
-        <v>21.72</v>
+        <v>30.66</v>
+      </c>
+      <c r="E42" s="7">
+        <v>-0.05</v>
       </c>
     </row>
     <row r="43" spans="1:5">
       <c r="A43" s="3" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="C43" s="5">
-        <v>-87.91</v>
+        <v>38.4</v>
       </c>
       <c r="D43" s="5">
-        <v>-76.40000000000001</v>
+        <v>42.41</v>
       </c>
       <c r="E43" s="6">
-        <v>11.51</v>
+        <v>4.01</v>
       </c>
     </row>
     <row r="44" spans="1:5">
       <c r="A44" s="3" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B44" s="3" t="s">
         <v>31</v>
       </c>
       <c r="C44" s="5">
-        <v>-2.69</v>
+        <v>69.59</v>
       </c>
       <c r="D44" s="5">
-        <v>-38.24</v>
+        <v>-19.45</v>
       </c>
       <c r="E44" s="7">
-        <v>-35.55</v>
+        <v>-89.04000000000001</v>
       </c>
     </row>
     <row r="45" spans="1:5">
       <c r="A45" s="3" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B45" s="3" t="s">
         <v>31</v>
       </c>
       <c r="C45" s="5">
-        <v>10.77</v>
+        <v>-76.40000000000001</v>
       </c>
       <c r="D45" s="5">
-        <v>-21.3</v>
+        <v>-89.42</v>
       </c>
       <c r="E45" s="7">
-        <v>-32.07</v>
+        <v>-13.02</v>
       </c>
     </row>
     <row r="46" spans="1:5">
       <c r="A46" s="3" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B46" s="3" t="s">
         <v>31</v>
       </c>
       <c r="C46" s="5">
-        <v>-44.09</v>
+        <v>-38.24</v>
       </c>
       <c r="D46" s="5">
+        <v>-48.93</v>
+      </c>
+      <c r="E46" s="7">
+        <v>-10.69</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5">
+      <c r="A47" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B47" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C47" s="5">
+        <v>-21.3</v>
+      </c>
+      <c r="D47" s="5">
+        <v>9.83</v>
+      </c>
+      <c r="E47" s="6">
+        <v>31.13</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5">
+      <c r="A48" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B48" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C48" s="5">
         <v>-13.04</v>
       </c>
-      <c r="E46" s="6">
-        <v>31.05</v>
+      <c r="D48" s="5">
+        <v>-11.02</v>
+      </c>
+      <c r="E48" s="6">
+        <v>2.02</v>
       </c>
     </row>
   </sheetData>
@@ -2374,13 +2408,13 @@
         <v>5</v>
       </c>
       <c r="D2" s="10">
-        <v>32.1</v>
+        <v>33.3</v>
       </c>
       <c r="E2" s="10">
         <v>20</v>
       </c>
       <c r="F2" s="10">
-        <v>-9.9</v>
+        <v>-9.199999999999999</v>
       </c>
       <c r="G2" s="10">
         <v>-7.5</v>
@@ -2508,19 +2542,19 @@
     </row>
     <row r="2" spans="1:5">
       <c r="A2" s="13">
-        <v>0.2057</v>
+        <v>0.2064</v>
       </c>
       <c r="B2" s="13">
-        <v>0.0716</v>
+        <v>0.0664</v>
       </c>
       <c r="C2" s="13">
-        <v>0.0218</v>
+        <v>0.0063</v>
       </c>
       <c r="D2" s="13">
-        <v>-0.0371</v>
+        <v>-0.0481</v>
       </c>
       <c r="E2" s="13">
-        <v>-0.2213</v>
+        <v>-0.2231</v>
       </c>
     </row>
   </sheetData>

--- a/HINDUJA_GROUP_Technical_Metrics.xlsx
+++ b/HINDUJA_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="211" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="222" uniqueCount="70">
   <si>
     <t>Symbol</t>
   </si>
@@ -163,7 +163,34 @@
     <t>▶  SIGNAL EVENTS (vs Previous Run)</t>
   </si>
   <si>
-    <t>No signal events detected since last run.</t>
+    <t>Signal</t>
+  </si>
+  <si>
+    <t>Change</t>
+  </si>
+  <si>
+    <t>Direction</t>
+  </si>
+  <si>
+    <t>Prev Value</t>
+  </si>
+  <si>
+    <t>Curr Value</t>
+  </si>
+  <si>
+    <t>RSI Oversold Recovery</t>
+  </si>
+  <si>
+    <t>29.8 → 41.5</t>
+  </si>
+  <si>
+    <t>🟢 BULLISH</t>
+  </si>
+  <si>
+    <t>29.8</t>
+  </si>
+  <si>
+    <t>41.5</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -365,17 +392,18 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -888,10 +916,10 @@
         <v>42</v>
       </c>
       <c r="C2">
-        <v>152.6</v>
+        <v>153.7</v>
       </c>
       <c r="D2">
-        <v>1.41</v>
+        <v>0.72</v>
       </c>
       <c r="E2">
         <v>208.37</v>
@@ -900,25 +928,25 @@
         <v>131.36</v>
       </c>
       <c r="G2">
-        <v>-26.76</v>
+        <v>-26.24</v>
       </c>
       <c r="H2">
-        <v>16.17</v>
+        <v>17.01</v>
       </c>
       <c r="I2">
-        <v>-4.07</v>
+        <v>-0.98</v>
       </c>
       <c r="J2">
-        <v>-9.109999999999999</v>
+        <v>-9.24</v>
       </c>
       <c r="K2">
-        <v>-8.140000000000001</v>
+        <v>-6.37</v>
       </c>
       <c r="L2">
-        <v>9.710000000000001</v>
+        <v>10.31</v>
       </c>
       <c r="M2">
-        <v>20.64</v>
+        <v>21.25</v>
       </c>
       <c r="N2">
         <v>79</v>
@@ -927,19 +955,19 @@
         <v>66</v>
       </c>
       <c r="P2">
-        <v>153.19</v>
+        <v>152.88</v>
       </c>
       <c r="Q2">
-        <v>160.37</v>
+        <v>159.6</v>
       </c>
       <c r="R2">
-        <v>166.84</v>
+        <v>166.9</v>
       </c>
       <c r="S2">
-        <v>169.82</v>
+        <v>169.76</v>
       </c>
       <c r="T2">
-        <v>-10.14</v>
+        <v>-9.460000000000001</v>
       </c>
       <c r="U2" t="s">
         <v>43</v>
@@ -954,34 +982,34 @@
         <v>0</v>
       </c>
       <c r="Y2">
-        <v>36.04</v>
+        <v>38.25</v>
       </c>
       <c r="Z2">
-        <v>-4.2</v>
+        <v>-4.14</v>
       </c>
       <c r="AA2">
-        <v>-3.32</v>
+        <v>-3.48</v>
       </c>
       <c r="AB2">
-        <v>-0.89</v>
+        <v>-0.66</v>
       </c>
       <c r="AC2">
-        <v>32.37</v>
+        <v>38.19</v>
       </c>
       <c r="AD2">
-        <v>32.08</v>
+        <v>32.86</v>
       </c>
       <c r="AE2">
-        <v>4.12</v>
+        <v>3.95</v>
       </c>
       <c r="AF2">
-        <v>-19.45</v>
+        <v>-16.72</v>
       </c>
       <c r="AG2">
-        <v>172.15</v>
+        <v>171</v>
       </c>
       <c r="AH2">
-        <v>148.59</v>
+        <v>148.2</v>
       </c>
       <c r="AI2">
         <v>164.26</v>
@@ -990,7 +1018,7 @@
         <v>45</v>
       </c>
       <c r="AK2">
-        <v>48</v>
+        <v>50.15</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1001,10 +1029,10 @@
         <v>42</v>
       </c>
       <c r="C3">
-        <v>347.7</v>
+        <v>372.45</v>
       </c>
       <c r="D3">
-        <v>-1.12</v>
+        <v>7.12</v>
       </c>
       <c r="E3">
         <v>456.15</v>
@@ -1013,46 +1041,46 @@
         <v>225</v>
       </c>
       <c r="G3">
-        <v>-23.78</v>
+        <v>-18.35</v>
       </c>
       <c r="H3">
-        <v>54.53</v>
+        <v>65.53</v>
       </c>
       <c r="I3">
-        <v>-9.48</v>
+        <v>-1.73</v>
       </c>
       <c r="J3">
-        <v>-11.23</v>
+        <v>-11.94</v>
       </c>
       <c r="K3">
-        <v>-13.95</v>
+        <v>-8.01</v>
       </c>
       <c r="L3">
-        <v>-2.15</v>
+        <v>6.96</v>
       </c>
       <c r="M3">
-        <v>6.64</v>
+        <v>7.95</v>
       </c>
       <c r="N3">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="O3">
-        <v>47</v>
+        <v>57</v>
       </c>
       <c r="P3">
-        <v>360.89</v>
+        <v>359.58</v>
       </c>
       <c r="Q3">
-        <v>409.89</v>
+        <v>407.14</v>
       </c>
       <c r="R3">
-        <v>406.74</v>
+        <v>406.25</v>
       </c>
       <c r="S3">
-        <v>338.29</v>
+        <v>338.64</v>
       </c>
       <c r="T3">
-        <v>2.78</v>
+        <v>9.98</v>
       </c>
       <c r="U3" t="s">
         <v>44</v>
@@ -1067,34 +1095,34 @@
         <v>3</v>
       </c>
       <c r="Y3">
-        <v>29.84</v>
+        <v>41.45</v>
       </c>
       <c r="Z3">
-        <v>-15.22</v>
+        <v>-14.88</v>
       </c>
       <c r="AA3">
-        <v>-6.04</v>
+        <v>-7.81</v>
       </c>
       <c r="AB3">
-        <v>-9.19</v>
+        <v>-7.08</v>
       </c>
       <c r="AC3">
-        <v>0</v>
+        <v>10.22</v>
       </c>
       <c r="AD3">
-        <v>0.09</v>
+        <v>3.41</v>
       </c>
       <c r="AE3">
-        <v>17.98</v>
+        <v>18.69</v>
       </c>
       <c r="AF3">
-        <v>-89.42</v>
+        <v>-73.84</v>
       </c>
       <c r="AG3">
-        <v>481.67</v>
+        <v>480.29</v>
       </c>
       <c r="AH3">
-        <v>338.11</v>
+        <v>333.99</v>
       </c>
       <c r="AI3">
         <v>404.18</v>
@@ -1103,7 +1131,7 @@
         <v>45</v>
       </c>
       <c r="AK3">
-        <v>52.01</v>
+        <v>48.68</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1114,10 +1142,10 @@
         <v>42</v>
       </c>
       <c r="C4">
-        <v>364.95</v>
+        <v>361.4</v>
       </c>
       <c r="D4">
-        <v>-0.57</v>
+        <v>-0.97</v>
       </c>
       <c r="E4">
         <v>534</v>
@@ -1126,46 +1154,46 @@
         <v>344.7</v>
       </c>
       <c r="G4">
-        <v>-31.66</v>
+        <v>-32.32</v>
       </c>
       <c r="H4">
-        <v>5.87</v>
+        <v>4.84</v>
       </c>
       <c r="I4">
-        <v>-3.09</v>
+        <v>-2.94</v>
       </c>
       <c r="J4">
-        <v>-7.16</v>
+        <v>-8.039999999999999</v>
       </c>
       <c r="K4">
-        <v>-11.07</v>
+        <v>-12.13</v>
       </c>
       <c r="L4">
-        <v>-26.98</v>
+        <v>-26.27</v>
       </c>
       <c r="M4">
-        <v>-22.31</v>
+        <v>-22.54</v>
       </c>
       <c r="N4">
         <v>21</v>
       </c>
       <c r="O4">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="P4">
-        <v>368.09</v>
+        <v>365.9</v>
       </c>
       <c r="Q4">
-        <v>379.69</v>
+        <v>377.79</v>
       </c>
       <c r="R4">
-        <v>398.61</v>
+        <v>397.39</v>
       </c>
       <c r="S4">
-        <v>406.85</v>
+        <v>406.43</v>
       </c>
       <c r="T4">
-        <v>-10.3</v>
+        <v>-11.08</v>
       </c>
       <c r="U4" t="s">
         <v>43</v>
@@ -1180,43 +1208,43 @@
         <v>0</v>
       </c>
       <c r="Y4">
-        <v>27.75</v>
+        <v>25.55</v>
       </c>
       <c r="Z4">
-        <v>-8.949999999999999</v>
+        <v>-9.279999999999999</v>
       </c>
       <c r="AA4">
-        <v>-8.380000000000001</v>
+        <v>-8.56</v>
       </c>
       <c r="AB4">
-        <v>-0.57</v>
+        <v>-0.71</v>
       </c>
       <c r="AC4">
-        <v>43.13</v>
+        <v>26.1</v>
       </c>
       <c r="AD4">
-        <v>33.71</v>
+        <v>34.27</v>
       </c>
       <c r="AE4">
-        <v>10.6</v>
+        <v>10.29</v>
       </c>
       <c r="AF4">
-        <v>-48.93</v>
+        <v>-5.66</v>
       </c>
       <c r="AG4">
-        <v>397.97</v>
+        <v>395.37</v>
       </c>
       <c r="AH4">
-        <v>361.4</v>
+        <v>360.22</v>
       </c>
       <c r="AI4">
-        <v>398.96</v>
+        <v>394.12</v>
       </c>
       <c r="AJ4" t="s">
         <v>45</v>
       </c>
       <c r="AK4">
-        <v>42.66</v>
+        <v>44.71</v>
       </c>
     </row>
     <row r="5" spans="1:37">
@@ -1227,58 +1255,58 @@
         <v>42</v>
       </c>
       <c r="C5">
-        <v>886.6</v>
+        <v>906.1</v>
       </c>
       <c r="D5">
-        <v>-0.03</v>
+        <v>2.2</v>
       </c>
       <c r="E5">
         <v>1069.3</v>
       </c>
       <c r="F5">
-        <v>735.55</v>
+        <v>739.3</v>
       </c>
       <c r="G5">
-        <v>-17.09</v>
+        <v>-15.26</v>
       </c>
       <c r="H5">
-        <v>20.54</v>
+        <v>22.56</v>
       </c>
       <c r="I5">
-        <v>-2.81</v>
+        <v>-0.4</v>
       </c>
       <c r="J5">
-        <v>-9.35</v>
+        <v>-9.82</v>
       </c>
       <c r="K5">
-        <v>-12.2</v>
+        <v>-11.36</v>
       </c>
       <c r="L5">
-        <v>22.56</v>
+        <v>23.19</v>
       </c>
       <c r="M5">
-        <v>-4.81</v>
+        <v>-3.78</v>
       </c>
       <c r="N5">
         <v>99</v>
       </c>
       <c r="O5">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="P5">
-        <v>892.51</v>
+        <v>891.79</v>
       </c>
       <c r="Q5">
-        <v>948.59</v>
+        <v>943.47</v>
       </c>
       <c r="R5">
-        <v>986.13</v>
+        <v>984.33</v>
       </c>
       <c r="S5">
-        <v>924.1900000000001</v>
+        <v>924.49</v>
       </c>
       <c r="T5">
-        <v>-4.07</v>
+        <v>-1.99</v>
       </c>
       <c r="U5" t="s">
         <v>43</v>
@@ -1293,34 +1321,34 @@
         <v>1</v>
       </c>
       <c r="Y5">
-        <v>30.66</v>
+        <v>38.15</v>
       </c>
       <c r="Z5">
-        <v>-28.88</v>
+        <v>-27.75</v>
       </c>
       <c r="AA5">
-        <v>-22.24</v>
+        <v>-23.34</v>
       </c>
       <c r="AB5">
-        <v>-6.65</v>
+        <v>-4.41</v>
       </c>
       <c r="AC5">
-        <v>40.63</v>
+        <v>53.27</v>
       </c>
       <c r="AD5">
-        <v>27.53</v>
+        <v>40.49</v>
       </c>
       <c r="AE5">
-        <v>21.89</v>
+        <v>22</v>
       </c>
       <c r="AF5">
-        <v>9.83</v>
+        <v>7.93</v>
       </c>
       <c r="AG5">
-        <v>1032.72</v>
+        <v>1024.66</v>
       </c>
       <c r="AH5">
-        <v>864.46</v>
+        <v>862.28</v>
       </c>
       <c r="AI5">
         <v>956.15</v>
@@ -1329,7 +1357,7 @@
         <v>45</v>
       </c>
       <c r="AK5">
-        <v>52.63</v>
+        <v>52.74</v>
       </c>
     </row>
     <row r="6" spans="1:37">
@@ -1340,10 +1368,10 @@
         <v>42</v>
       </c>
       <c r="C6">
-        <v>2.59</v>
+        <v>2.57</v>
       </c>
       <c r="D6">
-        <v>1.97</v>
+        <v>-0.77</v>
       </c>
       <c r="E6">
         <v>3.38</v>
@@ -1352,46 +1380,46 @@
         <v>1.84</v>
       </c>
       <c r="G6">
-        <v>-23.37</v>
+        <v>-23.96</v>
       </c>
       <c r="H6">
-        <v>40.76</v>
+        <v>39.67</v>
       </c>
       <c r="I6">
-        <v>-0.77</v>
+        <v>-3.75</v>
       </c>
       <c r="J6">
-        <v>-9.119999999999999</v>
+        <v>-9.19</v>
       </c>
       <c r="K6">
-        <v>7.92</v>
+        <v>7.98</v>
       </c>
       <c r="L6">
-        <v>-22.69</v>
+        <v>-23.05</v>
       </c>
       <c r="M6">
-        <v>0.63</v>
+        <v>0.47</v>
       </c>
       <c r="N6">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="O6">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="P6">
-        <v>2.61</v>
+        <v>2.59</v>
       </c>
       <c r="Q6">
-        <v>2.76</v>
+        <v>2.75</v>
       </c>
       <c r="R6">
         <v>2.62</v>
       </c>
       <c r="S6">
-        <v>2.66</v>
+        <v>2.65</v>
       </c>
       <c r="T6">
-        <v>-2.45</v>
+        <v>-3.13</v>
       </c>
       <c r="U6" t="s">
         <v>44</v>
@@ -1406,34 +1434,34 @@
         <v>1</v>
       </c>
       <c r="Y6">
-        <v>42.41</v>
+        <v>41.25</v>
       </c>
       <c r="Z6">
-        <v>-0.03</v>
+        <v>-0.04</v>
       </c>
       <c r="AA6">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="AB6">
         <v>-0.04</v>
       </c>
       <c r="AC6">
-        <v>8.279999999999999</v>
+        <v>11.52</v>
       </c>
       <c r="AD6">
-        <v>7.43</v>
+        <v>7.86</v>
       </c>
       <c r="AE6">
         <v>0.14</v>
       </c>
       <c r="AF6">
-        <v>-11.02</v>
+        <v>-5.99</v>
       </c>
       <c r="AG6">
         <v>3.02</v>
       </c>
       <c r="AH6">
-        <v>2.51</v>
+        <v>2.48</v>
       </c>
       <c r="AI6">
         <v>2.99</v>
@@ -1442,7 +1470,7 @@
         <v>45</v>
       </c>
       <c r="AK6">
-        <v>31.37</v>
+        <v>30.46</v>
       </c>
     </row>
   </sheetData>
@@ -1603,12 +1631,47 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="3" t="s">
         <v>47</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
+      <c r="A3" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>56</v>
       </c>
     </row>
     <row r="5" spans="1:6">
       <c r="A5" s="2" t="s">
-        <v>48</v>
+        <v>57</v>
       </c>
       <c r="B5" s="2"/>
       <c r="C5" s="2"/>
@@ -1616,734 +1679,734 @@
       <c r="E5" s="2"/>
     </row>
     <row r="6" spans="1:6">
-      <c r="A6" s="4" t="s">
+      <c r="A6" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B6" s="4" t="s">
-        <v>49</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="D6" s="4" t="s">
-        <v>51</v>
-      </c>
-      <c r="E6" s="4" t="s">
-        <v>52</v>
+      <c r="B6" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>61</v>
       </c>
     </row>
     <row r="7" spans="1:6">
-      <c r="A7" s="3" t="s">
+      <c r="A7" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B7" s="3" t="s">
+      <c r="B7" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C7" s="5">
-        <v>-11.76</v>
-      </c>
-      <c r="D7" s="5">
+      <c r="C7" s="6">
         <v>-9.109999999999999</v>
       </c>
-      <c r="E7" s="6">
-        <v>2.65</v>
+      <c r="D7" s="6">
+        <v>-9.24</v>
+      </c>
+      <c r="E7" s="7">
+        <v>-0.13</v>
       </c>
     </row>
     <row r="8" spans="1:6">
-      <c r="A8" s="3" t="s">
+      <c r="A8" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B8" s="3" t="s">
+      <c r="B8" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C8" s="5">
-        <v>-9.220000000000001</v>
-      </c>
-      <c r="D8" s="5">
+      <c r="C8" s="6">
         <v>-11.23</v>
       </c>
+      <c r="D8" s="6">
+        <v>-11.94</v>
+      </c>
       <c r="E8" s="7">
-        <v>-2.01</v>
+        <v>-0.71</v>
       </c>
     </row>
     <row r="9" spans="1:6">
-      <c r="A9" s="3" t="s">
+      <c r="A9" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B9" s="3" t="s">
+      <c r="B9" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C9" s="5">
-        <v>-6.77</v>
-      </c>
-      <c r="D9" s="5">
+      <c r="C9" s="6">
         <v>-7.16</v>
       </c>
+      <c r="D9" s="6">
+        <v>-8.039999999999999</v>
+      </c>
       <c r="E9" s="7">
-        <v>-0.39</v>
+        <v>-0.88</v>
       </c>
     </row>
     <row r="10" spans="1:6">
-      <c r="A10" s="3" t="s">
+      <c r="A10" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="B10" s="3" t="s">
+      <c r="B10" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C10" s="5">
-        <v>-10.65</v>
-      </c>
-      <c r="D10" s="5">
+      <c r="C10" s="6">
         <v>-9.35</v>
       </c>
-      <c r="E10" s="6">
-        <v>1.3</v>
+      <c r="D10" s="6">
+        <v>-9.82</v>
+      </c>
+      <c r="E10" s="7">
+        <v>-0.47</v>
       </c>
     </row>
     <row r="11" spans="1:6">
-      <c r="A11" s="3" t="s">
+      <c r="A11" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B11" s="3" t="s">
+      <c r="B11" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C11" s="5">
-        <v>-10.88</v>
-      </c>
-      <c r="D11" s="5">
+      <c r="C11" s="6">
         <v>-9.119999999999999</v>
       </c>
-      <c r="E11" s="6">
-        <v>1.76</v>
+      <c r="D11" s="6">
+        <v>-9.19</v>
+      </c>
+      <c r="E11" s="7">
+        <v>-0.07000000000000001</v>
       </c>
     </row>
     <row r="12" spans="1:6">
-      <c r="A12" s="3" t="s">
+      <c r="A12" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B12" s="3" t="s">
+      <c r="B12" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="C12" s="5">
-        <v>-4.34</v>
-      </c>
-      <c r="D12" s="5">
+      <c r="C12" s="6">
         <v>-4.07</v>
       </c>
-      <c r="E12" s="6">
-        <v>0.27</v>
+      <c r="D12" s="6">
+        <v>-0.98</v>
+      </c>
+      <c r="E12" s="8">
+        <v>3.09</v>
       </c>
     </row>
     <row r="13" spans="1:6">
-      <c r="A13" s="3" t="s">
+      <c r="A13" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B13" s="3" t="s">
+      <c r="B13" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="C13" s="5">
-        <v>-7.52</v>
-      </c>
-      <c r="D13" s="5">
+      <c r="C13" s="6">
         <v>-9.48</v>
       </c>
-      <c r="E13" s="7">
-        <v>-1.96</v>
+      <c r="D13" s="6">
+        <v>-1.73</v>
+      </c>
+      <c r="E13" s="8">
+        <v>7.75</v>
       </c>
     </row>
     <row r="14" spans="1:6">
-      <c r="A14" s="3" t="s">
+      <c r="A14" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B14" s="3" t="s">
+      <c r="B14" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="C14" s="5">
-        <v>-2</v>
-      </c>
-      <c r="D14" s="5">
+      <c r="C14" s="6">
         <v>-3.09</v>
       </c>
-      <c r="E14" s="7">
-        <v>-1.09</v>
+      <c r="D14" s="6">
+        <v>-2.94</v>
+      </c>
+      <c r="E14" s="8">
+        <v>0.15</v>
       </c>
     </row>
     <row r="15" spans="1:6">
-      <c r="A15" s="3" t="s">
+      <c r="A15" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="B15" s="3" t="s">
+      <c r="B15" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="C15" s="5">
+      <c r="C15" s="6">
+        <v>-2.81</v>
+      </c>
+      <c r="D15" s="6">
+        <v>-0.4</v>
+      </c>
+      <c r="E15" s="8">
+        <v>2.41</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6">
+      <c r="A16" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B16" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C16" s="6">
+        <v>-0.77</v>
+      </c>
+      <c r="D16" s="6">
+        <v>-3.75</v>
+      </c>
+      <c r="E16" s="7">
+        <v>-2.98</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B17" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C17" s="6">
+        <v>9.710000000000001</v>
+      </c>
+      <c r="D17" s="6">
+        <v>10.31</v>
+      </c>
+      <c r="E17" s="8">
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B18" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C18" s="6">
+        <v>-2.15</v>
+      </c>
+      <c r="D18" s="6">
+        <v>6.96</v>
+      </c>
+      <c r="E18" s="8">
+        <v>9.109999999999999</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B19" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C19" s="6">
+        <v>-26.98</v>
+      </c>
+      <c r="D19" s="6">
+        <v>-26.27</v>
+      </c>
+      <c r="E19" s="8">
+        <v>0.71</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B20" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C20" s="6">
+        <v>22.56</v>
+      </c>
+      <c r="D20" s="6">
+        <v>23.19</v>
+      </c>
+      <c r="E20" s="8">
+        <v>0.63</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B21" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C21" s="6">
+        <v>-22.69</v>
+      </c>
+      <c r="D21" s="6">
+        <v>-23.05</v>
+      </c>
+      <c r="E21" s="7">
+        <v>-0.36</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B22" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C22" s="6">
+        <v>-8.140000000000001</v>
+      </c>
+      <c r="D22" s="6">
+        <v>-6.37</v>
+      </c>
+      <c r="E22" s="8">
+        <v>1.77</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B23" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C23" s="6">
+        <v>-13.95</v>
+      </c>
+      <c r="D23" s="6">
+        <v>-8.01</v>
+      </c>
+      <c r="E23" s="8">
+        <v>5.94</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5">
+      <c r="A24" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B24" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C24" s="6">
+        <v>-11.07</v>
+      </c>
+      <c r="D24" s="6">
+        <v>-12.13</v>
+      </c>
+      <c r="E24" s="7">
+        <v>-1.06</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5">
+      <c r="A25" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B25" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C25" s="6">
+        <v>-12.2</v>
+      </c>
+      <c r="D25" s="6">
+        <v>-11.36</v>
+      </c>
+      <c r="E25" s="8">
+        <v>0.84</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
+      <c r="A26" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B26" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C26" s="6">
+        <v>7.92</v>
+      </c>
+      <c r="D26" s="6">
+        <v>7.98</v>
+      </c>
+      <c r="E26" s="8">
+        <v>0.06</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5">
+      <c r="A27" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B27" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C27" s="6">
+        <v>-26.76</v>
+      </c>
+      <c r="D27" s="6">
+        <v>-26.24</v>
+      </c>
+      <c r="E27" s="8">
+        <v>0.52</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5">
+      <c r="A28" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B28" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C28" s="6">
+        <v>-23.78</v>
+      </c>
+      <c r="D28" s="6">
+        <v>-18.35</v>
+      </c>
+      <c r="E28" s="8">
+        <v>5.43</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5">
+      <c r="A29" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B29" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C29" s="6">
+        <v>-31.66</v>
+      </c>
+      <c r="D29" s="6">
+        <v>-32.32</v>
+      </c>
+      <c r="E29" s="7">
+        <v>-0.66</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5">
+      <c r="A30" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B30" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C30" s="6">
+        <v>-17.09</v>
+      </c>
+      <c r="D30" s="6">
+        <v>-15.26</v>
+      </c>
+      <c r="E30" s="8">
+        <v>1.83</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5">
+      <c r="A31" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B31" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C31" s="6">
+        <v>-23.37</v>
+      </c>
+      <c r="D31" s="6">
+        <v>-23.96</v>
+      </c>
+      <c r="E31" s="7">
+        <v>-0.59</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5">
+      <c r="A32" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B32" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C32" s="6">
+        <v>152.6</v>
+      </c>
+      <c r="D32" s="6">
+        <v>153.7</v>
+      </c>
+      <c r="E32" s="8">
+        <v>1.1</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5">
+      <c r="A33" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B33" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C33" s="6">
+        <v>347.7</v>
+      </c>
+      <c r="D33" s="6">
+        <v>372.45</v>
+      </c>
+      <c r="E33" s="8">
+        <v>24.75</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5">
+      <c r="A34" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B34" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C34" s="6">
+        <v>364.95</v>
+      </c>
+      <c r="D34" s="6">
+        <v>361.4</v>
+      </c>
+      <c r="E34" s="7">
         <v>-3.55</v>
       </c>
-      <c r="D15" s="5">
-        <v>-2.81</v>
-      </c>
-      <c r="E15" s="6">
-        <v>0.74</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
-      <c r="A16" s="3" t="s">
+    </row>
+    <row r="35" spans="1:5">
+      <c r="A35" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B35" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C35" s="6">
+        <v>886.6</v>
+      </c>
+      <c r="D35" s="6">
+        <v>906.1</v>
+      </c>
+      <c r="E35" s="8">
+        <v>19.5</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5">
+      <c r="A36" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B16" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C16" s="5">
-        <v>-5.58</v>
-      </c>
-      <c r="D16" s="5">
-        <v>-0.77</v>
-      </c>
-      <c r="E16" s="6">
-        <v>4.81</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5">
-      <c r="A17" s="3" t="s">
+      <c r="B36" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C36" s="6">
+        <v>2.59</v>
+      </c>
+      <c r="D36" s="6">
+        <v>2.57</v>
+      </c>
+      <c r="E36" s="7">
+        <v>-0.02</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5">
+      <c r="A37" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B37" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C37" s="6">
+        <v>40</v>
+      </c>
+      <c r="D37" s="6">
+        <v>60</v>
+      </c>
+      <c r="E37" s="8">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5">
+      <c r="A38" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B38" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C38" s="6">
+        <v>60</v>
+      </c>
+      <c r="D38" s="6">
+        <v>40</v>
+      </c>
+      <c r="E38" s="7">
+        <v>-20</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5">
+      <c r="A39" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B17" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C17" s="5">
-        <v>8.56</v>
-      </c>
-      <c r="D17" s="5">
-        <v>9.710000000000001</v>
-      </c>
-      <c r="E17" s="6">
-        <v>1.15</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5">
-      <c r="A18" s="3" t="s">
+      <c r="B39" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C39" s="6">
+        <v>36.04</v>
+      </c>
+      <c r="D39" s="6">
+        <v>38.25</v>
+      </c>
+      <c r="E39" s="8">
+        <v>2.21</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5">
+      <c r="A40" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B18" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C18" s="5">
-        <v>0.03</v>
-      </c>
-      <c r="D18" s="5">
-        <v>-2.15</v>
-      </c>
-      <c r="E18" s="7">
-        <v>-2.18</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5">
-      <c r="A19" s="3" t="s">
+      <c r="B40" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C40" s="6">
+        <v>29.84</v>
+      </c>
+      <c r="D40" s="6">
+        <v>41.45</v>
+      </c>
+      <c r="E40" s="8">
+        <v>11.61</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5">
+      <c r="A41" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B19" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C19" s="5">
-        <v>-27.6</v>
-      </c>
-      <c r="D19" s="5">
-        <v>-26.98</v>
-      </c>
-      <c r="E19" s="6">
-        <v>0.62</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5">
-      <c r="A20" s="3" t="s">
+      <c r="B41" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C41" s="6">
+        <v>27.75</v>
+      </c>
+      <c r="D41" s="6">
+        <v>25.55</v>
+      </c>
+      <c r="E41" s="7">
+        <v>-2.2</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5">
+      <c r="A42" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="B20" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C20" s="5">
-        <v>24.43</v>
-      </c>
-      <c r="D20" s="5">
-        <v>22.56</v>
-      </c>
-      <c r="E20" s="7">
-        <v>-1.87</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5">
-      <c r="A21" s="3" t="s">
+      <c r="B42" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C42" s="6">
+        <v>30.66</v>
+      </c>
+      <c r="D42" s="6">
+        <v>38.15</v>
+      </c>
+      <c r="E42" s="8">
+        <v>7.49</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5">
+      <c r="A43" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B21" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C21" s="5">
-        <v>-24.63</v>
-      </c>
-      <c r="D21" s="5">
-        <v>-22.69</v>
-      </c>
-      <c r="E21" s="6">
-        <v>1.94</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5">
-      <c r="A22" s="3" t="s">
+      <c r="B43" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C43" s="6">
+        <v>42.41</v>
+      </c>
+      <c r="D43" s="6">
+        <v>41.25</v>
+      </c>
+      <c r="E43" s="7">
+        <v>-1.16</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5">
+      <c r="A44" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B22" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C22" s="5">
-        <v>-8.44</v>
-      </c>
-      <c r="D22" s="5">
-        <v>-8.140000000000001</v>
-      </c>
-      <c r="E22" s="6">
-        <v>0.3</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5">
-      <c r="A23" s="3" t="s">
+      <c r="B44" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C44" s="6">
+        <v>-19.45</v>
+      </c>
+      <c r="D44" s="6">
+        <v>-16.72</v>
+      </c>
+      <c r="E44" s="8">
+        <v>2.73</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5">
+      <c r="A45" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B23" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C23" s="5">
-        <v>-12.85</v>
-      </c>
-      <c r="D23" s="5">
-        <v>-13.95</v>
-      </c>
-      <c r="E23" s="7">
-        <v>-1.1</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5">
-      <c r="A24" s="3" t="s">
+      <c r="B45" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C45" s="6">
+        <v>-89.42</v>
+      </c>
+      <c r="D45" s="6">
+        <v>-73.84</v>
+      </c>
+      <c r="E45" s="8">
+        <v>15.58</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5">
+      <c r="A46" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B24" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C24" s="5">
-        <v>-11.89</v>
-      </c>
-      <c r="D24" s="5">
-        <v>-11.07</v>
-      </c>
-      <c r="E24" s="6">
-        <v>0.82</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5">
-      <c r="A25" s="3" t="s">
+      <c r="B46" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C46" s="6">
+        <v>-48.93</v>
+      </c>
+      <c r="D46" s="6">
+        <v>-5.66</v>
+      </c>
+      <c r="E46" s="8">
+        <v>43.27</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5">
+      <c r="A47" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="B25" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C25" s="5">
-        <v>-8.98</v>
-      </c>
-      <c r="D25" s="5">
-        <v>-12.2</v>
-      </c>
-      <c r="E25" s="7">
-        <v>-3.22</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5">
-      <c r="A26" s="3" t="s">
+      <c r="B47" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C47" s="6">
+        <v>9.83</v>
+      </c>
+      <c r="D47" s="6">
+        <v>7.93</v>
+      </c>
+      <c r="E47" s="7">
+        <v>-1.9</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5">
+      <c r="A48" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B26" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C26" s="5">
-        <v>4.53</v>
-      </c>
-      <c r="D26" s="5">
-        <v>7.92</v>
-      </c>
-      <c r="E26" s="6">
-        <v>3.39</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5">
-      <c r="A27" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B27" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C27" s="5">
-        <v>-27.78</v>
-      </c>
-      <c r="D27" s="5">
-        <v>-26.76</v>
-      </c>
-      <c r="E27" s="6">
-        <v>1.02</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5">
-      <c r="A28" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="B28" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C28" s="5">
-        <v>-22.91</v>
-      </c>
-      <c r="D28" s="5">
-        <v>-23.78</v>
-      </c>
-      <c r="E28" s="7">
-        <v>-0.87</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5">
-      <c r="A29" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="B29" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C29" s="5">
-        <v>-31.26</v>
-      </c>
-      <c r="D29" s="5">
-        <v>-31.66</v>
-      </c>
-      <c r="E29" s="7">
-        <v>-0.4</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5">
-      <c r="A30" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="B30" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C30" s="5">
-        <v>-17.06</v>
-      </c>
-      <c r="D30" s="5">
-        <v>-17.09</v>
-      </c>
-      <c r="E30" s="7">
-        <v>-0.03</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5">
-      <c r="A31" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="B31" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C31" s="5">
-        <v>-24.85</v>
-      </c>
-      <c r="D31" s="5">
-        <v>-23.37</v>
-      </c>
-      <c r="E31" s="6">
-        <v>1.48</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5">
-      <c r="A32" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B32" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C32" s="5">
-        <v>150.48</v>
-      </c>
-      <c r="D32" s="5">
-        <v>152.6</v>
-      </c>
-      <c r="E32" s="6">
-        <v>2.12</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5">
-      <c r="A33" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="B33" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C33" s="5">
-        <v>351.65</v>
-      </c>
-      <c r="D33" s="5">
-        <v>347.7</v>
-      </c>
-      <c r="E33" s="7">
-        <v>-3.95</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5">
-      <c r="A34" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="B34" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C34" s="5">
-        <v>367.05</v>
-      </c>
-      <c r="D34" s="5">
-        <v>364.95</v>
-      </c>
-      <c r="E34" s="7">
-        <v>-2.1</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5">
-      <c r="A35" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="B35" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C35" s="5">
-        <v>886.85</v>
-      </c>
-      <c r="D35" s="5">
-        <v>886.6</v>
-      </c>
-      <c r="E35" s="7">
-        <v>-0.25</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5">
-      <c r="A36" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="B36" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C36" s="5">
-        <v>2.54</v>
-      </c>
-      <c r="D36" s="5">
-        <v>2.59</v>
-      </c>
-      <c r="E36" s="6">
-        <v>0.05</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5">
-      <c r="A37" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="B37" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="C37" s="5">
-        <v>60</v>
-      </c>
-      <c r="D37" s="5">
-        <v>40</v>
-      </c>
-      <c r="E37" s="7">
-        <v>-20</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5">
-      <c r="A38" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="B38" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="C38" s="5">
-        <v>40</v>
-      </c>
-      <c r="D38" s="5">
-        <v>60</v>
-      </c>
-      <c r="E38" s="6">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5">
-      <c r="A39" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B39" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C39" s="5">
-        <v>31.66</v>
-      </c>
-      <c r="D39" s="5">
-        <v>36.04</v>
-      </c>
-      <c r="E39" s="6">
-        <v>4.38</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5">
-      <c r="A40" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="B40" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C40" s="5">
-        <v>30.74</v>
-      </c>
-      <c r="D40" s="5">
-        <v>29.84</v>
-      </c>
-      <c r="E40" s="7">
-        <v>-0.9</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5">
-      <c r="A41" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="B41" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C41" s="5">
-        <v>29.13</v>
-      </c>
-      <c r="D41" s="5">
-        <v>27.75</v>
-      </c>
-      <c r="E41" s="7">
-        <v>-1.38</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5">
-      <c r="A42" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="B42" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C42" s="5">
-        <v>30.71</v>
-      </c>
-      <c r="D42" s="5">
-        <v>30.66</v>
-      </c>
-      <c r="E42" s="7">
-        <v>-0.05</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5">
-      <c r="A43" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="B43" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C43" s="5">
-        <v>38.4</v>
-      </c>
-      <c r="D43" s="5">
-        <v>42.41</v>
-      </c>
-      <c r="E43" s="6">
-        <v>4.01</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5">
-      <c r="A44" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B44" s="3" t="s">
+      <c r="B48" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="C44" s="5">
-        <v>69.59</v>
-      </c>
-      <c r="D44" s="5">
-        <v>-19.45</v>
-      </c>
-      <c r="E44" s="7">
-        <v>-89.04000000000001</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5">
-      <c r="A45" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="B45" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C45" s="5">
-        <v>-76.40000000000001</v>
-      </c>
-      <c r="D45" s="5">
-        <v>-89.42</v>
-      </c>
-      <c r="E45" s="7">
-        <v>-13.02</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5">
-      <c r="A46" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="B46" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C46" s="5">
-        <v>-38.24</v>
-      </c>
-      <c r="D46" s="5">
-        <v>-48.93</v>
-      </c>
-      <c r="E46" s="7">
-        <v>-10.69</v>
-      </c>
-    </row>
-    <row r="47" spans="1:5">
-      <c r="A47" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="B47" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C47" s="5">
-        <v>-21.3</v>
-      </c>
-      <c r="D47" s="5">
-        <v>9.83</v>
-      </c>
-      <c r="E47" s="6">
-        <v>31.13</v>
-      </c>
-    </row>
-    <row r="48" spans="1:5">
-      <c r="A48" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="B48" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C48" s="5">
-        <v>-13.04</v>
-      </c>
-      <c r="D48" s="5">
+      <c r="C48" s="6">
         <v>-11.02</v>
       </c>
-      <c r="E48" s="6">
-        <v>2.02</v>
+      <c r="D48" s="6">
+        <v>-5.99</v>
+      </c>
+      <c r="E48" s="8">
+        <v>5.03</v>
       </c>
     </row>
   </sheetData>
@@ -2369,60 +2432,60 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="28" customHeight="1">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="8" t="s">
-        <v>53</v>
-      </c>
-      <c r="C1" s="8" t="s">
-        <v>54</v>
-      </c>
-      <c r="D1" s="8" t="s">
-        <v>55</v>
-      </c>
-      <c r="E1" s="8" t="s">
-        <v>56</v>
-      </c>
-      <c r="F1" s="8" t="s">
-        <v>57</v>
-      </c>
-      <c r="G1" s="8" t="s">
-        <v>58</v>
-      </c>
-      <c r="H1" s="8" t="s">
-        <v>59</v>
-      </c>
-      <c r="I1" s="8" t="s">
-        <v>60</v>
+      <c r="B1" s="9" t="s">
+        <v>62</v>
+      </c>
+      <c r="C1" s="9" t="s">
+        <v>63</v>
+      </c>
+      <c r="D1" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="E1" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="F1" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="G1" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="H1" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="I1" s="9" t="s">
+        <v>69</v>
       </c>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="9" t="s">
+      <c r="A2" s="10" t="s">
         <v>42</v>
       </c>
-      <c r="B2" s="10">
+      <c r="B2" s="11">
         <v>41.92</v>
       </c>
-      <c r="C2" s="11">
+      <c r="C2" s="12">
         <v>5</v>
       </c>
-      <c r="D2" s="10">
-        <v>33.3</v>
-      </c>
-      <c r="E2" s="10">
+      <c r="D2" s="11">
+        <v>36.9</v>
+      </c>
+      <c r="E2" s="11">
         <v>20</v>
       </c>
-      <c r="F2" s="10">
-        <v>-9.199999999999999</v>
-      </c>
-      <c r="G2" s="10">
-        <v>-7.5</v>
-      </c>
-      <c r="H2" s="10">
+      <c r="F2" s="11">
+        <v>-9.6</v>
+      </c>
+      <c r="G2" s="11">
+        <v>-6</v>
+      </c>
+      <c r="H2" s="11">
         <v>59.8</v>
       </c>
-      <c r="I2" s="10">
+      <c r="I2" s="11">
         <v>20</v>
       </c>
     </row>
@@ -2524,37 +2587,37 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
-      <c r="A1" s="12" t="s">
+      <c r="A1" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="B1" s="12" t="s">
+      <c r="B1" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="C1" s="12" t="s">
+      <c r="C1" s="13" t="s">
         <v>41</v>
       </c>
-      <c r="D1" s="12" t="s">
+      <c r="D1" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="E1" s="12" t="s">
+      <c r="E1" s="13" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="2" spans="1:5">
-      <c r="A2" s="13">
-        <v>0.2064</v>
-      </c>
-      <c r="B2" s="13">
-        <v>0.0664</v>
-      </c>
-      <c r="C2" s="13">
-        <v>0.0063</v>
-      </c>
-      <c r="D2" s="13">
-        <v>-0.0481</v>
-      </c>
-      <c r="E2" s="13">
-        <v>-0.2231</v>
+      <c r="A2" s="14">
+        <v>0.2125</v>
+      </c>
+      <c r="B2" s="14">
+        <v>0.0795</v>
+      </c>
+      <c r="C2" s="14">
+        <v>0.004699999999999999</v>
+      </c>
+      <c r="D2" s="14">
+        <v>-0.0378</v>
+      </c>
+      <c r="E2" s="14">
+        <v>-0.2254</v>
       </c>
     </row>
   </sheetData>

--- a/HINDUJA_GROUP_Technical_Metrics.xlsx
+++ b/HINDUJA_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="222" uniqueCount="70">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="224" uniqueCount="68">
   <si>
     <t>Symbol</t>
   </si>
@@ -178,19 +178,13 @@
     <t>Curr Value</t>
   </si>
   <si>
-    <t>RSI Oversold Recovery</t>
-  </si>
-  <si>
-    <t>29.8 → 41.5</t>
-  </si>
-  <si>
-    <t>🟢 BULLISH</t>
-  </si>
-  <si>
-    <t>29.8</t>
-  </si>
-  <si>
-    <t>41.5</t>
+    <t>Yes → No</t>
+  </si>
+  <si>
+    <t>🔴 BEARISH</t>
+  </si>
+  <si>
+    <t>20 DMA &gt; 50 DMA</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -276,14 +270,14 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FF9C0006"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FF006100"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -316,13 +310,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -402,8 +396,8 @@
     <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -916,10 +910,10 @@
         <v>42</v>
       </c>
       <c r="C2">
-        <v>153.7</v>
+        <v>149.2</v>
       </c>
       <c r="D2">
-        <v>0.72</v>
+        <v>-2.93</v>
       </c>
       <c r="E2">
         <v>208.37</v>
@@ -928,46 +922,46 @@
         <v>131.36</v>
       </c>
       <c r="G2">
-        <v>-26.24</v>
+        <v>-28.4</v>
       </c>
       <c r="H2">
-        <v>17.01</v>
+        <v>13.58</v>
       </c>
       <c r="I2">
-        <v>-0.98</v>
+        <v>-2.76</v>
       </c>
       <c r="J2">
-        <v>-9.24</v>
+        <v>-11.72</v>
       </c>
       <c r="K2">
-        <v>-6.37</v>
+        <v>-4.49</v>
       </c>
       <c r="L2">
-        <v>10.31</v>
+        <v>8.17</v>
       </c>
       <c r="M2">
-        <v>21.25</v>
+        <v>19.45</v>
       </c>
       <c r="N2">
         <v>79</v>
       </c>
       <c r="O2">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="P2">
-        <v>152.88</v>
+        <v>152.03</v>
       </c>
       <c r="Q2">
-        <v>159.6</v>
+        <v>158.56</v>
       </c>
       <c r="R2">
-        <v>166.9</v>
+        <v>166.78</v>
       </c>
       <c r="S2">
-        <v>169.76</v>
+        <v>169.69</v>
       </c>
       <c r="T2">
-        <v>-9.460000000000001</v>
+        <v>-12.08</v>
       </c>
       <c r="U2" t="s">
         <v>43</v>
@@ -982,43 +976,43 @@
         <v>0</v>
       </c>
       <c r="Y2">
-        <v>38.25</v>
+        <v>33.19</v>
       </c>
       <c r="Z2">
-        <v>-4.14</v>
+        <v>-4.4</v>
       </c>
       <c r="AA2">
-        <v>-3.48</v>
+        <v>-3.66</v>
       </c>
       <c r="AB2">
-        <v>-0.66</v>
+        <v>-0.74</v>
       </c>
       <c r="AC2">
-        <v>38.19</v>
+        <v>37.51</v>
       </c>
       <c r="AD2">
-        <v>32.86</v>
+        <v>36.02</v>
       </c>
       <c r="AE2">
-        <v>3.95</v>
+        <v>4.03</v>
       </c>
       <c r="AF2">
-        <v>-16.72</v>
+        <v>-0.98</v>
       </c>
       <c r="AG2">
-        <v>171</v>
+        <v>169.76</v>
       </c>
       <c r="AH2">
-        <v>148.2</v>
+        <v>147.36</v>
       </c>
       <c r="AI2">
-        <v>164.26</v>
+        <v>163.11</v>
       </c>
       <c r="AJ2" t="s">
         <v>45</v>
       </c>
       <c r="AK2">
-        <v>50.15</v>
+        <v>53.22</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1029,10 +1023,10 @@
         <v>42</v>
       </c>
       <c r="C3">
-        <v>372.45</v>
+        <v>367.85</v>
       </c>
       <c r="D3">
-        <v>7.12</v>
+        <v>-1.24</v>
       </c>
       <c r="E3">
         <v>456.15</v>
@@ -1041,88 +1035,88 @@
         <v>225</v>
       </c>
       <c r="G3">
-        <v>-18.35</v>
+        <v>-19.36</v>
       </c>
       <c r="H3">
-        <v>65.53</v>
+        <v>63.49</v>
       </c>
       <c r="I3">
-        <v>-1.73</v>
+        <v>1.15</v>
       </c>
       <c r="J3">
-        <v>-11.94</v>
+        <v>-13.94</v>
       </c>
       <c r="K3">
-        <v>-8.01</v>
+        <v>-6.76</v>
       </c>
       <c r="L3">
-        <v>6.96</v>
+        <v>2.22</v>
       </c>
       <c r="M3">
-        <v>7.95</v>
+        <v>7.26</v>
       </c>
       <c r="N3">
         <v>60</v>
       </c>
       <c r="O3">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="P3">
-        <v>359.58</v>
+        <v>360.42</v>
       </c>
       <c r="Q3">
-        <v>407.14</v>
+        <v>403.69</v>
       </c>
       <c r="R3">
-        <v>406.25</v>
+        <v>405.69</v>
       </c>
       <c r="S3">
-        <v>338.64</v>
+        <v>339</v>
       </c>
       <c r="T3">
-        <v>9.98</v>
+        <v>8.51</v>
       </c>
       <c r="U3" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="V3" t="s">
         <v>44</v>
       </c>
       <c r="W3" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="X3">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Y3">
-        <v>41.45</v>
+        <v>40.12</v>
       </c>
       <c r="Z3">
-        <v>-14.88</v>
+        <v>-14.81</v>
       </c>
       <c r="AA3">
-        <v>-7.81</v>
+        <v>-9.210000000000001</v>
       </c>
       <c r="AB3">
-        <v>-7.08</v>
+        <v>-5.61</v>
       </c>
       <c r="AC3">
-        <v>10.22</v>
+        <v>19.26</v>
       </c>
       <c r="AD3">
-        <v>3.41</v>
+        <v>9.83</v>
       </c>
       <c r="AE3">
-        <v>18.69</v>
+        <v>18.31</v>
       </c>
       <c r="AF3">
-        <v>-73.84</v>
+        <v>-69.92</v>
       </c>
       <c r="AG3">
-        <v>480.29</v>
+        <v>477.43</v>
       </c>
       <c r="AH3">
-        <v>333.99</v>
+        <v>329.94</v>
       </c>
       <c r="AI3">
         <v>404.18</v>
@@ -1131,7 +1125,7 @@
         <v>45</v>
       </c>
       <c r="AK3">
-        <v>48.68</v>
+        <v>45.8</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1142,10 +1136,10 @@
         <v>42</v>
       </c>
       <c r="C4">
-        <v>361.4</v>
+        <v>363</v>
       </c>
       <c r="D4">
-        <v>-0.97</v>
+        <v>0.44</v>
       </c>
       <c r="E4">
         <v>534</v>
@@ -1154,46 +1148,46 @@
         <v>344.7</v>
       </c>
       <c r="G4">
-        <v>-32.32</v>
+        <v>-32.02</v>
       </c>
       <c r="H4">
-        <v>4.84</v>
+        <v>5.31</v>
       </c>
       <c r="I4">
-        <v>-2.94</v>
+        <v>-0.83</v>
       </c>
       <c r="J4">
-        <v>-8.039999999999999</v>
+        <v>-9.08</v>
       </c>
       <c r="K4">
-        <v>-12.13</v>
+        <v>-10.57</v>
       </c>
       <c r="L4">
-        <v>-26.27</v>
+        <v>-26.9</v>
       </c>
       <c r="M4">
-        <v>-22.54</v>
+        <v>-22.61</v>
       </c>
       <c r="N4">
         <v>21</v>
       </c>
       <c r="O4">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="P4">
-        <v>365.9</v>
+        <v>365.29</v>
       </c>
       <c r="Q4">
-        <v>377.79</v>
+        <v>376.17</v>
       </c>
       <c r="R4">
-        <v>397.39</v>
+        <v>396.2</v>
       </c>
       <c r="S4">
-        <v>406.43</v>
+        <v>406.05</v>
       </c>
       <c r="T4">
-        <v>-11.08</v>
+        <v>-10.6</v>
       </c>
       <c r="U4" t="s">
         <v>43</v>
@@ -1208,43 +1202,43 @@
         <v>0</v>
       </c>
       <c r="Y4">
-        <v>25.55</v>
+        <v>28.31</v>
       </c>
       <c r="Z4">
-        <v>-9.279999999999999</v>
+        <v>-9.289999999999999</v>
       </c>
       <c r="AA4">
-        <v>-8.56</v>
+        <v>-8.710000000000001</v>
       </c>
       <c r="AB4">
-        <v>-0.71</v>
+        <v>-0.59</v>
       </c>
       <c r="AC4">
-        <v>26.1</v>
+        <v>23.62</v>
       </c>
       <c r="AD4">
-        <v>34.27</v>
+        <v>30.95</v>
       </c>
       <c r="AE4">
-        <v>10.29</v>
+        <v>10.11</v>
       </c>
       <c r="AF4">
-        <v>-5.66</v>
+        <v>11.42</v>
       </c>
       <c r="AG4">
-        <v>395.37</v>
+        <v>392.83</v>
       </c>
       <c r="AH4">
-        <v>360.22</v>
+        <v>359.51</v>
       </c>
       <c r="AI4">
-        <v>394.12</v>
+        <v>393.03</v>
       </c>
       <c r="AJ4" t="s">
         <v>45</v>
       </c>
       <c r="AK4">
-        <v>44.71</v>
+        <v>46.89</v>
       </c>
     </row>
     <row r="5" spans="1:37">
@@ -1255,10 +1249,10 @@
         <v>42</v>
       </c>
       <c r="C5">
-        <v>906.1</v>
+        <v>874.9</v>
       </c>
       <c r="D5">
-        <v>2.2</v>
+        <v>-3.44</v>
       </c>
       <c r="E5">
         <v>1069.3</v>
@@ -1267,46 +1261,46 @@
         <v>739.3</v>
       </c>
       <c r="G5">
-        <v>-15.26</v>
+        <v>-18.18</v>
       </c>
       <c r="H5">
-        <v>22.56</v>
+        <v>18.34</v>
       </c>
       <c r="I5">
-        <v>-0.4</v>
+        <v>-0.35</v>
       </c>
       <c r="J5">
-        <v>-9.82</v>
+        <v>-13.25</v>
       </c>
       <c r="K5">
-        <v>-11.36</v>
+        <v>-12.04</v>
       </c>
       <c r="L5">
-        <v>23.19</v>
+        <v>17.73</v>
       </c>
       <c r="M5">
-        <v>-3.78</v>
+        <v>-5.03</v>
       </c>
       <c r="N5">
         <v>99</v>
       </c>
       <c r="O5">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="P5">
-        <v>891.79</v>
+        <v>891.17</v>
       </c>
       <c r="Q5">
-        <v>943.47</v>
+        <v>937.3099999999999</v>
       </c>
       <c r="R5">
-        <v>984.33</v>
+        <v>981.6900000000001</v>
       </c>
       <c r="S5">
-        <v>924.49</v>
+        <v>924.7</v>
       </c>
       <c r="T5">
-        <v>-1.99</v>
+        <v>-5.39</v>
       </c>
       <c r="U5" t="s">
         <v>43</v>
@@ -1321,43 +1315,43 @@
         <v>1</v>
       </c>
       <c r="Y5">
-        <v>38.15</v>
+        <v>32.16</v>
       </c>
       <c r="Z5">
-        <v>-27.75</v>
+        <v>-29.03</v>
       </c>
       <c r="AA5">
-        <v>-23.34</v>
+        <v>-24.48</v>
       </c>
       <c r="AB5">
-        <v>-4.41</v>
+        <v>-4.56</v>
       </c>
       <c r="AC5">
-        <v>53.27</v>
+        <v>55.99</v>
       </c>
       <c r="AD5">
-        <v>40.49</v>
+        <v>49.97</v>
       </c>
       <c r="AE5">
-        <v>22</v>
+        <v>22.95</v>
       </c>
       <c r="AF5">
-        <v>7.93</v>
+        <v>7.95</v>
       </c>
       <c r="AG5">
-        <v>1024.66</v>
+        <v>1019.75</v>
       </c>
       <c r="AH5">
-        <v>862.28</v>
+        <v>854.87</v>
       </c>
       <c r="AI5">
-        <v>956.15</v>
+        <v>955.92</v>
       </c>
       <c r="AJ5" t="s">
         <v>45</v>
       </c>
       <c r="AK5">
-        <v>52.74</v>
+        <v>54.06</v>
       </c>
     </row>
     <row r="6" spans="1:37">
@@ -1368,10 +1362,10 @@
         <v>42</v>
       </c>
       <c r="C6">
-        <v>2.57</v>
+        <v>2.6</v>
       </c>
       <c r="D6">
-        <v>-0.77</v>
+        <v>1.17</v>
       </c>
       <c r="E6">
         <v>3.38</v>
@@ -1380,46 +1374,46 @@
         <v>1.84</v>
       </c>
       <c r="G6">
-        <v>-23.96</v>
+        <v>-23.08</v>
       </c>
       <c r="H6">
-        <v>39.67</v>
+        <v>41.3</v>
       </c>
       <c r="I6">
-        <v>-3.75</v>
+        <v>-0.76</v>
       </c>
       <c r="J6">
-        <v>-9.19</v>
+        <v>-8.130000000000001</v>
       </c>
       <c r="K6">
-        <v>7.98</v>
+        <v>11.59</v>
       </c>
       <c r="L6">
-        <v>-23.05</v>
+        <v>-22.16</v>
       </c>
       <c r="M6">
-        <v>0.47</v>
+        <v>0.55</v>
       </c>
       <c r="N6">
         <v>40</v>
       </c>
       <c r="O6">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="P6">
-        <v>2.59</v>
+        <v>2.58</v>
       </c>
       <c r="Q6">
-        <v>2.75</v>
+        <v>2.73</v>
       </c>
       <c r="R6">
-        <v>2.62</v>
+        <v>2.63</v>
       </c>
       <c r="S6">
         <v>2.65</v>
       </c>
       <c r="T6">
-        <v>-3.13</v>
+        <v>-1.93</v>
       </c>
       <c r="U6" t="s">
         <v>44</v>
@@ -1434,31 +1428,31 @@
         <v>1</v>
       </c>
       <c r="Y6">
-        <v>41.25</v>
+        <v>43.73</v>
       </c>
       <c r="Z6">
         <v>-0.04</v>
       </c>
       <c r="AA6">
-        <v>0</v>
+        <v>-0.01</v>
       </c>
       <c r="AB6">
-        <v>-0.04</v>
+        <v>-0.03</v>
       </c>
       <c r="AC6">
-        <v>11.52</v>
+        <v>22.96</v>
       </c>
       <c r="AD6">
-        <v>7.86</v>
+        <v>14.26</v>
       </c>
       <c r="AE6">
         <v>0.14</v>
       </c>
       <c r="AF6">
-        <v>-5.99</v>
+        <v>-37.01</v>
       </c>
       <c r="AG6">
-        <v>3.02</v>
+        <v>2.99</v>
       </c>
       <c r="AH6">
         <v>2.48</v>
@@ -1470,7 +1464,7 @@
         <v>45</v>
       </c>
       <c r="AK6">
-        <v>30.46</v>
+        <v>29.66</v>
       </c>
     </row>
   </sheetData>
@@ -1611,7 +1605,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F48"/>
+  <dimension ref="A1:F47"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.7109375" customWidth="1"/>
@@ -1654,765 +1648,751 @@
         <v>38</v>
       </c>
       <c r="B3" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C3" s="4" t="s">
         <v>52</v>
       </c>
-      <c r="C3" s="4" t="s">
+      <c r="D3" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="D3" s="4" t="s">
+      <c r="E3" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6">
+      <c r="A4" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="B4" s="4" t="s">
         <v>54</v>
       </c>
-      <c r="E3" s="4" t="s">
+      <c r="C4" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="F4" s="4" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6">
+      <c r="A6" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="F3" s="4" t="s">
+      <c r="B6" s="2"/>
+      <c r="C6" s="2"/>
+      <c r="D6" s="2"/>
+      <c r="E6" s="2"/>
+    </row>
+    <row r="7" spans="1:6">
+      <c r="A7" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B7" s="3" t="s">
         <v>56</v>
       </c>
-    </row>
-    <row r="5" spans="1:6">
-      <c r="A5" s="2" t="s">
+      <c r="C7" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="B5" s="2"/>
-      <c r="C5" s="2"/>
-      <c r="D5" s="2"/>
-      <c r="E5" s="2"/>
-    </row>
-    <row r="6" spans="1:6">
-      <c r="A6" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B6" s="3" t="s">
+      <c r="D7" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="C6" s="3" t="s">
+      <c r="E7" s="3" t="s">
         <v>59</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="E6" s="3" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6">
-      <c r="A7" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B7" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C7" s="6">
-        <v>-9.109999999999999</v>
-      </c>
-      <c r="D7" s="6">
-        <v>-9.24</v>
-      </c>
-      <c r="E7" s="7">
-        <v>-0.13</v>
       </c>
     </row>
     <row r="8" spans="1:6">
       <c r="A8" s="5" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B8" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C8" s="6">
-        <v>-11.23</v>
+        <v>-9.24</v>
       </c>
       <c r="D8" s="6">
-        <v>-11.94</v>
+        <v>-11.72</v>
       </c>
       <c r="E8" s="7">
-        <v>-0.71</v>
+        <v>-2.48</v>
       </c>
     </row>
     <row r="9" spans="1:6">
       <c r="A9" s="5" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B9" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C9" s="6">
-        <v>-7.16</v>
+        <v>-11.94</v>
       </c>
       <c r="D9" s="6">
-        <v>-8.039999999999999</v>
+        <v>-13.94</v>
       </c>
       <c r="E9" s="7">
-        <v>-0.88</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="10" spans="1:6">
       <c r="A10" s="5" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B10" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C10" s="6">
-        <v>-9.35</v>
+        <v>-8.039999999999999</v>
       </c>
       <c r="D10" s="6">
-        <v>-9.82</v>
+        <v>-9.08</v>
       </c>
       <c r="E10" s="7">
-        <v>-0.47</v>
+        <v>-1.04</v>
       </c>
     </row>
     <row r="11" spans="1:6">
       <c r="A11" s="5" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B11" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C11" s="6">
-        <v>-9.119999999999999</v>
+        <v>-9.82</v>
       </c>
       <c r="D11" s="6">
-        <v>-9.19</v>
+        <v>-13.25</v>
       </c>
       <c r="E11" s="7">
-        <v>-0.07000000000000001</v>
+        <v>-3.43</v>
       </c>
     </row>
     <row r="12" spans="1:6">
       <c r="A12" s="5" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C12" s="6">
-        <v>-4.07</v>
+        <v>-9.19</v>
       </c>
       <c r="D12" s="6">
-        <v>-0.98</v>
+        <v>-8.130000000000001</v>
       </c>
       <c r="E12" s="8">
-        <v>3.09</v>
+        <v>1.06</v>
       </c>
     </row>
     <row r="13" spans="1:6">
       <c r="A13" s="5" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B13" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C13" s="6">
-        <v>-9.48</v>
+        <v>-0.98</v>
       </c>
       <c r="D13" s="6">
-        <v>-1.73</v>
-      </c>
-      <c r="E13" s="8">
-        <v>7.75</v>
+        <v>-2.76</v>
+      </c>
+      <c r="E13" s="7">
+        <v>-1.78</v>
       </c>
     </row>
     <row r="14" spans="1:6">
       <c r="A14" s="5" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B14" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C14" s="6">
-        <v>-3.09</v>
+        <v>-1.73</v>
       </c>
       <c r="D14" s="6">
-        <v>-2.94</v>
+        <v>1.15</v>
       </c>
       <c r="E14" s="8">
-        <v>0.15</v>
+        <v>2.88</v>
       </c>
     </row>
     <row r="15" spans="1:6">
       <c r="A15" s="5" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B15" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C15" s="6">
-        <v>-2.81</v>
+        <v>-2.94</v>
       </c>
       <c r="D15" s="6">
-        <v>-0.4</v>
+        <v>-0.83</v>
       </c>
       <c r="E15" s="8">
-        <v>2.41</v>
+        <v>2.11</v>
       </c>
     </row>
     <row r="16" spans="1:6">
       <c r="A16" s="5" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B16" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C16" s="6">
-        <v>-0.77</v>
+        <v>-0.4</v>
       </c>
       <c r="D16" s="6">
-        <v>-3.75</v>
-      </c>
-      <c r="E16" s="7">
-        <v>-2.98</v>
+        <v>-0.35</v>
+      </c>
+      <c r="E16" s="8">
+        <v>0.05</v>
       </c>
     </row>
     <row r="17" spans="1:5">
       <c r="A17" s="5" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="C17" s="6">
-        <v>9.710000000000001</v>
+        <v>-3.75</v>
       </c>
       <c r="D17" s="6">
-        <v>10.31</v>
+        <v>-0.76</v>
       </c>
       <c r="E17" s="8">
-        <v>0.6</v>
+        <v>2.99</v>
       </c>
     </row>
     <row r="18" spans="1:5">
       <c r="A18" s="5" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B18" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C18" s="6">
-        <v>-2.15</v>
+        <v>10.31</v>
       </c>
       <c r="D18" s="6">
-        <v>6.96</v>
-      </c>
-      <c r="E18" s="8">
-        <v>9.109999999999999</v>
+        <v>8.17</v>
+      </c>
+      <c r="E18" s="7">
+        <v>-2.14</v>
       </c>
     </row>
     <row r="19" spans="1:5">
       <c r="A19" s="5" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B19" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C19" s="6">
-        <v>-26.98</v>
+        <v>6.96</v>
       </c>
       <c r="D19" s="6">
-        <v>-26.27</v>
-      </c>
-      <c r="E19" s="8">
-        <v>0.71</v>
+        <v>2.22</v>
+      </c>
+      <c r="E19" s="7">
+        <v>-4.74</v>
       </c>
     </row>
     <row r="20" spans="1:5">
       <c r="A20" s="5" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B20" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C20" s="6">
-        <v>22.56</v>
+        <v>-26.27</v>
       </c>
       <c r="D20" s="6">
-        <v>23.19</v>
-      </c>
-      <c r="E20" s="8">
-        <v>0.63</v>
+        <v>-26.9</v>
+      </c>
+      <c r="E20" s="7">
+        <v>-0.63</v>
       </c>
     </row>
     <row r="21" spans="1:5">
       <c r="A21" s="5" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B21" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C21" s="6">
-        <v>-22.69</v>
+        <v>23.19</v>
       </c>
       <c r="D21" s="6">
-        <v>-23.05</v>
+        <v>17.73</v>
       </c>
       <c r="E21" s="7">
-        <v>-0.36</v>
+        <v>-5.46</v>
       </c>
     </row>
     <row r="22" spans="1:5">
       <c r="A22" s="5" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C22" s="6">
-        <v>-8.140000000000001</v>
+        <v>-23.05</v>
       </c>
       <c r="D22" s="6">
-        <v>-6.37</v>
+        <v>-22.16</v>
       </c>
       <c r="E22" s="8">
-        <v>1.77</v>
+        <v>0.89</v>
       </c>
     </row>
     <row r="23" spans="1:5">
       <c r="A23" s="5" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B23" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C23" s="6">
-        <v>-13.95</v>
+        <v>-6.37</v>
       </c>
       <c r="D23" s="6">
-        <v>-8.01</v>
+        <v>-4.49</v>
       </c>
       <c r="E23" s="8">
-        <v>5.94</v>
+        <v>1.88</v>
       </c>
     </row>
     <row r="24" spans="1:5">
       <c r="A24" s="5" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B24" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C24" s="6">
-        <v>-11.07</v>
+        <v>-8.01</v>
       </c>
       <c r="D24" s="6">
-        <v>-12.13</v>
-      </c>
-      <c r="E24" s="7">
-        <v>-1.06</v>
+        <v>-6.76</v>
+      </c>
+      <c r="E24" s="8">
+        <v>1.25</v>
       </c>
     </row>
     <row r="25" spans="1:5">
       <c r="A25" s="5" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B25" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C25" s="6">
-        <v>-12.2</v>
+        <v>-12.13</v>
       </c>
       <c r="D25" s="6">
-        <v>-11.36</v>
+        <v>-10.57</v>
       </c>
       <c r="E25" s="8">
-        <v>0.84</v>
+        <v>1.56</v>
       </c>
     </row>
     <row r="26" spans="1:5">
       <c r="A26" s="5" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B26" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C26" s="6">
-        <v>7.92</v>
+        <v>-11.36</v>
       </c>
       <c r="D26" s="6">
-        <v>7.98</v>
-      </c>
-      <c r="E26" s="8">
-        <v>0.06</v>
+        <v>-12.04</v>
+      </c>
+      <c r="E26" s="7">
+        <v>-0.68</v>
       </c>
     </row>
     <row r="27" spans="1:5">
       <c r="A27" s="5" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="B27" s="5" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C27" s="6">
-        <v>-26.76</v>
+        <v>7.98</v>
       </c>
       <c r="D27" s="6">
-        <v>-26.24</v>
+        <v>11.59</v>
       </c>
       <c r="E27" s="8">
-        <v>0.52</v>
+        <v>3.61</v>
       </c>
     </row>
     <row r="28" spans="1:5">
       <c r="A28" s="5" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B28" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C28" s="6">
-        <v>-23.78</v>
+        <v>-26.24</v>
       </c>
       <c r="D28" s="6">
-        <v>-18.35</v>
-      </c>
-      <c r="E28" s="8">
-        <v>5.43</v>
+        <v>-28.4</v>
+      </c>
+      <c r="E28" s="7">
+        <v>-2.16</v>
       </c>
     </row>
     <row r="29" spans="1:5">
       <c r="A29" s="5" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B29" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C29" s="6">
-        <v>-31.66</v>
+        <v>-18.35</v>
       </c>
       <c r="D29" s="6">
-        <v>-32.32</v>
+        <v>-19.36</v>
       </c>
       <c r="E29" s="7">
-        <v>-0.66</v>
+        <v>-1.01</v>
       </c>
     </row>
     <row r="30" spans="1:5">
       <c r="A30" s="5" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B30" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C30" s="6">
-        <v>-17.09</v>
+        <v>-32.32</v>
       </c>
       <c r="D30" s="6">
-        <v>-15.26</v>
+        <v>-32.02</v>
       </c>
       <c r="E30" s="8">
-        <v>1.83</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="31" spans="1:5">
       <c r="A31" s="5" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B31" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C31" s="6">
-        <v>-23.37</v>
+        <v>-15.26</v>
       </c>
       <c r="D31" s="6">
-        <v>-23.96</v>
+        <v>-18.18</v>
       </c>
       <c r="E31" s="7">
-        <v>-0.59</v>
+        <v>-2.92</v>
       </c>
     </row>
     <row r="32" spans="1:5">
       <c r="A32" s="5" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="B32" s="5" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C32" s="6">
-        <v>152.6</v>
+        <v>-23.96</v>
       </c>
       <c r="D32" s="6">
-        <v>153.7</v>
+        <v>-23.08</v>
       </c>
       <c r="E32" s="8">
-        <v>1.1</v>
+        <v>0.88</v>
       </c>
     </row>
     <row r="33" spans="1:5">
       <c r="A33" s="5" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B33" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C33" s="6">
-        <v>347.7</v>
+        <v>153.7</v>
       </c>
       <c r="D33" s="6">
-        <v>372.45</v>
-      </c>
-      <c r="E33" s="8">
-        <v>24.75</v>
+        <v>149.2</v>
+      </c>
+      <c r="E33" s="7">
+        <v>-4.5</v>
       </c>
     </row>
     <row r="34" spans="1:5">
       <c r="A34" s="5" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B34" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C34" s="6">
-        <v>364.95</v>
+        <v>372.45</v>
       </c>
       <c r="D34" s="6">
-        <v>361.4</v>
+        <v>367.85</v>
       </c>
       <c r="E34" s="7">
-        <v>-3.55</v>
+        <v>-4.6</v>
       </c>
     </row>
     <row r="35" spans="1:5">
       <c r="A35" s="5" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B35" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C35" s="6">
-        <v>886.6</v>
+        <v>361.4</v>
       </c>
       <c r="D35" s="6">
-        <v>906.1</v>
+        <v>363</v>
       </c>
       <c r="E35" s="8">
-        <v>19.5</v>
+        <v>1.6</v>
       </c>
     </row>
     <row r="36" spans="1:5">
       <c r="A36" s="5" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B36" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C36" s="6">
-        <v>2.59</v>
+        <v>906.1</v>
       </c>
       <c r="D36" s="6">
-        <v>2.57</v>
+        <v>874.9</v>
       </c>
       <c r="E36" s="7">
-        <v>-0.02</v>
+        <v>-31.2</v>
       </c>
     </row>
     <row r="37" spans="1:5">
       <c r="A37" s="5" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="B37" s="5" t="s">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="C37" s="6">
-        <v>40</v>
+        <v>2.57</v>
       </c>
       <c r="D37" s="6">
-        <v>60</v>
+        <v>2.6</v>
       </c>
       <c r="E37" s="8">
-        <v>20</v>
+        <v>0.03</v>
       </c>
     </row>
     <row r="38" spans="1:5">
       <c r="A38" s="5" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="B38" s="5" t="s">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="C38" s="6">
-        <v>60</v>
+        <v>38.25</v>
       </c>
       <c r="D38" s="6">
-        <v>40</v>
+        <v>33.19</v>
       </c>
       <c r="E38" s="7">
-        <v>-20</v>
+        <v>-5.06</v>
       </c>
     </row>
     <row r="39" spans="1:5">
       <c r="A39" s="5" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B39" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C39" s="6">
-        <v>36.04</v>
+        <v>41.45</v>
       </c>
       <c r="D39" s="6">
-        <v>38.25</v>
-      </c>
-      <c r="E39" s="8">
-        <v>2.21</v>
+        <v>40.12</v>
+      </c>
+      <c r="E39" s="7">
+        <v>-1.33</v>
       </c>
     </row>
     <row r="40" spans="1:5">
       <c r="A40" s="5" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B40" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C40" s="6">
-        <v>29.84</v>
+        <v>25.55</v>
       </c>
       <c r="D40" s="6">
-        <v>41.45</v>
+        <v>28.31</v>
       </c>
       <c r="E40" s="8">
-        <v>11.61</v>
+        <v>2.76</v>
       </c>
     </row>
     <row r="41" spans="1:5">
       <c r="A41" s="5" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B41" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C41" s="6">
-        <v>27.75</v>
+        <v>38.15</v>
       </c>
       <c r="D41" s="6">
-        <v>25.55</v>
+        <v>32.16</v>
       </c>
       <c r="E41" s="7">
-        <v>-2.2</v>
+        <v>-5.99</v>
       </c>
     </row>
     <row r="42" spans="1:5">
       <c r="A42" s="5" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B42" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C42" s="6">
-        <v>30.66</v>
+        <v>41.25</v>
       </c>
       <c r="D42" s="6">
-        <v>38.15</v>
+        <v>43.73</v>
       </c>
       <c r="E42" s="8">
-        <v>7.49</v>
+        <v>2.48</v>
       </c>
     </row>
     <row r="43" spans="1:5">
       <c r="A43" s="5" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="B43" s="5" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="C43" s="6">
-        <v>42.41</v>
+        <v>-16.72</v>
       </c>
       <c r="D43" s="6">
-        <v>41.25</v>
-      </c>
-      <c r="E43" s="7">
-        <v>-1.16</v>
+        <v>-0.98</v>
+      </c>
+      <c r="E43" s="8">
+        <v>15.74</v>
       </c>
     </row>
     <row r="44" spans="1:5">
       <c r="A44" s="5" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B44" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C44" s="6">
-        <v>-19.45</v>
+        <v>-73.84</v>
       </c>
       <c r="D44" s="6">
-        <v>-16.72</v>
+        <v>-69.92</v>
       </c>
       <c r="E44" s="8">
-        <v>2.73</v>
+        <v>3.92</v>
       </c>
     </row>
     <row r="45" spans="1:5">
       <c r="A45" s="5" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B45" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C45" s="6">
-        <v>-89.42</v>
+        <v>-5.66</v>
       </c>
       <c r="D45" s="6">
-        <v>-73.84</v>
+        <v>11.42</v>
       </c>
       <c r="E45" s="8">
-        <v>15.58</v>
+        <v>17.08</v>
       </c>
     </row>
     <row r="46" spans="1:5">
       <c r="A46" s="5" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B46" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C46" s="6">
-        <v>-48.93</v>
+        <v>7.93</v>
       </c>
       <c r="D46" s="6">
-        <v>-5.66</v>
+        <v>7.95</v>
       </c>
       <c r="E46" s="8">
-        <v>43.27</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="47" spans="1:5">
       <c r="A47" s="5" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B47" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C47" s="6">
-        <v>9.83</v>
+        <v>-5.99</v>
       </c>
       <c r="D47" s="6">
-        <v>7.93</v>
+        <v>-37.01</v>
       </c>
       <c r="E47" s="7">
-        <v>-1.9</v>
-      </c>
-    </row>
-    <row r="48" spans="1:5">
-      <c r="A48" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B48" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C48" s="6">
-        <v>-11.02</v>
-      </c>
-      <c r="D48" s="6">
-        <v>-5.99</v>
-      </c>
-      <c r="E48" s="8">
-        <v>5.03</v>
+        <v>-31.02</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A5:E5"/>
+    <mergeCell ref="A6:E6"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2436,28 +2416,28 @@
         <v>1</v>
       </c>
       <c r="B1" s="9" t="s">
+        <v>60</v>
+      </c>
+      <c r="C1" s="9" t="s">
+        <v>61</v>
+      </c>
+      <c r="D1" s="9" t="s">
         <v>62</v>
       </c>
-      <c r="C1" s="9" t="s">
+      <c r="E1" s="9" t="s">
         <v>63</v>
       </c>
-      <c r="D1" s="9" t="s">
+      <c r="F1" s="9" t="s">
         <v>64</v>
       </c>
-      <c r="E1" s="9" t="s">
+      <c r="G1" s="9" t="s">
         <v>65</v>
       </c>
-      <c r="F1" s="9" t="s">
+      <c r="H1" s="9" t="s">
         <v>66</v>
       </c>
-      <c r="G1" s="9" t="s">
+      <c r="I1" s="9" t="s">
         <v>67</v>
-      </c>
-      <c r="H1" s="9" t="s">
-        <v>68</v>
-      </c>
-      <c r="I1" s="9" t="s">
-        <v>69</v>
       </c>
     </row>
     <row r="2" spans="1:9">
@@ -2471,22 +2451,22 @@
         <v>5</v>
       </c>
       <c r="D2" s="11">
-        <v>36.9</v>
+        <v>35.5</v>
       </c>
       <c r="E2" s="11">
         <v>20</v>
       </c>
       <c r="F2" s="11">
-        <v>-9.6</v>
+        <v>-11.2</v>
       </c>
       <c r="G2" s="11">
-        <v>-6</v>
+        <v>-4.5</v>
       </c>
       <c r="H2" s="11">
         <v>59.8</v>
       </c>
       <c r="I2" s="11">
-        <v>20</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -2605,19 +2585,19 @@
     </row>
     <row r="2" spans="1:5">
       <c r="A2" s="14">
-        <v>0.2125</v>
+        <v>0.1945</v>
       </c>
       <c r="B2" s="14">
-        <v>0.0795</v>
+        <v>0.0726</v>
       </c>
       <c r="C2" s="14">
-        <v>0.004699999999999999</v>
+        <v>0.005500000000000001</v>
       </c>
       <c r="D2" s="14">
-        <v>-0.0378</v>
+        <v>-0.0503</v>
       </c>
       <c r="E2" s="14">
-        <v>-0.2254</v>
+        <v>-0.2261</v>
       </c>
     </row>
   </sheetData>

--- a/HINDUJA_GROUP_Technical_Metrics.xlsx
+++ b/HINDUJA_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="224" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="211" uniqueCount="61">
   <si>
     <t>Symbol</t>
   </si>
@@ -163,28 +163,7 @@
     <t>▶  SIGNAL EVENTS (vs Previous Run)</t>
   </si>
   <si>
-    <t>Signal</t>
-  </si>
-  <si>
-    <t>Change</t>
-  </si>
-  <si>
-    <t>Direction</t>
-  </si>
-  <si>
-    <t>Prev Value</t>
-  </si>
-  <si>
-    <t>Curr Value</t>
-  </si>
-  <si>
-    <t>Yes → No</t>
-  </si>
-  <si>
-    <t>🔴 BEARISH</t>
-  </si>
-  <si>
-    <t>20 DMA &gt; 50 DMA</t>
+    <t>No signal events detected since last run.</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -386,15 +365,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -910,10 +888,10 @@
         <v>42</v>
       </c>
       <c r="C2">
-        <v>149.2</v>
+        <v>145.02</v>
       </c>
       <c r="D2">
-        <v>-2.93</v>
+        <v>-2.8</v>
       </c>
       <c r="E2">
         <v>208.37</v>
@@ -922,46 +900,46 @@
         <v>131.36</v>
       </c>
       <c r="G2">
-        <v>-28.4</v>
+        <v>-30.4</v>
       </c>
       <c r="H2">
-        <v>13.58</v>
+        <v>10.4</v>
       </c>
       <c r="I2">
-        <v>-2.76</v>
+        <v>-5.95</v>
       </c>
       <c r="J2">
-        <v>-11.72</v>
+        <v>-14.69</v>
       </c>
       <c r="K2">
-        <v>-4.49</v>
+        <v>-6.55</v>
       </c>
       <c r="L2">
-        <v>8.17</v>
+        <v>6.23</v>
       </c>
       <c r="M2">
-        <v>19.45</v>
+        <v>18.94</v>
       </c>
       <c r="N2">
         <v>79</v>
       </c>
       <c r="O2">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="P2">
-        <v>152.03</v>
+        <v>150.2</v>
       </c>
       <c r="Q2">
-        <v>158.56</v>
+        <v>157.36</v>
       </c>
       <c r="R2">
-        <v>166.78</v>
+        <v>166.53</v>
       </c>
       <c r="S2">
-        <v>169.69</v>
+        <v>169.57</v>
       </c>
       <c r="T2">
-        <v>-12.08</v>
+        <v>-14.48</v>
       </c>
       <c r="U2" t="s">
         <v>43</v>
@@ -976,43 +954,43 @@
         <v>0</v>
       </c>
       <c r="Y2">
-        <v>33.19</v>
+        <v>29.32</v>
       </c>
       <c r="Z2">
-        <v>-4.4</v>
+        <v>-4.89</v>
       </c>
       <c r="AA2">
-        <v>-3.66</v>
+        <v>-3.91</v>
       </c>
       <c r="AB2">
-        <v>-0.74</v>
+        <v>-0.98</v>
       </c>
       <c r="AC2">
-        <v>37.51</v>
+        <v>23.18</v>
       </c>
       <c r="AD2">
-        <v>36.02</v>
+        <v>32.96</v>
       </c>
       <c r="AE2">
-        <v>4.03</v>
+        <v>4.12</v>
       </c>
       <c r="AF2">
-        <v>-0.98</v>
+        <v>33.42</v>
       </c>
       <c r="AG2">
-        <v>169.76</v>
+        <v>168.99</v>
       </c>
       <c r="AH2">
-        <v>147.36</v>
+        <v>145.74</v>
       </c>
       <c r="AI2">
-        <v>163.11</v>
+        <v>159.51</v>
       </c>
       <c r="AJ2" t="s">
         <v>45</v>
       </c>
       <c r="AK2">
-        <v>53.22</v>
+        <v>56.79</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1023,10 +1001,10 @@
         <v>42</v>
       </c>
       <c r="C3">
-        <v>367.85</v>
+        <v>357.6</v>
       </c>
       <c r="D3">
-        <v>-1.24</v>
+        <v>-2.79</v>
       </c>
       <c r="E3">
         <v>456.15</v>
@@ -1035,46 +1013,46 @@
         <v>225</v>
       </c>
       <c r="G3">
-        <v>-19.36</v>
+        <v>-21.6</v>
       </c>
       <c r="H3">
-        <v>63.49</v>
+        <v>58.93</v>
       </c>
       <c r="I3">
-        <v>1.15</v>
+        <v>-1.34</v>
       </c>
       <c r="J3">
-        <v>-13.94</v>
+        <v>-18.16</v>
       </c>
       <c r="K3">
-        <v>-6.76</v>
+        <v>-12.78</v>
       </c>
       <c r="L3">
-        <v>2.22</v>
+        <v>-0.98</v>
       </c>
       <c r="M3">
-        <v>7.26</v>
+        <v>6.98</v>
       </c>
       <c r="N3">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="O3">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="P3">
-        <v>360.42</v>
+        <v>359.45</v>
       </c>
       <c r="Q3">
-        <v>403.69</v>
+        <v>399.79</v>
       </c>
       <c r="R3">
-        <v>405.69</v>
+        <v>405.08</v>
       </c>
       <c r="S3">
-        <v>339</v>
+        <v>339.33</v>
       </c>
       <c r="T3">
-        <v>8.51</v>
+        <v>5.38</v>
       </c>
       <c r="U3" t="s">
         <v>43</v>
@@ -1089,34 +1067,34 @@
         <v>2</v>
       </c>
       <c r="Y3">
-        <v>40.12</v>
+        <v>37.26</v>
       </c>
       <c r="Z3">
-        <v>-14.81</v>
+        <v>-15.41</v>
       </c>
       <c r="AA3">
-        <v>-9.210000000000001</v>
+        <v>-10.45</v>
       </c>
       <c r="AB3">
-        <v>-5.61</v>
+        <v>-4.96</v>
       </c>
       <c r="AC3">
-        <v>19.26</v>
+        <v>26.45</v>
       </c>
       <c r="AD3">
-        <v>9.83</v>
+        <v>18.64</v>
       </c>
       <c r="AE3">
-        <v>18.31</v>
+        <v>17.9</v>
       </c>
       <c r="AF3">
-        <v>-69.92</v>
+        <v>-81.59999999999999</v>
       </c>
       <c r="AG3">
-        <v>477.43</v>
+        <v>474.66</v>
       </c>
       <c r="AH3">
-        <v>329.94</v>
+        <v>324.91</v>
       </c>
       <c r="AI3">
         <v>404.18</v>
@@ -1125,7 +1103,7 @@
         <v>45</v>
       </c>
       <c r="AK3">
-        <v>45.8</v>
+        <v>44.17</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1136,10 +1114,10 @@
         <v>42</v>
       </c>
       <c r="C4">
-        <v>363</v>
+        <v>358.95</v>
       </c>
       <c r="D4">
-        <v>0.44</v>
+        <v>-1.12</v>
       </c>
       <c r="E4">
         <v>534</v>
@@ -1148,46 +1126,46 @@
         <v>344.7</v>
       </c>
       <c r="G4">
-        <v>-32.02</v>
+        <v>-32.78</v>
       </c>
       <c r="H4">
-        <v>5.31</v>
+        <v>4.13</v>
       </c>
       <c r="I4">
-        <v>-0.83</v>
+        <v>-3</v>
       </c>
       <c r="J4">
-        <v>-9.08</v>
+        <v>-9.25</v>
       </c>
       <c r="K4">
-        <v>-10.57</v>
+        <v>-12.43</v>
       </c>
       <c r="L4">
-        <v>-26.9</v>
+        <v>-28.81</v>
       </c>
       <c r="M4">
-        <v>-22.61</v>
+        <v>-22.82</v>
       </c>
       <c r="N4">
         <v>21</v>
       </c>
       <c r="O4">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="P4">
-        <v>365.29</v>
+        <v>363.07</v>
       </c>
       <c r="Q4">
-        <v>376.17</v>
+        <v>374.72</v>
       </c>
       <c r="R4">
-        <v>396.2</v>
+        <v>394.95</v>
       </c>
       <c r="S4">
-        <v>406.05</v>
+        <v>405.66</v>
       </c>
       <c r="T4">
-        <v>-10.6</v>
+        <v>-11.51</v>
       </c>
       <c r="U4" t="s">
         <v>43</v>
@@ -1202,43 +1180,43 @@
         <v>0</v>
       </c>
       <c r="Y4">
-        <v>28.31</v>
+        <v>25.71</v>
       </c>
       <c r="Z4">
-        <v>-9.289999999999999</v>
+        <v>-9.529999999999999</v>
       </c>
       <c r="AA4">
-        <v>-8.710000000000001</v>
+        <v>-8.869999999999999</v>
       </c>
       <c r="AB4">
-        <v>-0.59</v>
+        <v>-0.65</v>
       </c>
       <c r="AC4">
-        <v>23.62</v>
+        <v>19.04</v>
       </c>
       <c r="AD4">
-        <v>30.95</v>
+        <v>22.92</v>
       </c>
       <c r="AE4">
-        <v>10.11</v>
+        <v>9.91</v>
       </c>
       <c r="AF4">
-        <v>11.42</v>
+        <v>-36.63</v>
       </c>
       <c r="AG4">
-        <v>392.83</v>
+        <v>392.09</v>
       </c>
       <c r="AH4">
-        <v>359.51</v>
+        <v>357.34</v>
       </c>
       <c r="AI4">
-        <v>393.03</v>
+        <v>390.55</v>
       </c>
       <c r="AJ4" t="s">
         <v>45</v>
       </c>
       <c r="AK4">
-        <v>46.89</v>
+        <v>49.28</v>
       </c>
     </row>
     <row r="5" spans="1:37">
@@ -1249,10 +1227,10 @@
         <v>42</v>
       </c>
       <c r="C5">
-        <v>874.9</v>
+        <v>864</v>
       </c>
       <c r="D5">
-        <v>-3.44</v>
+        <v>-1.25</v>
       </c>
       <c r="E5">
         <v>1069.3</v>
@@ -1261,46 +1239,46 @@
         <v>739.3</v>
       </c>
       <c r="G5">
-        <v>-18.18</v>
+        <v>-19.2</v>
       </c>
       <c r="H5">
-        <v>18.34</v>
+        <v>16.87</v>
       </c>
       <c r="I5">
-        <v>-0.35</v>
+        <v>-4.15</v>
       </c>
       <c r="J5">
-        <v>-13.25</v>
+        <v>-13.43</v>
       </c>
       <c r="K5">
-        <v>-12.04</v>
+        <v>-14.89</v>
       </c>
       <c r="L5">
-        <v>17.73</v>
+        <v>15.6</v>
       </c>
       <c r="M5">
-        <v>-5.03</v>
+        <v>-5.39</v>
       </c>
       <c r="N5">
         <v>99</v>
       </c>
       <c r="O5">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="P5">
-        <v>891.17</v>
+        <v>883.6900000000001</v>
       </c>
       <c r="Q5">
-        <v>937.3099999999999</v>
+        <v>930.63</v>
       </c>
       <c r="R5">
-        <v>981.6900000000001</v>
+        <v>979.13</v>
       </c>
       <c r="S5">
-        <v>924.7</v>
+        <v>924.85</v>
       </c>
       <c r="T5">
-        <v>-5.39</v>
+        <v>-6.58</v>
       </c>
       <c r="U5" t="s">
         <v>43</v>
@@ -1315,43 +1293,43 @@
         <v>1</v>
       </c>
       <c r="Y5">
-        <v>32.16</v>
+        <v>30.37</v>
       </c>
       <c r="Z5">
-        <v>-29.03</v>
+        <v>-30.58</v>
       </c>
       <c r="AA5">
-        <v>-24.48</v>
+        <v>-25.7</v>
       </c>
       <c r="AB5">
-        <v>-4.56</v>
+        <v>-4.88</v>
       </c>
       <c r="AC5">
-        <v>55.99</v>
+        <v>55.45</v>
       </c>
       <c r="AD5">
-        <v>49.97</v>
+        <v>54.91</v>
       </c>
       <c r="AE5">
-        <v>22.95</v>
+        <v>22.8</v>
       </c>
       <c r="AF5">
-        <v>7.95</v>
+        <v>-26.94</v>
       </c>
       <c r="AG5">
-        <v>1019.75</v>
+        <v>1014.12</v>
       </c>
       <c r="AH5">
-        <v>854.87</v>
+        <v>847.13</v>
       </c>
       <c r="AI5">
-        <v>955.92</v>
+        <v>935.89</v>
       </c>
       <c r="AJ5" t="s">
         <v>45</v>
       </c>
       <c r="AK5">
-        <v>54.06</v>
+        <v>56.19</v>
       </c>
     </row>
     <row r="6" spans="1:37">
@@ -1362,10 +1340,10 @@
         <v>42</v>
       </c>
       <c r="C6">
-        <v>2.6</v>
+        <v>2.58</v>
       </c>
       <c r="D6">
-        <v>1.17</v>
+        <v>-0.77</v>
       </c>
       <c r="E6">
         <v>3.38</v>
@@ -1374,46 +1352,46 @@
         <v>1.84</v>
       </c>
       <c r="G6">
-        <v>-23.08</v>
+        <v>-23.67</v>
       </c>
       <c r="H6">
-        <v>41.3</v>
+        <v>40.22</v>
       </c>
       <c r="I6">
-        <v>-0.76</v>
+        <v>-1.15</v>
       </c>
       <c r="J6">
-        <v>-8.130000000000001</v>
+        <v>-13.42</v>
       </c>
       <c r="K6">
-        <v>11.59</v>
+        <v>7.95</v>
       </c>
       <c r="L6">
-        <v>-22.16</v>
+        <v>-23.67</v>
       </c>
       <c r="M6">
-        <v>0.55</v>
+        <v>1.12</v>
       </c>
       <c r="N6">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="O6">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="P6">
         <v>2.58</v>
       </c>
       <c r="Q6">
-        <v>2.73</v>
+        <v>2.72</v>
       </c>
       <c r="R6">
-        <v>2.63</v>
+        <v>2.64</v>
       </c>
       <c r="S6">
         <v>2.65</v>
       </c>
       <c r="T6">
-        <v>-1.93</v>
+        <v>-2.62</v>
       </c>
       <c r="U6" t="s">
         <v>44</v>
@@ -1428,7 +1406,7 @@
         <v>1</v>
       </c>
       <c r="Y6">
-        <v>43.73</v>
+        <v>42.44</v>
       </c>
       <c r="Z6">
         <v>-0.04</v>
@@ -1440,22 +1418,22 @@
         <v>-0.03</v>
       </c>
       <c r="AC6">
-        <v>22.96</v>
+        <v>26.03</v>
       </c>
       <c r="AD6">
-        <v>14.26</v>
+        <v>20.17</v>
       </c>
       <c r="AE6">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="AF6">
-        <v>-37.01</v>
+        <v>-11.69</v>
       </c>
       <c r="AG6">
-        <v>2.99</v>
+        <v>2.96</v>
       </c>
       <c r="AH6">
-        <v>2.48</v>
+        <v>2.47</v>
       </c>
       <c r="AI6">
         <v>2.99</v>
@@ -1464,7 +1442,7 @@
         <v>45</v>
       </c>
       <c r="AK6">
-        <v>29.66</v>
+        <v>28.98</v>
       </c>
     </row>
   </sheetData>
@@ -1605,7 +1583,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F47"/>
+  <dimension ref="A1:F48"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.7109375" customWidth="1"/>
@@ -1625,774 +1603,753 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="3" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6">
+      <c r="A5" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="B5" s="2"/>
+      <c r="C5" s="2"/>
+      <c r="D5" s="2"/>
+      <c r="E5" s="2"/>
+    </row>
+    <row r="6" spans="1:6">
+      <c r="A6" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="D2" s="3" t="s">
+      <c r="B6" s="4" t="s">
         <v>49</v>
       </c>
-      <c r="E2" s="3" t="s">
+      <c r="C6" s="4" t="s">
         <v>50</v>
       </c>
-      <c r="F2" s="3" t="s">
+      <c r="D6" s="4" t="s">
         <v>51</v>
       </c>
-    </row>
-    <row r="3" spans="1:6">
-      <c r="A3" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="B3" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="C3" s="4" t="s">
+      <c r="E6" s="4" t="s">
         <v>52</v>
       </c>
-      <c r="D3" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="E3" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="F3" s="4" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6">
-      <c r="A4" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="B4" s="4" t="s">
-        <v>54</v>
-      </c>
-      <c r="C4" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="D4" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="E4" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="F4" s="4" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6">
-      <c r="A6" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="B6" s="2"/>
-      <c r="C6" s="2"/>
-      <c r="D6" s="2"/>
-      <c r="E6" s="2"/>
     </row>
     <row r="7" spans="1:6">
       <c r="A7" s="3" t="s">
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="D7" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="E7" s="3" t="s">
-        <v>59</v>
+        <v>9</v>
+      </c>
+      <c r="C7" s="5">
+        <v>-11.72</v>
+      </c>
+      <c r="D7" s="5">
+        <v>-14.69</v>
+      </c>
+      <c r="E7" s="6">
+        <v>-2.97</v>
       </c>
     </row>
     <row r="8" spans="1:6">
-      <c r="A8" s="5" t="s">
+      <c r="A8" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C8" s="5">
+        <v>-13.94</v>
+      </c>
+      <c r="D8" s="5">
+        <v>-18.16</v>
+      </c>
+      <c r="E8" s="6">
+        <v>-4.22</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="A9" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C9" s="5">
+        <v>-9.08</v>
+      </c>
+      <c r="D9" s="5">
+        <v>-9.25</v>
+      </c>
+      <c r="E9" s="6">
+        <v>-0.17</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="A10" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C10" s="5">
+        <v>-13.25</v>
+      </c>
+      <c r="D10" s="5">
+        <v>-13.43</v>
+      </c>
+      <c r="E10" s="6">
+        <v>-0.18</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="A11" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C11" s="5">
+        <v>-8.130000000000001</v>
+      </c>
+      <c r="D11" s="5">
+        <v>-13.42</v>
+      </c>
+      <c r="E11" s="6">
+        <v>-5.29</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6">
+      <c r="A12" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B8" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C8" s="6">
-        <v>-9.24</v>
-      </c>
-      <c r="D8" s="6">
-        <v>-11.72</v>
-      </c>
-      <c r="E8" s="7">
-        <v>-2.48</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
-      <c r="A9" s="5" t="s">
+      <c r="B12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C12" s="5">
+        <v>-2.76</v>
+      </c>
+      <c r="D12" s="5">
+        <v>-5.95</v>
+      </c>
+      <c r="E12" s="6">
+        <v>-3.19</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6">
+      <c r="A13" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B9" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C9" s="6">
-        <v>-11.94</v>
-      </c>
-      <c r="D9" s="6">
-        <v>-13.94</v>
-      </c>
-      <c r="E9" s="7">
+      <c r="B13" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C13" s="5">
+        <v>1.15</v>
+      </c>
+      <c r="D13" s="5">
+        <v>-1.34</v>
+      </c>
+      <c r="E13" s="6">
+        <v>-2.49</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6">
+      <c r="A14" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C14" s="5">
+        <v>-0.83</v>
+      </c>
+      <c r="D14" s="5">
+        <v>-3</v>
+      </c>
+      <c r="E14" s="6">
+        <v>-2.17</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6">
+      <c r="A15" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C15" s="5">
+        <v>-0.35</v>
+      </c>
+      <c r="D15" s="5">
+        <v>-4.15</v>
+      </c>
+      <c r="E15" s="6">
+        <v>-3.8</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6">
+      <c r="A16" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C16" s="5">
+        <v>-0.76</v>
+      </c>
+      <c r="D16" s="5">
+        <v>-1.15</v>
+      </c>
+      <c r="E16" s="6">
+        <v>-0.39</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C17" s="5">
+        <v>8.17</v>
+      </c>
+      <c r="D17" s="5">
+        <v>6.23</v>
+      </c>
+      <c r="E17" s="6">
+        <v>-1.94</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C18" s="5">
+        <v>2.22</v>
+      </c>
+      <c r="D18" s="5">
+        <v>-0.98</v>
+      </c>
+      <c r="E18" s="6">
+        <v>-3.2</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C19" s="5">
+        <v>-26.9</v>
+      </c>
+      <c r="D19" s="5">
+        <v>-28.81</v>
+      </c>
+      <c r="E19" s="6">
+        <v>-1.91</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C20" s="5">
+        <v>17.73</v>
+      </c>
+      <c r="D20" s="5">
+        <v>15.6</v>
+      </c>
+      <c r="E20" s="6">
+        <v>-2.13</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C21" s="5">
+        <v>-22.16</v>
+      </c>
+      <c r="D21" s="5">
+        <v>-23.67</v>
+      </c>
+      <c r="E21" s="6">
+        <v>-1.51</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B22" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C22" s="5">
+        <v>-4.49</v>
+      </c>
+      <c r="D22" s="5">
+        <v>-6.55</v>
+      </c>
+      <c r="E22" s="6">
+        <v>-2.06</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B23" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C23" s="5">
+        <v>-6.76</v>
+      </c>
+      <c r="D23" s="5">
+        <v>-12.78</v>
+      </c>
+      <c r="E23" s="6">
+        <v>-6.02</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5">
+      <c r="A24" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B24" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C24" s="5">
+        <v>-10.57</v>
+      </c>
+      <c r="D24" s="5">
+        <v>-12.43</v>
+      </c>
+      <c r="E24" s="6">
+        <v>-1.86</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5">
+      <c r="A25" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B25" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C25" s="5">
+        <v>-12.04</v>
+      </c>
+      <c r="D25" s="5">
+        <v>-14.89</v>
+      </c>
+      <c r="E25" s="6">
+        <v>-2.85</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
+      <c r="A26" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B26" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C26" s="5">
+        <v>11.59</v>
+      </c>
+      <c r="D26" s="5">
+        <v>7.95</v>
+      </c>
+      <c r="E26" s="6">
+        <v>-3.64</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5">
+      <c r="A27" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B27" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C27" s="5">
+        <v>-28.4</v>
+      </c>
+      <c r="D27" s="5">
+        <v>-30.4</v>
+      </c>
+      <c r="E27" s="6">
         <v>-2</v>
       </c>
     </row>
-    <row r="10" spans="1:6">
-      <c r="A10" s="5" t="s">
+    <row r="28" spans="1:5">
+      <c r="A28" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B28" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C28" s="5">
+        <v>-19.36</v>
+      </c>
+      <c r="D28" s="5">
+        <v>-21.6</v>
+      </c>
+      <c r="E28" s="6">
+        <v>-2.24</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5">
+      <c r="A29" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B10" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C10" s="6">
-        <v>-8.039999999999999</v>
-      </c>
-      <c r="D10" s="6">
-        <v>-9.08</v>
-      </c>
-      <c r="E10" s="7">
-        <v>-1.04</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
-      <c r="A11" s="5" t="s">
+      <c r="B29" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C29" s="5">
+        <v>-32.02</v>
+      </c>
+      <c r="D29" s="5">
+        <v>-32.78</v>
+      </c>
+      <c r="E29" s="6">
+        <v>-0.76</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5">
+      <c r="A30" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="B11" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C11" s="6">
-        <v>-9.82</v>
-      </c>
-      <c r="D11" s="6">
-        <v>-13.25</v>
-      </c>
-      <c r="E11" s="7">
-        <v>-3.43</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
-      <c r="A12" s="5" t="s">
+      <c r="B30" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C30" s="5">
+        <v>-18.18</v>
+      </c>
+      <c r="D30" s="5">
+        <v>-19.2</v>
+      </c>
+      <c r="E30" s="6">
+        <v>-1.02</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5">
+      <c r="A31" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="B12" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C12" s="6">
-        <v>-9.19</v>
-      </c>
-      <c r="D12" s="6">
-        <v>-8.130000000000001</v>
-      </c>
-      <c r="E12" s="8">
-        <v>1.06</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
-      <c r="A13" s="5" t="s">
+      <c r="B31" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C31" s="5">
+        <v>-23.08</v>
+      </c>
+      <c r="D31" s="5">
+        <v>-23.67</v>
+      </c>
+      <c r="E31" s="6">
+        <v>-0.59</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5">
+      <c r="A32" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B13" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C13" s="6">
+      <c r="B32" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C32" s="5">
+        <v>149.2</v>
+      </c>
+      <c r="D32" s="5">
+        <v>145.02</v>
+      </c>
+      <c r="E32" s="6">
+        <v>-4.18</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5">
+      <c r="A33" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B33" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C33" s="5">
+        <v>367.85</v>
+      </c>
+      <c r="D33" s="5">
+        <v>357.6</v>
+      </c>
+      <c r="E33" s="6">
+        <v>-10.25</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5">
+      <c r="A34" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B34" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C34" s="5">
+        <v>363</v>
+      </c>
+      <c r="D34" s="5">
+        <v>358.95</v>
+      </c>
+      <c r="E34" s="6">
+        <v>-4.05</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5">
+      <c r="A35" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B35" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C35" s="5">
+        <v>874.9</v>
+      </c>
+      <c r="D35" s="5">
+        <v>864</v>
+      </c>
+      <c r="E35" s="6">
+        <v>-10.9</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5">
+      <c r="A36" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B36" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C36" s="5">
+        <v>2.6</v>
+      </c>
+      <c r="D36" s="5">
+        <v>2.58</v>
+      </c>
+      <c r="E36" s="6">
+        <v>-0.02</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5">
+      <c r="A37" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B37" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C37" s="5">
+        <v>60</v>
+      </c>
+      <c r="D37" s="5">
+        <v>40</v>
+      </c>
+      <c r="E37" s="6">
+        <v>-20</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5">
+      <c r="A38" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B38" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C38" s="5">
+        <v>40</v>
+      </c>
+      <c r="D38" s="5">
+        <v>60</v>
+      </c>
+      <c r="E38" s="7">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5">
+      <c r="A39" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B39" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C39" s="5">
+        <v>33.19</v>
+      </c>
+      <c r="D39" s="5">
+        <v>29.32</v>
+      </c>
+      <c r="E39" s="6">
+        <v>-3.87</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5">
+      <c r="A40" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B40" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C40" s="5">
+        <v>40.12</v>
+      </c>
+      <c r="D40" s="5">
+        <v>37.26</v>
+      </c>
+      <c r="E40" s="6">
+        <v>-2.86</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5">
+      <c r="A41" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B41" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C41" s="5">
+        <v>28.31</v>
+      </c>
+      <c r="D41" s="5">
+        <v>25.71</v>
+      </c>
+      <c r="E41" s="6">
+        <v>-2.6</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5">
+      <c r="A42" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B42" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C42" s="5">
+        <v>32.16</v>
+      </c>
+      <c r="D42" s="5">
+        <v>30.37</v>
+      </c>
+      <c r="E42" s="6">
+        <v>-1.79</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5">
+      <c r="A43" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B43" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C43" s="5">
+        <v>43.73</v>
+      </c>
+      <c r="D43" s="5">
+        <v>42.44</v>
+      </c>
+      <c r="E43" s="6">
+        <v>-1.29</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5">
+      <c r="A44" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B44" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C44" s="5">
         <v>-0.98</v>
       </c>
-      <c r="D13" s="6">
-        <v>-2.76</v>
-      </c>
-      <c r="E13" s="7">
-        <v>-1.78</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
-      <c r="A14" s="5" t="s">
+      <c r="D44" s="5">
+        <v>33.42</v>
+      </c>
+      <c r="E44" s="7">
+        <v>34.4</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5">
+      <c r="A45" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B14" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C14" s="6">
-        <v>-1.73</v>
-      </c>
-      <c r="D14" s="6">
-        <v>1.15</v>
-      </c>
-      <c r="E14" s="8">
-        <v>2.88</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6">
-      <c r="A15" s="5" t="s">
+      <c r="B45" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C45" s="5">
+        <v>-69.92</v>
+      </c>
+      <c r="D45" s="5">
+        <v>-81.59999999999999</v>
+      </c>
+      <c r="E45" s="6">
+        <v>-11.68</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5">
+      <c r="A46" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B15" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C15" s="6">
-        <v>-2.94</v>
-      </c>
-      <c r="D15" s="6">
-        <v>-0.83</v>
-      </c>
-      <c r="E15" s="8">
-        <v>2.11</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
-      <c r="A16" s="5" t="s">
+      <c r="B46" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C46" s="5">
+        <v>11.42</v>
+      </c>
+      <c r="D46" s="5">
+        <v>-36.63</v>
+      </c>
+      <c r="E46" s="6">
+        <v>-48.05</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5">
+      <c r="A47" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="B16" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C16" s="6">
-        <v>-0.4</v>
-      </c>
-      <c r="D16" s="6">
-        <v>-0.35</v>
-      </c>
-      <c r="E16" s="8">
-        <v>0.05</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5">
-      <c r="A17" s="5" t="s">
+      <c r="B47" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C47" s="5">
+        <v>7.95</v>
+      </c>
+      <c r="D47" s="5">
+        <v>-26.94</v>
+      </c>
+      <c r="E47" s="6">
+        <v>-34.89</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5">
+      <c r="A48" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="B17" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C17" s="6">
-        <v>-3.75</v>
-      </c>
-      <c r="D17" s="6">
-        <v>-0.76</v>
-      </c>
-      <c r="E17" s="8">
-        <v>2.99</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5">
-      <c r="A18" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B18" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C18" s="6">
-        <v>10.31</v>
-      </c>
-      <c r="D18" s="6">
-        <v>8.17</v>
-      </c>
-      <c r="E18" s="7">
-        <v>-2.14</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5">
-      <c r="A19" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B19" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C19" s="6">
-        <v>6.96</v>
-      </c>
-      <c r="D19" s="6">
-        <v>2.22</v>
-      </c>
-      <c r="E19" s="7">
-        <v>-4.74</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5">
-      <c r="A20" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B20" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C20" s="6">
-        <v>-26.27</v>
-      </c>
-      <c r="D20" s="6">
-        <v>-26.9</v>
-      </c>
-      <c r="E20" s="7">
-        <v>-0.63</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5">
-      <c r="A21" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B21" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C21" s="6">
-        <v>23.19</v>
-      </c>
-      <c r="D21" s="6">
-        <v>17.73</v>
-      </c>
-      <c r="E21" s="7">
-        <v>-5.46</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5">
-      <c r="A22" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B22" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C22" s="6">
-        <v>-23.05</v>
-      </c>
-      <c r="D22" s="6">
-        <v>-22.16</v>
-      </c>
-      <c r="E22" s="8">
-        <v>0.89</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5">
-      <c r="A23" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B23" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C23" s="6">
-        <v>-6.37</v>
-      </c>
-      <c r="D23" s="6">
-        <v>-4.49</v>
-      </c>
-      <c r="E23" s="8">
-        <v>1.88</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5">
-      <c r="A24" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B24" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C24" s="6">
-        <v>-8.01</v>
-      </c>
-      <c r="D24" s="6">
-        <v>-6.76</v>
-      </c>
-      <c r="E24" s="8">
-        <v>1.25</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5">
-      <c r="A25" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B25" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C25" s="6">
-        <v>-12.13</v>
-      </c>
-      <c r="D25" s="6">
-        <v>-10.57</v>
-      </c>
-      <c r="E25" s="8">
-        <v>1.56</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5">
-      <c r="A26" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B26" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C26" s="6">
-        <v>-11.36</v>
-      </c>
-      <c r="D26" s="6">
-        <v>-12.04</v>
-      </c>
-      <c r="E26" s="7">
-        <v>-0.68</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5">
-      <c r="A27" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B27" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C27" s="6">
-        <v>7.98</v>
-      </c>
-      <c r="D27" s="6">
-        <v>11.59</v>
-      </c>
-      <c r="E27" s="8">
-        <v>3.61</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5">
-      <c r="A28" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B28" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C28" s="6">
-        <v>-26.24</v>
-      </c>
-      <c r="D28" s="6">
-        <v>-28.4</v>
-      </c>
-      <c r="E28" s="7">
-        <v>-2.16</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5">
-      <c r="A29" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B29" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C29" s="6">
-        <v>-18.35</v>
-      </c>
-      <c r="D29" s="6">
-        <v>-19.36</v>
-      </c>
-      <c r="E29" s="7">
-        <v>-1.01</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5">
-      <c r="A30" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B30" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C30" s="6">
-        <v>-32.32</v>
-      </c>
-      <c r="D30" s="6">
-        <v>-32.02</v>
-      </c>
-      <c r="E30" s="8">
-        <v>0.3</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5">
-      <c r="A31" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B31" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C31" s="6">
-        <v>-15.26</v>
-      </c>
-      <c r="D31" s="6">
-        <v>-18.18</v>
-      </c>
-      <c r="E31" s="7">
-        <v>-2.92</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5">
-      <c r="A32" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B32" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C32" s="6">
-        <v>-23.96</v>
-      </c>
-      <c r="D32" s="6">
-        <v>-23.08</v>
-      </c>
-      <c r="E32" s="8">
-        <v>0.88</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5">
-      <c r="A33" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B33" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C33" s="6">
-        <v>153.7</v>
-      </c>
-      <c r="D33" s="6">
-        <v>149.2</v>
-      </c>
-      <c r="E33" s="7">
-        <v>-4.5</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5">
-      <c r="A34" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B34" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C34" s="6">
-        <v>372.45</v>
-      </c>
-      <c r="D34" s="6">
-        <v>367.85</v>
-      </c>
-      <c r="E34" s="7">
-        <v>-4.6</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5">
-      <c r="A35" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B35" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C35" s="6">
-        <v>361.4</v>
-      </c>
-      <c r="D35" s="6">
-        <v>363</v>
-      </c>
-      <c r="E35" s="8">
-        <v>1.6</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5">
-      <c r="A36" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B36" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C36" s="6">
-        <v>906.1</v>
-      </c>
-      <c r="D36" s="6">
-        <v>874.9</v>
-      </c>
-      <c r="E36" s="7">
-        <v>-31.2</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5">
-      <c r="A37" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B37" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C37" s="6">
-        <v>2.57</v>
-      </c>
-      <c r="D37" s="6">
-        <v>2.6</v>
-      </c>
-      <c r="E37" s="8">
-        <v>0.03</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5">
-      <c r="A38" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B38" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C38" s="6">
-        <v>38.25</v>
-      </c>
-      <c r="D38" s="6">
-        <v>33.19</v>
-      </c>
-      <c r="E38" s="7">
-        <v>-5.06</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5">
-      <c r="A39" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B39" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C39" s="6">
-        <v>41.45</v>
-      </c>
-      <c r="D39" s="6">
-        <v>40.12</v>
-      </c>
-      <c r="E39" s="7">
-        <v>-1.33</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5">
-      <c r="A40" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B40" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C40" s="6">
-        <v>25.55</v>
-      </c>
-      <c r="D40" s="6">
-        <v>28.31</v>
-      </c>
-      <c r="E40" s="8">
-        <v>2.76</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5">
-      <c r="A41" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B41" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C41" s="6">
-        <v>38.15</v>
-      </c>
-      <c r="D41" s="6">
-        <v>32.16</v>
-      </c>
-      <c r="E41" s="7">
-        <v>-5.99</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5">
-      <c r="A42" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B42" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C42" s="6">
-        <v>41.25</v>
-      </c>
-      <c r="D42" s="6">
-        <v>43.73</v>
-      </c>
-      <c r="E42" s="8">
-        <v>2.48</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5">
-      <c r="A43" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B43" s="5" t="s">
+      <c r="B48" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="C43" s="6">
-        <v>-16.72</v>
-      </c>
-      <c r="D43" s="6">
-        <v>-0.98</v>
-      </c>
-      <c r="E43" s="8">
-        <v>15.74</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5">
-      <c r="A44" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B44" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C44" s="6">
-        <v>-73.84</v>
-      </c>
-      <c r="D44" s="6">
-        <v>-69.92</v>
-      </c>
-      <c r="E44" s="8">
-        <v>3.92</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5">
-      <c r="A45" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B45" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C45" s="6">
-        <v>-5.66</v>
-      </c>
-      <c r="D45" s="6">
-        <v>11.42</v>
-      </c>
-      <c r="E45" s="8">
-        <v>17.08</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5">
-      <c r="A46" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B46" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C46" s="6">
-        <v>7.93</v>
-      </c>
-      <c r="D46" s="6">
-        <v>7.95</v>
-      </c>
-      <c r="E46" s="8">
-        <v>0.02</v>
-      </c>
-    </row>
-    <row r="47" spans="1:5">
-      <c r="A47" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B47" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C47" s="6">
-        <v>-5.99</v>
-      </c>
-      <c r="D47" s="6">
+      <c r="C48" s="5">
         <v>-37.01</v>
       </c>
-      <c r="E47" s="7">
-        <v>-31.02</v>
+      <c r="D48" s="5">
+        <v>-11.69</v>
+      </c>
+      <c r="E48" s="7">
+        <v>25.32</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A6:E6"/>
+    <mergeCell ref="A5:E5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2412,60 +2369,60 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="28" customHeight="1">
-      <c r="A1" s="9" t="s">
+      <c r="A1" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="9" t="s">
+      <c r="B1" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="C1" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="D1" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="E1" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="F1" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="G1" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="H1" s="8" t="s">
+        <v>59</v>
+      </c>
+      <c r="I1" s="8" t="s">
         <v>60</v>
       </c>
-      <c r="C1" s="9" t="s">
-        <v>61</v>
-      </c>
-      <c r="D1" s="9" t="s">
-        <v>62</v>
-      </c>
-      <c r="E1" s="9" t="s">
-        <v>63</v>
-      </c>
-      <c r="F1" s="9" t="s">
-        <v>64</v>
-      </c>
-      <c r="G1" s="9" t="s">
-        <v>65</v>
-      </c>
-      <c r="H1" s="9" t="s">
-        <v>66</v>
-      </c>
-      <c r="I1" s="9" t="s">
-        <v>67</v>
-      </c>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="10" t="s">
+      <c r="A2" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="B2" s="11">
+      <c r="B2" s="10">
         <v>41.92</v>
       </c>
-      <c r="C2" s="12">
+      <c r="C2" s="11">
         <v>5</v>
       </c>
-      <c r="D2" s="11">
-        <v>35.5</v>
-      </c>
-      <c r="E2" s="11">
+      <c r="D2" s="10">
+        <v>33</v>
+      </c>
+      <c r="E2" s="10">
         <v>20</v>
       </c>
-      <c r="F2" s="11">
-        <v>-11.2</v>
-      </c>
-      <c r="G2" s="11">
-        <v>-4.5</v>
-      </c>
-      <c r="H2" s="11">
+      <c r="F2" s="10">
+        <v>-13.8</v>
+      </c>
+      <c r="G2" s="10">
+        <v>-7.7</v>
+      </c>
+      <c r="H2" s="10">
         <v>59.8</v>
       </c>
-      <c r="I2" s="11">
+      <c r="I2" s="10">
         <v>0</v>
       </c>
     </row>
@@ -2567,37 +2524,37 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
-      <c r="A1" s="13" t="s">
+      <c r="A1" s="12" t="s">
         <v>37</v>
       </c>
-      <c r="B1" s="13" t="s">
+      <c r="B1" s="12" t="s">
         <v>38</v>
       </c>
-      <c r="C1" s="13" t="s">
+      <c r="C1" s="12" t="s">
         <v>41</v>
       </c>
-      <c r="D1" s="13" t="s">
+      <c r="D1" s="12" t="s">
         <v>40</v>
       </c>
-      <c r="E1" s="13" t="s">
+      <c r="E1" s="12" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="2" spans="1:5">
-      <c r="A2" s="14">
-        <v>0.1945</v>
-      </c>
-      <c r="B2" s="14">
-        <v>0.0726</v>
-      </c>
-      <c r="C2" s="14">
-        <v>0.005500000000000001</v>
-      </c>
-      <c r="D2" s="14">
-        <v>-0.0503</v>
-      </c>
-      <c r="E2" s="14">
-        <v>-0.2261</v>
+      <c r="A2" s="13">
+        <v>0.1894</v>
+      </c>
+      <c r="B2" s="13">
+        <v>0.0698</v>
+      </c>
+      <c r="C2" s="13">
+        <v>0.0112</v>
+      </c>
+      <c r="D2" s="13">
+        <v>-0.0539</v>
+      </c>
+      <c r="E2" s="13">
+        <v>-0.2282</v>
       </c>
     </row>
   </sheetData>

--- a/HINDUJA_GROUP_Technical_Metrics.xlsx
+++ b/HINDUJA_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="211" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="123" uniqueCount="58">
   <si>
     <t>Symbol</t>
   </si>
@@ -169,16 +169,7 @@
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
   </si>
   <si>
-    <t>Metric</t>
-  </si>
-  <si>
-    <t>Previous</t>
-  </si>
-  <si>
-    <t>Current</t>
-  </si>
-  <si>
-    <t>Delta</t>
+    <t>No numeric changes detected since last run.</t>
   </si>
   <si>
     <t>Rank</t>
@@ -209,13 +200,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="4">
-    <numFmt numFmtId="164" formatCode="0.00"/>
-    <numFmt numFmtId="165" formatCode="+0.00;-0.00"/>
-    <numFmt numFmtId="166" formatCode="0.0"/>
-    <numFmt numFmtId="167" formatCode="0.00%"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="0.0"/>
+    <numFmt numFmtId="165" formatCode="0.00%"/>
   </numFmts>
-  <fonts count="6">
+  <fonts count="4">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -247,22 +236,8 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
-  <fills count="9">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -278,24 +253,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF2E4057"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF4A6FA5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -365,33 +322,27 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
@@ -1583,7 +1534,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F48"/>
+  <dimension ref="A1:F6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.7109375" customWidth="1"/>
@@ -1616,734 +1567,8 @@
       <c r="E5" s="2"/>
     </row>
     <row r="6" spans="1:6">
-      <c r="A6" s="4" t="s">
-        <v>0</v>
-      </c>
-      <c r="B6" s="4" t="s">
+      <c r="A6" s="3" t="s">
         <v>49</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="D6" s="4" t="s">
-        <v>51</v>
-      </c>
-      <c r="E6" s="4" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6">
-      <c r="A7" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C7" s="5">
-        <v>-11.72</v>
-      </c>
-      <c r="D7" s="5">
-        <v>-14.69</v>
-      </c>
-      <c r="E7" s="6">
-        <v>-2.97</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6">
-      <c r="A8" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="B8" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C8" s="5">
-        <v>-13.94</v>
-      </c>
-      <c r="D8" s="5">
-        <v>-18.16</v>
-      </c>
-      <c r="E8" s="6">
-        <v>-4.22</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
-      <c r="A9" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="B9" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C9" s="5">
-        <v>-9.08</v>
-      </c>
-      <c r="D9" s="5">
-        <v>-9.25</v>
-      </c>
-      <c r="E9" s="6">
-        <v>-0.17</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
-      <c r="A10" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="B10" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C10" s="5">
-        <v>-13.25</v>
-      </c>
-      <c r="D10" s="5">
-        <v>-13.43</v>
-      </c>
-      <c r="E10" s="6">
-        <v>-0.18</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
-      <c r="A11" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="B11" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C11" s="5">
-        <v>-8.130000000000001</v>
-      </c>
-      <c r="D11" s="5">
-        <v>-13.42</v>
-      </c>
-      <c r="E11" s="6">
-        <v>-5.29</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
-      <c r="A12" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B12" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C12" s="5">
-        <v>-2.76</v>
-      </c>
-      <c r="D12" s="5">
-        <v>-5.95</v>
-      </c>
-      <c r="E12" s="6">
-        <v>-3.19</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
-      <c r="A13" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="B13" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C13" s="5">
-        <v>1.15</v>
-      </c>
-      <c r="D13" s="5">
-        <v>-1.34</v>
-      </c>
-      <c r="E13" s="6">
-        <v>-2.49</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
-      <c r="A14" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="B14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C14" s="5">
-        <v>-0.83</v>
-      </c>
-      <c r="D14" s="5">
-        <v>-3</v>
-      </c>
-      <c r="E14" s="6">
-        <v>-2.17</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6">
-      <c r="A15" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="B15" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C15" s="5">
-        <v>-0.35</v>
-      </c>
-      <c r="D15" s="5">
-        <v>-4.15</v>
-      </c>
-      <c r="E15" s="6">
-        <v>-3.8</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
-      <c r="A16" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="B16" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C16" s="5">
-        <v>-0.76</v>
-      </c>
-      <c r="D16" s="5">
-        <v>-1.15</v>
-      </c>
-      <c r="E16" s="6">
-        <v>-0.39</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5">
-      <c r="A17" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B17" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C17" s="5">
-        <v>8.17</v>
-      </c>
-      <c r="D17" s="5">
-        <v>6.23</v>
-      </c>
-      <c r="E17" s="6">
-        <v>-1.94</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5">
-      <c r="A18" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="B18" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C18" s="5">
-        <v>2.22</v>
-      </c>
-      <c r="D18" s="5">
-        <v>-0.98</v>
-      </c>
-      <c r="E18" s="6">
-        <v>-3.2</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5">
-      <c r="A19" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="B19" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C19" s="5">
-        <v>-26.9</v>
-      </c>
-      <c r="D19" s="5">
-        <v>-28.81</v>
-      </c>
-      <c r="E19" s="6">
-        <v>-1.91</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5">
-      <c r="A20" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="B20" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C20" s="5">
-        <v>17.73</v>
-      </c>
-      <c r="D20" s="5">
-        <v>15.6</v>
-      </c>
-      <c r="E20" s="6">
-        <v>-2.13</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5">
-      <c r="A21" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="B21" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C21" s="5">
-        <v>-22.16</v>
-      </c>
-      <c r="D21" s="5">
-        <v>-23.67</v>
-      </c>
-      <c r="E21" s="6">
-        <v>-1.51</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5">
-      <c r="A22" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B22" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C22" s="5">
-        <v>-4.49</v>
-      </c>
-      <c r="D22" s="5">
-        <v>-6.55</v>
-      </c>
-      <c r="E22" s="6">
-        <v>-2.06</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5">
-      <c r="A23" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="B23" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C23" s="5">
-        <v>-6.76</v>
-      </c>
-      <c r="D23" s="5">
-        <v>-12.78</v>
-      </c>
-      <c r="E23" s="6">
-        <v>-6.02</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5">
-      <c r="A24" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="B24" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C24" s="5">
-        <v>-10.57</v>
-      </c>
-      <c r="D24" s="5">
-        <v>-12.43</v>
-      </c>
-      <c r="E24" s="6">
-        <v>-1.86</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5">
-      <c r="A25" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="B25" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C25" s="5">
-        <v>-12.04</v>
-      </c>
-      <c r="D25" s="5">
-        <v>-14.89</v>
-      </c>
-      <c r="E25" s="6">
-        <v>-2.85</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5">
-      <c r="A26" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="B26" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C26" s="5">
-        <v>11.59</v>
-      </c>
-      <c r="D26" s="5">
-        <v>7.95</v>
-      </c>
-      <c r="E26" s="6">
-        <v>-3.64</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5">
-      <c r="A27" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B27" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C27" s="5">
-        <v>-28.4</v>
-      </c>
-      <c r="D27" s="5">
-        <v>-30.4</v>
-      </c>
-      <c r="E27" s="6">
-        <v>-2</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5">
-      <c r="A28" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="B28" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C28" s="5">
-        <v>-19.36</v>
-      </c>
-      <c r="D28" s="5">
-        <v>-21.6</v>
-      </c>
-      <c r="E28" s="6">
-        <v>-2.24</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5">
-      <c r="A29" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="B29" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C29" s="5">
-        <v>-32.02</v>
-      </c>
-      <c r="D29" s="5">
-        <v>-32.78</v>
-      </c>
-      <c r="E29" s="6">
-        <v>-0.76</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5">
-      <c r="A30" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="B30" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C30" s="5">
-        <v>-18.18</v>
-      </c>
-      <c r="D30" s="5">
-        <v>-19.2</v>
-      </c>
-      <c r="E30" s="6">
-        <v>-1.02</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5">
-      <c r="A31" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="B31" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C31" s="5">
-        <v>-23.08</v>
-      </c>
-      <c r="D31" s="5">
-        <v>-23.67</v>
-      </c>
-      <c r="E31" s="6">
-        <v>-0.59</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5">
-      <c r="A32" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B32" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C32" s="5">
-        <v>149.2</v>
-      </c>
-      <c r="D32" s="5">
-        <v>145.02</v>
-      </c>
-      <c r="E32" s="6">
-        <v>-4.18</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5">
-      <c r="A33" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="B33" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C33" s="5">
-        <v>367.85</v>
-      </c>
-      <c r="D33" s="5">
-        <v>357.6</v>
-      </c>
-      <c r="E33" s="6">
-        <v>-10.25</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5">
-      <c r="A34" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="B34" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C34" s="5">
-        <v>363</v>
-      </c>
-      <c r="D34" s="5">
-        <v>358.95</v>
-      </c>
-      <c r="E34" s="6">
-        <v>-4.05</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5">
-      <c r="A35" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="B35" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C35" s="5">
-        <v>874.9</v>
-      </c>
-      <c r="D35" s="5">
-        <v>864</v>
-      </c>
-      <c r="E35" s="6">
-        <v>-10.9</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5">
-      <c r="A36" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="B36" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C36" s="5">
-        <v>2.6</v>
-      </c>
-      <c r="D36" s="5">
-        <v>2.58</v>
-      </c>
-      <c r="E36" s="6">
-        <v>-0.02</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5">
-      <c r="A37" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="B37" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="C37" s="5">
-        <v>60</v>
-      </c>
-      <c r="D37" s="5">
-        <v>40</v>
-      </c>
-      <c r="E37" s="6">
-        <v>-20</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5">
-      <c r="A38" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="B38" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="C38" s="5">
-        <v>40</v>
-      </c>
-      <c r="D38" s="5">
-        <v>60</v>
-      </c>
-      <c r="E38" s="7">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5">
-      <c r="A39" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B39" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C39" s="5">
-        <v>33.19</v>
-      </c>
-      <c r="D39" s="5">
-        <v>29.32</v>
-      </c>
-      <c r="E39" s="6">
-        <v>-3.87</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5">
-      <c r="A40" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="B40" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C40" s="5">
-        <v>40.12</v>
-      </c>
-      <c r="D40" s="5">
-        <v>37.26</v>
-      </c>
-      <c r="E40" s="6">
-        <v>-2.86</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5">
-      <c r="A41" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="B41" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C41" s="5">
-        <v>28.31</v>
-      </c>
-      <c r="D41" s="5">
-        <v>25.71</v>
-      </c>
-      <c r="E41" s="6">
-        <v>-2.6</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5">
-      <c r="A42" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="B42" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C42" s="5">
-        <v>32.16</v>
-      </c>
-      <c r="D42" s="5">
-        <v>30.37</v>
-      </c>
-      <c r="E42" s="6">
-        <v>-1.79</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5">
-      <c r="A43" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="B43" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C43" s="5">
-        <v>43.73</v>
-      </c>
-      <c r="D43" s="5">
-        <v>42.44</v>
-      </c>
-      <c r="E43" s="6">
-        <v>-1.29</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5">
-      <c r="A44" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B44" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C44" s="5">
-        <v>-0.98</v>
-      </c>
-      <c r="D44" s="5">
-        <v>33.42</v>
-      </c>
-      <c r="E44" s="7">
-        <v>34.4</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5">
-      <c r="A45" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="B45" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C45" s="5">
-        <v>-69.92</v>
-      </c>
-      <c r="D45" s="5">
-        <v>-81.59999999999999</v>
-      </c>
-      <c r="E45" s="6">
-        <v>-11.68</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5">
-      <c r="A46" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="B46" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C46" s="5">
-        <v>11.42</v>
-      </c>
-      <c r="D46" s="5">
-        <v>-36.63</v>
-      </c>
-      <c r="E46" s="6">
-        <v>-48.05</v>
-      </c>
-    </row>
-    <row r="47" spans="1:5">
-      <c r="A47" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="B47" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C47" s="5">
-        <v>7.95</v>
-      </c>
-      <c r="D47" s="5">
-        <v>-26.94</v>
-      </c>
-      <c r="E47" s="6">
-        <v>-34.89</v>
-      </c>
-    </row>
-    <row r="48" spans="1:5">
-      <c r="A48" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="B48" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C48" s="5">
-        <v>-37.01</v>
-      </c>
-      <c r="D48" s="5">
-        <v>-11.69</v>
-      </c>
-      <c r="E48" s="7">
-        <v>25.32</v>
       </c>
     </row>
   </sheetData>
@@ -2369,60 +1594,60 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="28" customHeight="1">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="8" t="s">
+      <c r="B1" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="D1" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="E1" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="C1" s="8" t="s">
+      <c r="F1" s="4" t="s">
         <v>54</v>
       </c>
-      <c r="D1" s="8" t="s">
+      <c r="G1" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="E1" s="8" t="s">
+      <c r="H1" s="4" t="s">
         <v>56</v>
       </c>
-      <c r="F1" s="8" t="s">
+      <c r="I1" s="4" t="s">
         <v>57</v>
-      </c>
-      <c r="G1" s="8" t="s">
-        <v>58</v>
-      </c>
-      <c r="H1" s="8" t="s">
-        <v>59</v>
-      </c>
-      <c r="I1" s="8" t="s">
-        <v>60</v>
       </c>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="9" t="s">
+      <c r="A2" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="B2" s="10">
+      <c r="B2" s="6">
         <v>41.92</v>
       </c>
-      <c r="C2" s="11">
+      <c r="C2" s="7">
         <v>5</v>
       </c>
-      <c r="D2" s="10">
+      <c r="D2" s="6">
         <v>33</v>
       </c>
-      <c r="E2" s="10">
+      <c r="E2" s="6">
         <v>20</v>
       </c>
-      <c r="F2" s="10">
+      <c r="F2" s="6">
         <v>-13.8</v>
       </c>
-      <c r="G2" s="10">
+      <c r="G2" s="6">
         <v>-7.7</v>
       </c>
-      <c r="H2" s="10">
+      <c r="H2" s="6">
         <v>59.8</v>
       </c>
-      <c r="I2" s="10">
+      <c r="I2" s="6">
         <v>0</v>
       </c>
     </row>
@@ -2524,36 +1749,36 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
-      <c r="A1" s="12" t="s">
+      <c r="A1" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="B1" s="12" t="s">
+      <c r="B1" s="8" t="s">
         <v>38</v>
       </c>
-      <c r="C1" s="12" t="s">
+      <c r="C1" s="8" t="s">
         <v>41</v>
       </c>
-      <c r="D1" s="12" t="s">
+      <c r="D1" s="8" t="s">
         <v>40</v>
       </c>
-      <c r="E1" s="12" t="s">
+      <c r="E1" s="8" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="2" spans="1:5">
-      <c r="A2" s="13">
+      <c r="A2" s="9">
         <v>0.1894</v>
       </c>
-      <c r="B2" s="13">
+      <c r="B2" s="9">
         <v>0.0698</v>
       </c>
-      <c r="C2" s="13">
+      <c r="C2" s="9">
         <v>0.0112</v>
       </c>
-      <c r="D2" s="13">
+      <c r="D2" s="9">
         <v>-0.0539</v>
       </c>
-      <c r="E2" s="13">
+      <c r="E2" s="9">
         <v>-0.2282</v>
       </c>
     </row>

--- a/HINDUJA_GROUP_Technical_Metrics.xlsx
+++ b/HINDUJA_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="123" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="201" uniqueCount="61">
   <si>
     <t>Symbol</t>
   </si>
@@ -169,7 +169,16 @@
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
   </si>
   <si>
-    <t>No numeric changes detected since last run.</t>
+    <t>Metric</t>
+  </si>
+  <si>
+    <t>Previous</t>
+  </si>
+  <si>
+    <t>Current</t>
+  </si>
+  <si>
+    <t>Delta</t>
   </si>
   <si>
     <t>Rank</t>
@@ -200,11 +209,13 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="0.0"/>
-    <numFmt numFmtId="165" formatCode="0.00%"/>
+  <numFmts count="4">
+    <numFmt numFmtId="164" formatCode="0.00"/>
+    <numFmt numFmtId="165" formatCode="+0.00;-0.00"/>
+    <numFmt numFmtId="166" formatCode="0.0"/>
+    <numFmt numFmtId="167" formatCode="0.00%"/>
   </numFmts>
-  <fonts count="4">
+  <fonts count="6">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -236,8 +247,22 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="6">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -253,6 +278,24 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF2E4057"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4A6FA5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -322,27 +365,33 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
@@ -839,10 +888,10 @@
         <v>42</v>
       </c>
       <c r="C2">
-        <v>145.02</v>
+        <v>145.06</v>
       </c>
       <c r="D2">
-        <v>-2.8</v>
+        <v>0.03</v>
       </c>
       <c r="E2">
         <v>208.37</v>
@@ -851,25 +900,25 @@
         <v>131.36</v>
       </c>
       <c r="G2">
-        <v>-30.4</v>
+        <v>-30.38</v>
       </c>
       <c r="H2">
-        <v>10.4</v>
+        <v>10.43</v>
       </c>
       <c r="I2">
-        <v>-5.95</v>
+        <v>-3.6</v>
       </c>
       <c r="J2">
-        <v>-14.69</v>
+        <v>-14.17</v>
       </c>
       <c r="K2">
-        <v>-6.55</v>
+        <v>-7.89</v>
       </c>
       <c r="L2">
-        <v>6.23</v>
+        <v>7.8</v>
       </c>
       <c r="M2">
-        <v>18.94</v>
+        <v>18.64</v>
       </c>
       <c r="N2">
         <v>79</v>
@@ -878,19 +927,19 @@
         <v>61</v>
       </c>
       <c r="P2">
-        <v>150.2</v>
+        <v>149.12</v>
       </c>
       <c r="Q2">
-        <v>157.36</v>
+        <v>156.27</v>
       </c>
       <c r="R2">
-        <v>166.53</v>
+        <v>166.27</v>
       </c>
       <c r="S2">
-        <v>169.57</v>
+        <v>169.44</v>
       </c>
       <c r="T2">
-        <v>-14.48</v>
+        <v>-14.39</v>
       </c>
       <c r="U2" t="s">
         <v>43</v>
@@ -905,43 +954,43 @@
         <v>0</v>
       </c>
       <c r="Y2">
-        <v>29.32</v>
+        <v>29.41</v>
       </c>
       <c r="Z2">
-        <v>-4.89</v>
+        <v>-5.21</v>
       </c>
       <c r="AA2">
-        <v>-3.91</v>
+        <v>-4.17</v>
       </c>
       <c r="AB2">
-        <v>-0.98</v>
+        <v>-1.04</v>
       </c>
       <c r="AC2">
-        <v>23.18</v>
+        <v>4.13</v>
       </c>
       <c r="AD2">
-        <v>32.96</v>
+        <v>21.61</v>
       </c>
       <c r="AE2">
-        <v>4.12</v>
+        <v>4.09</v>
       </c>
       <c r="AF2">
-        <v>33.42</v>
+        <v>-9.25</v>
       </c>
       <c r="AG2">
-        <v>168.99</v>
+        <v>168.2</v>
       </c>
       <c r="AH2">
-        <v>145.74</v>
+        <v>144.34</v>
       </c>
       <c r="AI2">
-        <v>159.51</v>
+        <v>157.74</v>
       </c>
       <c r="AJ2" t="s">
         <v>45</v>
       </c>
       <c r="AK2">
-        <v>56.79</v>
+        <v>60.04</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -952,10 +1001,10 @@
         <v>42</v>
       </c>
       <c r="C3">
-        <v>357.6</v>
+        <v>357.5</v>
       </c>
       <c r="D3">
-        <v>-2.79</v>
+        <v>-0.03</v>
       </c>
       <c r="E3">
         <v>456.15</v>
@@ -964,25 +1013,25 @@
         <v>225</v>
       </c>
       <c r="G3">
-        <v>-21.6</v>
+        <v>-21.63</v>
       </c>
       <c r="H3">
-        <v>58.93</v>
+        <v>58.89</v>
       </c>
       <c r="I3">
-        <v>-1.34</v>
+        <v>1.66</v>
       </c>
       <c r="J3">
-        <v>-18.16</v>
+        <v>-17.93</v>
       </c>
       <c r="K3">
-        <v>-12.78</v>
+        <v>-12.01</v>
       </c>
       <c r="L3">
-        <v>-0.98</v>
+        <v>-0.75</v>
       </c>
       <c r="M3">
-        <v>6.98</v>
+        <v>3.15</v>
       </c>
       <c r="N3">
         <v>40</v>
@@ -991,19 +1040,19 @@
         <v>49</v>
       </c>
       <c r="P3">
-        <v>359.45</v>
+        <v>360.62</v>
       </c>
       <c r="Q3">
-        <v>399.79</v>
+        <v>396.08</v>
       </c>
       <c r="R3">
-        <v>405.08</v>
+        <v>404.57</v>
       </c>
       <c r="S3">
-        <v>339.33</v>
+        <v>339.65</v>
       </c>
       <c r="T3">
-        <v>5.38</v>
+        <v>5.26</v>
       </c>
       <c r="U3" t="s">
         <v>43</v>
@@ -1018,34 +1067,34 @@
         <v>2</v>
       </c>
       <c r="Y3">
-        <v>37.26</v>
+        <v>37.23</v>
       </c>
       <c r="Z3">
-        <v>-15.41</v>
+        <v>-15.7</v>
       </c>
       <c r="AA3">
-        <v>-10.45</v>
+        <v>-11.5</v>
       </c>
       <c r="AB3">
-        <v>-4.96</v>
+        <v>-4.21</v>
       </c>
       <c r="AC3">
-        <v>26.45</v>
+        <v>23.39</v>
       </c>
       <c r="AD3">
-        <v>18.64</v>
+        <v>23.03</v>
       </c>
       <c r="AE3">
-        <v>17.9</v>
+        <v>17.33</v>
       </c>
       <c r="AF3">
-        <v>-81.59999999999999</v>
+        <v>-85.31</v>
       </c>
       <c r="AG3">
-        <v>474.66</v>
+        <v>471.65</v>
       </c>
       <c r="AH3">
-        <v>324.91</v>
+        <v>320.5</v>
       </c>
       <c r="AI3">
         <v>404.18</v>
@@ -1054,7 +1103,7 @@
         <v>45</v>
       </c>
       <c r="AK3">
-        <v>44.17</v>
+        <v>42.82</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1065,10 +1114,10 @@
         <v>42</v>
       </c>
       <c r="C4">
-        <v>358.95</v>
+        <v>355.55</v>
       </c>
       <c r="D4">
-        <v>-1.12</v>
+        <v>-0.95</v>
       </c>
       <c r="E4">
         <v>534</v>
@@ -1077,25 +1126,25 @@
         <v>344.7</v>
       </c>
       <c r="G4">
-        <v>-32.78</v>
+        <v>-33.42</v>
       </c>
       <c r="H4">
-        <v>4.13</v>
+        <v>3.15</v>
       </c>
       <c r="I4">
-        <v>-3</v>
+        <v>-3.13</v>
       </c>
       <c r="J4">
-        <v>-9.25</v>
+        <v>-8.35</v>
       </c>
       <c r="K4">
-        <v>-12.43</v>
+        <v>-13.96</v>
       </c>
       <c r="L4">
-        <v>-28.81</v>
+        <v>-28</v>
       </c>
       <c r="M4">
-        <v>-22.82</v>
+        <v>-22.8</v>
       </c>
       <c r="N4">
         <v>21</v>
@@ -1104,19 +1153,19 @@
         <v>29</v>
       </c>
       <c r="P4">
-        <v>363.07</v>
+        <v>360.77</v>
       </c>
       <c r="Q4">
-        <v>374.72</v>
+        <v>373.26</v>
       </c>
       <c r="R4">
-        <v>394.95</v>
+        <v>393.59</v>
       </c>
       <c r="S4">
-        <v>405.66</v>
+        <v>405.23</v>
       </c>
       <c r="T4">
-        <v>-11.51</v>
+        <v>-12.26</v>
       </c>
       <c r="U4" t="s">
         <v>43</v>
@@ -1131,43 +1180,43 @@
         <v>0</v>
       </c>
       <c r="Y4">
-        <v>25.71</v>
+        <v>23.74</v>
       </c>
       <c r="Z4">
-        <v>-9.529999999999999</v>
+        <v>-9.869999999999999</v>
       </c>
       <c r="AA4">
-        <v>-8.869999999999999</v>
+        <v>-9.07</v>
       </c>
       <c r="AB4">
-        <v>-0.65</v>
+        <v>-0.8</v>
       </c>
       <c r="AC4">
-        <v>19.04</v>
+        <v>16.16</v>
       </c>
       <c r="AD4">
-        <v>22.92</v>
+        <v>19.61</v>
       </c>
       <c r="AE4">
-        <v>9.91</v>
+        <v>9.93</v>
       </c>
       <c r="AF4">
-        <v>-36.63</v>
+        <v>13.02</v>
       </c>
       <c r="AG4">
-        <v>392.09</v>
+        <v>391.94</v>
       </c>
       <c r="AH4">
-        <v>357.34</v>
+        <v>354.57</v>
       </c>
       <c r="AI4">
-        <v>390.55</v>
+        <v>386.47</v>
       </c>
       <c r="AJ4" t="s">
         <v>45</v>
       </c>
       <c r="AK4">
-        <v>49.28</v>
+        <v>52.65</v>
       </c>
     </row>
     <row r="5" spans="1:37">
@@ -1178,37 +1227,37 @@
         <v>42</v>
       </c>
       <c r="C5">
-        <v>864</v>
+        <v>861.65</v>
       </c>
       <c r="D5">
-        <v>-1.25</v>
+        <v>-0.27</v>
       </c>
       <c r="E5">
         <v>1069.3</v>
       </c>
       <c r="F5">
-        <v>739.3</v>
+        <v>739.5</v>
       </c>
       <c r="G5">
-        <v>-19.2</v>
+        <v>-19.42</v>
       </c>
       <c r="H5">
-        <v>16.87</v>
+        <v>16.52</v>
       </c>
       <c r="I5">
-        <v>-4.15</v>
+        <v>-2.84</v>
       </c>
       <c r="J5">
-        <v>-13.43</v>
+        <v>-13.64</v>
       </c>
       <c r="K5">
-        <v>-14.89</v>
+        <v>-15.18</v>
       </c>
       <c r="L5">
-        <v>15.6</v>
+        <v>16.55</v>
       </c>
       <c r="M5">
-        <v>-5.39</v>
+        <v>-5.43</v>
       </c>
       <c r="N5">
         <v>99</v>
@@ -1217,19 +1266,19 @@
         <v>63</v>
       </c>
       <c r="P5">
-        <v>883.6900000000001</v>
+        <v>878.65</v>
       </c>
       <c r="Q5">
-        <v>930.63</v>
+        <v>923.51</v>
       </c>
       <c r="R5">
-        <v>979.13</v>
+        <v>976.12</v>
       </c>
       <c r="S5">
-        <v>924.85</v>
+        <v>924.9299999999999</v>
       </c>
       <c r="T5">
-        <v>-6.58</v>
+        <v>-6.84</v>
       </c>
       <c r="U5" t="s">
         <v>43</v>
@@ -1244,43 +1293,43 @@
         <v>1</v>
       </c>
       <c r="Y5">
-        <v>30.37</v>
+        <v>29.98</v>
       </c>
       <c r="Z5">
-        <v>-30.58</v>
+        <v>-31.63</v>
       </c>
       <c r="AA5">
-        <v>-25.7</v>
+        <v>-26.88</v>
       </c>
       <c r="AB5">
-        <v>-4.88</v>
+        <v>-4.74</v>
       </c>
       <c r="AC5">
-        <v>55.45</v>
+        <v>41.01</v>
       </c>
       <c r="AD5">
-        <v>54.91</v>
+        <v>50.82</v>
       </c>
       <c r="AE5">
-        <v>22.8</v>
+        <v>21.99</v>
       </c>
       <c r="AF5">
-        <v>-26.94</v>
+        <v>-51.16</v>
       </c>
       <c r="AG5">
-        <v>1014.12</v>
+        <v>1004.91</v>
       </c>
       <c r="AH5">
-        <v>847.13</v>
+        <v>842.11</v>
       </c>
       <c r="AI5">
-        <v>935.89</v>
+        <v>929.63</v>
       </c>
       <c r="AJ5" t="s">
         <v>45</v>
       </c>
       <c r="AK5">
-        <v>56.19</v>
+        <v>58.05</v>
       </c>
     </row>
     <row r="6" spans="1:37">
@@ -1294,7 +1343,7 @@
         <v>2.58</v>
       </c>
       <c r="D6">
-        <v>-0.77</v>
+        <v>0</v>
       </c>
       <c r="E6">
         <v>3.38</v>
@@ -1309,19 +1358,19 @@
         <v>40.22</v>
       </c>
       <c r="I6">
-        <v>-1.15</v>
+        <v>1.57</v>
       </c>
       <c r="J6">
-        <v>-13.42</v>
+        <v>-11.64</v>
       </c>
       <c r="K6">
-        <v>7.95</v>
+        <v>7.5</v>
       </c>
       <c r="L6">
-        <v>-23.67</v>
+        <v>-21.34</v>
       </c>
       <c r="M6">
-        <v>1.12</v>
+        <v>1.21</v>
       </c>
       <c r="N6">
         <v>60</v>
@@ -1333,7 +1382,7 @@
         <v>2.58</v>
       </c>
       <c r="Q6">
-        <v>2.72</v>
+        <v>2.7</v>
       </c>
       <c r="R6">
         <v>2.64</v>
@@ -1342,7 +1391,7 @@
         <v>2.65</v>
       </c>
       <c r="T6">
-        <v>-2.62</v>
+        <v>-2.55</v>
       </c>
       <c r="U6" t="s">
         <v>44</v>
@@ -1363,37 +1412,37 @@
         <v>-0.04</v>
       </c>
       <c r="AA6">
-        <v>-0.01</v>
+        <v>-0.02</v>
       </c>
       <c r="AB6">
-        <v>-0.03</v>
+        <v>-0.02</v>
       </c>
       <c r="AC6">
-        <v>26.03</v>
+        <v>31.05</v>
       </c>
       <c r="AD6">
-        <v>20.17</v>
+        <v>26.68</v>
       </c>
       <c r="AE6">
         <v>0.13</v>
       </c>
       <c r="AF6">
-        <v>-11.69</v>
+        <v>-38.12</v>
       </c>
       <c r="AG6">
-        <v>2.96</v>
+        <v>2.93</v>
       </c>
       <c r="AH6">
         <v>2.47</v>
       </c>
       <c r="AI6">
-        <v>2.99</v>
+        <v>2.97</v>
       </c>
       <c r="AJ6" t="s">
         <v>45</v>
       </c>
       <c r="AK6">
-        <v>28.98</v>
+        <v>29.1</v>
       </c>
     </row>
   </sheetData>
@@ -1534,7 +1583,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:F43"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.7109375" customWidth="1"/>
@@ -1567,8 +1616,649 @@
       <c r="E5" s="2"/>
     </row>
     <row r="6" spans="1:6">
-      <c r="A6" s="3" t="s">
+      <c r="A6" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="B6" s="4" t="s">
         <v>49</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="E6" s="4" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6">
+      <c r="A7" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C7" s="5">
+        <v>-14.69</v>
+      </c>
+      <c r="D7" s="5">
+        <v>-14.17</v>
+      </c>
+      <c r="E7" s="6">
+        <v>0.52</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6">
+      <c r="A8" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C8" s="5">
+        <v>-18.16</v>
+      </c>
+      <c r="D8" s="5">
+        <v>-17.93</v>
+      </c>
+      <c r="E8" s="6">
+        <v>0.23</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="A9" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C9" s="5">
+        <v>-9.25</v>
+      </c>
+      <c r="D9" s="5">
+        <v>-8.35</v>
+      </c>
+      <c r="E9" s="6">
+        <v>0.9</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="A10" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C10" s="5">
+        <v>-13.43</v>
+      </c>
+      <c r="D10" s="5">
+        <v>-13.64</v>
+      </c>
+      <c r="E10" s="7">
+        <v>-0.21</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="A11" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C11" s="5">
+        <v>-13.42</v>
+      </c>
+      <c r="D11" s="5">
+        <v>-11.64</v>
+      </c>
+      <c r="E11" s="6">
+        <v>1.78</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6">
+      <c r="A12" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C12" s="5">
+        <v>-5.95</v>
+      </c>
+      <c r="D12" s="5">
+        <v>-3.6</v>
+      </c>
+      <c r="E12" s="6">
+        <v>2.35</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6">
+      <c r="A13" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C13" s="5">
+        <v>-1.34</v>
+      </c>
+      <c r="D13" s="5">
+        <v>1.66</v>
+      </c>
+      <c r="E13" s="6">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6">
+      <c r="A14" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C14" s="5">
+        <v>-3</v>
+      </c>
+      <c r="D14" s="5">
+        <v>-3.13</v>
+      </c>
+      <c r="E14" s="7">
+        <v>-0.13</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6">
+      <c r="A15" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C15" s="5">
+        <v>-4.15</v>
+      </c>
+      <c r="D15" s="5">
+        <v>-2.84</v>
+      </c>
+      <c r="E15" s="6">
+        <v>1.31</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6">
+      <c r="A16" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C16" s="5">
+        <v>-1.15</v>
+      </c>
+      <c r="D16" s="5">
+        <v>1.57</v>
+      </c>
+      <c r="E16" s="6">
+        <v>2.72</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C17" s="5">
+        <v>6.23</v>
+      </c>
+      <c r="D17" s="5">
+        <v>7.8</v>
+      </c>
+      <c r="E17" s="6">
+        <v>1.57</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C18" s="5">
+        <v>-0.98</v>
+      </c>
+      <c r="D18" s="5">
+        <v>-0.75</v>
+      </c>
+      <c r="E18" s="6">
+        <v>0.23</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C19" s="5">
+        <v>-28.81</v>
+      </c>
+      <c r="D19" s="5">
+        <v>-28</v>
+      </c>
+      <c r="E19" s="6">
+        <v>0.8100000000000001</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C20" s="5">
+        <v>15.6</v>
+      </c>
+      <c r="D20" s="5">
+        <v>16.55</v>
+      </c>
+      <c r="E20" s="6">
+        <v>0.95</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C21" s="5">
+        <v>-23.67</v>
+      </c>
+      <c r="D21" s="5">
+        <v>-21.34</v>
+      </c>
+      <c r="E21" s="6">
+        <v>2.33</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B22" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C22" s="5">
+        <v>-6.55</v>
+      </c>
+      <c r="D22" s="5">
+        <v>-7.89</v>
+      </c>
+      <c r="E22" s="7">
+        <v>-1.34</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B23" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C23" s="5">
+        <v>-12.78</v>
+      </c>
+      <c r="D23" s="5">
+        <v>-12.01</v>
+      </c>
+      <c r="E23" s="6">
+        <v>0.77</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5">
+      <c r="A24" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B24" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C24" s="5">
+        <v>-12.43</v>
+      </c>
+      <c r="D24" s="5">
+        <v>-13.96</v>
+      </c>
+      <c r="E24" s="7">
+        <v>-1.53</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5">
+      <c r="A25" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B25" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C25" s="5">
+        <v>-14.89</v>
+      </c>
+      <c r="D25" s="5">
+        <v>-15.18</v>
+      </c>
+      <c r="E25" s="7">
+        <v>-0.29</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
+      <c r="A26" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B26" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C26" s="5">
+        <v>7.95</v>
+      </c>
+      <c r="D26" s="5">
+        <v>7.5</v>
+      </c>
+      <c r="E26" s="7">
+        <v>-0.45</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5">
+      <c r="A27" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B27" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C27" s="5">
+        <v>-30.4</v>
+      </c>
+      <c r="D27" s="5">
+        <v>-30.38</v>
+      </c>
+      <c r="E27" s="6">
+        <v>0.02</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5">
+      <c r="A28" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B28" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C28" s="5">
+        <v>-21.6</v>
+      </c>
+      <c r="D28" s="5">
+        <v>-21.63</v>
+      </c>
+      <c r="E28" s="7">
+        <v>-0.03</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5">
+      <c r="A29" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B29" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C29" s="5">
+        <v>-32.78</v>
+      </c>
+      <c r="D29" s="5">
+        <v>-33.42</v>
+      </c>
+      <c r="E29" s="7">
+        <v>-0.64</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5">
+      <c r="A30" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B30" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C30" s="5">
+        <v>-19.2</v>
+      </c>
+      <c r="D30" s="5">
+        <v>-19.42</v>
+      </c>
+      <c r="E30" s="7">
+        <v>-0.22</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5">
+      <c r="A31" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B31" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C31" s="5">
+        <v>145.02</v>
+      </c>
+      <c r="D31" s="5">
+        <v>145.06</v>
+      </c>
+      <c r="E31" s="6">
+        <v>0.04</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5">
+      <c r="A32" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B32" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C32" s="5">
+        <v>357.6</v>
+      </c>
+      <c r="D32" s="5">
+        <v>357.5</v>
+      </c>
+      <c r="E32" s="7">
+        <v>-0.1</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5">
+      <c r="A33" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B33" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C33" s="5">
+        <v>358.95</v>
+      </c>
+      <c r="D33" s="5">
+        <v>355.55</v>
+      </c>
+      <c r="E33" s="7">
+        <v>-3.4</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5">
+      <c r="A34" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B34" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C34" s="5">
+        <v>864</v>
+      </c>
+      <c r="D34" s="5">
+        <v>861.65</v>
+      </c>
+      <c r="E34" s="7">
+        <v>-2.35</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5">
+      <c r="A35" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B35" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C35" s="5">
+        <v>29.32</v>
+      </c>
+      <c r="D35" s="5">
+        <v>29.41</v>
+      </c>
+      <c r="E35" s="6">
+        <v>0.09</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5">
+      <c r="A36" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B36" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C36" s="5">
+        <v>37.26</v>
+      </c>
+      <c r="D36" s="5">
+        <v>37.23</v>
+      </c>
+      <c r="E36" s="7">
+        <v>-0.03</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5">
+      <c r="A37" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B37" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C37" s="5">
+        <v>25.71</v>
+      </c>
+      <c r="D37" s="5">
+        <v>23.74</v>
+      </c>
+      <c r="E37" s="7">
+        <v>-1.97</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5">
+      <c r="A38" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B38" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C38" s="5">
+        <v>30.37</v>
+      </c>
+      <c r="D38" s="5">
+        <v>29.98</v>
+      </c>
+      <c r="E38" s="7">
+        <v>-0.39</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5">
+      <c r="A39" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B39" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C39" s="5">
+        <v>33.42</v>
+      </c>
+      <c r="D39" s="5">
+        <v>-9.25</v>
+      </c>
+      <c r="E39" s="7">
+        <v>-42.67</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5">
+      <c r="A40" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B40" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C40" s="5">
+        <v>-81.59999999999999</v>
+      </c>
+      <c r="D40" s="5">
+        <v>-85.31</v>
+      </c>
+      <c r="E40" s="7">
+        <v>-3.71</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5">
+      <c r="A41" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B41" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C41" s="5">
+        <v>-36.63</v>
+      </c>
+      <c r="D41" s="5">
+        <v>13.02</v>
+      </c>
+      <c r="E41" s="6">
+        <v>49.65</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5">
+      <c r="A42" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B42" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C42" s="5">
+        <v>-26.94</v>
+      </c>
+      <c r="D42" s="5">
+        <v>-51.16</v>
+      </c>
+      <c r="E42" s="7">
+        <v>-24.22</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5">
+      <c r="A43" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B43" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C43" s="5">
+        <v>-11.69</v>
+      </c>
+      <c r="D43" s="5">
+        <v>-38.12</v>
+      </c>
+      <c r="E43" s="7">
+        <v>-26.43</v>
       </c>
     </row>
   </sheetData>
@@ -1594,60 +2284,60 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="28" customHeight="1">
-      <c r="A1" s="4" t="s">
+      <c r="A1" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="C1" s="4" t="s">
-        <v>51</v>
-      </c>
-      <c r="D1" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="E1" s="4" t="s">
+      <c r="B1" s="8" t="s">
         <v>53</v>
       </c>
-      <c r="F1" s="4" t="s">
+      <c r="C1" s="8" t="s">
         <v>54</v>
       </c>
-      <c r="G1" s="4" t="s">
+      <c r="D1" s="8" t="s">
         <v>55</v>
       </c>
-      <c r="H1" s="4" t="s">
+      <c r="E1" s="8" t="s">
         <v>56</v>
       </c>
-      <c r="I1" s="4" t="s">
+      <c r="F1" s="8" t="s">
         <v>57</v>
       </c>
+      <c r="G1" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="H1" s="8" t="s">
+        <v>59</v>
+      </c>
+      <c r="I1" s="8" t="s">
+        <v>60</v>
+      </c>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="5" t="s">
+      <c r="A2" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="B2" s="6">
+      <c r="B2" s="10">
         <v>41.92</v>
       </c>
-      <c r="C2" s="7">
+      <c r="C2" s="11">
         <v>5</v>
       </c>
-      <c r="D2" s="6">
-        <v>33</v>
-      </c>
-      <c r="E2" s="6">
+      <c r="D2" s="10">
+        <v>32.6</v>
+      </c>
+      <c r="E2" s="10">
         <v>20</v>
       </c>
-      <c r="F2" s="6">
-        <v>-13.8</v>
-      </c>
-      <c r="G2" s="6">
-        <v>-7.7</v>
-      </c>
-      <c r="H2" s="6">
+      <c r="F2" s="10">
+        <v>-13.1</v>
+      </c>
+      <c r="G2" s="10">
+        <v>-8.300000000000001</v>
+      </c>
+      <c r="H2" s="10">
         <v>59.8</v>
       </c>
-      <c r="I2" s="6">
+      <c r="I2" s="10">
         <v>0</v>
       </c>
     </row>
@@ -1749,37 +2439,37 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="12" t="s">
         <v>37</v>
       </c>
-      <c r="B1" s="8" t="s">
+      <c r="B1" s="12" t="s">
         <v>38</v>
       </c>
-      <c r="C1" s="8" t="s">
+      <c r="C1" s="12" t="s">
         <v>41</v>
       </c>
-      <c r="D1" s="8" t="s">
+      <c r="D1" s="12" t="s">
         <v>40</v>
       </c>
-      <c r="E1" s="8" t="s">
+      <c r="E1" s="12" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="2" spans="1:5">
-      <c r="A2" s="9">
-        <v>0.1894</v>
-      </c>
-      <c r="B2" s="9">
-        <v>0.0698</v>
-      </c>
-      <c r="C2" s="9">
-        <v>0.0112</v>
-      </c>
-      <c r="D2" s="9">
-        <v>-0.0539</v>
-      </c>
-      <c r="E2" s="9">
-        <v>-0.2282</v>
+      <c r="A2" s="13">
+        <v>0.1864</v>
+      </c>
+      <c r="B2" s="13">
+        <v>0.0315</v>
+      </c>
+      <c r="C2" s="13">
+        <v>0.0121</v>
+      </c>
+      <c r="D2" s="13">
+        <v>-0.05429999999999999</v>
+      </c>
+      <c r="E2" s="13">
+        <v>-0.228</v>
       </c>
     </row>
   </sheetData>

--- a/HINDUJA_GROUP_Technical_Metrics.xlsx
+++ b/HINDUJA_GROUP_Technical_Metrics.xlsx
@@ -924,7 +924,7 @@
         <v>79</v>
       </c>
       <c r="O2">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="P2">
         <v>149.12</v>
@@ -1037,7 +1037,7 @@
         <v>40</v>
       </c>
       <c r="O3">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="P3">
         <v>360.62</v>
@@ -1150,7 +1150,7 @@
         <v>21</v>
       </c>
       <c r="O4">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="P4">
         <v>360.77</v>
@@ -1376,7 +1376,7 @@
         <v>60</v>
       </c>
       <c r="O6">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="P6">
         <v>2.58</v>

--- a/HINDUJA_GROUP_Technical_Metrics.xlsx
+++ b/HINDUJA_GROUP_Technical_Metrics.xlsx
@@ -888,10 +888,10 @@
         <v>42</v>
       </c>
       <c r="C2">
-        <v>145.06</v>
+        <v>144.25</v>
       </c>
       <c r="D2">
-        <v>0.03</v>
+        <v>-0.5600000000000001</v>
       </c>
       <c r="E2">
         <v>208.37</v>
@@ -900,46 +900,46 @@
         <v>131.36</v>
       </c>
       <c r="G2">
-        <v>-30.38</v>
+        <v>-30.77</v>
       </c>
       <c r="H2">
-        <v>10.43</v>
+        <v>9.81</v>
       </c>
       <c r="I2">
-        <v>-3.6</v>
+        <v>-5.47</v>
       </c>
       <c r="J2">
-        <v>-14.17</v>
+        <v>-13.62</v>
       </c>
       <c r="K2">
-        <v>-7.89</v>
+        <v>-9.4</v>
       </c>
       <c r="L2">
-        <v>7.8</v>
+        <v>5.63</v>
       </c>
       <c r="M2">
-        <v>18.64</v>
+        <v>18.09</v>
       </c>
       <c r="N2">
         <v>79</v>
       </c>
       <c r="O2">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="P2">
-        <v>149.12</v>
+        <v>147.45</v>
       </c>
       <c r="Q2">
-        <v>156.27</v>
+        <v>155.17</v>
       </c>
       <c r="R2">
-        <v>166.27</v>
+        <v>166</v>
       </c>
       <c r="S2">
-        <v>169.44</v>
+        <v>169.3</v>
       </c>
       <c r="T2">
-        <v>-14.39</v>
+        <v>-14.79</v>
       </c>
       <c r="U2" t="s">
         <v>43</v>
@@ -954,34 +954,34 @@
         <v>0</v>
       </c>
       <c r="Y2">
-        <v>29.41</v>
+        <v>28.65</v>
       </c>
       <c r="Z2">
-        <v>-5.21</v>
+        <v>-5.47</v>
       </c>
       <c r="AA2">
-        <v>-4.17</v>
+        <v>-4.43</v>
       </c>
       <c r="AB2">
         <v>-1.04</v>
       </c>
       <c r="AC2">
-        <v>4.13</v>
+        <v>0.19</v>
       </c>
       <c r="AD2">
-        <v>21.61</v>
+        <v>9.17</v>
       </c>
       <c r="AE2">
         <v>4.09</v>
       </c>
       <c r="AF2">
-        <v>-9.25</v>
+        <v>1.05</v>
       </c>
       <c r="AG2">
-        <v>168.2</v>
+        <v>167.31</v>
       </c>
       <c r="AH2">
-        <v>144.34</v>
+        <v>143.04</v>
       </c>
       <c r="AI2">
         <v>157.74</v>
@@ -990,7 +990,7 @@
         <v>45</v>
       </c>
       <c r="AK2">
-        <v>60.04</v>
+        <v>61.3</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1001,10 +1001,10 @@
         <v>42</v>
       </c>
       <c r="C3">
-        <v>357.5</v>
+        <v>349.15</v>
       </c>
       <c r="D3">
-        <v>-0.03</v>
+        <v>-2.34</v>
       </c>
       <c r="E3">
         <v>456.15</v>
@@ -1013,46 +1013,46 @@
         <v>225</v>
       </c>
       <c r="G3">
-        <v>-21.63</v>
+        <v>-23.46</v>
       </c>
       <c r="H3">
-        <v>58.89</v>
+        <v>55.18</v>
       </c>
       <c r="I3">
-        <v>1.66</v>
+        <v>0.42</v>
       </c>
       <c r="J3">
-        <v>-17.93</v>
+        <v>-19.12</v>
       </c>
       <c r="K3">
-        <v>-12.01</v>
+        <v>-13.35</v>
       </c>
       <c r="L3">
-        <v>-0.75</v>
+        <v>-0.04</v>
       </c>
       <c r="M3">
-        <v>3.15</v>
+        <v>0.52</v>
       </c>
       <c r="N3">
         <v>40</v>
       </c>
       <c r="O3">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="P3">
-        <v>360.62</v>
+        <v>360.91</v>
       </c>
       <c r="Q3">
-        <v>396.08</v>
+        <v>391.92</v>
       </c>
       <c r="R3">
-        <v>404.57</v>
+        <v>403.8</v>
       </c>
       <c r="S3">
-        <v>339.65</v>
+        <v>339.91</v>
       </c>
       <c r="T3">
-        <v>5.26</v>
+        <v>2.72</v>
       </c>
       <c r="U3" t="s">
         <v>43</v>
@@ -1067,34 +1067,34 @@
         <v>2</v>
       </c>
       <c r="Y3">
-        <v>37.23</v>
+        <v>34.87</v>
       </c>
       <c r="Z3">
-        <v>-15.7</v>
+        <v>-16.42</v>
       </c>
       <c r="AA3">
-        <v>-11.5</v>
+        <v>-12.48</v>
       </c>
       <c r="AB3">
-        <v>-4.21</v>
+        <v>-3.94</v>
       </c>
       <c r="AC3">
-        <v>23.39</v>
+        <v>24.85</v>
       </c>
       <c r="AD3">
-        <v>23.03</v>
+        <v>24.89</v>
       </c>
       <c r="AE3">
-        <v>17.33</v>
+        <v>17.06</v>
       </c>
       <c r="AF3">
-        <v>-85.31</v>
+        <v>-78.87</v>
       </c>
       <c r="AG3">
-        <v>471.65</v>
+        <v>468.26</v>
       </c>
       <c r="AH3">
-        <v>320.5</v>
+        <v>315.59</v>
       </c>
       <c r="AI3">
         <v>404.18</v>
@@ -1103,7 +1103,7 @@
         <v>45</v>
       </c>
       <c r="AK3">
-        <v>42.82</v>
+        <v>42.86</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1114,10 +1114,10 @@
         <v>42</v>
       </c>
       <c r="C4">
-        <v>355.55</v>
+        <v>351.95</v>
       </c>
       <c r="D4">
-        <v>-0.95</v>
+        <v>-1.01</v>
       </c>
       <c r="E4">
         <v>534</v>
@@ -1126,46 +1126,46 @@
         <v>344.7</v>
       </c>
       <c r="G4">
-        <v>-33.42</v>
+        <v>-34.09</v>
       </c>
       <c r="H4">
-        <v>3.15</v>
+        <v>2.1</v>
       </c>
       <c r="I4">
-        <v>-3.13</v>
+        <v>-3.56</v>
       </c>
       <c r="J4">
-        <v>-8.35</v>
+        <v>-8.529999999999999</v>
       </c>
       <c r="K4">
-        <v>-13.96</v>
+        <v>-15.68</v>
       </c>
       <c r="L4">
-        <v>-28</v>
+        <v>-28.63</v>
       </c>
       <c r="M4">
-        <v>-22.8</v>
+        <v>-23.01</v>
       </c>
       <c r="N4">
         <v>21</v>
       </c>
       <c r="O4">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="P4">
-        <v>360.77</v>
+        <v>358.17</v>
       </c>
       <c r="Q4">
-        <v>373.26</v>
+        <v>371.66</v>
       </c>
       <c r="R4">
-        <v>393.59</v>
+        <v>392.12</v>
       </c>
       <c r="S4">
-        <v>405.23</v>
+        <v>404.76</v>
       </c>
       <c r="T4">
-        <v>-12.26</v>
+        <v>-13.05</v>
       </c>
       <c r="U4" t="s">
         <v>43</v>
@@ -1180,43 +1180,43 @@
         <v>0</v>
       </c>
       <c r="Y4">
-        <v>23.74</v>
+        <v>21.83</v>
       </c>
       <c r="Z4">
-        <v>-9.869999999999999</v>
+        <v>-10.32</v>
       </c>
       <c r="AA4">
-        <v>-9.07</v>
+        <v>-9.32</v>
       </c>
       <c r="AB4">
-        <v>-0.8</v>
+        <v>-0.99</v>
       </c>
       <c r="AC4">
-        <v>16.16</v>
+        <v>4.94</v>
       </c>
       <c r="AD4">
-        <v>19.61</v>
+        <v>13.38</v>
       </c>
       <c r="AE4">
-        <v>9.93</v>
+        <v>10.08</v>
       </c>
       <c r="AF4">
-        <v>13.02</v>
+        <v>-33.15</v>
       </c>
       <c r="AG4">
-        <v>391.94</v>
+        <v>391.92</v>
       </c>
       <c r="AH4">
-        <v>354.57</v>
+        <v>351.41</v>
       </c>
       <c r="AI4">
-        <v>386.47</v>
+        <v>384.24</v>
       </c>
       <c r="AJ4" t="s">
         <v>45</v>
       </c>
       <c r="AK4">
-        <v>52.65</v>
+        <v>56.14</v>
       </c>
     </row>
     <row r="5" spans="1:37">
@@ -1227,10 +1227,10 @@
         <v>42</v>
       </c>
       <c r="C5">
-        <v>861.65</v>
+        <v>853</v>
       </c>
       <c r="D5">
-        <v>-0.27</v>
+        <v>-1</v>
       </c>
       <c r="E5">
         <v>1069.3</v>
@@ -1239,46 +1239,46 @@
         <v>739.5</v>
       </c>
       <c r="G5">
-        <v>-19.42</v>
+        <v>-20.23</v>
       </c>
       <c r="H5">
-        <v>16.52</v>
+        <v>15.35</v>
       </c>
       <c r="I5">
-        <v>-2.84</v>
+        <v>-3.79</v>
       </c>
       <c r="J5">
-        <v>-13.64</v>
+        <v>-15.04</v>
       </c>
       <c r="K5">
-        <v>-15.18</v>
+        <v>-15.79</v>
       </c>
       <c r="L5">
-        <v>16.55</v>
+        <v>13.89</v>
       </c>
       <c r="M5">
-        <v>-5.43</v>
+        <v>-5.75</v>
       </c>
       <c r="N5">
         <v>99</v>
       </c>
       <c r="O5">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="P5">
-        <v>878.65</v>
+        <v>871.9299999999999</v>
       </c>
       <c r="Q5">
-        <v>923.51</v>
+        <v>916.5</v>
       </c>
       <c r="R5">
-        <v>976.12</v>
+        <v>972.95</v>
       </c>
       <c r="S5">
-        <v>924.9299999999999</v>
+        <v>924.91</v>
       </c>
       <c r="T5">
-        <v>-6.84</v>
+        <v>-7.78</v>
       </c>
       <c r="U5" t="s">
         <v>43</v>
@@ -1293,43 +1293,43 @@
         <v>1</v>
       </c>
       <c r="Y5">
-        <v>29.98</v>
+        <v>28.54</v>
       </c>
       <c r="Z5">
-        <v>-31.63</v>
+        <v>-32.78</v>
       </c>
       <c r="AA5">
-        <v>-26.88</v>
+        <v>-28.06</v>
       </c>
       <c r="AB5">
-        <v>-4.74</v>
+        <v>-4.72</v>
       </c>
       <c r="AC5">
-        <v>41.01</v>
+        <v>34.85</v>
       </c>
       <c r="AD5">
-        <v>50.82</v>
+        <v>43.77</v>
       </c>
       <c r="AE5">
-        <v>21.99</v>
+        <v>21.88</v>
       </c>
       <c r="AF5">
-        <v>-51.16</v>
+        <v>120.56</v>
       </c>
       <c r="AG5">
-        <v>1004.91</v>
+        <v>996.75</v>
       </c>
       <c r="AH5">
-        <v>842.11</v>
+        <v>836.24</v>
       </c>
       <c r="AI5">
-        <v>929.63</v>
+        <v>921.99</v>
       </c>
       <c r="AJ5" t="s">
         <v>45</v>
       </c>
       <c r="AK5">
-        <v>58.05</v>
+        <v>60.39</v>
       </c>
     </row>
     <row r="6" spans="1:37">
@@ -1358,31 +1358,31 @@
         <v>40.22</v>
       </c>
       <c r="I6">
-        <v>1.57</v>
+        <v>-0.39</v>
       </c>
       <c r="J6">
-        <v>-11.64</v>
+        <v>-11.95</v>
       </c>
       <c r="K6">
-        <v>7.5</v>
+        <v>7.95</v>
       </c>
       <c r="L6">
-        <v>-21.34</v>
+        <v>-20.12</v>
       </c>
       <c r="M6">
-        <v>1.21</v>
+        <v>1.46</v>
       </c>
       <c r="N6">
         <v>60</v>
       </c>
       <c r="O6">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="P6">
         <v>2.58</v>
       </c>
       <c r="Q6">
-        <v>2.7</v>
+        <v>2.68</v>
       </c>
       <c r="R6">
         <v>2.64</v>
@@ -1391,7 +1391,7 @@
         <v>2.65</v>
       </c>
       <c r="T6">
-        <v>-2.55</v>
+        <v>-2.47</v>
       </c>
       <c r="U6" t="s">
         <v>44</v>
@@ -1418,31 +1418,31 @@
         <v>-0.02</v>
       </c>
       <c r="AC6">
-        <v>31.05</v>
+        <v>30.97</v>
       </c>
       <c r="AD6">
-        <v>26.68</v>
+        <v>29.35</v>
       </c>
       <c r="AE6">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="AF6">
-        <v>-38.12</v>
+        <v>-35.22</v>
       </c>
       <c r="AG6">
-        <v>2.93</v>
+        <v>2.9</v>
       </c>
       <c r="AH6">
-        <v>2.47</v>
+        <v>2.46</v>
       </c>
       <c r="AI6">
-        <v>2.97</v>
+        <v>2.95</v>
       </c>
       <c r="AJ6" t="s">
         <v>45</v>
       </c>
       <c r="AK6">
-        <v>29.1</v>
+        <v>29.21</v>
       </c>
     </row>
   </sheetData>
@@ -1640,13 +1640,13 @@
         <v>9</v>
       </c>
       <c r="C7" s="5">
-        <v>-14.69</v>
+        <v>-14.17</v>
       </c>
       <c r="D7" s="5">
-        <v>-14.17</v>
+        <v>-13.62</v>
       </c>
       <c r="E7" s="6">
-        <v>0.52</v>
+        <v>0.55</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -1657,13 +1657,13 @@
         <v>9</v>
       </c>
       <c r="C8" s="5">
-        <v>-18.16</v>
+        <v>-17.93</v>
       </c>
       <c r="D8" s="5">
-        <v>-17.93</v>
-      </c>
-      <c r="E8" s="6">
-        <v>0.23</v>
+        <v>-19.12</v>
+      </c>
+      <c r="E8" s="7">
+        <v>-1.19</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -1674,13 +1674,13 @@
         <v>9</v>
       </c>
       <c r="C9" s="5">
-        <v>-9.25</v>
+        <v>-8.35</v>
       </c>
       <c r="D9" s="5">
-        <v>-8.35</v>
-      </c>
-      <c r="E9" s="6">
-        <v>0.9</v>
+        <v>-8.529999999999999</v>
+      </c>
+      <c r="E9" s="7">
+        <v>-0.18</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -1691,13 +1691,13 @@
         <v>9</v>
       </c>
       <c r="C10" s="5">
-        <v>-13.43</v>
+        <v>-13.64</v>
       </c>
       <c r="D10" s="5">
-        <v>-13.64</v>
+        <v>-15.04</v>
       </c>
       <c r="E10" s="7">
-        <v>-0.21</v>
+        <v>-1.4</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -1708,13 +1708,13 @@
         <v>9</v>
       </c>
       <c r="C11" s="5">
-        <v>-13.42</v>
+        <v>-11.64</v>
       </c>
       <c r="D11" s="5">
-        <v>-11.64</v>
-      </c>
-      <c r="E11" s="6">
-        <v>1.78</v>
+        <v>-11.95</v>
+      </c>
+      <c r="E11" s="7">
+        <v>-0.31</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -1725,13 +1725,13 @@
         <v>8</v>
       </c>
       <c r="C12" s="5">
-        <v>-5.95</v>
+        <v>-3.6</v>
       </c>
       <c r="D12" s="5">
-        <v>-3.6</v>
-      </c>
-      <c r="E12" s="6">
-        <v>2.35</v>
+        <v>-5.47</v>
+      </c>
+      <c r="E12" s="7">
+        <v>-1.87</v>
       </c>
     </row>
     <row r="13" spans="1:6">
@@ -1742,13 +1742,13 @@
         <v>8</v>
       </c>
       <c r="C13" s="5">
-        <v>-1.34</v>
+        <v>1.66</v>
       </c>
       <c r="D13" s="5">
-        <v>1.66</v>
-      </c>
-      <c r="E13" s="6">
-        <v>3</v>
+        <v>0.42</v>
+      </c>
+      <c r="E13" s="7">
+        <v>-1.24</v>
       </c>
     </row>
     <row r="14" spans="1:6">
@@ -1759,13 +1759,13 @@
         <v>8</v>
       </c>
       <c r="C14" s="5">
-        <v>-3</v>
+        <v>-3.13</v>
       </c>
       <c r="D14" s="5">
-        <v>-3.13</v>
+        <v>-3.56</v>
       </c>
       <c r="E14" s="7">
-        <v>-0.13</v>
+        <v>-0.43</v>
       </c>
     </row>
     <row r="15" spans="1:6">
@@ -1776,13 +1776,13 @@
         <v>8</v>
       </c>
       <c r="C15" s="5">
-        <v>-4.15</v>
+        <v>-2.84</v>
       </c>
       <c r="D15" s="5">
-        <v>-2.84</v>
-      </c>
-      <c r="E15" s="6">
-        <v>1.31</v>
+        <v>-3.79</v>
+      </c>
+      <c r="E15" s="7">
+        <v>-0.95</v>
       </c>
     </row>
     <row r="16" spans="1:6">
@@ -1793,13 +1793,13 @@
         <v>8</v>
       </c>
       <c r="C16" s="5">
-        <v>-1.15</v>
+        <v>1.57</v>
       </c>
       <c r="D16" s="5">
-        <v>1.57</v>
-      </c>
-      <c r="E16" s="6">
-        <v>2.72</v>
+        <v>-0.39</v>
+      </c>
+      <c r="E16" s="7">
+        <v>-1.96</v>
       </c>
     </row>
     <row r="17" spans="1:5">
@@ -1810,13 +1810,13 @@
         <v>11</v>
       </c>
       <c r="C17" s="5">
-        <v>6.23</v>
+        <v>7.8</v>
       </c>
       <c r="D17" s="5">
-        <v>7.8</v>
-      </c>
-      <c r="E17" s="6">
-        <v>1.57</v>
+        <v>5.63</v>
+      </c>
+      <c r="E17" s="7">
+        <v>-2.17</v>
       </c>
     </row>
     <row r="18" spans="1:5">
@@ -1827,13 +1827,13 @@
         <v>11</v>
       </c>
       <c r="C18" s="5">
-        <v>-0.98</v>
+        <v>-0.75</v>
       </c>
       <c r="D18" s="5">
-        <v>-0.75</v>
+        <v>-0.04</v>
       </c>
       <c r="E18" s="6">
-        <v>0.23</v>
+        <v>0.71</v>
       </c>
     </row>
     <row r="19" spans="1:5">
@@ -1844,13 +1844,13 @@
         <v>11</v>
       </c>
       <c r="C19" s="5">
-        <v>-28.81</v>
+        <v>-28</v>
       </c>
       <c r="D19" s="5">
-        <v>-28</v>
-      </c>
-      <c r="E19" s="6">
-        <v>0.8100000000000001</v>
+        <v>-28.63</v>
+      </c>
+      <c r="E19" s="7">
+        <v>-0.63</v>
       </c>
     </row>
     <row r="20" spans="1:5">
@@ -1861,13 +1861,13 @@
         <v>11</v>
       </c>
       <c r="C20" s="5">
-        <v>15.6</v>
+        <v>16.55</v>
       </c>
       <c r="D20" s="5">
-        <v>16.55</v>
-      </c>
-      <c r="E20" s="6">
-        <v>0.95</v>
+        <v>13.89</v>
+      </c>
+      <c r="E20" s="7">
+        <v>-2.66</v>
       </c>
     </row>
     <row r="21" spans="1:5">
@@ -1878,13 +1878,13 @@
         <v>11</v>
       </c>
       <c r="C21" s="5">
-        <v>-23.67</v>
+        <v>-21.34</v>
       </c>
       <c r="D21" s="5">
-        <v>-21.34</v>
+        <v>-20.12</v>
       </c>
       <c r="E21" s="6">
-        <v>2.33</v>
+        <v>1.22</v>
       </c>
     </row>
     <row r="22" spans="1:5">
@@ -1895,13 +1895,13 @@
         <v>10</v>
       </c>
       <c r="C22" s="5">
-        <v>-6.55</v>
+        <v>-7.89</v>
       </c>
       <c r="D22" s="5">
-        <v>-7.89</v>
+        <v>-9.4</v>
       </c>
       <c r="E22" s="7">
-        <v>-1.34</v>
+        <v>-1.51</v>
       </c>
     </row>
     <row r="23" spans="1:5">
@@ -1912,13 +1912,13 @@
         <v>10</v>
       </c>
       <c r="C23" s="5">
-        <v>-12.78</v>
+        <v>-12.01</v>
       </c>
       <c r="D23" s="5">
-        <v>-12.01</v>
-      </c>
-      <c r="E23" s="6">
-        <v>0.77</v>
+        <v>-13.35</v>
+      </c>
+      <c r="E23" s="7">
+        <v>-1.34</v>
       </c>
     </row>
     <row r="24" spans="1:5">
@@ -1929,13 +1929,13 @@
         <v>10</v>
       </c>
       <c r="C24" s="5">
-        <v>-12.43</v>
+        <v>-13.96</v>
       </c>
       <c r="D24" s="5">
-        <v>-13.96</v>
+        <v>-15.68</v>
       </c>
       <c r="E24" s="7">
-        <v>-1.53</v>
+        <v>-1.72</v>
       </c>
     </row>
     <row r="25" spans="1:5">
@@ -1946,13 +1946,13 @@
         <v>10</v>
       </c>
       <c r="C25" s="5">
-        <v>-14.89</v>
+        <v>-15.18</v>
       </c>
       <c r="D25" s="5">
-        <v>-15.18</v>
+        <v>-15.79</v>
       </c>
       <c r="E25" s="7">
-        <v>-0.29</v>
+        <v>-0.61</v>
       </c>
     </row>
     <row r="26" spans="1:5">
@@ -1963,13 +1963,13 @@
         <v>10</v>
       </c>
       <c r="C26" s="5">
+        <v>7.5</v>
+      </c>
+      <c r="D26" s="5">
         <v>7.95</v>
       </c>
-      <c r="D26" s="5">
-        <v>7.5</v>
-      </c>
-      <c r="E26" s="7">
-        <v>-0.45</v>
+      <c r="E26" s="6">
+        <v>0.45</v>
       </c>
     </row>
     <row r="27" spans="1:5">
@@ -1980,13 +1980,13 @@
         <v>6</v>
       </c>
       <c r="C27" s="5">
-        <v>-30.4</v>
+        <v>-30.38</v>
       </c>
       <c r="D27" s="5">
-        <v>-30.38</v>
-      </c>
-      <c r="E27" s="6">
-        <v>0.02</v>
+        <v>-30.77</v>
+      </c>
+      <c r="E27" s="7">
+        <v>-0.39</v>
       </c>
     </row>
     <row r="28" spans="1:5">
@@ -1997,13 +1997,13 @@
         <v>6</v>
       </c>
       <c r="C28" s="5">
-        <v>-21.6</v>
+        <v>-21.63</v>
       </c>
       <c r="D28" s="5">
-        <v>-21.63</v>
+        <v>-23.46</v>
       </c>
       <c r="E28" s="7">
-        <v>-0.03</v>
+        <v>-1.83</v>
       </c>
     </row>
     <row r="29" spans="1:5">
@@ -2014,13 +2014,13 @@
         <v>6</v>
       </c>
       <c r="C29" s="5">
-        <v>-32.78</v>
+        <v>-33.42</v>
       </c>
       <c r="D29" s="5">
-        <v>-33.42</v>
+        <v>-34.09</v>
       </c>
       <c r="E29" s="7">
-        <v>-0.64</v>
+        <v>-0.67</v>
       </c>
     </row>
     <row r="30" spans="1:5">
@@ -2031,13 +2031,13 @@
         <v>6</v>
       </c>
       <c r="C30" s="5">
-        <v>-19.2</v>
+        <v>-19.42</v>
       </c>
       <c r="D30" s="5">
-        <v>-19.42</v>
+        <v>-20.23</v>
       </c>
       <c r="E30" s="7">
-        <v>-0.22</v>
+        <v>-0.8100000000000001</v>
       </c>
     </row>
     <row r="31" spans="1:5">
@@ -2048,13 +2048,13 @@
         <v>2</v>
       </c>
       <c r="C31" s="5">
-        <v>145.02</v>
+        <v>145.06</v>
       </c>
       <c r="D31" s="5">
-        <v>145.06</v>
-      </c>
-      <c r="E31" s="6">
-        <v>0.04</v>
+        <v>144.25</v>
+      </c>
+      <c r="E31" s="7">
+        <v>-0.8100000000000001</v>
       </c>
     </row>
     <row r="32" spans="1:5">
@@ -2065,13 +2065,13 @@
         <v>2</v>
       </c>
       <c r="C32" s="5">
-        <v>357.6</v>
+        <v>357.5</v>
       </c>
       <c r="D32" s="5">
-        <v>357.5</v>
+        <v>349.15</v>
       </c>
       <c r="E32" s="7">
-        <v>-0.1</v>
+        <v>-8.35</v>
       </c>
     </row>
     <row r="33" spans="1:5">
@@ -2082,13 +2082,13 @@
         <v>2</v>
       </c>
       <c r="C33" s="5">
-        <v>358.95</v>
+        <v>355.55</v>
       </c>
       <c r="D33" s="5">
-        <v>355.55</v>
+        <v>351.95</v>
       </c>
       <c r="E33" s="7">
-        <v>-3.4</v>
+        <v>-3.6</v>
       </c>
     </row>
     <row r="34" spans="1:5">
@@ -2099,13 +2099,13 @@
         <v>2</v>
       </c>
       <c r="C34" s="5">
-        <v>864</v>
+        <v>861.65</v>
       </c>
       <c r="D34" s="5">
-        <v>861.65</v>
+        <v>853</v>
       </c>
       <c r="E34" s="7">
-        <v>-2.35</v>
+        <v>-8.65</v>
       </c>
     </row>
     <row r="35" spans="1:5">
@@ -2116,13 +2116,13 @@
         <v>24</v>
       </c>
       <c r="C35" s="5">
-        <v>29.32</v>
+        <v>29.41</v>
       </c>
       <c r="D35" s="5">
-        <v>29.41</v>
-      </c>
-      <c r="E35" s="6">
-        <v>0.09</v>
+        <v>28.65</v>
+      </c>
+      <c r="E35" s="7">
+        <v>-0.76</v>
       </c>
     </row>
     <row r="36" spans="1:5">
@@ -2133,13 +2133,13 @@
         <v>24</v>
       </c>
       <c r="C36" s="5">
-        <v>37.26</v>
+        <v>37.23</v>
       </c>
       <c r="D36" s="5">
-        <v>37.23</v>
+        <v>34.87</v>
       </c>
       <c r="E36" s="7">
-        <v>-0.03</v>
+        <v>-2.36</v>
       </c>
     </row>
     <row r="37" spans="1:5">
@@ -2150,13 +2150,13 @@
         <v>24</v>
       </c>
       <c r="C37" s="5">
-        <v>25.71</v>
+        <v>23.74</v>
       </c>
       <c r="D37" s="5">
-        <v>23.74</v>
+        <v>21.83</v>
       </c>
       <c r="E37" s="7">
-        <v>-1.97</v>
+        <v>-1.91</v>
       </c>
     </row>
     <row r="38" spans="1:5">
@@ -2167,13 +2167,13 @@
         <v>24</v>
       </c>
       <c r="C38" s="5">
-        <v>30.37</v>
+        <v>29.98</v>
       </c>
       <c r="D38" s="5">
-        <v>29.98</v>
+        <v>28.54</v>
       </c>
       <c r="E38" s="7">
-        <v>-0.39</v>
+        <v>-1.44</v>
       </c>
     </row>
     <row r="39" spans="1:5">
@@ -2184,13 +2184,13 @@
         <v>31</v>
       </c>
       <c r="C39" s="5">
-        <v>33.42</v>
+        <v>-9.25</v>
       </c>
       <c r="D39" s="5">
-        <v>-9.25</v>
-      </c>
-      <c r="E39" s="7">
-        <v>-42.67</v>
+        <v>1.05</v>
+      </c>
+      <c r="E39" s="6">
+        <v>10.3</v>
       </c>
     </row>
     <row r="40" spans="1:5">
@@ -2201,13 +2201,13 @@
         <v>31</v>
       </c>
       <c r="C40" s="5">
-        <v>-81.59999999999999</v>
+        <v>-85.31</v>
       </c>
       <c r="D40" s="5">
-        <v>-85.31</v>
-      </c>
-      <c r="E40" s="7">
-        <v>-3.71</v>
+        <v>-78.87</v>
+      </c>
+      <c r="E40" s="6">
+        <v>6.44</v>
       </c>
     </row>
     <row r="41" spans="1:5">
@@ -2218,13 +2218,13 @@
         <v>31</v>
       </c>
       <c r="C41" s="5">
-        <v>-36.63</v>
+        <v>13.02</v>
       </c>
       <c r="D41" s="5">
-        <v>13.02</v>
-      </c>
-      <c r="E41" s="6">
-        <v>49.65</v>
+        <v>-33.15</v>
+      </c>
+      <c r="E41" s="7">
+        <v>-46.17</v>
       </c>
     </row>
     <row r="42" spans="1:5">
@@ -2235,13 +2235,13 @@
         <v>31</v>
       </c>
       <c r="C42" s="5">
-        <v>-26.94</v>
+        <v>-51.16</v>
       </c>
       <c r="D42" s="5">
-        <v>-51.16</v>
-      </c>
-      <c r="E42" s="7">
-        <v>-24.22</v>
+        <v>120.56</v>
+      </c>
+      <c r="E42" s="6">
+        <v>171.72</v>
       </c>
     </row>
     <row r="43" spans="1:5">
@@ -2252,13 +2252,13 @@
         <v>31</v>
       </c>
       <c r="C43" s="5">
-        <v>-11.69</v>
+        <v>-38.12</v>
       </c>
       <c r="D43" s="5">
-        <v>-38.12</v>
-      </c>
-      <c r="E43" s="7">
-        <v>-26.43</v>
+        <v>-35.22</v>
+      </c>
+      <c r="E43" s="6">
+        <v>2.9</v>
       </c>
     </row>
   </sheetData>
@@ -2323,16 +2323,16 @@
         <v>5</v>
       </c>
       <c r="D2" s="10">
-        <v>32.6</v>
+        <v>31.3</v>
       </c>
       <c r="E2" s="10">
         <v>20</v>
       </c>
       <c r="F2" s="10">
-        <v>-13.1</v>
+        <v>-13.7</v>
       </c>
       <c r="G2" s="10">
-        <v>-8.300000000000001</v>
+        <v>-9.300000000000001</v>
       </c>
       <c r="H2" s="10">
         <v>59.8</v>
@@ -2443,10 +2443,10 @@
         <v>37</v>
       </c>
       <c r="B1" s="12" t="s">
+        <v>41</v>
+      </c>
+      <c r="C1" s="12" t="s">
         <v>38</v>
-      </c>
-      <c r="C1" s="12" t="s">
-        <v>41</v>
       </c>
       <c r="D1" s="12" t="s">
         <v>40</v>
@@ -2457,19 +2457,19 @@
     </row>
     <row r="2" spans="1:5">
       <c r="A2" s="13">
-        <v>0.1864</v>
+        <v>0.1809</v>
       </c>
       <c r="B2" s="13">
-        <v>0.0315</v>
+        <v>0.0146</v>
       </c>
       <c r="C2" s="13">
-        <v>0.0121</v>
+        <v>0.0052</v>
       </c>
       <c r="D2" s="13">
-        <v>-0.05429999999999999</v>
+        <v>-0.0575</v>
       </c>
       <c r="E2" s="13">
-        <v>-0.228</v>
+        <v>-0.2301</v>
       </c>
     </row>
   </sheetData>

--- a/HINDUJA_GROUP_Technical_Metrics.xlsx
+++ b/HINDUJA_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="201" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="236" uniqueCount="79">
   <si>
     <t>Symbol</t>
   </si>
@@ -163,7 +163,61 @@
     <t>▶  SIGNAL EVENTS (vs Previous Run)</t>
   </si>
   <si>
-    <t>No signal events detected since last run.</t>
+    <t>Signal</t>
+  </si>
+  <si>
+    <t>Change</t>
+  </si>
+  <si>
+    <t>Direction</t>
+  </si>
+  <si>
+    <t>Prev Value</t>
+  </si>
+  <si>
+    <t>Curr Value</t>
+  </si>
+  <si>
+    <t>50 DMA &gt; 200 DMA</t>
+  </si>
+  <si>
+    <t>No → Yes</t>
+  </si>
+  <si>
+    <t>🟢 GOLDEN CROSS</t>
+  </si>
+  <si>
+    <t>RSI Oversold Recovery</t>
+  </si>
+  <si>
+    <t>28.6 → 35.5</t>
+  </si>
+  <si>
+    <t>🟢 BULLISH</t>
+  </si>
+  <si>
+    <t>28.6</t>
+  </si>
+  <si>
+    <t>35.5</t>
+  </si>
+  <si>
+    <t>21.8 → 32.6</t>
+  </si>
+  <si>
+    <t>21.8</t>
+  </si>
+  <si>
+    <t>32.6</t>
+  </si>
+  <si>
+    <t>28.5 → 37.6</t>
+  </si>
+  <si>
+    <t>28.5</t>
+  </si>
+  <si>
+    <t>37.6</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -365,14 +419,15 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -888,10 +943,10 @@
         <v>42</v>
       </c>
       <c r="C2">
-        <v>144.25</v>
+        <v>147.37</v>
       </c>
       <c r="D2">
-        <v>-0.5600000000000001</v>
+        <v>2.16</v>
       </c>
       <c r="E2">
         <v>208.37</v>
@@ -900,46 +955,46 @@
         <v>131.36</v>
       </c>
       <c r="G2">
-        <v>-30.77</v>
+        <v>-29.27</v>
       </c>
       <c r="H2">
-        <v>9.81</v>
+        <v>12.19</v>
       </c>
       <c r="I2">
-        <v>-5.47</v>
+        <v>-4.12</v>
       </c>
       <c r="J2">
-        <v>-13.62</v>
+        <v>-11.29</v>
       </c>
       <c r="K2">
-        <v>-9.4</v>
+        <v>-5.04</v>
       </c>
       <c r="L2">
-        <v>5.63</v>
+        <v>8.27</v>
       </c>
       <c r="M2">
-        <v>18.09</v>
+        <v>17.38</v>
       </c>
       <c r="N2">
         <v>79</v>
       </c>
       <c r="O2">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="P2">
-        <v>147.45</v>
+        <v>146.18</v>
       </c>
       <c r="Q2">
-        <v>155.17</v>
+        <v>154.35</v>
       </c>
       <c r="R2">
-        <v>166</v>
+        <v>165.62</v>
       </c>
       <c r="S2">
-        <v>169.3</v>
+        <v>169.16</v>
       </c>
       <c r="T2">
-        <v>-14.79</v>
+        <v>-12.88</v>
       </c>
       <c r="U2" t="s">
         <v>43</v>
@@ -954,43 +1009,43 @@
         <v>0</v>
       </c>
       <c r="Y2">
-        <v>28.65</v>
+        <v>35.49</v>
       </c>
       <c r="Z2">
-        <v>-5.47</v>
+        <v>-5.36</v>
       </c>
       <c r="AA2">
-        <v>-4.43</v>
+        <v>-4.62</v>
       </c>
       <c r="AB2">
-        <v>-1.04</v>
+        <v>-0.75</v>
       </c>
       <c r="AC2">
-        <v>0.19</v>
+        <v>14.46</v>
       </c>
       <c r="AD2">
-        <v>9.17</v>
+        <v>6.26</v>
       </c>
       <c r="AE2">
-        <v>4.09</v>
+        <v>4.07</v>
       </c>
       <c r="AF2">
-        <v>1.05</v>
+        <v>-15.75</v>
       </c>
       <c r="AG2">
-        <v>167.31</v>
+        <v>166.26</v>
       </c>
       <c r="AH2">
-        <v>143.04</v>
+        <v>142.45</v>
       </c>
       <c r="AI2">
-        <v>157.74</v>
+        <v>157.65</v>
       </c>
       <c r="AJ2" t="s">
         <v>45</v>
       </c>
       <c r="AK2">
-        <v>61.3</v>
+        <v>62.58</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1001,10 +1056,10 @@
         <v>42</v>
       </c>
       <c r="C3">
-        <v>349.15</v>
+        <v>354.5</v>
       </c>
       <c r="D3">
-        <v>-2.34</v>
+        <v>1.53</v>
       </c>
       <c r="E3">
         <v>456.15</v>
@@ -1013,46 +1068,46 @@
         <v>225</v>
       </c>
       <c r="G3">
-        <v>-23.46</v>
+        <v>-22.28</v>
       </c>
       <c r="H3">
-        <v>55.18</v>
+        <v>57.56</v>
       </c>
       <c r="I3">
-        <v>0.42</v>
+        <v>-4.82</v>
       </c>
       <c r="J3">
-        <v>-19.12</v>
+        <v>-17.98</v>
       </c>
       <c r="K3">
-        <v>-13.35</v>
+        <v>-12.12</v>
       </c>
       <c r="L3">
-        <v>-0.04</v>
+        <v>1.78</v>
       </c>
       <c r="M3">
-        <v>0.52</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="N3">
         <v>40</v>
       </c>
       <c r="O3">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="P3">
-        <v>360.91</v>
+        <v>357.32</v>
       </c>
       <c r="Q3">
-        <v>391.92</v>
+        <v>387.57</v>
       </c>
       <c r="R3">
-        <v>403.8</v>
+        <v>402.84</v>
       </c>
       <c r="S3">
-        <v>339.91</v>
+        <v>340.22</v>
       </c>
       <c r="T3">
-        <v>2.72</v>
+        <v>4.2</v>
       </c>
       <c r="U3" t="s">
         <v>43</v>
@@ -1067,43 +1122,43 @@
         <v>2</v>
       </c>
       <c r="Y3">
-        <v>34.87</v>
+        <v>37.6</v>
       </c>
       <c r="Z3">
-        <v>-16.42</v>
+        <v>-16.38</v>
       </c>
       <c r="AA3">
-        <v>-12.48</v>
+        <v>-13.26</v>
       </c>
       <c r="AB3">
-        <v>-3.94</v>
+        <v>-3.11</v>
       </c>
       <c r="AC3">
-        <v>24.85</v>
+        <v>39.93</v>
       </c>
       <c r="AD3">
-        <v>24.89</v>
+        <v>29.39</v>
       </c>
       <c r="AE3">
-        <v>17.06</v>
+        <v>16.92</v>
       </c>
       <c r="AF3">
-        <v>-78.87</v>
+        <v>-79.14</v>
       </c>
       <c r="AG3">
-        <v>468.26</v>
+        <v>461.89</v>
       </c>
       <c r="AH3">
-        <v>315.59</v>
+        <v>313.25</v>
       </c>
       <c r="AI3">
-        <v>404.18</v>
+        <v>401.23</v>
       </c>
       <c r="AJ3" t="s">
         <v>45</v>
       </c>
       <c r="AK3">
-        <v>42.86</v>
+        <v>43.58</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1114,10 +1169,10 @@
         <v>42</v>
       </c>
       <c r="C4">
-        <v>351.95</v>
+        <v>358.6</v>
       </c>
       <c r="D4">
-        <v>-1.01</v>
+        <v>1.89</v>
       </c>
       <c r="E4">
         <v>534</v>
@@ -1126,46 +1181,46 @@
         <v>344.7</v>
       </c>
       <c r="G4">
-        <v>-34.09</v>
+        <v>-32.85</v>
       </c>
       <c r="H4">
-        <v>2.1</v>
+        <v>4.03</v>
       </c>
       <c r="I4">
-        <v>-3.56</v>
+        <v>-0.77</v>
       </c>
       <c r="J4">
-        <v>-8.529999999999999</v>
+        <v>-6.58</v>
       </c>
       <c r="K4">
-        <v>-15.68</v>
+        <v>-20.94</v>
       </c>
       <c r="L4">
-        <v>-28.63</v>
+        <v>-26.96</v>
       </c>
       <c r="M4">
-        <v>-23.01</v>
+        <v>-22.61</v>
       </c>
       <c r="N4">
         <v>21</v>
       </c>
       <c r="O4">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="P4">
-        <v>358.17</v>
+        <v>357.61</v>
       </c>
       <c r="Q4">
-        <v>371.66</v>
+        <v>370.52</v>
       </c>
       <c r="R4">
-        <v>392.12</v>
+        <v>390.83</v>
       </c>
       <c r="S4">
-        <v>404.76</v>
+        <v>404.24</v>
       </c>
       <c r="T4">
-        <v>-13.05</v>
+        <v>-11.29</v>
       </c>
       <c r="U4" t="s">
         <v>43</v>
@@ -1180,34 +1235,34 @@
         <v>0</v>
       </c>
       <c r="Y4">
-        <v>21.83</v>
+        <v>32.61</v>
       </c>
       <c r="Z4">
-        <v>-10.32</v>
+        <v>-10.02</v>
       </c>
       <c r="AA4">
-        <v>-9.32</v>
+        <v>-9.460000000000001</v>
       </c>
       <c r="AB4">
-        <v>-0.99</v>
+        <v>-0.5600000000000001</v>
       </c>
       <c r="AC4">
-        <v>4.94</v>
+        <v>33.33</v>
       </c>
       <c r="AD4">
-        <v>13.38</v>
+        <v>18.15</v>
       </c>
       <c r="AE4">
-        <v>10.08</v>
+        <v>10</v>
       </c>
       <c r="AF4">
-        <v>-33.15</v>
+        <v>-56.34</v>
       </c>
       <c r="AG4">
-        <v>391.92</v>
+        <v>391.03</v>
       </c>
       <c r="AH4">
-        <v>351.41</v>
+        <v>350.01</v>
       </c>
       <c r="AI4">
         <v>384.24</v>
@@ -1216,7 +1271,7 @@
         <v>45</v>
       </c>
       <c r="AK4">
-        <v>56.14</v>
+        <v>57.99</v>
       </c>
     </row>
     <row r="5" spans="1:37">
@@ -1227,10 +1282,10 @@
         <v>42</v>
       </c>
       <c r="C5">
-        <v>853</v>
+        <v>877.35</v>
       </c>
       <c r="D5">
-        <v>-1</v>
+        <v>2.85</v>
       </c>
       <c r="E5">
         <v>1069.3</v>
@@ -1239,46 +1294,46 @@
         <v>739.5</v>
       </c>
       <c r="G5">
-        <v>-20.23</v>
+        <v>-17.95</v>
       </c>
       <c r="H5">
-        <v>15.35</v>
+        <v>18.64</v>
       </c>
       <c r="I5">
-        <v>-3.79</v>
+        <v>-3.17</v>
       </c>
       <c r="J5">
-        <v>-15.04</v>
+        <v>-11.67</v>
       </c>
       <c r="K5">
-        <v>-15.79</v>
+        <v>-12.03</v>
       </c>
       <c r="L5">
-        <v>13.89</v>
+        <v>18.41</v>
       </c>
       <c r="M5">
-        <v>-5.75</v>
+        <v>-5.26</v>
       </c>
       <c r="N5">
         <v>99</v>
       </c>
       <c r="O5">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="P5">
-        <v>871.9299999999999</v>
+        <v>866.1799999999999</v>
       </c>
       <c r="Q5">
-        <v>916.5</v>
+        <v>911.45</v>
       </c>
       <c r="R5">
-        <v>972.95</v>
+        <v>970.25</v>
       </c>
       <c r="S5">
-        <v>924.91</v>
+        <v>925.05</v>
       </c>
       <c r="T5">
-        <v>-7.78</v>
+        <v>-5.16</v>
       </c>
       <c r="U5" t="s">
         <v>43</v>
@@ -1293,34 +1348,34 @@
         <v>1</v>
       </c>
       <c r="Y5">
-        <v>28.54</v>
+        <v>37.65</v>
       </c>
       <c r="Z5">
-        <v>-32.78</v>
+        <v>-31.36</v>
       </c>
       <c r="AA5">
-        <v>-28.06</v>
+        <v>-28.72</v>
       </c>
       <c r="AB5">
-        <v>-4.72</v>
+        <v>-2.64</v>
       </c>
       <c r="AC5">
-        <v>34.85</v>
+        <v>50.21</v>
       </c>
       <c r="AD5">
-        <v>43.77</v>
+        <v>42.03</v>
       </c>
       <c r="AE5">
-        <v>21.88</v>
+        <v>22.77</v>
       </c>
       <c r="AF5">
-        <v>120.56</v>
+        <v>109</v>
       </c>
       <c r="AG5">
-        <v>996.75</v>
+        <v>987.97</v>
       </c>
       <c r="AH5">
-        <v>836.24</v>
+        <v>834.9400000000001</v>
       </c>
       <c r="AI5">
         <v>921.99</v>
@@ -1329,7 +1384,7 @@
         <v>45</v>
       </c>
       <c r="AK5">
-        <v>60.39</v>
+        <v>57.88</v>
       </c>
     </row>
     <row r="6" spans="1:37">
@@ -1358,52 +1413,52 @@
         <v>40.22</v>
       </c>
       <c r="I6">
-        <v>-0.39</v>
+        <v>0.39</v>
       </c>
       <c r="J6">
-        <v>-11.95</v>
+        <v>-11.03</v>
       </c>
       <c r="K6">
-        <v>7.95</v>
+        <v>9.32</v>
       </c>
       <c r="L6">
-        <v>-20.12</v>
+        <v>-19.38</v>
       </c>
       <c r="M6">
-        <v>1.46</v>
+        <v>0.39</v>
       </c>
       <c r="N6">
         <v>60</v>
       </c>
       <c r="O6">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="P6">
         <v>2.58</v>
       </c>
       <c r="Q6">
-        <v>2.68</v>
+        <v>2.67</v>
       </c>
       <c r="R6">
+        <v>2.65</v>
+      </c>
+      <c r="S6">
         <v>2.64</v>
       </c>
-      <c r="S6">
-        <v>2.65</v>
-      </c>
       <c r="T6">
-        <v>-2.47</v>
+        <v>-2.39</v>
       </c>
       <c r="U6" t="s">
         <v>44</v>
       </c>
       <c r="V6" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="W6" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="X6">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y6">
         <v>42.44</v>
@@ -1412,37 +1467,37 @@
         <v>-0.04</v>
       </c>
       <c r="AA6">
-        <v>-0.02</v>
+        <v>-0.03</v>
       </c>
       <c r="AB6">
-        <v>-0.02</v>
+        <v>-0.01</v>
       </c>
       <c r="AC6">
-        <v>30.97</v>
+        <v>32.52</v>
       </c>
       <c r="AD6">
-        <v>29.35</v>
+        <v>31.51</v>
       </c>
       <c r="AE6">
         <v>0.12</v>
       </c>
       <c r="AF6">
-        <v>-35.22</v>
+        <v>-27.62</v>
       </c>
       <c r="AG6">
-        <v>2.9</v>
+        <v>2.87</v>
       </c>
       <c r="AH6">
         <v>2.46</v>
       </c>
       <c r="AI6">
-        <v>2.95</v>
+        <v>2.93</v>
       </c>
       <c r="AJ6" t="s">
         <v>45</v>
       </c>
       <c r="AK6">
-        <v>29.21</v>
+        <v>29.73</v>
       </c>
     </row>
   </sheetData>
@@ -1583,7 +1638,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F43"/>
+  <dimension ref="A1:F47"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.7109375" customWidth="1"/>
@@ -1603,668 +1658,783 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="3" t="s">
         <v>47</v>
       </c>
+      <c r="C2" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
+      <c r="A3" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6">
+      <c r="A4" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="F4" s="4" t="s">
+        <v>59</v>
+      </c>
     </row>
     <row r="5" spans="1:6">
-      <c r="A5" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="B5" s="2"/>
-      <c r="C5" s="2"/>
-      <c r="D5" s="2"/>
-      <c r="E5" s="2"/>
+      <c r="A5" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="E5" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="F5" s="4" t="s">
+        <v>62</v>
+      </c>
     </row>
     <row r="6" spans="1:6">
       <c r="A6" s="4" t="s">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>50</v>
+        <v>63</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>52</v>
+        <v>64</v>
+      </c>
+      <c r="F6" s="4" t="s">
+        <v>65</v>
       </c>
     </row>
     <row r="7" spans="1:6">
-      <c r="A7" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C7" s="5">
-        <v>-14.17</v>
-      </c>
-      <c r="D7" s="5">
-        <v>-13.62</v>
-      </c>
-      <c r="E7" s="6">
-        <v>0.55</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6">
-      <c r="A8" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="B8" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C8" s="5">
-        <v>-17.93</v>
-      </c>
-      <c r="D8" s="5">
-        <v>-19.12</v>
-      </c>
-      <c r="E8" s="7">
-        <v>-1.19</v>
+      <c r="A7" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="D7" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="E7" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="F7" s="4" t="s">
+        <v>44</v>
       </c>
     </row>
     <row r="9" spans="1:6">
-      <c r="A9" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="B9" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C9" s="5">
-        <v>-8.35</v>
-      </c>
-      <c r="D9" s="5">
-        <v>-8.529999999999999</v>
-      </c>
-      <c r="E9" s="7">
-        <v>-0.18</v>
-      </c>
+      <c r="A9" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="B9" s="2"/>
+      <c r="C9" s="2"/>
+      <c r="D9" s="2"/>
+      <c r="E9" s="2"/>
     </row>
     <row r="10" spans="1:6">
       <c r="A10" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="D10" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="A11" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B11" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C11" s="6">
+        <v>-13.62</v>
+      </c>
+      <c r="D11" s="6">
+        <v>-11.29</v>
+      </c>
+      <c r="E11" s="7">
+        <v>2.33</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6">
+      <c r="A12" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B12" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C12" s="6">
+        <v>-19.12</v>
+      </c>
+      <c r="D12" s="6">
+        <v>-17.98</v>
+      </c>
+      <c r="E12" s="7">
+        <v>1.14</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6">
+      <c r="A13" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B13" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C13" s="6">
+        <v>-8.529999999999999</v>
+      </c>
+      <c r="D13" s="6">
+        <v>-6.58</v>
+      </c>
+      <c r="E13" s="7">
+        <v>1.95</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6">
+      <c r="A14" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="B10" s="3" t="s">
+      <c r="B14" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C10" s="5">
-        <v>-13.64</v>
-      </c>
-      <c r="D10" s="5">
+      <c r="C14" s="6">
         <v>-15.04</v>
       </c>
-      <c r="E10" s="7">
-        <v>-1.4</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
-      <c r="A11" s="3" t="s">
+      <c r="D14" s="6">
+        <v>-11.67</v>
+      </c>
+      <c r="E14" s="7">
+        <v>3.37</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6">
+      <c r="A15" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B11" s="3" t="s">
+      <c r="B15" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C11" s="5">
-        <v>-11.64</v>
-      </c>
-      <c r="D11" s="5">
+      <c r="C15" s="6">
         <v>-11.95</v>
       </c>
-      <c r="E11" s="7">
-        <v>-0.31</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
-      <c r="A12" s="3" t="s">
+      <c r="D15" s="6">
+        <v>-11.03</v>
+      </c>
+      <c r="E15" s="7">
+        <v>0.92</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6">
+      <c r="A16" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B12" s="3" t="s">
+      <c r="B16" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="C12" s="5">
-        <v>-3.6</v>
-      </c>
-      <c r="D12" s="5">
+      <c r="C16" s="6">
         <v>-5.47</v>
       </c>
-      <c r="E12" s="7">
-        <v>-1.87</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
-      <c r="A13" s="3" t="s">
+      <c r="D16" s="6">
+        <v>-4.12</v>
+      </c>
+      <c r="E16" s="7">
+        <v>1.35</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B13" s="3" t="s">
+      <c r="B17" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="C13" s="5">
-        <v>1.66</v>
-      </c>
-      <c r="D13" s="5">
+      <c r="C17" s="6">
         <v>0.42</v>
       </c>
-      <c r="E13" s="7">
-        <v>-1.24</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
-      <c r="A14" s="3" t="s">
+      <c r="D17" s="6">
+        <v>-4.82</v>
+      </c>
+      <c r="E17" s="8">
+        <v>-5.24</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B14" s="3" t="s">
+      <c r="B18" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="C14" s="5">
-        <v>-3.13</v>
-      </c>
-      <c r="D14" s="5">
+      <c r="C18" s="6">
         <v>-3.56</v>
       </c>
-      <c r="E14" s="7">
-        <v>-0.43</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6">
-      <c r="A15" s="3" t="s">
+      <c r="D18" s="6">
+        <v>-0.77</v>
+      </c>
+      <c r="E18" s="7">
+        <v>2.79</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="B15" s="3" t="s">
+      <c r="B19" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="C15" s="5">
-        <v>-2.84</v>
-      </c>
-      <c r="D15" s="5">
+      <c r="C19" s="6">
         <v>-3.79</v>
       </c>
-      <c r="E15" s="7">
-        <v>-0.95</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
-      <c r="A16" s="3" t="s">
+      <c r="D19" s="6">
+        <v>-3.17</v>
+      </c>
+      <c r="E19" s="7">
+        <v>0.62</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B16" s="3" t="s">
+      <c r="B20" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="C16" s="5">
-        <v>1.57</v>
-      </c>
-      <c r="D16" s="5">
+      <c r="C20" s="6">
         <v>-0.39</v>
       </c>
-      <c r="E16" s="7">
-        <v>-1.96</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5">
-      <c r="A17" s="3" t="s">
+      <c r="D20" s="6">
+        <v>0.39</v>
+      </c>
+      <c r="E20" s="7">
+        <v>0.78</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B17" s="3" t="s">
+      <c r="B21" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="C17" s="5">
-        <v>7.8</v>
-      </c>
-      <c r="D17" s="5">
+      <c r="C21" s="6">
         <v>5.63</v>
       </c>
-      <c r="E17" s="7">
-        <v>-2.17</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5">
-      <c r="A18" s="3" t="s">
+      <c r="D21" s="6">
+        <v>8.27</v>
+      </c>
+      <c r="E21" s="7">
+        <v>2.64</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B18" s="3" t="s">
+      <c r="B22" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="C18" s="5">
-        <v>-0.75</v>
-      </c>
-      <c r="D18" s="5">
+      <c r="C22" s="6">
         <v>-0.04</v>
       </c>
-      <c r="E18" s="6">
-        <v>0.71</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5">
-      <c r="A19" s="3" t="s">
+      <c r="D22" s="6">
+        <v>1.78</v>
+      </c>
+      <c r="E22" s="7">
+        <v>1.82</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B19" s="3" t="s">
+      <c r="B23" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="C19" s="5">
-        <v>-28</v>
-      </c>
-      <c r="D19" s="5">
+      <c r="C23" s="6">
         <v>-28.63</v>
       </c>
-      <c r="E19" s="7">
-        <v>-0.63</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5">
-      <c r="A20" s="3" t="s">
+      <c r="D23" s="6">
+        <v>-26.96</v>
+      </c>
+      <c r="E23" s="7">
+        <v>1.67</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5">
+      <c r="A24" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="B20" s="3" t="s">
+      <c r="B24" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="C20" s="5">
-        <v>16.55</v>
-      </c>
-      <c r="D20" s="5">
+      <c r="C24" s="6">
         <v>13.89</v>
       </c>
-      <c r="E20" s="7">
-        <v>-2.66</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5">
-      <c r="A21" s="3" t="s">
+      <c r="D24" s="6">
+        <v>18.41</v>
+      </c>
+      <c r="E24" s="7">
+        <v>4.52</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5">
+      <c r="A25" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B21" s="3" t="s">
+      <c r="B25" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="C21" s="5">
-        <v>-21.34</v>
-      </c>
-      <c r="D21" s="5">
+      <c r="C25" s="6">
         <v>-20.12</v>
       </c>
-      <c r="E21" s="6">
-        <v>1.22</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5">
-      <c r="A22" s="3" t="s">
+      <c r="D25" s="6">
+        <v>-19.38</v>
+      </c>
+      <c r="E25" s="7">
+        <v>0.74</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
+      <c r="A26" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B22" s="3" t="s">
+      <c r="B26" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="C22" s="5">
-        <v>-7.89</v>
-      </c>
-      <c r="D22" s="5">
+      <c r="C26" s="6">
         <v>-9.4</v>
       </c>
-      <c r="E22" s="7">
-        <v>-1.51</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5">
-      <c r="A23" s="3" t="s">
+      <c r="D26" s="6">
+        <v>-5.04</v>
+      </c>
+      <c r="E26" s="7">
+        <v>4.36</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5">
+      <c r="A27" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B23" s="3" t="s">
+      <c r="B27" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="C23" s="5">
-        <v>-12.01</v>
-      </c>
-      <c r="D23" s="5">
+      <c r="C27" s="6">
         <v>-13.35</v>
       </c>
-      <c r="E23" s="7">
-        <v>-1.34</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5">
-      <c r="A24" s="3" t="s">
+      <c r="D27" s="6">
+        <v>-12.12</v>
+      </c>
+      <c r="E27" s="7">
+        <v>1.23</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5">
+      <c r="A28" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B24" s="3" t="s">
+      <c r="B28" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="C24" s="5">
-        <v>-13.96</v>
-      </c>
-      <c r="D24" s="5">
+      <c r="C28" s="6">
         <v>-15.68</v>
       </c>
-      <c r="E24" s="7">
-        <v>-1.72</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5">
-      <c r="A25" s="3" t="s">
+      <c r="D28" s="6">
+        <v>-20.94</v>
+      </c>
+      <c r="E28" s="8">
+        <v>-5.26</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5">
+      <c r="A29" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="B25" s="3" t="s">
+      <c r="B29" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="C25" s="5">
-        <v>-15.18</v>
-      </c>
-      <c r="D25" s="5">
+      <c r="C29" s="6">
         <v>-15.79</v>
       </c>
-      <c r="E25" s="7">
-        <v>-0.61</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5">
-      <c r="A26" s="3" t="s">
+      <c r="D29" s="6">
+        <v>-12.03</v>
+      </c>
+      <c r="E29" s="7">
+        <v>3.76</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5">
+      <c r="A30" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B26" s="3" t="s">
+      <c r="B30" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="C26" s="5">
-        <v>7.5</v>
-      </c>
-      <c r="D26" s="5">
+      <c r="C30" s="6">
         <v>7.95</v>
       </c>
-      <c r="E26" s="6">
-        <v>0.45</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5">
-      <c r="A27" s="3" t="s">
+      <c r="D30" s="6">
+        <v>9.32</v>
+      </c>
+      <c r="E30" s="7">
+        <v>1.37</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5">
+      <c r="A31" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B27" s="3" t="s">
+      <c r="B31" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="C27" s="5">
-        <v>-30.38</v>
-      </c>
-      <c r="D27" s="5">
+      <c r="C31" s="6">
         <v>-30.77</v>
       </c>
-      <c r="E27" s="7">
-        <v>-0.39</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5">
-      <c r="A28" s="3" t="s">
+      <c r="D31" s="6">
+        <v>-29.27</v>
+      </c>
+      <c r="E31" s="7">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5">
+      <c r="A32" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B28" s="3" t="s">
+      <c r="B32" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="C28" s="5">
-        <v>-21.63</v>
-      </c>
-      <c r="D28" s="5">
+      <c r="C32" s="6">
         <v>-23.46</v>
       </c>
-      <c r="E28" s="7">
-        <v>-1.83</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5">
-      <c r="A29" s="3" t="s">
+      <c r="D32" s="6">
+        <v>-22.28</v>
+      </c>
+      <c r="E32" s="7">
+        <v>1.18</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5">
+      <c r="A33" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B29" s="3" t="s">
+      <c r="B33" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="C29" s="5">
-        <v>-33.42</v>
-      </c>
-      <c r="D29" s="5">
+      <c r="C33" s="6">
         <v>-34.09</v>
       </c>
-      <c r="E29" s="7">
-        <v>-0.67</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5">
-      <c r="A30" s="3" t="s">
+      <c r="D33" s="6">
+        <v>-32.85</v>
+      </c>
+      <c r="E33" s="7">
+        <v>1.24</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5">
+      <c r="A34" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="B30" s="3" t="s">
+      <c r="B34" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="C30" s="5">
-        <v>-19.42</v>
-      </c>
-      <c r="D30" s="5">
+      <c r="C34" s="6">
         <v>-20.23</v>
       </c>
-      <c r="E30" s="7">
-        <v>-0.8100000000000001</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5">
-      <c r="A31" s="3" t="s">
+      <c r="D34" s="6">
+        <v>-17.95</v>
+      </c>
+      <c r="E34" s="7">
+        <v>2.28</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5">
+      <c r="A35" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B31" s="3" t="s">
+      <c r="B35" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="C31" s="5">
-        <v>145.06</v>
-      </c>
-      <c r="D31" s="5">
+      <c r="C35" s="6">
         <v>144.25</v>
       </c>
-      <c r="E31" s="7">
-        <v>-0.8100000000000001</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5">
-      <c r="A32" s="3" t="s">
+      <c r="D35" s="6">
+        <v>147.37</v>
+      </c>
+      <c r="E35" s="7">
+        <v>3.12</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5">
+      <c r="A36" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B32" s="3" t="s">
+      <c r="B36" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="C32" s="5">
-        <v>357.5</v>
-      </c>
-      <c r="D32" s="5">
+      <c r="C36" s="6">
         <v>349.15</v>
       </c>
-      <c r="E32" s="7">
-        <v>-8.35</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5">
-      <c r="A33" s="3" t="s">
+      <c r="D36" s="6">
+        <v>354.5</v>
+      </c>
+      <c r="E36" s="7">
+        <v>5.35</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5">
+      <c r="A37" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B33" s="3" t="s">
+      <c r="B37" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="C33" s="5">
-        <v>355.55</v>
-      </c>
-      <c r="D33" s="5">
+      <c r="C37" s="6">
         <v>351.95</v>
       </c>
-      <c r="E33" s="7">
-        <v>-3.6</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5">
-      <c r="A34" s="3" t="s">
+      <c r="D37" s="6">
+        <v>358.6</v>
+      </c>
+      <c r="E37" s="7">
+        <v>6.65</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5">
+      <c r="A38" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="B34" s="3" t="s">
+      <c r="B38" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="C34" s="5">
-        <v>861.65</v>
-      </c>
-      <c r="D34" s="5">
+      <c r="C38" s="6">
         <v>853</v>
       </c>
-      <c r="E34" s="7">
-        <v>-8.65</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5">
-      <c r="A35" s="3" t="s">
+      <c r="D38" s="6">
+        <v>877.35</v>
+      </c>
+      <c r="E38" s="7">
+        <v>24.35</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5">
+      <c r="A39" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B35" s="3" t="s">
+      <c r="B39" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="C35" s="5">
-        <v>29.41</v>
-      </c>
-      <c r="D35" s="5">
+      <c r="C39" s="6">
         <v>28.65</v>
       </c>
-      <c r="E35" s="7">
-        <v>-0.76</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5">
-      <c r="A36" s="3" t="s">
+      <c r="D39" s="6">
+        <v>35.49</v>
+      </c>
+      <c r="E39" s="7">
+        <v>6.84</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5">
+      <c r="A40" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B36" s="3" t="s">
+      <c r="B40" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="C36" s="5">
-        <v>37.23</v>
-      </c>
-      <c r="D36" s="5">
+      <c r="C40" s="6">
         <v>34.87</v>
       </c>
-      <c r="E36" s="7">
-        <v>-2.36</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5">
-      <c r="A37" s="3" t="s">
+      <c r="D40" s="6">
+        <v>37.6</v>
+      </c>
+      <c r="E40" s="7">
+        <v>2.73</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5">
+      <c r="A41" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B37" s="3" t="s">
+      <c r="B41" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="C37" s="5">
-        <v>23.74</v>
-      </c>
-      <c r="D37" s="5">
+      <c r="C41" s="6">
         <v>21.83</v>
       </c>
-      <c r="E37" s="7">
-        <v>-1.91</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5">
-      <c r="A38" s="3" t="s">
+      <c r="D41" s="6">
+        <v>32.61</v>
+      </c>
+      <c r="E41" s="7">
+        <v>10.78</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5">
+      <c r="A42" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="B38" s="3" t="s">
+      <c r="B42" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="C38" s="5">
-        <v>29.98</v>
-      </c>
-      <c r="D38" s="5">
+      <c r="C42" s="6">
         <v>28.54</v>
       </c>
-      <c r="E38" s="7">
-        <v>-1.44</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5">
-      <c r="A39" s="3" t="s">
+      <c r="D42" s="6">
+        <v>37.65</v>
+      </c>
+      <c r="E42" s="7">
+        <v>9.109999999999999</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5">
+      <c r="A43" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B39" s="3" t="s">
+      <c r="B43" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="C39" s="5">
-        <v>-9.25</v>
-      </c>
-      <c r="D39" s="5">
+      <c r="C43" s="6">
         <v>1.05</v>
       </c>
-      <c r="E39" s="6">
-        <v>10.3</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5">
-      <c r="A40" s="3" t="s">
+      <c r="D43" s="6">
+        <v>-15.75</v>
+      </c>
+      <c r="E43" s="8">
+        <v>-16.8</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5">
+      <c r="A44" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B40" s="3" t="s">
+      <c r="B44" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="C40" s="5">
-        <v>-85.31</v>
-      </c>
-      <c r="D40" s="5">
+      <c r="C44" s="6">
         <v>-78.87</v>
       </c>
-      <c r="E40" s="6">
-        <v>6.44</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5">
-      <c r="A41" s="3" t="s">
+      <c r="D44" s="6">
+        <v>-79.14</v>
+      </c>
+      <c r="E44" s="8">
+        <v>-0.27</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5">
+      <c r="A45" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B41" s="3" t="s">
+      <c r="B45" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="C41" s="5">
-        <v>13.02</v>
-      </c>
-      <c r="D41" s="5">
+      <c r="C45" s="6">
         <v>-33.15</v>
       </c>
-      <c r="E41" s="7">
-        <v>-46.17</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5">
-      <c r="A42" s="3" t="s">
+      <c r="D45" s="6">
+        <v>-56.34</v>
+      </c>
+      <c r="E45" s="8">
+        <v>-23.19</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5">
+      <c r="A46" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="B42" s="3" t="s">
+      <c r="B46" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="C42" s="5">
-        <v>-51.16</v>
-      </c>
-      <c r="D42" s="5">
+      <c r="C46" s="6">
         <v>120.56</v>
       </c>
-      <c r="E42" s="6">
-        <v>171.72</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5">
-      <c r="A43" s="3" t="s">
+      <c r="D46" s="6">
+        <v>109</v>
+      </c>
+      <c r="E46" s="8">
+        <v>-11.56</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5">
+      <c r="A47" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B43" s="3" t="s">
+      <c r="B47" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="C43" s="5">
-        <v>-38.12</v>
-      </c>
-      <c r="D43" s="5">
+      <c r="C47" s="6">
         <v>-35.22</v>
       </c>
-      <c r="E43" s="6">
-        <v>2.9</v>
+      <c r="D47" s="6">
+        <v>-27.62</v>
+      </c>
+      <c r="E47" s="7">
+        <v>7.6</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A5:E5"/>
+    <mergeCell ref="A9:E9"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2284,61 +2454,61 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="28" customHeight="1">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="8" t="s">
-        <v>53</v>
-      </c>
-      <c r="C1" s="8" t="s">
-        <v>54</v>
-      </c>
-      <c r="D1" s="8" t="s">
-        <v>55</v>
-      </c>
-      <c r="E1" s="8" t="s">
-        <v>56</v>
-      </c>
-      <c r="F1" s="8" t="s">
-        <v>57</v>
-      </c>
-      <c r="G1" s="8" t="s">
-        <v>58</v>
-      </c>
-      <c r="H1" s="8" t="s">
-        <v>59</v>
-      </c>
-      <c r="I1" s="8" t="s">
-        <v>60</v>
+      <c r="B1" s="9" t="s">
+        <v>71</v>
+      </c>
+      <c r="C1" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="D1" s="9" t="s">
+        <v>73</v>
+      </c>
+      <c r="E1" s="9" t="s">
+        <v>74</v>
+      </c>
+      <c r="F1" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="G1" s="9" t="s">
+        <v>76</v>
+      </c>
+      <c r="H1" s="9" t="s">
+        <v>77</v>
+      </c>
+      <c r="I1" s="9" t="s">
+        <v>78</v>
       </c>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="9" t="s">
+      <c r="A2" s="10" t="s">
         <v>42</v>
       </c>
-      <c r="B2" s="10">
+      <c r="B2" s="11">
         <v>41.92</v>
       </c>
-      <c r="C2" s="11">
+      <c r="C2" s="12">
         <v>5</v>
       </c>
-      <c r="D2" s="10">
-        <v>31.3</v>
-      </c>
-      <c r="E2" s="10">
+      <c r="D2" s="11">
+        <v>37.2</v>
+      </c>
+      <c r="E2" s="11">
         <v>20</v>
       </c>
-      <c r="F2" s="10">
-        <v>-13.7</v>
-      </c>
-      <c r="G2" s="10">
-        <v>-9.300000000000001</v>
-      </c>
-      <c r="H2" s="10">
+      <c r="F2" s="11">
+        <v>-11.7</v>
+      </c>
+      <c r="G2" s="11">
+        <v>-8.199999999999999</v>
+      </c>
+      <c r="H2" s="11">
         <v>59.8</v>
       </c>
-      <c r="I2" s="10">
-        <v>0</v>
+      <c r="I2" s="11">
+        <v>20</v>
       </c>
     </row>
   </sheetData>
@@ -2439,37 +2609,37 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
-      <c r="A1" s="12" t="s">
+      <c r="A1" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="B1" s="12" t="s">
+      <c r="B1" s="13" t="s">
+        <v>38</v>
+      </c>
+      <c r="C1" s="13" t="s">
         <v>41</v>
       </c>
-      <c r="C1" s="12" t="s">
-        <v>38</v>
-      </c>
-      <c r="D1" s="12" t="s">
+      <c r="D1" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="E1" s="12" t="s">
+      <c r="E1" s="13" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="2" spans="1:5">
-      <c r="A2" s="13">
-        <v>0.1809</v>
-      </c>
-      <c r="B2" s="13">
-        <v>0.0146</v>
-      </c>
-      <c r="C2" s="13">
-        <v>0.0052</v>
-      </c>
-      <c r="D2" s="13">
-        <v>-0.0575</v>
-      </c>
-      <c r="E2" s="13">
-        <v>-0.2301</v>
+      <c r="A2" s="14">
+        <v>0.1738</v>
+      </c>
+      <c r="B2" s="14">
+        <v>0.008100000000000001</v>
+      </c>
+      <c r="C2" s="14">
+        <v>0.0039</v>
+      </c>
+      <c r="D2" s="14">
+        <v>-0.0526</v>
+      </c>
+      <c r="E2" s="14">
+        <v>-0.2261</v>
       </c>
     </row>
   </sheetData>

--- a/HINDUJA_GROUP_Technical_Metrics.xlsx
+++ b/HINDUJA_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="236" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="207" uniqueCount="61">
   <si>
     <t>Symbol</t>
   </si>
@@ -163,61 +163,7 @@
     <t>▶  SIGNAL EVENTS (vs Previous Run)</t>
   </si>
   <si>
-    <t>Signal</t>
-  </si>
-  <si>
-    <t>Change</t>
-  </si>
-  <si>
-    <t>Direction</t>
-  </si>
-  <si>
-    <t>Prev Value</t>
-  </si>
-  <si>
-    <t>Curr Value</t>
-  </si>
-  <si>
-    <t>50 DMA &gt; 200 DMA</t>
-  </si>
-  <si>
-    <t>No → Yes</t>
-  </si>
-  <si>
-    <t>🟢 GOLDEN CROSS</t>
-  </si>
-  <si>
-    <t>RSI Oversold Recovery</t>
-  </si>
-  <si>
-    <t>28.6 → 35.5</t>
-  </si>
-  <si>
-    <t>🟢 BULLISH</t>
-  </si>
-  <si>
-    <t>28.6</t>
-  </si>
-  <si>
-    <t>35.5</t>
-  </si>
-  <si>
-    <t>21.8 → 32.6</t>
-  </si>
-  <si>
-    <t>21.8</t>
-  </si>
-  <si>
-    <t>32.6</t>
-  </si>
-  <si>
-    <t>28.5 → 37.6</t>
-  </si>
-  <si>
-    <t>28.5</t>
-  </si>
-  <si>
-    <t>37.6</t>
+    <t>No signal events detected since last run.</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -303,14 +249,14 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FF9C0006"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FF006100"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -343,13 +289,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -419,15 +365,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -943,10 +888,10 @@
         <v>42</v>
       </c>
       <c r="C2">
-        <v>147.37</v>
+        <v>145</v>
       </c>
       <c r="D2">
-        <v>2.16</v>
+        <v>-1.61</v>
       </c>
       <c r="E2">
         <v>208.37</v>
@@ -955,46 +900,46 @@
         <v>131.36</v>
       </c>
       <c r="G2">
-        <v>-29.27</v>
+        <v>-30.41</v>
       </c>
       <c r="H2">
-        <v>12.19</v>
+        <v>10.38</v>
       </c>
       <c r="I2">
-        <v>-4.12</v>
+        <v>-2.82</v>
       </c>
       <c r="J2">
-        <v>-11.29</v>
+        <v>-11.45</v>
       </c>
       <c r="K2">
-        <v>-5.04</v>
+        <v>-7.36</v>
       </c>
       <c r="L2">
-        <v>8.27</v>
+        <v>7.09</v>
       </c>
       <c r="M2">
-        <v>17.38</v>
+        <v>17.27</v>
       </c>
       <c r="N2">
         <v>79</v>
       </c>
       <c r="O2">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="P2">
-        <v>146.18</v>
+        <v>145.34</v>
       </c>
       <c r="Q2">
-        <v>154.35</v>
+        <v>153.77</v>
       </c>
       <c r="R2">
-        <v>165.62</v>
+        <v>165.03</v>
       </c>
       <c r="S2">
-        <v>169.16</v>
+        <v>169.02</v>
       </c>
       <c r="T2">
-        <v>-12.88</v>
+        <v>-14.21</v>
       </c>
       <c r="U2" t="s">
         <v>43</v>
@@ -1009,43 +954,43 @@
         <v>0</v>
       </c>
       <c r="Y2">
-        <v>35.49</v>
+        <v>32.91</v>
       </c>
       <c r="Z2">
-        <v>-5.36</v>
+        <v>-5.41</v>
       </c>
       <c r="AA2">
-        <v>-4.62</v>
+        <v>-4.77</v>
       </c>
       <c r="AB2">
-        <v>-0.75</v>
+        <v>-0.63</v>
       </c>
       <c r="AC2">
-        <v>14.46</v>
+        <v>26.2</v>
       </c>
       <c r="AD2">
-        <v>6.26</v>
+        <v>13.61</v>
       </c>
       <c r="AE2">
-        <v>4.07</v>
+        <v>4.01</v>
       </c>
       <c r="AF2">
-        <v>-15.75</v>
+        <v>38.67</v>
       </c>
       <c r="AG2">
-        <v>166.26</v>
+        <v>166.33</v>
       </c>
       <c r="AH2">
-        <v>142.45</v>
+        <v>141.22</v>
       </c>
       <c r="AI2">
-        <v>157.65</v>
+        <v>157.56</v>
       </c>
       <c r="AJ2" t="s">
         <v>45</v>
       </c>
       <c r="AK2">
-        <v>62.58</v>
+        <v>63.69</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1056,10 +1001,10 @@
         <v>42</v>
       </c>
       <c r="C3">
-        <v>354.5</v>
+        <v>367</v>
       </c>
       <c r="D3">
-        <v>1.53</v>
+        <v>3.53</v>
       </c>
       <c r="E3">
         <v>456.15</v>
@@ -1068,46 +1013,46 @@
         <v>225</v>
       </c>
       <c r="G3">
-        <v>-22.28</v>
+        <v>-19.54</v>
       </c>
       <c r="H3">
-        <v>57.56</v>
+        <v>63.11</v>
       </c>
       <c r="I3">
-        <v>-4.82</v>
+        <v>-0.23</v>
       </c>
       <c r="J3">
-        <v>-17.98</v>
+        <v>-16.88</v>
       </c>
       <c r="K3">
-        <v>-12.12</v>
+        <v>-8.99</v>
       </c>
       <c r="L3">
-        <v>1.78</v>
+        <v>3.98</v>
       </c>
       <c r="M3">
-        <v>0.8100000000000001</v>
+        <v>1.44</v>
       </c>
       <c r="N3">
         <v>40</v>
       </c>
       <c r="O3">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="P3">
-        <v>357.32</v>
+        <v>357.15</v>
       </c>
       <c r="Q3">
-        <v>387.57</v>
+        <v>384.14</v>
       </c>
       <c r="R3">
-        <v>402.84</v>
+        <v>401.86</v>
       </c>
       <c r="S3">
-        <v>340.22</v>
+        <v>340.59</v>
       </c>
       <c r="T3">
-        <v>4.2</v>
+        <v>7.75</v>
       </c>
       <c r="U3" t="s">
         <v>43</v>
@@ -1122,34 +1067,34 @@
         <v>2</v>
       </c>
       <c r="Y3">
-        <v>37.6</v>
+        <v>43.53</v>
       </c>
       <c r="Z3">
-        <v>-16.38</v>
+        <v>-15.15</v>
       </c>
       <c r="AA3">
-        <v>-13.26</v>
+        <v>-13.64</v>
       </c>
       <c r="AB3">
-        <v>-3.11</v>
+        <v>-1.51</v>
       </c>
       <c r="AC3">
-        <v>39.93</v>
+        <v>66.11</v>
       </c>
       <c r="AD3">
-        <v>29.39</v>
+        <v>43.63</v>
       </c>
       <c r="AE3">
-        <v>16.92</v>
+        <v>17.14</v>
       </c>
       <c r="AF3">
-        <v>-79.14</v>
+        <v>-59.11</v>
       </c>
       <c r="AG3">
-        <v>461.89</v>
+        <v>455.39</v>
       </c>
       <c r="AH3">
-        <v>313.25</v>
+        <v>312.89</v>
       </c>
       <c r="AI3">
         <v>401.23</v>
@@ -1158,7 +1103,7 @@
         <v>45</v>
       </c>
       <c r="AK3">
-        <v>43.58</v>
+        <v>39.27</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1169,10 +1114,10 @@
         <v>42</v>
       </c>
       <c r="C4">
-        <v>358.6</v>
+        <v>361.85</v>
       </c>
       <c r="D4">
-        <v>1.89</v>
+        <v>0.91</v>
       </c>
       <c r="E4">
         <v>534</v>
@@ -1181,46 +1126,46 @@
         <v>344.7</v>
       </c>
       <c r="G4">
-        <v>-32.85</v>
+        <v>-32.24</v>
       </c>
       <c r="H4">
-        <v>4.03</v>
+        <v>4.98</v>
       </c>
       <c r="I4">
-        <v>-0.77</v>
+        <v>-0.32</v>
       </c>
       <c r="J4">
-        <v>-6.58</v>
+        <v>-5.14</v>
       </c>
       <c r="K4">
-        <v>-20.94</v>
+        <v>-18.83</v>
       </c>
       <c r="L4">
-        <v>-26.96</v>
+        <v>-26.88</v>
       </c>
       <c r="M4">
-        <v>-22.61</v>
+        <v>-22.43</v>
       </c>
       <c r="N4">
         <v>21</v>
       </c>
       <c r="O4">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="P4">
-        <v>357.61</v>
+        <v>357.38</v>
       </c>
       <c r="Q4">
-        <v>370.52</v>
+        <v>369.53</v>
       </c>
       <c r="R4">
-        <v>390.83</v>
+        <v>389.46</v>
       </c>
       <c r="S4">
-        <v>404.24</v>
+        <v>403.79</v>
       </c>
       <c r="T4">
-        <v>-11.29</v>
+        <v>-10.39</v>
       </c>
       <c r="U4" t="s">
         <v>43</v>
@@ -1235,34 +1180,34 @@
         <v>0</v>
       </c>
       <c r="Y4">
-        <v>32.61</v>
+        <v>37.17</v>
       </c>
       <c r="Z4">
-        <v>-10.02</v>
+        <v>-9.41</v>
       </c>
       <c r="AA4">
-        <v>-9.460000000000001</v>
+        <v>-9.449999999999999</v>
       </c>
       <c r="AB4">
-        <v>-0.5600000000000001</v>
+        <v>0.04</v>
       </c>
       <c r="AC4">
-        <v>33.33</v>
+        <v>66.67</v>
       </c>
       <c r="AD4">
-        <v>18.15</v>
+        <v>34.98</v>
       </c>
       <c r="AE4">
-        <v>10</v>
+        <v>9.9</v>
       </c>
       <c r="AF4">
-        <v>-56.34</v>
+        <v>-28.21</v>
       </c>
       <c r="AG4">
-        <v>391.03</v>
+        <v>389.69</v>
       </c>
       <c r="AH4">
-        <v>350.01</v>
+        <v>349.37</v>
       </c>
       <c r="AI4">
         <v>384.24</v>
@@ -1271,7 +1216,7 @@
         <v>45</v>
       </c>
       <c r="AK4">
-        <v>57.99</v>
+        <v>54.34</v>
       </c>
     </row>
     <row r="5" spans="1:37">
@@ -1282,10 +1227,10 @@
         <v>42</v>
       </c>
       <c r="C5">
-        <v>877.35</v>
+        <v>866</v>
       </c>
       <c r="D5">
-        <v>2.85</v>
+        <v>-1.29</v>
       </c>
       <c r="E5">
         <v>1069.3</v>
@@ -1294,46 +1239,46 @@
         <v>739.5</v>
       </c>
       <c r="G5">
-        <v>-17.95</v>
+        <v>-19.01</v>
       </c>
       <c r="H5">
-        <v>18.64</v>
+        <v>17.11</v>
       </c>
       <c r="I5">
-        <v>-3.17</v>
+        <v>-1.02</v>
       </c>
       <c r="J5">
-        <v>-11.67</v>
+        <v>-11.47</v>
       </c>
       <c r="K5">
-        <v>-12.03</v>
+        <v>-14.23</v>
       </c>
       <c r="L5">
-        <v>18.41</v>
+        <v>15.6</v>
       </c>
       <c r="M5">
-        <v>-5.26</v>
+        <v>-5.91</v>
       </c>
       <c r="N5">
         <v>99</v>
       </c>
       <c r="O5">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="P5">
-        <v>866.1799999999999</v>
+        <v>864.4</v>
       </c>
       <c r="Q5">
-        <v>911.45</v>
+        <v>906.9299999999999</v>
       </c>
       <c r="R5">
-        <v>970.25</v>
+        <v>966.99</v>
       </c>
       <c r="S5">
-        <v>925.05</v>
+        <v>925.14</v>
       </c>
       <c r="T5">
-        <v>-5.16</v>
+        <v>-6.39</v>
       </c>
       <c r="U5" t="s">
         <v>43</v>
@@ -1348,34 +1293,34 @@
         <v>1</v>
       </c>
       <c r="Y5">
-        <v>37.65</v>
+        <v>35.38</v>
       </c>
       <c r="Z5">
-        <v>-31.36</v>
+        <v>-30.8</v>
       </c>
       <c r="AA5">
-        <v>-28.72</v>
+        <v>-29.14</v>
       </c>
       <c r="AB5">
-        <v>-2.64</v>
+        <v>-1.67</v>
       </c>
       <c r="AC5">
-        <v>50.21</v>
+        <v>64.58</v>
       </c>
       <c r="AD5">
-        <v>42.03</v>
+        <v>49.88</v>
       </c>
       <c r="AE5">
-        <v>22.77</v>
+        <v>22.43</v>
       </c>
       <c r="AF5">
-        <v>109</v>
+        <v>27.85</v>
       </c>
       <c r="AG5">
-        <v>987.97</v>
+        <v>982.9299999999999</v>
       </c>
       <c r="AH5">
-        <v>834.9400000000001</v>
+        <v>830.9299999999999</v>
       </c>
       <c r="AI5">
         <v>921.99</v>
@@ -1384,7 +1329,7 @@
         <v>45</v>
       </c>
       <c r="AK5">
-        <v>57.88</v>
+        <v>54.78</v>
       </c>
     </row>
     <row r="6" spans="1:37">
@@ -1395,10 +1340,10 @@
         <v>42</v>
       </c>
       <c r="C6">
-        <v>2.58</v>
+        <v>2.61</v>
       </c>
       <c r="D6">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="E6">
         <v>3.38</v>
@@ -1407,37 +1352,37 @@
         <v>1.84</v>
       </c>
       <c r="G6">
-        <v>-23.67</v>
+        <v>-22.78</v>
       </c>
       <c r="H6">
-        <v>40.22</v>
+        <v>41.85</v>
       </c>
       <c r="I6">
-        <v>0.39</v>
+        <v>0.38</v>
       </c>
       <c r="J6">
-        <v>-11.03</v>
+        <v>-8.74</v>
       </c>
       <c r="K6">
-        <v>9.32</v>
+        <v>9.66</v>
       </c>
       <c r="L6">
-        <v>-19.38</v>
+        <v>-18.18</v>
       </c>
       <c r="M6">
-        <v>0.39</v>
+        <v>0.7</v>
       </c>
       <c r="N6">
         <v>60</v>
       </c>
       <c r="O6">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="P6">
-        <v>2.58</v>
+        <v>2.59</v>
       </c>
       <c r="Q6">
-        <v>2.67</v>
+        <v>2.66</v>
       </c>
       <c r="R6">
         <v>2.65</v>
@@ -1446,7 +1391,7 @@
         <v>2.64</v>
       </c>
       <c r="T6">
-        <v>-2.39</v>
+        <v>-1.18</v>
       </c>
       <c r="U6" t="s">
         <v>44</v>
@@ -1461,7 +1406,7 @@
         <v>2</v>
       </c>
       <c r="Y6">
-        <v>42.44</v>
+        <v>45.67</v>
       </c>
       <c r="Z6">
         <v>-0.04</v>
@@ -1473,19 +1418,19 @@
         <v>-0.01</v>
       </c>
       <c r="AC6">
-        <v>32.52</v>
+        <v>55.44</v>
       </c>
       <c r="AD6">
-        <v>31.51</v>
+        <v>39.65</v>
       </c>
       <c r="AE6">
         <v>0.12</v>
       </c>
       <c r="AF6">
-        <v>-27.62</v>
+        <v>-14.03</v>
       </c>
       <c r="AG6">
-        <v>2.87</v>
+        <v>2.86</v>
       </c>
       <c r="AH6">
         <v>2.46</v>
@@ -1497,7 +1442,7 @@
         <v>45</v>
       </c>
       <c r="AK6">
-        <v>29.73</v>
+        <v>28.49</v>
       </c>
     </row>
   </sheetData>
@@ -1638,7 +1583,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F47"/>
+  <dimension ref="A1:F46"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.7109375" customWidth="1"/>
@@ -1658,783 +1603,719 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="C2" s="3" t="s">
+    </row>
+    <row r="5" spans="1:6">
+      <c r="A5" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="D2" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="E2" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="F2" s="3" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6">
-      <c r="A3" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="B3" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="C3" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="D3" s="4" t="s">
-        <v>54</v>
-      </c>
-      <c r="E3" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="F3" s="4" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6">
-      <c r="A4" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="B4" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="C4" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="D4" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="E4" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="F4" s="4" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6">
-      <c r="A5" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="B5" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="C5" s="4" t="s">
-        <v>60</v>
-      </c>
-      <c r="D5" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="E5" s="4" t="s">
-        <v>61</v>
-      </c>
-      <c r="F5" s="4" t="s">
-        <v>62</v>
-      </c>
+      <c r="B5" s="2"/>
+      <c r="C5" s="2"/>
+      <c r="D5" s="2"/>
+      <c r="E5" s="2"/>
     </row>
     <row r="6" spans="1:6">
       <c r="A6" s="4" t="s">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>63</v>
+        <v>50</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>64</v>
-      </c>
-      <c r="F6" s="4" t="s">
-        <v>65</v>
+        <v>52</v>
       </c>
     </row>
     <row r="7" spans="1:6">
-      <c r="A7" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="B7" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="C7" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="D7" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="E7" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="F7" s="4" t="s">
-        <v>44</v>
+      <c r="A7" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C7" s="5">
+        <v>-11.29</v>
+      </c>
+      <c r="D7" s="5">
+        <v>-11.45</v>
+      </c>
+      <c r="E7" s="6">
+        <v>-0.16</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6">
+      <c r="A8" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C8" s="5">
+        <v>-17.98</v>
+      </c>
+      <c r="D8" s="5">
+        <v>-16.88</v>
+      </c>
+      <c r="E8" s="7">
+        <v>1.1</v>
       </c>
     </row>
     <row r="9" spans="1:6">
-      <c r="A9" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="B9" s="2"/>
-      <c r="C9" s="2"/>
-      <c r="D9" s="2"/>
-      <c r="E9" s="2"/>
+      <c r="A9" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C9" s="5">
+        <v>-6.58</v>
+      </c>
+      <c r="D9" s="5">
+        <v>-5.14</v>
+      </c>
+      <c r="E9" s="7">
+        <v>1.44</v>
+      </c>
     </row>
     <row r="10" spans="1:6">
       <c r="A10" s="3" t="s">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="C10" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="D10" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="E10" s="3" t="s">
-        <v>70</v>
+        <v>9</v>
+      </c>
+      <c r="C10" s="5">
+        <v>-11.67</v>
+      </c>
+      <c r="D10" s="5">
+        <v>-11.47</v>
+      </c>
+      <c r="E10" s="7">
+        <v>0.2</v>
       </c>
     </row>
     <row r="11" spans="1:6">
-      <c r="A11" s="5" t="s">
+      <c r="A11" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C11" s="5">
+        <v>-11.03</v>
+      </c>
+      <c r="D11" s="5">
+        <v>-8.74</v>
+      </c>
+      <c r="E11" s="7">
+        <v>2.29</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6">
+      <c r="A12" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B11" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C11" s="6">
-        <v>-13.62</v>
-      </c>
-      <c r="D11" s="6">
-        <v>-11.29</v>
-      </c>
-      <c r="E11" s="7">
-        <v>2.33</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
-      <c r="A12" s="5" t="s">
+      <c r="B12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C12" s="5">
+        <v>-4.12</v>
+      </c>
+      <c r="D12" s="5">
+        <v>-2.82</v>
+      </c>
+      <c r="E12" s="7">
+        <v>1.3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6">
+      <c r="A13" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B12" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C12" s="6">
-        <v>-19.12</v>
-      </c>
-      <c r="D12" s="6">
-        <v>-17.98</v>
-      </c>
-      <c r="E12" s="7">
-        <v>1.14</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
-      <c r="A13" s="5" t="s">
+      <c r="B13" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C13" s="5">
+        <v>-4.82</v>
+      </c>
+      <c r="D13" s="5">
+        <v>-0.23</v>
+      </c>
+      <c r="E13" s="7">
+        <v>4.59</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6">
+      <c r="A14" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B13" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C13" s="6">
-        <v>-8.529999999999999</v>
-      </c>
-      <c r="D13" s="6">
-        <v>-6.58</v>
-      </c>
-      <c r="E13" s="7">
-        <v>1.95</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
-      <c r="A14" s="5" t="s">
+      <c r="B14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C14" s="5">
+        <v>-0.77</v>
+      </c>
+      <c r="D14" s="5">
+        <v>-0.32</v>
+      </c>
+      <c r="E14" s="7">
+        <v>0.45</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6">
+      <c r="A15" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="B14" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C14" s="6">
-        <v>-15.04</v>
-      </c>
-      <c r="D14" s="6">
-        <v>-11.67</v>
-      </c>
-      <c r="E14" s="7">
-        <v>3.37</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6">
-      <c r="A15" s="5" t="s">
+      <c r="B15" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C15" s="5">
+        <v>-3.17</v>
+      </c>
+      <c r="D15" s="5">
+        <v>-1.02</v>
+      </c>
+      <c r="E15" s="7">
+        <v>2.15</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6">
+      <c r="A16" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="B15" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C15" s="6">
-        <v>-11.95</v>
-      </c>
-      <c r="D15" s="6">
-        <v>-11.03</v>
-      </c>
-      <c r="E15" s="7">
-        <v>0.92</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
-      <c r="A16" s="5" t="s">
+      <c r="B16" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C16" s="5">
+        <v>0.39</v>
+      </c>
+      <c r="D16" s="5">
+        <v>0.38</v>
+      </c>
+      <c r="E16" s="6">
+        <v>-0.01</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B16" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C16" s="6">
-        <v>-5.47</v>
-      </c>
-      <c r="D16" s="6">
-        <v>-4.12</v>
-      </c>
-      <c r="E16" s="7">
-        <v>1.35</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5">
-      <c r="A17" s="5" t="s">
+      <c r="B17" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C17" s="5">
+        <v>8.27</v>
+      </c>
+      <c r="D17" s="5">
+        <v>7.09</v>
+      </c>
+      <c r="E17" s="6">
+        <v>-1.18</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B17" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C17" s="6">
-        <v>0.42</v>
-      </c>
-      <c r="D17" s="6">
-        <v>-4.82</v>
-      </c>
-      <c r="E17" s="8">
-        <v>-5.24</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5">
-      <c r="A18" s="5" t="s">
+      <c r="B18" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C18" s="5">
+        <v>1.78</v>
+      </c>
+      <c r="D18" s="5">
+        <v>3.98</v>
+      </c>
+      <c r="E18" s="7">
+        <v>2.2</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B18" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C18" s="6">
-        <v>-3.56</v>
-      </c>
-      <c r="D18" s="6">
-        <v>-0.77</v>
-      </c>
-      <c r="E18" s="7">
-        <v>2.79</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5">
-      <c r="A19" s="5" t="s">
+      <c r="B19" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C19" s="5">
+        <v>-26.96</v>
+      </c>
+      <c r="D19" s="5">
+        <v>-26.88</v>
+      </c>
+      <c r="E19" s="7">
+        <v>0.08</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="B19" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C19" s="6">
-        <v>-3.79</v>
-      </c>
-      <c r="D19" s="6">
-        <v>-3.17</v>
-      </c>
-      <c r="E19" s="7">
-        <v>0.62</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5">
-      <c r="A20" s="5" t="s">
+      <c r="B20" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C20" s="5">
+        <v>18.41</v>
+      </c>
+      <c r="D20" s="5">
+        <v>15.6</v>
+      </c>
+      <c r="E20" s="6">
+        <v>-2.81</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="B20" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C20" s="6">
-        <v>-0.39</v>
-      </c>
-      <c r="D20" s="6">
-        <v>0.39</v>
-      </c>
-      <c r="E20" s="7">
-        <v>0.78</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5">
-      <c r="A21" s="5" t="s">
+      <c r="B21" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C21" s="5">
+        <v>-19.38</v>
+      </c>
+      <c r="D21" s="5">
+        <v>-18.18</v>
+      </c>
+      <c r="E21" s="7">
+        <v>1.2</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B21" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C21" s="6">
-        <v>5.63</v>
-      </c>
-      <c r="D21" s="6">
-        <v>8.27</v>
-      </c>
-      <c r="E21" s="7">
-        <v>2.64</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5">
-      <c r="A22" s="5" t="s">
+      <c r="B22" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C22" s="5">
+        <v>-5.04</v>
+      </c>
+      <c r="D22" s="5">
+        <v>-7.36</v>
+      </c>
+      <c r="E22" s="6">
+        <v>-2.32</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B22" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C22" s="6">
-        <v>-0.04</v>
-      </c>
-      <c r="D22" s="6">
-        <v>1.78</v>
-      </c>
-      <c r="E22" s="7">
-        <v>1.82</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5">
-      <c r="A23" s="5" t="s">
+      <c r="B23" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C23" s="5">
+        <v>-12.12</v>
+      </c>
+      <c r="D23" s="5">
+        <v>-8.99</v>
+      </c>
+      <c r="E23" s="7">
+        <v>3.13</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5">
+      <c r="A24" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B23" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C23" s="6">
-        <v>-28.63</v>
-      </c>
-      <c r="D23" s="6">
-        <v>-26.96</v>
-      </c>
-      <c r="E23" s="7">
-        <v>1.67</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5">
-      <c r="A24" s="5" t="s">
+      <c r="B24" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C24" s="5">
+        <v>-20.94</v>
+      </c>
+      <c r="D24" s="5">
+        <v>-18.83</v>
+      </c>
+      <c r="E24" s="7">
+        <v>2.11</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5">
+      <c r="A25" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="B24" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C24" s="6">
-        <v>13.89</v>
-      </c>
-      <c r="D24" s="6">
-        <v>18.41</v>
-      </c>
-      <c r="E24" s="7">
-        <v>4.52</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5">
-      <c r="A25" s="5" t="s">
+      <c r="B25" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C25" s="5">
+        <v>-12.03</v>
+      </c>
+      <c r="D25" s="5">
+        <v>-14.23</v>
+      </c>
+      <c r="E25" s="6">
+        <v>-2.2</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
+      <c r="A26" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="B25" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C25" s="6">
-        <v>-20.12</v>
-      </c>
-      <c r="D25" s="6">
-        <v>-19.38</v>
-      </c>
-      <c r="E25" s="7">
-        <v>0.74</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5">
-      <c r="A26" s="5" t="s">
+      <c r="B26" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C26" s="5">
+        <v>9.32</v>
+      </c>
+      <c r="D26" s="5">
+        <v>9.66</v>
+      </c>
+      <c r="E26" s="7">
+        <v>0.34</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5">
+      <c r="A27" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B26" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C26" s="6">
-        <v>-9.4</v>
-      </c>
-      <c r="D26" s="6">
-        <v>-5.04</v>
-      </c>
-      <c r="E26" s="7">
-        <v>4.36</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5">
-      <c r="A27" s="5" t="s">
+      <c r="B27" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C27" s="5">
+        <v>-29.27</v>
+      </c>
+      <c r="D27" s="5">
+        <v>-30.41</v>
+      </c>
+      <c r="E27" s="6">
+        <v>-1.14</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5">
+      <c r="A28" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B27" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C27" s="6">
-        <v>-13.35</v>
-      </c>
-      <c r="D27" s="6">
-        <v>-12.12</v>
-      </c>
-      <c r="E27" s="7">
-        <v>1.23</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5">
-      <c r="A28" s="5" t="s">
+      <c r="B28" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C28" s="5">
+        <v>-22.28</v>
+      </c>
+      <c r="D28" s="5">
+        <v>-19.54</v>
+      </c>
+      <c r="E28" s="7">
+        <v>2.74</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5">
+      <c r="A29" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B28" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C28" s="6">
-        <v>-15.68</v>
-      </c>
-      <c r="D28" s="6">
-        <v>-20.94</v>
-      </c>
-      <c r="E28" s="8">
-        <v>-5.26</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5">
-      <c r="A29" s="5" t="s">
+      <c r="B29" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C29" s="5">
+        <v>-32.85</v>
+      </c>
+      <c r="D29" s="5">
+        <v>-32.24</v>
+      </c>
+      <c r="E29" s="7">
+        <v>0.61</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5">
+      <c r="A30" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="B29" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C29" s="6">
-        <v>-15.79</v>
-      </c>
-      <c r="D29" s="6">
-        <v>-12.03</v>
-      </c>
-      <c r="E29" s="7">
-        <v>3.76</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5">
-      <c r="A30" s="5" t="s">
+      <c r="B30" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C30" s="5">
+        <v>-17.95</v>
+      </c>
+      <c r="D30" s="5">
+        <v>-19.01</v>
+      </c>
+      <c r="E30" s="6">
+        <v>-1.06</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5">
+      <c r="A31" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="B30" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C30" s="6">
-        <v>7.95</v>
-      </c>
-      <c r="D30" s="6">
-        <v>9.32</v>
-      </c>
-      <c r="E30" s="7">
-        <v>1.37</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5">
-      <c r="A31" s="5" t="s">
+      <c r="B31" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C31" s="5">
+        <v>-23.67</v>
+      </c>
+      <c r="D31" s="5">
+        <v>-22.78</v>
+      </c>
+      <c r="E31" s="7">
+        <v>0.89</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5">
+      <c r="A32" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B31" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C31" s="6">
-        <v>-30.77</v>
-      </c>
-      <c r="D31" s="6">
-        <v>-29.27</v>
-      </c>
-      <c r="E31" s="7">
-        <v>1.5</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5">
-      <c r="A32" s="5" t="s">
+      <c r="B32" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C32" s="5">
+        <v>147.37</v>
+      </c>
+      <c r="D32" s="5">
+        <v>145</v>
+      </c>
+      <c r="E32" s="6">
+        <v>-2.37</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5">
+      <c r="A33" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B32" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C32" s="6">
-        <v>-23.46</v>
-      </c>
-      <c r="D32" s="6">
-        <v>-22.28</v>
-      </c>
-      <c r="E32" s="7">
-        <v>1.18</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5">
-      <c r="A33" s="5" t="s">
+      <c r="B33" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C33" s="5">
+        <v>354.5</v>
+      </c>
+      <c r="D33" s="5">
+        <v>367</v>
+      </c>
+      <c r="E33" s="7">
+        <v>12.5</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5">
+      <c r="A34" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B33" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C33" s="6">
-        <v>-34.09</v>
-      </c>
-      <c r="D33" s="6">
-        <v>-32.85</v>
-      </c>
-      <c r="E33" s="7">
-        <v>1.24</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5">
-      <c r="A34" s="5" t="s">
+      <c r="B34" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C34" s="5">
+        <v>358.6</v>
+      </c>
+      <c r="D34" s="5">
+        <v>361.85</v>
+      </c>
+      <c r="E34" s="7">
+        <v>3.25</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5">
+      <c r="A35" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="B34" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C34" s="6">
-        <v>-20.23</v>
-      </c>
-      <c r="D34" s="6">
-        <v>-17.95</v>
-      </c>
-      <c r="E34" s="7">
-        <v>2.28</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5">
-      <c r="A35" s="5" t="s">
+      <c r="B35" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C35" s="5">
+        <v>877.35</v>
+      </c>
+      <c r="D35" s="5">
+        <v>866</v>
+      </c>
+      <c r="E35" s="6">
+        <v>-11.35</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5">
+      <c r="A36" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B36" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C36" s="5">
+        <v>2.58</v>
+      </c>
+      <c r="D36" s="5">
+        <v>2.61</v>
+      </c>
+      <c r="E36" s="7">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5">
+      <c r="A37" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B35" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C35" s="6">
-        <v>144.25</v>
-      </c>
-      <c r="D35" s="6">
-        <v>147.37</v>
-      </c>
-      <c r="E35" s="7">
-        <v>3.12</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5">
-      <c r="A36" s="5" t="s">
+      <c r="B37" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C37" s="5">
+        <v>35.49</v>
+      </c>
+      <c r="D37" s="5">
+        <v>32.91</v>
+      </c>
+      <c r="E37" s="6">
+        <v>-2.58</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5">
+      <c r="A38" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B36" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C36" s="6">
-        <v>349.15</v>
-      </c>
-      <c r="D36" s="6">
-        <v>354.5</v>
-      </c>
-      <c r="E36" s="7">
-        <v>5.35</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5">
-      <c r="A37" s="5" t="s">
+      <c r="B38" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C38" s="5">
+        <v>37.6</v>
+      </c>
+      <c r="D38" s="5">
+        <v>43.53</v>
+      </c>
+      <c r="E38" s="7">
+        <v>5.93</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5">
+      <c r="A39" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B37" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C37" s="6">
-        <v>351.95</v>
-      </c>
-      <c r="D37" s="6">
-        <v>358.6</v>
-      </c>
-      <c r="E37" s="7">
-        <v>6.65</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5">
-      <c r="A38" s="5" t="s">
+      <c r="B39" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C39" s="5">
+        <v>32.61</v>
+      </c>
+      <c r="D39" s="5">
+        <v>37.17</v>
+      </c>
+      <c r="E39" s="7">
+        <v>4.56</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5">
+      <c r="A40" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="B38" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C38" s="6">
-        <v>853</v>
-      </c>
-      <c r="D38" s="6">
-        <v>877.35</v>
-      </c>
-      <c r="E38" s="7">
-        <v>24.35</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5">
-      <c r="A39" s="5" t="s">
+      <c r="B40" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C40" s="5">
+        <v>37.65</v>
+      </c>
+      <c r="D40" s="5">
+        <v>35.38</v>
+      </c>
+      <c r="E40" s="6">
+        <v>-2.27</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5">
+      <c r="A41" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B41" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C41" s="5">
+        <v>42.44</v>
+      </c>
+      <c r="D41" s="5">
+        <v>45.67</v>
+      </c>
+      <c r="E41" s="7">
+        <v>3.23</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5">
+      <c r="A42" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B39" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C39" s="6">
-        <v>28.65</v>
-      </c>
-      <c r="D39" s="6">
-        <v>35.49</v>
-      </c>
-      <c r="E39" s="7">
-        <v>6.84</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5">
-      <c r="A40" s="5" t="s">
+      <c r="B42" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C42" s="5">
+        <v>-15.75</v>
+      </c>
+      <c r="D42" s="5">
+        <v>38.67</v>
+      </c>
+      <c r="E42" s="7">
+        <v>54.42</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5">
+      <c r="A43" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B40" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C40" s="6">
-        <v>34.87</v>
-      </c>
-      <c r="D40" s="6">
-        <v>37.6</v>
-      </c>
-      <c r="E40" s="7">
-        <v>2.73</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5">
-      <c r="A41" s="5" t="s">
+      <c r="B43" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C43" s="5">
+        <v>-79.14</v>
+      </c>
+      <c r="D43" s="5">
+        <v>-59.11</v>
+      </c>
+      <c r="E43" s="7">
+        <v>20.03</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5">
+      <c r="A44" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B41" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C41" s="6">
-        <v>21.83</v>
-      </c>
-      <c r="D41" s="6">
-        <v>32.61</v>
-      </c>
-      <c r="E41" s="7">
-        <v>10.78</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5">
-      <c r="A42" s="5" t="s">
+      <c r="B44" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C44" s="5">
+        <v>-56.34</v>
+      </c>
+      <c r="D44" s="5">
+        <v>-28.21</v>
+      </c>
+      <c r="E44" s="7">
+        <v>28.13</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5">
+      <c r="A45" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="B42" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C42" s="6">
-        <v>28.54</v>
-      </c>
-      <c r="D42" s="6">
-        <v>37.65</v>
-      </c>
-      <c r="E42" s="7">
-        <v>9.109999999999999</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5">
-      <c r="A43" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B43" s="5" t="s">
+      <c r="B45" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="C43" s="6">
-        <v>1.05</v>
-      </c>
-      <c r="D43" s="6">
-        <v>-15.75</v>
-      </c>
-      <c r="E43" s="8">
-        <v>-16.8</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5">
-      <c r="A44" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B44" s="5" t="s">
+      <c r="C45" s="5">
+        <v>109</v>
+      </c>
+      <c r="D45" s="5">
+        <v>27.85</v>
+      </c>
+      <c r="E45" s="6">
+        <v>-81.15000000000001</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5">
+      <c r="A46" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B46" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="C44" s="6">
-        <v>-78.87</v>
-      </c>
-      <c r="D44" s="6">
-        <v>-79.14</v>
-      </c>
-      <c r="E44" s="8">
-        <v>-0.27</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5">
-      <c r="A45" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B45" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C45" s="6">
-        <v>-33.15</v>
-      </c>
-      <c r="D45" s="6">
-        <v>-56.34</v>
-      </c>
-      <c r="E45" s="8">
-        <v>-23.19</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5">
-      <c r="A46" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B46" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C46" s="6">
-        <v>120.56</v>
-      </c>
-      <c r="D46" s="6">
-        <v>109</v>
-      </c>
-      <c r="E46" s="8">
-        <v>-11.56</v>
-      </c>
-    </row>
-    <row r="47" spans="1:5">
-      <c r="A47" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B47" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C47" s="6">
-        <v>-35.22</v>
-      </c>
-      <c r="D47" s="6">
+      <c r="C46" s="5">
         <v>-27.62</v>
       </c>
-      <c r="E47" s="7">
-        <v>7.6</v>
+      <c r="D46" s="5">
+        <v>-14.03</v>
+      </c>
+      <c r="E46" s="7">
+        <v>13.59</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A9:E9"/>
+    <mergeCell ref="A5:E5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2454,60 +2335,60 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="28" customHeight="1">
-      <c r="A1" s="9" t="s">
+      <c r="A1" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="9" t="s">
-        <v>71</v>
-      </c>
-      <c r="C1" s="9" t="s">
-        <v>72</v>
-      </c>
-      <c r="D1" s="9" t="s">
-        <v>73</v>
-      </c>
-      <c r="E1" s="9" t="s">
-        <v>74</v>
-      </c>
-      <c r="F1" s="9" t="s">
-        <v>75</v>
-      </c>
-      <c r="G1" s="9" t="s">
-        <v>76</v>
-      </c>
-      <c r="H1" s="9" t="s">
-        <v>77</v>
-      </c>
-      <c r="I1" s="9" t="s">
-        <v>78</v>
+      <c r="B1" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="C1" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="D1" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="E1" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="F1" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="G1" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="H1" s="8" t="s">
+        <v>59</v>
+      </c>
+      <c r="I1" s="8" t="s">
+        <v>60</v>
       </c>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="10" t="s">
+      <c r="A2" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="B2" s="11">
+      <c r="B2" s="10">
         <v>41.92</v>
       </c>
-      <c r="C2" s="12">
+      <c r="C2" s="11">
         <v>5</v>
       </c>
-      <c r="D2" s="11">
-        <v>37.2</v>
-      </c>
-      <c r="E2" s="11">
+      <c r="D2" s="10">
+        <v>38.9</v>
+      </c>
+      <c r="E2" s="10">
         <v>20</v>
       </c>
-      <c r="F2" s="11">
-        <v>-11.7</v>
-      </c>
-      <c r="G2" s="11">
-        <v>-8.199999999999999</v>
-      </c>
-      <c r="H2" s="11">
+      <c r="F2" s="10">
+        <v>-10.7</v>
+      </c>
+      <c r="G2" s="10">
+        <v>-8</v>
+      </c>
+      <c r="H2" s="10">
         <v>59.8</v>
       </c>
-      <c r="I2" s="11">
+      <c r="I2" s="10">
         <v>20</v>
       </c>
     </row>
@@ -2609,37 +2490,37 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
-      <c r="A1" s="13" t="s">
+      <c r="A1" s="12" t="s">
         <v>37</v>
       </c>
-      <c r="B1" s="13" t="s">
+      <c r="B1" s="12" t="s">
         <v>38</v>
       </c>
-      <c r="C1" s="13" t="s">
+      <c r="C1" s="12" t="s">
         <v>41</v>
       </c>
-      <c r="D1" s="13" t="s">
+      <c r="D1" s="12" t="s">
         <v>40</v>
       </c>
-      <c r="E1" s="13" t="s">
+      <c r="E1" s="12" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="2" spans="1:5">
-      <c r="A2" s="14">
-        <v>0.1738</v>
-      </c>
-      <c r="B2" s="14">
-        <v>0.008100000000000001</v>
-      </c>
-      <c r="C2" s="14">
-        <v>0.0039</v>
-      </c>
-      <c r="D2" s="14">
-        <v>-0.0526</v>
-      </c>
-      <c r="E2" s="14">
-        <v>-0.2261</v>
+      <c r="A2" s="13">
+        <v>0.1727</v>
+      </c>
+      <c r="B2" s="13">
+        <v>0.0144</v>
+      </c>
+      <c r="C2" s="13">
+        <v>0.006999999999999999</v>
+      </c>
+      <c r="D2" s="13">
+        <v>-0.0591</v>
+      </c>
+      <c r="E2" s="13">
+        <v>-0.2243</v>
       </c>
     </row>
   </sheetData>

--- a/HINDUJA_GROUP_Technical_Metrics.xlsx
+++ b/HINDUJA_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="207" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="230" uniqueCount="68">
   <si>
     <t>Symbol</t>
   </si>
@@ -163,7 +163,28 @@
     <t>▶  SIGNAL EVENTS (vs Previous Run)</t>
   </si>
   <si>
-    <t>No signal events detected since last run.</t>
+    <t>Signal</t>
+  </si>
+  <si>
+    <t>Change</t>
+  </si>
+  <si>
+    <t>Direction</t>
+  </si>
+  <si>
+    <t>Prev Value</t>
+  </si>
+  <si>
+    <t>Curr Value</t>
+  </si>
+  <si>
+    <t>Yes → No</t>
+  </si>
+  <si>
+    <t>🔴 BEARISH</t>
+  </si>
+  <si>
+    <t>20 DMA &gt; 50 DMA</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -365,17 +386,18 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -888,10 +910,10 @@
         <v>42</v>
       </c>
       <c r="C2">
-        <v>145</v>
+        <v>148.18</v>
       </c>
       <c r="D2">
-        <v>-1.61</v>
+        <v>2.19</v>
       </c>
       <c r="E2">
         <v>208.37</v>
@@ -900,46 +922,46 @@
         <v>131.36</v>
       </c>
       <c r="G2">
-        <v>-30.41</v>
+        <v>-28.89</v>
       </c>
       <c r="H2">
-        <v>10.38</v>
+        <v>12.8</v>
       </c>
       <c r="I2">
-        <v>-2.82</v>
+        <v>2.18</v>
       </c>
       <c r="J2">
-        <v>-11.45</v>
+        <v>-5.41</v>
       </c>
       <c r="K2">
-        <v>-7.36</v>
+        <v>-4.32</v>
       </c>
       <c r="L2">
-        <v>7.09</v>
+        <v>10.31</v>
       </c>
       <c r="M2">
-        <v>17.27</v>
+        <v>17.82</v>
       </c>
       <c r="N2">
-        <v>79</v>
+        <v>99</v>
       </c>
       <c r="O2">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="P2">
-        <v>145.34</v>
+        <v>145.97</v>
       </c>
       <c r="Q2">
-        <v>153.77</v>
+        <v>153.35</v>
       </c>
       <c r="R2">
-        <v>165.03</v>
+        <v>164.55</v>
       </c>
       <c r="S2">
-        <v>169.02</v>
+        <v>168.9</v>
       </c>
       <c r="T2">
-        <v>-14.21</v>
+        <v>-12.27</v>
       </c>
       <c r="U2" t="s">
         <v>43</v>
@@ -954,34 +976,34 @@
         <v>0</v>
       </c>
       <c r="Y2">
-        <v>32.91</v>
+        <v>39.28</v>
       </c>
       <c r="Z2">
-        <v>-5.41</v>
+        <v>-5.12</v>
       </c>
       <c r="AA2">
-        <v>-4.77</v>
+        <v>-4.84</v>
       </c>
       <c r="AB2">
-        <v>-0.63</v>
+        <v>-0.28</v>
       </c>
       <c r="AC2">
-        <v>26.2</v>
+        <v>55.99</v>
       </c>
       <c r="AD2">
-        <v>13.61</v>
+        <v>32.22</v>
       </c>
       <c r="AE2">
-        <v>4.01</v>
+        <v>4.14</v>
       </c>
       <c r="AF2">
-        <v>38.67</v>
+        <v>72</v>
       </c>
       <c r="AG2">
-        <v>166.33</v>
+        <v>166.08</v>
       </c>
       <c r="AH2">
-        <v>141.22</v>
+        <v>140.63</v>
       </c>
       <c r="AI2">
         <v>157.56</v>
@@ -990,7 +1012,7 @@
         <v>45</v>
       </c>
       <c r="AK2">
-        <v>63.69</v>
+        <v>58.31</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1001,10 +1023,10 @@
         <v>42</v>
       </c>
       <c r="C3">
-        <v>367</v>
+        <v>362.2</v>
       </c>
       <c r="D3">
-        <v>3.53</v>
+        <v>-1.31</v>
       </c>
       <c r="E3">
         <v>456.15</v>
@@ -1013,46 +1035,46 @@
         <v>225</v>
       </c>
       <c r="G3">
-        <v>-19.54</v>
+        <v>-20.6</v>
       </c>
       <c r="H3">
-        <v>63.11</v>
+        <v>60.98</v>
       </c>
       <c r="I3">
-        <v>-0.23</v>
+        <v>1.29</v>
       </c>
       <c r="J3">
-        <v>-16.88</v>
+        <v>-16.86</v>
       </c>
       <c r="K3">
-        <v>-8.99</v>
+        <v>-10.11</v>
       </c>
       <c r="L3">
-        <v>3.98</v>
+        <v>3.13</v>
       </c>
       <c r="M3">
-        <v>1.44</v>
+        <v>1.66</v>
       </c>
       <c r="N3">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="O3">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="P3">
-        <v>357.15</v>
+        <v>358.07</v>
       </c>
       <c r="Q3">
-        <v>384.14</v>
+        <v>380.83</v>
       </c>
       <c r="R3">
-        <v>401.86</v>
+        <v>400.87</v>
       </c>
       <c r="S3">
-        <v>340.59</v>
+        <v>340.95</v>
       </c>
       <c r="T3">
-        <v>7.75</v>
+        <v>6.23</v>
       </c>
       <c r="U3" t="s">
         <v>43</v>
@@ -1067,34 +1089,34 @@
         <v>2</v>
       </c>
       <c r="Y3">
-        <v>43.53</v>
+        <v>41.89</v>
       </c>
       <c r="Z3">
-        <v>-15.15</v>
+        <v>-14.41</v>
       </c>
       <c r="AA3">
-        <v>-13.64</v>
+        <v>-13.79</v>
       </c>
       <c r="AB3">
-        <v>-1.51</v>
+        <v>-0.61</v>
       </c>
       <c r="AC3">
-        <v>66.11</v>
+        <v>84.92</v>
       </c>
       <c r="AD3">
-        <v>43.63</v>
+        <v>63.65</v>
       </c>
       <c r="AE3">
-        <v>17.14</v>
+        <v>16.52</v>
       </c>
       <c r="AF3">
-        <v>-59.11</v>
+        <v>-86.95999999999999</v>
       </c>
       <c r="AG3">
-        <v>455.39</v>
+        <v>449.52</v>
       </c>
       <c r="AH3">
-        <v>312.89</v>
+        <v>312.13</v>
       </c>
       <c r="AI3">
         <v>401.23</v>
@@ -1103,7 +1125,7 @@
         <v>45</v>
       </c>
       <c r="AK3">
-        <v>39.27</v>
+        <v>35.54</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1114,10 +1136,10 @@
         <v>42</v>
       </c>
       <c r="C4">
-        <v>361.85</v>
+        <v>357.8</v>
       </c>
       <c r="D4">
-        <v>0.91</v>
+        <v>-1.12</v>
       </c>
       <c r="E4">
         <v>534</v>
@@ -1126,46 +1148,46 @@
         <v>344.7</v>
       </c>
       <c r="G4">
-        <v>-32.24</v>
+        <v>-33</v>
       </c>
       <c r="H4">
-        <v>4.98</v>
+        <v>3.8</v>
       </c>
       <c r="I4">
         <v>-0.32</v>
       </c>
       <c r="J4">
-        <v>-5.14</v>
+        <v>-6.24</v>
       </c>
       <c r="K4">
-        <v>-18.83</v>
+        <v>-18.15</v>
       </c>
       <c r="L4">
-        <v>-26.88</v>
+        <v>-27.64</v>
       </c>
       <c r="M4">
-        <v>-22.43</v>
+        <v>-22.61</v>
       </c>
       <c r="N4">
         <v>21</v>
       </c>
       <c r="O4">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="P4">
-        <v>357.38</v>
+        <v>357.15</v>
       </c>
       <c r="Q4">
-        <v>369.53</v>
+        <v>368.12</v>
       </c>
       <c r="R4">
-        <v>389.46</v>
+        <v>388.18</v>
       </c>
       <c r="S4">
-        <v>403.79</v>
+        <v>403.33</v>
       </c>
       <c r="T4">
-        <v>-10.39</v>
+        <v>-11.29</v>
       </c>
       <c r="U4" t="s">
         <v>43</v>
@@ -1180,34 +1202,34 @@
         <v>0</v>
       </c>
       <c r="Y4">
-        <v>37.17</v>
+        <v>34.08</v>
       </c>
       <c r="Z4">
-        <v>-9.41</v>
+        <v>-9.15</v>
       </c>
       <c r="AA4">
-        <v>-9.449999999999999</v>
+        <v>-9.390000000000001</v>
       </c>
       <c r="AB4">
-        <v>0.04</v>
+        <v>0.24</v>
       </c>
       <c r="AC4">
-        <v>66.67</v>
+        <v>93.28</v>
       </c>
       <c r="AD4">
-        <v>34.98</v>
+        <v>64.43000000000001</v>
       </c>
       <c r="AE4">
         <v>9.9</v>
       </c>
       <c r="AF4">
-        <v>-28.21</v>
+        <v>35.31</v>
       </c>
       <c r="AG4">
-        <v>389.69</v>
+        <v>387.35</v>
       </c>
       <c r="AH4">
-        <v>349.37</v>
+        <v>348.89</v>
       </c>
       <c r="AI4">
         <v>384.24</v>
@@ -1216,7 +1238,7 @@
         <v>45</v>
       </c>
       <c r="AK4">
-        <v>54.34</v>
+        <v>52.12</v>
       </c>
     </row>
     <row r="5" spans="1:37">
@@ -1227,10 +1249,10 @@
         <v>42</v>
       </c>
       <c r="C5">
-        <v>866</v>
+        <v>885.4</v>
       </c>
       <c r="D5">
-        <v>-1.29</v>
+        <v>2.24</v>
       </c>
       <c r="E5">
         <v>1069.3</v>
@@ -1239,46 +1261,46 @@
         <v>739.5</v>
       </c>
       <c r="G5">
-        <v>-19.01</v>
+        <v>-17.2</v>
       </c>
       <c r="H5">
-        <v>17.11</v>
+        <v>19.73</v>
       </c>
       <c r="I5">
-        <v>-1.02</v>
+        <v>2.48</v>
       </c>
       <c r="J5">
-        <v>-11.47</v>
+        <v>-7.43</v>
       </c>
       <c r="K5">
-        <v>-14.23</v>
+        <v>-12.64</v>
       </c>
       <c r="L5">
-        <v>15.6</v>
+        <v>15.99</v>
       </c>
       <c r="M5">
-        <v>-5.91</v>
+        <v>-5.65</v>
       </c>
       <c r="N5">
-        <v>99</v>
+        <v>79</v>
       </c>
       <c r="O5">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="P5">
-        <v>864.4</v>
+        <v>868.6799999999999</v>
       </c>
       <c r="Q5">
-        <v>906.9299999999999</v>
+        <v>903.87</v>
       </c>
       <c r="R5">
-        <v>966.99</v>
+        <v>964.1799999999999</v>
       </c>
       <c r="S5">
-        <v>925.14</v>
+        <v>925.3200000000001</v>
       </c>
       <c r="T5">
-        <v>-6.39</v>
+        <v>-4.31</v>
       </c>
       <c r="U5" t="s">
         <v>43</v>
@@ -1293,34 +1315,34 @@
         <v>1</v>
       </c>
       <c r="Y5">
-        <v>35.38</v>
+        <v>41.82</v>
       </c>
       <c r="Z5">
-        <v>-30.8</v>
+        <v>-28.47</v>
       </c>
       <c r="AA5">
-        <v>-29.14</v>
+        <v>-29</v>
       </c>
       <c r="AB5">
-        <v>-1.67</v>
+        <v>0.54</v>
       </c>
       <c r="AC5">
-        <v>64.58</v>
+        <v>88.19</v>
       </c>
       <c r="AD5">
-        <v>49.88</v>
+        <v>67.66</v>
       </c>
       <c r="AE5">
-        <v>22.43</v>
+        <v>22.78</v>
       </c>
       <c r="AF5">
-        <v>27.85</v>
+        <v>-27.2</v>
       </c>
       <c r="AG5">
-        <v>982.9299999999999</v>
+        <v>978.0700000000001</v>
       </c>
       <c r="AH5">
-        <v>830.9299999999999</v>
+        <v>829.6799999999999</v>
       </c>
       <c r="AI5">
         <v>921.99</v>
@@ -1329,7 +1351,7 @@
         <v>45</v>
       </c>
       <c r="AK5">
-        <v>54.78</v>
+        <v>49.64</v>
       </c>
     </row>
     <row r="6" spans="1:37">
@@ -1340,10 +1362,10 @@
         <v>42</v>
       </c>
       <c r="C6">
-        <v>2.61</v>
+        <v>2.57</v>
       </c>
       <c r="D6">
-        <v>1.16</v>
+        <v>-1.53</v>
       </c>
       <c r="E6">
         <v>3.38</v>
@@ -1352,61 +1374,61 @@
         <v>1.84</v>
       </c>
       <c r="G6">
-        <v>-22.78</v>
+        <v>-23.96</v>
       </c>
       <c r="H6">
-        <v>41.85</v>
+        <v>39.67</v>
       </c>
       <c r="I6">
-        <v>0.38</v>
+        <v>-0.39</v>
       </c>
       <c r="J6">
-        <v>-8.74</v>
+        <v>-6.55</v>
       </c>
       <c r="K6">
-        <v>9.66</v>
+        <v>6.64</v>
       </c>
       <c r="L6">
-        <v>-18.18</v>
+        <v>-20.19</v>
       </c>
       <c r="M6">
-        <v>0.7</v>
+        <v>0.39</v>
       </c>
       <c r="N6">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="O6">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="P6">
-        <v>2.59</v>
+        <v>2.58</v>
       </c>
       <c r="Q6">
+        <v>2.65</v>
+      </c>
+      <c r="R6">
         <v>2.66</v>
-      </c>
-      <c r="R6">
-        <v>2.65</v>
       </c>
       <c r="S6">
         <v>2.64</v>
       </c>
       <c r="T6">
-        <v>-1.18</v>
+        <v>-2.62</v>
       </c>
       <c r="U6" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="V6" t="s">
         <v>44</v>
       </c>
       <c r="W6" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="X6">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y6">
-        <v>45.67</v>
+        <v>42.27</v>
       </c>
       <c r="Z6">
         <v>-0.04</v>
@@ -1418,31 +1440,31 @@
         <v>-0.01</v>
       </c>
       <c r="AC6">
-        <v>55.44</v>
+        <v>61.83</v>
       </c>
       <c r="AD6">
-        <v>39.65</v>
+        <v>49.93</v>
       </c>
       <c r="AE6">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="AF6">
-        <v>-14.03</v>
+        <v>8.19</v>
       </c>
       <c r="AG6">
-        <v>2.86</v>
+        <v>2.82</v>
       </c>
       <c r="AH6">
-        <v>2.46</v>
+        <v>2.47</v>
       </c>
       <c r="AI6">
-        <v>2.93</v>
+        <v>2.92</v>
       </c>
       <c r="AJ6" t="s">
         <v>45</v>
       </c>
       <c r="AK6">
-        <v>28.49</v>
+        <v>27.97</v>
       </c>
     </row>
   </sheetData>
@@ -1583,7 +1605,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F46"/>
+  <dimension ref="A1:F50"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.7109375" customWidth="1"/>
@@ -1603,719 +1625,825 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="3" t="s">
         <v>47</v>
       </c>
-    </row>
-    <row r="5" spans="1:6">
-      <c r="A5" s="2" t="s">
+      <c r="C2" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="B5" s="2"/>
-      <c r="C5" s="2"/>
-      <c r="D5" s="2"/>
-      <c r="E5" s="2"/>
+      <c r="D2" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
+      <c r="A3" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6">
+      <c r="A4" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="F4" s="4" t="s">
+        <v>43</v>
+      </c>
     </row>
     <row r="6" spans="1:6">
-      <c r="A6" s="4" t="s">
-        <v>0</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>49</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="D6" s="4" t="s">
-        <v>51</v>
-      </c>
-      <c r="E6" s="4" t="s">
-        <v>52</v>
-      </c>
+      <c r="A6" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="B6" s="2"/>
+      <c r="C6" s="2"/>
+      <c r="D6" s="2"/>
+      <c r="E6" s="2"/>
     </row>
     <row r="7" spans="1:6">
       <c r="A7" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6">
+      <c r="A8" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B7" s="3" t="s">
+      <c r="B8" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C7" s="5">
-        <v>-11.29</v>
-      </c>
-      <c r="D7" s="5">
+      <c r="C8" s="6">
         <v>-11.45</v>
       </c>
-      <c r="E7" s="6">
-        <v>-0.16</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6">
-      <c r="A8" s="3" t="s">
+      <c r="D8" s="6">
+        <v>-5.41</v>
+      </c>
+      <c r="E8" s="7">
+        <v>6.04</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="A9" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B8" s="3" t="s">
+      <c r="B9" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C8" s="5">
-        <v>-17.98</v>
-      </c>
-      <c r="D8" s="5">
+      <c r="C9" s="6">
         <v>-16.88</v>
       </c>
-      <c r="E8" s="7">
-        <v>1.1</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
-      <c r="A9" s="3" t="s">
+      <c r="D9" s="6">
+        <v>-16.86</v>
+      </c>
+      <c r="E9" s="7">
+        <v>0.02</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="A10" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B9" s="3" t="s">
+      <c r="B10" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C9" s="5">
-        <v>-6.58</v>
-      </c>
-      <c r="D9" s="5">
+      <c r="C10" s="6">
         <v>-5.14</v>
       </c>
-      <c r="E9" s="7">
-        <v>1.44</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
-      <c r="A10" s="3" t="s">
+      <c r="D10" s="6">
+        <v>-6.24</v>
+      </c>
+      <c r="E10" s="8">
+        <v>-1.1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="A11" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="B10" s="3" t="s">
+      <c r="B11" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C10" s="5">
-        <v>-11.67</v>
-      </c>
-      <c r="D10" s="5">
+      <c r="C11" s="6">
         <v>-11.47</v>
       </c>
-      <c r="E10" s="7">
-        <v>0.2</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
-      <c r="A11" s="3" t="s">
+      <c r="D11" s="6">
+        <v>-7.43</v>
+      </c>
+      <c r="E11" s="7">
+        <v>4.04</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6">
+      <c r="A12" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B11" s="3" t="s">
+      <c r="B12" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C11" s="5">
-        <v>-11.03</v>
-      </c>
-      <c r="D11" s="5">
+      <c r="C12" s="6">
         <v>-8.74</v>
       </c>
-      <c r="E11" s="7">
-        <v>2.29</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
-      <c r="A12" s="3" t="s">
+      <c r="D12" s="6">
+        <v>-6.55</v>
+      </c>
+      <c r="E12" s="7">
+        <v>2.19</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6">
+      <c r="A13" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B12" s="3" t="s">
+      <c r="B13" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="C12" s="5">
-        <v>-4.12</v>
-      </c>
-      <c r="D12" s="5">
+      <c r="C13" s="6">
         <v>-2.82</v>
       </c>
-      <c r="E12" s="7">
-        <v>1.3</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
-      <c r="A13" s="3" t="s">
+      <c r="D13" s="6">
+        <v>2.18</v>
+      </c>
+      <c r="E13" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6">
+      <c r="A14" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B13" s="3" t="s">
+      <c r="B14" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="C13" s="5">
-        <v>-4.82</v>
-      </c>
-      <c r="D13" s="5">
+      <c r="C14" s="6">
         <v>-0.23</v>
       </c>
-      <c r="E13" s="7">
-        <v>4.59</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
-      <c r="A14" s="3" t="s">
+      <c r="D14" s="6">
+        <v>1.29</v>
+      </c>
+      <c r="E14" s="7">
+        <v>1.52</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6">
+      <c r="A15" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B15" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C15" s="6">
+        <v>-1.02</v>
+      </c>
+      <c r="D15" s="6">
+        <v>2.48</v>
+      </c>
+      <c r="E15" s="7">
+        <v>3.5</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6">
+      <c r="A16" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B16" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C16" s="6">
+        <v>0.38</v>
+      </c>
+      <c r="D16" s="6">
+        <v>-0.39</v>
+      </c>
+      <c r="E16" s="8">
+        <v>-0.77</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B17" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C17" s="6">
+        <v>7.09</v>
+      </c>
+      <c r="D17" s="6">
+        <v>10.31</v>
+      </c>
+      <c r="E17" s="7">
+        <v>3.22</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B18" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C18" s="6">
+        <v>3.98</v>
+      </c>
+      <c r="D18" s="6">
+        <v>3.13</v>
+      </c>
+      <c r="E18" s="8">
+        <v>-0.85</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C14" s="5">
-        <v>-0.77</v>
-      </c>
-      <c r="D14" s="5">
-        <v>-0.32</v>
-      </c>
-      <c r="E14" s="7">
-        <v>0.45</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6">
-      <c r="A15" s="3" t="s">
+      <c r="B19" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C19" s="6">
+        <v>-26.88</v>
+      </c>
+      <c r="D19" s="6">
+        <v>-27.64</v>
+      </c>
+      <c r="E19" s="8">
+        <v>-0.76</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="B15" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C15" s="5">
-        <v>-3.17</v>
-      </c>
-      <c r="D15" s="5">
-        <v>-1.02</v>
-      </c>
-      <c r="E15" s="7">
-        <v>2.15</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
-      <c r="A16" s="3" t="s">
+      <c r="B20" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C20" s="6">
+        <v>15.6</v>
+      </c>
+      <c r="D20" s="6">
+        <v>15.99</v>
+      </c>
+      <c r="E20" s="7">
+        <v>0.39</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B16" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C16" s="5">
-        <v>0.39</v>
-      </c>
-      <c r="D16" s="5">
-        <v>0.38</v>
-      </c>
-      <c r="E16" s="6">
-        <v>-0.01</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5">
-      <c r="A17" s="3" t="s">
+      <c r="B21" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C21" s="6">
+        <v>-18.18</v>
+      </c>
+      <c r="D21" s="6">
+        <v>-20.19</v>
+      </c>
+      <c r="E21" s="8">
+        <v>-2.01</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B17" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C17" s="5">
-        <v>8.27</v>
-      </c>
-      <c r="D17" s="5">
-        <v>7.09</v>
-      </c>
-      <c r="E17" s="6">
+      <c r="B22" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C22" s="6">
+        <v>-7.36</v>
+      </c>
+      <c r="D22" s="6">
+        <v>-4.32</v>
+      </c>
+      <c r="E22" s="7">
+        <v>3.04</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B23" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C23" s="6">
+        <v>-8.99</v>
+      </c>
+      <c r="D23" s="6">
+        <v>-10.11</v>
+      </c>
+      <c r="E23" s="8">
+        <v>-1.12</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5">
+      <c r="A24" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B24" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C24" s="6">
+        <v>-18.83</v>
+      </c>
+      <c r="D24" s="6">
+        <v>-18.15</v>
+      </c>
+      <c r="E24" s="7">
+        <v>0.68</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5">
+      <c r="A25" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B25" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C25" s="6">
+        <v>-14.23</v>
+      </c>
+      <c r="D25" s="6">
+        <v>-12.64</v>
+      </c>
+      <c r="E25" s="7">
+        <v>1.59</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
+      <c r="A26" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B26" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C26" s="6">
+        <v>9.66</v>
+      </c>
+      <c r="D26" s="6">
+        <v>6.64</v>
+      </c>
+      <c r="E26" s="8">
+        <v>-3.02</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5">
+      <c r="A27" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B27" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C27" s="6">
+        <v>-30.41</v>
+      </c>
+      <c r="D27" s="6">
+        <v>-28.89</v>
+      </c>
+      <c r="E27" s="7">
+        <v>1.52</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5">
+      <c r="A28" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B28" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C28" s="6">
+        <v>-19.54</v>
+      </c>
+      <c r="D28" s="6">
+        <v>-20.6</v>
+      </c>
+      <c r="E28" s="8">
+        <v>-1.06</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5">
+      <c r="A29" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B29" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C29" s="6">
+        <v>-32.24</v>
+      </c>
+      <c r="D29" s="6">
+        <v>-33</v>
+      </c>
+      <c r="E29" s="8">
+        <v>-0.76</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5">
+      <c r="A30" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B30" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C30" s="6">
+        <v>-19.01</v>
+      </c>
+      <c r="D30" s="6">
+        <v>-17.2</v>
+      </c>
+      <c r="E30" s="7">
+        <v>1.81</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5">
+      <c r="A31" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B31" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C31" s="6">
+        <v>-22.78</v>
+      </c>
+      <c r="D31" s="6">
+        <v>-23.96</v>
+      </c>
+      <c r="E31" s="8">
         <v>-1.18</v>
       </c>
     </row>
-    <row r="18" spans="1:5">
-      <c r="A18" s="3" t="s">
+    <row r="32" spans="1:5">
+      <c r="A32" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B32" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C32" s="6">
+        <v>145</v>
+      </c>
+      <c r="D32" s="6">
+        <v>148.18</v>
+      </c>
+      <c r="E32" s="7">
+        <v>3.18</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5">
+      <c r="A33" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B18" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C18" s="5">
-        <v>1.78</v>
-      </c>
-      <c r="D18" s="5">
-        <v>3.98</v>
-      </c>
-      <c r="E18" s="7">
-        <v>2.2</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5">
-      <c r="A19" s="3" t="s">
+      <c r="B33" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C33" s="6">
+        <v>367</v>
+      </c>
+      <c r="D33" s="6">
+        <v>362.2</v>
+      </c>
+      <c r="E33" s="8">
+        <v>-4.8</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5">
+      <c r="A34" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B19" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C19" s="5">
-        <v>-26.96</v>
-      </c>
-      <c r="D19" s="5">
-        <v>-26.88</v>
-      </c>
-      <c r="E19" s="7">
-        <v>0.08</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5">
-      <c r="A20" s="3" t="s">
+      <c r="B34" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C34" s="6">
+        <v>361.85</v>
+      </c>
+      <c r="D34" s="6">
+        <v>357.8</v>
+      </c>
+      <c r="E34" s="8">
+        <v>-4.05</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5">
+      <c r="A35" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="B20" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C20" s="5">
-        <v>18.41</v>
-      </c>
-      <c r="D20" s="5">
-        <v>15.6</v>
-      </c>
-      <c r="E20" s="6">
-        <v>-2.81</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5">
-      <c r="A21" s="3" t="s">
+      <c r="B35" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C35" s="6">
+        <v>866</v>
+      </c>
+      <c r="D35" s="6">
+        <v>885.4</v>
+      </c>
+      <c r="E35" s="7">
+        <v>19.4</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5">
+      <c r="A36" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B21" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C21" s="5">
-        <v>-19.38</v>
-      </c>
-      <c r="D21" s="5">
-        <v>-18.18</v>
-      </c>
-      <c r="E21" s="7">
-        <v>1.2</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5">
-      <c r="A22" s="3" t="s">
+      <c r="B36" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C36" s="6">
+        <v>2.61</v>
+      </c>
+      <c r="D36" s="6">
+        <v>2.57</v>
+      </c>
+      <c r="E36" s="8">
+        <v>-0.04</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5">
+      <c r="A37" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B22" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C22" s="5">
-        <v>-5.04</v>
-      </c>
-      <c r="D22" s="5">
-        <v>-7.36</v>
-      </c>
-      <c r="E22" s="6">
-        <v>-2.32</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5">
-      <c r="A23" s="3" t="s">
+      <c r="B37" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C37" s="6">
+        <v>79</v>
+      </c>
+      <c r="D37" s="6">
+        <v>99</v>
+      </c>
+      <c r="E37" s="7">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5">
+      <c r="A38" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B23" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C23" s="5">
-        <v>-12.12</v>
-      </c>
-      <c r="D23" s="5">
-        <v>-8.99</v>
-      </c>
-      <c r="E23" s="7">
-        <v>3.13</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5">
-      <c r="A24" s="3" t="s">
+      <c r="B38" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C38" s="6">
+        <v>40</v>
+      </c>
+      <c r="D38" s="6">
+        <v>60</v>
+      </c>
+      <c r="E38" s="7">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5">
+      <c r="A39" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B39" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C39" s="6">
+        <v>99</v>
+      </c>
+      <c r="D39" s="6">
+        <v>79</v>
+      </c>
+      <c r="E39" s="8">
+        <v>-20</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5">
+      <c r="A40" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B40" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C40" s="6">
+        <v>60</v>
+      </c>
+      <c r="D40" s="6">
+        <v>40</v>
+      </c>
+      <c r="E40" s="8">
+        <v>-20</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5">
+      <c r="A41" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B41" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C41" s="6">
+        <v>32.91</v>
+      </c>
+      <c r="D41" s="6">
+        <v>39.28</v>
+      </c>
+      <c r="E41" s="7">
+        <v>6.37</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5">
+      <c r="A42" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B42" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C42" s="6">
+        <v>43.53</v>
+      </c>
+      <c r="D42" s="6">
+        <v>41.89</v>
+      </c>
+      <c r="E42" s="8">
+        <v>-1.64</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5">
+      <c r="A43" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B24" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C24" s="5">
-        <v>-20.94</v>
-      </c>
-      <c r="D24" s="5">
-        <v>-18.83</v>
-      </c>
-      <c r="E24" s="7">
-        <v>2.11</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5">
-      <c r="A25" s="3" t="s">
+      <c r="B43" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C43" s="6">
+        <v>37.17</v>
+      </c>
+      <c r="D43" s="6">
+        <v>34.08</v>
+      </c>
+      <c r="E43" s="8">
+        <v>-3.09</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5">
+      <c r="A44" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="B25" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C25" s="5">
-        <v>-12.03</v>
-      </c>
-      <c r="D25" s="5">
-        <v>-14.23</v>
-      </c>
-      <c r="E25" s="6">
-        <v>-2.2</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5">
-      <c r="A26" s="3" t="s">
+      <c r="B44" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C44" s="6">
+        <v>35.38</v>
+      </c>
+      <c r="D44" s="6">
+        <v>41.82</v>
+      </c>
+      <c r="E44" s="7">
+        <v>6.44</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5">
+      <c r="A45" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B26" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C26" s="5">
-        <v>9.32</v>
-      </c>
-      <c r="D26" s="5">
-        <v>9.66</v>
-      </c>
-      <c r="E26" s="7">
-        <v>0.34</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5">
-      <c r="A27" s="3" t="s">
+      <c r="B45" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C45" s="6">
+        <v>45.67</v>
+      </c>
+      <c r="D45" s="6">
+        <v>42.27</v>
+      </c>
+      <c r="E45" s="8">
+        <v>-3.4</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5">
+      <c r="A46" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B27" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C27" s="5">
-        <v>-29.27</v>
-      </c>
-      <c r="D27" s="5">
-        <v>-30.41</v>
-      </c>
-      <c r="E27" s="6">
-        <v>-1.14</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5">
-      <c r="A28" s="3" t="s">
+      <c r="B46" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C46" s="6">
+        <v>38.67</v>
+      </c>
+      <c r="D46" s="6">
+        <v>72</v>
+      </c>
+      <c r="E46" s="7">
+        <v>33.33</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5">
+      <c r="A47" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B28" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C28" s="5">
-        <v>-22.28</v>
-      </c>
-      <c r="D28" s="5">
-        <v>-19.54</v>
-      </c>
-      <c r="E28" s="7">
-        <v>2.74</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5">
-      <c r="A29" s="3" t="s">
+      <c r="B47" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C47" s="6">
+        <v>-59.11</v>
+      </c>
+      <c r="D47" s="6">
+        <v>-86.95999999999999</v>
+      </c>
+      <c r="E47" s="8">
+        <v>-27.85</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5">
+      <c r="A48" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B29" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C29" s="5">
-        <v>-32.85</v>
-      </c>
-      <c r="D29" s="5">
-        <v>-32.24</v>
-      </c>
-      <c r="E29" s="7">
-        <v>0.61</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5">
-      <c r="A30" s="3" t="s">
+      <c r="B48" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C48" s="6">
+        <v>-28.21</v>
+      </c>
+      <c r="D48" s="6">
+        <v>35.31</v>
+      </c>
+      <c r="E48" s="7">
+        <v>63.52</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5">
+      <c r="A49" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="B30" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C30" s="5">
-        <v>-17.95</v>
-      </c>
-      <c r="D30" s="5">
-        <v>-19.01</v>
-      </c>
-      <c r="E30" s="6">
-        <v>-1.06</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5">
-      <c r="A31" s="3" t="s">
+      <c r="B49" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C49" s="6">
+        <v>27.85</v>
+      </c>
+      <c r="D49" s="6">
+        <v>-27.2</v>
+      </c>
+      <c r="E49" s="8">
+        <v>-55.05</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5">
+      <c r="A50" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B31" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C31" s="5">
-        <v>-23.67</v>
-      </c>
-      <c r="D31" s="5">
-        <v>-22.78</v>
-      </c>
-      <c r="E31" s="7">
-        <v>0.89</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5">
-      <c r="A32" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B32" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C32" s="5">
-        <v>147.37</v>
-      </c>
-      <c r="D32" s="5">
-        <v>145</v>
-      </c>
-      <c r="E32" s="6">
-        <v>-2.37</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5">
-      <c r="A33" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="B33" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C33" s="5">
-        <v>354.5</v>
-      </c>
-      <c r="D33" s="5">
-        <v>367</v>
-      </c>
-      <c r="E33" s="7">
-        <v>12.5</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5">
-      <c r="A34" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="B34" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C34" s="5">
-        <v>358.6</v>
-      </c>
-      <c r="D34" s="5">
-        <v>361.85</v>
-      </c>
-      <c r="E34" s="7">
-        <v>3.25</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5">
-      <c r="A35" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="B35" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C35" s="5">
-        <v>877.35</v>
-      </c>
-      <c r="D35" s="5">
-        <v>866</v>
-      </c>
-      <c r="E35" s="6">
-        <v>-11.35</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5">
-      <c r="A36" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="B36" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C36" s="5">
-        <v>2.58</v>
-      </c>
-      <c r="D36" s="5">
-        <v>2.61</v>
-      </c>
-      <c r="E36" s="7">
-        <v>0.03</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5">
-      <c r="A37" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B37" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C37" s="5">
-        <v>35.49</v>
-      </c>
-      <c r="D37" s="5">
-        <v>32.91</v>
-      </c>
-      <c r="E37" s="6">
-        <v>-2.58</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5">
-      <c r="A38" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="B38" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C38" s="5">
-        <v>37.6</v>
-      </c>
-      <c r="D38" s="5">
-        <v>43.53</v>
-      </c>
-      <c r="E38" s="7">
-        <v>5.93</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5">
-      <c r="A39" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="B39" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C39" s="5">
-        <v>32.61</v>
-      </c>
-      <c r="D39" s="5">
-        <v>37.17</v>
-      </c>
-      <c r="E39" s="7">
-        <v>4.56</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5">
-      <c r="A40" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="B40" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C40" s="5">
-        <v>37.65</v>
-      </c>
-      <c r="D40" s="5">
-        <v>35.38</v>
-      </c>
-      <c r="E40" s="6">
-        <v>-2.27</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5">
-      <c r="A41" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="B41" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C41" s="5">
-        <v>42.44</v>
-      </c>
-      <c r="D41" s="5">
-        <v>45.67</v>
-      </c>
-      <c r="E41" s="7">
-        <v>3.23</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5">
-      <c r="A42" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B42" s="3" t="s">
+      <c r="B50" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="C42" s="5">
-        <v>-15.75</v>
-      </c>
-      <c r="D42" s="5">
-        <v>38.67</v>
-      </c>
-      <c r="E42" s="7">
-        <v>54.42</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5">
-      <c r="A43" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="B43" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C43" s="5">
-        <v>-79.14</v>
-      </c>
-      <c r="D43" s="5">
-        <v>-59.11</v>
-      </c>
-      <c r="E43" s="7">
-        <v>20.03</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5">
-      <c r="A44" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="B44" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C44" s="5">
-        <v>-56.34</v>
-      </c>
-      <c r="D44" s="5">
-        <v>-28.21</v>
-      </c>
-      <c r="E44" s="7">
-        <v>28.13</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5">
-      <c r="A45" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="B45" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C45" s="5">
-        <v>109</v>
-      </c>
-      <c r="D45" s="5">
-        <v>27.85</v>
-      </c>
-      <c r="E45" s="6">
-        <v>-81.15000000000001</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5">
-      <c r="A46" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="B46" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C46" s="5">
-        <v>-27.62</v>
-      </c>
-      <c r="D46" s="5">
+      <c r="C50" s="6">
         <v>-14.03</v>
       </c>
-      <c r="E46" s="7">
-        <v>13.59</v>
+      <c r="D50" s="6">
+        <v>8.19</v>
+      </c>
+      <c r="E50" s="7">
+        <v>22.22</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A5:E5"/>
+    <mergeCell ref="A6:E6"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2335,61 +2463,61 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="28" customHeight="1">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="8" t="s">
-        <v>53</v>
-      </c>
-      <c r="C1" s="8" t="s">
-        <v>54</v>
-      </c>
-      <c r="D1" s="8" t="s">
-        <v>55</v>
-      </c>
-      <c r="E1" s="8" t="s">
-        <v>56</v>
-      </c>
-      <c r="F1" s="8" t="s">
-        <v>57</v>
-      </c>
-      <c r="G1" s="8" t="s">
-        <v>58</v>
-      </c>
-      <c r="H1" s="8" t="s">
-        <v>59</v>
-      </c>
-      <c r="I1" s="8" t="s">
+      <c r="B1" s="9" t="s">
         <v>60</v>
       </c>
+      <c r="C1" s="9" t="s">
+        <v>61</v>
+      </c>
+      <c r="D1" s="9" t="s">
+        <v>62</v>
+      </c>
+      <c r="E1" s="9" t="s">
+        <v>63</v>
+      </c>
+      <c r="F1" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="G1" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="H1" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="I1" s="9" t="s">
+        <v>67</v>
+      </c>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="9" t="s">
+      <c r="A2" s="10" t="s">
         <v>42</v>
       </c>
-      <c r="B2" s="10">
+      <c r="B2" s="11">
         <v>41.92</v>
       </c>
-      <c r="C2" s="11">
+      <c r="C2" s="12">
         <v>5</v>
       </c>
-      <c r="D2" s="10">
-        <v>38.9</v>
-      </c>
-      <c r="E2" s="10">
+      <c r="D2" s="11">
+        <v>39.9</v>
+      </c>
+      <c r="E2" s="11">
         <v>20</v>
       </c>
-      <c r="F2" s="10">
-        <v>-10.7</v>
-      </c>
-      <c r="G2" s="10">
-        <v>-8</v>
-      </c>
-      <c r="H2" s="10">
+      <c r="F2" s="11">
+        <v>-8.5</v>
+      </c>
+      <c r="G2" s="11">
+        <v>-7.7</v>
+      </c>
+      <c r="H2" s="11">
         <v>59.8</v>
       </c>
-      <c r="I2" s="10">
-        <v>20</v>
+      <c r="I2" s="11">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -2490,37 +2618,37 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
-      <c r="A1" s="12" t="s">
+      <c r="A1" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="B1" s="12" t="s">
+      <c r="B1" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="C1" s="12" t="s">
+      <c r="C1" s="13" t="s">
         <v>41</v>
       </c>
-      <c r="D1" s="12" t="s">
+      <c r="D1" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="E1" s="12" t="s">
+      <c r="E1" s="13" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="2" spans="1:5">
-      <c r="A2" s="13">
-        <v>0.1727</v>
-      </c>
-      <c r="B2" s="13">
-        <v>0.0144</v>
-      </c>
-      <c r="C2" s="13">
-        <v>0.006999999999999999</v>
-      </c>
-      <c r="D2" s="13">
-        <v>-0.0591</v>
-      </c>
-      <c r="E2" s="13">
-        <v>-0.2243</v>
+      <c r="A2" s="14">
+        <v>0.1782</v>
+      </c>
+      <c r="B2" s="14">
+        <v>0.0166</v>
+      </c>
+      <c r="C2" s="14">
+        <v>0.0039</v>
+      </c>
+      <c r="D2" s="14">
+        <v>-0.0565</v>
+      </c>
+      <c r="E2" s="14">
+        <v>-0.2261</v>
       </c>
     </row>
   </sheetData>

--- a/HINDUJA_GROUP_Technical_Metrics.xlsx
+++ b/HINDUJA_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="230" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="207" uniqueCount="61">
   <si>
     <t>Symbol</t>
   </si>
@@ -163,28 +163,7 @@
     <t>▶  SIGNAL EVENTS (vs Previous Run)</t>
   </si>
   <si>
-    <t>Signal</t>
-  </si>
-  <si>
-    <t>Change</t>
-  </si>
-  <si>
-    <t>Direction</t>
-  </si>
-  <si>
-    <t>Prev Value</t>
-  </si>
-  <si>
-    <t>Curr Value</t>
-  </si>
-  <si>
-    <t>Yes → No</t>
-  </si>
-  <si>
-    <t>🔴 BEARISH</t>
-  </si>
-  <si>
-    <t>20 DMA &gt; 50 DMA</t>
+    <t>No signal events detected since last run.</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -270,14 +249,14 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FF006100"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FF9C0006"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -310,13 +289,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -386,18 +365,17 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -910,10 +888,10 @@
         <v>42</v>
       </c>
       <c r="C2">
-        <v>148.18</v>
+        <v>148.91</v>
       </c>
       <c r="D2">
-        <v>2.19</v>
+        <v>0.49</v>
       </c>
       <c r="E2">
         <v>208.37</v>
@@ -922,25 +900,25 @@
         <v>131.36</v>
       </c>
       <c r="G2">
-        <v>-28.89</v>
+        <v>-28.54</v>
       </c>
       <c r="H2">
-        <v>12.8</v>
+        <v>13.36</v>
       </c>
       <c r="I2">
-        <v>2.18</v>
+        <v>2.65</v>
       </c>
       <c r="J2">
-        <v>-5.41</v>
+        <v>-4.85</v>
       </c>
       <c r="K2">
-        <v>-4.32</v>
+        <v>-4.07</v>
       </c>
       <c r="L2">
-        <v>10.31</v>
+        <v>10.96</v>
       </c>
       <c r="M2">
-        <v>17.82</v>
+        <v>17.93</v>
       </c>
       <c r="N2">
         <v>99</v>
@@ -949,19 +927,19 @@
         <v>67</v>
       </c>
       <c r="P2">
-        <v>145.97</v>
+        <v>146.74</v>
       </c>
       <c r="Q2">
-        <v>153.35</v>
+        <v>152.87</v>
       </c>
       <c r="R2">
-        <v>164.55</v>
+        <v>163.99</v>
       </c>
       <c r="S2">
-        <v>168.9</v>
+        <v>168.79</v>
       </c>
       <c r="T2">
-        <v>-12.27</v>
+        <v>-11.78</v>
       </c>
       <c r="U2" t="s">
         <v>43</v>
@@ -976,34 +954,34 @@
         <v>0</v>
       </c>
       <c r="Y2">
-        <v>39.28</v>
+        <v>40.67</v>
       </c>
       <c r="Z2">
-        <v>-5.12</v>
+        <v>-4.79</v>
       </c>
       <c r="AA2">
-        <v>-4.84</v>
+        <v>-4.83</v>
       </c>
       <c r="AB2">
-        <v>-0.28</v>
+        <v>0.05</v>
       </c>
       <c r="AC2">
-        <v>55.99</v>
+        <v>75.04000000000001</v>
       </c>
       <c r="AD2">
-        <v>32.22</v>
+        <v>52.41</v>
       </c>
       <c r="AE2">
-        <v>4.14</v>
+        <v>3.99</v>
       </c>
       <c r="AF2">
-        <v>72</v>
+        <v>-11.32</v>
       </c>
       <c r="AG2">
-        <v>166.08</v>
+        <v>165.49</v>
       </c>
       <c r="AH2">
-        <v>140.63</v>
+        <v>140.25</v>
       </c>
       <c r="AI2">
         <v>157.56</v>
@@ -1012,7 +990,7 @@
         <v>45</v>
       </c>
       <c r="AK2">
-        <v>58.31</v>
+        <v>53.65</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1023,10 +1001,10 @@
         <v>42</v>
       </c>
       <c r="C3">
-        <v>362.2</v>
+        <v>365.2</v>
       </c>
       <c r="D3">
-        <v>-1.31</v>
+        <v>0.83</v>
       </c>
       <c r="E3">
         <v>456.15</v>
@@ -1035,46 +1013,46 @@
         <v>225</v>
       </c>
       <c r="G3">
-        <v>-20.6</v>
+        <v>-19.94</v>
       </c>
       <c r="H3">
-        <v>60.98</v>
+        <v>62.31</v>
       </c>
       <c r="I3">
-        <v>1.29</v>
+        <v>2.15</v>
       </c>
       <c r="J3">
-        <v>-16.86</v>
+        <v>-14.75</v>
       </c>
       <c r="K3">
-        <v>-10.11</v>
+        <v>-9.539999999999999</v>
       </c>
       <c r="L3">
-        <v>3.13</v>
+        <v>3.66</v>
       </c>
       <c r="M3">
-        <v>1.66</v>
+        <v>1.82</v>
       </c>
       <c r="N3">
         <v>60</v>
       </c>
       <c r="O3">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="P3">
-        <v>358.07</v>
+        <v>359.61</v>
       </c>
       <c r="Q3">
-        <v>380.83</v>
+        <v>376.28</v>
       </c>
       <c r="R3">
-        <v>400.87</v>
+        <v>399.93</v>
       </c>
       <c r="S3">
-        <v>340.95</v>
+        <v>341.34</v>
       </c>
       <c r="T3">
-        <v>6.23</v>
+        <v>6.99</v>
       </c>
       <c r="U3" t="s">
         <v>43</v>
@@ -1089,34 +1067,34 @@
         <v>2</v>
       </c>
       <c r="Y3">
-        <v>41.89</v>
+        <v>43.33</v>
       </c>
       <c r="Z3">
-        <v>-14.41</v>
+        <v>-13.42</v>
       </c>
       <c r="AA3">
-        <v>-13.79</v>
+        <v>-13.72</v>
       </c>
       <c r="AB3">
-        <v>-0.61</v>
+        <v>0.3</v>
       </c>
       <c r="AC3">
-        <v>84.92</v>
+        <v>95.48999999999999</v>
       </c>
       <c r="AD3">
-        <v>63.65</v>
+        <v>82.17</v>
       </c>
       <c r="AE3">
-        <v>16.52</v>
+        <v>16.08</v>
       </c>
       <c r="AF3">
-        <v>-86.95999999999999</v>
+        <v>-82.48999999999999</v>
       </c>
       <c r="AG3">
-        <v>449.52</v>
+        <v>435.35</v>
       </c>
       <c r="AH3">
-        <v>312.13</v>
+        <v>317.21</v>
       </c>
       <c r="AI3">
         <v>401.23</v>
@@ -1125,7 +1103,7 @@
         <v>45</v>
       </c>
       <c r="AK3">
-        <v>35.54</v>
+        <v>31.36</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1136,10 +1114,10 @@
         <v>42</v>
       </c>
       <c r="C4">
-        <v>357.8</v>
+        <v>357.75</v>
       </c>
       <c r="D4">
-        <v>-1.12</v>
+        <v>-0.01</v>
       </c>
       <c r="E4">
         <v>534</v>
@@ -1148,25 +1126,25 @@
         <v>344.7</v>
       </c>
       <c r="G4">
-        <v>-33</v>
+        <v>-33.01</v>
       </c>
       <c r="H4">
-        <v>3.8</v>
+        <v>3.79</v>
       </c>
       <c r="I4">
-        <v>-0.32</v>
+        <v>0.62</v>
       </c>
       <c r="J4">
-        <v>-6.24</v>
+        <v>-7.33</v>
       </c>
       <c r="K4">
-        <v>-18.15</v>
+        <v>-17.1</v>
       </c>
       <c r="L4">
-        <v>-27.64</v>
+        <v>-27.63</v>
       </c>
       <c r="M4">
-        <v>-22.61</v>
+        <v>-22.6</v>
       </c>
       <c r="N4">
         <v>21</v>
@@ -1175,19 +1153,19 @@
         <v>20</v>
       </c>
       <c r="P4">
-        <v>357.15</v>
+        <v>357.59</v>
       </c>
       <c r="Q4">
-        <v>368.12</v>
+        <v>366.69</v>
       </c>
       <c r="R4">
-        <v>388.18</v>
+        <v>386.87</v>
       </c>
       <c r="S4">
-        <v>403.33</v>
+        <v>402.91</v>
       </c>
       <c r="T4">
-        <v>-11.29</v>
+        <v>-11.21</v>
       </c>
       <c r="U4" t="s">
         <v>43</v>
@@ -1202,34 +1180,34 @@
         <v>0</v>
       </c>
       <c r="Y4">
-        <v>34.08</v>
+        <v>34.04</v>
       </c>
       <c r="Z4">
-        <v>-9.15</v>
+        <v>-8.84</v>
       </c>
       <c r="AA4">
-        <v>-9.390000000000001</v>
+        <v>-9.279999999999999</v>
       </c>
       <c r="AB4">
-        <v>0.24</v>
+        <v>0.44</v>
       </c>
       <c r="AC4">
-        <v>93.28</v>
+        <v>86.47</v>
       </c>
       <c r="AD4">
-        <v>64.43000000000001</v>
+        <v>82.14</v>
       </c>
       <c r="AE4">
-        <v>9.9</v>
+        <v>9.609999999999999</v>
       </c>
       <c r="AF4">
-        <v>35.31</v>
+        <v>52.42</v>
       </c>
       <c r="AG4">
-        <v>387.35</v>
+        <v>384.4</v>
       </c>
       <c r="AH4">
-        <v>348.89</v>
+        <v>348.98</v>
       </c>
       <c r="AI4">
         <v>384.24</v>
@@ -1238,7 +1216,7 @@
         <v>45</v>
       </c>
       <c r="AK4">
-        <v>52.12</v>
+        <v>50.29</v>
       </c>
     </row>
     <row r="5" spans="1:37">
@@ -1249,10 +1227,10 @@
         <v>42</v>
       </c>
       <c r="C5">
-        <v>885.4</v>
+        <v>877</v>
       </c>
       <c r="D5">
-        <v>2.24</v>
+        <v>-0.95</v>
       </c>
       <c r="E5">
         <v>1069.3</v>
@@ -1261,46 +1239,46 @@
         <v>739.5</v>
       </c>
       <c r="G5">
-        <v>-17.2</v>
+        <v>-17.98</v>
       </c>
       <c r="H5">
-        <v>19.73</v>
+        <v>18.59</v>
       </c>
       <c r="I5">
-        <v>2.48</v>
+        <v>1.78</v>
       </c>
       <c r="J5">
-        <v>-7.43</v>
+        <v>-7.34</v>
       </c>
       <c r="K5">
-        <v>-12.64</v>
+        <v>-14.62</v>
       </c>
       <c r="L5">
-        <v>15.99</v>
+        <v>15.41</v>
       </c>
       <c r="M5">
-        <v>-5.65</v>
+        <v>-5.83</v>
       </c>
       <c r="N5">
         <v>79</v>
       </c>
       <c r="O5">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="P5">
-        <v>868.6799999999999</v>
+        <v>871.75</v>
       </c>
       <c r="Q5">
-        <v>903.87</v>
+        <v>899.8099999999999</v>
       </c>
       <c r="R5">
-        <v>964.1799999999999</v>
+        <v>961.34</v>
       </c>
       <c r="S5">
-        <v>925.3200000000001</v>
+        <v>925.5</v>
       </c>
       <c r="T5">
-        <v>-4.31</v>
+        <v>-5.24</v>
       </c>
       <c r="U5" t="s">
         <v>43</v>
@@ -1315,34 +1293,34 @@
         <v>1</v>
       </c>
       <c r="Y5">
-        <v>41.82</v>
+        <v>39.97</v>
       </c>
       <c r="Z5">
-        <v>-28.47</v>
+        <v>-26.98</v>
       </c>
       <c r="AA5">
-        <v>-29</v>
+        <v>-28.6</v>
       </c>
       <c r="AB5">
-        <v>0.54</v>
+        <v>1.62</v>
       </c>
       <c r="AC5">
-        <v>88.19</v>
+        <v>90.23</v>
       </c>
       <c r="AD5">
-        <v>67.66</v>
+        <v>81</v>
       </c>
       <c r="AE5">
-        <v>22.78</v>
+        <v>22.37</v>
       </c>
       <c r="AF5">
-        <v>-27.2</v>
+        <v>-38.43</v>
       </c>
       <c r="AG5">
-        <v>978.0700000000001</v>
+        <v>970.28</v>
       </c>
       <c r="AH5">
-        <v>829.6799999999999</v>
+        <v>829.34</v>
       </c>
       <c r="AI5">
         <v>921.99</v>
@@ -1351,7 +1329,7 @@
         <v>45</v>
       </c>
       <c r="AK5">
-        <v>49.64</v>
+        <v>45.18</v>
       </c>
     </row>
     <row r="6" spans="1:37">
@@ -1362,10 +1340,10 @@
         <v>42</v>
       </c>
       <c r="C6">
-        <v>2.57</v>
+        <v>2.6</v>
       </c>
       <c r="D6">
-        <v>-1.53</v>
+        <v>1.17</v>
       </c>
       <c r="E6">
         <v>3.38</v>
@@ -1374,37 +1352,37 @@
         <v>1.84</v>
       </c>
       <c r="G6">
-        <v>-23.96</v>
+        <v>-23.08</v>
       </c>
       <c r="H6">
-        <v>39.67</v>
+        <v>41.3</v>
       </c>
       <c r="I6">
-        <v>-0.39</v>
+        <v>0.78</v>
       </c>
       <c r="J6">
-        <v>-6.55</v>
+        <v>-10.03</v>
       </c>
       <c r="K6">
-        <v>6.64</v>
+        <v>10.17</v>
       </c>
       <c r="L6">
-        <v>-20.19</v>
+        <v>-18.75</v>
       </c>
       <c r="M6">
-        <v>0.39</v>
+        <v>0.63</v>
       </c>
       <c r="N6">
         <v>40</v>
       </c>
       <c r="O6">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="P6">
-        <v>2.58</v>
+        <v>2.59</v>
       </c>
       <c r="Q6">
-        <v>2.65</v>
+        <v>2.63</v>
       </c>
       <c r="R6">
         <v>2.66</v>
@@ -1413,7 +1391,7 @@
         <v>2.64</v>
       </c>
       <c r="T6">
-        <v>-2.62</v>
+        <v>-1.43</v>
       </c>
       <c r="U6" t="s">
         <v>43</v>
@@ -1428,7 +1406,7 @@
         <v>1</v>
       </c>
       <c r="Y6">
-        <v>42.27</v>
+        <v>45.54</v>
       </c>
       <c r="Z6">
         <v>-0.04</v>
@@ -1437,25 +1415,25 @@
         <v>-0.03</v>
       </c>
       <c r="AB6">
-        <v>-0.01</v>
+        <v>-0</v>
       </c>
       <c r="AC6">
-        <v>61.83</v>
+        <v>83.23999999999999</v>
       </c>
       <c r="AD6">
-        <v>49.93</v>
+        <v>66.84</v>
       </c>
       <c r="AE6">
         <v>0.11</v>
       </c>
       <c r="AF6">
-        <v>8.19</v>
+        <v>-7.36</v>
       </c>
       <c r="AG6">
-        <v>2.82</v>
+        <v>2.79</v>
       </c>
       <c r="AH6">
-        <v>2.47</v>
+        <v>2.48</v>
       </c>
       <c r="AI6">
         <v>2.92</v>
@@ -1464,7 +1442,7 @@
         <v>45</v>
       </c>
       <c r="AK6">
-        <v>27.97</v>
+        <v>27.52</v>
       </c>
     </row>
   </sheetData>
@@ -1605,7 +1583,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F50"/>
+  <dimension ref="A1:F46"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.7109375" customWidth="1"/>
@@ -1625,825 +1603,719 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="3" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6">
+      <c r="A5" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="B5" s="2"/>
+      <c r="C5" s="2"/>
+      <c r="D5" s="2"/>
+      <c r="E5" s="2"/>
+    </row>
+    <row r="6" spans="1:6">
+      <c r="A6" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="D2" s="3" t="s">
+      <c r="B6" s="4" t="s">
         <v>49</v>
       </c>
-      <c r="E2" s="3" t="s">
+      <c r="C6" s="4" t="s">
         <v>50</v>
       </c>
-      <c r="F2" s="3" t="s">
+      <c r="D6" s="4" t="s">
         <v>51</v>
       </c>
-    </row>
-    <row r="3" spans="1:6">
-      <c r="A3" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="B3" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="C3" s="4" t="s">
+      <c r="E6" s="4" t="s">
         <v>52</v>
       </c>
-      <c r="D3" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="E3" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="F3" s="4" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6">
-      <c r="A4" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="B4" s="4" t="s">
-        <v>54</v>
-      </c>
-      <c r="C4" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="D4" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="E4" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="F4" s="4" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6">
-      <c r="A6" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="B6" s="2"/>
-      <c r="C6" s="2"/>
-      <c r="D6" s="2"/>
-      <c r="E6" s="2"/>
     </row>
     <row r="7" spans="1:6">
       <c r="A7" s="3" t="s">
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="D7" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="E7" s="3" t="s">
-        <v>59</v>
+        <v>9</v>
+      </c>
+      <c r="C7" s="5">
+        <v>-5.41</v>
+      </c>
+      <c r="D7" s="5">
+        <v>-4.85</v>
+      </c>
+      <c r="E7" s="6">
+        <v>0.5600000000000001</v>
       </c>
     </row>
     <row r="8" spans="1:6">
-      <c r="A8" s="5" t="s">
+      <c r="A8" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C8" s="5">
+        <v>-16.86</v>
+      </c>
+      <c r="D8" s="5">
+        <v>-14.75</v>
+      </c>
+      <c r="E8" s="6">
+        <v>2.11</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="A9" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C9" s="5">
+        <v>-6.24</v>
+      </c>
+      <c r="D9" s="5">
+        <v>-7.33</v>
+      </c>
+      <c r="E9" s="7">
+        <v>-1.09</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="A10" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C10" s="5">
+        <v>-7.43</v>
+      </c>
+      <c r="D10" s="5">
+        <v>-7.34</v>
+      </c>
+      <c r="E10" s="6">
+        <v>0.09</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="A11" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C11" s="5">
+        <v>-6.55</v>
+      </c>
+      <c r="D11" s="5">
+        <v>-10.03</v>
+      </c>
+      <c r="E11" s="7">
+        <v>-3.48</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6">
+      <c r="A12" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B8" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C8" s="6">
-        <v>-11.45</v>
-      </c>
-      <c r="D8" s="6">
-        <v>-5.41</v>
-      </c>
-      <c r="E8" s="7">
-        <v>6.04</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
-      <c r="A9" s="5" t="s">
+      <c r="B12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C12" s="5">
+        <v>2.18</v>
+      </c>
+      <c r="D12" s="5">
+        <v>2.65</v>
+      </c>
+      <c r="E12" s="6">
+        <v>0.47</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6">
+      <c r="A13" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B9" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C9" s="6">
-        <v>-16.88</v>
-      </c>
-      <c r="D9" s="6">
-        <v>-16.86</v>
-      </c>
-      <c r="E9" s="7">
-        <v>0.02</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
-      <c r="A10" s="5" t="s">
+      <c r="B13" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C13" s="5">
+        <v>1.29</v>
+      </c>
+      <c r="D13" s="5">
+        <v>2.15</v>
+      </c>
+      <c r="E13" s="6">
+        <v>0.86</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6">
+      <c r="A14" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B10" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C10" s="6">
-        <v>-5.14</v>
-      </c>
-      <c r="D10" s="6">
-        <v>-6.24</v>
-      </c>
-      <c r="E10" s="8">
-        <v>-1.1</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
-      <c r="A11" s="5" t="s">
+      <c r="B14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C14" s="5">
+        <v>-0.32</v>
+      </c>
+      <c r="D14" s="5">
+        <v>0.62</v>
+      </c>
+      <c r="E14" s="6">
+        <v>0.9399999999999999</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6">
+      <c r="A15" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="B11" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C11" s="6">
-        <v>-11.47</v>
-      </c>
-      <c r="D11" s="6">
-        <v>-7.43</v>
-      </c>
-      <c r="E11" s="7">
-        <v>4.04</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
-      <c r="A12" s="5" t="s">
+      <c r="B15" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C15" s="5">
+        <v>2.48</v>
+      </c>
+      <c r="D15" s="5">
+        <v>1.78</v>
+      </c>
+      <c r="E15" s="7">
+        <v>-0.7</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6">
+      <c r="A16" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="B12" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C12" s="6">
-        <v>-8.74</v>
-      </c>
-      <c r="D12" s="6">
-        <v>-6.55</v>
-      </c>
-      <c r="E12" s="7">
-        <v>2.19</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
-      <c r="A13" s="5" t="s">
+      <c r="B16" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C16" s="5">
+        <v>-0.39</v>
+      </c>
+      <c r="D16" s="5">
+        <v>0.78</v>
+      </c>
+      <c r="E16" s="6">
+        <v>1.17</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B13" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C13" s="6">
-        <v>-2.82</v>
-      </c>
-      <c r="D13" s="6">
-        <v>2.18</v>
-      </c>
-      <c r="E13" s="7">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
-      <c r="A14" s="5" t="s">
+      <c r="B17" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C17" s="5">
+        <v>10.31</v>
+      </c>
+      <c r="D17" s="5">
+        <v>10.96</v>
+      </c>
+      <c r="E17" s="6">
+        <v>0.65</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B14" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C14" s="6">
-        <v>-0.23</v>
-      </c>
-      <c r="D14" s="6">
-        <v>1.29</v>
-      </c>
-      <c r="E14" s="7">
-        <v>1.52</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6">
-      <c r="A15" s="5" t="s">
+      <c r="B18" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C18" s="5">
+        <v>3.13</v>
+      </c>
+      <c r="D18" s="5">
+        <v>3.66</v>
+      </c>
+      <c r="E18" s="6">
+        <v>0.53</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C19" s="5">
+        <v>-27.64</v>
+      </c>
+      <c r="D19" s="5">
+        <v>-27.63</v>
+      </c>
+      <c r="E19" s="6">
+        <v>0.01</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="B15" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C15" s="6">
-        <v>-1.02</v>
-      </c>
-      <c r="D15" s="6">
-        <v>2.48</v>
-      </c>
-      <c r="E15" s="7">
-        <v>3.5</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
-      <c r="A16" s="5" t="s">
+      <c r="B20" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C20" s="5">
+        <v>15.99</v>
+      </c>
+      <c r="D20" s="5">
+        <v>15.41</v>
+      </c>
+      <c r="E20" s="7">
+        <v>-0.58</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="B16" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C16" s="6">
-        <v>0.38</v>
-      </c>
-      <c r="D16" s="6">
-        <v>-0.39</v>
-      </c>
-      <c r="E16" s="8">
-        <v>-0.77</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5">
-      <c r="A17" s="5" t="s">
+      <c r="B21" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C21" s="5">
+        <v>-20.19</v>
+      </c>
+      <c r="D21" s="5">
+        <v>-18.75</v>
+      </c>
+      <c r="E21" s="6">
+        <v>1.44</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B17" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C17" s="6">
-        <v>7.09</v>
-      </c>
-      <c r="D17" s="6">
-        <v>10.31</v>
-      </c>
-      <c r="E17" s="7">
-        <v>3.22</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5">
-      <c r="A18" s="5" t="s">
+      <c r="B22" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C22" s="5">
+        <v>-4.32</v>
+      </c>
+      <c r="D22" s="5">
+        <v>-4.07</v>
+      </c>
+      <c r="E22" s="6">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B18" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C18" s="6">
-        <v>3.98</v>
-      </c>
-      <c r="D18" s="6">
-        <v>3.13</v>
-      </c>
-      <c r="E18" s="8">
-        <v>-0.85</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5">
-      <c r="A19" s="5" t="s">
+      <c r="B23" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C23" s="5">
+        <v>-10.11</v>
+      </c>
+      <c r="D23" s="5">
+        <v>-9.539999999999999</v>
+      </c>
+      <c r="E23" s="6">
+        <v>0.57</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5">
+      <c r="A24" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B19" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C19" s="6">
-        <v>-26.88</v>
-      </c>
-      <c r="D19" s="6">
-        <v>-27.64</v>
-      </c>
-      <c r="E19" s="8">
-        <v>-0.76</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5">
-      <c r="A20" s="5" t="s">
+      <c r="B24" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C24" s="5">
+        <v>-18.15</v>
+      </c>
+      <c r="D24" s="5">
+        <v>-17.1</v>
+      </c>
+      <c r="E24" s="6">
+        <v>1.05</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5">
+      <c r="A25" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="B20" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C20" s="6">
-        <v>15.6</v>
-      </c>
-      <c r="D20" s="6">
-        <v>15.99</v>
-      </c>
-      <c r="E20" s="7">
-        <v>0.39</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5">
-      <c r="A21" s="5" t="s">
+      <c r="B25" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C25" s="5">
+        <v>-12.64</v>
+      </c>
+      <c r="D25" s="5">
+        <v>-14.62</v>
+      </c>
+      <c r="E25" s="7">
+        <v>-1.98</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
+      <c r="A26" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="B21" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C21" s="6">
-        <v>-18.18</v>
-      </c>
-      <c r="D21" s="6">
-        <v>-20.19</v>
-      </c>
-      <c r="E21" s="8">
-        <v>-2.01</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5">
-      <c r="A22" s="5" t="s">
+      <c r="B26" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C26" s="5">
+        <v>6.64</v>
+      </c>
+      <c r="D26" s="5">
+        <v>10.17</v>
+      </c>
+      <c r="E26" s="6">
+        <v>3.53</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5">
+      <c r="A27" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B22" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C22" s="6">
+      <c r="B27" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C27" s="5">
+        <v>-28.89</v>
+      </c>
+      <c r="D27" s="5">
+        <v>-28.54</v>
+      </c>
+      <c r="E27" s="6">
+        <v>0.35</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5">
+      <c r="A28" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B28" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C28" s="5">
+        <v>-20.6</v>
+      </c>
+      <c r="D28" s="5">
+        <v>-19.94</v>
+      </c>
+      <c r="E28" s="6">
+        <v>0.66</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5">
+      <c r="A29" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B29" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C29" s="5">
+        <v>-33</v>
+      </c>
+      <c r="D29" s="5">
+        <v>-33.01</v>
+      </c>
+      <c r="E29" s="7">
+        <v>-0.01</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5">
+      <c r="A30" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B30" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C30" s="5">
+        <v>-17.2</v>
+      </c>
+      <c r="D30" s="5">
+        <v>-17.98</v>
+      </c>
+      <c r="E30" s="7">
+        <v>-0.78</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5">
+      <c r="A31" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B31" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C31" s="5">
+        <v>-23.96</v>
+      </c>
+      <c r="D31" s="5">
+        <v>-23.08</v>
+      </c>
+      <c r="E31" s="6">
+        <v>0.88</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5">
+      <c r="A32" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B32" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C32" s="5">
+        <v>148.18</v>
+      </c>
+      <c r="D32" s="5">
+        <v>148.91</v>
+      </c>
+      <c r="E32" s="6">
+        <v>0.73</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5">
+      <c r="A33" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B33" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C33" s="5">
+        <v>362.2</v>
+      </c>
+      <c r="D33" s="5">
+        <v>365.2</v>
+      </c>
+      <c r="E33" s="6">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5">
+      <c r="A34" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B34" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C34" s="5">
+        <v>357.8</v>
+      </c>
+      <c r="D34" s="5">
+        <v>357.75</v>
+      </c>
+      <c r="E34" s="7">
+        <v>-0.05</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5">
+      <c r="A35" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B35" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C35" s="5">
+        <v>885.4</v>
+      </c>
+      <c r="D35" s="5">
+        <v>877</v>
+      </c>
+      <c r="E35" s="7">
+        <v>-8.4</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5">
+      <c r="A36" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B36" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C36" s="5">
+        <v>2.57</v>
+      </c>
+      <c r="D36" s="5">
+        <v>2.6</v>
+      </c>
+      <c r="E36" s="6">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5">
+      <c r="A37" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B37" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C37" s="5">
+        <v>39.28</v>
+      </c>
+      <c r="D37" s="5">
+        <v>40.67</v>
+      </c>
+      <c r="E37" s="6">
+        <v>1.39</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5">
+      <c r="A38" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B38" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C38" s="5">
+        <v>41.89</v>
+      </c>
+      <c r="D38" s="5">
+        <v>43.33</v>
+      </c>
+      <c r="E38" s="6">
+        <v>1.44</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5">
+      <c r="A39" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B39" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C39" s="5">
+        <v>34.08</v>
+      </c>
+      <c r="D39" s="5">
+        <v>34.04</v>
+      </c>
+      <c r="E39" s="7">
+        <v>-0.04</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5">
+      <c r="A40" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B40" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C40" s="5">
+        <v>41.82</v>
+      </c>
+      <c r="D40" s="5">
+        <v>39.97</v>
+      </c>
+      <c r="E40" s="7">
+        <v>-1.85</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5">
+      <c r="A41" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B41" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C41" s="5">
+        <v>42.27</v>
+      </c>
+      <c r="D41" s="5">
+        <v>45.54</v>
+      </c>
+      <c r="E41" s="6">
+        <v>3.27</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5">
+      <c r="A42" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B42" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C42" s="5">
+        <v>72</v>
+      </c>
+      <c r="D42" s="5">
+        <v>-11.32</v>
+      </c>
+      <c r="E42" s="7">
+        <v>-83.31999999999999</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5">
+      <c r="A43" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B43" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C43" s="5">
+        <v>-86.95999999999999</v>
+      </c>
+      <c r="D43" s="5">
+        <v>-82.48999999999999</v>
+      </c>
+      <c r="E43" s="6">
+        <v>4.47</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5">
+      <c r="A44" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B44" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C44" s="5">
+        <v>35.31</v>
+      </c>
+      <c r="D44" s="5">
+        <v>52.42</v>
+      </c>
+      <c r="E44" s="6">
+        <v>17.11</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5">
+      <c r="A45" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B45" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C45" s="5">
+        <v>-27.2</v>
+      </c>
+      <c r="D45" s="5">
+        <v>-38.43</v>
+      </c>
+      <c r="E45" s="7">
+        <v>-11.23</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5">
+      <c r="A46" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B46" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C46" s="5">
+        <v>8.19</v>
+      </c>
+      <c r="D46" s="5">
         <v>-7.36</v>
       </c>
-      <c r="D22" s="6">
-        <v>-4.32</v>
-      </c>
-      <c r="E22" s="7">
-        <v>3.04</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5">
-      <c r="A23" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B23" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C23" s="6">
-        <v>-8.99</v>
-      </c>
-      <c r="D23" s="6">
-        <v>-10.11</v>
-      </c>
-      <c r="E23" s="8">
-        <v>-1.12</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5">
-      <c r="A24" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B24" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C24" s="6">
-        <v>-18.83</v>
-      </c>
-      <c r="D24" s="6">
-        <v>-18.15</v>
-      </c>
-      <c r="E24" s="7">
-        <v>0.68</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5">
-      <c r="A25" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B25" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C25" s="6">
-        <v>-14.23</v>
-      </c>
-      <c r="D25" s="6">
-        <v>-12.64</v>
-      </c>
-      <c r="E25" s="7">
-        <v>1.59</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5">
-      <c r="A26" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B26" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C26" s="6">
-        <v>9.66</v>
-      </c>
-      <c r="D26" s="6">
-        <v>6.64</v>
-      </c>
-      <c r="E26" s="8">
-        <v>-3.02</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5">
-      <c r="A27" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B27" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C27" s="6">
-        <v>-30.41</v>
-      </c>
-      <c r="D27" s="6">
-        <v>-28.89</v>
-      </c>
-      <c r="E27" s="7">
-        <v>1.52</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5">
-      <c r="A28" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B28" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C28" s="6">
-        <v>-19.54</v>
-      </c>
-      <c r="D28" s="6">
-        <v>-20.6</v>
-      </c>
-      <c r="E28" s="8">
-        <v>-1.06</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5">
-      <c r="A29" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B29" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C29" s="6">
-        <v>-32.24</v>
-      </c>
-      <c r="D29" s="6">
-        <v>-33</v>
-      </c>
-      <c r="E29" s="8">
-        <v>-0.76</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5">
-      <c r="A30" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B30" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C30" s="6">
-        <v>-19.01</v>
-      </c>
-      <c r="D30" s="6">
-        <v>-17.2</v>
-      </c>
-      <c r="E30" s="7">
-        <v>1.81</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5">
-      <c r="A31" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B31" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C31" s="6">
-        <v>-22.78</v>
-      </c>
-      <c r="D31" s="6">
-        <v>-23.96</v>
-      </c>
-      <c r="E31" s="8">
-        <v>-1.18</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5">
-      <c r="A32" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B32" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C32" s="6">
-        <v>145</v>
-      </c>
-      <c r="D32" s="6">
-        <v>148.18</v>
-      </c>
-      <c r="E32" s="7">
-        <v>3.18</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5">
-      <c r="A33" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B33" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C33" s="6">
-        <v>367</v>
-      </c>
-      <c r="D33" s="6">
-        <v>362.2</v>
-      </c>
-      <c r="E33" s="8">
-        <v>-4.8</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5">
-      <c r="A34" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B34" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C34" s="6">
-        <v>361.85</v>
-      </c>
-      <c r="D34" s="6">
-        <v>357.8</v>
-      </c>
-      <c r="E34" s="8">
-        <v>-4.05</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5">
-      <c r="A35" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B35" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C35" s="6">
-        <v>866</v>
-      </c>
-      <c r="D35" s="6">
-        <v>885.4</v>
-      </c>
-      <c r="E35" s="7">
-        <v>19.4</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5">
-      <c r="A36" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B36" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C36" s="6">
-        <v>2.61</v>
-      </c>
-      <c r="D36" s="6">
-        <v>2.57</v>
-      </c>
-      <c r="E36" s="8">
-        <v>-0.04</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5">
-      <c r="A37" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B37" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="C37" s="6">
-        <v>79</v>
-      </c>
-      <c r="D37" s="6">
-        <v>99</v>
-      </c>
-      <c r="E37" s="7">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5">
-      <c r="A38" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B38" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="C38" s="6">
-        <v>40</v>
-      </c>
-      <c r="D38" s="6">
-        <v>60</v>
-      </c>
-      <c r="E38" s="7">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5">
-      <c r="A39" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B39" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="C39" s="6">
-        <v>99</v>
-      </c>
-      <c r="D39" s="6">
-        <v>79</v>
-      </c>
-      <c r="E39" s="8">
-        <v>-20</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5">
-      <c r="A40" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B40" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="C40" s="6">
-        <v>60</v>
-      </c>
-      <c r="D40" s="6">
-        <v>40</v>
-      </c>
-      <c r="E40" s="8">
-        <v>-20</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5">
-      <c r="A41" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B41" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C41" s="6">
-        <v>32.91</v>
-      </c>
-      <c r="D41" s="6">
-        <v>39.28</v>
-      </c>
-      <c r="E41" s="7">
-        <v>6.37</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5">
-      <c r="A42" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B42" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C42" s="6">
-        <v>43.53</v>
-      </c>
-      <c r="D42" s="6">
-        <v>41.89</v>
-      </c>
-      <c r="E42" s="8">
-        <v>-1.64</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5">
-      <c r="A43" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B43" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C43" s="6">
-        <v>37.17</v>
-      </c>
-      <c r="D43" s="6">
-        <v>34.08</v>
-      </c>
-      <c r="E43" s="8">
-        <v>-3.09</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5">
-      <c r="A44" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B44" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C44" s="6">
-        <v>35.38</v>
-      </c>
-      <c r="D44" s="6">
-        <v>41.82</v>
-      </c>
-      <c r="E44" s="7">
-        <v>6.44</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5">
-      <c r="A45" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B45" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C45" s="6">
-        <v>45.67</v>
-      </c>
-      <c r="D45" s="6">
-        <v>42.27</v>
-      </c>
-      <c r="E45" s="8">
-        <v>-3.4</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5">
-      <c r="A46" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B46" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C46" s="6">
-        <v>38.67</v>
-      </c>
-      <c r="D46" s="6">
-        <v>72</v>
-      </c>
       <c r="E46" s="7">
-        <v>33.33</v>
-      </c>
-    </row>
-    <row r="47" spans="1:5">
-      <c r="A47" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B47" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C47" s="6">
-        <v>-59.11</v>
-      </c>
-      <c r="D47" s="6">
-        <v>-86.95999999999999</v>
-      </c>
-      <c r="E47" s="8">
-        <v>-27.85</v>
-      </c>
-    </row>
-    <row r="48" spans="1:5">
-      <c r="A48" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B48" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C48" s="6">
-        <v>-28.21</v>
-      </c>
-      <c r="D48" s="6">
-        <v>35.31</v>
-      </c>
-      <c r="E48" s="7">
-        <v>63.52</v>
-      </c>
-    </row>
-    <row r="49" spans="1:5">
-      <c r="A49" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B49" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C49" s="6">
-        <v>27.85</v>
-      </c>
-      <c r="D49" s="6">
-        <v>-27.2</v>
-      </c>
-      <c r="E49" s="8">
-        <v>-55.05</v>
-      </c>
-    </row>
-    <row r="50" spans="1:5">
-      <c r="A50" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B50" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C50" s="6">
-        <v>-14.03</v>
-      </c>
-      <c r="D50" s="6">
-        <v>8.19</v>
-      </c>
-      <c r="E50" s="7">
-        <v>22.22</v>
+        <v>-15.55</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A6:E6"/>
+    <mergeCell ref="A5:E5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2463,60 +2335,60 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="28" customHeight="1">
-      <c r="A1" s="9" t="s">
+      <c r="A1" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="9" t="s">
+      <c r="B1" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="C1" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="D1" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="E1" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="F1" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="G1" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="H1" s="8" t="s">
+        <v>59</v>
+      </c>
+      <c r="I1" s="8" t="s">
         <v>60</v>
       </c>
-      <c r="C1" s="9" t="s">
-        <v>61</v>
-      </c>
-      <c r="D1" s="9" t="s">
-        <v>62</v>
-      </c>
-      <c r="E1" s="9" t="s">
-        <v>63</v>
-      </c>
-      <c r="F1" s="9" t="s">
-        <v>64</v>
-      </c>
-      <c r="G1" s="9" t="s">
-        <v>65</v>
-      </c>
-      <c r="H1" s="9" t="s">
-        <v>66</v>
-      </c>
-      <c r="I1" s="9" t="s">
-        <v>67</v>
-      </c>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="10" t="s">
+      <c r="A2" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="B2" s="11">
+      <c r="B2" s="10">
         <v>41.92</v>
       </c>
-      <c r="C2" s="12">
+      <c r="C2" s="11">
         <v>5</v>
       </c>
-      <c r="D2" s="11">
-        <v>39.9</v>
-      </c>
-      <c r="E2" s="11">
+      <c r="D2" s="10">
+        <v>40.7</v>
+      </c>
+      <c r="E2" s="10">
         <v>20</v>
       </c>
-      <c r="F2" s="11">
-        <v>-8.5</v>
-      </c>
-      <c r="G2" s="11">
-        <v>-7.7</v>
-      </c>
-      <c r="H2" s="11">
+      <c r="F2" s="10">
+        <v>-8.9</v>
+      </c>
+      <c r="G2" s="10">
+        <v>-7</v>
+      </c>
+      <c r="H2" s="10">
         <v>59.8</v>
       </c>
-      <c r="I2" s="11">
+      <c r="I2" s="10">
         <v>0</v>
       </c>
     </row>
@@ -2618,37 +2490,37 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
-      <c r="A1" s="13" t="s">
+      <c r="A1" s="12" t="s">
         <v>37</v>
       </c>
-      <c r="B1" s="13" t="s">
+      <c r="B1" s="12" t="s">
         <v>38</v>
       </c>
-      <c r="C1" s="13" t="s">
+      <c r="C1" s="12" t="s">
         <v>41</v>
       </c>
-      <c r="D1" s="13" t="s">
+      <c r="D1" s="12" t="s">
         <v>40</v>
       </c>
-      <c r="E1" s="13" t="s">
+      <c r="E1" s="12" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="2" spans="1:5">
-      <c r="A2" s="14">
-        <v>0.1782</v>
-      </c>
-      <c r="B2" s="14">
-        <v>0.0166</v>
-      </c>
-      <c r="C2" s="14">
-        <v>0.0039</v>
-      </c>
-      <c r="D2" s="14">
-        <v>-0.0565</v>
-      </c>
-      <c r="E2" s="14">
-        <v>-0.2261</v>
+      <c r="A2" s="13">
+        <v>0.1793</v>
+      </c>
+      <c r="B2" s="13">
+        <v>0.0182</v>
+      </c>
+      <c r="C2" s="13">
+        <v>0.0063</v>
+      </c>
+      <c r="D2" s="13">
+        <v>-0.0583</v>
+      </c>
+      <c r="E2" s="13">
+        <v>-0.226</v>
       </c>
     </row>
   </sheetData>

--- a/HINDUJA_GROUP_Technical_Metrics.xlsx
+++ b/HINDUJA_GROUP_Technical_Metrics.xlsx
@@ -249,14 +249,14 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FF9C0006"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FF006100"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -289,13 +289,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -888,10 +888,10 @@
         <v>42</v>
       </c>
       <c r="C2">
-        <v>148.91</v>
+        <v>147.72</v>
       </c>
       <c r="D2">
-        <v>0.49</v>
+        <v>-0.8</v>
       </c>
       <c r="E2">
         <v>208.37</v>
@@ -900,25 +900,25 @@
         <v>131.36</v>
       </c>
       <c r="G2">
-        <v>-28.54</v>
+        <v>-29.11</v>
       </c>
       <c r="H2">
-        <v>13.36</v>
+        <v>12.45</v>
       </c>
       <c r="I2">
-        <v>2.65</v>
+        <v>2.41</v>
       </c>
       <c r="J2">
-        <v>-4.85</v>
+        <v>-6.87</v>
       </c>
       <c r="K2">
-        <v>-4.07</v>
+        <v>-4.57</v>
       </c>
       <c r="L2">
-        <v>10.96</v>
+        <v>11.71</v>
       </c>
       <c r="M2">
-        <v>17.93</v>
+        <v>18.55</v>
       </c>
       <c r="N2">
         <v>99</v>
@@ -927,19 +927,19 @@
         <v>67</v>
       </c>
       <c r="P2">
-        <v>146.74</v>
+        <v>147.44</v>
       </c>
       <c r="Q2">
-        <v>152.87</v>
+        <v>152.11</v>
       </c>
       <c r="R2">
-        <v>163.99</v>
+        <v>163.39</v>
       </c>
       <c r="S2">
-        <v>168.79</v>
+        <v>168.65</v>
       </c>
       <c r="T2">
-        <v>-11.78</v>
+        <v>-12.41</v>
       </c>
       <c r="U2" t="s">
         <v>43</v>
@@ -954,34 +954,34 @@
         <v>0</v>
       </c>
       <c r="Y2">
-        <v>40.67</v>
+        <v>39.1</v>
       </c>
       <c r="Z2">
-        <v>-4.79</v>
+        <v>-4.56</v>
       </c>
       <c r="AA2">
-        <v>-4.83</v>
+        <v>-4.78</v>
       </c>
       <c r="AB2">
-        <v>0.05</v>
+        <v>0.22</v>
       </c>
       <c r="AC2">
-        <v>75.04000000000001</v>
+        <v>92.09</v>
       </c>
       <c r="AD2">
-        <v>52.41</v>
+        <v>74.37</v>
       </c>
       <c r="AE2">
-        <v>3.99</v>
+        <v>3.86</v>
       </c>
       <c r="AF2">
-        <v>-11.32</v>
+        <v>-31.82</v>
       </c>
       <c r="AG2">
-        <v>165.49</v>
+        <v>163.97</v>
       </c>
       <c r="AH2">
-        <v>140.25</v>
+        <v>140.24</v>
       </c>
       <c r="AI2">
         <v>157.56</v>
@@ -990,7 +990,7 @@
         <v>45</v>
       </c>
       <c r="AK2">
-        <v>53.65</v>
+        <v>50.39</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1001,10 +1001,10 @@
         <v>42</v>
       </c>
       <c r="C3">
-        <v>365.2</v>
+        <v>368.7</v>
       </c>
       <c r="D3">
-        <v>0.83</v>
+        <v>0.96</v>
       </c>
       <c r="E3">
         <v>456.15</v>
@@ -1013,46 +1013,46 @@
         <v>225</v>
       </c>
       <c r="G3">
-        <v>-19.94</v>
+        <v>-19.17</v>
       </c>
       <c r="H3">
-        <v>62.31</v>
+        <v>63.87</v>
       </c>
       <c r="I3">
-        <v>2.15</v>
+        <v>5.6</v>
       </c>
       <c r="J3">
-        <v>-14.75</v>
+        <v>-19.17</v>
       </c>
       <c r="K3">
-        <v>-9.539999999999999</v>
+        <v>-8.08</v>
       </c>
       <c r="L3">
-        <v>3.66</v>
+        <v>4.98</v>
       </c>
       <c r="M3">
-        <v>1.82</v>
+        <v>2.83</v>
       </c>
       <c r="N3">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="O3">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="P3">
-        <v>359.61</v>
+        <v>363.52</v>
       </c>
       <c r="Q3">
-        <v>376.28</v>
+        <v>372.41</v>
       </c>
       <c r="R3">
-        <v>399.93</v>
+        <v>399.09</v>
       </c>
       <c r="S3">
-        <v>341.34</v>
+        <v>341.73</v>
       </c>
       <c r="T3">
-        <v>6.99</v>
+        <v>7.89</v>
       </c>
       <c r="U3" t="s">
         <v>43</v>
@@ -1067,34 +1067,34 @@
         <v>2</v>
       </c>
       <c r="Y3">
-        <v>43.33</v>
+        <v>45.05</v>
       </c>
       <c r="Z3">
+        <v>-12.21</v>
+      </c>
+      <c r="AA3">
         <v>-13.42</v>
       </c>
-      <c r="AA3">
-        <v>-13.72</v>
-      </c>
       <c r="AB3">
-        <v>0.3</v>
+        <v>1.21</v>
       </c>
       <c r="AC3">
         <v>95.48999999999999</v>
       </c>
       <c r="AD3">
-        <v>82.17</v>
+        <v>91.97</v>
       </c>
       <c r="AE3">
-        <v>16.08</v>
+        <v>16.87</v>
       </c>
       <c r="AF3">
-        <v>-82.48999999999999</v>
+        <v>-7.91</v>
       </c>
       <c r="AG3">
-        <v>435.35</v>
+        <v>421.52</v>
       </c>
       <c r="AH3">
-        <v>317.21</v>
+        <v>323.3</v>
       </c>
       <c r="AI3">
         <v>401.23</v>
@@ -1103,7 +1103,7 @@
         <v>45</v>
       </c>
       <c r="AK3">
-        <v>31.36</v>
+        <v>30.38</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1114,10 +1114,10 @@
         <v>42</v>
       </c>
       <c r="C4">
-        <v>357.75</v>
+        <v>351</v>
       </c>
       <c r="D4">
-        <v>-0.01</v>
+        <v>-1.89</v>
       </c>
       <c r="E4">
         <v>534</v>
@@ -1126,46 +1126,46 @@
         <v>344.7</v>
       </c>
       <c r="G4">
-        <v>-33.01</v>
+        <v>-34.27</v>
       </c>
       <c r="H4">
-        <v>3.79</v>
+        <v>1.83</v>
       </c>
       <c r="I4">
-        <v>0.62</v>
+        <v>-0.27</v>
       </c>
       <c r="J4">
-        <v>-7.33</v>
+        <v>-9.15</v>
       </c>
       <c r="K4">
-        <v>-17.1</v>
+        <v>-18.32</v>
       </c>
       <c r="L4">
-        <v>-27.63</v>
+        <v>-28.85</v>
       </c>
       <c r="M4">
-        <v>-22.6</v>
+        <v>-22.87</v>
       </c>
       <c r="N4">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="O4">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="P4">
-        <v>357.59</v>
+        <v>357.4</v>
       </c>
       <c r="Q4">
-        <v>366.69</v>
+        <v>365.27</v>
       </c>
       <c r="R4">
-        <v>386.87</v>
+        <v>385.43</v>
       </c>
       <c r="S4">
-        <v>402.91</v>
+        <v>402.43</v>
       </c>
       <c r="T4">
-        <v>-11.21</v>
+        <v>-12.78</v>
       </c>
       <c r="U4" t="s">
         <v>43</v>
@@ -1180,43 +1180,43 @@
         <v>0</v>
       </c>
       <c r="Y4">
-        <v>34.04</v>
+        <v>29.32</v>
       </c>
       <c r="Z4">
-        <v>-8.84</v>
+        <v>-9.039999999999999</v>
       </c>
       <c r="AA4">
-        <v>-9.279999999999999</v>
+        <v>-9.23</v>
       </c>
       <c r="AB4">
-        <v>0.44</v>
+        <v>0.19</v>
       </c>
       <c r="AC4">
-        <v>86.47</v>
+        <v>69.42</v>
       </c>
       <c r="AD4">
-        <v>82.14</v>
+        <v>83.06</v>
       </c>
       <c r="AE4">
-        <v>9.609999999999999</v>
+        <v>9.68</v>
       </c>
       <c r="AF4">
-        <v>52.42</v>
+        <v>20.49</v>
       </c>
       <c r="AG4">
-        <v>384.4</v>
+        <v>383.24</v>
       </c>
       <c r="AH4">
-        <v>348.98</v>
+        <v>347.3</v>
       </c>
       <c r="AI4">
-        <v>384.24</v>
+        <v>381.44</v>
       </c>
       <c r="AJ4" t="s">
         <v>45</v>
       </c>
       <c r="AK4">
-        <v>50.29</v>
+        <v>51.45</v>
       </c>
     </row>
     <row r="5" spans="1:37">
@@ -1227,10 +1227,10 @@
         <v>42</v>
       </c>
       <c r="C5">
-        <v>877</v>
+        <v>863.2</v>
       </c>
       <c r="D5">
-        <v>-0.95</v>
+        <v>-1.57</v>
       </c>
       <c r="E5">
         <v>1069.3</v>
@@ -1239,46 +1239,46 @@
         <v>739.5</v>
       </c>
       <c r="G5">
-        <v>-17.98</v>
+        <v>-19.27</v>
       </c>
       <c r="H5">
-        <v>18.59</v>
+        <v>16.73</v>
       </c>
       <c r="I5">
-        <v>1.78</v>
+        <v>1.2</v>
       </c>
       <c r="J5">
-        <v>-7.34</v>
+        <v>-9.91</v>
       </c>
       <c r="K5">
-        <v>-14.62</v>
+        <v>-16.43</v>
       </c>
       <c r="L5">
-        <v>15.41</v>
+        <v>15.03</v>
       </c>
       <c r="M5">
-        <v>-5.83</v>
+        <v>-5.72</v>
       </c>
       <c r="N5">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="O5">
         <v>60</v>
       </c>
       <c r="P5">
-        <v>871.75</v>
+        <v>873.79</v>
       </c>
       <c r="Q5">
-        <v>899.8099999999999</v>
+        <v>894.66</v>
       </c>
       <c r="R5">
-        <v>961.34</v>
+        <v>958.28</v>
       </c>
       <c r="S5">
-        <v>925.5</v>
+        <v>925.61</v>
       </c>
       <c r="T5">
-        <v>-5.24</v>
+        <v>-6.74</v>
       </c>
       <c r="U5" t="s">
         <v>43</v>
@@ -1293,34 +1293,34 @@
         <v>1</v>
       </c>
       <c r="Y5">
-        <v>39.97</v>
+        <v>37.05</v>
       </c>
       <c r="Z5">
-        <v>-26.98</v>
+        <v>-26.61</v>
       </c>
       <c r="AA5">
-        <v>-28.6</v>
+        <v>-28.2</v>
       </c>
       <c r="AB5">
-        <v>1.62</v>
+        <v>1.59</v>
       </c>
       <c r="AC5">
-        <v>90.23</v>
+        <v>87.84</v>
       </c>
       <c r="AD5">
-        <v>81</v>
+        <v>88.75</v>
       </c>
       <c r="AE5">
-        <v>22.37</v>
+        <v>22.41</v>
       </c>
       <c r="AF5">
-        <v>-38.43</v>
+        <v>-53.96</v>
       </c>
       <c r="AG5">
-        <v>970.28</v>
+        <v>959.51</v>
       </c>
       <c r="AH5">
-        <v>829.34</v>
+        <v>829.8099999999999</v>
       </c>
       <c r="AI5">
         <v>921.99</v>
@@ -1329,7 +1329,7 @@
         <v>45</v>
       </c>
       <c r="AK5">
-        <v>45.18</v>
+        <v>43.7</v>
       </c>
     </row>
     <row r="6" spans="1:37">
@@ -1343,7 +1343,7 @@
         <v>2.6</v>
       </c>
       <c r="D6">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="E6">
         <v>3.38</v>
@@ -1361,22 +1361,22 @@
         <v>0.78</v>
       </c>
       <c r="J6">
-        <v>-10.03</v>
+        <v>-7.8</v>
       </c>
       <c r="K6">
-        <v>10.17</v>
+        <v>10.64</v>
       </c>
       <c r="L6">
-        <v>-18.75</v>
+        <v>-17.98</v>
       </c>
       <c r="M6">
-        <v>0.63</v>
+        <v>1.45</v>
       </c>
       <c r="N6">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="O6">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="P6">
         <v>2.59</v>
@@ -1385,13 +1385,13 @@
         <v>2.63</v>
       </c>
       <c r="R6">
-        <v>2.66</v>
+        <v>2.67</v>
       </c>
       <c r="S6">
         <v>2.64</v>
       </c>
       <c r="T6">
-        <v>-1.43</v>
+        <v>-1.36</v>
       </c>
       <c r="U6" t="s">
         <v>43</v>
@@ -1409,7 +1409,7 @@
         <v>45.54</v>
       </c>
       <c r="Z6">
-        <v>-0.04</v>
+        <v>-0.03</v>
       </c>
       <c r="AA6">
         <v>-0.03</v>
@@ -1418,36 +1418,96 @@
         <v>-0</v>
       </c>
       <c r="AC6">
-        <v>83.23999999999999</v>
+        <v>83.27</v>
       </c>
       <c r="AD6">
-        <v>66.84</v>
+        <v>76.11</v>
       </c>
       <c r="AE6">
         <v>0.11</v>
       </c>
       <c r="AF6">
-        <v>-7.36</v>
+        <v>-23.62</v>
       </c>
       <c r="AG6">
-        <v>2.79</v>
+        <v>2.77</v>
       </c>
       <c r="AH6">
         <v>2.48</v>
       </c>
       <c r="AI6">
-        <v>2.92</v>
+        <v>2.91</v>
       </c>
       <c r="AJ6" t="s">
         <v>45</v>
       </c>
       <c r="AK6">
-        <v>27.52</v>
+        <v>27.13</v>
       </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AK6"/>
   <conditionalFormatting sqref="AF2:AF6">
+    <cfRule type="colorScale" priority="13">
+      <colorScale>
+        <cfvo type="min" val="0"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max" val="0"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFFFFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D2:D6">
+    <cfRule type="colorScale" priority="7">
+      <colorScale>
+        <cfvo type="min" val="0"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max" val="0"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFFFFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I2:I6">
+    <cfRule type="colorScale" priority="8">
+      <colorScale>
+        <cfvo type="min" val="0"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max" val="0"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFFFFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J2:J6">
+    <cfRule type="colorScale" priority="9">
+      <colorScale>
+        <cfvo type="min" val="0"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max" val="0"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFFFFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K2:K6">
+    <cfRule type="colorScale" priority="10">
+      <colorScale>
+        <cfvo type="min" val="0"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max" val="0"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFFFFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="L2:L6">
     <cfRule type="colorScale" priority="11">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -1459,8 +1519,14 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D2:D6">
-    <cfRule type="colorScale" priority="5">
+  <conditionalFormatting sqref="N2:N6">
+    <cfRule type="cellIs" dxfId="2" priority="5" operator="greaterThanOrEqual">
+      <formula>80</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="3" priority="6" operator="lessThanOrEqual">
+      <formula>20</formula>
+    </cfRule>
+    <cfRule type="colorScale" priority="12">
       <colorScale>
         <cfvo type="min" val="0"/>
         <cfvo type="percentile" val="50"/>
@@ -1471,72 +1537,6 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I2:I6">
-    <cfRule type="colorScale" priority="6">
-      <colorScale>
-        <cfvo type="min" val="0"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max" val="0"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFFFFFF"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="J2:J6">
-    <cfRule type="colorScale" priority="7">
-      <colorScale>
-        <cfvo type="min" val="0"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max" val="0"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFFFFFF"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="K2:K6">
-    <cfRule type="colorScale" priority="8">
-      <colorScale>
-        <cfvo type="min" val="0"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max" val="0"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFFFFFF"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="L2:L6">
-    <cfRule type="colorScale" priority="9">
-      <colorScale>
-        <cfvo type="min" val="0"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max" val="0"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFFFFFF"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="N2:N6">
-    <cfRule type="colorScale" priority="10">
-      <colorScale>
-        <cfvo type="min" val="0"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max" val="0"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFFFFFF"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="2" priority="18" operator="greaterThanOrEqual">
-      <formula>80</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="3" priority="19" operator="lessThanOrEqual">
-      <formula>20</formula>
-    </cfRule>
-  </conditionalFormatting>
   <conditionalFormatting sqref="T2:T6">
     <cfRule type="cellIs" dxfId="1" priority="3" operator="greaterThan">
       <formula>0</formula>
@@ -1546,26 +1546,26 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="U2:U6">
-    <cfRule type="containsText" dxfId="1" priority="12" operator="containsText" text="Yes">
+    <cfRule type="containsText" dxfId="1" priority="14" operator="containsText" text="Yes">
       <formula>NOT(ISERROR(SEARCH("Yes",U2)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="0" priority="13" operator="containsText" text="No">
+    <cfRule type="containsText" dxfId="0" priority="15" operator="containsText" text="No">
       <formula>NOT(ISERROR(SEARCH("No",U2)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V2:V6">
-    <cfRule type="containsText" dxfId="1" priority="14" operator="containsText" text="Yes">
+    <cfRule type="containsText" dxfId="1" priority="16" operator="containsText" text="Yes">
       <formula>NOT(ISERROR(SEARCH("Yes",V2)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="0" priority="15" operator="containsText" text="No">
+    <cfRule type="containsText" dxfId="0" priority="17" operator="containsText" text="No">
       <formula>NOT(ISERROR(SEARCH("No",V2)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="W2:W6">
-    <cfRule type="containsText" dxfId="1" priority="16" operator="containsText" text="Yes">
+    <cfRule type="containsText" dxfId="1" priority="18" operator="containsText" text="Yes">
       <formula>NOT(ISERROR(SEARCH("Yes",W2)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="0" priority="17" operator="containsText" text="No">
+    <cfRule type="containsText" dxfId="0" priority="19" operator="containsText" text="No">
       <formula>NOT(ISERROR(SEARCH("No",W2)))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -1640,13 +1640,13 @@
         <v>9</v>
       </c>
       <c r="C7" s="5">
-        <v>-5.41</v>
+        <v>-4.85</v>
       </c>
       <c r="D7" s="5">
-        <v>-4.85</v>
+        <v>-6.87</v>
       </c>
       <c r="E7" s="6">
-        <v>0.5600000000000001</v>
+        <v>-2.02</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -1657,13 +1657,13 @@
         <v>9</v>
       </c>
       <c r="C8" s="5">
-        <v>-16.86</v>
+        <v>-14.75</v>
       </c>
       <c r="D8" s="5">
-        <v>-14.75</v>
+        <v>-19.17</v>
       </c>
       <c r="E8" s="6">
-        <v>2.11</v>
+        <v>-4.42</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -1674,13 +1674,13 @@
         <v>9</v>
       </c>
       <c r="C9" s="5">
-        <v>-6.24</v>
+        <v>-7.33</v>
       </c>
       <c r="D9" s="5">
-        <v>-7.33</v>
-      </c>
-      <c r="E9" s="7">
-        <v>-1.09</v>
+        <v>-9.15</v>
+      </c>
+      <c r="E9" s="6">
+        <v>-1.82</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -1691,13 +1691,13 @@
         <v>9</v>
       </c>
       <c r="C10" s="5">
-        <v>-7.43</v>
+        <v>-7.34</v>
       </c>
       <c r="D10" s="5">
-        <v>-7.34</v>
+        <v>-9.91</v>
       </c>
       <c r="E10" s="6">
-        <v>0.09</v>
+        <v>-2.57</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -1708,13 +1708,13 @@
         <v>9</v>
       </c>
       <c r="C11" s="5">
-        <v>-6.55</v>
+        <v>-10.03</v>
       </c>
       <c r="D11" s="5">
-        <v>-10.03</v>
+        <v>-7.8</v>
       </c>
       <c r="E11" s="7">
-        <v>-3.48</v>
+        <v>2.23</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -1725,13 +1725,13 @@
         <v>8</v>
       </c>
       <c r="C12" s="5">
-        <v>2.18</v>
+        <v>2.65</v>
       </c>
       <c r="D12" s="5">
-        <v>2.65</v>
+        <v>2.41</v>
       </c>
       <c r="E12" s="6">
-        <v>0.47</v>
+        <v>-0.24</v>
       </c>
     </row>
     <row r="13" spans="1:6">
@@ -1742,13 +1742,13 @@
         <v>8</v>
       </c>
       <c r="C13" s="5">
-        <v>1.29</v>
+        <v>2.15</v>
       </c>
       <c r="D13" s="5">
-        <v>2.15</v>
-      </c>
-      <c r="E13" s="6">
-        <v>0.86</v>
+        <v>5.6</v>
+      </c>
+      <c r="E13" s="7">
+        <v>3.45</v>
       </c>
     </row>
     <row r="14" spans="1:6">
@@ -1759,13 +1759,13 @@
         <v>8</v>
       </c>
       <c r="C14" s="5">
-        <v>-0.32</v>
+        <v>0.62</v>
       </c>
       <c r="D14" s="5">
-        <v>0.62</v>
+        <v>-0.27</v>
       </c>
       <c r="E14" s="6">
-        <v>0.9399999999999999</v>
+        <v>-0.89</v>
       </c>
     </row>
     <row r="15" spans="1:6">
@@ -1776,455 +1776,455 @@
         <v>8</v>
       </c>
       <c r="C15" s="5">
-        <v>2.48</v>
+        <v>1.78</v>
       </c>
       <c r="D15" s="5">
-        <v>1.78</v>
-      </c>
-      <c r="E15" s="7">
-        <v>-0.7</v>
+        <v>1.2</v>
+      </c>
+      <c r="E15" s="6">
+        <v>-0.58</v>
       </c>
     </row>
     <row r="16" spans="1:6">
       <c r="A16" s="3" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="C16" s="5">
-        <v>-0.39</v>
+        <v>10.96</v>
       </c>
       <c r="D16" s="5">
-        <v>0.78</v>
-      </c>
-      <c r="E16" s="6">
-        <v>1.17</v>
+        <v>11.71</v>
+      </c>
+      <c r="E16" s="7">
+        <v>0.75</v>
       </c>
     </row>
     <row r="17" spans="1:5">
       <c r="A17" s="3" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B17" s="3" t="s">
         <v>11</v>
       </c>
       <c r="C17" s="5">
-        <v>10.31</v>
+        <v>3.66</v>
       </c>
       <c r="D17" s="5">
-        <v>10.96</v>
-      </c>
-      <c r="E17" s="6">
-        <v>0.65</v>
+        <v>4.98</v>
+      </c>
+      <c r="E17" s="7">
+        <v>1.32</v>
       </c>
     </row>
     <row r="18" spans="1:5">
       <c r="A18" s="3" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B18" s="3" t="s">
         <v>11</v>
       </c>
       <c r="C18" s="5">
-        <v>3.13</v>
+        <v>-27.63</v>
       </c>
       <c r="D18" s="5">
-        <v>3.66</v>
+        <v>-28.85</v>
       </c>
       <c r="E18" s="6">
-        <v>0.53</v>
+        <v>-1.22</v>
       </c>
     </row>
     <row r="19" spans="1:5">
       <c r="A19" s="3" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B19" s="3" t="s">
         <v>11</v>
       </c>
       <c r="C19" s="5">
-        <v>-27.64</v>
+        <v>15.41</v>
       </c>
       <c r="D19" s="5">
-        <v>-27.63</v>
+        <v>15.03</v>
       </c>
       <c r="E19" s="6">
-        <v>0.01</v>
+        <v>-0.38</v>
       </c>
     </row>
     <row r="20" spans="1:5">
       <c r="A20" s="3" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B20" s="3" t="s">
         <v>11</v>
       </c>
       <c r="C20" s="5">
-        <v>15.99</v>
+        <v>-18.75</v>
       </c>
       <c r="D20" s="5">
-        <v>15.41</v>
+        <v>-17.98</v>
       </c>
       <c r="E20" s="7">
-        <v>-0.58</v>
+        <v>0.77</v>
       </c>
     </row>
     <row r="21" spans="1:5">
       <c r="A21" s="3" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C21" s="5">
-        <v>-20.19</v>
+        <v>-4.07</v>
       </c>
       <c r="D21" s="5">
-        <v>-18.75</v>
+        <v>-4.57</v>
       </c>
       <c r="E21" s="6">
-        <v>1.44</v>
+        <v>-0.5</v>
       </c>
     </row>
     <row r="22" spans="1:5">
       <c r="A22" s="3" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B22" s="3" t="s">
         <v>10</v>
       </c>
       <c r="C22" s="5">
-        <v>-4.32</v>
+        <v>-9.539999999999999</v>
       </c>
       <c r="D22" s="5">
-        <v>-4.07</v>
-      </c>
-      <c r="E22" s="6">
-        <v>0.25</v>
+        <v>-8.08</v>
+      </c>
+      <c r="E22" s="7">
+        <v>1.46</v>
       </c>
     </row>
     <row r="23" spans="1:5">
       <c r="A23" s="3" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B23" s="3" t="s">
         <v>10</v>
       </c>
       <c r="C23" s="5">
-        <v>-10.11</v>
+        <v>-17.1</v>
       </c>
       <c r="D23" s="5">
-        <v>-9.539999999999999</v>
+        <v>-18.32</v>
       </c>
       <c r="E23" s="6">
-        <v>0.57</v>
+        <v>-1.22</v>
       </c>
     </row>
     <row r="24" spans="1:5">
       <c r="A24" s="3" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B24" s="3" t="s">
         <v>10</v>
       </c>
       <c r="C24" s="5">
-        <v>-18.15</v>
+        <v>-14.62</v>
       </c>
       <c r="D24" s="5">
-        <v>-17.1</v>
+        <v>-16.43</v>
       </c>
       <c r="E24" s="6">
-        <v>1.05</v>
+        <v>-1.81</v>
       </c>
     </row>
     <row r="25" spans="1:5">
       <c r="A25" s="3" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B25" s="3" t="s">
         <v>10</v>
       </c>
       <c r="C25" s="5">
-        <v>-12.64</v>
+        <v>10.17</v>
       </c>
       <c r="D25" s="5">
-        <v>-14.62</v>
+        <v>10.64</v>
       </c>
       <c r="E25" s="7">
-        <v>-1.98</v>
+        <v>0.47</v>
       </c>
     </row>
     <row r="26" spans="1:5">
       <c r="A26" s="3" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C26" s="5">
-        <v>6.64</v>
+        <v>-28.54</v>
       </c>
       <c r="D26" s="5">
-        <v>10.17</v>
+        <v>-29.11</v>
       </c>
       <c r="E26" s="6">
-        <v>3.53</v>
+        <v>-0.57</v>
       </c>
     </row>
     <row r="27" spans="1:5">
       <c r="A27" s="3" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B27" s="3" t="s">
         <v>6</v>
       </c>
       <c r="C27" s="5">
-        <v>-28.89</v>
+        <v>-19.94</v>
       </c>
       <c r="D27" s="5">
-        <v>-28.54</v>
-      </c>
-      <c r="E27" s="6">
-        <v>0.35</v>
+        <v>-19.17</v>
+      </c>
+      <c r="E27" s="7">
+        <v>0.77</v>
       </c>
     </row>
     <row r="28" spans="1:5">
       <c r="A28" s="3" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B28" s="3" t="s">
         <v>6</v>
       </c>
       <c r="C28" s="5">
-        <v>-20.6</v>
+        <v>-33.01</v>
       </c>
       <c r="D28" s="5">
-        <v>-19.94</v>
+        <v>-34.27</v>
       </c>
       <c r="E28" s="6">
-        <v>0.66</v>
+        <v>-1.26</v>
       </c>
     </row>
     <row r="29" spans="1:5">
       <c r="A29" s="3" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B29" s="3" t="s">
         <v>6</v>
       </c>
       <c r="C29" s="5">
-        <v>-33</v>
+        <v>-17.98</v>
       </c>
       <c r="D29" s="5">
-        <v>-33.01</v>
-      </c>
-      <c r="E29" s="7">
-        <v>-0.01</v>
+        <v>-19.27</v>
+      </c>
+      <c r="E29" s="6">
+        <v>-1.29</v>
       </c>
     </row>
     <row r="30" spans="1:5">
       <c r="A30" s="3" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="C30" s="5">
-        <v>-17.2</v>
+        <v>148.91</v>
       </c>
       <c r="D30" s="5">
-        <v>-17.98</v>
-      </c>
-      <c r="E30" s="7">
-        <v>-0.78</v>
+        <v>147.72</v>
+      </c>
+      <c r="E30" s="6">
+        <v>-1.19</v>
       </c>
     </row>
     <row r="31" spans="1:5">
       <c r="A31" s="3" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="C31" s="5">
-        <v>-23.96</v>
+        <v>365.2</v>
       </c>
       <c r="D31" s="5">
-        <v>-23.08</v>
-      </c>
-      <c r="E31" s="6">
-        <v>0.88</v>
+        <v>368.7</v>
+      </c>
+      <c r="E31" s="7">
+        <v>3.5</v>
       </c>
     </row>
     <row r="32" spans="1:5">
       <c r="A32" s="3" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B32" s="3" t="s">
         <v>2</v>
       </c>
       <c r="C32" s="5">
-        <v>148.18</v>
+        <v>357.75</v>
       </c>
       <c r="D32" s="5">
-        <v>148.91</v>
+        <v>351</v>
       </c>
       <c r="E32" s="6">
-        <v>0.73</v>
+        <v>-6.75</v>
       </c>
     </row>
     <row r="33" spans="1:5">
       <c r="A33" s="3" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B33" s="3" t="s">
         <v>2</v>
       </c>
       <c r="C33" s="5">
-        <v>362.2</v>
+        <v>877</v>
       </c>
       <c r="D33" s="5">
-        <v>365.2</v>
+        <v>863.2</v>
       </c>
       <c r="E33" s="6">
-        <v>3</v>
+        <v>-13.8</v>
       </c>
     </row>
     <row r="34" spans="1:5">
       <c r="A34" s="3" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="C34" s="5">
-        <v>357.8</v>
+        <v>60</v>
       </c>
       <c r="D34" s="5">
-        <v>357.75</v>
-      </c>
-      <c r="E34" s="7">
-        <v>-0.05</v>
+        <v>40</v>
+      </c>
+      <c r="E34" s="6">
+        <v>-20</v>
       </c>
     </row>
     <row r="35" spans="1:5">
       <c r="A35" s="3" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="C35" s="5">
-        <v>885.4</v>
+        <v>21</v>
       </c>
       <c r="D35" s="5">
-        <v>877</v>
-      </c>
-      <c r="E35" s="7">
-        <v>-8.4</v>
+        <v>20</v>
+      </c>
+      <c r="E35" s="6">
+        <v>-1</v>
       </c>
     </row>
     <row r="36" spans="1:5">
       <c r="A36" s="3" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="C36" s="5">
-        <v>2.57</v>
+        <v>79</v>
       </c>
       <c r="D36" s="5">
-        <v>2.6</v>
-      </c>
-      <c r="E36" s="6">
-        <v>0.03</v>
+        <v>80</v>
+      </c>
+      <c r="E36" s="7">
+        <v>1</v>
       </c>
     </row>
     <row r="37" spans="1:5">
       <c r="A37" s="3" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="C37" s="5">
-        <v>39.28</v>
+        <v>40</v>
       </c>
       <c r="D37" s="5">
-        <v>40.67</v>
-      </c>
-      <c r="E37" s="6">
-        <v>1.39</v>
+        <v>60</v>
+      </c>
+      <c r="E37" s="7">
+        <v>20</v>
       </c>
     </row>
     <row r="38" spans="1:5">
       <c r="A38" s="3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B38" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C38" s="5">
-        <v>41.89</v>
+        <v>40.67</v>
       </c>
       <c r="D38" s="5">
-        <v>43.33</v>
+        <v>39.1</v>
       </c>
       <c r="E38" s="6">
-        <v>1.44</v>
+        <v>-1.57</v>
       </c>
     </row>
     <row r="39" spans="1:5">
       <c r="A39" s="3" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B39" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C39" s="5">
-        <v>34.08</v>
+        <v>43.33</v>
       </c>
       <c r="D39" s="5">
-        <v>34.04</v>
+        <v>45.05</v>
       </c>
       <c r="E39" s="7">
-        <v>-0.04</v>
+        <v>1.72</v>
       </c>
     </row>
     <row r="40" spans="1:5">
       <c r="A40" s="3" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B40" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C40" s="5">
-        <v>41.82</v>
+        <v>34.04</v>
       </c>
       <c r="D40" s="5">
-        <v>39.97</v>
-      </c>
-      <c r="E40" s="7">
-        <v>-1.85</v>
+        <v>29.32</v>
+      </c>
+      <c r="E40" s="6">
+        <v>-4.72</v>
       </c>
     </row>
     <row r="41" spans="1:5">
       <c r="A41" s="3" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B41" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C41" s="5">
-        <v>42.27</v>
+        <v>39.97</v>
       </c>
       <c r="D41" s="5">
-        <v>45.54</v>
+        <v>37.05</v>
       </c>
       <c r="E41" s="6">
-        <v>3.27</v>
+        <v>-2.92</v>
       </c>
     </row>
     <row r="42" spans="1:5">
@@ -2235,13 +2235,13 @@
         <v>31</v>
       </c>
       <c r="C42" s="5">
-        <v>72</v>
+        <v>-11.32</v>
       </c>
       <c r="D42" s="5">
-        <v>-11.32</v>
-      </c>
-      <c r="E42" s="7">
-        <v>-83.31999999999999</v>
+        <v>-31.82</v>
+      </c>
+      <c r="E42" s="6">
+        <v>-20.5</v>
       </c>
     </row>
     <row r="43" spans="1:5">
@@ -2252,13 +2252,13 @@
         <v>31</v>
       </c>
       <c r="C43" s="5">
-        <v>-86.95999999999999</v>
+        <v>-82.48999999999999</v>
       </c>
       <c r="D43" s="5">
-        <v>-82.48999999999999</v>
-      </c>
-      <c r="E43" s="6">
-        <v>4.47</v>
+        <v>-7.91</v>
+      </c>
+      <c r="E43" s="7">
+        <v>74.58</v>
       </c>
     </row>
     <row r="44" spans="1:5">
@@ -2269,13 +2269,13 @@
         <v>31</v>
       </c>
       <c r="C44" s="5">
-        <v>35.31</v>
+        <v>52.42</v>
       </c>
       <c r="D44" s="5">
-        <v>52.42</v>
+        <v>20.49</v>
       </c>
       <c r="E44" s="6">
-        <v>17.11</v>
+        <v>-31.93</v>
       </c>
     </row>
     <row r="45" spans="1:5">
@@ -2286,13 +2286,13 @@
         <v>31</v>
       </c>
       <c r="C45" s="5">
-        <v>-27.2</v>
+        <v>-38.43</v>
       </c>
       <c r="D45" s="5">
-        <v>-38.43</v>
-      </c>
-      <c r="E45" s="7">
-        <v>-11.23</v>
+        <v>-53.96</v>
+      </c>
+      <c r="E45" s="6">
+        <v>-15.53</v>
       </c>
     </row>
     <row r="46" spans="1:5">
@@ -2303,13 +2303,13 @@
         <v>31</v>
       </c>
       <c r="C46" s="5">
-        <v>8.19</v>
+        <v>-7.36</v>
       </c>
       <c r="D46" s="5">
-        <v>-7.36</v>
-      </c>
-      <c r="E46" s="7">
-        <v>-15.55</v>
+        <v>-23.62</v>
+      </c>
+      <c r="E46" s="6">
+        <v>-16.26</v>
       </c>
     </row>
   </sheetData>
@@ -2374,16 +2374,16 @@
         <v>5</v>
       </c>
       <c r="D2" s="10">
-        <v>40.7</v>
+        <v>39.2</v>
       </c>
       <c r="E2" s="10">
         <v>20</v>
       </c>
       <c r="F2" s="10">
-        <v>-8.9</v>
+        <v>-10.6</v>
       </c>
       <c r="G2" s="10">
-        <v>-7</v>
+        <v>-7.4</v>
       </c>
       <c r="H2" s="10">
         <v>59.8</v>
@@ -2508,19 +2508,19 @@
     </row>
     <row r="2" spans="1:5">
       <c r="A2" s="13">
-        <v>0.1793</v>
+        <v>0.1855</v>
       </c>
       <c r="B2" s="13">
-        <v>0.0182</v>
+        <v>0.0283</v>
       </c>
       <c r="C2" s="13">
-        <v>0.0063</v>
+        <v>0.0145</v>
       </c>
       <c r="D2" s="13">
-        <v>-0.0583</v>
+        <v>-0.0572</v>
       </c>
       <c r="E2" s="13">
-        <v>-0.226</v>
+        <v>-0.2287</v>
       </c>
     </row>
   </sheetData>

--- a/HINDUJA_GROUP_Technical_Metrics.xlsx
+++ b/HINDUJA_GROUP_Technical_Metrics.xlsx
@@ -888,10 +888,10 @@
         <v>42</v>
       </c>
       <c r="C2">
-        <v>147.72</v>
+        <v>146.74</v>
       </c>
       <c r="D2">
-        <v>-0.8</v>
+        <v>-0.66</v>
       </c>
       <c r="E2">
         <v>208.37</v>
@@ -900,46 +900,46 @@
         <v>131.36</v>
       </c>
       <c r="G2">
-        <v>-29.11</v>
+        <v>-29.58</v>
       </c>
       <c r="H2">
-        <v>12.45</v>
+        <v>11.71</v>
       </c>
       <c r="I2">
-        <v>2.41</v>
+        <v>-0.43</v>
       </c>
       <c r="J2">
-        <v>-6.87</v>
+        <v>-9.98</v>
       </c>
       <c r="K2">
-        <v>-4.57</v>
+        <v>-4.68</v>
       </c>
       <c r="L2">
-        <v>11.71</v>
+        <v>10.73</v>
       </c>
       <c r="M2">
-        <v>18.55</v>
+        <v>18.16</v>
       </c>
       <c r="N2">
         <v>99</v>
       </c>
       <c r="O2">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="P2">
-        <v>147.44</v>
+        <v>147.31</v>
       </c>
       <c r="Q2">
-        <v>152.11</v>
+        <v>151.36</v>
       </c>
       <c r="R2">
-        <v>163.39</v>
+        <v>162.78</v>
       </c>
       <c r="S2">
-        <v>168.65</v>
+        <v>168.5</v>
       </c>
       <c r="T2">
-        <v>-12.41</v>
+        <v>-12.91</v>
       </c>
       <c r="U2" t="s">
         <v>43</v>
@@ -954,34 +954,34 @@
         <v>0</v>
       </c>
       <c r="Y2">
-        <v>39.1</v>
+        <v>37.8</v>
       </c>
       <c r="Z2">
-        <v>-4.56</v>
+        <v>-4.41</v>
       </c>
       <c r="AA2">
-        <v>-4.78</v>
+        <v>-4.71</v>
       </c>
       <c r="AB2">
-        <v>0.22</v>
+        <v>0.29</v>
       </c>
       <c r="AC2">
-        <v>92.09</v>
+        <v>87.66</v>
       </c>
       <c r="AD2">
-        <v>74.37</v>
+        <v>84.93000000000001</v>
       </c>
       <c r="AE2">
-        <v>3.86</v>
+        <v>3.89</v>
       </c>
       <c r="AF2">
-        <v>-31.82</v>
+        <v>-35.59</v>
       </c>
       <c r="AG2">
-        <v>163.97</v>
+        <v>162.53</v>
       </c>
       <c r="AH2">
-        <v>140.24</v>
+        <v>140.18</v>
       </c>
       <c r="AI2">
         <v>157.56</v>
@@ -990,7 +990,7 @@
         <v>45</v>
       </c>
       <c r="AK2">
-        <v>50.39</v>
+        <v>49.99</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1001,10 +1001,10 @@
         <v>42</v>
       </c>
       <c r="C3">
-        <v>368.7</v>
+        <v>347.3</v>
       </c>
       <c r="D3">
-        <v>0.96</v>
+        <v>-5.8</v>
       </c>
       <c r="E3">
         <v>456.15</v>
@@ -1013,46 +1013,46 @@
         <v>225</v>
       </c>
       <c r="G3">
-        <v>-19.17</v>
+        <v>-23.86</v>
       </c>
       <c r="H3">
-        <v>63.87</v>
+        <v>54.36</v>
       </c>
       <c r="I3">
-        <v>5.6</v>
+        <v>-2.03</v>
       </c>
       <c r="J3">
-        <v>-19.17</v>
+        <v>-22.15</v>
       </c>
       <c r="K3">
-        <v>-8.08</v>
+        <v>-13.03</v>
       </c>
       <c r="L3">
-        <v>4.98</v>
+        <v>-3.93</v>
       </c>
       <c r="M3">
-        <v>2.83</v>
+        <v>2.29</v>
       </c>
       <c r="N3">
         <v>40</v>
       </c>
       <c r="O3">
-        <v>55</v>
+        <v>45</v>
       </c>
       <c r="P3">
-        <v>363.52</v>
+        <v>362.08</v>
       </c>
       <c r="Q3">
-        <v>372.41</v>
+        <v>367.1</v>
       </c>
       <c r="R3">
-        <v>399.09</v>
+        <v>397.27</v>
       </c>
       <c r="S3">
-        <v>341.73</v>
+        <v>341.99</v>
       </c>
       <c r="T3">
-        <v>7.89</v>
+        <v>1.55</v>
       </c>
       <c r="U3" t="s">
         <v>43</v>
@@ -1067,34 +1067,34 @@
         <v>2</v>
       </c>
       <c r="Y3">
-        <v>45.05</v>
+        <v>37.56</v>
       </c>
       <c r="Z3">
-        <v>-12.21</v>
+        <v>-12.83</v>
       </c>
       <c r="AA3">
-        <v>-13.42</v>
+        <v>-13.3</v>
       </c>
       <c r="AB3">
-        <v>1.21</v>
+        <v>0.47</v>
       </c>
       <c r="AC3">
-        <v>95.48999999999999</v>
+        <v>83.09</v>
       </c>
       <c r="AD3">
-        <v>91.97</v>
+        <v>91.36</v>
       </c>
       <c r="AE3">
-        <v>16.87</v>
+        <v>17.32</v>
       </c>
       <c r="AF3">
-        <v>-7.91</v>
+        <v>-53.66</v>
       </c>
       <c r="AG3">
-        <v>421.52</v>
+        <v>399.41</v>
       </c>
       <c r="AH3">
-        <v>323.3</v>
+        <v>334.8</v>
       </c>
       <c r="AI3">
         <v>401.23</v>
@@ -1103,7 +1103,7 @@
         <v>45</v>
       </c>
       <c r="AK3">
-        <v>30.38</v>
+        <v>26.47</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1114,10 +1114,10 @@
         <v>42</v>
       </c>
       <c r="C4">
-        <v>351</v>
+        <v>348.2</v>
       </c>
       <c r="D4">
-        <v>-1.89</v>
+        <v>-0.8</v>
       </c>
       <c r="E4">
         <v>534</v>
@@ -1126,46 +1126,46 @@
         <v>344.7</v>
       </c>
       <c r="G4">
-        <v>-34.27</v>
+        <v>-34.79</v>
       </c>
       <c r="H4">
-        <v>1.83</v>
+        <v>1.02</v>
       </c>
       <c r="I4">
-        <v>-0.27</v>
+        <v>-2.9</v>
       </c>
       <c r="J4">
-        <v>-9.15</v>
+        <v>-8.220000000000001</v>
       </c>
       <c r="K4">
-        <v>-18.32</v>
+        <v>-19.16</v>
       </c>
       <c r="L4">
-        <v>-28.85</v>
+        <v>-29.03</v>
       </c>
       <c r="M4">
-        <v>-22.87</v>
+        <v>-22.8</v>
       </c>
       <c r="N4">
         <v>20</v>
       </c>
       <c r="O4">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="P4">
-        <v>357.4</v>
+        <v>355.32</v>
       </c>
       <c r="Q4">
-        <v>365.27</v>
+        <v>363.79</v>
       </c>
       <c r="R4">
-        <v>385.43</v>
+        <v>383.82</v>
       </c>
       <c r="S4">
-        <v>402.43</v>
+        <v>401.95</v>
       </c>
       <c r="T4">
-        <v>-12.78</v>
+        <v>-13.37</v>
       </c>
       <c r="U4" t="s">
         <v>43</v>
@@ -1180,43 +1180,43 @@
         <v>0</v>
       </c>
       <c r="Y4">
-        <v>29.32</v>
+        <v>27.62</v>
       </c>
       <c r="Z4">
-        <v>-9.039999999999999</v>
+        <v>-9.32</v>
       </c>
       <c r="AA4">
-        <v>-9.23</v>
+        <v>-9.25</v>
       </c>
       <c r="AB4">
-        <v>0.19</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="AC4">
-        <v>69.42</v>
+        <v>55.39</v>
       </c>
       <c r="AD4">
-        <v>83.06</v>
+        <v>70.43000000000001</v>
       </c>
       <c r="AE4">
-        <v>9.68</v>
+        <v>9.470000000000001</v>
       </c>
       <c r="AF4">
-        <v>20.49</v>
+        <v>-30.11</v>
       </c>
       <c r="AG4">
-        <v>383.24</v>
+        <v>382.29</v>
       </c>
       <c r="AH4">
-        <v>347.3</v>
+        <v>345.29</v>
       </c>
       <c r="AI4">
-        <v>381.44</v>
+        <v>377.54</v>
       </c>
       <c r="AJ4" t="s">
         <v>45</v>
       </c>
       <c r="AK4">
-        <v>51.45</v>
+        <v>52.8</v>
       </c>
     </row>
     <row r="5" spans="1:37">
@@ -1227,10 +1227,10 @@
         <v>42</v>
       </c>
       <c r="C5">
-        <v>863.2</v>
+        <v>849.55</v>
       </c>
       <c r="D5">
-        <v>-1.57</v>
+        <v>-1.58</v>
       </c>
       <c r="E5">
         <v>1069.3</v>
@@ -1239,46 +1239,46 @@
         <v>739.5</v>
       </c>
       <c r="G5">
-        <v>-19.27</v>
+        <v>-20.55</v>
       </c>
       <c r="H5">
-        <v>16.73</v>
+        <v>14.88</v>
       </c>
       <c r="I5">
-        <v>1.2</v>
+        <v>-3.17</v>
       </c>
       <c r="J5">
-        <v>-9.91</v>
+        <v>-12.08</v>
       </c>
       <c r="K5">
-        <v>-16.43</v>
+        <v>-20.11</v>
       </c>
       <c r="L5">
-        <v>15.03</v>
+        <v>14.79</v>
       </c>
       <c r="M5">
-        <v>-5.72</v>
+        <v>-5.87</v>
       </c>
       <c r="N5">
         <v>80</v>
       </c>
       <c r="O5">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="P5">
-        <v>873.79</v>
+        <v>868.23</v>
       </c>
       <c r="Q5">
-        <v>894.66</v>
+        <v>889.34</v>
       </c>
       <c r="R5">
-        <v>958.28</v>
+        <v>954.83</v>
       </c>
       <c r="S5">
-        <v>925.61</v>
+        <v>925.54</v>
       </c>
       <c r="T5">
-        <v>-6.74</v>
+        <v>-8.210000000000001</v>
       </c>
       <c r="U5" t="s">
         <v>43</v>
@@ -1293,43 +1293,43 @@
         <v>1</v>
       </c>
       <c r="Y5">
-        <v>37.05</v>
+        <v>34.39</v>
       </c>
       <c r="Z5">
-        <v>-26.61</v>
+        <v>-27.11</v>
       </c>
       <c r="AA5">
-        <v>-28.2</v>
+        <v>-27.98</v>
       </c>
       <c r="AB5">
-        <v>1.59</v>
+        <v>0.88</v>
       </c>
       <c r="AC5">
-        <v>87.84</v>
+        <v>69.18000000000001</v>
       </c>
       <c r="AD5">
-        <v>88.75</v>
+        <v>82.42</v>
       </c>
       <c r="AE5">
-        <v>22.41</v>
+        <v>23.47</v>
       </c>
       <c r="AF5">
-        <v>-53.96</v>
+        <v>-25.35</v>
       </c>
       <c r="AG5">
-        <v>959.51</v>
+        <v>950.35</v>
       </c>
       <c r="AH5">
-        <v>829.8099999999999</v>
+        <v>828.3200000000001</v>
       </c>
       <c r="AI5">
-        <v>921.99</v>
+        <v>920.22</v>
       </c>
       <c r="AJ5" t="s">
         <v>45</v>
       </c>
       <c r="AK5">
-        <v>43.7</v>
+        <v>45.53</v>
       </c>
     </row>
     <row r="6" spans="1:37">
@@ -1340,10 +1340,10 @@
         <v>42</v>
       </c>
       <c r="C6">
-        <v>2.6</v>
+        <v>2.46</v>
       </c>
       <c r="D6">
-        <v>0</v>
+        <v>-5.38</v>
       </c>
       <c r="E6">
         <v>3.38</v>
@@ -1352,46 +1352,46 @@
         <v>1.84</v>
       </c>
       <c r="G6">
-        <v>-23.08</v>
+        <v>-27.22</v>
       </c>
       <c r="H6">
-        <v>41.3</v>
+        <v>33.7</v>
       </c>
       <c r="I6">
-        <v>0.78</v>
+        <v>-4.65</v>
       </c>
       <c r="J6">
-        <v>-7.8</v>
+        <v>-11.51</v>
       </c>
       <c r="K6">
-        <v>10.64</v>
+        <v>4.68</v>
       </c>
       <c r="L6">
-        <v>-17.98</v>
+        <v>-21.66</v>
       </c>
       <c r="M6">
-        <v>1.45</v>
+        <v>0.92</v>
       </c>
       <c r="N6">
         <v>60</v>
       </c>
       <c r="O6">
-        <v>57</v>
+        <v>50</v>
       </c>
       <c r="P6">
-        <v>2.59</v>
+        <v>2.57</v>
       </c>
       <c r="Q6">
-        <v>2.63</v>
+        <v>2.61</v>
       </c>
       <c r="R6">
         <v>2.67</v>
       </c>
       <c r="S6">
-        <v>2.64</v>
+        <v>2.63</v>
       </c>
       <c r="T6">
-        <v>-1.36</v>
+        <v>-6.59</v>
       </c>
       <c r="U6" t="s">
         <v>43</v>
@@ -1406,43 +1406,43 @@
         <v>1</v>
       </c>
       <c r="Y6">
-        <v>45.54</v>
+        <v>34.85</v>
       </c>
       <c r="Z6">
-        <v>-0.03</v>
+        <v>-0.04</v>
       </c>
       <c r="AA6">
-        <v>-0.03</v>
+        <v>-0.04</v>
       </c>
       <c r="AB6">
-        <v>-0</v>
+        <v>-0.01</v>
       </c>
       <c r="AC6">
-        <v>83.27</v>
+        <v>65.52</v>
       </c>
       <c r="AD6">
-        <v>76.11</v>
+        <v>77.34</v>
       </c>
       <c r="AE6">
         <v>0.11</v>
       </c>
       <c r="AF6">
-        <v>-23.62</v>
+        <v>59.9</v>
       </c>
       <c r="AG6">
-        <v>2.77</v>
+        <v>2.75</v>
       </c>
       <c r="AH6">
-        <v>2.48</v>
+        <v>2.47</v>
       </c>
       <c r="AI6">
-        <v>2.91</v>
+        <v>2.87</v>
       </c>
       <c r="AJ6" t="s">
         <v>45</v>
       </c>
       <c r="AK6">
-        <v>27.13</v>
+        <v>31.91</v>
       </c>
     </row>
   </sheetData>
@@ -1640,13 +1640,13 @@
         <v>9</v>
       </c>
       <c r="C7" s="5">
-        <v>-4.85</v>
+        <v>-6.87</v>
       </c>
       <c r="D7" s="5">
-        <v>-6.87</v>
+        <v>-9.98</v>
       </c>
       <c r="E7" s="6">
-        <v>-2.02</v>
+        <v>-3.11</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -1657,13 +1657,13 @@
         <v>9</v>
       </c>
       <c r="C8" s="5">
-        <v>-14.75</v>
+        <v>-19.17</v>
       </c>
       <c r="D8" s="5">
-        <v>-19.17</v>
+        <v>-22.15</v>
       </c>
       <c r="E8" s="6">
-        <v>-4.42</v>
+        <v>-2.98</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -1674,13 +1674,13 @@
         <v>9</v>
       </c>
       <c r="C9" s="5">
-        <v>-7.33</v>
+        <v>-9.15</v>
       </c>
       <c r="D9" s="5">
-        <v>-9.15</v>
-      </c>
-      <c r="E9" s="6">
-        <v>-1.82</v>
+        <v>-8.220000000000001</v>
+      </c>
+      <c r="E9" s="7">
+        <v>0.93</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -1691,13 +1691,13 @@
         <v>9</v>
       </c>
       <c r="C10" s="5">
-        <v>-7.34</v>
+        <v>-9.91</v>
       </c>
       <c r="D10" s="5">
-        <v>-9.91</v>
+        <v>-12.08</v>
       </c>
       <c r="E10" s="6">
-        <v>-2.57</v>
+        <v>-2.17</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -1708,13 +1708,13 @@
         <v>9</v>
       </c>
       <c r="C11" s="5">
-        <v>-10.03</v>
+        <v>-7.8</v>
       </c>
       <c r="D11" s="5">
-        <v>-7.8</v>
-      </c>
-      <c r="E11" s="7">
-        <v>2.23</v>
+        <v>-11.51</v>
+      </c>
+      <c r="E11" s="6">
+        <v>-3.71</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -1725,13 +1725,13 @@
         <v>8</v>
       </c>
       <c r="C12" s="5">
-        <v>2.65</v>
+        <v>2.41</v>
       </c>
       <c r="D12" s="5">
-        <v>2.41</v>
+        <v>-0.43</v>
       </c>
       <c r="E12" s="6">
-        <v>-0.24</v>
+        <v>-2.84</v>
       </c>
     </row>
     <row r="13" spans="1:6">
@@ -1742,13 +1742,13 @@
         <v>8</v>
       </c>
       <c r="C13" s="5">
-        <v>2.15</v>
+        <v>5.6</v>
       </c>
       <c r="D13" s="5">
-        <v>5.6</v>
-      </c>
-      <c r="E13" s="7">
-        <v>3.45</v>
+        <v>-2.03</v>
+      </c>
+      <c r="E13" s="6">
+        <v>-7.63</v>
       </c>
     </row>
     <row r="14" spans="1:6">
@@ -1759,13 +1759,13 @@
         <v>8</v>
       </c>
       <c r="C14" s="5">
-        <v>0.62</v>
+        <v>-0.27</v>
       </c>
       <c r="D14" s="5">
-        <v>-0.27</v>
+        <v>-2.9</v>
       </c>
       <c r="E14" s="6">
-        <v>-0.89</v>
+        <v>-2.63</v>
       </c>
     </row>
     <row r="15" spans="1:6">
@@ -1776,455 +1776,455 @@
         <v>8</v>
       </c>
       <c r="C15" s="5">
-        <v>1.78</v>
+        <v>1.2</v>
       </c>
       <c r="D15" s="5">
-        <v>1.2</v>
+        <v>-3.17</v>
       </c>
       <c r="E15" s="6">
-        <v>-0.58</v>
+        <v>-4.37</v>
       </c>
     </row>
     <row r="16" spans="1:6">
       <c r="A16" s="3" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="C16" s="5">
-        <v>10.96</v>
+        <v>0.78</v>
       </c>
       <c r="D16" s="5">
-        <v>11.71</v>
-      </c>
-      <c r="E16" s="7">
-        <v>0.75</v>
+        <v>-4.65</v>
+      </c>
+      <c r="E16" s="6">
+        <v>-5.43</v>
       </c>
     </row>
     <row r="17" spans="1:5">
       <c r="A17" s="3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B17" s="3" t="s">
         <v>11</v>
       </c>
       <c r="C17" s="5">
-        <v>3.66</v>
+        <v>11.71</v>
       </c>
       <c r="D17" s="5">
-        <v>4.98</v>
-      </c>
-      <c r="E17" s="7">
-        <v>1.32</v>
+        <v>10.73</v>
+      </c>
+      <c r="E17" s="6">
+        <v>-0.98</v>
       </c>
     </row>
     <row r="18" spans="1:5">
       <c r="A18" s="3" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B18" s="3" t="s">
         <v>11</v>
       </c>
       <c r="C18" s="5">
-        <v>-27.63</v>
+        <v>4.98</v>
       </c>
       <c r="D18" s="5">
-        <v>-28.85</v>
+        <v>-3.93</v>
       </c>
       <c r="E18" s="6">
-        <v>-1.22</v>
+        <v>-8.91</v>
       </c>
     </row>
     <row r="19" spans="1:5">
       <c r="A19" s="3" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B19" s="3" t="s">
         <v>11</v>
       </c>
       <c r="C19" s="5">
-        <v>15.41</v>
+        <v>-28.85</v>
       </c>
       <c r="D19" s="5">
-        <v>15.03</v>
+        <v>-29.03</v>
       </c>
       <c r="E19" s="6">
-        <v>-0.38</v>
+        <v>-0.18</v>
       </c>
     </row>
     <row r="20" spans="1:5">
       <c r="A20" s="3" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B20" s="3" t="s">
         <v>11</v>
       </c>
       <c r="C20" s="5">
-        <v>-18.75</v>
+        <v>15.03</v>
       </c>
       <c r="D20" s="5">
-        <v>-17.98</v>
-      </c>
-      <c r="E20" s="7">
-        <v>0.77</v>
+        <v>14.79</v>
+      </c>
+      <c r="E20" s="6">
+        <v>-0.24</v>
       </c>
     </row>
     <row r="21" spans="1:5">
       <c r="A21" s="3" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C21" s="5">
-        <v>-4.07</v>
+        <v>-17.98</v>
       </c>
       <c r="D21" s="5">
-        <v>-4.57</v>
+        <v>-21.66</v>
       </c>
       <c r="E21" s="6">
-        <v>-0.5</v>
+        <v>-3.68</v>
       </c>
     </row>
     <row r="22" spans="1:5">
       <c r="A22" s="3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B22" s="3" t="s">
         <v>10</v>
       </c>
       <c r="C22" s="5">
-        <v>-9.539999999999999</v>
+        <v>-4.57</v>
       </c>
       <c r="D22" s="5">
-        <v>-8.08</v>
-      </c>
-      <c r="E22" s="7">
-        <v>1.46</v>
+        <v>-4.68</v>
+      </c>
+      <c r="E22" s="6">
+        <v>-0.11</v>
       </c>
     </row>
     <row r="23" spans="1:5">
       <c r="A23" s="3" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B23" s="3" t="s">
         <v>10</v>
       </c>
       <c r="C23" s="5">
-        <v>-17.1</v>
+        <v>-8.08</v>
       </c>
       <c r="D23" s="5">
-        <v>-18.32</v>
+        <v>-13.03</v>
       </c>
       <c r="E23" s="6">
-        <v>-1.22</v>
+        <v>-4.95</v>
       </c>
     </row>
     <row r="24" spans="1:5">
       <c r="A24" s="3" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B24" s="3" t="s">
         <v>10</v>
       </c>
       <c r="C24" s="5">
-        <v>-14.62</v>
+        <v>-18.32</v>
       </c>
       <c r="D24" s="5">
-        <v>-16.43</v>
+        <v>-19.16</v>
       </c>
       <c r="E24" s="6">
-        <v>-1.81</v>
+        <v>-0.84</v>
       </c>
     </row>
     <row r="25" spans="1:5">
       <c r="A25" s="3" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B25" s="3" t="s">
         <v>10</v>
       </c>
       <c r="C25" s="5">
-        <v>10.17</v>
+        <v>-16.43</v>
       </c>
       <c r="D25" s="5">
-        <v>10.64</v>
-      </c>
-      <c r="E25" s="7">
-        <v>0.47</v>
+        <v>-20.11</v>
+      </c>
+      <c r="E25" s="6">
+        <v>-3.68</v>
       </c>
     </row>
     <row r="26" spans="1:5">
       <c r="A26" s="3" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C26" s="5">
-        <v>-28.54</v>
+        <v>10.64</v>
       </c>
       <c r="D26" s="5">
-        <v>-29.11</v>
+        <v>4.68</v>
       </c>
       <c r="E26" s="6">
-        <v>-0.57</v>
+        <v>-5.96</v>
       </c>
     </row>
     <row r="27" spans="1:5">
       <c r="A27" s="3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B27" s="3" t="s">
         <v>6</v>
       </c>
       <c r="C27" s="5">
-        <v>-19.94</v>
+        <v>-29.11</v>
       </c>
       <c r="D27" s="5">
-        <v>-19.17</v>
-      </c>
-      <c r="E27" s="7">
-        <v>0.77</v>
+        <v>-29.58</v>
+      </c>
+      <c r="E27" s="6">
+        <v>-0.47</v>
       </c>
     </row>
     <row r="28" spans="1:5">
       <c r="A28" s="3" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B28" s="3" t="s">
         <v>6</v>
       </c>
       <c r="C28" s="5">
-        <v>-33.01</v>
+        <v>-19.17</v>
       </c>
       <c r="D28" s="5">
-        <v>-34.27</v>
+        <v>-23.86</v>
       </c>
       <c r="E28" s="6">
-        <v>-1.26</v>
+        <v>-4.69</v>
       </c>
     </row>
     <row r="29" spans="1:5">
       <c r="A29" s="3" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B29" s="3" t="s">
         <v>6</v>
       </c>
       <c r="C29" s="5">
-        <v>-17.98</v>
+        <v>-34.27</v>
       </c>
       <c r="D29" s="5">
-        <v>-19.27</v>
+        <v>-34.79</v>
       </c>
       <c r="E29" s="6">
-        <v>-1.29</v>
+        <v>-0.52</v>
       </c>
     </row>
     <row r="30" spans="1:5">
       <c r="A30" s="3" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C30" s="5">
-        <v>148.91</v>
+        <v>-19.27</v>
       </c>
       <c r="D30" s="5">
-        <v>147.72</v>
+        <v>-20.55</v>
       </c>
       <c r="E30" s="6">
-        <v>-1.19</v>
+        <v>-1.28</v>
       </c>
     </row>
     <row r="31" spans="1:5">
       <c r="A31" s="3" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C31" s="5">
-        <v>365.2</v>
+        <v>-23.08</v>
       </c>
       <c r="D31" s="5">
-        <v>368.7</v>
-      </c>
-      <c r="E31" s="7">
-        <v>3.5</v>
+        <v>-27.22</v>
+      </c>
+      <c r="E31" s="6">
+        <v>-4.14</v>
       </c>
     </row>
     <row r="32" spans="1:5">
       <c r="A32" s="3" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B32" s="3" t="s">
         <v>2</v>
       </c>
       <c r="C32" s="5">
-        <v>357.75</v>
+        <v>147.72</v>
       </c>
       <c r="D32" s="5">
-        <v>351</v>
+        <v>146.74</v>
       </c>
       <c r="E32" s="6">
-        <v>-6.75</v>
+        <v>-0.98</v>
       </c>
     </row>
     <row r="33" spans="1:5">
       <c r="A33" s="3" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B33" s="3" t="s">
         <v>2</v>
       </c>
       <c r="C33" s="5">
-        <v>877</v>
+        <v>368.7</v>
       </c>
       <c r="D33" s="5">
-        <v>863.2</v>
+        <v>347.3</v>
       </c>
       <c r="E33" s="6">
-        <v>-13.8</v>
+        <v>-21.4</v>
       </c>
     </row>
     <row r="34" spans="1:5">
       <c r="A34" s="3" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="C34" s="5">
-        <v>60</v>
+        <v>351</v>
       </c>
       <c r="D34" s="5">
-        <v>40</v>
+        <v>348.2</v>
       </c>
       <c r="E34" s="6">
-        <v>-20</v>
+        <v>-2.8</v>
       </c>
     </row>
     <row r="35" spans="1:5">
       <c r="A35" s="3" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="C35" s="5">
-        <v>21</v>
+        <v>863.2</v>
       </c>
       <c r="D35" s="5">
-        <v>20</v>
+        <v>849.55</v>
       </c>
       <c r="E35" s="6">
-        <v>-1</v>
+        <v>-13.65</v>
       </c>
     </row>
     <row r="36" spans="1:5">
       <c r="A36" s="3" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="C36" s="5">
-        <v>79</v>
+        <v>2.6</v>
       </c>
       <c r="D36" s="5">
-        <v>80</v>
-      </c>
-      <c r="E36" s="7">
-        <v>1</v>
+        <v>2.46</v>
+      </c>
+      <c r="E36" s="6">
+        <v>-0.14</v>
       </c>
     </row>
     <row r="37" spans="1:5">
       <c r="A37" s="3" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="C37" s="5">
-        <v>40</v>
+        <v>39.1</v>
       </c>
       <c r="D37" s="5">
-        <v>60</v>
-      </c>
-      <c r="E37" s="7">
-        <v>20</v>
+        <v>37.8</v>
+      </c>
+      <c r="E37" s="6">
+        <v>-1.3</v>
       </c>
     </row>
     <row r="38" spans="1:5">
       <c r="A38" s="3" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B38" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C38" s="5">
-        <v>40.67</v>
+        <v>45.05</v>
       </c>
       <c r="D38" s="5">
-        <v>39.1</v>
+        <v>37.56</v>
       </c>
       <c r="E38" s="6">
-        <v>-1.57</v>
+        <v>-7.49</v>
       </c>
     </row>
     <row r="39" spans="1:5">
       <c r="A39" s="3" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B39" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C39" s="5">
-        <v>43.33</v>
+        <v>29.32</v>
       </c>
       <c r="D39" s="5">
-        <v>45.05</v>
-      </c>
-      <c r="E39" s="7">
-        <v>1.72</v>
+        <v>27.62</v>
+      </c>
+      <c r="E39" s="6">
+        <v>-1.7</v>
       </c>
     </row>
     <row r="40" spans="1:5">
       <c r="A40" s="3" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B40" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C40" s="5">
-        <v>34.04</v>
+        <v>37.05</v>
       </c>
       <c r="D40" s="5">
-        <v>29.32</v>
+        <v>34.39</v>
       </c>
       <c r="E40" s="6">
-        <v>-4.72</v>
+        <v>-2.66</v>
       </c>
     </row>
     <row r="41" spans="1:5">
       <c r="A41" s="3" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B41" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C41" s="5">
-        <v>39.97</v>
+        <v>45.54</v>
       </c>
       <c r="D41" s="5">
-        <v>37.05</v>
+        <v>34.85</v>
       </c>
       <c r="E41" s="6">
-        <v>-2.92</v>
+        <v>-10.69</v>
       </c>
     </row>
     <row r="42" spans="1:5">
@@ -2235,13 +2235,13 @@
         <v>31</v>
       </c>
       <c r="C42" s="5">
-        <v>-11.32</v>
+        <v>-31.82</v>
       </c>
       <c r="D42" s="5">
-        <v>-31.82</v>
+        <v>-35.59</v>
       </c>
       <c r="E42" s="6">
-        <v>-20.5</v>
+        <v>-3.77</v>
       </c>
     </row>
     <row r="43" spans="1:5">
@@ -2252,13 +2252,13 @@
         <v>31</v>
       </c>
       <c r="C43" s="5">
-        <v>-82.48999999999999</v>
+        <v>-7.91</v>
       </c>
       <c r="D43" s="5">
-        <v>-7.91</v>
-      </c>
-      <c r="E43" s="7">
-        <v>74.58</v>
+        <v>-53.66</v>
+      </c>
+      <c r="E43" s="6">
+        <v>-45.75</v>
       </c>
     </row>
     <row r="44" spans="1:5">
@@ -2269,13 +2269,13 @@
         <v>31</v>
       </c>
       <c r="C44" s="5">
-        <v>52.42</v>
+        <v>20.49</v>
       </c>
       <c r="D44" s="5">
-        <v>20.49</v>
+        <v>-30.11</v>
       </c>
       <c r="E44" s="6">
-        <v>-31.93</v>
+        <v>-50.6</v>
       </c>
     </row>
     <row r="45" spans="1:5">
@@ -2286,13 +2286,13 @@
         <v>31</v>
       </c>
       <c r="C45" s="5">
-        <v>-38.43</v>
+        <v>-53.96</v>
       </c>
       <c r="D45" s="5">
-        <v>-53.96</v>
-      </c>
-      <c r="E45" s="6">
-        <v>-15.53</v>
+        <v>-25.35</v>
+      </c>
+      <c r="E45" s="7">
+        <v>28.61</v>
       </c>
     </row>
     <row r="46" spans="1:5">
@@ -2303,13 +2303,13 @@
         <v>31</v>
       </c>
       <c r="C46" s="5">
-        <v>-7.36</v>
+        <v>-23.62</v>
       </c>
       <c r="D46" s="5">
-        <v>-23.62</v>
-      </c>
-      <c r="E46" s="6">
-        <v>-16.26</v>
+        <v>59.9</v>
+      </c>
+      <c r="E46" s="7">
+        <v>83.52</v>
       </c>
     </row>
   </sheetData>
@@ -2374,16 +2374,16 @@
         <v>5</v>
       </c>
       <c r="D2" s="10">
-        <v>39.2</v>
+        <v>34.4</v>
       </c>
       <c r="E2" s="10">
         <v>20</v>
       </c>
       <c r="F2" s="10">
-        <v>-10.6</v>
+        <v>-12.8</v>
       </c>
       <c r="G2" s="10">
-        <v>-7.4</v>
+        <v>-10.5</v>
       </c>
       <c r="H2" s="10">
         <v>59.8</v>
@@ -2508,19 +2508,19 @@
     </row>
     <row r="2" spans="1:5">
       <c r="A2" s="13">
-        <v>0.1855</v>
+        <v>0.1816</v>
       </c>
       <c r="B2" s="13">
-        <v>0.0283</v>
+        <v>0.0229</v>
       </c>
       <c r="C2" s="13">
-        <v>0.0145</v>
+        <v>0.0092</v>
       </c>
       <c r="D2" s="13">
-        <v>-0.0572</v>
+        <v>-0.0587</v>
       </c>
       <c r="E2" s="13">
-        <v>-0.2287</v>
+        <v>-0.228</v>
       </c>
     </row>
   </sheetData>

--- a/HINDUJA_GROUP_Technical_Metrics.xlsx
+++ b/HINDUJA_GROUP_Technical_Metrics.xlsx
@@ -249,14 +249,14 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FF006100"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FF9C0006"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -289,13 +289,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -888,10 +888,10 @@
         <v>42</v>
       </c>
       <c r="C2">
-        <v>146.74</v>
+        <v>146.03</v>
       </c>
       <c r="D2">
-        <v>-0.66</v>
+        <v>-0.48</v>
       </c>
       <c r="E2">
         <v>208.37</v>
@@ -900,25 +900,25 @@
         <v>131.36</v>
       </c>
       <c r="G2">
-        <v>-29.58</v>
+        <v>-29.92</v>
       </c>
       <c r="H2">
-        <v>11.71</v>
+        <v>11.17</v>
       </c>
       <c r="I2">
-        <v>-0.43</v>
+        <v>0.71</v>
       </c>
       <c r="J2">
-        <v>-9.98</v>
+        <v>-9.720000000000001</v>
       </c>
       <c r="K2">
-        <v>-4.68</v>
+        <v>-4.24</v>
       </c>
       <c r="L2">
-        <v>10.73</v>
+        <v>8.949999999999999</v>
       </c>
       <c r="M2">
-        <v>18.16</v>
+        <v>18.36</v>
       </c>
       <c r="N2">
         <v>99</v>
@@ -927,19 +927,19 @@
         <v>72</v>
       </c>
       <c r="P2">
-        <v>147.31</v>
+        <v>147.52</v>
       </c>
       <c r="Q2">
-        <v>151.36</v>
+        <v>150.62</v>
       </c>
       <c r="R2">
-        <v>162.78</v>
+        <v>162.22</v>
       </c>
       <c r="S2">
-        <v>168.5</v>
+        <v>168.32</v>
       </c>
       <c r="T2">
-        <v>-12.91</v>
+        <v>-13.24</v>
       </c>
       <c r="U2" t="s">
         <v>43</v>
@@ -954,43 +954,43 @@
         <v>0</v>
       </c>
       <c r="Y2">
-        <v>37.8</v>
+        <v>36.85</v>
       </c>
       <c r="Z2">
-        <v>-4.41</v>
+        <v>-4.3</v>
       </c>
       <c r="AA2">
-        <v>-4.71</v>
+        <v>-4.63</v>
       </c>
       <c r="AB2">
-        <v>0.29</v>
+        <v>0.32</v>
       </c>
       <c r="AC2">
-        <v>87.66</v>
+        <v>77.05</v>
       </c>
       <c r="AD2">
-        <v>84.93000000000001</v>
+        <v>85.59999999999999</v>
       </c>
       <c r="AE2">
-        <v>3.89</v>
+        <v>3.91</v>
       </c>
       <c r="AF2">
-        <v>-35.59</v>
+        <v>-19.83</v>
       </c>
       <c r="AG2">
-        <v>162.53</v>
+        <v>161.11</v>
       </c>
       <c r="AH2">
-        <v>140.18</v>
+        <v>140.13</v>
       </c>
       <c r="AI2">
-        <v>157.56</v>
+        <v>156.9</v>
       </c>
       <c r="AJ2" t="s">
         <v>45</v>
       </c>
       <c r="AK2">
-        <v>49.99</v>
+        <v>50.24</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1001,10 +1001,10 @@
         <v>42</v>
       </c>
       <c r="C3">
-        <v>347.3</v>
+        <v>340.05</v>
       </c>
       <c r="D3">
-        <v>-5.8</v>
+        <v>-2.09</v>
       </c>
       <c r="E3">
         <v>456.15</v>
@@ -1013,46 +1013,46 @@
         <v>225</v>
       </c>
       <c r="G3">
-        <v>-23.86</v>
+        <v>-25.45</v>
       </c>
       <c r="H3">
-        <v>54.36</v>
+        <v>51.13</v>
       </c>
       <c r="I3">
-        <v>-2.03</v>
+        <v>-7.34</v>
       </c>
       <c r="J3">
-        <v>-22.15</v>
+        <v>-25.01</v>
       </c>
       <c r="K3">
-        <v>-13.03</v>
+        <v>-13.5</v>
       </c>
       <c r="L3">
-        <v>-3.93</v>
+        <v>-5.58</v>
       </c>
       <c r="M3">
-        <v>2.29</v>
+        <v>2.5</v>
       </c>
       <c r="N3">
         <v>40</v>
       </c>
       <c r="O3">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="P3">
-        <v>362.08</v>
+        <v>356.69</v>
       </c>
       <c r="Q3">
-        <v>367.1</v>
+        <v>363.55</v>
       </c>
       <c r="R3">
-        <v>397.27</v>
+        <v>395.51</v>
       </c>
       <c r="S3">
-        <v>341.99</v>
+        <v>342.24</v>
       </c>
       <c r="T3">
-        <v>1.55</v>
+        <v>-0.64</v>
       </c>
       <c r="U3" t="s">
         <v>43</v>
@@ -1064,46 +1064,46 @@
         <v>43</v>
       </c>
       <c r="X3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y3">
-        <v>37.56</v>
+        <v>35.41</v>
       </c>
       <c r="Z3">
-        <v>-12.83</v>
+        <v>-13.75</v>
       </c>
       <c r="AA3">
-        <v>-13.3</v>
+        <v>-13.39</v>
       </c>
       <c r="AB3">
-        <v>0.47</v>
+        <v>-0.36</v>
       </c>
       <c r="AC3">
-        <v>83.09</v>
+        <v>62.48</v>
       </c>
       <c r="AD3">
-        <v>91.36</v>
+        <v>80.34999999999999</v>
       </c>
       <c r="AE3">
-        <v>17.32</v>
+        <v>16.82</v>
       </c>
       <c r="AF3">
-        <v>-53.66</v>
+        <v>-71.06</v>
       </c>
       <c r="AG3">
-        <v>399.41</v>
+        <v>390.72</v>
       </c>
       <c r="AH3">
-        <v>334.8</v>
+        <v>336.39</v>
       </c>
       <c r="AI3">
-        <v>401.23</v>
+        <v>392.42</v>
       </c>
       <c r="AJ3" t="s">
         <v>45</v>
       </c>
       <c r="AK3">
-        <v>26.47</v>
+        <v>24.93</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1114,37 +1114,37 @@
         <v>42</v>
       </c>
       <c r="C4">
-        <v>348.2</v>
+        <v>344.6</v>
       </c>
       <c r="D4">
-        <v>-0.8</v>
+        <v>-1.03</v>
       </c>
       <c r="E4">
         <v>534</v>
       </c>
       <c r="F4">
-        <v>344.7</v>
+        <v>344.6</v>
       </c>
       <c r="G4">
-        <v>-34.79</v>
+        <v>-35.47</v>
       </c>
       <c r="H4">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="I4">
-        <v>-2.9</v>
+        <v>-4.77</v>
       </c>
       <c r="J4">
-        <v>-8.220000000000001</v>
+        <v>-8.789999999999999</v>
       </c>
       <c r="K4">
-        <v>-19.16</v>
+        <v>-19.46</v>
       </c>
       <c r="L4">
-        <v>-29.03</v>
+        <v>-29.83</v>
       </c>
       <c r="M4">
-        <v>-22.8</v>
+        <v>-22.84</v>
       </c>
       <c r="N4">
         <v>20</v>
@@ -1153,19 +1153,19 @@
         <v>22</v>
       </c>
       <c r="P4">
-        <v>355.32</v>
+        <v>351.87</v>
       </c>
       <c r="Q4">
-        <v>363.79</v>
+        <v>362.04</v>
       </c>
       <c r="R4">
-        <v>383.82</v>
+        <v>382.47</v>
       </c>
       <c r="S4">
-        <v>401.95</v>
+        <v>401.38</v>
       </c>
       <c r="T4">
-        <v>-13.37</v>
+        <v>-14.15</v>
       </c>
       <c r="U4" t="s">
         <v>43</v>
@@ -1180,43 +1180,43 @@
         <v>0</v>
       </c>
       <c r="Y4">
-        <v>27.62</v>
+        <v>25.55</v>
       </c>
       <c r="Z4">
-        <v>-9.32</v>
+        <v>-9.720000000000001</v>
       </c>
       <c r="AA4">
-        <v>-9.25</v>
+        <v>-9.34</v>
       </c>
       <c r="AB4">
-        <v>-0.07000000000000001</v>
+        <v>-0.37</v>
       </c>
       <c r="AC4">
-        <v>55.39</v>
+        <v>36.95</v>
       </c>
       <c r="AD4">
-        <v>70.43000000000001</v>
+        <v>53.92</v>
       </c>
       <c r="AE4">
-        <v>9.470000000000001</v>
+        <v>9.16</v>
       </c>
       <c r="AF4">
-        <v>-30.11</v>
+        <v>-8.76</v>
       </c>
       <c r="AG4">
-        <v>382.29</v>
+        <v>380.84</v>
       </c>
       <c r="AH4">
-        <v>345.29</v>
+        <v>343.23</v>
       </c>
       <c r="AI4">
-        <v>377.54</v>
+        <v>373.03</v>
       </c>
       <c r="AJ4" t="s">
         <v>45</v>
       </c>
       <c r="AK4">
-        <v>52.8</v>
+        <v>54.58</v>
       </c>
     </row>
     <row r="5" spans="1:37">
@@ -1227,58 +1227,58 @@
         <v>42</v>
       </c>
       <c r="C5">
-        <v>849.55</v>
+        <v>850.5</v>
       </c>
       <c r="D5">
-        <v>-1.58</v>
+        <v>0.11</v>
       </c>
       <c r="E5">
         <v>1069.3</v>
       </c>
       <c r="F5">
-        <v>739.5</v>
+        <v>751</v>
       </c>
       <c r="G5">
-        <v>-20.55</v>
+        <v>-20.46</v>
       </c>
       <c r="H5">
-        <v>14.88</v>
+        <v>13.25</v>
       </c>
       <c r="I5">
-        <v>-3.17</v>
+        <v>-1.79</v>
       </c>
       <c r="J5">
-        <v>-12.08</v>
+        <v>-11.04</v>
       </c>
       <c r="K5">
-        <v>-20.11</v>
+        <v>-20.46</v>
       </c>
       <c r="L5">
-        <v>14.79</v>
+        <v>15.01</v>
       </c>
       <c r="M5">
-        <v>-5.87</v>
+        <v>-6.04</v>
       </c>
       <c r="N5">
         <v>80</v>
       </c>
       <c r="O5">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="P5">
-        <v>868.23</v>
+        <v>865.13</v>
       </c>
       <c r="Q5">
-        <v>889.34</v>
+        <v>884.11</v>
       </c>
       <c r="R5">
-        <v>954.83</v>
+        <v>951.29</v>
       </c>
       <c r="S5">
-        <v>925.54</v>
+        <v>925.34</v>
       </c>
       <c r="T5">
-        <v>-8.210000000000001</v>
+        <v>-8.09</v>
       </c>
       <c r="U5" t="s">
         <v>43</v>
@@ -1293,43 +1293,43 @@
         <v>1</v>
       </c>
       <c r="Y5">
-        <v>34.39</v>
+        <v>34.74</v>
       </c>
       <c r="Z5">
         <v>-27.11</v>
       </c>
       <c r="AA5">
-        <v>-27.98</v>
+        <v>-27.81</v>
       </c>
       <c r="AB5">
-        <v>0.88</v>
+        <v>0.7</v>
       </c>
       <c r="AC5">
-        <v>69.18000000000001</v>
+        <v>54.81</v>
       </c>
       <c r="AD5">
-        <v>82.42</v>
+        <v>70.61</v>
       </c>
       <c r="AE5">
-        <v>23.47</v>
+        <v>23.34</v>
       </c>
       <c r="AF5">
-        <v>-25.35</v>
+        <v>-47.73</v>
       </c>
       <c r="AG5">
-        <v>950.35</v>
+        <v>939.04</v>
       </c>
       <c r="AH5">
-        <v>828.3200000000001</v>
+        <v>829.1799999999999</v>
       </c>
       <c r="AI5">
-        <v>920.22</v>
+        <v>918.48</v>
       </c>
       <c r="AJ5" t="s">
         <v>45</v>
       </c>
       <c r="AK5">
-        <v>45.53</v>
+        <v>47.11</v>
       </c>
     </row>
     <row r="6" spans="1:37">
@@ -1340,10 +1340,10 @@
         <v>42</v>
       </c>
       <c r="C6">
-        <v>2.46</v>
+        <v>2.44</v>
       </c>
       <c r="D6">
-        <v>-5.38</v>
+        <v>-0.8100000000000001</v>
       </c>
       <c r="E6">
         <v>3.38</v>
@@ -1352,37 +1352,37 @@
         <v>1.84</v>
       </c>
       <c r="G6">
-        <v>-27.22</v>
+        <v>-27.81</v>
       </c>
       <c r="H6">
-        <v>33.7</v>
+        <v>32.61</v>
       </c>
       <c r="I6">
-        <v>-4.65</v>
+        <v>-6.51</v>
       </c>
       <c r="J6">
-        <v>-11.51</v>
+        <v>-12.54</v>
       </c>
       <c r="K6">
-        <v>4.68</v>
+        <v>4.27</v>
       </c>
       <c r="L6">
-        <v>-21.66</v>
+        <v>-23.03</v>
       </c>
       <c r="M6">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="N6">
         <v>60</v>
       </c>
       <c r="O6">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="P6">
-        <v>2.57</v>
+        <v>2.53</v>
       </c>
       <c r="Q6">
-        <v>2.61</v>
+        <v>2.59</v>
       </c>
       <c r="R6">
         <v>2.67</v>
@@ -1391,7 +1391,7 @@
         <v>2.63</v>
       </c>
       <c r="T6">
-        <v>-6.59</v>
+        <v>-7.26</v>
       </c>
       <c r="U6" t="s">
         <v>43</v>
@@ -1406,10 +1406,10 @@
         <v>1</v>
       </c>
       <c r="Y6">
-        <v>34.85</v>
+        <v>33.63</v>
       </c>
       <c r="Z6">
-        <v>-0.04</v>
+        <v>-0.05</v>
       </c>
       <c r="AA6">
         <v>-0.04</v>
@@ -1418,31 +1418,31 @@
         <v>-0.01</v>
       </c>
       <c r="AC6">
-        <v>65.52</v>
+        <v>32.76</v>
       </c>
       <c r="AD6">
-        <v>77.34</v>
+        <v>60.51</v>
       </c>
       <c r="AE6">
         <v>0.11</v>
       </c>
       <c r="AF6">
-        <v>59.9</v>
+        <v>-28.66</v>
       </c>
       <c r="AG6">
-        <v>2.75</v>
+        <v>2.73</v>
       </c>
       <c r="AH6">
-        <v>2.47</v>
+        <v>2.45</v>
       </c>
       <c r="AI6">
-        <v>2.87</v>
+        <v>2.81</v>
       </c>
       <c r="AJ6" t="s">
         <v>45</v>
       </c>
       <c r="AK6">
-        <v>31.91</v>
+        <v>36.06</v>
       </c>
     </row>
   </sheetData>
@@ -1640,13 +1640,13 @@
         <v>9</v>
       </c>
       <c r="C7" s="5">
-        <v>-6.87</v>
+        <v>-9.98</v>
       </c>
       <c r="D7" s="5">
-        <v>-9.98</v>
+        <v>-9.720000000000001</v>
       </c>
       <c r="E7" s="6">
-        <v>-3.11</v>
+        <v>0.26</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -1657,13 +1657,13 @@
         <v>9</v>
       </c>
       <c r="C8" s="5">
-        <v>-19.17</v>
+        <v>-22.15</v>
       </c>
       <c r="D8" s="5">
-        <v>-22.15</v>
-      </c>
-      <c r="E8" s="6">
-        <v>-2.98</v>
+        <v>-25.01</v>
+      </c>
+      <c r="E8" s="7">
+        <v>-2.86</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -1674,13 +1674,13 @@
         <v>9</v>
       </c>
       <c r="C9" s="5">
-        <v>-9.15</v>
+        <v>-8.220000000000001</v>
       </c>
       <c r="D9" s="5">
-        <v>-8.220000000000001</v>
+        <v>-8.789999999999999</v>
       </c>
       <c r="E9" s="7">
-        <v>0.93</v>
+        <v>-0.57</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -1691,13 +1691,13 @@
         <v>9</v>
       </c>
       <c r="C10" s="5">
-        <v>-9.91</v>
+        <v>-12.08</v>
       </c>
       <c r="D10" s="5">
-        <v>-12.08</v>
+        <v>-11.04</v>
       </c>
       <c r="E10" s="6">
-        <v>-2.17</v>
+        <v>1.04</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -1708,13 +1708,13 @@
         <v>9</v>
       </c>
       <c r="C11" s="5">
-        <v>-7.8</v>
+        <v>-11.51</v>
       </c>
       <c r="D11" s="5">
-        <v>-11.51</v>
-      </c>
-      <c r="E11" s="6">
-        <v>-3.71</v>
+        <v>-12.54</v>
+      </c>
+      <c r="E11" s="7">
+        <v>-1.03</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -1725,13 +1725,13 @@
         <v>8</v>
       </c>
       <c r="C12" s="5">
-        <v>2.41</v>
+        <v>-0.43</v>
       </c>
       <c r="D12" s="5">
-        <v>-0.43</v>
+        <v>0.71</v>
       </c>
       <c r="E12" s="6">
-        <v>-2.84</v>
+        <v>1.14</v>
       </c>
     </row>
     <row r="13" spans="1:6">
@@ -1742,13 +1742,13 @@
         <v>8</v>
       </c>
       <c r="C13" s="5">
-        <v>5.6</v>
+        <v>-2.03</v>
       </c>
       <c r="D13" s="5">
-        <v>-2.03</v>
-      </c>
-      <c r="E13" s="6">
-        <v>-7.63</v>
+        <v>-7.34</v>
+      </c>
+      <c r="E13" s="7">
+        <v>-5.31</v>
       </c>
     </row>
     <row r="14" spans="1:6">
@@ -1759,13 +1759,13 @@
         <v>8</v>
       </c>
       <c r="C14" s="5">
-        <v>-0.27</v>
+        <v>-2.9</v>
       </c>
       <c r="D14" s="5">
-        <v>-2.9</v>
-      </c>
-      <c r="E14" s="6">
-        <v>-2.63</v>
+        <v>-4.77</v>
+      </c>
+      <c r="E14" s="7">
+        <v>-1.87</v>
       </c>
     </row>
     <row r="15" spans="1:6">
@@ -1776,13 +1776,13 @@
         <v>8</v>
       </c>
       <c r="C15" s="5">
-        <v>1.2</v>
+        <v>-3.17</v>
       </c>
       <c r="D15" s="5">
-        <v>-3.17</v>
+        <v>-1.79</v>
       </c>
       <c r="E15" s="6">
-        <v>-4.37</v>
+        <v>1.38</v>
       </c>
     </row>
     <row r="16" spans="1:6">
@@ -1793,13 +1793,13 @@
         <v>8</v>
       </c>
       <c r="C16" s="5">
-        <v>0.78</v>
+        <v>-4.65</v>
       </c>
       <c r="D16" s="5">
-        <v>-4.65</v>
-      </c>
-      <c r="E16" s="6">
-        <v>-5.43</v>
+        <v>-6.51</v>
+      </c>
+      <c r="E16" s="7">
+        <v>-1.86</v>
       </c>
     </row>
     <row r="17" spans="1:5">
@@ -1810,13 +1810,13 @@
         <v>11</v>
       </c>
       <c r="C17" s="5">
-        <v>11.71</v>
+        <v>10.73</v>
       </c>
       <c r="D17" s="5">
-        <v>10.73</v>
-      </c>
-      <c r="E17" s="6">
-        <v>-0.98</v>
+        <v>8.949999999999999</v>
+      </c>
+      <c r="E17" s="7">
+        <v>-1.78</v>
       </c>
     </row>
     <row r="18" spans="1:5">
@@ -1827,13 +1827,13 @@
         <v>11</v>
       </c>
       <c r="C18" s="5">
-        <v>4.98</v>
+        <v>-3.93</v>
       </c>
       <c r="D18" s="5">
-        <v>-3.93</v>
-      </c>
-      <c r="E18" s="6">
-        <v>-8.91</v>
+        <v>-5.58</v>
+      </c>
+      <c r="E18" s="7">
+        <v>-1.65</v>
       </c>
     </row>
     <row r="19" spans="1:5">
@@ -1844,13 +1844,13 @@
         <v>11</v>
       </c>
       <c r="C19" s="5">
-        <v>-28.85</v>
+        <v>-29.03</v>
       </c>
       <c r="D19" s="5">
-        <v>-29.03</v>
-      </c>
-      <c r="E19" s="6">
-        <v>-0.18</v>
+        <v>-29.83</v>
+      </c>
+      <c r="E19" s="7">
+        <v>-0.8</v>
       </c>
     </row>
     <row r="20" spans="1:5">
@@ -1861,13 +1861,13 @@
         <v>11</v>
       </c>
       <c r="C20" s="5">
-        <v>15.03</v>
+        <v>14.79</v>
       </c>
       <c r="D20" s="5">
-        <v>14.79</v>
+        <v>15.01</v>
       </c>
       <c r="E20" s="6">
-        <v>-0.24</v>
+        <v>0.22</v>
       </c>
     </row>
     <row r="21" spans="1:5">
@@ -1878,13 +1878,13 @@
         <v>11</v>
       </c>
       <c r="C21" s="5">
-        <v>-17.98</v>
+        <v>-21.66</v>
       </c>
       <c r="D21" s="5">
-        <v>-21.66</v>
-      </c>
-      <c r="E21" s="6">
-        <v>-3.68</v>
+        <v>-23.03</v>
+      </c>
+      <c r="E21" s="7">
+        <v>-1.37</v>
       </c>
     </row>
     <row r="22" spans="1:5">
@@ -1895,13 +1895,13 @@
         <v>10</v>
       </c>
       <c r="C22" s="5">
-        <v>-4.57</v>
+        <v>-4.68</v>
       </c>
       <c r="D22" s="5">
-        <v>-4.68</v>
+        <v>-4.24</v>
       </c>
       <c r="E22" s="6">
-        <v>-0.11</v>
+        <v>0.44</v>
       </c>
     </row>
     <row r="23" spans="1:5">
@@ -1912,13 +1912,13 @@
         <v>10</v>
       </c>
       <c r="C23" s="5">
-        <v>-8.08</v>
+        <v>-13.03</v>
       </c>
       <c r="D23" s="5">
-        <v>-13.03</v>
-      </c>
-      <c r="E23" s="6">
-        <v>-4.95</v>
+        <v>-13.5</v>
+      </c>
+      <c r="E23" s="7">
+        <v>-0.47</v>
       </c>
     </row>
     <row r="24" spans="1:5">
@@ -1929,13 +1929,13 @@
         <v>10</v>
       </c>
       <c r="C24" s="5">
-        <v>-18.32</v>
+        <v>-19.16</v>
       </c>
       <c r="D24" s="5">
-        <v>-19.16</v>
-      </c>
-      <c r="E24" s="6">
-        <v>-0.84</v>
+        <v>-19.46</v>
+      </c>
+      <c r="E24" s="7">
+        <v>-0.3</v>
       </c>
     </row>
     <row r="25" spans="1:5">
@@ -1946,13 +1946,13 @@
         <v>10</v>
       </c>
       <c r="C25" s="5">
-        <v>-16.43</v>
+        <v>-20.11</v>
       </c>
       <c r="D25" s="5">
-        <v>-20.11</v>
-      </c>
-      <c r="E25" s="6">
-        <v>-3.68</v>
+        <v>-20.46</v>
+      </c>
+      <c r="E25" s="7">
+        <v>-0.35</v>
       </c>
     </row>
     <row r="26" spans="1:5">
@@ -1963,13 +1963,13 @@
         <v>10</v>
       </c>
       <c r="C26" s="5">
-        <v>10.64</v>
+        <v>4.68</v>
       </c>
       <c r="D26" s="5">
-        <v>4.68</v>
-      </c>
-      <c r="E26" s="6">
-        <v>-5.96</v>
+        <v>4.27</v>
+      </c>
+      <c r="E26" s="7">
+        <v>-0.41</v>
       </c>
     </row>
     <row r="27" spans="1:5">
@@ -1980,13 +1980,13 @@
         <v>6</v>
       </c>
       <c r="C27" s="5">
-        <v>-29.11</v>
+        <v>-29.58</v>
       </c>
       <c r="D27" s="5">
-        <v>-29.58</v>
-      </c>
-      <c r="E27" s="6">
-        <v>-0.47</v>
+        <v>-29.92</v>
+      </c>
+      <c r="E27" s="7">
+        <v>-0.34</v>
       </c>
     </row>
     <row r="28" spans="1:5">
@@ -1997,13 +1997,13 @@
         <v>6</v>
       </c>
       <c r="C28" s="5">
-        <v>-19.17</v>
+        <v>-23.86</v>
       </c>
       <c r="D28" s="5">
-        <v>-23.86</v>
-      </c>
-      <c r="E28" s="6">
-        <v>-4.69</v>
+        <v>-25.45</v>
+      </c>
+      <c r="E28" s="7">
+        <v>-1.59</v>
       </c>
     </row>
     <row r="29" spans="1:5">
@@ -2014,13 +2014,13 @@
         <v>6</v>
       </c>
       <c r="C29" s="5">
-        <v>-34.27</v>
+        <v>-34.79</v>
       </c>
       <c r="D29" s="5">
-        <v>-34.79</v>
-      </c>
-      <c r="E29" s="6">
-        <v>-0.52</v>
+        <v>-35.47</v>
+      </c>
+      <c r="E29" s="7">
+        <v>-0.68</v>
       </c>
     </row>
     <row r="30" spans="1:5">
@@ -2031,13 +2031,13 @@
         <v>6</v>
       </c>
       <c r="C30" s="5">
-        <v>-19.27</v>
+        <v>-20.55</v>
       </c>
       <c r="D30" s="5">
-        <v>-20.55</v>
+        <v>-20.46</v>
       </c>
       <c r="E30" s="6">
-        <v>-1.28</v>
+        <v>0.09</v>
       </c>
     </row>
     <row r="31" spans="1:5">
@@ -2048,13 +2048,13 @@
         <v>6</v>
       </c>
       <c r="C31" s="5">
-        <v>-23.08</v>
+        <v>-27.22</v>
       </c>
       <c r="D31" s="5">
-        <v>-27.22</v>
-      </c>
-      <c r="E31" s="6">
-        <v>-4.14</v>
+        <v>-27.81</v>
+      </c>
+      <c r="E31" s="7">
+        <v>-0.59</v>
       </c>
     </row>
     <row r="32" spans="1:5">
@@ -2065,13 +2065,13 @@
         <v>2</v>
       </c>
       <c r="C32" s="5">
-        <v>147.72</v>
+        <v>146.74</v>
       </c>
       <c r="D32" s="5">
-        <v>146.74</v>
-      </c>
-      <c r="E32" s="6">
-        <v>-0.98</v>
+        <v>146.03</v>
+      </c>
+      <c r="E32" s="7">
+        <v>-0.71</v>
       </c>
     </row>
     <row r="33" spans="1:5">
@@ -2082,13 +2082,13 @@
         <v>2</v>
       </c>
       <c r="C33" s="5">
-        <v>368.7</v>
+        <v>347.3</v>
       </c>
       <c r="D33" s="5">
-        <v>347.3</v>
-      </c>
-      <c r="E33" s="6">
-        <v>-21.4</v>
+        <v>340.05</v>
+      </c>
+      <c r="E33" s="7">
+        <v>-7.25</v>
       </c>
     </row>
     <row r="34" spans="1:5">
@@ -2099,13 +2099,13 @@
         <v>2</v>
       </c>
       <c r="C34" s="5">
-        <v>351</v>
+        <v>348.2</v>
       </c>
       <c r="D34" s="5">
-        <v>348.2</v>
-      </c>
-      <c r="E34" s="6">
-        <v>-2.8</v>
+        <v>344.6</v>
+      </c>
+      <c r="E34" s="7">
+        <v>-3.6</v>
       </c>
     </row>
     <row r="35" spans="1:5">
@@ -2116,13 +2116,13 @@
         <v>2</v>
       </c>
       <c r="C35" s="5">
-        <v>863.2</v>
+        <v>849.55</v>
       </c>
       <c r="D35" s="5">
-        <v>849.55</v>
+        <v>850.5</v>
       </c>
       <c r="E35" s="6">
-        <v>-13.65</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="36" spans="1:5">
@@ -2133,13 +2133,13 @@
         <v>2</v>
       </c>
       <c r="C36" s="5">
-        <v>2.6</v>
+        <v>2.46</v>
       </c>
       <c r="D36" s="5">
-        <v>2.46</v>
-      </c>
-      <c r="E36" s="6">
-        <v>-0.14</v>
+        <v>2.44</v>
+      </c>
+      <c r="E36" s="7">
+        <v>-0.02</v>
       </c>
     </row>
     <row r="37" spans="1:5">
@@ -2150,13 +2150,13 @@
         <v>24</v>
       </c>
       <c r="C37" s="5">
-        <v>39.1</v>
+        <v>37.8</v>
       </c>
       <c r="D37" s="5">
-        <v>37.8</v>
-      </c>
-      <c r="E37" s="6">
-        <v>-1.3</v>
+        <v>36.85</v>
+      </c>
+      <c r="E37" s="7">
+        <v>-0.95</v>
       </c>
     </row>
     <row r="38" spans="1:5">
@@ -2167,13 +2167,13 @@
         <v>24</v>
       </c>
       <c r="C38" s="5">
-        <v>45.05</v>
+        <v>37.56</v>
       </c>
       <c r="D38" s="5">
-        <v>37.56</v>
-      </c>
-      <c r="E38" s="6">
-        <v>-7.49</v>
+        <v>35.41</v>
+      </c>
+      <c r="E38" s="7">
+        <v>-2.15</v>
       </c>
     </row>
     <row r="39" spans="1:5">
@@ -2184,13 +2184,13 @@
         <v>24</v>
       </c>
       <c r="C39" s="5">
-        <v>29.32</v>
+        <v>27.62</v>
       </c>
       <c r="D39" s="5">
-        <v>27.62</v>
-      </c>
-      <c r="E39" s="6">
-        <v>-1.7</v>
+        <v>25.55</v>
+      </c>
+      <c r="E39" s="7">
+        <v>-2.07</v>
       </c>
     </row>
     <row r="40" spans="1:5">
@@ -2201,13 +2201,13 @@
         <v>24</v>
       </c>
       <c r="C40" s="5">
-        <v>37.05</v>
+        <v>34.39</v>
       </c>
       <c r="D40" s="5">
-        <v>34.39</v>
+        <v>34.74</v>
       </c>
       <c r="E40" s="6">
-        <v>-2.66</v>
+        <v>0.35</v>
       </c>
     </row>
     <row r="41" spans="1:5">
@@ -2218,13 +2218,13 @@
         <v>24</v>
       </c>
       <c r="C41" s="5">
-        <v>45.54</v>
+        <v>34.85</v>
       </c>
       <c r="D41" s="5">
-        <v>34.85</v>
-      </c>
-      <c r="E41" s="6">
-        <v>-10.69</v>
+        <v>33.63</v>
+      </c>
+      <c r="E41" s="7">
+        <v>-1.22</v>
       </c>
     </row>
     <row r="42" spans="1:5">
@@ -2235,13 +2235,13 @@
         <v>31</v>
       </c>
       <c r="C42" s="5">
-        <v>-31.82</v>
+        <v>-35.59</v>
       </c>
       <c r="D42" s="5">
-        <v>-35.59</v>
+        <v>-19.83</v>
       </c>
       <c r="E42" s="6">
-        <v>-3.77</v>
+        <v>15.76</v>
       </c>
     </row>
     <row r="43" spans="1:5">
@@ -2252,13 +2252,13 @@
         <v>31</v>
       </c>
       <c r="C43" s="5">
-        <v>-7.91</v>
+        <v>-53.66</v>
       </c>
       <c r="D43" s="5">
-        <v>-53.66</v>
-      </c>
-      <c r="E43" s="6">
-        <v>-45.75</v>
+        <v>-71.06</v>
+      </c>
+      <c r="E43" s="7">
+        <v>-17.4</v>
       </c>
     </row>
     <row r="44" spans="1:5">
@@ -2269,13 +2269,13 @@
         <v>31</v>
       </c>
       <c r="C44" s="5">
-        <v>20.49</v>
+        <v>-30.11</v>
       </c>
       <c r="D44" s="5">
-        <v>-30.11</v>
+        <v>-8.76</v>
       </c>
       <c r="E44" s="6">
-        <v>-50.6</v>
+        <v>21.35</v>
       </c>
     </row>
     <row r="45" spans="1:5">
@@ -2286,13 +2286,13 @@
         <v>31</v>
       </c>
       <c r="C45" s="5">
-        <v>-53.96</v>
+        <v>-25.35</v>
       </c>
       <c r="D45" s="5">
-        <v>-25.35</v>
+        <v>-47.73</v>
       </c>
       <c r="E45" s="7">
-        <v>28.61</v>
+        <v>-22.38</v>
       </c>
     </row>
     <row r="46" spans="1:5">
@@ -2303,13 +2303,13 @@
         <v>31</v>
       </c>
       <c r="C46" s="5">
-        <v>-23.62</v>
+        <v>59.9</v>
       </c>
       <c r="D46" s="5">
-        <v>59.9</v>
+        <v>-28.66</v>
       </c>
       <c r="E46" s="7">
-        <v>83.52</v>
+        <v>-88.56</v>
       </c>
     </row>
   </sheetData>
@@ -2368,22 +2368,22 @@
         <v>42</v>
       </c>
       <c r="B2" s="10">
-        <v>41.92</v>
+        <v>33.92</v>
       </c>
       <c r="C2" s="11">
         <v>5</v>
       </c>
       <c r="D2" s="10">
-        <v>34.4</v>
+        <v>33.2</v>
       </c>
       <c r="E2" s="10">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="F2" s="10">
-        <v>-12.8</v>
+        <v>-13.4</v>
       </c>
       <c r="G2" s="10">
-        <v>-10.5</v>
+        <v>-10.7</v>
       </c>
       <c r="H2" s="10">
         <v>59.8</v>
@@ -2508,19 +2508,19 @@
     </row>
     <row r="2" spans="1:5">
       <c r="A2" s="13">
-        <v>0.1816</v>
+        <v>0.1836</v>
       </c>
       <c r="B2" s="13">
-        <v>0.0229</v>
+        <v>0.025</v>
       </c>
       <c r="C2" s="13">
-        <v>0.0092</v>
+        <v>0.009300000000000001</v>
       </c>
       <c r="D2" s="13">
-        <v>-0.0587</v>
+        <v>-0.0604</v>
       </c>
       <c r="E2" s="13">
-        <v>-0.228</v>
+        <v>-0.2284</v>
       </c>
     </row>
   </sheetData>

--- a/HINDUJA_GROUP_Technical_Metrics.xlsx
+++ b/HINDUJA_GROUP_Technical_Metrics.xlsx
@@ -249,14 +249,14 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FF9C0006"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FF006100"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -289,13 +289,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -888,37 +888,37 @@
         <v>42</v>
       </c>
       <c r="C2">
-        <v>146.03</v>
+        <v>144.95</v>
       </c>
       <c r="D2">
-        <v>-0.48</v>
+        <v>-0.74</v>
       </c>
       <c r="E2">
         <v>208.37</v>
       </c>
       <c r="F2">
-        <v>131.36</v>
+        <v>132.66</v>
       </c>
       <c r="G2">
-        <v>-29.92</v>
+        <v>-30.44</v>
       </c>
       <c r="H2">
-        <v>11.17</v>
+        <v>9.26</v>
       </c>
       <c r="I2">
-        <v>0.71</v>
+        <v>-2.18</v>
       </c>
       <c r="J2">
-        <v>-9.720000000000001</v>
+        <v>-9.83</v>
       </c>
       <c r="K2">
-        <v>-4.24</v>
+        <v>-3.78</v>
       </c>
       <c r="L2">
-        <v>8.949999999999999</v>
+        <v>10.35</v>
       </c>
       <c r="M2">
-        <v>18.36</v>
+        <v>18.51</v>
       </c>
       <c r="N2">
         <v>99</v>
@@ -927,19 +927,19 @@
         <v>72</v>
       </c>
       <c r="P2">
-        <v>147.52</v>
+        <v>146.87</v>
       </c>
       <c r="Q2">
-        <v>150.62</v>
+        <v>149.72</v>
       </c>
       <c r="R2">
-        <v>162.22</v>
+        <v>161.62</v>
       </c>
       <c r="S2">
-        <v>168.32</v>
+        <v>168.12</v>
       </c>
       <c r="T2">
-        <v>-13.24</v>
+        <v>-13.78</v>
       </c>
       <c r="U2" t="s">
         <v>43</v>
@@ -954,43 +954,43 @@
         <v>0</v>
       </c>
       <c r="Y2">
-        <v>36.85</v>
+        <v>35.38</v>
       </c>
       <c r="Z2">
-        <v>-4.3</v>
+        <v>-4.25</v>
       </c>
       <c r="AA2">
-        <v>-4.63</v>
+        <v>-4.55</v>
       </c>
       <c r="AB2">
-        <v>0.32</v>
+        <v>0.3</v>
       </c>
       <c r="AC2">
-        <v>77.05</v>
+        <v>66.75</v>
       </c>
       <c r="AD2">
-        <v>85.59999999999999</v>
+        <v>77.15000000000001</v>
       </c>
       <c r="AE2">
-        <v>3.91</v>
+        <v>3.93</v>
       </c>
       <c r="AF2">
-        <v>-19.83</v>
+        <v>42.66</v>
       </c>
       <c r="AG2">
-        <v>161.11</v>
+        <v>158.76</v>
       </c>
       <c r="AH2">
-        <v>140.13</v>
+        <v>140.68</v>
       </c>
       <c r="AI2">
-        <v>156.9</v>
+        <v>155.93</v>
       </c>
       <c r="AJ2" t="s">
         <v>45</v>
       </c>
       <c r="AK2">
-        <v>50.24</v>
+        <v>51.05</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1001,10 +1001,10 @@
         <v>42</v>
       </c>
       <c r="C3">
-        <v>340.05</v>
+        <v>321.25</v>
       </c>
       <c r="D3">
-        <v>-2.09</v>
+        <v>-5.53</v>
       </c>
       <c r="E3">
         <v>456.15</v>
@@ -1013,46 +1013,46 @@
         <v>225</v>
       </c>
       <c r="G3">
-        <v>-25.45</v>
+        <v>-29.57</v>
       </c>
       <c r="H3">
-        <v>51.13</v>
+        <v>42.78</v>
       </c>
       <c r="I3">
-        <v>-7.34</v>
+        <v>-11.31</v>
       </c>
       <c r="J3">
-        <v>-25.01</v>
+        <v>-21.85</v>
       </c>
       <c r="K3">
-        <v>-13.5</v>
+        <v>-17.8</v>
       </c>
       <c r="L3">
-        <v>-5.58</v>
+        <v>-8.83</v>
       </c>
       <c r="M3">
-        <v>2.5</v>
+        <v>1.01</v>
       </c>
       <c r="N3">
         <v>40</v>
       </c>
       <c r="O3">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="P3">
-        <v>356.69</v>
+        <v>348.5</v>
       </c>
       <c r="Q3">
-        <v>363.55</v>
+        <v>359.98</v>
       </c>
       <c r="R3">
-        <v>395.51</v>
+        <v>393.34</v>
       </c>
       <c r="S3">
-        <v>342.24</v>
+        <v>342.38</v>
       </c>
       <c r="T3">
-        <v>-0.64</v>
+        <v>-6.17</v>
       </c>
       <c r="U3" t="s">
         <v>43</v>
@@ -1067,43 +1067,43 @@
         <v>1</v>
       </c>
       <c r="Y3">
-        <v>35.41</v>
+        <v>30.54</v>
       </c>
       <c r="Z3">
-        <v>-13.75</v>
+        <v>-15.81</v>
       </c>
       <c r="AA3">
-        <v>-13.39</v>
+        <v>-13.87</v>
       </c>
       <c r="AB3">
-        <v>-0.36</v>
+        <v>-1.94</v>
       </c>
       <c r="AC3">
-        <v>62.48</v>
+        <v>30.68</v>
       </c>
       <c r="AD3">
-        <v>80.34999999999999</v>
+        <v>58.75</v>
       </c>
       <c r="AE3">
-        <v>16.82</v>
+        <v>17.6</v>
       </c>
       <c r="AF3">
-        <v>-71.06</v>
+        <v>4.91</v>
       </c>
       <c r="AG3">
-        <v>390.72</v>
+        <v>389.66</v>
       </c>
       <c r="AH3">
-        <v>336.39</v>
+        <v>330.29</v>
       </c>
       <c r="AI3">
-        <v>392.42</v>
+        <v>379.88</v>
       </c>
       <c r="AJ3" t="s">
         <v>45</v>
       </c>
       <c r="AK3">
-        <v>24.93</v>
+        <v>27.1</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1114,58 +1114,58 @@
         <v>42</v>
       </c>
       <c r="C4">
-        <v>344.6</v>
+        <v>337.95</v>
       </c>
       <c r="D4">
-        <v>-1.03</v>
+        <v>-1.93</v>
       </c>
       <c r="E4">
         <v>534</v>
       </c>
       <c r="F4">
-        <v>344.6</v>
+        <v>337.95</v>
       </c>
       <c r="G4">
-        <v>-35.47</v>
+        <v>-36.71</v>
       </c>
       <c r="H4">
         <v>0</v>
       </c>
       <c r="I4">
-        <v>-4.77</v>
+        <v>-5.55</v>
       </c>
       <c r="J4">
-        <v>-8.789999999999999</v>
+        <v>-10.98</v>
       </c>
       <c r="K4">
-        <v>-19.46</v>
+        <v>-20.61</v>
       </c>
       <c r="L4">
-        <v>-29.83</v>
+        <v>-30.88</v>
       </c>
       <c r="M4">
-        <v>-22.84</v>
+        <v>-22.62</v>
       </c>
       <c r="N4">
         <v>20</v>
       </c>
       <c r="O4">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="P4">
-        <v>351.87</v>
+        <v>347.9</v>
       </c>
       <c r="Q4">
-        <v>362.04</v>
+        <v>360.01</v>
       </c>
       <c r="R4">
-        <v>382.47</v>
+        <v>381</v>
       </c>
       <c r="S4">
-        <v>401.38</v>
+        <v>400.8</v>
       </c>
       <c r="T4">
-        <v>-14.15</v>
+        <v>-15.68</v>
       </c>
       <c r="U4" t="s">
         <v>43</v>
@@ -1180,43 +1180,43 @@
         <v>0</v>
       </c>
       <c r="Y4">
-        <v>25.55</v>
+        <v>22.25</v>
       </c>
       <c r="Z4">
-        <v>-9.720000000000001</v>
+        <v>-10.45</v>
       </c>
       <c r="AA4">
-        <v>-9.34</v>
+        <v>-9.56</v>
       </c>
       <c r="AB4">
-        <v>-0.37</v>
+        <v>-0.88</v>
       </c>
       <c r="AC4">
-        <v>36.95</v>
+        <v>21.59</v>
       </c>
       <c r="AD4">
-        <v>53.92</v>
+        <v>37.98</v>
       </c>
       <c r="AE4">
-        <v>9.16</v>
+        <v>9.5</v>
       </c>
       <c r="AF4">
-        <v>-8.76</v>
+        <v>83.18000000000001</v>
       </c>
       <c r="AG4">
-        <v>380.84</v>
+        <v>380.05</v>
       </c>
       <c r="AH4">
-        <v>343.23</v>
+        <v>339.97</v>
       </c>
       <c r="AI4">
-        <v>373.03</v>
+        <v>366.54</v>
       </c>
       <c r="AJ4" t="s">
         <v>45</v>
       </c>
       <c r="AK4">
-        <v>54.58</v>
+        <v>57.88</v>
       </c>
     </row>
     <row r="5" spans="1:37">
@@ -1227,58 +1227,58 @@
         <v>42</v>
       </c>
       <c r="C5">
-        <v>850.5</v>
+        <v>835</v>
       </c>
       <c r="D5">
-        <v>0.11</v>
+        <v>-1.82</v>
       </c>
       <c r="E5">
         <v>1069.3</v>
       </c>
       <c r="F5">
-        <v>751</v>
+        <v>752.45</v>
       </c>
       <c r="G5">
-        <v>-20.46</v>
+        <v>-21.91</v>
       </c>
       <c r="H5">
-        <v>13.25</v>
+        <v>10.97</v>
       </c>
       <c r="I5">
-        <v>-1.79</v>
+        <v>-5.69</v>
       </c>
       <c r="J5">
-        <v>-11.04</v>
+        <v>-12.57</v>
       </c>
       <c r="K5">
-        <v>-20.46</v>
+        <v>-16.96</v>
       </c>
       <c r="L5">
-        <v>15.01</v>
+        <v>11.19</v>
       </c>
       <c r="M5">
-        <v>-6.04</v>
+        <v>-6.09</v>
       </c>
       <c r="N5">
         <v>80</v>
       </c>
       <c r="O5">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="P5">
-        <v>865.13</v>
+        <v>855.05</v>
       </c>
       <c r="Q5">
-        <v>884.11</v>
+        <v>877.9</v>
       </c>
       <c r="R5">
-        <v>951.29</v>
+        <v>947.8200000000001</v>
       </c>
       <c r="S5">
-        <v>925.34</v>
+        <v>925</v>
       </c>
       <c r="T5">
-        <v>-8.09</v>
+        <v>-9.73</v>
       </c>
       <c r="U5" t="s">
         <v>43</v>
@@ -1293,43 +1293,43 @@
         <v>1</v>
       </c>
       <c r="Y5">
-        <v>34.74</v>
+        <v>31.75</v>
       </c>
       <c r="Z5">
-        <v>-27.11</v>
+        <v>-28.04</v>
       </c>
       <c r="AA5">
-        <v>-27.81</v>
+        <v>-27.86</v>
       </c>
       <c r="AB5">
-        <v>0.7</v>
+        <v>-0.19</v>
       </c>
       <c r="AC5">
-        <v>54.81</v>
+        <v>38.27</v>
       </c>
       <c r="AD5">
-        <v>70.61</v>
+        <v>54.08</v>
       </c>
       <c r="AE5">
-        <v>23.34</v>
+        <v>23.15</v>
       </c>
       <c r="AF5">
-        <v>-47.73</v>
+        <v>-19.28</v>
       </c>
       <c r="AG5">
-        <v>939.04</v>
+        <v>924.5</v>
       </c>
       <c r="AH5">
-        <v>829.1799999999999</v>
+        <v>831.29</v>
       </c>
       <c r="AI5">
-        <v>918.48</v>
+        <v>911.14</v>
       </c>
       <c r="AJ5" t="s">
         <v>45</v>
       </c>
       <c r="AK5">
-        <v>47.11</v>
+        <v>49.02</v>
       </c>
     </row>
     <row r="6" spans="1:37">
@@ -1340,10 +1340,10 @@
         <v>42</v>
       </c>
       <c r="C6">
-        <v>2.44</v>
+        <v>2.49</v>
       </c>
       <c r="D6">
-        <v>-0.8100000000000001</v>
+        <v>2.05</v>
       </c>
       <c r="E6">
         <v>3.38</v>
@@ -1352,46 +1352,46 @@
         <v>1.84</v>
       </c>
       <c r="G6">
-        <v>-27.81</v>
+        <v>-26.33</v>
       </c>
       <c r="H6">
-        <v>32.61</v>
+        <v>35.33</v>
       </c>
       <c r="I6">
-        <v>-6.51</v>
+        <v>-3.11</v>
       </c>
       <c r="J6">
-        <v>-12.54</v>
+        <v>-9.779999999999999</v>
       </c>
       <c r="K6">
-        <v>4.27</v>
+        <v>7.33</v>
       </c>
       <c r="L6">
-        <v>-23.03</v>
+        <v>-21.2</v>
       </c>
       <c r="M6">
-        <v>0.93</v>
+        <v>0.41</v>
       </c>
       <c r="N6">
         <v>60</v>
       </c>
       <c r="O6">
-        <v>51</v>
+        <v>60</v>
       </c>
       <c r="P6">
-        <v>2.53</v>
+        <v>2.52</v>
       </c>
       <c r="Q6">
-        <v>2.59</v>
+        <v>2.58</v>
       </c>
       <c r="R6">
-        <v>2.67</v>
+        <v>2.68</v>
       </c>
       <c r="S6">
         <v>2.63</v>
       </c>
       <c r="T6">
-        <v>-7.26</v>
+        <v>-5.28</v>
       </c>
       <c r="U6" t="s">
         <v>43</v>
@@ -1406,7 +1406,7 @@
         <v>1</v>
       </c>
       <c r="Y6">
-        <v>33.63</v>
+        <v>39.33</v>
       </c>
       <c r="Z6">
         <v>-0.05</v>
@@ -1418,22 +1418,22 @@
         <v>-0.01</v>
       </c>
       <c r="AC6">
-        <v>32.76</v>
+        <v>15.78</v>
       </c>
       <c r="AD6">
-        <v>60.51</v>
+        <v>38.02</v>
       </c>
       <c r="AE6">
-        <v>0.11</v>
+        <v>0.15</v>
       </c>
       <c r="AF6">
-        <v>-28.66</v>
+        <v>79.28</v>
       </c>
       <c r="AG6">
-        <v>2.73</v>
+        <v>2.7</v>
       </c>
       <c r="AH6">
-        <v>2.45</v>
+        <v>2.46</v>
       </c>
       <c r="AI6">
         <v>2.81</v>
@@ -1442,7 +1442,7 @@
         <v>45</v>
       </c>
       <c r="AK6">
-        <v>36.06</v>
+        <v>37.16</v>
       </c>
     </row>
   </sheetData>
@@ -1640,13 +1640,13 @@
         <v>9</v>
       </c>
       <c r="C7" s="5">
-        <v>-9.98</v>
+        <v>-9.720000000000001</v>
       </c>
       <c r="D7" s="5">
-        <v>-9.720000000000001</v>
+        <v>-9.83</v>
       </c>
       <c r="E7" s="6">
-        <v>0.26</v>
+        <v>-0.11</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -1657,13 +1657,13 @@
         <v>9</v>
       </c>
       <c r="C8" s="5">
-        <v>-22.15</v>
+        <v>-25.01</v>
       </c>
       <c r="D8" s="5">
-        <v>-25.01</v>
+        <v>-21.85</v>
       </c>
       <c r="E8" s="7">
-        <v>-2.86</v>
+        <v>3.16</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -1674,13 +1674,13 @@
         <v>9</v>
       </c>
       <c r="C9" s="5">
-        <v>-8.220000000000001</v>
+        <v>-8.789999999999999</v>
       </c>
       <c r="D9" s="5">
-        <v>-8.789999999999999</v>
-      </c>
-      <c r="E9" s="7">
-        <v>-0.57</v>
+        <v>-10.98</v>
+      </c>
+      <c r="E9" s="6">
+        <v>-2.19</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -1691,13 +1691,13 @@
         <v>9</v>
       </c>
       <c r="C10" s="5">
-        <v>-12.08</v>
+        <v>-11.04</v>
       </c>
       <c r="D10" s="5">
-        <v>-11.04</v>
+        <v>-12.57</v>
       </c>
       <c r="E10" s="6">
-        <v>1.04</v>
+        <v>-1.53</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -1708,13 +1708,13 @@
         <v>9</v>
       </c>
       <c r="C11" s="5">
-        <v>-11.51</v>
+        <v>-12.54</v>
       </c>
       <c r="D11" s="5">
-        <v>-12.54</v>
+        <v>-9.779999999999999</v>
       </c>
       <c r="E11" s="7">
-        <v>-1.03</v>
+        <v>2.76</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -1725,13 +1725,13 @@
         <v>8</v>
       </c>
       <c r="C12" s="5">
-        <v>-0.43</v>
+        <v>0.71</v>
       </c>
       <c r="D12" s="5">
-        <v>0.71</v>
+        <v>-2.18</v>
       </c>
       <c r="E12" s="6">
-        <v>1.14</v>
+        <v>-2.89</v>
       </c>
     </row>
     <row r="13" spans="1:6">
@@ -1742,13 +1742,13 @@
         <v>8</v>
       </c>
       <c r="C13" s="5">
-        <v>-2.03</v>
+        <v>-7.34</v>
       </c>
       <c r="D13" s="5">
-        <v>-7.34</v>
-      </c>
-      <c r="E13" s="7">
-        <v>-5.31</v>
+        <v>-11.31</v>
+      </c>
+      <c r="E13" s="6">
+        <v>-3.97</v>
       </c>
     </row>
     <row r="14" spans="1:6">
@@ -1759,13 +1759,13 @@
         <v>8</v>
       </c>
       <c r="C14" s="5">
-        <v>-2.9</v>
+        <v>-4.77</v>
       </c>
       <c r="D14" s="5">
-        <v>-4.77</v>
-      </c>
-      <c r="E14" s="7">
-        <v>-1.87</v>
+        <v>-5.55</v>
+      </c>
+      <c r="E14" s="6">
+        <v>-0.78</v>
       </c>
     </row>
     <row r="15" spans="1:6">
@@ -1776,13 +1776,13 @@
         <v>8</v>
       </c>
       <c r="C15" s="5">
-        <v>-3.17</v>
+        <v>-1.79</v>
       </c>
       <c r="D15" s="5">
-        <v>-1.79</v>
+        <v>-5.69</v>
       </c>
       <c r="E15" s="6">
-        <v>1.38</v>
+        <v>-3.9</v>
       </c>
     </row>
     <row r="16" spans="1:6">
@@ -1793,13 +1793,13 @@
         <v>8</v>
       </c>
       <c r="C16" s="5">
-        <v>-4.65</v>
+        <v>-6.51</v>
       </c>
       <c r="D16" s="5">
-        <v>-6.51</v>
+        <v>-3.11</v>
       </c>
       <c r="E16" s="7">
-        <v>-1.86</v>
+        <v>3.4</v>
       </c>
     </row>
     <row r="17" spans="1:5">
@@ -1810,13 +1810,13 @@
         <v>11</v>
       </c>
       <c r="C17" s="5">
-        <v>10.73</v>
+        <v>8.949999999999999</v>
       </c>
       <c r="D17" s="5">
-        <v>8.949999999999999</v>
+        <v>10.35</v>
       </c>
       <c r="E17" s="7">
-        <v>-1.78</v>
+        <v>1.4</v>
       </c>
     </row>
     <row r="18" spans="1:5">
@@ -1827,13 +1827,13 @@
         <v>11</v>
       </c>
       <c r="C18" s="5">
-        <v>-3.93</v>
+        <v>-5.58</v>
       </c>
       <c r="D18" s="5">
-        <v>-5.58</v>
-      </c>
-      <c r="E18" s="7">
-        <v>-1.65</v>
+        <v>-8.83</v>
+      </c>
+      <c r="E18" s="6">
+        <v>-3.25</v>
       </c>
     </row>
     <row r="19" spans="1:5">
@@ -1844,13 +1844,13 @@
         <v>11</v>
       </c>
       <c r="C19" s="5">
-        <v>-29.03</v>
+        <v>-29.83</v>
       </c>
       <c r="D19" s="5">
-        <v>-29.83</v>
-      </c>
-      <c r="E19" s="7">
-        <v>-0.8</v>
+        <v>-30.88</v>
+      </c>
+      <c r="E19" s="6">
+        <v>-1.05</v>
       </c>
     </row>
     <row r="20" spans="1:5">
@@ -1861,13 +1861,13 @@
         <v>11</v>
       </c>
       <c r="C20" s="5">
-        <v>14.79</v>
+        <v>15.01</v>
       </c>
       <c r="D20" s="5">
-        <v>15.01</v>
+        <v>11.19</v>
       </c>
       <c r="E20" s="6">
-        <v>0.22</v>
+        <v>-3.82</v>
       </c>
     </row>
     <row r="21" spans="1:5">
@@ -1878,13 +1878,13 @@
         <v>11</v>
       </c>
       <c r="C21" s="5">
-        <v>-21.66</v>
+        <v>-23.03</v>
       </c>
       <c r="D21" s="5">
-        <v>-23.03</v>
+        <v>-21.2</v>
       </c>
       <c r="E21" s="7">
-        <v>-1.37</v>
+        <v>1.83</v>
       </c>
     </row>
     <row r="22" spans="1:5">
@@ -1895,13 +1895,13 @@
         <v>10</v>
       </c>
       <c r="C22" s="5">
-        <v>-4.68</v>
+        <v>-4.24</v>
       </c>
       <c r="D22" s="5">
-        <v>-4.24</v>
-      </c>
-      <c r="E22" s="6">
-        <v>0.44</v>
+        <v>-3.78</v>
+      </c>
+      <c r="E22" s="7">
+        <v>0.46</v>
       </c>
     </row>
     <row r="23" spans="1:5">
@@ -1912,13 +1912,13 @@
         <v>10</v>
       </c>
       <c r="C23" s="5">
-        <v>-13.03</v>
+        <v>-13.5</v>
       </c>
       <c r="D23" s="5">
-        <v>-13.5</v>
-      </c>
-      <c r="E23" s="7">
-        <v>-0.47</v>
+        <v>-17.8</v>
+      </c>
+      <c r="E23" s="6">
+        <v>-4.3</v>
       </c>
     </row>
     <row r="24" spans="1:5">
@@ -1929,13 +1929,13 @@
         <v>10</v>
       </c>
       <c r="C24" s="5">
-        <v>-19.16</v>
+        <v>-19.46</v>
       </c>
       <c r="D24" s="5">
-        <v>-19.46</v>
-      </c>
-      <c r="E24" s="7">
-        <v>-0.3</v>
+        <v>-20.61</v>
+      </c>
+      <c r="E24" s="6">
+        <v>-1.15</v>
       </c>
     </row>
     <row r="25" spans="1:5">
@@ -1946,13 +1946,13 @@
         <v>10</v>
       </c>
       <c r="C25" s="5">
-        <v>-20.11</v>
+        <v>-20.46</v>
       </c>
       <c r="D25" s="5">
-        <v>-20.46</v>
+        <v>-16.96</v>
       </c>
       <c r="E25" s="7">
-        <v>-0.35</v>
+        <v>3.5</v>
       </c>
     </row>
     <row r="26" spans="1:5">
@@ -1963,13 +1963,13 @@
         <v>10</v>
       </c>
       <c r="C26" s="5">
-        <v>4.68</v>
+        <v>4.27</v>
       </c>
       <c r="D26" s="5">
-        <v>4.27</v>
+        <v>7.33</v>
       </c>
       <c r="E26" s="7">
-        <v>-0.41</v>
+        <v>3.06</v>
       </c>
     </row>
     <row r="27" spans="1:5">
@@ -1980,13 +1980,13 @@
         <v>6</v>
       </c>
       <c r="C27" s="5">
-        <v>-29.58</v>
+        <v>-29.92</v>
       </c>
       <c r="D27" s="5">
-        <v>-29.92</v>
-      </c>
-      <c r="E27" s="7">
-        <v>-0.34</v>
+        <v>-30.44</v>
+      </c>
+      <c r="E27" s="6">
+        <v>-0.52</v>
       </c>
     </row>
     <row r="28" spans="1:5">
@@ -1997,13 +1997,13 @@
         <v>6</v>
       </c>
       <c r="C28" s="5">
-        <v>-23.86</v>
+        <v>-25.45</v>
       </c>
       <c r="D28" s="5">
-        <v>-25.45</v>
-      </c>
-      <c r="E28" s="7">
-        <v>-1.59</v>
+        <v>-29.57</v>
+      </c>
+      <c r="E28" s="6">
+        <v>-4.12</v>
       </c>
     </row>
     <row r="29" spans="1:5">
@@ -2014,13 +2014,13 @@
         <v>6</v>
       </c>
       <c r="C29" s="5">
-        <v>-34.79</v>
+        <v>-35.47</v>
       </c>
       <c r="D29" s="5">
-        <v>-35.47</v>
-      </c>
-      <c r="E29" s="7">
-        <v>-0.68</v>
+        <v>-36.71</v>
+      </c>
+      <c r="E29" s="6">
+        <v>-1.24</v>
       </c>
     </row>
     <row r="30" spans="1:5">
@@ -2031,13 +2031,13 @@
         <v>6</v>
       </c>
       <c r="C30" s="5">
-        <v>-20.55</v>
+        <v>-20.46</v>
       </c>
       <c r="D30" s="5">
-        <v>-20.46</v>
+        <v>-21.91</v>
       </c>
       <c r="E30" s="6">
-        <v>0.09</v>
+        <v>-1.45</v>
       </c>
     </row>
     <row r="31" spans="1:5">
@@ -2048,13 +2048,13 @@
         <v>6</v>
       </c>
       <c r="C31" s="5">
-        <v>-27.22</v>
+        <v>-27.81</v>
       </c>
       <c r="D31" s="5">
-        <v>-27.81</v>
+        <v>-26.33</v>
       </c>
       <c r="E31" s="7">
-        <v>-0.59</v>
+        <v>1.48</v>
       </c>
     </row>
     <row r="32" spans="1:5">
@@ -2065,13 +2065,13 @@
         <v>2</v>
       </c>
       <c r="C32" s="5">
-        <v>146.74</v>
+        <v>146.03</v>
       </c>
       <c r="D32" s="5">
-        <v>146.03</v>
-      </c>
-      <c r="E32" s="7">
-        <v>-0.71</v>
+        <v>144.95</v>
+      </c>
+      <c r="E32" s="6">
+        <v>-1.08</v>
       </c>
     </row>
     <row r="33" spans="1:5">
@@ -2082,13 +2082,13 @@
         <v>2</v>
       </c>
       <c r="C33" s="5">
-        <v>347.3</v>
+        <v>340.05</v>
       </c>
       <c r="D33" s="5">
-        <v>340.05</v>
-      </c>
-      <c r="E33" s="7">
-        <v>-7.25</v>
+        <v>321.25</v>
+      </c>
+      <c r="E33" s="6">
+        <v>-18.8</v>
       </c>
     </row>
     <row r="34" spans="1:5">
@@ -2099,13 +2099,13 @@
         <v>2</v>
       </c>
       <c r="C34" s="5">
-        <v>348.2</v>
+        <v>344.6</v>
       </c>
       <c r="D34" s="5">
-        <v>344.6</v>
-      </c>
-      <c r="E34" s="7">
-        <v>-3.6</v>
+        <v>337.95</v>
+      </c>
+      <c r="E34" s="6">
+        <v>-6.65</v>
       </c>
     </row>
     <row r="35" spans="1:5">
@@ -2116,13 +2116,13 @@
         <v>2</v>
       </c>
       <c r="C35" s="5">
-        <v>849.55</v>
+        <v>850.5</v>
       </c>
       <c r="D35" s="5">
-        <v>850.5</v>
+        <v>835</v>
       </c>
       <c r="E35" s="6">
-        <v>0.95</v>
+        <v>-15.5</v>
       </c>
     </row>
     <row r="36" spans="1:5">
@@ -2133,13 +2133,13 @@
         <v>2</v>
       </c>
       <c r="C36" s="5">
-        <v>2.46</v>
+        <v>2.44</v>
       </c>
       <c r="D36" s="5">
-        <v>2.44</v>
+        <v>2.49</v>
       </c>
       <c r="E36" s="7">
-        <v>-0.02</v>
+        <v>0.05</v>
       </c>
     </row>
     <row r="37" spans="1:5">
@@ -2150,13 +2150,13 @@
         <v>24</v>
       </c>
       <c r="C37" s="5">
-        <v>37.8</v>
+        <v>36.85</v>
       </c>
       <c r="D37" s="5">
-        <v>36.85</v>
-      </c>
-      <c r="E37" s="7">
-        <v>-0.95</v>
+        <v>35.38</v>
+      </c>
+      <c r="E37" s="6">
+        <v>-1.47</v>
       </c>
     </row>
     <row r="38" spans="1:5">
@@ -2167,13 +2167,13 @@
         <v>24</v>
       </c>
       <c r="C38" s="5">
-        <v>37.56</v>
+        <v>35.41</v>
       </c>
       <c r="D38" s="5">
-        <v>35.41</v>
-      </c>
-      <c r="E38" s="7">
-        <v>-2.15</v>
+        <v>30.54</v>
+      </c>
+      <c r="E38" s="6">
+        <v>-4.87</v>
       </c>
     </row>
     <row r="39" spans="1:5">
@@ -2184,13 +2184,13 @@
         <v>24</v>
       </c>
       <c r="C39" s="5">
-        <v>27.62</v>
+        <v>25.55</v>
       </c>
       <c r="D39" s="5">
-        <v>25.55</v>
-      </c>
-      <c r="E39" s="7">
-        <v>-2.07</v>
+        <v>22.25</v>
+      </c>
+      <c r="E39" s="6">
+        <v>-3.3</v>
       </c>
     </row>
     <row r="40" spans="1:5">
@@ -2201,13 +2201,13 @@
         <v>24</v>
       </c>
       <c r="C40" s="5">
-        <v>34.39</v>
+        <v>34.74</v>
       </c>
       <c r="D40" s="5">
-        <v>34.74</v>
+        <v>31.75</v>
       </c>
       <c r="E40" s="6">
-        <v>0.35</v>
+        <v>-2.99</v>
       </c>
     </row>
     <row r="41" spans="1:5">
@@ -2218,13 +2218,13 @@
         <v>24</v>
       </c>
       <c r="C41" s="5">
-        <v>34.85</v>
+        <v>33.63</v>
       </c>
       <c r="D41" s="5">
-        <v>33.63</v>
+        <v>39.33</v>
       </c>
       <c r="E41" s="7">
-        <v>-1.22</v>
+        <v>5.7</v>
       </c>
     </row>
     <row r="42" spans="1:5">
@@ -2235,13 +2235,13 @@
         <v>31</v>
       </c>
       <c r="C42" s="5">
-        <v>-35.59</v>
+        <v>-19.83</v>
       </c>
       <c r="D42" s="5">
-        <v>-19.83</v>
-      </c>
-      <c r="E42" s="6">
-        <v>15.76</v>
+        <v>42.66</v>
+      </c>
+      <c r="E42" s="7">
+        <v>62.49</v>
       </c>
     </row>
     <row r="43" spans="1:5">
@@ -2252,13 +2252,13 @@
         <v>31</v>
       </c>
       <c r="C43" s="5">
-        <v>-53.66</v>
+        <v>-71.06</v>
       </c>
       <c r="D43" s="5">
-        <v>-71.06</v>
+        <v>4.91</v>
       </c>
       <c r="E43" s="7">
-        <v>-17.4</v>
+        <v>75.97</v>
       </c>
     </row>
     <row r="44" spans="1:5">
@@ -2269,13 +2269,13 @@
         <v>31</v>
       </c>
       <c r="C44" s="5">
-        <v>-30.11</v>
+        <v>-8.76</v>
       </c>
       <c r="D44" s="5">
-        <v>-8.76</v>
-      </c>
-      <c r="E44" s="6">
-        <v>21.35</v>
+        <v>83.18000000000001</v>
+      </c>
+      <c r="E44" s="7">
+        <v>91.94</v>
       </c>
     </row>
     <row r="45" spans="1:5">
@@ -2286,13 +2286,13 @@
         <v>31</v>
       </c>
       <c r="C45" s="5">
-        <v>-25.35</v>
+        <v>-47.73</v>
       </c>
       <c r="D45" s="5">
-        <v>-47.73</v>
+        <v>-19.28</v>
       </c>
       <c r="E45" s="7">
-        <v>-22.38</v>
+        <v>28.45</v>
       </c>
     </row>
     <row r="46" spans="1:5">
@@ -2303,13 +2303,13 @@
         <v>31</v>
       </c>
       <c r="C46" s="5">
-        <v>59.9</v>
+        <v>-28.66</v>
       </c>
       <c r="D46" s="5">
-        <v>-28.66</v>
+        <v>79.28</v>
       </c>
       <c r="E46" s="7">
-        <v>-88.56</v>
+        <v>107.94</v>
       </c>
     </row>
   </sheetData>
@@ -2374,16 +2374,16 @@
         <v>5</v>
       </c>
       <c r="D2" s="10">
-        <v>33.2</v>
+        <v>31.8</v>
       </c>
       <c r="E2" s="10">
         <v>0</v>
       </c>
       <c r="F2" s="10">
-        <v>-13.4</v>
+        <v>-13</v>
       </c>
       <c r="G2" s="10">
-        <v>-10.7</v>
+        <v>-10.4</v>
       </c>
       <c r="H2" s="10">
         <v>59.8</v>
@@ -2508,19 +2508,19 @@
     </row>
     <row r="2" spans="1:5">
       <c r="A2" s="13">
-        <v>0.1836</v>
+        <v>0.1851</v>
       </c>
       <c r="B2" s="13">
-        <v>0.025</v>
+        <v>0.0101</v>
       </c>
       <c r="C2" s="13">
-        <v>0.009300000000000001</v>
+        <v>0.004099999999999999</v>
       </c>
       <c r="D2" s="13">
-        <v>-0.0604</v>
+        <v>-0.0609</v>
       </c>
       <c r="E2" s="13">
-        <v>-0.2284</v>
+        <v>-0.2262</v>
       </c>
     </row>
   </sheetData>

--- a/HINDUJA_GROUP_Technical_Metrics.xlsx
+++ b/HINDUJA_GROUP_Technical_Metrics.xlsx
@@ -888,58 +888,58 @@
         <v>42</v>
       </c>
       <c r="C2">
-        <v>144.95</v>
+        <v>141.9</v>
       </c>
       <c r="D2">
-        <v>-0.74</v>
+        <v>-2.1</v>
       </c>
       <c r="E2">
         <v>208.37</v>
       </c>
       <c r="F2">
-        <v>132.66</v>
+        <v>133.05</v>
       </c>
       <c r="G2">
-        <v>-30.44</v>
+        <v>-31.9</v>
       </c>
       <c r="H2">
-        <v>9.26</v>
+        <v>6.65</v>
       </c>
       <c r="I2">
-        <v>-2.18</v>
+        <v>-4.71</v>
       </c>
       <c r="J2">
-        <v>-9.83</v>
+        <v>-12.89</v>
       </c>
       <c r="K2">
-        <v>-3.78</v>
+        <v>-6.07</v>
       </c>
       <c r="L2">
-        <v>10.35</v>
+        <v>6.97</v>
       </c>
       <c r="M2">
-        <v>18.51</v>
+        <v>16.99</v>
       </c>
       <c r="N2">
         <v>99</v>
       </c>
       <c r="O2">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="P2">
-        <v>146.87</v>
+        <v>145.47</v>
       </c>
       <c r="Q2">
-        <v>149.72</v>
+        <v>148.95</v>
       </c>
       <c r="R2">
-        <v>161.62</v>
+        <v>160.92</v>
       </c>
       <c r="S2">
-        <v>168.12</v>
+        <v>167.9</v>
       </c>
       <c r="T2">
-        <v>-13.78</v>
+        <v>-15.49</v>
       </c>
       <c r="U2" t="s">
         <v>43</v>
@@ -954,43 +954,43 @@
         <v>0</v>
       </c>
       <c r="Y2">
-        <v>35.38</v>
+        <v>31.57</v>
       </c>
       <c r="Z2">
-        <v>-4.25</v>
+        <v>-4.41</v>
       </c>
       <c r="AA2">
-        <v>-4.55</v>
+        <v>-4.52</v>
       </c>
       <c r="AB2">
-        <v>0.3</v>
+        <v>0.11</v>
       </c>
       <c r="AC2">
-        <v>66.75</v>
+        <v>49.46</v>
       </c>
       <c r="AD2">
-        <v>77.15000000000001</v>
+        <v>64.42</v>
       </c>
       <c r="AE2">
-        <v>3.93</v>
+        <v>4.01</v>
       </c>
       <c r="AF2">
-        <v>42.66</v>
+        <v>55.93</v>
       </c>
       <c r="AG2">
-        <v>158.76</v>
+        <v>157.89</v>
       </c>
       <c r="AH2">
-        <v>140.68</v>
+        <v>140.01</v>
       </c>
       <c r="AI2">
-        <v>155.93</v>
+        <v>154.47</v>
       </c>
       <c r="AJ2" t="s">
         <v>45</v>
       </c>
       <c r="AK2">
-        <v>51.05</v>
+        <v>52.75</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1001,10 +1001,10 @@
         <v>42</v>
       </c>
       <c r="C3">
-        <v>321.25</v>
+        <v>315.65</v>
       </c>
       <c r="D3">
-        <v>-5.53</v>
+        <v>-1.74</v>
       </c>
       <c r="E3">
         <v>456.15</v>
@@ -1013,46 +1013,46 @@
         <v>225</v>
       </c>
       <c r="G3">
-        <v>-29.57</v>
+        <v>-30.8</v>
       </c>
       <c r="H3">
-        <v>42.78</v>
+        <v>40.29</v>
       </c>
       <c r="I3">
-        <v>-11.31</v>
+        <v>-13.57</v>
       </c>
       <c r="J3">
-        <v>-21.85</v>
+        <v>-19.63</v>
       </c>
       <c r="K3">
-        <v>-17.8</v>
+        <v>-20.4</v>
       </c>
       <c r="L3">
-        <v>-8.83</v>
+        <v>-9.5</v>
       </c>
       <c r="M3">
-        <v>1.01</v>
+        <v>0.72</v>
       </c>
       <c r="N3">
         <v>40</v>
       </c>
       <c r="O3">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="P3">
-        <v>348.5</v>
+        <v>338.59</v>
       </c>
       <c r="Q3">
-        <v>359.98</v>
+        <v>356.75</v>
       </c>
       <c r="R3">
-        <v>393.34</v>
+        <v>391.02</v>
       </c>
       <c r="S3">
-        <v>342.38</v>
+        <v>342.52</v>
       </c>
       <c r="T3">
-        <v>-6.17</v>
+        <v>-7.84</v>
       </c>
       <c r="U3" t="s">
         <v>43</v>
@@ -1067,43 +1067,43 @@
         <v>1</v>
       </c>
       <c r="Y3">
-        <v>30.54</v>
+        <v>29.24</v>
       </c>
       <c r="Z3">
-        <v>-15.81</v>
+        <v>-17.7</v>
       </c>
       <c r="AA3">
-        <v>-13.87</v>
+        <v>-14.64</v>
       </c>
       <c r="AB3">
-        <v>-1.94</v>
+        <v>-3.06</v>
       </c>
       <c r="AC3">
-        <v>30.68</v>
+        <v>13.75</v>
       </c>
       <c r="AD3">
-        <v>58.75</v>
+        <v>35.63</v>
       </c>
       <c r="AE3">
-        <v>17.6</v>
+        <v>17.46</v>
       </c>
       <c r="AF3">
-        <v>4.91</v>
+        <v>14.71</v>
       </c>
       <c r="AG3">
-        <v>389.66</v>
+        <v>390.87</v>
       </c>
       <c r="AH3">
-        <v>330.29</v>
+        <v>322.62</v>
       </c>
       <c r="AI3">
-        <v>379.88</v>
+        <v>372.58</v>
       </c>
       <c r="AJ3" t="s">
         <v>45</v>
       </c>
       <c r="AK3">
-        <v>27.1</v>
+        <v>29.08</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1114,58 +1114,58 @@
         <v>42</v>
       </c>
       <c r="C4">
-        <v>337.95</v>
+        <v>334.75</v>
       </c>
       <c r="D4">
-        <v>-1.93</v>
+        <v>-0.95</v>
       </c>
       <c r="E4">
         <v>534</v>
       </c>
       <c r="F4">
-        <v>337.95</v>
+        <v>334.75</v>
       </c>
       <c r="G4">
-        <v>-36.71</v>
+        <v>-37.31</v>
       </c>
       <c r="H4">
         <v>0</v>
       </c>
       <c r="I4">
-        <v>-5.55</v>
+        <v>-6.43</v>
       </c>
       <c r="J4">
-        <v>-10.98</v>
+        <v>-11.56</v>
       </c>
       <c r="K4">
-        <v>-20.61</v>
+        <v>-20.78</v>
       </c>
       <c r="L4">
-        <v>-30.88</v>
+        <v>-31.57</v>
       </c>
       <c r="M4">
-        <v>-22.62</v>
+        <v>-22.88</v>
       </c>
       <c r="N4">
         <v>20</v>
       </c>
       <c r="O4">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="P4">
-        <v>347.9</v>
+        <v>343.3</v>
       </c>
       <c r="Q4">
-        <v>360.01</v>
+        <v>358.02</v>
       </c>
       <c r="R4">
-        <v>381</v>
+        <v>379.56</v>
       </c>
       <c r="S4">
-        <v>400.8</v>
+        <v>400.23</v>
       </c>
       <c r="T4">
-        <v>-15.68</v>
+        <v>-16.36</v>
       </c>
       <c r="U4" t="s">
         <v>43</v>
@@ -1180,34 +1180,34 @@
         <v>0</v>
       </c>
       <c r="Y4">
-        <v>22.25</v>
+        <v>20.85</v>
       </c>
       <c r="Z4">
-        <v>-10.45</v>
+        <v>-11.16</v>
       </c>
       <c r="AA4">
-        <v>-9.56</v>
+        <v>-9.880000000000001</v>
       </c>
       <c r="AB4">
-        <v>-0.88</v>
+        <v>-1.27</v>
       </c>
       <c r="AC4">
-        <v>21.59</v>
+        <v>9.01</v>
       </c>
       <c r="AD4">
-        <v>37.98</v>
+        <v>22.52</v>
       </c>
       <c r="AE4">
-        <v>9.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AF4">
-        <v>83.18000000000001</v>
+        <v>45.82</v>
       </c>
       <c r="AG4">
-        <v>380.05</v>
+        <v>379.81</v>
       </c>
       <c r="AH4">
-        <v>339.97</v>
+        <v>336.23</v>
       </c>
       <c r="AI4">
         <v>366.54</v>
@@ -1216,7 +1216,7 @@
         <v>45</v>
       </c>
       <c r="AK4">
-        <v>57.88</v>
+        <v>60.74</v>
       </c>
     </row>
     <row r="5" spans="1:37">
@@ -1227,10 +1227,10 @@
         <v>42</v>
       </c>
       <c r="C5">
-        <v>835</v>
+        <v>844.5</v>
       </c>
       <c r="D5">
-        <v>-1.82</v>
+        <v>1.14</v>
       </c>
       <c r="E5">
         <v>1069.3</v>
@@ -1239,46 +1239,46 @@
         <v>752.45</v>
       </c>
       <c r="G5">
-        <v>-21.91</v>
+        <v>-21.02</v>
       </c>
       <c r="H5">
-        <v>10.97</v>
+        <v>12.23</v>
       </c>
       <c r="I5">
-        <v>-5.69</v>
+        <v>-3.71</v>
       </c>
       <c r="J5">
-        <v>-12.57</v>
+        <v>-11.97</v>
       </c>
       <c r="K5">
-        <v>-16.96</v>
+        <v>-15.22</v>
       </c>
       <c r="L5">
-        <v>11.19</v>
+        <v>11.15</v>
       </c>
       <c r="M5">
-        <v>-6.09</v>
+        <v>-5.5</v>
       </c>
       <c r="N5">
         <v>80</v>
       </c>
       <c r="O5">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="P5">
-        <v>855.05</v>
+        <v>848.55</v>
       </c>
       <c r="Q5">
-        <v>877.9</v>
+        <v>874.15</v>
       </c>
       <c r="R5">
-        <v>947.8200000000001</v>
+        <v>944.36</v>
       </c>
       <c r="S5">
-        <v>925</v>
+        <v>924.73</v>
       </c>
       <c r="T5">
-        <v>-9.73</v>
+        <v>-8.68</v>
       </c>
       <c r="U5" t="s">
         <v>43</v>
@@ -1293,34 +1293,34 @@
         <v>1</v>
       </c>
       <c r="Y5">
-        <v>31.75</v>
+        <v>35.42</v>
       </c>
       <c r="Z5">
-        <v>-28.04</v>
+        <v>-27.69</v>
       </c>
       <c r="AA5">
-        <v>-27.86</v>
+        <v>-27.82</v>
       </c>
       <c r="AB5">
-        <v>-0.19</v>
+        <v>0.13</v>
       </c>
       <c r="AC5">
-        <v>38.27</v>
+        <v>40.86</v>
       </c>
       <c r="AD5">
-        <v>54.08</v>
+        <v>44.65</v>
       </c>
       <c r="AE5">
-        <v>23.15</v>
+        <v>23.1</v>
       </c>
       <c r="AF5">
-        <v>-19.28</v>
+        <v>-7.37</v>
       </c>
       <c r="AG5">
-        <v>924.5</v>
+        <v>918.6799999999999</v>
       </c>
       <c r="AH5">
-        <v>831.29</v>
+        <v>829.61</v>
       </c>
       <c r="AI5">
         <v>911.14</v>
@@ -1329,7 +1329,7 @@
         <v>45</v>
       </c>
       <c r="AK5">
-        <v>49.02</v>
+        <v>49.75</v>
       </c>
     </row>
     <row r="6" spans="1:37">
@@ -1340,10 +1340,10 @@
         <v>42</v>
       </c>
       <c r="C6">
-        <v>2.49</v>
+        <v>2.52</v>
       </c>
       <c r="D6">
-        <v>2.05</v>
+        <v>1.2</v>
       </c>
       <c r="E6">
         <v>3.38</v>
@@ -1352,37 +1352,37 @@
         <v>1.84</v>
       </c>
       <c r="G6">
-        <v>-26.33</v>
+        <v>-25.44</v>
       </c>
       <c r="H6">
-        <v>35.33</v>
+        <v>36.96</v>
       </c>
       <c r="I6">
-        <v>-3.11</v>
+        <v>-3.08</v>
       </c>
       <c r="J6">
-        <v>-9.779999999999999</v>
+        <v>-8.699999999999999</v>
       </c>
       <c r="K6">
-        <v>7.33</v>
+        <v>9.09</v>
       </c>
       <c r="L6">
-        <v>-21.2</v>
+        <v>-20.25</v>
       </c>
       <c r="M6">
-        <v>0.41</v>
+        <v>-0.39</v>
       </c>
       <c r="N6">
         <v>60</v>
       </c>
       <c r="O6">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="P6">
-        <v>2.52</v>
+        <v>2.5</v>
       </c>
       <c r="Q6">
-        <v>2.58</v>
+        <v>2.57</v>
       </c>
       <c r="R6">
         <v>2.68</v>
@@ -1391,7 +1391,7 @@
         <v>2.63</v>
       </c>
       <c r="T6">
-        <v>-5.28</v>
+        <v>-4.06</v>
       </c>
       <c r="U6" t="s">
         <v>43</v>
@@ -1406,7 +1406,7 @@
         <v>1</v>
       </c>
       <c r="Y6">
-        <v>39.33</v>
+        <v>42.52</v>
       </c>
       <c r="Z6">
         <v>-0.05</v>
@@ -1418,19 +1418,19 @@
         <v>-0.01</v>
       </c>
       <c r="AC6">
-        <v>15.78</v>
+        <v>40.38</v>
       </c>
       <c r="AD6">
-        <v>38.02</v>
+        <v>29.64</v>
       </c>
       <c r="AE6">
         <v>0.15</v>
       </c>
       <c r="AF6">
-        <v>79.28</v>
+        <v>-6.2</v>
       </c>
       <c r="AG6">
-        <v>2.7</v>
+        <v>2.68</v>
       </c>
       <c r="AH6">
         <v>2.46</v>
@@ -1442,7 +1442,7 @@
         <v>45</v>
       </c>
       <c r="AK6">
-        <v>37.16</v>
+        <v>38.12</v>
       </c>
     </row>
   </sheetData>
@@ -1640,13 +1640,13 @@
         <v>9</v>
       </c>
       <c r="C7" s="5">
-        <v>-9.720000000000001</v>
+        <v>-9.83</v>
       </c>
       <c r="D7" s="5">
-        <v>-9.83</v>
+        <v>-12.89</v>
       </c>
       <c r="E7" s="6">
-        <v>-0.11</v>
+        <v>-3.06</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -1657,13 +1657,13 @@
         <v>9</v>
       </c>
       <c r="C8" s="5">
-        <v>-25.01</v>
+        <v>-21.85</v>
       </c>
       <c r="D8" s="5">
-        <v>-21.85</v>
+        <v>-19.63</v>
       </c>
       <c r="E8" s="7">
-        <v>3.16</v>
+        <v>2.22</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -1674,13 +1674,13 @@
         <v>9</v>
       </c>
       <c r="C9" s="5">
-        <v>-8.789999999999999</v>
+        <v>-10.98</v>
       </c>
       <c r="D9" s="5">
-        <v>-10.98</v>
+        <v>-11.56</v>
       </c>
       <c r="E9" s="6">
-        <v>-2.19</v>
+        <v>-0.58</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -1691,13 +1691,13 @@
         <v>9</v>
       </c>
       <c r="C10" s="5">
-        <v>-11.04</v>
+        <v>-12.57</v>
       </c>
       <c r="D10" s="5">
-        <v>-12.57</v>
-      </c>
-      <c r="E10" s="6">
-        <v>-1.53</v>
+        <v>-11.97</v>
+      </c>
+      <c r="E10" s="7">
+        <v>0.6</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -1708,13 +1708,13 @@
         <v>9</v>
       </c>
       <c r="C11" s="5">
-        <v>-12.54</v>
+        <v>-9.779999999999999</v>
       </c>
       <c r="D11" s="5">
-        <v>-9.779999999999999</v>
+        <v>-8.699999999999999</v>
       </c>
       <c r="E11" s="7">
-        <v>2.76</v>
+        <v>1.08</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -1725,13 +1725,13 @@
         <v>8</v>
       </c>
       <c r="C12" s="5">
-        <v>0.71</v>
+        <v>-2.18</v>
       </c>
       <c r="D12" s="5">
-        <v>-2.18</v>
+        <v>-4.71</v>
       </c>
       <c r="E12" s="6">
-        <v>-2.89</v>
+        <v>-2.53</v>
       </c>
     </row>
     <row r="13" spans="1:6">
@@ -1742,13 +1742,13 @@
         <v>8</v>
       </c>
       <c r="C13" s="5">
-        <v>-7.34</v>
+        <v>-11.31</v>
       </c>
       <c r="D13" s="5">
-        <v>-11.31</v>
+        <v>-13.57</v>
       </c>
       <c r="E13" s="6">
-        <v>-3.97</v>
+        <v>-2.26</v>
       </c>
     </row>
     <row r="14" spans="1:6">
@@ -1759,13 +1759,13 @@
         <v>8</v>
       </c>
       <c r="C14" s="5">
-        <v>-4.77</v>
+        <v>-5.55</v>
       </c>
       <c r="D14" s="5">
-        <v>-5.55</v>
+        <v>-6.43</v>
       </c>
       <c r="E14" s="6">
-        <v>-0.78</v>
+        <v>-0.88</v>
       </c>
     </row>
     <row r="15" spans="1:6">
@@ -1776,13 +1776,13 @@
         <v>8</v>
       </c>
       <c r="C15" s="5">
-        <v>-1.79</v>
+        <v>-5.69</v>
       </c>
       <c r="D15" s="5">
-        <v>-5.69</v>
-      </c>
-      <c r="E15" s="6">
-        <v>-3.9</v>
+        <v>-3.71</v>
+      </c>
+      <c r="E15" s="7">
+        <v>1.98</v>
       </c>
     </row>
     <row r="16" spans="1:6">
@@ -1793,13 +1793,13 @@
         <v>8</v>
       </c>
       <c r="C16" s="5">
-        <v>-6.51</v>
+        <v>-3.11</v>
       </c>
       <c r="D16" s="5">
-        <v>-3.11</v>
+        <v>-3.08</v>
       </c>
       <c r="E16" s="7">
-        <v>3.4</v>
+        <v>0.03</v>
       </c>
     </row>
     <row r="17" spans="1:5">
@@ -1810,13 +1810,13 @@
         <v>11</v>
       </c>
       <c r="C17" s="5">
-        <v>8.949999999999999</v>
+        <v>10.35</v>
       </c>
       <c r="D17" s="5">
-        <v>10.35</v>
-      </c>
-      <c r="E17" s="7">
-        <v>1.4</v>
+        <v>6.97</v>
+      </c>
+      <c r="E17" s="6">
+        <v>-3.38</v>
       </c>
     </row>
     <row r="18" spans="1:5">
@@ -1827,13 +1827,13 @@
         <v>11</v>
       </c>
       <c r="C18" s="5">
-        <v>-5.58</v>
+        <v>-8.83</v>
       </c>
       <c r="D18" s="5">
-        <v>-8.83</v>
+        <v>-9.5</v>
       </c>
       <c r="E18" s="6">
-        <v>-3.25</v>
+        <v>-0.67</v>
       </c>
     </row>
     <row r="19" spans="1:5">
@@ -1844,13 +1844,13 @@
         <v>11</v>
       </c>
       <c r="C19" s="5">
-        <v>-29.83</v>
+        <v>-30.88</v>
       </c>
       <c r="D19" s="5">
-        <v>-30.88</v>
+        <v>-31.57</v>
       </c>
       <c r="E19" s="6">
-        <v>-1.05</v>
+        <v>-0.6899999999999999</v>
       </c>
     </row>
     <row r="20" spans="1:5">
@@ -1861,13 +1861,13 @@
         <v>11</v>
       </c>
       <c r="C20" s="5">
-        <v>15.01</v>
+        <v>11.19</v>
       </c>
       <c r="D20" s="5">
-        <v>11.19</v>
+        <v>11.15</v>
       </c>
       <c r="E20" s="6">
-        <v>-3.82</v>
+        <v>-0.04</v>
       </c>
     </row>
     <row r="21" spans="1:5">
@@ -1878,13 +1878,13 @@
         <v>11</v>
       </c>
       <c r="C21" s="5">
-        <v>-23.03</v>
+        <v>-21.2</v>
       </c>
       <c r="D21" s="5">
-        <v>-21.2</v>
+        <v>-20.25</v>
       </c>
       <c r="E21" s="7">
-        <v>1.83</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="22" spans="1:5">
@@ -1895,13 +1895,13 @@
         <v>10</v>
       </c>
       <c r="C22" s="5">
-        <v>-4.24</v>
+        <v>-3.78</v>
       </c>
       <c r="D22" s="5">
-        <v>-3.78</v>
-      </c>
-      <c r="E22" s="7">
-        <v>0.46</v>
+        <v>-6.07</v>
+      </c>
+      <c r="E22" s="6">
+        <v>-2.29</v>
       </c>
     </row>
     <row r="23" spans="1:5">
@@ -1912,13 +1912,13 @@
         <v>10</v>
       </c>
       <c r="C23" s="5">
-        <v>-13.5</v>
+        <v>-17.8</v>
       </c>
       <c r="D23" s="5">
-        <v>-17.8</v>
+        <v>-20.4</v>
       </c>
       <c r="E23" s="6">
-        <v>-4.3</v>
+        <v>-2.6</v>
       </c>
     </row>
     <row r="24" spans="1:5">
@@ -1929,13 +1929,13 @@
         <v>10</v>
       </c>
       <c r="C24" s="5">
-        <v>-19.46</v>
+        <v>-20.61</v>
       </c>
       <c r="D24" s="5">
-        <v>-20.61</v>
+        <v>-20.78</v>
       </c>
       <c r="E24" s="6">
-        <v>-1.15</v>
+        <v>-0.17</v>
       </c>
     </row>
     <row r="25" spans="1:5">
@@ -1946,13 +1946,13 @@
         <v>10</v>
       </c>
       <c r="C25" s="5">
-        <v>-20.46</v>
+        <v>-16.96</v>
       </c>
       <c r="D25" s="5">
-        <v>-16.96</v>
+        <v>-15.22</v>
       </c>
       <c r="E25" s="7">
-        <v>3.5</v>
+        <v>1.74</v>
       </c>
     </row>
     <row r="26" spans="1:5">
@@ -1963,13 +1963,13 @@
         <v>10</v>
       </c>
       <c r="C26" s="5">
-        <v>4.27</v>
+        <v>7.33</v>
       </c>
       <c r="D26" s="5">
-        <v>7.33</v>
+        <v>9.09</v>
       </c>
       <c r="E26" s="7">
-        <v>3.06</v>
+        <v>1.76</v>
       </c>
     </row>
     <row r="27" spans="1:5">
@@ -1980,13 +1980,13 @@
         <v>6</v>
       </c>
       <c r="C27" s="5">
-        <v>-29.92</v>
+        <v>-30.44</v>
       </c>
       <c r="D27" s="5">
-        <v>-30.44</v>
+        <v>-31.9</v>
       </c>
       <c r="E27" s="6">
-        <v>-0.52</v>
+        <v>-1.46</v>
       </c>
     </row>
     <row r="28" spans="1:5">
@@ -1997,13 +1997,13 @@
         <v>6</v>
       </c>
       <c r="C28" s="5">
-        <v>-25.45</v>
+        <v>-29.57</v>
       </c>
       <c r="D28" s="5">
-        <v>-29.57</v>
+        <v>-30.8</v>
       </c>
       <c r="E28" s="6">
-        <v>-4.12</v>
+        <v>-1.23</v>
       </c>
     </row>
     <row r="29" spans="1:5">
@@ -2014,13 +2014,13 @@
         <v>6</v>
       </c>
       <c r="C29" s="5">
-        <v>-35.47</v>
+        <v>-36.71</v>
       </c>
       <c r="D29" s="5">
-        <v>-36.71</v>
+        <v>-37.31</v>
       </c>
       <c r="E29" s="6">
-        <v>-1.24</v>
+        <v>-0.6</v>
       </c>
     </row>
     <row r="30" spans="1:5">
@@ -2031,13 +2031,13 @@
         <v>6</v>
       </c>
       <c r="C30" s="5">
-        <v>-20.46</v>
+        <v>-21.91</v>
       </c>
       <c r="D30" s="5">
-        <v>-21.91</v>
-      </c>
-      <c r="E30" s="6">
-        <v>-1.45</v>
+        <v>-21.02</v>
+      </c>
+      <c r="E30" s="7">
+        <v>0.89</v>
       </c>
     </row>
     <row r="31" spans="1:5">
@@ -2048,13 +2048,13 @@
         <v>6</v>
       </c>
       <c r="C31" s="5">
-        <v>-27.81</v>
+        <v>-26.33</v>
       </c>
       <c r="D31" s="5">
-        <v>-26.33</v>
+        <v>-25.44</v>
       </c>
       <c r="E31" s="7">
-        <v>1.48</v>
+        <v>0.89</v>
       </c>
     </row>
     <row r="32" spans="1:5">
@@ -2065,13 +2065,13 @@
         <v>2</v>
       </c>
       <c r="C32" s="5">
-        <v>146.03</v>
+        <v>144.95</v>
       </c>
       <c r="D32" s="5">
-        <v>144.95</v>
+        <v>141.9</v>
       </c>
       <c r="E32" s="6">
-        <v>-1.08</v>
+        <v>-3.05</v>
       </c>
     </row>
     <row r="33" spans="1:5">
@@ -2082,13 +2082,13 @@
         <v>2</v>
       </c>
       <c r="C33" s="5">
-        <v>340.05</v>
+        <v>321.25</v>
       </c>
       <c r="D33" s="5">
-        <v>321.25</v>
+        <v>315.65</v>
       </c>
       <c r="E33" s="6">
-        <v>-18.8</v>
+        <v>-5.6</v>
       </c>
     </row>
     <row r="34" spans="1:5">
@@ -2099,13 +2099,13 @@
         <v>2</v>
       </c>
       <c r="C34" s="5">
-        <v>344.6</v>
+        <v>337.95</v>
       </c>
       <c r="D34" s="5">
-        <v>337.95</v>
+        <v>334.75</v>
       </c>
       <c r="E34" s="6">
-        <v>-6.65</v>
+        <v>-3.2</v>
       </c>
     </row>
     <row r="35" spans="1:5">
@@ -2116,13 +2116,13 @@
         <v>2</v>
       </c>
       <c r="C35" s="5">
-        <v>850.5</v>
+        <v>835</v>
       </c>
       <c r="D35" s="5">
-        <v>835</v>
-      </c>
-      <c r="E35" s="6">
-        <v>-15.5</v>
+        <v>844.5</v>
+      </c>
+      <c r="E35" s="7">
+        <v>9.5</v>
       </c>
     </row>
     <row r="36" spans="1:5">
@@ -2133,13 +2133,13 @@
         <v>2</v>
       </c>
       <c r="C36" s="5">
-        <v>2.44</v>
+        <v>2.49</v>
       </c>
       <c r="D36" s="5">
-        <v>2.49</v>
+        <v>2.52</v>
       </c>
       <c r="E36" s="7">
-        <v>0.05</v>
+        <v>0.03</v>
       </c>
     </row>
     <row r="37" spans="1:5">
@@ -2150,13 +2150,13 @@
         <v>24</v>
       </c>
       <c r="C37" s="5">
-        <v>36.85</v>
+        <v>35.38</v>
       </c>
       <c r="D37" s="5">
-        <v>35.38</v>
+        <v>31.57</v>
       </c>
       <c r="E37" s="6">
-        <v>-1.47</v>
+        <v>-3.81</v>
       </c>
     </row>
     <row r="38" spans="1:5">
@@ -2167,13 +2167,13 @@
         <v>24</v>
       </c>
       <c r="C38" s="5">
-        <v>35.41</v>
+        <v>30.54</v>
       </c>
       <c r="D38" s="5">
-        <v>30.54</v>
+        <v>29.24</v>
       </c>
       <c r="E38" s="6">
-        <v>-4.87</v>
+        <v>-1.3</v>
       </c>
     </row>
     <row r="39" spans="1:5">
@@ -2184,13 +2184,13 @@
         <v>24</v>
       </c>
       <c r="C39" s="5">
-        <v>25.55</v>
+        <v>22.25</v>
       </c>
       <c r="D39" s="5">
-        <v>22.25</v>
+        <v>20.85</v>
       </c>
       <c r="E39" s="6">
-        <v>-3.3</v>
+        <v>-1.4</v>
       </c>
     </row>
     <row r="40" spans="1:5">
@@ -2201,13 +2201,13 @@
         <v>24</v>
       </c>
       <c r="C40" s="5">
-        <v>34.74</v>
+        <v>31.75</v>
       </c>
       <c r="D40" s="5">
-        <v>31.75</v>
-      </c>
-      <c r="E40" s="6">
-        <v>-2.99</v>
+        <v>35.42</v>
+      </c>
+      <c r="E40" s="7">
+        <v>3.67</v>
       </c>
     </row>
     <row r="41" spans="1:5">
@@ -2218,13 +2218,13 @@
         <v>24</v>
       </c>
       <c r="C41" s="5">
-        <v>33.63</v>
+        <v>39.33</v>
       </c>
       <c r="D41" s="5">
-        <v>39.33</v>
+        <v>42.52</v>
       </c>
       <c r="E41" s="7">
-        <v>5.7</v>
+        <v>3.19</v>
       </c>
     </row>
     <row r="42" spans="1:5">
@@ -2235,13 +2235,13 @@
         <v>31</v>
       </c>
       <c r="C42" s="5">
-        <v>-19.83</v>
+        <v>42.66</v>
       </c>
       <c r="D42" s="5">
-        <v>42.66</v>
+        <v>55.93</v>
       </c>
       <c r="E42" s="7">
-        <v>62.49</v>
+        <v>13.27</v>
       </c>
     </row>
     <row r="43" spans="1:5">
@@ -2252,13 +2252,13 @@
         <v>31</v>
       </c>
       <c r="C43" s="5">
-        <v>-71.06</v>
+        <v>4.91</v>
       </c>
       <c r="D43" s="5">
-        <v>4.91</v>
+        <v>14.71</v>
       </c>
       <c r="E43" s="7">
-        <v>75.97</v>
+        <v>9.800000000000001</v>
       </c>
     </row>
     <row r="44" spans="1:5">
@@ -2269,13 +2269,13 @@
         <v>31</v>
       </c>
       <c r="C44" s="5">
-        <v>-8.76</v>
+        <v>83.18000000000001</v>
       </c>
       <c r="D44" s="5">
-        <v>83.18000000000001</v>
-      </c>
-      <c r="E44" s="7">
-        <v>91.94</v>
+        <v>45.82</v>
+      </c>
+      <c r="E44" s="6">
+        <v>-37.36</v>
       </c>
     </row>
     <row r="45" spans="1:5">
@@ -2286,13 +2286,13 @@
         <v>31</v>
       </c>
       <c r="C45" s="5">
-        <v>-47.73</v>
+        <v>-19.28</v>
       </c>
       <c r="D45" s="5">
-        <v>-19.28</v>
+        <v>-7.37</v>
       </c>
       <c r="E45" s="7">
-        <v>28.45</v>
+        <v>11.91</v>
       </c>
     </row>
     <row r="46" spans="1:5">
@@ -2303,13 +2303,13 @@
         <v>31</v>
       </c>
       <c r="C46" s="5">
-        <v>-28.66</v>
+        <v>79.28</v>
       </c>
       <c r="D46" s="5">
-        <v>79.28</v>
-      </c>
-      <c r="E46" s="7">
-        <v>107.94</v>
+        <v>-6.2</v>
+      </c>
+      <c r="E46" s="6">
+        <v>-85.48</v>
       </c>
     </row>
   </sheetData>
@@ -2374,7 +2374,7 @@
         <v>5</v>
       </c>
       <c r="D2" s="10">
-        <v>31.8</v>
+        <v>31.9</v>
       </c>
       <c r="E2" s="10">
         <v>0</v>
@@ -2383,7 +2383,7 @@
         <v>-13</v>
       </c>
       <c r="G2" s="10">
-        <v>-10.4</v>
+        <v>-10.7</v>
       </c>
       <c r="H2" s="10">
         <v>59.8</v>
@@ -2508,19 +2508,19 @@
     </row>
     <row r="2" spans="1:5">
       <c r="A2" s="13">
-        <v>0.1851</v>
+        <v>0.1699</v>
       </c>
       <c r="B2" s="13">
-        <v>0.0101</v>
+        <v>0.0072</v>
       </c>
       <c r="C2" s="13">
-        <v>0.004099999999999999</v>
+        <v>-0.0039</v>
       </c>
       <c r="D2" s="13">
-        <v>-0.0609</v>
+        <v>-0.055</v>
       </c>
       <c r="E2" s="13">
-        <v>-0.2262</v>
+        <v>-0.2288</v>
       </c>
     </row>
   </sheetData>

--- a/HINDUJA_GROUP_Technical_Metrics.xlsx
+++ b/HINDUJA_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="207" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="218" uniqueCount="70">
   <si>
     <t>Symbol</t>
   </si>
@@ -163,7 +163,34 @@
     <t>▶  SIGNAL EVENTS (vs Previous Run)</t>
   </si>
   <si>
-    <t>No signal events detected since last run.</t>
+    <t>Signal</t>
+  </si>
+  <si>
+    <t>Change</t>
+  </si>
+  <si>
+    <t>Direction</t>
+  </si>
+  <si>
+    <t>Prev Value</t>
+  </si>
+  <si>
+    <t>Curr Value</t>
+  </si>
+  <si>
+    <t>RSI Oversold Recovery</t>
+  </si>
+  <si>
+    <t>29.2 → 31.5</t>
+  </si>
+  <si>
+    <t>🟢 BULLISH</t>
+  </si>
+  <si>
+    <t>29.2</t>
+  </si>
+  <si>
+    <t>31.5</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -249,14 +276,14 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FF006100"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FF9C0006"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -289,13 +316,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -365,14 +392,15 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -888,58 +916,58 @@
         <v>42</v>
       </c>
       <c r="C2">
-        <v>141.9</v>
+        <v>142</v>
       </c>
       <c r="D2">
-        <v>-2.1</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="E2">
         <v>208.37</v>
       </c>
       <c r="F2">
-        <v>133.05</v>
+        <v>133.16</v>
       </c>
       <c r="G2">
-        <v>-31.9</v>
+        <v>-31.85</v>
       </c>
       <c r="H2">
-        <v>6.65</v>
+        <v>6.64</v>
       </c>
       <c r="I2">
-        <v>-4.71</v>
+        <v>-3.87</v>
       </c>
       <c r="J2">
-        <v>-12.89</v>
+        <v>-9.73</v>
       </c>
       <c r="K2">
-        <v>-6.07</v>
+        <v>-8.42</v>
       </c>
       <c r="L2">
-        <v>6.97</v>
+        <v>6.73</v>
       </c>
       <c r="M2">
-        <v>16.99</v>
+        <v>17.26</v>
       </c>
       <c r="N2">
         <v>99</v>
       </c>
       <c r="O2">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="P2">
-        <v>145.47</v>
+        <v>144.32</v>
       </c>
       <c r="Q2">
-        <v>148.95</v>
+        <v>148.1</v>
       </c>
       <c r="R2">
-        <v>160.92</v>
+        <v>160.24</v>
       </c>
       <c r="S2">
-        <v>167.9</v>
+        <v>167.7</v>
       </c>
       <c r="T2">
-        <v>-15.49</v>
+        <v>-15.32</v>
       </c>
       <c r="U2" t="s">
         <v>43</v>
@@ -954,31 +982,31 @@
         <v>0</v>
       </c>
       <c r="Y2">
-        <v>31.57</v>
+        <v>31.83</v>
       </c>
       <c r="Z2">
-        <v>-4.41</v>
+        <v>-4.47</v>
       </c>
       <c r="AA2">
-        <v>-4.52</v>
+        <v>-4.51</v>
       </c>
       <c r="AB2">
-        <v>0.11</v>
+        <v>0.04</v>
       </c>
       <c r="AC2">
-        <v>49.46</v>
+        <v>35.55</v>
       </c>
       <c r="AD2">
-        <v>64.42</v>
+        <v>50.59</v>
       </c>
       <c r="AE2">
-        <v>4.01</v>
+        <v>3.97</v>
       </c>
       <c r="AF2">
-        <v>55.93</v>
+        <v>53.79</v>
       </c>
       <c r="AG2">
-        <v>157.89</v>
+        <v>156.19</v>
       </c>
       <c r="AH2">
         <v>140.01</v>
@@ -990,7 +1018,7 @@
         <v>45</v>
       </c>
       <c r="AK2">
-        <v>52.75</v>
+        <v>53.45</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1001,10 +1029,10 @@
         <v>42</v>
       </c>
       <c r="C3">
-        <v>315.65</v>
+        <v>319.65</v>
       </c>
       <c r="D3">
-        <v>-1.74</v>
+        <v>1.27</v>
       </c>
       <c r="E3">
         <v>456.15</v>
@@ -1013,46 +1041,46 @@
         <v>225</v>
       </c>
       <c r="G3">
-        <v>-30.8</v>
+        <v>-29.92</v>
       </c>
       <c r="H3">
-        <v>40.29</v>
+        <v>42.07</v>
       </c>
       <c r="I3">
-        <v>-13.57</v>
+        <v>-13.3</v>
       </c>
       <c r="J3">
-        <v>-19.63</v>
+        <v>-15.94</v>
       </c>
       <c r="K3">
-        <v>-20.4</v>
+        <v>-19.27</v>
       </c>
       <c r="L3">
-        <v>-9.5</v>
+        <v>-9.84</v>
       </c>
       <c r="M3">
-        <v>0.72</v>
+        <v>1.26</v>
       </c>
       <c r="N3">
         <v>40</v>
       </c>
       <c r="O3">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="P3">
-        <v>338.59</v>
+        <v>328.78</v>
       </c>
       <c r="Q3">
-        <v>356.75</v>
+        <v>353.53</v>
       </c>
       <c r="R3">
-        <v>391.02</v>
+        <v>388.79</v>
       </c>
       <c r="S3">
-        <v>342.52</v>
+        <v>342.68</v>
       </c>
       <c r="T3">
-        <v>-7.84</v>
+        <v>-6.72</v>
       </c>
       <c r="U3" t="s">
         <v>43</v>
@@ -1067,43 +1095,43 @@
         <v>1</v>
       </c>
       <c r="Y3">
-        <v>29.24</v>
+        <v>31.47</v>
       </c>
       <c r="Z3">
-        <v>-17.7</v>
+        <v>-18.65</v>
       </c>
       <c r="AA3">
-        <v>-14.64</v>
+        <v>-15.44</v>
       </c>
       <c r="AB3">
-        <v>-3.06</v>
+        <v>-3.21</v>
       </c>
       <c r="AC3">
-        <v>13.75</v>
+        <v>6.24</v>
       </c>
       <c r="AD3">
-        <v>35.63</v>
+        <v>16.89</v>
       </c>
       <c r="AE3">
-        <v>17.46</v>
+        <v>16.91</v>
       </c>
       <c r="AF3">
-        <v>14.71</v>
+        <v>-65.64</v>
       </c>
       <c r="AG3">
-        <v>390.87</v>
+        <v>388.92</v>
       </c>
       <c r="AH3">
-        <v>322.62</v>
+        <v>318.13</v>
       </c>
       <c r="AI3">
-        <v>372.58</v>
+        <v>370.85</v>
       </c>
       <c r="AJ3" t="s">
         <v>45</v>
       </c>
       <c r="AK3">
-        <v>29.08</v>
+        <v>30.8</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1114,10 +1142,10 @@
         <v>42</v>
       </c>
       <c r="C4">
-        <v>334.75</v>
+        <v>337.55</v>
       </c>
       <c r="D4">
-        <v>-0.95</v>
+        <v>0.84</v>
       </c>
       <c r="E4">
         <v>534</v>
@@ -1126,46 +1154,46 @@
         <v>334.75</v>
       </c>
       <c r="G4">
-        <v>-37.31</v>
+        <v>-36.79</v>
       </c>
       <c r="H4">
-        <v>0</v>
+        <v>0.84</v>
       </c>
       <c r="I4">
-        <v>-6.43</v>
+        <v>-3.83</v>
       </c>
       <c r="J4">
-        <v>-11.56</v>
+        <v>-9.880000000000001</v>
       </c>
       <c r="K4">
-        <v>-20.78</v>
+        <v>-20.12</v>
       </c>
       <c r="L4">
-        <v>-31.57</v>
+        <v>-31.25</v>
       </c>
       <c r="M4">
-        <v>-22.88</v>
+        <v>-22.77</v>
       </c>
       <c r="N4">
         <v>20</v>
       </c>
       <c r="O4">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="P4">
-        <v>343.3</v>
+        <v>340.61</v>
       </c>
       <c r="Q4">
-        <v>358.02</v>
+        <v>356.07</v>
       </c>
       <c r="R4">
-        <v>379.56</v>
+        <v>378.22</v>
       </c>
       <c r="S4">
-        <v>400.23</v>
+        <v>399.68</v>
       </c>
       <c r="T4">
-        <v>-16.36</v>
+        <v>-15.54</v>
       </c>
       <c r="U4" t="s">
         <v>43</v>
@@ -1180,43 +1208,43 @@
         <v>0</v>
       </c>
       <c r="Y4">
-        <v>20.85</v>
+        <v>25.27</v>
       </c>
       <c r="Z4">
-        <v>-11.16</v>
+        <v>-11.36</v>
       </c>
       <c r="AA4">
-        <v>-9.880000000000001</v>
+        <v>-10.18</v>
       </c>
       <c r="AB4">
-        <v>-1.27</v>
+        <v>-1.18</v>
       </c>
       <c r="AC4">
-        <v>9.01</v>
+        <v>9.949999999999999</v>
       </c>
       <c r="AD4">
-        <v>22.52</v>
+        <v>13.52</v>
       </c>
       <c r="AE4">
-        <v>9.800000000000001</v>
+        <v>9.619999999999999</v>
       </c>
       <c r="AF4">
-        <v>45.82</v>
+        <v>-13.82</v>
       </c>
       <c r="AG4">
-        <v>379.81</v>
+        <v>377.84</v>
       </c>
       <c r="AH4">
-        <v>336.23</v>
+        <v>334.29</v>
       </c>
       <c r="AI4">
-        <v>366.54</v>
+        <v>364.51</v>
       </c>
       <c r="AJ4" t="s">
         <v>45</v>
       </c>
       <c r="AK4">
-        <v>60.74</v>
+        <v>63.22</v>
       </c>
     </row>
     <row r="5" spans="1:37">
@@ -1227,10 +1255,10 @@
         <v>42</v>
       </c>
       <c r="C5">
-        <v>844.5</v>
+        <v>833.3</v>
       </c>
       <c r="D5">
-        <v>1.14</v>
+        <v>-1.33</v>
       </c>
       <c r="E5">
         <v>1069.3</v>
@@ -1239,46 +1267,46 @@
         <v>752.45</v>
       </c>
       <c r="G5">
-        <v>-21.02</v>
+        <v>-22.07</v>
       </c>
       <c r="H5">
-        <v>12.23</v>
+        <v>10.74</v>
       </c>
       <c r="I5">
-        <v>-3.71</v>
+        <v>-3.46</v>
       </c>
       <c r="J5">
-        <v>-11.97</v>
+        <v>-9.369999999999999</v>
       </c>
       <c r="K5">
-        <v>-15.22</v>
+        <v>-17.22</v>
       </c>
       <c r="L5">
-        <v>11.15</v>
+        <v>9.869999999999999</v>
       </c>
       <c r="M5">
-        <v>-5.5</v>
+        <v>-5.55</v>
       </c>
       <c r="N5">
         <v>80</v>
       </c>
       <c r="O5">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="P5">
-        <v>848.55</v>
+        <v>842.5700000000001</v>
       </c>
       <c r="Q5">
-        <v>874.15</v>
+        <v>870.2</v>
       </c>
       <c r="R5">
-        <v>944.36</v>
+        <v>940.53</v>
       </c>
       <c r="S5">
-        <v>924.73</v>
+        <v>924.3200000000001</v>
       </c>
       <c r="T5">
-        <v>-8.68</v>
+        <v>-9.85</v>
       </c>
       <c r="U5" t="s">
         <v>43</v>
@@ -1293,43 +1321,43 @@
         <v>1</v>
       </c>
       <c r="Y5">
-        <v>35.42</v>
+        <v>33.15</v>
       </c>
       <c r="Z5">
-        <v>-27.69</v>
+        <v>-28</v>
       </c>
       <c r="AA5">
-        <v>-27.82</v>
+        <v>-27.86</v>
       </c>
       <c r="AB5">
-        <v>0.13</v>
+        <v>-0.14</v>
       </c>
       <c r="AC5">
-        <v>40.86</v>
+        <v>36.88</v>
       </c>
       <c r="AD5">
-        <v>44.65</v>
+        <v>38.67</v>
       </c>
       <c r="AE5">
-        <v>23.1</v>
+        <v>22.77</v>
       </c>
       <c r="AF5">
-        <v>-7.37</v>
+        <v>24.28</v>
       </c>
       <c r="AG5">
-        <v>918.6799999999999</v>
+        <v>914.52</v>
       </c>
       <c r="AH5">
-        <v>829.61</v>
+        <v>825.88</v>
       </c>
       <c r="AI5">
-        <v>911.14</v>
+        <v>910.86</v>
       </c>
       <c r="AJ5" t="s">
         <v>45</v>
       </c>
       <c r="AK5">
-        <v>49.75</v>
+        <v>50.39</v>
       </c>
     </row>
     <row r="6" spans="1:37">
@@ -1340,10 +1368,10 @@
         <v>42</v>
       </c>
       <c r="C6">
-        <v>2.52</v>
+        <v>2.51</v>
       </c>
       <c r="D6">
-        <v>1.2</v>
+        <v>-0.4</v>
       </c>
       <c r="E6">
         <v>3.38</v>
@@ -1352,34 +1380,34 @@
         <v>1.84</v>
       </c>
       <c r="G6">
-        <v>-25.44</v>
+        <v>-25.74</v>
       </c>
       <c r="H6">
-        <v>36.96</v>
+        <v>36.41</v>
       </c>
       <c r="I6">
-        <v>-3.08</v>
+        <v>-3.46</v>
       </c>
       <c r="J6">
-        <v>-8.699999999999999</v>
+        <v>-6.69</v>
       </c>
       <c r="K6">
-        <v>9.09</v>
+        <v>8.19</v>
       </c>
       <c r="L6">
-        <v>-20.25</v>
+        <v>-23.48</v>
       </c>
       <c r="M6">
-        <v>-0.39</v>
+        <v>-1.38</v>
       </c>
       <c r="N6">
         <v>60</v>
       </c>
       <c r="O6">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="P6">
-        <v>2.5</v>
+        <v>2.48</v>
       </c>
       <c r="Q6">
         <v>2.57</v>
@@ -1388,10 +1416,10 @@
         <v>2.68</v>
       </c>
       <c r="S6">
-        <v>2.63</v>
+        <v>2.62</v>
       </c>
       <c r="T6">
-        <v>-4.06</v>
+        <v>-4.37</v>
       </c>
       <c r="U6" t="s">
         <v>43</v>
@@ -1406,34 +1434,34 @@
         <v>1</v>
       </c>
       <c r="Y6">
-        <v>42.52</v>
+        <v>41.73</v>
       </c>
       <c r="Z6">
         <v>-0.05</v>
       </c>
       <c r="AA6">
-        <v>-0.04</v>
+        <v>-0.05</v>
       </c>
       <c r="AB6">
         <v>-0.01</v>
       </c>
       <c r="AC6">
-        <v>40.38</v>
+        <v>62.8</v>
       </c>
       <c r="AD6">
-        <v>29.64</v>
+        <v>39.65</v>
       </c>
       <c r="AE6">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="AF6">
-        <v>-6.2</v>
+        <v>-60.72</v>
       </c>
       <c r="AG6">
         <v>2.68</v>
       </c>
       <c r="AH6">
-        <v>2.46</v>
+        <v>2.45</v>
       </c>
       <c r="AI6">
         <v>2.81</v>
@@ -1442,7 +1470,7 @@
         <v>45</v>
       </c>
       <c r="AK6">
-        <v>38.12</v>
+        <v>38.95</v>
       </c>
     </row>
   </sheetData>
@@ -1603,12 +1631,47 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="3" t="s">
         <v>47</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
+      <c r="A3" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>56</v>
       </c>
     </row>
     <row r="5" spans="1:6">
       <c r="A5" s="2" t="s">
-        <v>48</v>
+        <v>57</v>
       </c>
       <c r="B5" s="2"/>
       <c r="C5" s="2"/>
@@ -1616,700 +1679,700 @@
       <c r="E5" s="2"/>
     </row>
     <row r="6" spans="1:6">
-      <c r="A6" s="4" t="s">
+      <c r="A6" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B6" s="4" t="s">
-        <v>49</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="D6" s="4" t="s">
-        <v>51</v>
-      </c>
-      <c r="E6" s="4" t="s">
-        <v>52</v>
+      <c r="B6" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>61</v>
       </c>
     </row>
     <row r="7" spans="1:6">
-      <c r="A7" s="3" t="s">
+      <c r="A7" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B7" s="3" t="s">
+      <c r="B7" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C7" s="5">
-        <v>-9.83</v>
-      </c>
-      <c r="D7" s="5">
+      <c r="C7" s="6">
         <v>-12.89</v>
       </c>
-      <c r="E7" s="6">
-        <v>-3.06</v>
+      <c r="D7" s="6">
+        <v>-9.73</v>
+      </c>
+      <c r="E7" s="7">
+        <v>3.16</v>
       </c>
     </row>
     <row r="8" spans="1:6">
-      <c r="A8" s="3" t="s">
+      <c r="A8" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B8" s="3" t="s">
+      <c r="B8" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C8" s="5">
-        <v>-21.85</v>
-      </c>
-      <c r="D8" s="5">
+      <c r="C8" s="6">
         <v>-19.63</v>
       </c>
+      <c r="D8" s="6">
+        <v>-15.94</v>
+      </c>
       <c r="E8" s="7">
-        <v>2.22</v>
+        <v>3.69</v>
       </c>
     </row>
     <row r="9" spans="1:6">
-      <c r="A9" s="3" t="s">
+      <c r="A9" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B9" s="3" t="s">
+      <c r="B9" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C9" s="5">
-        <v>-10.98</v>
-      </c>
-      <c r="D9" s="5">
+      <c r="C9" s="6">
         <v>-11.56</v>
       </c>
-      <c r="E9" s="6">
-        <v>-0.58</v>
+      <c r="D9" s="6">
+        <v>-9.880000000000001</v>
+      </c>
+      <c r="E9" s="7">
+        <v>1.68</v>
       </c>
     </row>
     <row r="10" spans="1:6">
-      <c r="A10" s="3" t="s">
+      <c r="A10" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="B10" s="3" t="s">
+      <c r="B10" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C10" s="5">
-        <v>-12.57</v>
-      </c>
-      <c r="D10" s="5">
+      <c r="C10" s="6">
         <v>-11.97</v>
       </c>
+      <c r="D10" s="6">
+        <v>-9.369999999999999</v>
+      </c>
       <c r="E10" s="7">
-        <v>0.6</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="11" spans="1:6">
-      <c r="A11" s="3" t="s">
+      <c r="A11" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B11" s="3" t="s">
+      <c r="B11" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C11" s="5">
-        <v>-9.779999999999999</v>
-      </c>
-      <c r="D11" s="5">
+      <c r="C11" s="6">
         <v>-8.699999999999999</v>
       </c>
+      <c r="D11" s="6">
+        <v>-6.69</v>
+      </c>
       <c r="E11" s="7">
-        <v>1.08</v>
+        <v>2.01</v>
       </c>
     </row>
     <row r="12" spans="1:6">
-      <c r="A12" s="3" t="s">
+      <c r="A12" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B12" s="3" t="s">
+      <c r="B12" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="C12" s="5">
-        <v>-2.18</v>
-      </c>
-      <c r="D12" s="5">
+      <c r="C12" s="6">
         <v>-4.71</v>
       </c>
-      <c r="E12" s="6">
-        <v>-2.53</v>
+      <c r="D12" s="6">
+        <v>-3.87</v>
+      </c>
+      <c r="E12" s="7">
+        <v>0.84</v>
       </c>
     </row>
     <row r="13" spans="1:6">
-      <c r="A13" s="3" t="s">
+      <c r="A13" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B13" s="3" t="s">
+      <c r="B13" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="C13" s="5">
-        <v>-11.31</v>
-      </c>
-      <c r="D13" s="5">
+      <c r="C13" s="6">
         <v>-13.57</v>
       </c>
-      <c r="E13" s="6">
-        <v>-2.26</v>
+      <c r="D13" s="6">
+        <v>-13.3</v>
+      </c>
+      <c r="E13" s="7">
+        <v>0.27</v>
       </c>
     </row>
     <row r="14" spans="1:6">
-      <c r="A14" s="3" t="s">
+      <c r="A14" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B14" s="3" t="s">
+      <c r="B14" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="C14" s="5">
-        <v>-5.55</v>
-      </c>
-      <c r="D14" s="5">
+      <c r="C14" s="6">
         <v>-6.43</v>
       </c>
-      <c r="E14" s="6">
-        <v>-0.88</v>
+      <c r="D14" s="6">
+        <v>-3.83</v>
+      </c>
+      <c r="E14" s="7">
+        <v>2.6</v>
       </c>
     </row>
     <row r="15" spans="1:6">
-      <c r="A15" s="3" t="s">
+      <c r="A15" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="B15" s="3" t="s">
+      <c r="B15" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="C15" s="5">
-        <v>-5.69</v>
-      </c>
-      <c r="D15" s="5">
+      <c r="C15" s="6">
         <v>-3.71</v>
       </c>
+      <c r="D15" s="6">
+        <v>-3.46</v>
+      </c>
       <c r="E15" s="7">
-        <v>1.98</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="16" spans="1:6">
-      <c r="A16" s="3" t="s">
+      <c r="A16" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B16" s="3" t="s">
+      <c r="B16" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="C16" s="5">
-        <v>-3.11</v>
-      </c>
-      <c r="D16" s="5">
+      <c r="C16" s="6">
         <v>-3.08</v>
       </c>
-      <c r="E16" s="7">
-        <v>0.03</v>
+      <c r="D16" s="6">
+        <v>-3.46</v>
+      </c>
+      <c r="E16" s="8">
+        <v>-0.38</v>
       </c>
     </row>
     <row r="17" spans="1:5">
-      <c r="A17" s="3" t="s">
+      <c r="A17" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B17" s="3" t="s">
+      <c r="B17" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="C17" s="5">
-        <v>10.35</v>
-      </c>
-      <c r="D17" s="5">
+      <c r="C17" s="6">
         <v>6.97</v>
       </c>
-      <c r="E17" s="6">
-        <v>-3.38</v>
+      <c r="D17" s="6">
+        <v>6.73</v>
+      </c>
+      <c r="E17" s="8">
+        <v>-0.24</v>
       </c>
     </row>
     <row r="18" spans="1:5">
-      <c r="A18" s="3" t="s">
+      <c r="A18" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B18" s="3" t="s">
+      <c r="B18" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="C18" s="5">
-        <v>-8.83</v>
-      </c>
-      <c r="D18" s="5">
+      <c r="C18" s="6">
         <v>-9.5</v>
       </c>
-      <c r="E18" s="6">
-        <v>-0.67</v>
+      <c r="D18" s="6">
+        <v>-9.84</v>
+      </c>
+      <c r="E18" s="8">
+        <v>-0.34</v>
       </c>
     </row>
     <row r="19" spans="1:5">
-      <c r="A19" s="3" t="s">
+      <c r="A19" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B19" s="3" t="s">
+      <c r="B19" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="C19" s="5">
-        <v>-30.88</v>
-      </c>
-      <c r="D19" s="5">
+      <c r="C19" s="6">
         <v>-31.57</v>
       </c>
-      <c r="E19" s="6">
-        <v>-0.6899999999999999</v>
+      <c r="D19" s="6">
+        <v>-31.25</v>
+      </c>
+      <c r="E19" s="7">
+        <v>0.32</v>
       </c>
     </row>
     <row r="20" spans="1:5">
-      <c r="A20" s="3" t="s">
+      <c r="A20" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="B20" s="3" t="s">
+      <c r="B20" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="C20" s="5">
-        <v>11.19</v>
-      </c>
-      <c r="D20" s="5">
+      <c r="C20" s="6">
         <v>11.15</v>
       </c>
-      <c r="E20" s="6">
-        <v>-0.04</v>
+      <c r="D20" s="6">
+        <v>9.869999999999999</v>
+      </c>
+      <c r="E20" s="8">
+        <v>-1.28</v>
       </c>
     </row>
     <row r="21" spans="1:5">
-      <c r="A21" s="3" t="s">
+      <c r="A21" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B21" s="3" t="s">
+      <c r="B21" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="C21" s="5">
-        <v>-21.2</v>
-      </c>
-      <c r="D21" s="5">
+      <c r="C21" s="6">
         <v>-20.25</v>
       </c>
-      <c r="E21" s="7">
-        <v>0.95</v>
+      <c r="D21" s="6">
+        <v>-23.48</v>
+      </c>
+      <c r="E21" s="8">
+        <v>-3.23</v>
       </c>
     </row>
     <row r="22" spans="1:5">
-      <c r="A22" s="3" t="s">
+      <c r="A22" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B22" s="3" t="s">
+      <c r="B22" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="C22" s="5">
-        <v>-3.78</v>
-      </c>
-      <c r="D22" s="5">
+      <c r="C22" s="6">
         <v>-6.07</v>
       </c>
-      <c r="E22" s="6">
-        <v>-2.29</v>
+      <c r="D22" s="6">
+        <v>-8.42</v>
+      </c>
+      <c r="E22" s="8">
+        <v>-2.35</v>
       </c>
     </row>
     <row r="23" spans="1:5">
-      <c r="A23" s="3" t="s">
+      <c r="A23" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B23" s="3" t="s">
+      <c r="B23" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="C23" s="5">
-        <v>-17.8</v>
-      </c>
-      <c r="D23" s="5">
+      <c r="C23" s="6">
         <v>-20.4</v>
       </c>
-      <c r="E23" s="6">
-        <v>-2.6</v>
+      <c r="D23" s="6">
+        <v>-19.27</v>
+      </c>
+      <c r="E23" s="7">
+        <v>1.13</v>
       </c>
     </row>
     <row r="24" spans="1:5">
-      <c r="A24" s="3" t="s">
+      <c r="A24" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B24" s="3" t="s">
+      <c r="B24" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="C24" s="5">
-        <v>-20.61</v>
-      </c>
-      <c r="D24" s="5">
+      <c r="C24" s="6">
         <v>-20.78</v>
       </c>
-      <c r="E24" s="6">
-        <v>-0.17</v>
+      <c r="D24" s="6">
+        <v>-20.12</v>
+      </c>
+      <c r="E24" s="7">
+        <v>0.66</v>
       </c>
     </row>
     <row r="25" spans="1:5">
-      <c r="A25" s="3" t="s">
+      <c r="A25" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="B25" s="3" t="s">
+      <c r="B25" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="C25" s="5">
-        <v>-16.96</v>
-      </c>
-      <c r="D25" s="5">
+      <c r="C25" s="6">
         <v>-15.22</v>
       </c>
-      <c r="E25" s="7">
-        <v>1.74</v>
+      <c r="D25" s="6">
+        <v>-17.22</v>
+      </c>
+      <c r="E25" s="8">
+        <v>-2</v>
       </c>
     </row>
     <row r="26" spans="1:5">
-      <c r="A26" s="3" t="s">
+      <c r="A26" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B26" s="3" t="s">
+      <c r="B26" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="C26" s="5">
-        <v>7.33</v>
-      </c>
-      <c r="D26" s="5">
+      <c r="C26" s="6">
         <v>9.09</v>
       </c>
-      <c r="E26" s="7">
-        <v>1.76</v>
+      <c r="D26" s="6">
+        <v>8.19</v>
+      </c>
+      <c r="E26" s="8">
+        <v>-0.9</v>
       </c>
     </row>
     <row r="27" spans="1:5">
-      <c r="A27" s="3" t="s">
+      <c r="A27" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B27" s="3" t="s">
+      <c r="B27" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="C27" s="5">
-        <v>-30.44</v>
-      </c>
-      <c r="D27" s="5">
+      <c r="C27" s="6">
         <v>-31.9</v>
       </c>
-      <c r="E27" s="6">
-        <v>-1.46</v>
+      <c r="D27" s="6">
+        <v>-31.85</v>
+      </c>
+      <c r="E27" s="7">
+        <v>0.05</v>
       </c>
     </row>
     <row r="28" spans="1:5">
-      <c r="A28" s="3" t="s">
+      <c r="A28" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B28" s="3" t="s">
+      <c r="B28" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="C28" s="5">
-        <v>-29.57</v>
-      </c>
-      <c r="D28" s="5">
+      <c r="C28" s="6">
         <v>-30.8</v>
       </c>
-      <c r="E28" s="6">
-        <v>-1.23</v>
+      <c r="D28" s="6">
+        <v>-29.92</v>
+      </c>
+      <c r="E28" s="7">
+        <v>0.88</v>
       </c>
     </row>
     <row r="29" spans="1:5">
-      <c r="A29" s="3" t="s">
+      <c r="A29" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B29" s="3" t="s">
+      <c r="B29" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="C29" s="5">
-        <v>-36.71</v>
-      </c>
-      <c r="D29" s="5">
+      <c r="C29" s="6">
         <v>-37.31</v>
       </c>
-      <c r="E29" s="6">
-        <v>-0.6</v>
+      <c r="D29" s="6">
+        <v>-36.79</v>
+      </c>
+      <c r="E29" s="7">
+        <v>0.52</v>
       </c>
     </row>
     <row r="30" spans="1:5">
-      <c r="A30" s="3" t="s">
+      <c r="A30" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="B30" s="3" t="s">
+      <c r="B30" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="C30" s="5">
-        <v>-21.91</v>
-      </c>
-      <c r="D30" s="5">
+      <c r="C30" s="6">
         <v>-21.02</v>
       </c>
-      <c r="E30" s="7">
-        <v>0.89</v>
+      <c r="D30" s="6">
+        <v>-22.07</v>
+      </c>
+      <c r="E30" s="8">
+        <v>-1.05</v>
       </c>
     </row>
     <row r="31" spans="1:5">
-      <c r="A31" s="3" t="s">
+      <c r="A31" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B31" s="3" t="s">
+      <c r="B31" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="C31" s="5">
-        <v>-26.33</v>
-      </c>
-      <c r="D31" s="5">
+      <c r="C31" s="6">
         <v>-25.44</v>
       </c>
-      <c r="E31" s="7">
-        <v>0.89</v>
+      <c r="D31" s="6">
+        <v>-25.74</v>
+      </c>
+      <c r="E31" s="8">
+        <v>-0.3</v>
       </c>
     </row>
     <row r="32" spans="1:5">
-      <c r="A32" s="3" t="s">
+      <c r="A32" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B32" s="3" t="s">
+      <c r="B32" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="C32" s="5">
-        <v>144.95</v>
-      </c>
-      <c r="D32" s="5">
+      <c r="C32" s="6">
         <v>141.9</v>
       </c>
-      <c r="E32" s="6">
-        <v>-3.05</v>
+      <c r="D32" s="6">
+        <v>142</v>
+      </c>
+      <c r="E32" s="7">
+        <v>0.1</v>
       </c>
     </row>
     <row r="33" spans="1:5">
-      <c r="A33" s="3" t="s">
+      <c r="A33" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B33" s="3" t="s">
+      <c r="B33" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="C33" s="5">
-        <v>321.25</v>
-      </c>
-      <c r="D33" s="5">
+      <c r="C33" s="6">
         <v>315.65</v>
       </c>
-      <c r="E33" s="6">
-        <v>-5.6</v>
+      <c r="D33" s="6">
+        <v>319.65</v>
+      </c>
+      <c r="E33" s="7">
+        <v>4</v>
       </c>
     </row>
     <row r="34" spans="1:5">
-      <c r="A34" s="3" t="s">
+      <c r="A34" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B34" s="3" t="s">
+      <c r="B34" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="C34" s="5">
-        <v>337.95</v>
-      </c>
-      <c r="D34" s="5">
+      <c r="C34" s="6">
         <v>334.75</v>
       </c>
-      <c r="E34" s="6">
-        <v>-3.2</v>
+      <c r="D34" s="6">
+        <v>337.55</v>
+      </c>
+      <c r="E34" s="7">
+        <v>2.8</v>
       </c>
     </row>
     <row r="35" spans="1:5">
-      <c r="A35" s="3" t="s">
+      <c r="A35" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="B35" s="3" t="s">
+      <c r="B35" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="C35" s="5">
-        <v>835</v>
-      </c>
-      <c r="D35" s="5">
+      <c r="C35" s="6">
         <v>844.5</v>
       </c>
-      <c r="E35" s="7">
-        <v>9.5</v>
+      <c r="D35" s="6">
+        <v>833.3</v>
+      </c>
+      <c r="E35" s="8">
+        <v>-11.2</v>
       </c>
     </row>
     <row r="36" spans="1:5">
-      <c r="A36" s="3" t="s">
+      <c r="A36" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B36" s="3" t="s">
+      <c r="B36" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="C36" s="5">
-        <v>2.49</v>
-      </c>
-      <c r="D36" s="5">
+      <c r="C36" s="6">
         <v>2.52</v>
       </c>
-      <c r="E36" s="7">
-        <v>0.03</v>
+      <c r="D36" s="6">
+        <v>2.51</v>
+      </c>
+      <c r="E36" s="8">
+        <v>-0.01</v>
       </c>
     </row>
     <row r="37" spans="1:5">
-      <c r="A37" s="3" t="s">
+      <c r="A37" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B37" s="3" t="s">
+      <c r="B37" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="C37" s="5">
-        <v>35.38</v>
-      </c>
-      <c r="D37" s="5">
+      <c r="C37" s="6">
         <v>31.57</v>
       </c>
-      <c r="E37" s="6">
-        <v>-3.81</v>
+      <c r="D37" s="6">
+        <v>31.83</v>
+      </c>
+      <c r="E37" s="7">
+        <v>0.26</v>
       </c>
     </row>
     <row r="38" spans="1:5">
-      <c r="A38" s="3" t="s">
+      <c r="A38" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B38" s="3" t="s">
+      <c r="B38" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="C38" s="5">
-        <v>30.54</v>
-      </c>
-      <c r="D38" s="5">
+      <c r="C38" s="6">
         <v>29.24</v>
       </c>
-      <c r="E38" s="6">
-        <v>-1.3</v>
+      <c r="D38" s="6">
+        <v>31.47</v>
+      </c>
+      <c r="E38" s="7">
+        <v>2.23</v>
       </c>
     </row>
     <row r="39" spans="1:5">
-      <c r="A39" s="3" t="s">
+      <c r="A39" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B39" s="3" t="s">
+      <c r="B39" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="C39" s="5">
-        <v>22.25</v>
-      </c>
-      <c r="D39" s="5">
+      <c r="C39" s="6">
         <v>20.85</v>
       </c>
-      <c r="E39" s="6">
-        <v>-1.4</v>
+      <c r="D39" s="6">
+        <v>25.27</v>
+      </c>
+      <c r="E39" s="7">
+        <v>4.42</v>
       </c>
     </row>
     <row r="40" spans="1:5">
-      <c r="A40" s="3" t="s">
+      <c r="A40" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="B40" s="3" t="s">
+      <c r="B40" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="C40" s="5">
-        <v>31.75</v>
-      </c>
-      <c r="D40" s="5">
+      <c r="C40" s="6">
         <v>35.42</v>
       </c>
-      <c r="E40" s="7">
-        <v>3.67</v>
+      <c r="D40" s="6">
+        <v>33.15</v>
+      </c>
+      <c r="E40" s="8">
+        <v>-2.27</v>
       </c>
     </row>
     <row r="41" spans="1:5">
-      <c r="A41" s="3" t="s">
+      <c r="A41" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B41" s="3" t="s">
+      <c r="B41" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="C41" s="5">
-        <v>39.33</v>
-      </c>
-      <c r="D41" s="5">
+      <c r="C41" s="6">
         <v>42.52</v>
       </c>
-      <c r="E41" s="7">
-        <v>3.19</v>
+      <c r="D41" s="6">
+        <v>41.73</v>
+      </c>
+      <c r="E41" s="8">
+        <v>-0.79</v>
       </c>
     </row>
     <row r="42" spans="1:5">
-      <c r="A42" s="3" t="s">
+      <c r="A42" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B42" s="3" t="s">
+      <c r="B42" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="C42" s="5">
-        <v>42.66</v>
-      </c>
-      <c r="D42" s="5">
+      <c r="C42" s="6">
         <v>55.93</v>
       </c>
-      <c r="E42" s="7">
-        <v>13.27</v>
+      <c r="D42" s="6">
+        <v>53.79</v>
+      </c>
+      <c r="E42" s="8">
+        <v>-2.14</v>
       </c>
     </row>
     <row r="43" spans="1:5">
-      <c r="A43" s="3" t="s">
+      <c r="A43" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B43" s="3" t="s">
+      <c r="B43" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="C43" s="5">
-        <v>4.91</v>
-      </c>
-      <c r="D43" s="5">
+      <c r="C43" s="6">
         <v>14.71</v>
       </c>
-      <c r="E43" s="7">
-        <v>9.800000000000001</v>
+      <c r="D43" s="6">
+        <v>-65.64</v>
+      </c>
+      <c r="E43" s="8">
+        <v>-80.34999999999999</v>
       </c>
     </row>
     <row r="44" spans="1:5">
-      <c r="A44" s="3" t="s">
+      <c r="A44" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B44" s="3" t="s">
+      <c r="B44" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="C44" s="5">
-        <v>83.18000000000001</v>
-      </c>
-      <c r="D44" s="5">
+      <c r="C44" s="6">
         <v>45.82</v>
       </c>
-      <c r="E44" s="6">
-        <v>-37.36</v>
+      <c r="D44" s="6">
+        <v>-13.82</v>
+      </c>
+      <c r="E44" s="8">
+        <v>-59.64</v>
       </c>
     </row>
     <row r="45" spans="1:5">
-      <c r="A45" s="3" t="s">
+      <c r="A45" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="B45" s="3" t="s">
+      <c r="B45" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="C45" s="5">
-        <v>-19.28</v>
-      </c>
-      <c r="D45" s="5">
+      <c r="C45" s="6">
         <v>-7.37</v>
       </c>
+      <c r="D45" s="6">
+        <v>24.28</v>
+      </c>
       <c r="E45" s="7">
-        <v>11.91</v>
+        <v>31.65</v>
       </c>
     </row>
     <row r="46" spans="1:5">
-      <c r="A46" s="3" t="s">
+      <c r="A46" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B46" s="3" t="s">
+      <c r="B46" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="C46" s="5">
-        <v>79.28</v>
-      </c>
-      <c r="D46" s="5">
+      <c r="C46" s="6">
         <v>-6.2</v>
       </c>
-      <c r="E46" s="6">
-        <v>-85.48</v>
+      <c r="D46" s="6">
+        <v>-60.72</v>
+      </c>
+      <c r="E46" s="8">
+        <v>-54.52</v>
       </c>
     </row>
   </sheetData>
@@ -2335,60 +2398,60 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="28" customHeight="1">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="8" t="s">
-        <v>53</v>
-      </c>
-      <c r="C1" s="8" t="s">
-        <v>54</v>
-      </c>
-      <c r="D1" s="8" t="s">
-        <v>55</v>
-      </c>
-      <c r="E1" s="8" t="s">
-        <v>56</v>
-      </c>
-      <c r="F1" s="8" t="s">
-        <v>57</v>
-      </c>
-      <c r="G1" s="8" t="s">
-        <v>58</v>
-      </c>
-      <c r="H1" s="8" t="s">
-        <v>59</v>
-      </c>
-      <c r="I1" s="8" t="s">
-        <v>60</v>
+      <c r="B1" s="9" t="s">
+        <v>62</v>
+      </c>
+      <c r="C1" s="9" t="s">
+        <v>63</v>
+      </c>
+      <c r="D1" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="E1" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="F1" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="G1" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="H1" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="I1" s="9" t="s">
+        <v>69</v>
       </c>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="9" t="s">
+      <c r="A2" s="10" t="s">
         <v>42</v>
       </c>
-      <c r="B2" s="10">
+      <c r="B2" s="11">
         <v>33.92</v>
       </c>
-      <c r="C2" s="11">
+      <c r="C2" s="12">
         <v>5</v>
       </c>
-      <c r="D2" s="10">
-        <v>31.9</v>
-      </c>
-      <c r="E2" s="10">
+      <c r="D2" s="11">
+        <v>32.7</v>
+      </c>
+      <c r="E2" s="11">
         <v>0</v>
       </c>
-      <c r="F2" s="10">
-        <v>-13</v>
-      </c>
-      <c r="G2" s="10">
-        <v>-10.7</v>
-      </c>
-      <c r="H2" s="10">
+      <c r="F2" s="11">
+        <v>-10.3</v>
+      </c>
+      <c r="G2" s="11">
+        <v>-11.4</v>
+      </c>
+      <c r="H2" s="11">
         <v>59.8</v>
       </c>
-      <c r="I2" s="10">
+      <c r="I2" s="11">
         <v>0</v>
       </c>
     </row>
@@ -2490,37 +2553,37 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
-      <c r="A1" s="12" t="s">
+      <c r="A1" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="B1" s="12" t="s">
+      <c r="B1" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="C1" s="12" t="s">
+      <c r="C1" s="13" t="s">
         <v>41</v>
       </c>
-      <c r="D1" s="12" t="s">
+      <c r="D1" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="E1" s="12" t="s">
+      <c r="E1" s="13" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="2" spans="1:5">
-      <c r="A2" s="13">
-        <v>0.1699</v>
-      </c>
-      <c r="B2" s="13">
-        <v>0.0072</v>
-      </c>
-      <c r="C2" s="13">
-        <v>-0.0039</v>
-      </c>
-      <c r="D2" s="13">
-        <v>-0.055</v>
-      </c>
-      <c r="E2" s="13">
-        <v>-0.2288</v>
+      <c r="A2" s="14">
+        <v>0.1726</v>
+      </c>
+      <c r="B2" s="14">
+        <v>0.0126</v>
+      </c>
+      <c r="C2" s="14">
+        <v>-0.0138</v>
+      </c>
+      <c r="D2" s="14">
+        <v>-0.0555</v>
+      </c>
+      <c r="E2" s="14">
+        <v>-0.2277</v>
       </c>
     </row>
   </sheetData>

--- a/HINDUJA_GROUP_Technical_Metrics.xlsx
+++ b/HINDUJA_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="218" uniqueCount="70">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="207" uniqueCount="61">
   <si>
     <t>Symbol</t>
   </si>
@@ -163,34 +163,7 @@
     <t>▶  SIGNAL EVENTS (vs Previous Run)</t>
   </si>
   <si>
-    <t>Signal</t>
-  </si>
-  <si>
-    <t>Change</t>
-  </si>
-  <si>
-    <t>Direction</t>
-  </si>
-  <si>
-    <t>Prev Value</t>
-  </si>
-  <si>
-    <t>Curr Value</t>
-  </si>
-  <si>
-    <t>RSI Oversold Recovery</t>
-  </si>
-  <si>
-    <t>29.2 → 31.5</t>
-  </si>
-  <si>
-    <t>🟢 BULLISH</t>
-  </si>
-  <si>
-    <t>29.2</t>
-  </si>
-  <si>
-    <t>31.5</t>
+    <t>No signal events detected since last run.</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -392,15 +365,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -916,10 +888,10 @@
         <v>42</v>
       </c>
       <c r="C2">
-        <v>142</v>
+        <v>144.85</v>
       </c>
       <c r="D2">
-        <v>0.07000000000000001</v>
+        <v>2.01</v>
       </c>
       <c r="E2">
         <v>208.37</v>
@@ -928,46 +900,46 @@
         <v>133.16</v>
       </c>
       <c r="G2">
-        <v>-31.85</v>
+        <v>-30.48</v>
       </c>
       <c r="H2">
-        <v>6.64</v>
+        <v>8.779999999999999</v>
       </c>
       <c r="I2">
-        <v>-3.87</v>
+        <v>-1.29</v>
       </c>
       <c r="J2">
-        <v>-9.73</v>
+        <v>-8.949999999999999</v>
       </c>
       <c r="K2">
-        <v>-8.42</v>
+        <v>-8.029999999999999</v>
       </c>
       <c r="L2">
-        <v>6.73</v>
+        <v>7.6</v>
       </c>
       <c r="M2">
-        <v>17.26</v>
+        <v>17.82</v>
       </c>
       <c r="N2">
         <v>99</v>
       </c>
       <c r="O2">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="P2">
-        <v>144.32</v>
+        <v>143.95</v>
       </c>
       <c r="Q2">
-        <v>148.1</v>
+        <v>147.58</v>
       </c>
       <c r="R2">
-        <v>160.24</v>
+        <v>159.7</v>
       </c>
       <c r="S2">
-        <v>167.7</v>
+        <v>167.51</v>
       </c>
       <c r="T2">
-        <v>-15.32</v>
+        <v>-13.53</v>
       </c>
       <c r="U2" t="s">
         <v>43</v>
@@ -982,34 +954,34 @@
         <v>0</v>
       </c>
       <c r="Y2">
-        <v>31.83</v>
+        <v>38.93</v>
       </c>
       <c r="Z2">
-        <v>-4.47</v>
+        <v>-4.25</v>
       </c>
       <c r="AA2">
-        <v>-4.51</v>
+        <v>-4.46</v>
       </c>
       <c r="AB2">
-        <v>0.04</v>
+        <v>0.21</v>
       </c>
       <c r="AC2">
-        <v>35.55</v>
+        <v>45.4</v>
       </c>
       <c r="AD2">
-        <v>50.59</v>
+        <v>43.47</v>
       </c>
       <c r="AE2">
-        <v>3.97</v>
+        <v>3.96</v>
       </c>
       <c r="AF2">
-        <v>53.79</v>
+        <v>-7.89</v>
       </c>
       <c r="AG2">
-        <v>156.19</v>
+        <v>155.05</v>
       </c>
       <c r="AH2">
-        <v>140.01</v>
+        <v>140.1</v>
       </c>
       <c r="AI2">
         <v>154.47</v>
@@ -1018,7 +990,7 @@
         <v>45</v>
       </c>
       <c r="AK2">
-        <v>53.45</v>
+        <v>54.44</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1029,10 +1001,10 @@
         <v>42</v>
       </c>
       <c r="C3">
-        <v>319.65</v>
+        <v>320.45</v>
       </c>
       <c r="D3">
-        <v>1.27</v>
+        <v>0.25</v>
       </c>
       <c r="E3">
         <v>456.15</v>
@@ -1041,46 +1013,46 @@
         <v>225</v>
       </c>
       <c r="G3">
-        <v>-29.92</v>
+        <v>-29.75</v>
       </c>
       <c r="H3">
-        <v>42.07</v>
+        <v>42.42</v>
       </c>
       <c r="I3">
-        <v>-13.3</v>
+        <v>-7.73</v>
       </c>
       <c r="J3">
-        <v>-15.94</v>
+        <v>-16.57</v>
       </c>
       <c r="K3">
-        <v>-19.27</v>
+        <v>-17.44</v>
       </c>
       <c r="L3">
-        <v>-9.84</v>
+        <v>-8.15</v>
       </c>
       <c r="M3">
-        <v>1.26</v>
+        <v>1.62</v>
       </c>
       <c r="N3">
         <v>40</v>
       </c>
       <c r="O3">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="P3">
-        <v>328.78</v>
+        <v>323.41</v>
       </c>
       <c r="Q3">
-        <v>353.53</v>
+        <v>350.6</v>
       </c>
       <c r="R3">
-        <v>388.79</v>
+        <v>387.26</v>
       </c>
       <c r="S3">
-        <v>342.68</v>
+        <v>342.86</v>
       </c>
       <c r="T3">
-        <v>-6.72</v>
+        <v>-6.54</v>
       </c>
       <c r="U3" t="s">
         <v>43</v>
@@ -1095,43 +1067,43 @@
         <v>1</v>
       </c>
       <c r="Y3">
-        <v>31.47</v>
+        <v>31.94</v>
       </c>
       <c r="Z3">
-        <v>-18.65</v>
+        <v>-19.12</v>
       </c>
       <c r="AA3">
-        <v>-15.44</v>
+        <v>-16.18</v>
       </c>
       <c r="AB3">
-        <v>-3.21</v>
+        <v>-2.95</v>
       </c>
       <c r="AC3">
-        <v>6.24</v>
+        <v>10.38</v>
       </c>
       <c r="AD3">
-        <v>16.89</v>
+        <v>10.12</v>
       </c>
       <c r="AE3">
-        <v>16.91</v>
+        <v>16.37</v>
       </c>
       <c r="AF3">
-        <v>-65.64</v>
+        <v>-55.38</v>
       </c>
       <c r="AG3">
-        <v>388.92</v>
+        <v>386.8</v>
       </c>
       <c r="AH3">
-        <v>318.13</v>
+        <v>314.39</v>
       </c>
       <c r="AI3">
-        <v>370.85</v>
+        <v>368.83</v>
       </c>
       <c r="AJ3" t="s">
         <v>45</v>
       </c>
       <c r="AK3">
-        <v>30.8</v>
+        <v>32.32</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1142,58 +1114,58 @@
         <v>42</v>
       </c>
       <c r="C4">
-        <v>337.55</v>
+        <v>334.25</v>
       </c>
       <c r="D4">
-        <v>0.84</v>
+        <v>-0.98</v>
       </c>
       <c r="E4">
         <v>534</v>
       </c>
       <c r="F4">
-        <v>334.75</v>
+        <v>334.25</v>
       </c>
       <c r="G4">
-        <v>-36.79</v>
+        <v>-37.41</v>
       </c>
       <c r="H4">
-        <v>0.84</v>
+        <v>0</v>
       </c>
       <c r="I4">
-        <v>-3.83</v>
+        <v>-4.01</v>
       </c>
       <c r="J4">
-        <v>-9.880000000000001</v>
+        <v>-11.25</v>
       </c>
       <c r="K4">
-        <v>-20.12</v>
+        <v>-20.61</v>
       </c>
       <c r="L4">
-        <v>-31.25</v>
+        <v>-33.34</v>
       </c>
       <c r="M4">
-        <v>-22.77</v>
+        <v>-22.89</v>
       </c>
       <c r="N4">
         <v>20</v>
       </c>
       <c r="O4">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="P4">
-        <v>340.61</v>
+        <v>337.82</v>
       </c>
       <c r="Q4">
-        <v>356.07</v>
+        <v>354.16</v>
       </c>
       <c r="R4">
-        <v>378.22</v>
+        <v>376.73</v>
       </c>
       <c r="S4">
-        <v>399.68</v>
+        <v>399.12</v>
       </c>
       <c r="T4">
-        <v>-15.54</v>
+        <v>-16.25</v>
       </c>
       <c r="U4" t="s">
         <v>43</v>
@@ -1208,34 +1180,34 @@
         <v>0</v>
       </c>
       <c r="Y4">
-        <v>25.27</v>
+        <v>23.6</v>
       </c>
       <c r="Z4">
-        <v>-11.36</v>
+        <v>-11.65</v>
       </c>
       <c r="AA4">
-        <v>-10.18</v>
+        <v>-10.47</v>
       </c>
       <c r="AB4">
         <v>-1.18</v>
       </c>
       <c r="AC4">
-        <v>9.949999999999999</v>
+        <v>14.65</v>
       </c>
       <c r="AD4">
-        <v>13.52</v>
+        <v>11.2</v>
       </c>
       <c r="AE4">
-        <v>9.619999999999999</v>
+        <v>9.99</v>
       </c>
       <c r="AF4">
-        <v>-13.82</v>
+        <v>7.62</v>
       </c>
       <c r="AG4">
-        <v>377.84</v>
+        <v>376.6</v>
       </c>
       <c r="AH4">
-        <v>334.29</v>
+        <v>331.73</v>
       </c>
       <c r="AI4">
         <v>364.51</v>
@@ -1244,7 +1216,7 @@
         <v>45</v>
       </c>
       <c r="AK4">
-        <v>63.22</v>
+        <v>58.89</v>
       </c>
     </row>
     <row r="5" spans="1:37">
@@ -1255,10 +1227,10 @@
         <v>42</v>
       </c>
       <c r="C5">
-        <v>833.3</v>
+        <v>851</v>
       </c>
       <c r="D5">
-        <v>-1.33</v>
+        <v>2.12</v>
       </c>
       <c r="E5">
         <v>1069.3</v>
@@ -1267,46 +1239,46 @@
         <v>752.45</v>
       </c>
       <c r="G5">
-        <v>-22.07</v>
+        <v>-20.42</v>
       </c>
       <c r="H5">
-        <v>10.74</v>
+        <v>13.1</v>
       </c>
       <c r="I5">
-        <v>-3.46</v>
+        <v>0.17</v>
       </c>
       <c r="J5">
-        <v>-9.369999999999999</v>
+        <v>-6.71</v>
       </c>
       <c r="K5">
-        <v>-17.22</v>
+        <v>-14.21</v>
       </c>
       <c r="L5">
-        <v>9.869999999999999</v>
+        <v>12.03</v>
       </c>
       <c r="M5">
-        <v>-5.55</v>
+        <v>-5.7</v>
       </c>
       <c r="N5">
         <v>80</v>
       </c>
       <c r="O5">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="P5">
-        <v>842.5700000000001</v>
+        <v>842.86</v>
       </c>
       <c r="Q5">
-        <v>870.2</v>
+        <v>867.26</v>
       </c>
       <c r="R5">
-        <v>940.53</v>
+        <v>937.13</v>
       </c>
       <c r="S5">
-        <v>924.3200000000001</v>
+        <v>924.09</v>
       </c>
       <c r="T5">
-        <v>-9.85</v>
+        <v>-7.91</v>
       </c>
       <c r="U5" t="s">
         <v>43</v>
@@ -1321,34 +1293,34 @@
         <v>1</v>
       </c>
       <c r="Y5">
-        <v>33.15</v>
+        <v>39.72</v>
       </c>
       <c r="Z5">
-        <v>-28</v>
+        <v>-26.5</v>
       </c>
       <c r="AA5">
-        <v>-27.86</v>
+        <v>-27.59</v>
       </c>
       <c r="AB5">
-        <v>-0.14</v>
+        <v>1.08</v>
       </c>
       <c r="AC5">
-        <v>36.88</v>
+        <v>56.88</v>
       </c>
       <c r="AD5">
-        <v>38.67</v>
+        <v>44.87</v>
       </c>
       <c r="AE5">
-        <v>22.77</v>
+        <v>22.71</v>
       </c>
       <c r="AF5">
-        <v>24.28</v>
+        <v>-15.22</v>
       </c>
       <c r="AG5">
-        <v>914.52</v>
+        <v>908.22</v>
       </c>
       <c r="AH5">
-        <v>825.88</v>
+        <v>826.3099999999999</v>
       </c>
       <c r="AI5">
         <v>910.86</v>
@@ -1357,7 +1329,7 @@
         <v>45</v>
       </c>
       <c r="AK5">
-        <v>50.39</v>
+        <v>49.75</v>
       </c>
     </row>
     <row r="6" spans="1:37">
@@ -1368,10 +1340,10 @@
         <v>42</v>
       </c>
       <c r="C6">
-        <v>2.51</v>
+        <v>2.52</v>
       </c>
       <c r="D6">
-        <v>-0.4</v>
+        <v>0.4</v>
       </c>
       <c r="E6">
         <v>3.38</v>
@@ -1380,46 +1352,46 @@
         <v>1.84</v>
       </c>
       <c r="G6">
-        <v>-25.74</v>
+        <v>-25.44</v>
       </c>
       <c r="H6">
-        <v>36.41</v>
+        <v>36.96</v>
       </c>
       <c r="I6">
-        <v>-3.46</v>
+        <v>2.44</v>
       </c>
       <c r="J6">
-        <v>-6.69</v>
+        <v>-3.45</v>
       </c>
       <c r="K6">
-        <v>8.19</v>
+        <v>11.01</v>
       </c>
       <c r="L6">
-        <v>-23.48</v>
+        <v>-25.22</v>
       </c>
       <c r="M6">
-        <v>-1.38</v>
+        <v>-1.87</v>
       </c>
       <c r="N6">
         <v>60</v>
       </c>
       <c r="O6">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="P6">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="Q6">
-        <v>2.57</v>
+        <v>2.56</v>
       </c>
       <c r="R6">
-        <v>2.68</v>
+        <v>2.69</v>
       </c>
       <c r="S6">
         <v>2.62</v>
       </c>
       <c r="T6">
-        <v>-4.37</v>
+        <v>-3.91</v>
       </c>
       <c r="U6" t="s">
         <v>43</v>
@@ -1434,7 +1406,7 @@
         <v>1</v>
       </c>
       <c r="Y6">
-        <v>41.73</v>
+        <v>42.87</v>
       </c>
       <c r="Z6">
         <v>-0.05</v>
@@ -1443,22 +1415,22 @@
         <v>-0.05</v>
       </c>
       <c r="AB6">
-        <v>-0.01</v>
+        <v>-0</v>
       </c>
       <c r="AC6">
-        <v>62.8</v>
+        <v>72.61</v>
       </c>
       <c r="AD6">
-        <v>39.65</v>
+        <v>58.6</v>
       </c>
       <c r="AE6">
         <v>0.14</v>
       </c>
       <c r="AF6">
-        <v>-60.72</v>
+        <v>-36.08</v>
       </c>
       <c r="AG6">
-        <v>2.68</v>
+        <v>2.66</v>
       </c>
       <c r="AH6">
         <v>2.45</v>
@@ -1470,7 +1442,7 @@
         <v>45</v>
       </c>
       <c r="AK6">
-        <v>38.95</v>
+        <v>39.67</v>
       </c>
     </row>
   </sheetData>
@@ -1631,47 +1603,12 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" s="3" t="s">
         <v>47</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="D2" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="E2" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="F2" s="3" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6">
-      <c r="A3" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="B3" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="C3" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="D3" s="4" t="s">
-        <v>54</v>
-      </c>
-      <c r="E3" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="F3" s="4" t="s">
-        <v>56</v>
       </c>
     </row>
     <row r="5" spans="1:6">
       <c r="A5" s="2" t="s">
-        <v>57</v>
+        <v>48</v>
       </c>
       <c r="B5" s="2"/>
       <c r="C5" s="2"/>
@@ -1679,700 +1616,700 @@
       <c r="E5" s="2"/>
     </row>
     <row r="6" spans="1:6">
-      <c r="A6" s="3" t="s">
+      <c r="A6" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B6" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="E6" s="3" t="s">
-        <v>61</v>
+      <c r="B6" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="E6" s="4" t="s">
+        <v>52</v>
       </c>
     </row>
     <row r="7" spans="1:6">
-      <c r="A7" s="5" t="s">
+      <c r="A7" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B7" s="5" t="s">
+      <c r="B7" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C7" s="6">
-        <v>-12.89</v>
-      </c>
-      <c r="D7" s="6">
+      <c r="C7" s="5">
         <v>-9.73</v>
       </c>
-      <c r="E7" s="7">
-        <v>3.16</v>
+      <c r="D7" s="5">
+        <v>-8.949999999999999</v>
+      </c>
+      <c r="E7" s="6">
+        <v>0.78</v>
       </c>
     </row>
     <row r="8" spans="1:6">
-      <c r="A8" s="5" t="s">
+      <c r="A8" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B8" s="5" t="s">
+      <c r="B8" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C8" s="6">
-        <v>-19.63</v>
-      </c>
-      <c r="D8" s="6">
+      <c r="C8" s="5">
         <v>-15.94</v>
       </c>
+      <c r="D8" s="5">
+        <v>-16.57</v>
+      </c>
       <c r="E8" s="7">
-        <v>3.69</v>
+        <v>-0.63</v>
       </c>
     </row>
     <row r="9" spans="1:6">
-      <c r="A9" s="5" t="s">
+      <c r="A9" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B9" s="5" t="s">
+      <c r="B9" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C9" s="6">
-        <v>-11.56</v>
-      </c>
-      <c r="D9" s="6">
+      <c r="C9" s="5">
         <v>-9.880000000000001</v>
       </c>
+      <c r="D9" s="5">
+        <v>-11.25</v>
+      </c>
       <c r="E9" s="7">
-        <v>1.68</v>
+        <v>-1.37</v>
       </c>
     </row>
     <row r="10" spans="1:6">
-      <c r="A10" s="5" t="s">
+      <c r="A10" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="B10" s="5" t="s">
+      <c r="B10" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C10" s="6">
-        <v>-11.97</v>
-      </c>
-      <c r="D10" s="6">
+      <c r="C10" s="5">
         <v>-9.369999999999999</v>
       </c>
-      <c r="E10" s="7">
-        <v>2.6</v>
+      <c r="D10" s="5">
+        <v>-6.71</v>
+      </c>
+      <c r="E10" s="6">
+        <v>2.66</v>
       </c>
     </row>
     <row r="11" spans="1:6">
-      <c r="A11" s="5" t="s">
+      <c r="A11" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="B11" s="5" t="s">
+      <c r="B11" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C11" s="6">
-        <v>-8.699999999999999</v>
-      </c>
-      <c r="D11" s="6">
+      <c r="C11" s="5">
         <v>-6.69</v>
       </c>
-      <c r="E11" s="7">
-        <v>2.01</v>
+      <c r="D11" s="5">
+        <v>-3.45</v>
+      </c>
+      <c r="E11" s="6">
+        <v>3.24</v>
       </c>
     </row>
     <row r="12" spans="1:6">
-      <c r="A12" s="5" t="s">
+      <c r="A12" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B12" s="5" t="s">
+      <c r="B12" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C12" s="6">
-        <v>-4.71</v>
-      </c>
-      <c r="D12" s="6">
+      <c r="C12" s="5">
         <v>-3.87</v>
       </c>
-      <c r="E12" s="7">
-        <v>0.84</v>
+      <c r="D12" s="5">
+        <v>-1.29</v>
+      </c>
+      <c r="E12" s="6">
+        <v>2.58</v>
       </c>
     </row>
     <row r="13" spans="1:6">
-      <c r="A13" s="5" t="s">
+      <c r="A13" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B13" s="5" t="s">
+      <c r="B13" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C13" s="6">
-        <v>-13.57</v>
-      </c>
-      <c r="D13" s="6">
+      <c r="C13" s="5">
         <v>-13.3</v>
       </c>
-      <c r="E13" s="7">
-        <v>0.27</v>
+      <c r="D13" s="5">
+        <v>-7.73</v>
+      </c>
+      <c r="E13" s="6">
+        <v>5.57</v>
       </c>
     </row>
     <row r="14" spans="1:6">
-      <c r="A14" s="5" t="s">
+      <c r="A14" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B14" s="5" t="s">
+      <c r="B14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C14" s="6">
-        <v>-6.43</v>
-      </c>
-      <c r="D14" s="6">
+      <c r="C14" s="5">
         <v>-3.83</v>
       </c>
+      <c r="D14" s="5">
+        <v>-4.01</v>
+      </c>
       <c r="E14" s="7">
-        <v>2.6</v>
+        <v>-0.18</v>
       </c>
     </row>
     <row r="15" spans="1:6">
-      <c r="A15" s="5" t="s">
+      <c r="A15" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="B15" s="5" t="s">
+      <c r="B15" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C15" s="6">
-        <v>-3.71</v>
-      </c>
-      <c r="D15" s="6">
+      <c r="C15" s="5">
         <v>-3.46</v>
       </c>
-      <c r="E15" s="7">
-        <v>0.25</v>
+      <c r="D15" s="5">
+        <v>0.17</v>
+      </c>
+      <c r="E15" s="6">
+        <v>3.63</v>
       </c>
     </row>
     <row r="16" spans="1:6">
-      <c r="A16" s="5" t="s">
+      <c r="A16" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="B16" s="5" t="s">
+      <c r="B16" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C16" s="6">
-        <v>-3.08</v>
-      </c>
-      <c r="D16" s="6">
+      <c r="C16" s="5">
         <v>-3.46</v>
       </c>
-      <c r="E16" s="8">
-        <v>-0.38</v>
+      <c r="D16" s="5">
+        <v>2.44</v>
+      </c>
+      <c r="E16" s="6">
+        <v>5.9</v>
       </c>
     </row>
     <row r="17" spans="1:5">
-      <c r="A17" s="5" t="s">
+      <c r="A17" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B17" s="5" t="s">
+      <c r="B17" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C17" s="6">
-        <v>6.97</v>
-      </c>
-      <c r="D17" s="6">
+      <c r="C17" s="5">
         <v>6.73</v>
       </c>
-      <c r="E17" s="8">
-        <v>-0.24</v>
+      <c r="D17" s="5">
+        <v>7.6</v>
+      </c>
+      <c r="E17" s="6">
+        <v>0.87</v>
       </c>
     </row>
     <row r="18" spans="1:5">
-      <c r="A18" s="5" t="s">
+      <c r="A18" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B18" s="5" t="s">
+      <c r="B18" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C18" s="6">
-        <v>-9.5</v>
-      </c>
-      <c r="D18" s="6">
+      <c r="C18" s="5">
         <v>-9.84</v>
       </c>
-      <c r="E18" s="8">
-        <v>-0.34</v>
+      <c r="D18" s="5">
+        <v>-8.15</v>
+      </c>
+      <c r="E18" s="6">
+        <v>1.69</v>
       </c>
     </row>
     <row r="19" spans="1:5">
-      <c r="A19" s="5" t="s">
+      <c r="A19" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B19" s="5" t="s">
+      <c r="B19" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C19" s="6">
-        <v>-31.57</v>
-      </c>
-      <c r="D19" s="6">
+      <c r="C19" s="5">
         <v>-31.25</v>
       </c>
+      <c r="D19" s="5">
+        <v>-33.34</v>
+      </c>
       <c r="E19" s="7">
-        <v>0.32</v>
+        <v>-2.09</v>
       </c>
     </row>
     <row r="20" spans="1:5">
-      <c r="A20" s="5" t="s">
+      <c r="A20" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="B20" s="5" t="s">
+      <c r="B20" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C20" s="6">
-        <v>11.15</v>
-      </c>
-      <c r="D20" s="6">
+      <c r="C20" s="5">
         <v>9.869999999999999</v>
       </c>
-      <c r="E20" s="8">
-        <v>-1.28</v>
+      <c r="D20" s="5">
+        <v>12.03</v>
+      </c>
+      <c r="E20" s="6">
+        <v>2.16</v>
       </c>
     </row>
     <row r="21" spans="1:5">
-      <c r="A21" s="5" t="s">
+      <c r="A21" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="B21" s="5" t="s">
+      <c r="B21" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C21" s="6">
-        <v>-20.25</v>
-      </c>
-      <c r="D21" s="6">
+      <c r="C21" s="5">
         <v>-23.48</v>
       </c>
-      <c r="E21" s="8">
-        <v>-3.23</v>
+      <c r="D21" s="5">
+        <v>-25.22</v>
+      </c>
+      <c r="E21" s="7">
+        <v>-1.74</v>
       </c>
     </row>
     <row r="22" spans="1:5">
-      <c r="A22" s="5" t="s">
+      <c r="A22" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B22" s="5" t="s">
+      <c r="B22" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C22" s="6">
-        <v>-6.07</v>
-      </c>
-      <c r="D22" s="6">
+      <c r="C22" s="5">
         <v>-8.42</v>
       </c>
-      <c r="E22" s="8">
-        <v>-2.35</v>
+      <c r="D22" s="5">
+        <v>-8.029999999999999</v>
+      </c>
+      <c r="E22" s="6">
+        <v>0.39</v>
       </c>
     </row>
     <row r="23" spans="1:5">
-      <c r="A23" s="5" t="s">
+      <c r="A23" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B23" s="5" t="s">
+      <c r="B23" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C23" s="6">
-        <v>-20.4</v>
-      </c>
-      <c r="D23" s="6">
+      <c r="C23" s="5">
         <v>-19.27</v>
       </c>
-      <c r="E23" s="7">
-        <v>1.13</v>
+      <c r="D23" s="5">
+        <v>-17.44</v>
+      </c>
+      <c r="E23" s="6">
+        <v>1.83</v>
       </c>
     </row>
     <row r="24" spans="1:5">
-      <c r="A24" s="5" t="s">
+      <c r="A24" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B24" s="5" t="s">
+      <c r="B24" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C24" s="6">
-        <v>-20.78</v>
-      </c>
-      <c r="D24" s="6">
+      <c r="C24" s="5">
         <v>-20.12</v>
       </c>
+      <c r="D24" s="5">
+        <v>-20.61</v>
+      </c>
       <c r="E24" s="7">
-        <v>0.66</v>
+        <v>-0.49</v>
       </c>
     </row>
     <row r="25" spans="1:5">
-      <c r="A25" s="5" t="s">
+      <c r="A25" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="B25" s="5" t="s">
+      <c r="B25" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C25" s="6">
+      <c r="C25" s="5">
+        <v>-17.22</v>
+      </c>
+      <c r="D25" s="5">
+        <v>-14.21</v>
+      </c>
+      <c r="E25" s="6">
+        <v>3.01</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
+      <c r="A26" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B26" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C26" s="5">
+        <v>8.19</v>
+      </c>
+      <c r="D26" s="5">
+        <v>11.01</v>
+      </c>
+      <c r="E26" s="6">
+        <v>2.82</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5">
+      <c r="A27" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B27" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C27" s="5">
+        <v>-31.85</v>
+      </c>
+      <c r="D27" s="5">
+        <v>-30.48</v>
+      </c>
+      <c r="E27" s="6">
+        <v>1.37</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5">
+      <c r="A28" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B28" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C28" s="5">
+        <v>-29.92</v>
+      </c>
+      <c r="D28" s="5">
+        <v>-29.75</v>
+      </c>
+      <c r="E28" s="6">
+        <v>0.17</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5">
+      <c r="A29" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B29" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C29" s="5">
+        <v>-36.79</v>
+      </c>
+      <c r="D29" s="5">
+        <v>-37.41</v>
+      </c>
+      <c r="E29" s="7">
+        <v>-0.62</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5">
+      <c r="A30" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B30" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C30" s="5">
+        <v>-22.07</v>
+      </c>
+      <c r="D30" s="5">
+        <v>-20.42</v>
+      </c>
+      <c r="E30" s="6">
+        <v>1.65</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5">
+      <c r="A31" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B31" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C31" s="5">
+        <v>-25.74</v>
+      </c>
+      <c r="D31" s="5">
+        <v>-25.44</v>
+      </c>
+      <c r="E31" s="6">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5">
+      <c r="A32" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B32" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C32" s="5">
+        <v>142</v>
+      </c>
+      <c r="D32" s="5">
+        <v>144.85</v>
+      </c>
+      <c r="E32" s="6">
+        <v>2.85</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5">
+      <c r="A33" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B33" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C33" s="5">
+        <v>319.65</v>
+      </c>
+      <c r="D33" s="5">
+        <v>320.45</v>
+      </c>
+      <c r="E33" s="6">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5">
+      <c r="A34" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B34" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C34" s="5">
+        <v>337.55</v>
+      </c>
+      <c r="D34" s="5">
+        <v>334.25</v>
+      </c>
+      <c r="E34" s="7">
+        <v>-3.3</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5">
+      <c r="A35" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B35" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C35" s="5">
+        <v>833.3</v>
+      </c>
+      <c r="D35" s="5">
+        <v>851</v>
+      </c>
+      <c r="E35" s="6">
+        <v>17.7</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5">
+      <c r="A36" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B36" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C36" s="5">
+        <v>2.51</v>
+      </c>
+      <c r="D36" s="5">
+        <v>2.52</v>
+      </c>
+      <c r="E36" s="6">
+        <v>0.01</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5">
+      <c r="A37" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B37" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C37" s="5">
+        <v>31.83</v>
+      </c>
+      <c r="D37" s="5">
+        <v>38.93</v>
+      </c>
+      <c r="E37" s="6">
+        <v>7.1</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5">
+      <c r="A38" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B38" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C38" s="5">
+        <v>31.47</v>
+      </c>
+      <c r="D38" s="5">
+        <v>31.94</v>
+      </c>
+      <c r="E38" s="6">
+        <v>0.47</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5">
+      <c r="A39" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B39" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C39" s="5">
+        <v>25.27</v>
+      </c>
+      <c r="D39" s="5">
+        <v>23.6</v>
+      </c>
+      <c r="E39" s="7">
+        <v>-1.67</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5">
+      <c r="A40" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B40" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C40" s="5">
+        <v>33.15</v>
+      </c>
+      <c r="D40" s="5">
+        <v>39.72</v>
+      </c>
+      <c r="E40" s="6">
+        <v>6.57</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5">
+      <c r="A41" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B41" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C41" s="5">
+        <v>41.73</v>
+      </c>
+      <c r="D41" s="5">
+        <v>42.87</v>
+      </c>
+      <c r="E41" s="6">
+        <v>1.14</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5">
+      <c r="A42" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B42" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C42" s="5">
+        <v>53.79</v>
+      </c>
+      <c r="D42" s="5">
+        <v>-7.89</v>
+      </c>
+      <c r="E42" s="7">
+        <v>-61.68</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5">
+      <c r="A43" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B43" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C43" s="5">
+        <v>-65.64</v>
+      </c>
+      <c r="D43" s="5">
+        <v>-55.38</v>
+      </c>
+      <c r="E43" s="6">
+        <v>10.26</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5">
+      <c r="A44" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B44" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C44" s="5">
+        <v>-13.82</v>
+      </c>
+      <c r="D44" s="5">
+        <v>7.62</v>
+      </c>
+      <c r="E44" s="6">
+        <v>21.44</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5">
+      <c r="A45" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B45" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C45" s="5">
+        <v>24.28</v>
+      </c>
+      <c r="D45" s="5">
         <v>-15.22</v>
       </c>
-      <c r="D25" s="6">
-        <v>-17.22</v>
-      </c>
-      <c r="E25" s="8">
-        <v>-2</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5">
-      <c r="A26" s="5" t="s">
+      <c r="E45" s="7">
+        <v>-39.5</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5">
+      <c r="A46" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="B26" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C26" s="6">
-        <v>9.09</v>
-      </c>
-      <c r="D26" s="6">
-        <v>8.19</v>
-      </c>
-      <c r="E26" s="8">
-        <v>-0.9</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5">
-      <c r="A27" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B27" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C27" s="6">
-        <v>-31.9</v>
-      </c>
-      <c r="D27" s="6">
-        <v>-31.85</v>
-      </c>
-      <c r="E27" s="7">
-        <v>0.05</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5">
-      <c r="A28" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B28" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C28" s="6">
-        <v>-30.8</v>
-      </c>
-      <c r="D28" s="6">
-        <v>-29.92</v>
-      </c>
-      <c r="E28" s="7">
-        <v>0.88</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5">
-      <c r="A29" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B29" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C29" s="6">
-        <v>-37.31</v>
-      </c>
-      <c r="D29" s="6">
-        <v>-36.79</v>
-      </c>
-      <c r="E29" s="7">
-        <v>0.52</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5">
-      <c r="A30" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B30" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C30" s="6">
-        <v>-21.02</v>
-      </c>
-      <c r="D30" s="6">
-        <v>-22.07</v>
-      </c>
-      <c r="E30" s="8">
-        <v>-1.05</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5">
-      <c r="A31" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B31" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C31" s="6">
-        <v>-25.44</v>
-      </c>
-      <c r="D31" s="6">
-        <v>-25.74</v>
-      </c>
-      <c r="E31" s="8">
-        <v>-0.3</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5">
-      <c r="A32" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B32" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C32" s="6">
-        <v>141.9</v>
-      </c>
-      <c r="D32" s="6">
-        <v>142</v>
-      </c>
-      <c r="E32" s="7">
-        <v>0.1</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5">
-      <c r="A33" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B33" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C33" s="6">
-        <v>315.65</v>
-      </c>
-      <c r="D33" s="6">
-        <v>319.65</v>
-      </c>
-      <c r="E33" s="7">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5">
-      <c r="A34" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B34" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C34" s="6">
-        <v>334.75</v>
-      </c>
-      <c r="D34" s="6">
-        <v>337.55</v>
-      </c>
-      <c r="E34" s="7">
-        <v>2.8</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5">
-      <c r="A35" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B35" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C35" s="6">
-        <v>844.5</v>
-      </c>
-      <c r="D35" s="6">
-        <v>833.3</v>
-      </c>
-      <c r="E35" s="8">
-        <v>-11.2</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5">
-      <c r="A36" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B36" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C36" s="6">
-        <v>2.52</v>
-      </c>
-      <c r="D36" s="6">
-        <v>2.51</v>
-      </c>
-      <c r="E36" s="8">
-        <v>-0.01</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5">
-      <c r="A37" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B37" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C37" s="6">
-        <v>31.57</v>
-      </c>
-      <c r="D37" s="6">
-        <v>31.83</v>
-      </c>
-      <c r="E37" s="7">
-        <v>0.26</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5">
-      <c r="A38" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B38" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C38" s="6">
-        <v>29.24</v>
-      </c>
-      <c r="D38" s="6">
-        <v>31.47</v>
-      </c>
-      <c r="E38" s="7">
-        <v>2.23</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5">
-      <c r="A39" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B39" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C39" s="6">
-        <v>20.85</v>
-      </c>
-      <c r="D39" s="6">
-        <v>25.27</v>
-      </c>
-      <c r="E39" s="7">
-        <v>4.42</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5">
-      <c r="A40" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B40" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C40" s="6">
-        <v>35.42</v>
-      </c>
-      <c r="D40" s="6">
-        <v>33.15</v>
-      </c>
-      <c r="E40" s="8">
-        <v>-2.27</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5">
-      <c r="A41" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B41" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C41" s="6">
-        <v>42.52</v>
-      </c>
-      <c r="D41" s="6">
-        <v>41.73</v>
-      </c>
-      <c r="E41" s="8">
-        <v>-0.79</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5">
-      <c r="A42" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B42" s="5" t="s">
+      <c r="B46" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="C42" s="6">
-        <v>55.93</v>
-      </c>
-      <c r="D42" s="6">
-        <v>53.79</v>
-      </c>
-      <c r="E42" s="8">
-        <v>-2.14</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5">
-      <c r="A43" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B43" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C43" s="6">
-        <v>14.71</v>
-      </c>
-      <c r="D43" s="6">
-        <v>-65.64</v>
-      </c>
-      <c r="E43" s="8">
-        <v>-80.34999999999999</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5">
-      <c r="A44" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B44" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C44" s="6">
-        <v>45.82</v>
-      </c>
-      <c r="D44" s="6">
-        <v>-13.82</v>
-      </c>
-      <c r="E44" s="8">
-        <v>-59.64</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5">
-      <c r="A45" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B45" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C45" s="6">
-        <v>-7.37</v>
-      </c>
-      <c r="D45" s="6">
-        <v>24.28</v>
-      </c>
-      <c r="E45" s="7">
-        <v>31.65</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5">
-      <c r="A46" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B46" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C46" s="6">
-        <v>-6.2</v>
-      </c>
-      <c r="D46" s="6">
+      <c r="C46" s="5">
         <v>-60.72</v>
       </c>
-      <c r="E46" s="8">
-        <v>-54.52</v>
+      <c r="D46" s="5">
+        <v>-36.08</v>
+      </c>
+      <c r="E46" s="6">
+        <v>24.64</v>
       </c>
     </row>
   </sheetData>
@@ -2398,60 +2335,60 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="28" customHeight="1">
-      <c r="A1" s="9" t="s">
+      <c r="A1" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="9" t="s">
-        <v>62</v>
-      </c>
-      <c r="C1" s="9" t="s">
-        <v>63</v>
-      </c>
-      <c r="D1" s="9" t="s">
-        <v>64</v>
-      </c>
-      <c r="E1" s="9" t="s">
-        <v>65</v>
-      </c>
-      <c r="F1" s="9" t="s">
-        <v>66</v>
-      </c>
-      <c r="G1" s="9" t="s">
-        <v>67</v>
-      </c>
-      <c r="H1" s="9" t="s">
-        <v>68</v>
-      </c>
-      <c r="I1" s="9" t="s">
-        <v>69</v>
+      <c r="B1" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="C1" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="D1" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="E1" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="F1" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="G1" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="H1" s="8" t="s">
+        <v>59</v>
+      </c>
+      <c r="I1" s="8" t="s">
+        <v>60</v>
       </c>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="10" t="s">
+      <c r="A2" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="B2" s="11">
+      <c r="B2" s="10">
         <v>33.92</v>
       </c>
-      <c r="C2" s="12">
+      <c r="C2" s="11">
         <v>5</v>
       </c>
-      <c r="D2" s="11">
-        <v>32.7</v>
-      </c>
-      <c r="E2" s="11">
+      <c r="D2" s="10">
+        <v>35.4</v>
+      </c>
+      <c r="E2" s="10">
         <v>0</v>
       </c>
-      <c r="F2" s="11">
-        <v>-10.3</v>
-      </c>
-      <c r="G2" s="11">
-        <v>-11.4</v>
-      </c>
-      <c r="H2" s="11">
+      <c r="F2" s="10">
+        <v>-9.4</v>
+      </c>
+      <c r="G2" s="10">
+        <v>-9.9</v>
+      </c>
+      <c r="H2" s="10">
         <v>59.8</v>
       </c>
-      <c r="I2" s="11">
+      <c r="I2" s="10">
         <v>0</v>
       </c>
     </row>
@@ -2553,37 +2490,37 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
-      <c r="A1" s="13" t="s">
+      <c r="A1" s="12" t="s">
         <v>37</v>
       </c>
-      <c r="B1" s="13" t="s">
+      <c r="B1" s="12" t="s">
         <v>38</v>
       </c>
-      <c r="C1" s="13" t="s">
+      <c r="C1" s="12" t="s">
         <v>41</v>
       </c>
-      <c r="D1" s="13" t="s">
+      <c r="D1" s="12" t="s">
         <v>40</v>
       </c>
-      <c r="E1" s="13" t="s">
+      <c r="E1" s="12" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="2" spans="1:5">
-      <c r="A2" s="14">
-        <v>0.1726</v>
-      </c>
-      <c r="B2" s="14">
-        <v>0.0126</v>
-      </c>
-      <c r="C2" s="14">
-        <v>-0.0138</v>
-      </c>
-      <c r="D2" s="14">
-        <v>-0.0555</v>
-      </c>
-      <c r="E2" s="14">
-        <v>-0.2277</v>
+      <c r="A2" s="13">
+        <v>0.1782</v>
+      </c>
+      <c r="B2" s="13">
+        <v>0.0162</v>
+      </c>
+      <c r="C2" s="13">
+        <v>-0.0187</v>
+      </c>
+      <c r="D2" s="13">
+        <v>-0.057</v>
+      </c>
+      <c r="E2" s="13">
+        <v>-0.2289</v>
       </c>
     </row>
   </sheetData>

--- a/HINDUJA_GROUP_Technical_Metrics.xlsx
+++ b/HINDUJA_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="207" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="222" uniqueCount="70">
   <si>
     <t>Symbol</t>
   </si>
@@ -163,7 +163,34 @@
     <t>▶  SIGNAL EVENTS (vs Previous Run)</t>
   </si>
   <si>
-    <t>No signal events detected since last run.</t>
+    <t>Signal</t>
+  </si>
+  <si>
+    <t>Change</t>
+  </si>
+  <si>
+    <t>Direction</t>
+  </si>
+  <si>
+    <t>Prev Value</t>
+  </si>
+  <si>
+    <t>Curr Value</t>
+  </si>
+  <si>
+    <t>RSI Oversold Recovery</t>
+  </si>
+  <si>
+    <t>23.6 → 37.2</t>
+  </si>
+  <si>
+    <t>🟢 BULLISH</t>
+  </si>
+  <si>
+    <t>23.6</t>
+  </si>
+  <si>
+    <t>37.2</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -365,14 +392,15 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -888,58 +916,58 @@
         <v>42</v>
       </c>
       <c r="C2">
-        <v>144.85</v>
+        <v>145</v>
       </c>
       <c r="D2">
-        <v>2.01</v>
+        <v>0.1</v>
       </c>
       <c r="E2">
         <v>208.37</v>
       </c>
       <c r="F2">
-        <v>133.16</v>
+        <v>136.22</v>
       </c>
       <c r="G2">
-        <v>-30.48</v>
+        <v>-30.41</v>
       </c>
       <c r="H2">
-        <v>8.779999999999999</v>
+        <v>6.45</v>
       </c>
       <c r="I2">
-        <v>-1.29</v>
+        <v>-0.71</v>
       </c>
       <c r="J2">
-        <v>-8.949999999999999</v>
+        <v>-6.58</v>
       </c>
       <c r="K2">
-        <v>-8.029999999999999</v>
+        <v>-8.199999999999999</v>
       </c>
       <c r="L2">
-        <v>7.6</v>
+        <v>8.890000000000001</v>
       </c>
       <c r="M2">
-        <v>17.82</v>
+        <v>17.66</v>
       </c>
       <c r="N2">
-        <v>99</v>
+        <v>80</v>
       </c>
       <c r="O2">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="P2">
-        <v>143.95</v>
+        <v>143.74</v>
       </c>
       <c r="Q2">
-        <v>147.58</v>
+        <v>147.16</v>
       </c>
       <c r="R2">
-        <v>159.7</v>
+        <v>159.06</v>
       </c>
       <c r="S2">
-        <v>167.51</v>
+        <v>167.33</v>
       </c>
       <c r="T2">
-        <v>-13.53</v>
+        <v>-13.34</v>
       </c>
       <c r="U2" t="s">
         <v>43</v>
@@ -954,34 +982,34 @@
         <v>0</v>
       </c>
       <c r="Y2">
-        <v>38.93</v>
+        <v>39.29</v>
       </c>
       <c r="Z2">
-        <v>-4.25</v>
+        <v>-4.01</v>
       </c>
       <c r="AA2">
-        <v>-4.46</v>
+        <v>-4.37</v>
       </c>
       <c r="AB2">
-        <v>0.21</v>
+        <v>0.36</v>
       </c>
       <c r="AC2">
-        <v>45.4</v>
+        <v>66.81999999999999</v>
       </c>
       <c r="AD2">
-        <v>43.47</v>
+        <v>49.25</v>
       </c>
       <c r="AE2">
-        <v>3.96</v>
+        <v>3.88</v>
       </c>
       <c r="AF2">
-        <v>-7.89</v>
+        <v>-40.24</v>
       </c>
       <c r="AG2">
-        <v>155.05</v>
+        <v>154.18</v>
       </c>
       <c r="AH2">
-        <v>140.1</v>
+        <v>140.14</v>
       </c>
       <c r="AI2">
         <v>154.47</v>
@@ -990,7 +1018,7 @@
         <v>45</v>
       </c>
       <c r="AK2">
-        <v>54.44</v>
+        <v>53.22</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1001,10 +1029,10 @@
         <v>42</v>
       </c>
       <c r="C3">
-        <v>320.45</v>
+        <v>322.4</v>
       </c>
       <c r="D3">
-        <v>0.25</v>
+        <v>0.61</v>
       </c>
       <c r="E3">
         <v>456.15</v>
@@ -1013,25 +1041,25 @@
         <v>225</v>
       </c>
       <c r="G3">
-        <v>-29.75</v>
+        <v>-29.32</v>
       </c>
       <c r="H3">
-        <v>42.42</v>
+        <v>43.29</v>
       </c>
       <c r="I3">
-        <v>-7.73</v>
+        <v>-5.19</v>
       </c>
       <c r="J3">
-        <v>-16.57</v>
+        <v>-14.93</v>
       </c>
       <c r="K3">
-        <v>-17.44</v>
+        <v>-15.81</v>
       </c>
       <c r="L3">
-        <v>-8.15</v>
+        <v>-8.44</v>
       </c>
       <c r="M3">
-        <v>1.62</v>
+        <v>1.9</v>
       </c>
       <c r="N3">
         <v>40</v>
@@ -1040,19 +1068,19 @@
         <v>44</v>
       </c>
       <c r="P3">
-        <v>323.41</v>
+        <v>319.88</v>
       </c>
       <c r="Q3">
-        <v>350.6</v>
+        <v>348.54</v>
       </c>
       <c r="R3">
-        <v>387.26</v>
+        <v>385.55</v>
       </c>
       <c r="S3">
-        <v>342.86</v>
+        <v>343.08</v>
       </c>
       <c r="T3">
-        <v>-6.54</v>
+        <v>-6.03</v>
       </c>
       <c r="U3" t="s">
         <v>43</v>
@@ -1067,34 +1095,34 @@
         <v>1</v>
       </c>
       <c r="Y3">
-        <v>31.94</v>
+        <v>33.12</v>
       </c>
       <c r="Z3">
         <v>-19.12</v>
       </c>
       <c r="AA3">
-        <v>-16.18</v>
+        <v>-16.77</v>
       </c>
       <c r="AB3">
-        <v>-2.95</v>
+        <v>-2.35</v>
       </c>
       <c r="AC3">
-        <v>10.38</v>
+        <v>18.56</v>
       </c>
       <c r="AD3">
-        <v>10.12</v>
+        <v>11.72</v>
       </c>
       <c r="AE3">
-        <v>16.37</v>
+        <v>15.69</v>
       </c>
       <c r="AF3">
-        <v>-55.38</v>
+        <v>-67.75</v>
       </c>
       <c r="AG3">
-        <v>386.8</v>
+        <v>386.27</v>
       </c>
       <c r="AH3">
-        <v>314.39</v>
+        <v>310.8</v>
       </c>
       <c r="AI3">
         <v>368.83</v>
@@ -1103,7 +1131,7 @@
         <v>45</v>
       </c>
       <c r="AK3">
-        <v>32.32</v>
+        <v>33.01</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1114,10 +1142,10 @@
         <v>42</v>
       </c>
       <c r="C4">
-        <v>334.25</v>
+        <v>344.25</v>
       </c>
       <c r="D4">
-        <v>-0.98</v>
+        <v>2.99</v>
       </c>
       <c r="E4">
         <v>534</v>
@@ -1126,46 +1154,46 @@
         <v>334.25</v>
       </c>
       <c r="G4">
-        <v>-37.41</v>
+        <v>-35.53</v>
       </c>
       <c r="H4">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="I4">
-        <v>-4.01</v>
+        <v>-0.1</v>
       </c>
       <c r="J4">
-        <v>-11.25</v>
+        <v>-7.55</v>
       </c>
       <c r="K4">
-        <v>-20.61</v>
+        <v>-18.78</v>
       </c>
       <c r="L4">
-        <v>-33.34</v>
+        <v>-33.93</v>
       </c>
       <c r="M4">
-        <v>-22.89</v>
+        <v>-22.27</v>
       </c>
       <c r="N4">
         <v>20</v>
       </c>
       <c r="O4">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="P4">
-        <v>337.82</v>
+        <v>337.75</v>
       </c>
       <c r="Q4">
-        <v>354.16</v>
+        <v>353.07</v>
       </c>
       <c r="R4">
-        <v>376.73</v>
+        <v>375.35</v>
       </c>
       <c r="S4">
-        <v>399.12</v>
+        <v>398.65</v>
       </c>
       <c r="T4">
-        <v>-16.25</v>
+        <v>-13.65</v>
       </c>
       <c r="U4" t="s">
         <v>43</v>
@@ -1180,34 +1208,34 @@
         <v>0</v>
       </c>
       <c r="Y4">
-        <v>23.6</v>
+        <v>37.18</v>
       </c>
       <c r="Z4">
-        <v>-11.65</v>
+        <v>-10.96</v>
       </c>
       <c r="AA4">
-        <v>-10.47</v>
+        <v>-10.57</v>
       </c>
       <c r="AB4">
-        <v>-1.18</v>
+        <v>-0.39</v>
       </c>
       <c r="AC4">
-        <v>14.65</v>
+        <v>47.98</v>
       </c>
       <c r="AD4">
-        <v>11.2</v>
+        <v>24.19</v>
       </c>
       <c r="AE4">
-        <v>9.99</v>
+        <v>10.45</v>
       </c>
       <c r="AF4">
-        <v>7.62</v>
+        <v>114.51</v>
       </c>
       <c r="AG4">
-        <v>376.6</v>
+        <v>375.19</v>
       </c>
       <c r="AH4">
-        <v>331.73</v>
+        <v>330.95</v>
       </c>
       <c r="AI4">
         <v>364.51</v>
@@ -1216,7 +1244,7 @@
         <v>45</v>
       </c>
       <c r="AK4">
-        <v>58.89</v>
+        <v>53.43</v>
       </c>
     </row>
     <row r="5" spans="1:37">
@@ -1227,10 +1255,10 @@
         <v>42</v>
       </c>
       <c r="C5">
-        <v>851</v>
+        <v>868</v>
       </c>
       <c r="D5">
-        <v>2.12</v>
+        <v>2</v>
       </c>
       <c r="E5">
         <v>1069.3</v>
@@ -1239,46 +1267,46 @@
         <v>752.45</v>
       </c>
       <c r="G5">
-        <v>-20.42</v>
+        <v>-18.83</v>
       </c>
       <c r="H5">
-        <v>13.1</v>
+        <v>15.36</v>
       </c>
       <c r="I5">
-        <v>0.17</v>
+        <v>2.06</v>
       </c>
       <c r="J5">
-        <v>-6.71</v>
+        <v>-4.58</v>
       </c>
       <c r="K5">
-        <v>-14.21</v>
+        <v>-14.25</v>
       </c>
       <c r="L5">
-        <v>12.03</v>
+        <v>14.96</v>
       </c>
       <c r="M5">
-        <v>-5.7</v>
+        <v>-4.74</v>
       </c>
       <c r="N5">
-        <v>80</v>
+        <v>99</v>
       </c>
       <c r="O5">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="P5">
-        <v>842.86</v>
+        <v>846.36</v>
       </c>
       <c r="Q5">
-        <v>867.26</v>
+        <v>866.76</v>
       </c>
       <c r="R5">
-        <v>937.13</v>
+        <v>934.08</v>
       </c>
       <c r="S5">
-        <v>924.09</v>
+        <v>924.01</v>
       </c>
       <c r="T5">
-        <v>-7.91</v>
+        <v>-6.06</v>
       </c>
       <c r="U5" t="s">
         <v>43</v>
@@ -1293,34 +1321,34 @@
         <v>1</v>
       </c>
       <c r="Y5">
-        <v>39.72</v>
+        <v>45.27</v>
       </c>
       <c r="Z5">
-        <v>-26.5</v>
+        <v>-23.68</v>
       </c>
       <c r="AA5">
-        <v>-27.59</v>
+        <v>-26.8</v>
       </c>
       <c r="AB5">
-        <v>1.08</v>
+        <v>3.13</v>
       </c>
       <c r="AC5">
-        <v>56.88</v>
+        <v>72.95999999999999</v>
       </c>
       <c r="AD5">
-        <v>44.87</v>
+        <v>55.57</v>
       </c>
       <c r="AE5">
-        <v>22.71</v>
+        <v>22.87</v>
       </c>
       <c r="AF5">
-        <v>-15.22</v>
+        <v>-19.27</v>
       </c>
       <c r="AG5">
-        <v>908.22</v>
+        <v>907.41</v>
       </c>
       <c r="AH5">
-        <v>826.3099999999999</v>
+        <v>826.12</v>
       </c>
       <c r="AI5">
         <v>910.86</v>
@@ -1329,7 +1357,7 @@
         <v>45</v>
       </c>
       <c r="AK5">
-        <v>49.75</v>
+        <v>44</v>
       </c>
     </row>
     <row r="6" spans="1:37">
@@ -1340,49 +1368,49 @@
         <v>42</v>
       </c>
       <c r="C6">
-        <v>2.52</v>
+        <v>2.51</v>
       </c>
       <c r="D6">
-        <v>0.4</v>
+        <v>-0.4</v>
       </c>
       <c r="E6">
-        <v>3.38</v>
+        <v>3.36</v>
       </c>
       <c r="F6">
         <v>1.84</v>
       </c>
       <c r="G6">
-        <v>-25.44</v>
+        <v>-25.3</v>
       </c>
       <c r="H6">
-        <v>36.96</v>
+        <v>36.41</v>
       </c>
       <c r="I6">
-        <v>2.44</v>
+        <v>2.87</v>
       </c>
       <c r="J6">
-        <v>-3.45</v>
+        <v>-5.99</v>
       </c>
       <c r="K6">
-        <v>11.01</v>
+        <v>6.36</v>
       </c>
       <c r="L6">
-        <v>-25.22</v>
+        <v>-25.74</v>
       </c>
       <c r="M6">
-        <v>-1.87</v>
+        <v>-1</v>
       </c>
       <c r="N6">
         <v>60</v>
       </c>
       <c r="O6">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="P6">
-        <v>2.5</v>
+        <v>2.51</v>
       </c>
       <c r="Q6">
-        <v>2.56</v>
+        <v>2.55</v>
       </c>
       <c r="R6">
         <v>2.69</v>
@@ -1391,7 +1419,7 @@
         <v>2.62</v>
       </c>
       <c r="T6">
-        <v>-3.91</v>
+        <v>-4.21</v>
       </c>
       <c r="U6" t="s">
         <v>43</v>
@@ -1406,7 +1434,7 @@
         <v>1</v>
       </c>
       <c r="Y6">
-        <v>42.87</v>
+        <v>41.98</v>
       </c>
       <c r="Z6">
         <v>-0.05</v>
@@ -1418,16 +1446,16 @@
         <v>-0</v>
       </c>
       <c r="AC6">
-        <v>72.61</v>
+        <v>71.13</v>
       </c>
       <c r="AD6">
-        <v>58.6</v>
+        <v>68.84999999999999</v>
       </c>
       <c r="AE6">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="AF6">
-        <v>-36.08</v>
+        <v>-31.79</v>
       </c>
       <c r="AG6">
         <v>2.66</v>
@@ -1442,7 +1470,7 @@
         <v>45</v>
       </c>
       <c r="AK6">
-        <v>39.67</v>
+        <v>38.63</v>
       </c>
     </row>
   </sheetData>
@@ -1583,7 +1611,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F46"/>
+  <dimension ref="A1:F48"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.7109375" customWidth="1"/>
@@ -1603,12 +1631,47 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="3" t="s">
         <v>47</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
+      <c r="A3" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>56</v>
       </c>
     </row>
     <row r="5" spans="1:6">
       <c r="A5" s="2" t="s">
-        <v>48</v>
+        <v>57</v>
       </c>
       <c r="B5" s="2"/>
       <c r="C5" s="2"/>
@@ -1616,700 +1679,734 @@
       <c r="E5" s="2"/>
     </row>
     <row r="6" spans="1:6">
-      <c r="A6" s="4" t="s">
+      <c r="A6" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B6" s="4" t="s">
-        <v>49</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="D6" s="4" t="s">
-        <v>51</v>
-      </c>
-      <c r="E6" s="4" t="s">
-        <v>52</v>
+      <c r="B6" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>61</v>
       </c>
     </row>
     <row r="7" spans="1:6">
-      <c r="A7" s="3" t="s">
+      <c r="A7" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B7" s="3" t="s">
+      <c r="B7" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C7" s="5">
-        <v>-9.73</v>
-      </c>
-      <c r="D7" s="5">
+      <c r="C7" s="6">
         <v>-8.949999999999999</v>
       </c>
-      <c r="E7" s="6">
-        <v>0.78</v>
+      <c r="D7" s="6">
+        <v>-6.58</v>
+      </c>
+      <c r="E7" s="7">
+        <v>2.37</v>
       </c>
     </row>
     <row r="8" spans="1:6">
-      <c r="A8" s="3" t="s">
+      <c r="A8" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B8" s="3" t="s">
+      <c r="B8" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C8" s="5">
-        <v>-15.94</v>
-      </c>
-      <c r="D8" s="5">
+      <c r="C8" s="6">
         <v>-16.57</v>
       </c>
+      <c r="D8" s="6">
+        <v>-14.93</v>
+      </c>
       <c r="E8" s="7">
-        <v>-0.63</v>
+        <v>1.64</v>
       </c>
     </row>
     <row r="9" spans="1:6">
-      <c r="A9" s="3" t="s">
+      <c r="A9" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B9" s="3" t="s">
+      <c r="B9" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C9" s="5">
-        <v>-9.880000000000001</v>
-      </c>
-      <c r="D9" s="5">
+      <c r="C9" s="6">
         <v>-11.25</v>
       </c>
+      <c r="D9" s="6">
+        <v>-7.55</v>
+      </c>
       <c r="E9" s="7">
-        <v>-1.37</v>
+        <v>3.7</v>
       </c>
     </row>
     <row r="10" spans="1:6">
-      <c r="A10" s="3" t="s">
+      <c r="A10" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="B10" s="3" t="s">
+      <c r="B10" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C10" s="5">
-        <v>-9.369999999999999</v>
-      </c>
-      <c r="D10" s="5">
+      <c r="C10" s="6">
         <v>-6.71</v>
       </c>
-      <c r="E10" s="6">
-        <v>2.66</v>
+      <c r="D10" s="6">
+        <v>-4.58</v>
+      </c>
+      <c r="E10" s="7">
+        <v>2.13</v>
       </c>
     </row>
     <row r="11" spans="1:6">
-      <c r="A11" s="3" t="s">
+      <c r="A11" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B11" s="3" t="s">
+      <c r="B11" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C11" s="5">
-        <v>-6.69</v>
-      </c>
-      <c r="D11" s="5">
+      <c r="C11" s="6">
         <v>-3.45</v>
       </c>
-      <c r="E11" s="6">
-        <v>3.24</v>
+      <c r="D11" s="6">
+        <v>-5.99</v>
+      </c>
+      <c r="E11" s="8">
+        <v>-2.54</v>
       </c>
     </row>
     <row r="12" spans="1:6">
-      <c r="A12" s="3" t="s">
+      <c r="A12" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B12" s="3" t="s">
+      <c r="B12" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="C12" s="5">
-        <v>-3.87</v>
-      </c>
-      <c r="D12" s="5">
+      <c r="C12" s="6">
         <v>-1.29</v>
       </c>
-      <c r="E12" s="6">
-        <v>2.58</v>
+      <c r="D12" s="6">
+        <v>-0.71</v>
+      </c>
+      <c r="E12" s="7">
+        <v>0.58</v>
       </c>
     </row>
     <row r="13" spans="1:6">
-      <c r="A13" s="3" t="s">
+      <c r="A13" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B13" s="3" t="s">
+      <c r="B13" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="C13" s="5">
-        <v>-13.3</v>
-      </c>
-      <c r="D13" s="5">
+      <c r="C13" s="6">
         <v>-7.73</v>
       </c>
-      <c r="E13" s="6">
-        <v>5.57</v>
+      <c r="D13" s="6">
+        <v>-5.19</v>
+      </c>
+      <c r="E13" s="7">
+        <v>2.54</v>
       </c>
     </row>
     <row r="14" spans="1:6">
-      <c r="A14" s="3" t="s">
+      <c r="A14" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B14" s="3" t="s">
+      <c r="B14" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="C14" s="5">
-        <v>-3.83</v>
-      </c>
-      <c r="D14" s="5">
+      <c r="C14" s="6">
         <v>-4.01</v>
       </c>
+      <c r="D14" s="6">
+        <v>-0.1</v>
+      </c>
       <c r="E14" s="7">
-        <v>-0.18</v>
+        <v>3.91</v>
       </c>
     </row>
     <row r="15" spans="1:6">
-      <c r="A15" s="3" t="s">
+      <c r="A15" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="B15" s="3" t="s">
+      <c r="B15" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="C15" s="5">
-        <v>-3.46</v>
-      </c>
-      <c r="D15" s="5">
+      <c r="C15" s="6">
         <v>0.17</v>
       </c>
-      <c r="E15" s="6">
-        <v>3.63</v>
+      <c r="D15" s="6">
+        <v>2.06</v>
+      </c>
+      <c r="E15" s="7">
+        <v>1.89</v>
       </c>
     </row>
     <row r="16" spans="1:6">
-      <c r="A16" s="3" t="s">
+      <c r="A16" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B16" s="3" t="s">
+      <c r="B16" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="C16" s="5">
-        <v>-3.46</v>
-      </c>
-      <c r="D16" s="5">
+      <c r="C16" s="6">
         <v>2.44</v>
       </c>
-      <c r="E16" s="6">
-        <v>5.9</v>
+      <c r="D16" s="6">
+        <v>2.87</v>
+      </c>
+      <c r="E16" s="7">
+        <v>0.43</v>
       </c>
     </row>
     <row r="17" spans="1:5">
-      <c r="A17" s="3" t="s">
+      <c r="A17" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B17" s="3" t="s">
+      <c r="B17" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="C17" s="5">
-        <v>6.73</v>
-      </c>
-      <c r="D17" s="5">
+      <c r="C17" s="6">
         <v>7.6</v>
       </c>
-      <c r="E17" s="6">
-        <v>0.87</v>
+      <c r="D17" s="6">
+        <v>8.890000000000001</v>
+      </c>
+      <c r="E17" s="7">
+        <v>1.29</v>
       </c>
     </row>
     <row r="18" spans="1:5">
-      <c r="A18" s="3" t="s">
+      <c r="A18" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B18" s="3" t="s">
+      <c r="B18" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="C18" s="5">
-        <v>-9.84</v>
-      </c>
-      <c r="D18" s="5">
+      <c r="C18" s="6">
         <v>-8.15</v>
       </c>
-      <c r="E18" s="6">
-        <v>1.69</v>
+      <c r="D18" s="6">
+        <v>-8.44</v>
+      </c>
+      <c r="E18" s="8">
+        <v>-0.29</v>
       </c>
     </row>
     <row r="19" spans="1:5">
-      <c r="A19" s="3" t="s">
+      <c r="A19" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B19" s="3" t="s">
+      <c r="B19" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="C19" s="5">
-        <v>-31.25</v>
-      </c>
-      <c r="D19" s="5">
+      <c r="C19" s="6">
         <v>-33.34</v>
       </c>
-      <c r="E19" s="7">
-        <v>-2.09</v>
+      <c r="D19" s="6">
+        <v>-33.93</v>
+      </c>
+      <c r="E19" s="8">
+        <v>-0.59</v>
       </c>
     </row>
     <row r="20" spans="1:5">
-      <c r="A20" s="3" t="s">
+      <c r="A20" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="B20" s="3" t="s">
+      <c r="B20" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="C20" s="5">
-        <v>9.869999999999999</v>
-      </c>
-      <c r="D20" s="5">
+      <c r="C20" s="6">
         <v>12.03</v>
       </c>
-      <c r="E20" s="6">
-        <v>2.16</v>
+      <c r="D20" s="6">
+        <v>14.96</v>
+      </c>
+      <c r="E20" s="7">
+        <v>2.93</v>
       </c>
     </row>
     <row r="21" spans="1:5">
-      <c r="A21" s="3" t="s">
+      <c r="A21" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B21" s="3" t="s">
+      <c r="B21" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="C21" s="5">
-        <v>-23.48</v>
-      </c>
-      <c r="D21" s="5">
+      <c r="C21" s="6">
         <v>-25.22</v>
       </c>
-      <c r="E21" s="7">
-        <v>-1.74</v>
+      <c r="D21" s="6">
+        <v>-25.74</v>
+      </c>
+      <c r="E21" s="8">
+        <v>-0.52</v>
       </c>
     </row>
     <row r="22" spans="1:5">
-      <c r="A22" s="3" t="s">
+      <c r="A22" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B22" s="3" t="s">
+      <c r="B22" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="C22" s="5">
-        <v>-8.42</v>
-      </c>
-      <c r="D22" s="5">
+      <c r="C22" s="6">
         <v>-8.029999999999999</v>
       </c>
-      <c r="E22" s="6">
-        <v>0.39</v>
+      <c r="D22" s="6">
+        <v>-8.199999999999999</v>
+      </c>
+      <c r="E22" s="8">
+        <v>-0.17</v>
       </c>
     </row>
     <row r="23" spans="1:5">
-      <c r="A23" s="3" t="s">
+      <c r="A23" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B23" s="3" t="s">
+      <c r="B23" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="C23" s="5">
+      <c r="C23" s="6">
+        <v>-17.44</v>
+      </c>
+      <c r="D23" s="6">
+        <v>-15.81</v>
+      </c>
+      <c r="E23" s="7">
+        <v>1.63</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5">
+      <c r="A24" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B24" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C24" s="6">
+        <v>-20.61</v>
+      </c>
+      <c r="D24" s="6">
+        <v>-18.78</v>
+      </c>
+      <c r="E24" s="7">
+        <v>1.83</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5">
+      <c r="A25" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B25" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C25" s="6">
+        <v>-14.21</v>
+      </c>
+      <c r="D25" s="6">
+        <v>-14.25</v>
+      </c>
+      <c r="E25" s="8">
+        <v>-0.04</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
+      <c r="A26" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B26" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C26" s="6">
+        <v>11.01</v>
+      </c>
+      <c r="D26" s="6">
+        <v>6.36</v>
+      </c>
+      <c r="E26" s="8">
+        <v>-4.65</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5">
+      <c r="A27" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B27" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C27" s="6">
+        <v>-30.48</v>
+      </c>
+      <c r="D27" s="6">
+        <v>-30.41</v>
+      </c>
+      <c r="E27" s="7">
+        <v>0.07000000000000001</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5">
+      <c r="A28" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B28" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C28" s="6">
+        <v>-29.75</v>
+      </c>
+      <c r="D28" s="6">
+        <v>-29.32</v>
+      </c>
+      <c r="E28" s="7">
+        <v>0.43</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5">
+      <c r="A29" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B29" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C29" s="6">
+        <v>-37.41</v>
+      </c>
+      <c r="D29" s="6">
+        <v>-35.53</v>
+      </c>
+      <c r="E29" s="7">
+        <v>1.88</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5">
+      <c r="A30" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B30" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C30" s="6">
+        <v>-20.42</v>
+      </c>
+      <c r="D30" s="6">
+        <v>-18.83</v>
+      </c>
+      <c r="E30" s="7">
+        <v>1.59</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5">
+      <c r="A31" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B31" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C31" s="6">
+        <v>-25.44</v>
+      </c>
+      <c r="D31" s="6">
+        <v>-25.3</v>
+      </c>
+      <c r="E31" s="7">
+        <v>0.14</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5">
+      <c r="A32" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B32" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C32" s="6">
+        <v>144.85</v>
+      </c>
+      <c r="D32" s="6">
+        <v>145</v>
+      </c>
+      <c r="E32" s="7">
+        <v>0.15</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5">
+      <c r="A33" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B33" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C33" s="6">
+        <v>320.45</v>
+      </c>
+      <c r="D33" s="6">
+        <v>322.4</v>
+      </c>
+      <c r="E33" s="7">
+        <v>1.95</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5">
+      <c r="A34" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B34" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C34" s="6">
+        <v>334.25</v>
+      </c>
+      <c r="D34" s="6">
+        <v>344.25</v>
+      </c>
+      <c r="E34" s="7">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5">
+      <c r="A35" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B35" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C35" s="6">
+        <v>851</v>
+      </c>
+      <c r="D35" s="6">
+        <v>868</v>
+      </c>
+      <c r="E35" s="7">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5">
+      <c r="A36" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B36" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C36" s="6">
+        <v>2.52</v>
+      </c>
+      <c r="D36" s="6">
+        <v>2.51</v>
+      </c>
+      <c r="E36" s="8">
+        <v>-0.01</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5">
+      <c r="A37" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B37" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C37" s="6">
+        <v>99</v>
+      </c>
+      <c r="D37" s="6">
+        <v>80</v>
+      </c>
+      <c r="E37" s="8">
+        <v>-19</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5">
+      <c r="A38" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B38" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C38" s="6">
+        <v>80</v>
+      </c>
+      <c r="D38" s="6">
+        <v>99</v>
+      </c>
+      <c r="E38" s="7">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5">
+      <c r="A39" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B39" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C39" s="6">
+        <v>38.93</v>
+      </c>
+      <c r="D39" s="6">
+        <v>39.29</v>
+      </c>
+      <c r="E39" s="7">
+        <v>0.36</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5">
+      <c r="A40" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B40" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C40" s="6">
+        <v>31.94</v>
+      </c>
+      <c r="D40" s="6">
+        <v>33.12</v>
+      </c>
+      <c r="E40" s="7">
+        <v>1.18</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5">
+      <c r="A41" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B41" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C41" s="6">
+        <v>23.6</v>
+      </c>
+      <c r="D41" s="6">
+        <v>37.18</v>
+      </c>
+      <c r="E41" s="7">
+        <v>13.58</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5">
+      <c r="A42" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B42" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C42" s="6">
+        <v>39.72</v>
+      </c>
+      <c r="D42" s="6">
+        <v>45.27</v>
+      </c>
+      <c r="E42" s="7">
+        <v>5.55</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5">
+      <c r="A43" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B43" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C43" s="6">
+        <v>42.87</v>
+      </c>
+      <c r="D43" s="6">
+        <v>41.98</v>
+      </c>
+      <c r="E43" s="8">
+        <v>-0.89</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5">
+      <c r="A44" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B44" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C44" s="6">
+        <v>-7.89</v>
+      </c>
+      <c r="D44" s="6">
+        <v>-40.24</v>
+      </c>
+      <c r="E44" s="8">
+        <v>-32.35</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5">
+      <c r="A45" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B45" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C45" s="6">
+        <v>-55.38</v>
+      </c>
+      <c r="D45" s="6">
+        <v>-67.75</v>
+      </c>
+      <c r="E45" s="8">
+        <v>-12.37</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5">
+      <c r="A46" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B46" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C46" s="6">
+        <v>7.62</v>
+      </c>
+      <c r="D46" s="6">
+        <v>114.51</v>
+      </c>
+      <c r="E46" s="7">
+        <v>106.89</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5">
+      <c r="A47" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B47" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C47" s="6">
+        <v>-15.22</v>
+      </c>
+      <c r="D47" s="6">
         <v>-19.27</v>
       </c>
-      <c r="D23" s="5">
-        <v>-17.44</v>
-      </c>
-      <c r="E23" s="6">
-        <v>1.83</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5">
-      <c r="A24" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="B24" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C24" s="5">
-        <v>-20.12</v>
-      </c>
-      <c r="D24" s="5">
-        <v>-20.61</v>
-      </c>
-      <c r="E24" s="7">
-        <v>-0.49</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5">
-      <c r="A25" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="B25" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C25" s="5">
-        <v>-17.22</v>
-      </c>
-      <c r="D25" s="5">
-        <v>-14.21</v>
-      </c>
-      <c r="E25" s="6">
-        <v>3.01</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5">
-      <c r="A26" s="3" t="s">
+      <c r="E47" s="8">
+        <v>-4.05</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5">
+      <c r="A48" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B26" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C26" s="5">
-        <v>8.19</v>
-      </c>
-      <c r="D26" s="5">
-        <v>11.01</v>
-      </c>
-      <c r="E26" s="6">
-        <v>2.82</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5">
-      <c r="A27" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B27" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C27" s="5">
-        <v>-31.85</v>
-      </c>
-      <c r="D27" s="5">
-        <v>-30.48</v>
-      </c>
-      <c r="E27" s="6">
-        <v>1.37</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5">
-      <c r="A28" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="B28" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C28" s="5">
-        <v>-29.92</v>
-      </c>
-      <c r="D28" s="5">
-        <v>-29.75</v>
-      </c>
-      <c r="E28" s="6">
-        <v>0.17</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5">
-      <c r="A29" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="B29" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C29" s="5">
-        <v>-36.79</v>
-      </c>
-      <c r="D29" s="5">
-        <v>-37.41</v>
-      </c>
-      <c r="E29" s="7">
-        <v>-0.62</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5">
-      <c r="A30" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="B30" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C30" s="5">
-        <v>-22.07</v>
-      </c>
-      <c r="D30" s="5">
-        <v>-20.42</v>
-      </c>
-      <c r="E30" s="6">
-        <v>1.65</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5">
-      <c r="A31" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="B31" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C31" s="5">
-        <v>-25.74</v>
-      </c>
-      <c r="D31" s="5">
-        <v>-25.44</v>
-      </c>
-      <c r="E31" s="6">
-        <v>0.3</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5">
-      <c r="A32" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B32" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C32" s="5">
-        <v>142</v>
-      </c>
-      <c r="D32" s="5">
-        <v>144.85</v>
-      </c>
-      <c r="E32" s="6">
-        <v>2.85</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5">
-      <c r="A33" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="B33" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C33" s="5">
-        <v>319.65</v>
-      </c>
-      <c r="D33" s="5">
-        <v>320.45</v>
-      </c>
-      <c r="E33" s="6">
-        <v>0.8</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5">
-      <c r="A34" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="B34" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C34" s="5">
-        <v>337.55</v>
-      </c>
-      <c r="D34" s="5">
-        <v>334.25</v>
-      </c>
-      <c r="E34" s="7">
-        <v>-3.3</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5">
-      <c r="A35" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="B35" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C35" s="5">
-        <v>833.3</v>
-      </c>
-      <c r="D35" s="5">
-        <v>851</v>
-      </c>
-      <c r="E35" s="6">
-        <v>17.7</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5">
-      <c r="A36" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="B36" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C36" s="5">
-        <v>2.51</v>
-      </c>
-      <c r="D36" s="5">
-        <v>2.52</v>
-      </c>
-      <c r="E36" s="6">
-        <v>0.01</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5">
-      <c r="A37" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B37" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C37" s="5">
-        <v>31.83</v>
-      </c>
-      <c r="D37" s="5">
-        <v>38.93</v>
-      </c>
-      <c r="E37" s="6">
-        <v>7.1</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5">
-      <c r="A38" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="B38" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C38" s="5">
-        <v>31.47</v>
-      </c>
-      <c r="D38" s="5">
-        <v>31.94</v>
-      </c>
-      <c r="E38" s="6">
-        <v>0.47</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5">
-      <c r="A39" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="B39" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C39" s="5">
-        <v>25.27</v>
-      </c>
-      <c r="D39" s="5">
-        <v>23.6</v>
-      </c>
-      <c r="E39" s="7">
-        <v>-1.67</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5">
-      <c r="A40" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="B40" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C40" s="5">
-        <v>33.15</v>
-      </c>
-      <c r="D40" s="5">
-        <v>39.72</v>
-      </c>
-      <c r="E40" s="6">
-        <v>6.57</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5">
-      <c r="A41" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="B41" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C41" s="5">
-        <v>41.73</v>
-      </c>
-      <c r="D41" s="5">
-        <v>42.87</v>
-      </c>
-      <c r="E41" s="6">
-        <v>1.14</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5">
-      <c r="A42" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B42" s="3" t="s">
+      <c r="B48" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="C42" s="5">
-        <v>53.79</v>
-      </c>
-      <c r="D42" s="5">
-        <v>-7.89</v>
-      </c>
-      <c r="E42" s="7">
-        <v>-61.68</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5">
-      <c r="A43" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="B43" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C43" s="5">
-        <v>-65.64</v>
-      </c>
-      <c r="D43" s="5">
-        <v>-55.38</v>
-      </c>
-      <c r="E43" s="6">
-        <v>10.26</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5">
-      <c r="A44" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="B44" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C44" s="5">
-        <v>-13.82</v>
-      </c>
-      <c r="D44" s="5">
-        <v>7.62</v>
-      </c>
-      <c r="E44" s="6">
-        <v>21.44</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5">
-      <c r="A45" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="B45" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C45" s="5">
-        <v>24.28</v>
-      </c>
-      <c r="D45" s="5">
-        <v>-15.22</v>
-      </c>
-      <c r="E45" s="7">
-        <v>-39.5</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5">
-      <c r="A46" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="B46" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C46" s="5">
-        <v>-60.72</v>
-      </c>
-      <c r="D46" s="5">
+      <c r="C48" s="6">
         <v>-36.08</v>
       </c>
-      <c r="E46" s="6">
-        <v>24.64</v>
+      <c r="D48" s="6">
+        <v>-31.79</v>
+      </c>
+      <c r="E48" s="7">
+        <v>4.29</v>
       </c>
     </row>
   </sheetData>
@@ -2335,60 +2432,60 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="28" customHeight="1">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="8" t="s">
-        <v>53</v>
-      </c>
-      <c r="C1" s="8" t="s">
-        <v>54</v>
-      </c>
-      <c r="D1" s="8" t="s">
-        <v>55</v>
-      </c>
-      <c r="E1" s="8" t="s">
-        <v>56</v>
-      </c>
-      <c r="F1" s="8" t="s">
-        <v>57</v>
-      </c>
-      <c r="G1" s="8" t="s">
-        <v>58</v>
-      </c>
-      <c r="H1" s="8" t="s">
-        <v>59</v>
-      </c>
-      <c r="I1" s="8" t="s">
-        <v>60</v>
+      <c r="B1" s="9" t="s">
+        <v>62</v>
+      </c>
+      <c r="C1" s="9" t="s">
+        <v>63</v>
+      </c>
+      <c r="D1" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="E1" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="F1" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="G1" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="H1" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="I1" s="9" t="s">
+        <v>69</v>
       </c>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="9" t="s">
+      <c r="A2" s="10" t="s">
         <v>42</v>
       </c>
-      <c r="B2" s="10">
+      <c r="B2" s="11">
         <v>33.92</v>
       </c>
-      <c r="C2" s="11">
+      <c r="C2" s="12">
         <v>5</v>
       </c>
-      <c r="D2" s="10">
-        <v>35.4</v>
-      </c>
-      <c r="E2" s="10">
+      <c r="D2" s="11">
+        <v>39.4</v>
+      </c>
+      <c r="E2" s="11">
         <v>0</v>
       </c>
-      <c r="F2" s="10">
-        <v>-9.4</v>
-      </c>
-      <c r="G2" s="10">
-        <v>-9.9</v>
-      </c>
-      <c r="H2" s="10">
+      <c r="F2" s="11">
+        <v>-7.9</v>
+      </c>
+      <c r="G2" s="11">
+        <v>-10.1</v>
+      </c>
+      <c r="H2" s="11">
         <v>59.8</v>
       </c>
-      <c r="I2" s="10">
+      <c r="I2" s="11">
         <v>0</v>
       </c>
     </row>
@@ -2490,37 +2587,37 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
-      <c r="A1" s="12" t="s">
+      <c r="A1" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="B1" s="12" t="s">
+      <c r="B1" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="C1" s="12" t="s">
+      <c r="C1" s="13" t="s">
         <v>41</v>
       </c>
-      <c r="D1" s="12" t="s">
+      <c r="D1" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="E1" s="12" t="s">
+      <c r="E1" s="13" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="2" spans="1:5">
-      <c r="A2" s="13">
-        <v>0.1782</v>
-      </c>
-      <c r="B2" s="13">
-        <v>0.0162</v>
-      </c>
-      <c r="C2" s="13">
-        <v>-0.0187</v>
-      </c>
-      <c r="D2" s="13">
-        <v>-0.057</v>
-      </c>
-      <c r="E2" s="13">
-        <v>-0.2289</v>
+      <c r="A2" s="14">
+        <v>0.1766</v>
+      </c>
+      <c r="B2" s="14">
+        <v>0.019</v>
+      </c>
+      <c r="C2" s="14">
+        <v>-0.01</v>
+      </c>
+      <c r="D2" s="14">
+        <v>-0.0474</v>
+      </c>
+      <c r="E2" s="14">
+        <v>-0.2227</v>
       </c>
     </row>
   </sheetData>

--- a/HINDUJA_GROUP_Technical_Metrics.xlsx
+++ b/HINDUJA_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="222" uniqueCount="70">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="211" uniqueCount="61">
   <si>
     <t>Symbol</t>
   </si>
@@ -163,34 +163,7 @@
     <t>▶  SIGNAL EVENTS (vs Previous Run)</t>
   </si>
   <si>
-    <t>Signal</t>
-  </si>
-  <si>
-    <t>Change</t>
-  </si>
-  <si>
-    <t>Direction</t>
-  </si>
-  <si>
-    <t>Prev Value</t>
-  </si>
-  <si>
-    <t>Curr Value</t>
-  </si>
-  <si>
-    <t>RSI Oversold Recovery</t>
-  </si>
-  <si>
-    <t>23.6 → 37.2</t>
-  </si>
-  <si>
-    <t>🟢 BULLISH</t>
-  </si>
-  <si>
-    <t>23.6</t>
-  </si>
-  <si>
-    <t>37.2</t>
+    <t>No signal events detected since last run.</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -392,15 +365,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -916,10 +888,10 @@
         <v>42</v>
       </c>
       <c r="C2">
-        <v>145</v>
+        <v>144.82</v>
       </c>
       <c r="D2">
-        <v>0.1</v>
+        <v>-0.12</v>
       </c>
       <c r="E2">
         <v>208.37</v>
@@ -928,46 +900,46 @@
         <v>136.22</v>
       </c>
       <c r="G2">
-        <v>-30.41</v>
+        <v>-30.5</v>
       </c>
       <c r="H2">
-        <v>6.45</v>
+        <v>6.31</v>
       </c>
       <c r="I2">
-        <v>-0.71</v>
+        <v>-0.09</v>
       </c>
       <c r="J2">
-        <v>-6.58</v>
+        <v>-5.62</v>
       </c>
       <c r="K2">
-        <v>-8.199999999999999</v>
+        <v>-8.390000000000001</v>
       </c>
       <c r="L2">
-        <v>8.890000000000001</v>
+        <v>5.31</v>
       </c>
       <c r="M2">
-        <v>17.66</v>
+        <v>17.34</v>
       </c>
       <c r="N2">
-        <v>80</v>
+        <v>99</v>
       </c>
       <c r="O2">
         <v>64</v>
       </c>
       <c r="P2">
-        <v>143.74</v>
+        <v>143.71</v>
       </c>
       <c r="Q2">
-        <v>147.16</v>
+        <v>146.69</v>
       </c>
       <c r="R2">
-        <v>159.06</v>
+        <v>158.43</v>
       </c>
       <c r="S2">
-        <v>167.33</v>
+        <v>167.13</v>
       </c>
       <c r="T2">
-        <v>-13.34</v>
+        <v>-13.35</v>
       </c>
       <c r="U2" t="s">
         <v>43</v>
@@ -982,34 +954,34 @@
         <v>0</v>
       </c>
       <c r="Y2">
-        <v>39.29</v>
+        <v>39</v>
       </c>
       <c r="Z2">
-        <v>-4.01</v>
+        <v>-3.79</v>
       </c>
       <c r="AA2">
-        <v>-4.37</v>
+        <v>-4.25</v>
       </c>
       <c r="AB2">
-        <v>0.36</v>
+        <v>0.46</v>
       </c>
       <c r="AC2">
-        <v>66.81999999999999</v>
+        <v>86.69</v>
       </c>
       <c r="AD2">
-        <v>49.25</v>
+        <v>66.3</v>
       </c>
       <c r="AE2">
-        <v>3.88</v>
+        <v>3.94</v>
       </c>
       <c r="AF2">
-        <v>-40.24</v>
+        <v>-22.49</v>
       </c>
       <c r="AG2">
-        <v>154.18</v>
+        <v>152.94</v>
       </c>
       <c r="AH2">
-        <v>140.14</v>
+        <v>140.43</v>
       </c>
       <c r="AI2">
         <v>154.47</v>
@@ -1018,7 +990,7 @@
         <v>45</v>
       </c>
       <c r="AK2">
-        <v>53.22</v>
+        <v>48.27</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1029,10 +1001,10 @@
         <v>42</v>
       </c>
       <c r="C3">
-        <v>322.4</v>
+        <v>308.4</v>
       </c>
       <c r="D3">
-        <v>0.61</v>
+        <v>-4.34</v>
       </c>
       <c r="E3">
         <v>456.15</v>
@@ -1041,46 +1013,46 @@
         <v>225</v>
       </c>
       <c r="G3">
-        <v>-29.32</v>
+        <v>-32.39</v>
       </c>
       <c r="H3">
-        <v>43.29</v>
+        <v>37.07</v>
       </c>
       <c r="I3">
-        <v>-5.19</v>
+        <v>-4</v>
       </c>
       <c r="J3">
-        <v>-14.93</v>
+        <v>-15.19</v>
       </c>
       <c r="K3">
-        <v>-15.81</v>
+        <v>-20.45</v>
       </c>
       <c r="L3">
-        <v>-8.44</v>
+        <v>-15.97</v>
       </c>
       <c r="M3">
-        <v>1.9</v>
+        <v>0.32</v>
       </c>
       <c r="N3">
         <v>40</v>
       </c>
       <c r="O3">
-        <v>44</v>
+        <v>35</v>
       </c>
       <c r="P3">
-        <v>319.88</v>
+        <v>317.31</v>
       </c>
       <c r="Q3">
-        <v>348.54</v>
+        <v>345.83</v>
       </c>
       <c r="R3">
-        <v>385.55</v>
+        <v>383.68</v>
       </c>
       <c r="S3">
-        <v>343.08</v>
+        <v>343.22</v>
       </c>
       <c r="T3">
-        <v>-6.03</v>
+        <v>-10.15</v>
       </c>
       <c r="U3" t="s">
         <v>43</v>
@@ -1095,43 +1067,43 @@
         <v>1</v>
       </c>
       <c r="Y3">
-        <v>33.12</v>
+        <v>29.19</v>
       </c>
       <c r="Z3">
-        <v>-19.12</v>
+        <v>-20.02</v>
       </c>
       <c r="AA3">
-        <v>-16.77</v>
+        <v>-17.42</v>
       </c>
       <c r="AB3">
-        <v>-2.35</v>
+        <v>-2.6</v>
       </c>
       <c r="AC3">
-        <v>18.56</v>
+        <v>13.85</v>
       </c>
       <c r="AD3">
-        <v>11.72</v>
+        <v>14.26</v>
       </c>
       <c r="AE3">
         <v>15.69</v>
       </c>
       <c r="AF3">
-        <v>-67.75</v>
+        <v>-34.7</v>
       </c>
       <c r="AG3">
-        <v>386.27</v>
+        <v>386.96</v>
       </c>
       <c r="AH3">
-        <v>310.8</v>
+        <v>304.7</v>
       </c>
       <c r="AI3">
-        <v>368.83</v>
+        <v>361.13</v>
       </c>
       <c r="AJ3" t="s">
         <v>45</v>
       </c>
       <c r="AK3">
-        <v>33.01</v>
+        <v>35.58</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1142,58 +1114,58 @@
         <v>42</v>
       </c>
       <c r="C4">
-        <v>344.25</v>
+        <v>333.7</v>
       </c>
       <c r="D4">
-        <v>2.99</v>
+        <v>-3.06</v>
       </c>
       <c r="E4">
-        <v>534</v>
+        <v>530.25</v>
       </c>
       <c r="F4">
-        <v>334.25</v>
+        <v>333.7</v>
       </c>
       <c r="G4">
-        <v>-35.53</v>
+        <v>-37.07</v>
       </c>
       <c r="H4">
-        <v>2.99</v>
+        <v>0</v>
       </c>
       <c r="I4">
-        <v>-0.1</v>
+        <v>-1.26</v>
       </c>
       <c r="J4">
-        <v>-7.55</v>
+        <v>-8.84</v>
       </c>
       <c r="K4">
-        <v>-18.78</v>
+        <v>-21.58</v>
       </c>
       <c r="L4">
-        <v>-33.93</v>
+        <v>-37.51</v>
       </c>
       <c r="M4">
-        <v>-22.27</v>
+        <v>-22.93</v>
       </c>
       <c r="N4">
         <v>20</v>
       </c>
       <c r="O4">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="P4">
-        <v>337.75</v>
+        <v>336.9</v>
       </c>
       <c r="Q4">
-        <v>353.07</v>
+        <v>351.26</v>
       </c>
       <c r="R4">
-        <v>375.35</v>
+        <v>373.89</v>
       </c>
       <c r="S4">
-        <v>398.65</v>
+        <v>398.17</v>
       </c>
       <c r="T4">
-        <v>-13.65</v>
+        <v>-16.19</v>
       </c>
       <c r="U4" t="s">
         <v>43</v>
@@ -1208,34 +1180,34 @@
         <v>0</v>
       </c>
       <c r="Y4">
-        <v>37.18</v>
+        <v>30.93</v>
       </c>
       <c r="Z4">
-        <v>-10.96</v>
+        <v>-11.12</v>
       </c>
       <c r="AA4">
-        <v>-10.57</v>
+        <v>-10.68</v>
       </c>
       <c r="AB4">
-        <v>-0.39</v>
+        <v>-0.44</v>
       </c>
       <c r="AC4">
-        <v>47.98</v>
+        <v>59.53</v>
       </c>
       <c r="AD4">
-        <v>24.19</v>
+        <v>40.72</v>
       </c>
       <c r="AE4">
-        <v>10.45</v>
+        <v>10.81</v>
       </c>
       <c r="AF4">
-        <v>114.51</v>
+        <v>64</v>
       </c>
       <c r="AG4">
-        <v>375.19</v>
+        <v>373.47</v>
       </c>
       <c r="AH4">
-        <v>330.95</v>
+        <v>329.04</v>
       </c>
       <c r="AI4">
         <v>364.51</v>
@@ -1244,7 +1216,7 @@
         <v>45</v>
       </c>
       <c r="AK4">
-        <v>53.43</v>
+        <v>50.16</v>
       </c>
     </row>
     <row r="5" spans="1:37">
@@ -1255,10 +1227,10 @@
         <v>42</v>
       </c>
       <c r="C5">
-        <v>868</v>
+        <v>838</v>
       </c>
       <c r="D5">
-        <v>2</v>
+        <v>-3.46</v>
       </c>
       <c r="E5">
         <v>1069.3</v>
@@ -1267,46 +1239,46 @@
         <v>752.45</v>
       </c>
       <c r="G5">
-        <v>-18.83</v>
+        <v>-21.63</v>
       </c>
       <c r="H5">
-        <v>15.36</v>
+        <v>11.37</v>
       </c>
       <c r="I5">
-        <v>2.06</v>
+        <v>0.36</v>
       </c>
       <c r="J5">
-        <v>-4.58</v>
+        <v>-4.56</v>
       </c>
       <c r="K5">
-        <v>-14.25</v>
+        <v>-17.15</v>
       </c>
       <c r="L5">
-        <v>14.96</v>
+        <v>8.82</v>
       </c>
       <c r="M5">
-        <v>-4.74</v>
+        <v>-6.83</v>
       </c>
       <c r="N5">
-        <v>99</v>
+        <v>80</v>
       </c>
       <c r="O5">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="P5">
-        <v>846.36</v>
+        <v>846.96</v>
       </c>
       <c r="Q5">
-        <v>866.76</v>
+        <v>863.59</v>
       </c>
       <c r="R5">
-        <v>934.08</v>
+        <v>930.54</v>
       </c>
       <c r="S5">
-        <v>924.01</v>
+        <v>923.79</v>
       </c>
       <c r="T5">
-        <v>-6.06</v>
+        <v>-9.289999999999999</v>
       </c>
       <c r="U5" t="s">
         <v>43</v>
@@ -1321,34 +1293,34 @@
         <v>1</v>
       </c>
       <c r="Y5">
-        <v>45.27</v>
+        <v>38.52</v>
       </c>
       <c r="Z5">
-        <v>-23.68</v>
+        <v>-23.59</v>
       </c>
       <c r="AA5">
-        <v>-26.8</v>
+        <v>-26.16</v>
       </c>
       <c r="AB5">
-        <v>3.13</v>
+        <v>2.58</v>
       </c>
       <c r="AC5">
-        <v>72.95999999999999</v>
+        <v>81.27</v>
       </c>
       <c r="AD5">
-        <v>55.57</v>
+        <v>70.37</v>
       </c>
       <c r="AE5">
-        <v>22.87</v>
+        <v>23.52</v>
       </c>
       <c r="AF5">
-        <v>-19.27</v>
+        <v>-19.76</v>
       </c>
       <c r="AG5">
-        <v>907.41</v>
+        <v>902.72</v>
       </c>
       <c r="AH5">
-        <v>826.12</v>
+        <v>824.47</v>
       </c>
       <c r="AI5">
         <v>910.86</v>
@@ -1357,7 +1329,7 @@
         <v>45</v>
       </c>
       <c r="AK5">
-        <v>44</v>
+        <v>40.57</v>
       </c>
     </row>
     <row r="6" spans="1:37">
@@ -1368,43 +1340,43 @@
         <v>42</v>
       </c>
       <c r="C6">
-        <v>2.51</v>
+        <v>2.47</v>
       </c>
       <c r="D6">
-        <v>-0.4</v>
+        <v>-1.59</v>
       </c>
       <c r="E6">
-        <v>3.36</v>
+        <v>3.35</v>
       </c>
       <c r="F6">
         <v>1.84</v>
       </c>
       <c r="G6">
-        <v>-25.3</v>
+        <v>-26.27</v>
       </c>
       <c r="H6">
-        <v>36.41</v>
+        <v>34.24</v>
       </c>
       <c r="I6">
-        <v>2.87</v>
+        <v>-0.8</v>
       </c>
       <c r="J6">
-        <v>-5.99</v>
+        <v>-5.73</v>
       </c>
       <c r="K6">
-        <v>6.36</v>
+        <v>5.11</v>
       </c>
       <c r="L6">
-        <v>-25.74</v>
+        <v>-26.49</v>
       </c>
       <c r="M6">
-        <v>-1</v>
+        <v>-2.27</v>
       </c>
       <c r="N6">
         <v>60</v>
       </c>
       <c r="O6">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="P6">
         <v>2.51</v>
@@ -1413,13 +1385,13 @@
         <v>2.55</v>
       </c>
       <c r="R6">
-        <v>2.69</v>
+        <v>2.7</v>
       </c>
       <c r="S6">
         <v>2.62</v>
       </c>
       <c r="T6">
-        <v>-4.21</v>
+        <v>-5.65</v>
       </c>
       <c r="U6" t="s">
         <v>43</v>
@@ -1434,7 +1406,7 @@
         <v>1</v>
       </c>
       <c r="Y6">
-        <v>41.98</v>
+        <v>38.56</v>
       </c>
       <c r="Z6">
         <v>-0.05</v>
@@ -1446,22 +1418,22 @@
         <v>-0</v>
       </c>
       <c r="AC6">
-        <v>71.13</v>
+        <v>62.36</v>
       </c>
       <c r="AD6">
-        <v>68.84999999999999</v>
+        <v>68.7</v>
       </c>
       <c r="AE6">
         <v>0.13</v>
       </c>
       <c r="AF6">
-        <v>-31.79</v>
+        <v>61.5</v>
       </c>
       <c r="AG6">
-        <v>2.66</v>
+        <v>2.65</v>
       </c>
       <c r="AH6">
-        <v>2.45</v>
+        <v>2.44</v>
       </c>
       <c r="AI6">
         <v>2.81</v>
@@ -1470,7 +1442,7 @@
         <v>45</v>
       </c>
       <c r="AK6">
-        <v>38.63</v>
+        <v>35.22</v>
       </c>
     </row>
   </sheetData>
@@ -1574,27 +1546,27 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="U2:U6">
-    <cfRule type="containsText" dxfId="1" priority="14" operator="containsText" text="Yes">
-      <formula>NOT(ISERROR(SEARCH("Yes",U2)))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="0" priority="15" operator="containsText" text="No">
-      <formula>NOT(ISERROR(SEARCH("No",U2)))</formula>
+    <cfRule type="cellIs" dxfId="1" priority="16" operator="equal">
+      <formula>"Yes"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="0" priority="17" operator="equal">
+      <formula>"No"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V2:V6">
-    <cfRule type="containsText" dxfId="1" priority="16" operator="containsText" text="Yes">
-      <formula>NOT(ISERROR(SEARCH("Yes",V2)))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="0" priority="17" operator="containsText" text="No">
-      <formula>NOT(ISERROR(SEARCH("No",V2)))</formula>
+    <cfRule type="cellIs" dxfId="1" priority="18" operator="equal">
+      <formula>"Yes"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="0" priority="19" operator="equal">
+      <formula>"No"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="W2:W6">
-    <cfRule type="containsText" dxfId="1" priority="18" operator="containsText" text="Yes">
-      <formula>NOT(ISERROR(SEARCH("Yes",W2)))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="0" priority="19" operator="containsText" text="No">
-      <formula>NOT(ISERROR(SEARCH("No",W2)))</formula>
+    <cfRule type="cellIs" dxfId="1" priority="14" operator="equal">
+      <formula>"Yes"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="0" priority="15" operator="equal">
+      <formula>"No"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Y2:Y6">
@@ -1631,47 +1603,12 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" s="3" t="s">
         <v>47</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="D2" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="E2" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="F2" s="3" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6">
-      <c r="A3" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="B3" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="C3" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="D3" s="4" t="s">
-        <v>54</v>
-      </c>
-      <c r="E3" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="F3" s="4" t="s">
-        <v>56</v>
       </c>
     </row>
     <row r="5" spans="1:6">
       <c r="A5" s="2" t="s">
-        <v>57</v>
+        <v>48</v>
       </c>
       <c r="B5" s="2"/>
       <c r="C5" s="2"/>
@@ -1679,734 +1616,734 @@
       <c r="E5" s="2"/>
     </row>
     <row r="6" spans="1:6">
-      <c r="A6" s="3" t="s">
+      <c r="A6" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B6" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="E6" s="3" t="s">
-        <v>61</v>
+      <c r="B6" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="E6" s="4" t="s">
+        <v>52</v>
       </c>
     </row>
     <row r="7" spans="1:6">
-      <c r="A7" s="5" t="s">
+      <c r="A7" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B7" s="5" t="s">
+      <c r="B7" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C7" s="6">
-        <v>-8.949999999999999</v>
-      </c>
-      <c r="D7" s="6">
+      <c r="C7" s="5">
         <v>-6.58</v>
       </c>
-      <c r="E7" s="7">
-        <v>2.37</v>
+      <c r="D7" s="5">
+        <v>-5.62</v>
+      </c>
+      <c r="E7" s="6">
+        <v>0.96</v>
       </c>
     </row>
     <row r="8" spans="1:6">
-      <c r="A8" s="5" t="s">
+      <c r="A8" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B8" s="5" t="s">
+      <c r="B8" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C8" s="6">
-        <v>-16.57</v>
-      </c>
-      <c r="D8" s="6">
+      <c r="C8" s="5">
         <v>-14.93</v>
       </c>
+      <c r="D8" s="5">
+        <v>-15.19</v>
+      </c>
       <c r="E8" s="7">
-        <v>1.64</v>
+        <v>-0.26</v>
       </c>
     </row>
     <row r="9" spans="1:6">
-      <c r="A9" s="5" t="s">
+      <c r="A9" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B9" s="5" t="s">
+      <c r="B9" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C9" s="6">
-        <v>-11.25</v>
-      </c>
-      <c r="D9" s="6">
+      <c r="C9" s="5">
         <v>-7.55</v>
       </c>
+      <c r="D9" s="5">
+        <v>-8.84</v>
+      </c>
       <c r="E9" s="7">
-        <v>3.7</v>
+        <v>-1.29</v>
       </c>
     </row>
     <row r="10" spans="1:6">
-      <c r="A10" s="5" t="s">
+      <c r="A10" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="B10" s="5" t="s">
+      <c r="B10" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C10" s="6">
-        <v>-6.71</v>
-      </c>
-      <c r="D10" s="6">
+      <c r="C10" s="5">
         <v>-4.58</v>
       </c>
-      <c r="E10" s="7">
-        <v>2.13</v>
+      <c r="D10" s="5">
+        <v>-4.56</v>
+      </c>
+      <c r="E10" s="6">
+        <v>0.02</v>
       </c>
     </row>
     <row r="11" spans="1:6">
-      <c r="A11" s="5" t="s">
+      <c r="A11" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="B11" s="5" t="s">
+      <c r="B11" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C11" s="6">
-        <v>-3.45</v>
-      </c>
-      <c r="D11" s="6">
+      <c r="C11" s="5">
         <v>-5.99</v>
       </c>
-      <c r="E11" s="8">
-        <v>-2.54</v>
+      <c r="D11" s="5">
+        <v>-5.73</v>
+      </c>
+      <c r="E11" s="6">
+        <v>0.26</v>
       </c>
     </row>
     <row r="12" spans="1:6">
-      <c r="A12" s="5" t="s">
+      <c r="A12" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B12" s="5" t="s">
+      <c r="B12" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C12" s="6">
-        <v>-1.29</v>
-      </c>
-      <c r="D12" s="6">
+      <c r="C12" s="5">
         <v>-0.71</v>
       </c>
-      <c r="E12" s="7">
-        <v>0.58</v>
+      <c r="D12" s="5">
+        <v>-0.09</v>
+      </c>
+      <c r="E12" s="6">
+        <v>0.62</v>
       </c>
     </row>
     <row r="13" spans="1:6">
-      <c r="A13" s="5" t="s">
+      <c r="A13" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B13" s="5" t="s">
+      <c r="B13" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C13" s="6">
-        <v>-7.73</v>
-      </c>
-      <c r="D13" s="6">
+      <c r="C13" s="5">
         <v>-5.19</v>
       </c>
-      <c r="E13" s="7">
-        <v>2.54</v>
+      <c r="D13" s="5">
+        <v>-4</v>
+      </c>
+      <c r="E13" s="6">
+        <v>1.19</v>
       </c>
     </row>
     <row r="14" spans="1:6">
-      <c r="A14" s="5" t="s">
+      <c r="A14" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B14" s="5" t="s">
+      <c r="B14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C14" s="6">
-        <v>-4.01</v>
-      </c>
-      <c r="D14" s="6">
+      <c r="C14" s="5">
         <v>-0.1</v>
       </c>
+      <c r="D14" s="5">
+        <v>-1.26</v>
+      </c>
       <c r="E14" s="7">
-        <v>3.91</v>
+        <v>-1.16</v>
       </c>
     </row>
     <row r="15" spans="1:6">
-      <c r="A15" s="5" t="s">
+      <c r="A15" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="B15" s="5" t="s">
+      <c r="B15" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C15" s="6">
-        <v>0.17</v>
-      </c>
-      <c r="D15" s="6">
+      <c r="C15" s="5">
         <v>2.06</v>
       </c>
+      <c r="D15" s="5">
+        <v>0.36</v>
+      </c>
       <c r="E15" s="7">
-        <v>1.89</v>
+        <v>-1.7</v>
       </c>
     </row>
     <row r="16" spans="1:6">
-      <c r="A16" s="5" t="s">
+      <c r="A16" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="B16" s="5" t="s">
+      <c r="B16" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C16" s="6">
-        <v>2.44</v>
-      </c>
-      <c r="D16" s="6">
+      <c r="C16" s="5">
         <v>2.87</v>
       </c>
+      <c r="D16" s="5">
+        <v>-0.8</v>
+      </c>
       <c r="E16" s="7">
-        <v>0.43</v>
+        <v>-3.67</v>
       </c>
     </row>
     <row r="17" spans="1:5">
-      <c r="A17" s="5" t="s">
+      <c r="A17" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B17" s="5" t="s">
+      <c r="B17" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C17" s="6">
-        <v>7.6</v>
-      </c>
-      <c r="D17" s="6">
+      <c r="C17" s="5">
         <v>8.890000000000001</v>
       </c>
+      <c r="D17" s="5">
+        <v>5.31</v>
+      </c>
       <c r="E17" s="7">
-        <v>1.29</v>
+        <v>-3.58</v>
       </c>
     </row>
     <row r="18" spans="1:5">
-      <c r="A18" s="5" t="s">
+      <c r="A18" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B18" s="5" t="s">
+      <c r="B18" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C18" s="6">
-        <v>-8.15</v>
-      </c>
-      <c r="D18" s="6">
+      <c r="C18" s="5">
         <v>-8.44</v>
       </c>
-      <c r="E18" s="8">
+      <c r="D18" s="5">
+        <v>-15.97</v>
+      </c>
+      <c r="E18" s="7">
+        <v>-7.53</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C19" s="5">
+        <v>-33.93</v>
+      </c>
+      <c r="D19" s="5">
+        <v>-37.51</v>
+      </c>
+      <c r="E19" s="7">
+        <v>-3.58</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C20" s="5">
+        <v>14.96</v>
+      </c>
+      <c r="D20" s="5">
+        <v>8.82</v>
+      </c>
+      <c r="E20" s="7">
+        <v>-6.14</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C21" s="5">
+        <v>-25.74</v>
+      </c>
+      <c r="D21" s="5">
+        <v>-26.49</v>
+      </c>
+      <c r="E21" s="7">
+        <v>-0.75</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B22" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C22" s="5">
+        <v>-8.199999999999999</v>
+      </c>
+      <c r="D22" s="5">
+        <v>-8.390000000000001</v>
+      </c>
+      <c r="E22" s="7">
+        <v>-0.19</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B23" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C23" s="5">
+        <v>-15.81</v>
+      </c>
+      <c r="D23" s="5">
+        <v>-20.45</v>
+      </c>
+      <c r="E23" s="7">
+        <v>-4.64</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5">
+      <c r="A24" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B24" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C24" s="5">
+        <v>-18.78</v>
+      </c>
+      <c r="D24" s="5">
+        <v>-21.58</v>
+      </c>
+      <c r="E24" s="7">
+        <v>-2.8</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5">
+      <c r="A25" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B25" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C25" s="5">
+        <v>-14.25</v>
+      </c>
+      <c r="D25" s="5">
+        <v>-17.15</v>
+      </c>
+      <c r="E25" s="7">
+        <v>-2.9</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
+      <c r="A26" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B26" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C26" s="5">
+        <v>6.36</v>
+      </c>
+      <c r="D26" s="5">
+        <v>5.11</v>
+      </c>
+      <c r="E26" s="7">
+        <v>-1.25</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5">
+      <c r="A27" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B27" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C27" s="5">
+        <v>-30.41</v>
+      </c>
+      <c r="D27" s="5">
+        <v>-30.5</v>
+      </c>
+      <c r="E27" s="7">
+        <v>-0.09</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5">
+      <c r="A28" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B28" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C28" s="5">
+        <v>-29.32</v>
+      </c>
+      <c r="D28" s="5">
+        <v>-32.39</v>
+      </c>
+      <c r="E28" s="7">
+        <v>-3.07</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5">
+      <c r="A29" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B29" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C29" s="5">
+        <v>-35.53</v>
+      </c>
+      <c r="D29" s="5">
+        <v>-37.07</v>
+      </c>
+      <c r="E29" s="7">
+        <v>-1.54</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5">
+      <c r="A30" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B30" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C30" s="5">
+        <v>-18.83</v>
+      </c>
+      <c r="D30" s="5">
+        <v>-21.63</v>
+      </c>
+      <c r="E30" s="7">
+        <v>-2.8</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5">
+      <c r="A31" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B31" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C31" s="5">
+        <v>-25.3</v>
+      </c>
+      <c r="D31" s="5">
+        <v>-26.27</v>
+      </c>
+      <c r="E31" s="7">
+        <v>-0.97</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5">
+      <c r="A32" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B32" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C32" s="5">
+        <v>145</v>
+      </c>
+      <c r="D32" s="5">
+        <v>144.82</v>
+      </c>
+      <c r="E32" s="7">
+        <v>-0.18</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5">
+      <c r="A33" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B33" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C33" s="5">
+        <v>322.4</v>
+      </c>
+      <c r="D33" s="5">
+        <v>308.4</v>
+      </c>
+      <c r="E33" s="7">
+        <v>-14</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5">
+      <c r="A34" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B34" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C34" s="5">
+        <v>344.25</v>
+      </c>
+      <c r="D34" s="5">
+        <v>333.7</v>
+      </c>
+      <c r="E34" s="7">
+        <v>-10.55</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5">
+      <c r="A35" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B35" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C35" s="5">
+        <v>868</v>
+      </c>
+      <c r="D35" s="5">
+        <v>838</v>
+      </c>
+      <c r="E35" s="7">
+        <v>-30</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5">
+      <c r="A36" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B36" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C36" s="5">
+        <v>2.51</v>
+      </c>
+      <c r="D36" s="5">
+        <v>2.47</v>
+      </c>
+      <c r="E36" s="7">
+        <v>-0.04</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5">
+      <c r="A37" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B37" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C37" s="5">
+        <v>80</v>
+      </c>
+      <c r="D37" s="5">
+        <v>99</v>
+      </c>
+      <c r="E37" s="6">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5">
+      <c r="A38" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B38" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C38" s="5">
+        <v>99</v>
+      </c>
+      <c r="D38" s="5">
+        <v>80</v>
+      </c>
+      <c r="E38" s="7">
+        <v>-19</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5">
+      <c r="A39" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B39" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C39" s="5">
+        <v>39.29</v>
+      </c>
+      <c r="D39" s="5">
+        <v>39</v>
+      </c>
+      <c r="E39" s="7">
         <v>-0.29</v>
       </c>
     </row>
-    <row r="19" spans="1:5">
-      <c r="A19" s="5" t="s">
+    <row r="40" spans="1:5">
+      <c r="A40" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B40" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C40" s="5">
+        <v>33.12</v>
+      </c>
+      <c r="D40" s="5">
+        <v>29.19</v>
+      </c>
+      <c r="E40" s="7">
+        <v>-3.93</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5">
+      <c r="A41" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B19" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C19" s="6">
-        <v>-33.34</v>
-      </c>
-      <c r="D19" s="6">
-        <v>-33.93</v>
-      </c>
-      <c r="E19" s="8">
-        <v>-0.59</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5">
-      <c r="A20" s="5" t="s">
+      <c r="B41" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C41" s="5">
+        <v>37.18</v>
+      </c>
+      <c r="D41" s="5">
+        <v>30.93</v>
+      </c>
+      <c r="E41" s="7">
+        <v>-6.25</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5">
+      <c r="A42" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="B20" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C20" s="6">
-        <v>12.03</v>
-      </c>
-      <c r="D20" s="6">
-        <v>14.96</v>
-      </c>
-      <c r="E20" s="7">
-        <v>2.93</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5">
-      <c r="A21" s="5" t="s">
+      <c r="B42" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C42" s="5">
+        <v>45.27</v>
+      </c>
+      <c r="D42" s="5">
+        <v>38.52</v>
+      </c>
+      <c r="E42" s="7">
+        <v>-6.75</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5">
+      <c r="A43" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="B21" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C21" s="6">
-        <v>-25.22</v>
-      </c>
-      <c r="D21" s="6">
-        <v>-25.74</v>
-      </c>
-      <c r="E21" s="8">
-        <v>-0.52</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5">
-      <c r="A22" s="5" t="s">
+      <c r="B43" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C43" s="5">
+        <v>41.98</v>
+      </c>
+      <c r="D43" s="5">
+        <v>38.56</v>
+      </c>
+      <c r="E43" s="7">
+        <v>-3.42</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5">
+      <c r="A44" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B22" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C22" s="6">
-        <v>-8.029999999999999</v>
-      </c>
-      <c r="D22" s="6">
-        <v>-8.199999999999999</v>
-      </c>
-      <c r="E22" s="8">
-        <v>-0.17</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5">
-      <c r="A23" s="5" t="s">
+      <c r="B44" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C44" s="5">
+        <v>-40.24</v>
+      </c>
+      <c r="D44" s="5">
+        <v>-22.49</v>
+      </c>
+      <c r="E44" s="6">
+        <v>17.75</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5">
+      <c r="A45" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B23" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C23" s="6">
-        <v>-17.44</v>
-      </c>
-      <c r="D23" s="6">
-        <v>-15.81</v>
-      </c>
-      <c r="E23" s="7">
-        <v>1.63</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5">
-      <c r="A24" s="5" t="s">
+      <c r="B45" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C45" s="5">
+        <v>-67.75</v>
+      </c>
+      <c r="D45" s="5">
+        <v>-34.7</v>
+      </c>
+      <c r="E45" s="6">
+        <v>33.05</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5">
+      <c r="A46" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B24" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C24" s="6">
-        <v>-20.61</v>
-      </c>
-      <c r="D24" s="6">
-        <v>-18.78</v>
-      </c>
-      <c r="E24" s="7">
-        <v>1.83</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5">
-      <c r="A25" s="5" t="s">
+      <c r="B46" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C46" s="5">
+        <v>114.51</v>
+      </c>
+      <c r="D46" s="5">
+        <v>64</v>
+      </c>
+      <c r="E46" s="7">
+        <v>-50.51</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5">
+      <c r="A47" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="B25" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C25" s="6">
-        <v>-14.21</v>
-      </c>
-      <c r="D25" s="6">
-        <v>-14.25</v>
-      </c>
-      <c r="E25" s="8">
-        <v>-0.04</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5">
-      <c r="A26" s="5" t="s">
+      <c r="B47" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C47" s="5">
+        <v>-19.27</v>
+      </c>
+      <c r="D47" s="5">
+        <v>-19.76</v>
+      </c>
+      <c r="E47" s="7">
+        <v>-0.49</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5">
+      <c r="A48" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="B26" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C26" s="6">
-        <v>11.01</v>
-      </c>
-      <c r="D26" s="6">
-        <v>6.36</v>
-      </c>
-      <c r="E26" s="8">
-        <v>-4.65</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5">
-      <c r="A27" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B27" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C27" s="6">
-        <v>-30.48</v>
-      </c>
-      <c r="D27" s="6">
-        <v>-30.41</v>
-      </c>
-      <c r="E27" s="7">
-        <v>0.07000000000000001</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5">
-      <c r="A28" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B28" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C28" s="6">
-        <v>-29.75</v>
-      </c>
-      <c r="D28" s="6">
-        <v>-29.32</v>
-      </c>
-      <c r="E28" s="7">
-        <v>0.43</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5">
-      <c r="A29" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B29" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C29" s="6">
-        <v>-37.41</v>
-      </c>
-      <c r="D29" s="6">
-        <v>-35.53</v>
-      </c>
-      <c r="E29" s="7">
-        <v>1.88</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5">
-      <c r="A30" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B30" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C30" s="6">
-        <v>-20.42</v>
-      </c>
-      <c r="D30" s="6">
-        <v>-18.83</v>
-      </c>
-      <c r="E30" s="7">
-        <v>1.59</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5">
-      <c r="A31" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B31" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C31" s="6">
-        <v>-25.44</v>
-      </c>
-      <c r="D31" s="6">
-        <v>-25.3</v>
-      </c>
-      <c r="E31" s="7">
-        <v>0.14</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5">
-      <c r="A32" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B32" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C32" s="6">
-        <v>144.85</v>
-      </c>
-      <c r="D32" s="6">
-        <v>145</v>
-      </c>
-      <c r="E32" s="7">
-        <v>0.15</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5">
-      <c r="A33" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B33" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C33" s="6">
-        <v>320.45</v>
-      </c>
-      <c r="D33" s="6">
-        <v>322.4</v>
-      </c>
-      <c r="E33" s="7">
-        <v>1.95</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5">
-      <c r="A34" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B34" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C34" s="6">
-        <v>334.25</v>
-      </c>
-      <c r="D34" s="6">
-        <v>344.25</v>
-      </c>
-      <c r="E34" s="7">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5">
-      <c r="A35" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B35" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C35" s="6">
-        <v>851</v>
-      </c>
-      <c r="D35" s="6">
-        <v>868</v>
-      </c>
-      <c r="E35" s="7">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5">
-      <c r="A36" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B36" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C36" s="6">
-        <v>2.52</v>
-      </c>
-      <c r="D36" s="6">
-        <v>2.51</v>
-      </c>
-      <c r="E36" s="8">
-        <v>-0.01</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5">
-      <c r="A37" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B37" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="C37" s="6">
-        <v>99</v>
-      </c>
-      <c r="D37" s="6">
-        <v>80</v>
-      </c>
-      <c r="E37" s="8">
-        <v>-19</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5">
-      <c r="A38" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B38" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="C38" s="6">
-        <v>80</v>
-      </c>
-      <c r="D38" s="6">
-        <v>99</v>
-      </c>
-      <c r="E38" s="7">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5">
-      <c r="A39" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B39" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C39" s="6">
-        <v>38.93</v>
-      </c>
-      <c r="D39" s="6">
-        <v>39.29</v>
-      </c>
-      <c r="E39" s="7">
-        <v>0.36</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5">
-      <c r="A40" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B40" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C40" s="6">
-        <v>31.94</v>
-      </c>
-      <c r="D40" s="6">
-        <v>33.12</v>
-      </c>
-      <c r="E40" s="7">
-        <v>1.18</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5">
-      <c r="A41" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B41" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C41" s="6">
-        <v>23.6</v>
-      </c>
-      <c r="D41" s="6">
-        <v>37.18</v>
-      </c>
-      <c r="E41" s="7">
-        <v>13.58</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5">
-      <c r="A42" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B42" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C42" s="6">
-        <v>39.72</v>
-      </c>
-      <c r="D42" s="6">
-        <v>45.27</v>
-      </c>
-      <c r="E42" s="7">
-        <v>5.55</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5">
-      <c r="A43" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B43" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C43" s="6">
-        <v>42.87</v>
-      </c>
-      <c r="D43" s="6">
-        <v>41.98</v>
-      </c>
-      <c r="E43" s="8">
-        <v>-0.89</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5">
-      <c r="A44" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B44" s="5" t="s">
+      <c r="B48" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="C44" s="6">
-        <v>-7.89</v>
-      </c>
-      <c r="D44" s="6">
-        <v>-40.24</v>
-      </c>
-      <c r="E44" s="8">
-        <v>-32.35</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5">
-      <c r="A45" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B45" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C45" s="6">
-        <v>-55.38</v>
-      </c>
-      <c r="D45" s="6">
-        <v>-67.75</v>
-      </c>
-      <c r="E45" s="8">
-        <v>-12.37</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5">
-      <c r="A46" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B46" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C46" s="6">
-        <v>7.62</v>
-      </c>
-      <c r="D46" s="6">
-        <v>114.51</v>
-      </c>
-      <c r="E46" s="7">
-        <v>106.89</v>
-      </c>
-    </row>
-    <row r="47" spans="1:5">
-      <c r="A47" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B47" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C47" s="6">
-        <v>-15.22</v>
-      </c>
-      <c r="D47" s="6">
-        <v>-19.27</v>
-      </c>
-      <c r="E47" s="8">
-        <v>-4.05</v>
-      </c>
-    </row>
-    <row r="48" spans="1:5">
-      <c r="A48" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B48" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C48" s="6">
-        <v>-36.08</v>
-      </c>
-      <c r="D48" s="6">
+      <c r="C48" s="5">
         <v>-31.79</v>
       </c>
-      <c r="E48" s="7">
-        <v>4.29</v>
+      <c r="D48" s="5">
+        <v>61.5</v>
+      </c>
+      <c r="E48" s="6">
+        <v>93.29000000000001</v>
       </c>
     </row>
   </sheetData>
@@ -2432,60 +2369,60 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="28" customHeight="1">
-      <c r="A1" s="9" t="s">
+      <c r="A1" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="9" t="s">
-        <v>62</v>
-      </c>
-      <c r="C1" s="9" t="s">
-        <v>63</v>
-      </c>
-      <c r="D1" s="9" t="s">
-        <v>64</v>
-      </c>
-      <c r="E1" s="9" t="s">
-        <v>65</v>
-      </c>
-      <c r="F1" s="9" t="s">
-        <v>66</v>
-      </c>
-      <c r="G1" s="9" t="s">
-        <v>67</v>
-      </c>
-      <c r="H1" s="9" t="s">
-        <v>68</v>
-      </c>
-      <c r="I1" s="9" t="s">
-        <v>69</v>
+      <c r="B1" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="C1" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="D1" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="E1" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="F1" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="G1" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="H1" s="8" t="s">
+        <v>59</v>
+      </c>
+      <c r="I1" s="8" t="s">
+        <v>60</v>
       </c>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="10" t="s">
+      <c r="A2" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="B2" s="11">
-        <v>33.92</v>
-      </c>
-      <c r="C2" s="12">
+      <c r="B2" s="10">
+        <v>33.9</v>
+      </c>
+      <c r="C2" s="11">
         <v>5</v>
       </c>
-      <c r="D2" s="11">
-        <v>39.4</v>
-      </c>
-      <c r="E2" s="11">
+      <c r="D2" s="10">
+        <v>35.2</v>
+      </c>
+      <c r="E2" s="10">
         <v>0</v>
       </c>
-      <c r="F2" s="11">
-        <v>-7.9</v>
-      </c>
-      <c r="G2" s="11">
-        <v>-10.1</v>
-      </c>
-      <c r="H2" s="11">
+      <c r="F2" s="10">
+        <v>-8</v>
+      </c>
+      <c r="G2" s="10">
+        <v>-12.5</v>
+      </c>
+      <c r="H2" s="10">
         <v>59.8</v>
       </c>
-      <c r="I2" s="11">
+      <c r="I2" s="10">
         <v>0</v>
       </c>
     </row>
@@ -2587,37 +2524,37 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
-      <c r="A1" s="13" t="s">
+      <c r="A1" s="12" t="s">
         <v>37</v>
       </c>
-      <c r="B1" s="13" t="s">
+      <c r="B1" s="12" t="s">
         <v>38</v>
       </c>
-      <c r="C1" s="13" t="s">
+      <c r="C1" s="12" t="s">
         <v>41</v>
       </c>
-      <c r="D1" s="13" t="s">
+      <c r="D1" s="12" t="s">
         <v>40</v>
       </c>
-      <c r="E1" s="13" t="s">
+      <c r="E1" s="12" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="2" spans="1:5">
-      <c r="A2" s="14">
-        <v>0.1766</v>
-      </c>
-      <c r="B2" s="14">
-        <v>0.019</v>
-      </c>
-      <c r="C2" s="14">
-        <v>-0.01</v>
-      </c>
-      <c r="D2" s="14">
-        <v>-0.0474</v>
-      </c>
-      <c r="E2" s="14">
-        <v>-0.2227</v>
+      <c r="A2" s="13">
+        <v>0.1734</v>
+      </c>
+      <c r="B2" s="13">
+        <v>0.0032</v>
+      </c>
+      <c r="C2" s="13">
+        <v>-0.0227</v>
+      </c>
+      <c r="D2" s="13">
+        <v>-0.0683</v>
+      </c>
+      <c r="E2" s="13">
+        <v>-0.2293</v>
       </c>
     </row>
   </sheetData>
